--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72976970672607</t>
+    <t xml:space="preserve">4.72977018356323</t>
   </si>
   <si>
     <t xml:space="preserve">IGD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81178855895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76804447174072</t>
+    <t xml:space="preserve">4.81178903579712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76804494857788</t>
   </si>
   <si>
     <t xml:space="preserve">4.7653112411499</t>
@@ -56,13 +56,13 @@
     <t xml:space="preserve">4.64775037765503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53839159011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56573057174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67235660552979</t>
+    <t xml:space="preserve">4.53839111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56573152542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67235565185547</t>
   </si>
   <si>
     <t xml:space="preserve">4.55206108093262</t>
@@ -71,46 +71,46 @@
     <t xml:space="preserve">4.33334302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16383743286133</t>
+    <t xml:space="preserve">4.16383695602417</t>
   </si>
   <si>
     <t xml:space="preserve">4.04627704620361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60884141921997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88223814964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95605540275574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03807497024536</t>
+    <t xml:space="preserve">3.60884165763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88223791122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95605564117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0380744934082</t>
   </si>
   <si>
     <t xml:space="preserve">3.97519326210022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9478542804718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81388902664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96425724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07088232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92051386833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69632887840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78654932975769</t>
+    <t xml:space="preserve">3.94785356521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.813889503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96425747871399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07088279724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92051410675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69632840156555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78654885292053</t>
   </si>
   <si>
     <t xml:space="preserve">3.45573902130127</t>
@@ -119,25 +119,25 @@
     <t xml:space="preserve">3.49948239326477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69086027145386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56783199310303</t>
+    <t xml:space="preserve">3.69085955619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56783223152161</t>
   </si>
   <si>
     <t xml:space="preserve">3.63891506195068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88497233390808</t>
+    <t xml:space="preserve">3.88497257232666</t>
   </si>
   <si>
     <t xml:space="preserve">3.82755923271179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93691778182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87130236625671</t>
+    <t xml:space="preserve">3.93691730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87130331993103</t>
   </si>
   <si>
     <t xml:space="preserve">4.05994701385498</t>
@@ -146,43 +146,43 @@
     <t xml:space="preserve">4.00800085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95332145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98612999916077</t>
+    <t xml:space="preserve">3.95332169532776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98612952232361</t>
   </si>
   <si>
     <t xml:space="preserve">3.99159717559814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03260660171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05447816848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2403883934021</t>
+    <t xml:space="preserve">4.03260707855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05447864532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24038887023926</t>
   </si>
   <si>
     <t xml:space="preserve">4.21031475067139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37435293197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33607864379883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3470139503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33881187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42903327941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52745628356934</t>
+    <t xml:space="preserve">4.37435340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33607769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34701299667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33881235122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42903232574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52745580673218</t>
   </si>
   <si>
     <t xml:space="preserve">4.51105213165283</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">4.46184062957764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57119989395142</t>
+    <t xml:space="preserve">4.5711989402771</t>
   </si>
   <si>
     <t xml:space="preserve">4.67508983612061</t>
@@ -200,82 +200,82 @@
     <t xml:space="preserve">4.60947465896606</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54932737350464</t>
+    <t xml:space="preserve">4.54932689666748</t>
   </si>
   <si>
     <t xml:space="preserve">4.48371171951294</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34974765777588</t>
+    <t xml:space="preserve">4.34974813461304</t>
   </si>
   <si>
     <t xml:space="preserve">4.42083024978638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42356491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2649941444397</t>
+    <t xml:space="preserve">4.42356443405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26499462127686</t>
   </si>
   <si>
     <t xml:space="preserve">4.25405883789062</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22398519515991</t>
+    <t xml:space="preserve">4.22398471832275</t>
   </si>
   <si>
     <t xml:space="preserve">4.22671890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23765516281128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3306097984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40169334411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31967353820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30600452423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36615085601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26772785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32514238357544</t>
+    <t xml:space="preserve">4.23765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33060932159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40169286727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31967401504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30600357055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36615133285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26772832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32514190673828</t>
   </si>
   <si>
     <t xml:space="preserve">4.29233455657959</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27046251296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29506731033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39895820617676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30873775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38802242279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42629861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34427881240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39075756072998</t>
+    <t xml:space="preserve">4.27046203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29506826400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39895915985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30873823165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38802337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42629909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34428024291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39075708389282</t>
   </si>
   <si>
     <t xml:space="preserve">4.30326986312866</t>
@@ -284,25 +284,25 @@
     <t xml:space="preserve">4.49522352218628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57292556762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65062856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091844558716</t>
+    <t xml:space="preserve">4.57292652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65062808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69091892242432</t>
   </si>
   <si>
     <t xml:space="preserve">4.67940664291382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69379568099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66213989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61609363555908</t>
+    <t xml:space="preserve">4.69379663467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66213941574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61609315872192</t>
   </si>
   <si>
     <t xml:space="preserve">4.57580327987671</t>
@@ -311,31 +311,31 @@
     <t xml:space="preserve">4.63623857498169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63048267364502</t>
+    <t xml:space="preserve">4.63048315048218</t>
   </si>
   <si>
     <t xml:space="preserve">4.63336086273193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63911581039429</t>
+    <t xml:space="preserve">4.6391167640686</t>
   </si>
   <si>
     <t xml:space="preserve">4.56429243087769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35133075714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066608428955</t>
+    <t xml:space="preserve">4.35133028030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066560745239</t>
   </si>
   <si>
     <t xml:space="preserve">4.08368873596191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95130705833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9714527130127</t>
+    <t xml:space="preserve">3.95130753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97145223617554</t>
   </si>
   <si>
     <t xml:space="preserve">4.16139125823975</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">4.20168161392212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.247727394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27650594711304</t>
+    <t xml:space="preserve">4.24772644042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2765064239502</t>
   </si>
   <si>
     <t xml:space="preserve">4.03476524353027</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">3.82755875587463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8448269367218</t>
+    <t xml:space="preserve">3.84482645988464</t>
   </si>
   <si>
     <t xml:space="preserve">3.85633754730225</t>
@@ -368,16 +368,16 @@
     <t xml:space="preserve">4.15851354598999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01749801635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83619260787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96281862258911</t>
+    <t xml:space="preserve">4.01749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784887313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83619213104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96281790733337</t>
   </si>
   <si>
     <t xml:space="preserve">4.05778837203979</t>
@@ -389,34 +389,34 @@
     <t xml:space="preserve">4.25636053085327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40313243865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3340630531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51824617385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41752147674561</t>
+    <t xml:space="preserve">4.40313148498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33406352996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5182466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41752099990845</t>
   </si>
   <si>
     <t xml:space="preserve">4.45493316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37435340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45781135559082</t>
+    <t xml:space="preserve">4.4837121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45781183242798</t>
   </si>
   <si>
     <t xml:space="preserve">4.53839206695557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52975797653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48946809768677</t>
+    <t xml:space="preserve">4.52975749969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48946857452393</t>
   </si>
   <si>
     <t xml:space="preserve">4.51536798477173</t>
@@ -425,10 +425,10 @@
     <t xml:space="preserve">4.25923919677734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38874244689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46644449234009</t>
+    <t xml:space="preserve">4.38874292373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46644401550293</t>
   </si>
   <si>
     <t xml:space="preserve">4.38298654556274</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">4.41464328765869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35996341705322</t>
+    <t xml:space="preserve">4.35996389389038</t>
   </si>
   <si>
     <t xml:space="preserve">4.33694124221802</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29377317428589</t>
+    <t xml:space="preserve">4.29377269744873</t>
   </si>
   <si>
     <t xml:space="preserve">4.31391763687134</t>
@@ -458,10 +458,10 @@
     <t xml:space="preserve">4.19880390167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22182607650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26211595535278</t>
+    <t xml:space="preserve">4.22182655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2621169090271</t>
   </si>
   <si>
     <t xml:space="preserve">4.25348329544067</t>
@@ -476,49 +476,49 @@
     <t xml:space="preserve">4.19592571258545</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16714715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15563583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1153450012207</t>
+    <t xml:space="preserve">4.16714763641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15563535690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11534547805786</t>
   </si>
   <si>
     <t xml:space="preserve">4.20743656158447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14700174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17865800857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07505559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9426736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79878044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77575731277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83907055854797</t>
+    <t xml:space="preserve">4.14700126647949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1786584854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0750560760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94267392158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497139930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79878067970276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77575707435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83907032012939</t>
   </si>
   <si>
     <t xml:space="preserve">3.74697875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7498562335968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85921621322632</t>
+    <t xml:space="preserve">3.74985647201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85921597480774</t>
   </si>
   <si>
     <t xml:space="preserve">3.82468104362488</t>
@@ -530,28 +530,28 @@
     <t xml:space="preserve">3.87936091423035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81029152870178</t>
+    <t xml:space="preserve">3.81029200553894</t>
   </si>
   <si>
     <t xml:space="preserve">3.7843918800354</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76424551010132</t>
+    <t xml:space="preserve">3.76424622535706</t>
   </si>
   <si>
     <t xml:space="preserve">3.72971153259277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71244406700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72395610809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84194827079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735355377197</t>
+    <t xml:space="preserve">3.71244430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72395634651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84194779396057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735331535339</t>
   </si>
   <si>
     <t xml:space="preserve">4.06354379653931</t>
@@ -566,52 +566,52 @@
     <t xml:space="preserve">4.08656644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03764343261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00310897827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97432994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91389513015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93979549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92540621757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92828488349915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89662742614746</t>
+    <t xml:space="preserve">4.03764295578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00310945510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97433042526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91389536857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93979597091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92540669441223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92828440666199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89662766456604</t>
   </si>
   <si>
     <t xml:space="preserve">3.8477041721344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75273442268372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75849032402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55704021453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64337563514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66927599906921</t>
+    <t xml:space="preserve">3.75273466110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75849080085754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55703973770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64337515830994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66927623748779</t>
   </si>
   <si>
     <t xml:space="preserve">3.65776491165161</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58006262779236</t>
+    <t xml:space="preserve">3.5800621509552</t>
   </si>
   <si>
     <t xml:space="preserve">3.59733009338379</t>
@@ -620,34 +620,34 @@
     <t xml:space="preserve">3.6030855178833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63186478614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6261088848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66064286231995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61459755897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80453610420227</t>
+    <t xml:space="preserve">3.63186454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62610816955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66064357757568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61459708213806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80453634262085</t>
   </si>
   <si>
     <t xml:space="preserve">3.95994067192078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07217741012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04339981079102</t>
+    <t xml:space="preserve">4.07217693328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04339933395386</t>
   </si>
   <si>
     <t xml:space="preserve">4.12685680389404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13261222839355</t>
+    <t xml:space="preserve">4.13261270523071</t>
   </si>
   <si>
     <t xml:space="preserve">4.12110185623169</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">4.36859750747681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28226137161255</t>
+    <t xml:space="preserve">4.28226089477539</t>
   </si>
   <si>
     <t xml:space="preserve">4.33981895446777</t>
@@ -671,34 +671,37 @@
     <t xml:space="preserve">4.30240631103516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27074956893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22758293151855</t>
+    <t xml:space="preserve">4.27075004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2275824546814</t>
   </si>
   <si>
     <t xml:space="preserve">4.21319246292114</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18153667449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09807872772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00598621368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.103835105896</t>
+    <t xml:space="preserve">4.18153619766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09807825088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00598669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10383462905884</t>
   </si>
   <si>
     <t xml:space="preserve">4.02900981903076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06929922103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21894884109497</t>
+    <t xml:space="preserve">4.06930017471313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04627656936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21894836425781</t>
   </si>
   <si>
     <t xml:space="preserve">4.30816221237183</t>
@@ -707,10 +710,10 @@
     <t xml:space="preserve">4.14987993240356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47220134735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51249074935913</t>
+    <t xml:space="preserve">4.47220087051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51249027252197</t>
   </si>
   <si>
     <t xml:space="preserve">4.37723064422607</t>
@@ -719,7 +722,7 @@
     <t xml:space="preserve">4.44342231750488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59307098388672</t>
+    <t xml:space="preserve">4.59307050704956</t>
   </si>
   <si>
     <t xml:space="preserve">4.62472772598267</t>
@@ -728,34 +731,34 @@
     <t xml:space="preserve">4.5700478553772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71969747543335</t>
+    <t xml:space="preserve">4.71969652175903</t>
   </si>
   <si>
     <t xml:space="preserve">4.70818567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80315494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73120880126953</t>
+    <t xml:space="preserve">4.80315446853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73120832443237</t>
   </si>
   <si>
     <t xml:space="preserve">4.70530796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7024302482605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64487218856812</t>
+    <t xml:space="preserve">4.70242977142334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64487314224243</t>
   </si>
   <si>
     <t xml:space="preserve">4.62184953689575</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54702472686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52688026428223</t>
+    <t xml:space="preserve">4.54702520370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52687978744507</t>
   </si>
   <si>
     <t xml:space="preserve">4.46068906784058</t>
@@ -764,10 +767,10 @@
     <t xml:space="preserve">4.6045823097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71394109725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66501760482788</t>
+    <t xml:space="preserve">4.71394062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66501712799072</t>
   </si>
   <si>
     <t xml:space="preserve">4.74559783935547</t>
@@ -776,13 +779,13 @@
     <t xml:space="preserve">4.76574277877808</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74847555160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78301048278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77149868011475</t>
+    <t xml:space="preserve">4.74847602844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78300952911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77149772644043</t>
   </si>
   <si>
     <t xml:space="preserve">4.82329988479614</t>
@@ -791,16 +794,16 @@
     <t xml:space="preserve">4.92690277099609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94992589950562</t>
+    <t xml:space="preserve">4.94992685317993</t>
   </si>
   <si>
     <t xml:space="preserve">4.98446035385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02475118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0564079284668</t>
+    <t xml:space="preserve">5.02475070953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05640745162964</t>
   </si>
   <si>
     <t xml:space="preserve">4.89236879348755</t>
@@ -812,22 +815,22 @@
     <t xml:space="preserve">4.82905578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87592363357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9116005897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93538570404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89970827102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92052030563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01268720626831</t>
+    <t xml:space="preserve">4.8759241104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91160106658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93538618087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89970874786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9205207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01268672943115</t>
   </si>
   <si>
     <t xml:space="preserve">4.96809101104736</t>
@@ -851,58 +854,58 @@
     <t xml:space="preserve">4.88781642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85511159896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79862260818481</t>
+    <t xml:space="preserve">4.85511112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79862308502197</t>
   </si>
   <si>
     <t xml:space="preserve">4.77186441421509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75105333328247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78673028945923</t>
+    <t xml:space="preserve">4.75105237960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78672981262207</t>
   </si>
   <si>
     <t xml:space="preserve">4.73321437835693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66185903549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5340142250061</t>
+    <t xml:space="preserve">4.66185855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53401470184326</t>
   </si>
   <si>
     <t xml:space="preserve">4.58455753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61726188659668</t>
+    <t xml:space="preserve">4.61726236343384</t>
   </si>
   <si>
     <t xml:space="preserve">4.70348310470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72132205963135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63807439804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72726774215698</t>
+    <t xml:space="preserve">4.72132110595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63807344436646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72726726531982</t>
   </si>
   <si>
     <t xml:space="preserve">4.81646108627319</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83132648468018</t>
+    <t xml:space="preserve">4.83132696151733</t>
   </si>
   <si>
     <t xml:space="preserve">4.93835973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94430541992188</t>
+    <t xml:space="preserve">4.94430589675903</t>
   </si>
   <si>
     <t xml:space="preserve">4.98295640945435</t>
@@ -911,25 +914,25 @@
     <t xml:space="preserve">4.95322513580322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90565490722656</t>
+    <t xml:space="preserve">4.90565538406372</t>
   </si>
   <si>
     <t xml:space="preserve">4.84619283676147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89078903198242</t>
+    <t xml:space="preserve">4.89078950881958</t>
   </si>
   <si>
     <t xml:space="preserve">5.00376796722412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05431175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04836559295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99782133102417</t>
+    <t xml:space="preserve">5.05431127548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04836511611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99782180786133</t>
   </si>
   <si>
     <t xml:space="preserve">4.98592948913574</t>
@@ -941,22 +944,22 @@
     <t xml:space="preserve">5.12566661834717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11080074310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07512331008911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0810694694519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09593534469604</t>
+    <t xml:space="preserve">5.11080121994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07512283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08106994628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09593486785889</t>
   </si>
   <si>
     <t xml:space="preserve">5.11377382278442</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03944540023804</t>
+    <t xml:space="preserve">5.0394458770752</t>
   </si>
   <si>
     <t xml:space="preserve">5.02755308151245</t>
@@ -965,31 +968,31 @@
     <t xml:space="preserve">4.97700977325439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05133819580078</t>
+    <t xml:space="preserve">5.05133867263794</t>
   </si>
   <si>
     <t xml:space="preserve">4.99484872817993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01566171646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06620359420776</t>
+    <t xml:space="preserve">5.01566123962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06620454788208</t>
   </si>
   <si>
     <t xml:space="preserve">5.13755893707275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2326979637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2445912361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23864507675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19702196121216</t>
+    <t xml:space="preserve">5.23269939422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24459075927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23864555358887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.197021484375</t>
   </si>
   <si>
     <t xml:space="preserve">5.17323637008667</t>
@@ -1004,10 +1007,10 @@
     <t xml:space="preserve">5.1940484046936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24756479263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25053787231445</t>
+    <t xml:space="preserve">5.24756383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25053739547729</t>
   </si>
   <si>
     <t xml:space="preserve">5.26243019104004</t>
@@ -1016,16 +1019,16 @@
     <t xml:space="preserve">5.14945125579834</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16431713104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21485996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35162448883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44081735610962</t>
+    <t xml:space="preserve">5.16431665420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21485948562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35162401199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44081687927246</t>
   </si>
   <si>
     <t xml:space="preserve">5.64893627166748</t>
@@ -1034,19 +1037,19 @@
     <t xml:space="preserve">5.67866706848145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47054862976074</t>
+    <t xml:space="preserve">5.47054815292358</t>
   </si>
   <si>
     <t xml:space="preserve">5.46757507324219</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55974292755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59541988372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58947420120239</t>
+    <t xml:space="preserve">5.55974245071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59541940689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58947372436523</t>
   </si>
   <si>
     <t xml:space="preserve">5.50325298309326</t>
@@ -1058,13 +1061,13 @@
     <t xml:space="preserve">5.75002288818359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90165233612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91651821136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20193767547607</t>
+    <t xml:space="preserve">5.90165185928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91651773452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20193719863892</t>
   </si>
   <si>
     <t xml:space="preserve">6.19004535675049</t>
@@ -1073,7 +1076,7 @@
     <t xml:space="preserve">6.11274385452271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12463569641113</t>
+    <t xml:space="preserve">6.12463617324829</t>
   </si>
   <si>
     <t xml:space="preserve">6.15436792373657</t>
@@ -1085,13 +1088,13 @@
     <t xml:space="preserve">5.97598028182983</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8897590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0057110786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29113101959229</t>
+    <t xml:space="preserve">5.88975954055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00571155548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29113054275513</t>
   </si>
   <si>
     <t xml:space="preserve">6.3446478843689</t>
@@ -1100,16 +1103,16 @@
     <t xml:space="preserve">6.17815208435059</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39816379547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38627195358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33275508880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43384075164795</t>
+    <t xml:space="preserve">6.39816331863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38627099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33275413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43384027481079</t>
   </si>
   <si>
     <t xml:space="preserve">6.46951866149902</t>
@@ -1118,37 +1121,37 @@
     <t xml:space="preserve">6.41600275039673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40410947799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24356126785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35653972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44573450088501</t>
+    <t xml:space="preserve">6.40410900115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2435622215271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35654020309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44573402404785</t>
   </si>
   <si>
     <t xml:space="preserve">6.6003360748291</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5884428024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71926116943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65979814529419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48141098022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07111930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82732343673706</t>
+    <t xml:space="preserve">6.58844375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71926069259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65979862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48141050338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07111978530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82732391357422</t>
   </si>
   <si>
     <t xml:space="preserve">5.76786088943481</t>
@@ -1160,25 +1163,25 @@
     <t xml:space="preserve">5.68164014816284</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73812961578369</t>
+    <t xml:space="preserve">5.73812913894653</t>
   </si>
   <si>
     <t xml:space="preserve">5.81840419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72623634338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85705518722534</t>
+    <t xml:space="preserve">5.73218393325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72623729705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85705471038818</t>
   </si>
   <si>
     <t xml:space="preserve">5.86300134658813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95814037322998</t>
+    <t xml:space="preserve">5.95814180374146</t>
   </si>
   <si>
     <t xml:space="preserve">5.92841005325317</t>
@@ -1187,43 +1190,43 @@
     <t xml:space="preserve">5.76191520690918</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70839786529541</t>
+    <t xml:space="preserve">5.70839834213257</t>
   </si>
   <si>
     <t xml:space="preserve">5.79759216308594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75596809387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68461322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69650602340698</t>
+    <t xml:space="preserve">5.75596857070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6846137046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69650650024414</t>
   </si>
   <si>
     <t xml:space="preserve">5.66082859039307</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50622701644897</t>
+    <t xml:space="preserve">5.5062255859375</t>
   </si>
   <si>
     <t xml:space="preserve">5.45865678787231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33973073959351</t>
+    <t xml:space="preserve">5.33973121643066</t>
   </si>
   <si>
     <t xml:space="preserve">5.15539693832397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.31000089645386</t>
+    <t xml:space="preserve">5.3100004196167</t>
   </si>
   <si>
     <t xml:space="preserve">5.0364727973938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91754674911499</t>
+    <t xml:space="preserve">4.91754722595215</t>
   </si>
   <si>
     <t xml:space="preserve">5.00079536437988</t>
@@ -1232,37 +1235,37 @@
     <t xml:space="preserve">4.86997699737549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85213804244995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14350557327271</t>
+    <t xml:space="preserve">4.85213899612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14350509643555</t>
   </si>
   <si>
     <t xml:space="preserve">4.75699901580811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79446029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70824003219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58812570571899</t>
+    <t xml:space="preserve">4.79445934295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70823907852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58812522888184</t>
   </si>
   <si>
     <t xml:space="preserve">4.47752571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46860599517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53104162216187</t>
+    <t xml:space="preserve">4.46860551834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53104209899902</t>
   </si>
   <si>
     <t xml:space="preserve">4.66483163833618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66840028762817</t>
+    <t xml:space="preserve">4.66839981079102</t>
   </si>
   <si>
     <t xml:space="preserve">4.55482625961304</t>
@@ -1271,7 +1274,7 @@
     <t xml:space="preserve">4.49774217605591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51260805130005</t>
+    <t xml:space="preserve">4.51260757446289</t>
   </si>
   <si>
     <t xml:space="preserve">4.41211605072021</t>
@@ -1280,25 +1283,25 @@
     <t xml:space="preserve">4.36811399459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29913759231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48525524139404</t>
+    <t xml:space="preserve">4.29913806915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4852557182312</t>
   </si>
   <si>
     <t xml:space="preserve">4.46503782272339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44184732437134</t>
+    <t xml:space="preserve">4.4418478012085</t>
   </si>
   <si>
     <t xml:space="preserve">4.29378652572632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19210529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57336091995239</t>
+    <t xml:space="preserve">4.19210577011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57336044311523</t>
   </si>
   <si>
     <t xml:space="preserve">4.65459394454956</t>
@@ -1310,7 +1313,7 @@
     <t xml:space="preserve">4.85351896286011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95713949203491</t>
+    <t xml:space="preserve">4.95713901519775</t>
   </si>
   <si>
     <t xml:space="preserve">5.14391183853149</t>
@@ -1319,16 +1322,16 @@
     <t xml:space="preserve">5.34731388092041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28271102905273</t>
+    <t xml:space="preserve">5.28271055221558</t>
   </si>
   <si>
     <t xml:space="preserve">5.17781209945679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01278734207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96993160247803</t>
+    <t xml:space="preserve">5.01278686523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96993207931519</t>
   </si>
   <si>
     <t xml:space="preserve">5.05244445800781</t>
@@ -1346,34 +1349,34 @@
     <t xml:space="preserve">5.0159854888916</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02621984481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01470613479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08506488800049</t>
+    <t xml:space="preserve">5.0262188911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01470565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08506536483765</t>
   </si>
   <si>
     <t xml:space="preserve">4.93539190292358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92579793930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9654541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02557992935181</t>
+    <t xml:space="preserve">4.92579698562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96545505523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02557945251465</t>
   </si>
   <si>
     <t xml:space="preserve">5.04029130935669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02110290527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11704683303833</t>
+    <t xml:space="preserve">5.02110242843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11704635620117</t>
   </si>
   <si>
     <t xml:space="preserve">5.05947971343994</t>
@@ -1382,13 +1385,13 @@
     <t xml:space="preserve">5.06971406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24497318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14135313034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97888708114624</t>
+    <t xml:space="preserve">5.24497365951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14135265350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97888660430908</t>
   </si>
   <si>
     <t xml:space="preserve">4.76461029052734</t>
@@ -1397,22 +1400,22 @@
     <t xml:space="preserve">4.83496999740601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78124046325684</t>
+    <t xml:space="preserve">4.78124141693115</t>
   </si>
   <si>
     <t xml:space="preserve">4.73326873779297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71471929550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66290950775146</t>
+    <t xml:space="preserve">4.71471881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66290855407715</t>
   </si>
   <si>
     <t xml:space="preserve">4.55097341537476</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32710218429565</t>
+    <t xml:space="preserve">4.32710313796997</t>
   </si>
   <si>
     <t xml:space="preserve">4.57400035858154</t>
@@ -1421,7 +1424,7 @@
     <t xml:space="preserve">4.65267515182495</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63092708587646</t>
+    <t xml:space="preserve">4.63092756271362</t>
   </si>
   <si>
     <t xml:space="preserve">4.72943067550659</t>
@@ -1430,52 +1433,52 @@
     <t xml:space="preserve">4.81961822509766</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79403305053711</t>
+    <t xml:space="preserve">4.79403352737427</t>
   </si>
   <si>
     <t xml:space="preserve">4.68401670455933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58679246902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8741979598999</t>
+    <t xml:space="preserve">4.58679294586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87419843673706</t>
   </si>
   <si>
     <t xml:space="preserve">4.99108505249023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88932418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98421001434326</t>
+    <t xml:space="preserve">4.88932466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9842095375061</t>
   </si>
   <si>
     <t xml:space="preserve">5.03165197372437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79375219345093</t>
+    <t xml:space="preserve">4.79375267028809</t>
   </si>
   <si>
     <t xml:space="preserve">4.79512739181519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76074886322021</t>
+    <t xml:space="preserve">4.76074838638306</t>
   </si>
   <si>
     <t xml:space="preserve">4.74630975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86113452911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79031467437744</t>
+    <t xml:space="preserve">4.86113405227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79031419754028</t>
   </si>
   <si>
     <t xml:space="preserve">4.81300401687622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72705793380737</t>
+    <t xml:space="preserve">4.72705745697021</t>
   </si>
   <si>
     <t xml:space="preserve">4.77174997329712</t>
@@ -1490,7 +1493,7 @@
     <t xml:space="preserve">4.78687620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76968669891357</t>
+    <t xml:space="preserve">4.76968717575073</t>
   </si>
   <si>
     <t xml:space="preserve">4.91614007949829</t>
@@ -1511,13 +1514,13 @@
     <t xml:space="preserve">4.86044645309448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89963817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93470478057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99177312850952</t>
+    <t xml:space="preserve">4.89963865280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93470430374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99177360534668</t>
   </si>
   <si>
     <t xml:space="preserve">5.0543417930603</t>
@@ -1526,13 +1529,13 @@
     <t xml:space="preserve">4.96151971817017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97939682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99246025085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8583836555481</t>
+    <t xml:space="preserve">4.9793963432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99246072769165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85838413238525</t>
   </si>
   <si>
     <t xml:space="preserve">4.98489713668823</t>
@@ -1541,7 +1544,7 @@
     <t xml:space="preserve">4.85219621658325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90307664871216</t>
+    <t xml:space="preserve">4.90307569503784</t>
   </si>
   <si>
     <t xml:space="preserve">4.97183322906494</t>
@@ -1550,7 +1553,7 @@
     <t xml:space="preserve">4.93882989883423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91682720184326</t>
+    <t xml:space="preserve">4.91682767868042</t>
   </si>
   <si>
     <t xml:space="preserve">4.83363151550293</t>
@@ -1559,10 +1562,10 @@
     <t xml:space="preserve">4.76556158065796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75868654251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75043535232544</t>
+    <t xml:space="preserve">4.75868558883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75043487548828</t>
   </si>
   <si>
     <t xml:space="preserve">4.67067670822144</t>
@@ -1571,22 +1574,22 @@
     <t xml:space="preserve">4.58129262924194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54278802871704</t>
+    <t xml:space="preserve">4.5427885055542</t>
   </si>
   <si>
     <t xml:space="preserve">4.4630298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48228168487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51941061019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60604476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59779453277588</t>
+    <t xml:space="preserve">4.48228216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51941108703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60604524612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59779405593872</t>
   </si>
   <si>
     <t xml:space="preserve">4.52972412109375</t>
@@ -1595,7 +1598,7 @@
     <t xml:space="preserve">4.5379753112793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57922983169556</t>
+    <t xml:space="preserve">4.5792293548584</t>
   </si>
   <si>
     <t xml:space="preserve">4.55172681808472</t>
@@ -1607,34 +1610,34 @@
     <t xml:space="preserve">4.55241394042969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51597261428833</t>
+    <t xml:space="preserve">4.50634670257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51597356796265</t>
   </si>
   <si>
     <t xml:space="preserve">4.49053287506104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52078533172607</t>
+    <t xml:space="preserve">4.52078580856323</t>
   </si>
   <si>
     <t xml:space="preserve">4.518723487854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53041172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5104718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52491140365601</t>
+    <t xml:space="preserve">4.53041219711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51047229766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52491092681885</t>
   </si>
   <si>
     <t xml:space="preserve">4.485032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47746896743774</t>
+    <t xml:space="preserve">4.47746849060059</t>
   </si>
   <si>
     <t xml:space="preserve">4.78412628173828</t>
@@ -1643,10 +1646,10 @@
     <t xml:space="preserve">4.6651759147644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65417528152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70299243927002</t>
+    <t xml:space="preserve">4.6541748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70299291610718</t>
   </si>
   <si>
     <t xml:space="preserve">4.73049545288086</t>
@@ -1661,25 +1664,25 @@
     <t xml:space="preserve">4.63354778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5503511428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50840902328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41558790206909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42727661132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40046119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33239126205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22237968444824</t>
+    <t xml:space="preserve">4.55035161972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50840997695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41558742523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42727613449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40046072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3323917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2223801612854</t>
   </si>
   <si>
     <t xml:space="preserve">4.20450305938721</t>
@@ -1688,7 +1691,7 @@
     <t xml:space="preserve">4.16256046295166</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06630086898804</t>
+    <t xml:space="preserve">4.0663013458252</t>
   </si>
   <si>
     <t xml:space="preserve">4.09311628341675</t>
@@ -1700,10 +1703,10 @@
     <t xml:space="preserve">4.05942535400391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09724187850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0497989654541</t>
+    <t xml:space="preserve">4.09724140167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04979848861694</t>
   </si>
   <si>
     <t xml:space="preserve">4.05323696136475</t>
@@ -1715,13 +1718,13 @@
     <t xml:space="preserve">4.09105348587036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.088303565979</t>
+    <t xml:space="preserve">4.08830308914185</t>
   </si>
   <si>
     <t xml:space="preserve">4.13161993026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21962928771973</t>
+    <t xml:space="preserve">4.21962976455688</t>
   </si>
   <si>
     <t xml:space="preserve">4.28563594818115</t>
@@ -1736,22 +1739,22 @@
     <t xml:space="preserve">4.22100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15293455123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36608219146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27601003646851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22513008117676</t>
+    <t xml:space="preserve">4.15293502807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36608266830444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27601051330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2251296043396</t>
   </si>
   <si>
     <t xml:space="preserve">4.19487714767456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12749481201172</t>
+    <t xml:space="preserve">4.12749433517456</t>
   </si>
   <si>
     <t xml:space="preserve">4.15224742889404</t>
@@ -1763,97 +1766,97 @@
     <t xml:space="preserve">4.09174108505249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03260946273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03467273712158</t>
+    <t xml:space="preserve">4.0326099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03467226028442</t>
   </si>
   <si>
     <t xml:space="preserve">4.054612159729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14537143707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22375440597534</t>
+    <t xml:space="preserve">4.14537191390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2237548828125</t>
   </si>
   <si>
     <t xml:space="preserve">4.23544311523438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19900226593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1886887550354</t>
+    <t xml:space="preserve">4.19900274276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18868923187256</t>
   </si>
   <si>
     <t xml:space="preserve">4.1137433052063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04429817199707</t>
+    <t xml:space="preserve">4.04429864883423</t>
   </si>
   <si>
     <t xml:space="preserve">4.02917242050171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99273061752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99891829490662</t>
+    <t xml:space="preserve">3.99273109436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99891877174377</t>
   </si>
   <si>
     <t xml:space="preserve">3.96316528320312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88684439659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98241662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90540933609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87378025054932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78164625167847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71013879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69501233100891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73351621627808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72870278358459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64894485473633</t>
+    <t xml:space="preserve">3.88684463500977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.982417345047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90540885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87378072738647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78164601325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71013832092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69501209259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73351550102234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72870302200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64894509315491</t>
   </si>
   <si>
     <t xml:space="preserve">3.70051264762878</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83115196228027</t>
+    <t xml:space="preserve">3.83115100860596</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990830421448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9934184551239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97829174995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06286287307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.048424243927</t>
+    <t xml:space="preserve">3.99341821670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9782919883728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06286334991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04842376708984</t>
   </si>
   <si>
     <t xml:space="preserve">4.06767606735229</t>
@@ -1862,25 +1865,25 @@
     <t xml:space="preserve">4.04292345046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99548101425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95491456985474</t>
+    <t xml:space="preserve">3.99548077583313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95491433143616</t>
   </si>
   <si>
     <t xml:space="preserve">4.04086112976074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02160835266113</t>
+    <t xml:space="preserve">4.02160882949829</t>
   </si>
   <si>
     <t xml:space="preserve">4.05804967880249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01335763931274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97004079818726</t>
+    <t xml:space="preserve">4.0133581161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97004103660583</t>
   </si>
   <si>
     <t xml:space="preserve">4.07180118560791</t>
@@ -1895,40 +1898,40 @@
     <t xml:space="preserve">4.31864023208618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2890739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29044961929321</t>
+    <t xml:space="preserve">4.28907442092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29044914245605</t>
   </si>
   <si>
     <t xml:space="preserve">4.25057029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24919462203979</t>
+    <t xml:space="preserve">4.24919509887695</t>
   </si>
   <si>
     <t xml:space="preserve">4.26982259750366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26294660568237</t>
+    <t xml:space="preserve">4.26294612884521</t>
   </si>
   <si>
     <t xml:space="preserve">4.24231958389282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13643312454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05392456054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12543249130249</t>
+    <t xml:space="preserve">4.13643360137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05392408370972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12543201446533</t>
   </si>
   <si>
     <t xml:space="preserve">4.0896782875061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13230752944946</t>
+    <t xml:space="preserve">4.13230800628662</t>
   </si>
   <si>
     <t xml:space="preserve">4.17149925231934</t>
@@ -1937,58 +1940,58 @@
     <t xml:space="preserve">4.23819398880005</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22169256210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2189416885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21481609344482</t>
+    <t xml:space="preserve">4.22169160842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21894216537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21481657028198</t>
   </si>
   <si>
     <t xml:space="preserve">4.16324853897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28494834899902</t>
+    <t xml:space="preserve">4.28494930267334</t>
   </si>
   <si>
     <t xml:space="preserve">4.34476757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2540078163147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33720397949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37433338165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50359630584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57441663742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47609376907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44171476364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44859075546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55654001235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57785415649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60948276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66173791885376</t>
+    <t xml:space="preserve">4.25400829315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33720445632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37433385848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50359725952148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57441711425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47609424591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44171524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4485912322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55653953552246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5778546333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6094822883606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66173839569092</t>
   </si>
   <si>
     <t xml:space="preserve">4.60673236846924</t>
@@ -2000,13 +2003,13 @@
     <t xml:space="preserve">4.57166624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50772190093994</t>
+    <t xml:space="preserve">4.5077223777771</t>
   </si>
   <si>
     <t xml:space="preserve">4.45752906799316</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41971254348755</t>
+    <t xml:space="preserve">4.41971302032471</t>
   </si>
   <si>
     <t xml:space="preserve">4.46234226226807</t>
@@ -2015,22 +2018,22 @@
     <t xml:space="preserve">4.4279637336731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54485130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52422380447388</t>
+    <t xml:space="preserve">4.54485082626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52422428131104</t>
   </si>
   <si>
     <t xml:space="preserve">4.55860280990601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58610582351685</t>
+    <t xml:space="preserve">4.58610534667969</t>
   </si>
   <si>
     <t xml:space="preserve">4.45546674728394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48296976089478</t>
+    <t xml:space="preserve">4.48296928405762</t>
   </si>
   <si>
     <t xml:space="preserve">4.53109979629517</t>
@@ -2039,49 +2042,46 @@
     <t xml:space="preserve">4.56547784805298</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59985637664795</t>
+    <t xml:space="preserve">4.59985685348511</t>
   </si>
   <si>
     <t xml:space="preserve">4.64111089706421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61360836029053</t>
+    <t xml:space="preserve">4.61360788345337</t>
   </si>
   <si>
     <t xml:space="preserve">4.62048387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62735986709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7167444229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65486288070679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4967212677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55228900909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61179637908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54485082626343</t>
+    <t xml:space="preserve">4.62735939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71674394607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65486192703247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49672079086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5522894859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6117959022522</t>
   </si>
   <si>
     <t xml:space="preserve">4.60435819625854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62667274475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69361877441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73824834823608</t>
+    <t xml:space="preserve">4.62667322158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6936182975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73824882507324</t>
   </si>
   <si>
     <t xml:space="preserve">4.71593379974365</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">4.65642690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58948135375977</t>
+    <t xml:space="preserve">4.58948183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.51509761810303</t>
@@ -2102,16 +2102,16 @@
     <t xml:space="preserve">4.57460451126099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56716585159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55972719192505</t>
+    <t xml:space="preserve">4.56716537475586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55972814559937</t>
   </si>
   <si>
     <t xml:space="preserve">4.64898824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64155006408691</t>
+    <t xml:space="preserve">4.64154958724976</t>
   </si>
   <si>
     <t xml:space="preserve">4.5820426940918</t>
@@ -2123,61 +2123,61 @@
     <t xml:space="preserve">4.4481520652771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38120651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42583703994751</t>
+    <t xml:space="preserve">4.38120603561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42583656311035</t>
   </si>
   <si>
     <t xml:space="preserve">4.37376832962036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41839838027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35889196395874</t>
+    <t xml:space="preserve">4.4183988571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35889148712158</t>
   </si>
   <si>
     <t xml:space="preserve">4.32913827896118</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32169961929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31426048278809</t>
+    <t xml:space="preserve">4.32169914245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31426095962524</t>
   </si>
   <si>
     <t xml:space="preserve">4.33657646179199</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59691905975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50765895843506</t>
+    <t xml:space="preserve">4.59691953659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5076584815979</t>
   </si>
   <si>
     <t xml:space="preserve">4.49278211593628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48534393310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43327569961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40352153778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38864469528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39608335494995</t>
+    <t xml:space="preserve">4.48534440994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43327522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40352249145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38864517211914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39608287811279</t>
   </si>
   <si>
     <t xml:space="preserve">4.35145282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24731588363647</t>
+    <t xml:space="preserve">4.24731540679932</t>
   </si>
   <si>
     <t xml:space="preserve">4.20268535614014</t>
@@ -2186,7 +2186,7 @@
     <t xml:space="preserve">4.19524669647217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10598611831665</t>
+    <t xml:space="preserve">4.10598659515381</t>
   </si>
   <si>
     <t xml:space="preserve">4.13573980331421</t>
@@ -2195,34 +2195,34 @@
     <t xml:space="preserve">4.01672601699829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0241641998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93490362167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9051501750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95721864700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89771151542664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98697209358215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92002654075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94234228134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97953391075134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97209572792053</t>
+    <t xml:space="preserve">4.02416372299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93490409851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90514993667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95721888542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89771175384521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98697257041931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92002701759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94234180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97953414916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97209548950195</t>
   </si>
   <si>
     <t xml:space="preserve">4.04647970199585</t>
@@ -2231,46 +2231,46 @@
     <t xml:space="preserve">4.06879425048828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.098548412323</t>
+    <t xml:space="preserve">4.09854793548584</t>
   </si>
   <si>
     <t xml:space="preserve">4.16549348831177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18780899047852</t>
+    <t xml:space="preserve">4.18780851364136</t>
   </si>
   <si>
     <t xml:space="preserve">4.18037033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17293214797974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11342525482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14317798614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1283016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15805530548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03904104232788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23243856430054</t>
+    <t xml:space="preserve">4.17293167114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11342477798462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14317846298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12830114364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1580548286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03904056549072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2324390411377</t>
   </si>
   <si>
     <t xml:space="preserve">4.23987722396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26963043212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30682229995728</t>
+    <t xml:space="preserve">4.26963090896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30682277679443</t>
   </si>
   <si>
     <t xml:space="preserve">4.29194593429565</t>
@@ -2282,13 +2282,13 @@
     <t xml:space="preserve">4.27706909179688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29938411712646</t>
+    <t xml:space="preserve">4.29938459396362</t>
   </si>
   <si>
     <t xml:space="preserve">4.28450775146484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41096019744873</t>
+    <t xml:space="preserve">4.41095972061157</t>
   </si>
   <si>
     <t xml:space="preserve">4.44071340560913</t>
@@ -2300,13 +2300,13 @@
     <t xml:space="preserve">4.47046709060669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45558977127075</t>
+    <t xml:space="preserve">4.45559024810791</t>
   </si>
   <si>
     <t xml:space="preserve">4.6638650894165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74568796157837</t>
+    <t xml:space="preserve">4.74568748474121</t>
   </si>
   <si>
     <t xml:space="preserve">4.79031753540039</t>
@@ -2318,10 +2318,10 @@
     <t xml:space="preserve">4.67874193191528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61923503875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75312566757202</t>
+    <t xml:space="preserve">4.61923456192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75312519073486</t>
   </si>
   <si>
     <t xml:space="preserve">4.67130374908447</t>
@@ -2333,16 +2333,16 @@
     <t xml:space="preserve">4.72337198257446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68618059158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08367156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06135606765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96465730667114</t>
+    <t xml:space="preserve">4.68618011474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08367109298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06135559082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96465754508972</t>
   </si>
   <si>
     <t xml:space="preserve">3.92746543884277</t>
@@ -2354,25 +2354,25 @@
     <t xml:space="preserve">3.38446354866028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37702488899231</t>
+    <t xml:space="preserve">3.37702536582947</t>
   </si>
   <si>
     <t xml:space="preserve">2.7187283039093</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76335883140564</t>
+    <t xml:space="preserve">2.76335859298706</t>
   </si>
   <si>
     <t xml:space="preserve">2.54020714759827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57367968559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70385122299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64806365966797</t>
+    <t xml:space="preserve">2.57368016242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7038516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64806389808655</t>
   </si>
   <si>
     <t xml:space="preserve">2.77451610565186</t>
@@ -2390,25 +2390,25 @@
     <t xml:space="preserve">2.83402323722839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82658457756042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68525552749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78939294815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80426979064941</t>
+    <t xml:space="preserve">2.826584815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68525576591492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78939270973206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80426955223083</t>
   </si>
   <si>
     <t xml:space="preserve">2.75220108032227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70013236999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7150092124939</t>
+    <t xml:space="preserve">2.7001326084137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71500897407532</t>
   </si>
   <si>
     <t xml:space="preserve">2.76707792282104</t>
@@ -2420,16 +2420,16 @@
     <t xml:space="preserve">2.69641304016113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60343360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66294026374817</t>
+    <t xml:space="preserve">2.60343337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66294050216675</t>
   </si>
   <si>
     <t xml:space="preserve">2.69269394874573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62946796417236</t>
+    <t xml:space="preserve">2.62946772575378</t>
   </si>
   <si>
     <t xml:space="preserve">2.62574863433838</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">2.63318705558777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59227561950684</t>
+    <t xml:space="preserve">2.59227585792542</t>
   </si>
   <si>
     <t xml:space="preserve">2.55508399009705</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">2.45466589927673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42491245269775</t>
+    <t xml:space="preserve">2.42491221427917</t>
   </si>
   <si>
     <t xml:space="preserve">2.3951587677002</t>
@@ -2480,7 +2480,7 @@
     <t xml:space="preserve">2.25754880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44722723960876</t>
+    <t xml:space="preserve">2.44722747802734</t>
   </si>
   <si>
     <t xml:space="preserve">2.38400101661682</t>
@@ -2525,10 +2525,10 @@
     <t xml:space="preserve">2.52904963493347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51045370101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58483743667603</t>
+    <t xml:space="preserve">2.51045346260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58483719825745</t>
   </si>
   <si>
     <t xml:space="preserve">2.58111834526062</t>
@@ -2537,10 +2537,10 @@
     <t xml:space="preserve">2.59971404075623</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63690638542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68530678749084</t>
+    <t xml:space="preserve">2.63690614700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68530654907227</t>
   </si>
   <si>
     <t xml:space="preserve">2.66147232055664</t>
@@ -2552,16 +2552,16 @@
     <t xml:space="preserve">2.5740807056427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51846814155579</t>
+    <t xml:space="preserve">2.51846790313721</t>
   </si>
   <si>
     <t xml:space="preserve">2.46285510063171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45491003990173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42710399627686</t>
+    <t xml:space="preserve">2.45491027832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42710375785828</t>
   </si>
   <si>
     <t xml:space="preserve">2.51052331924438</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">2.47079968452454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49066138267517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53435754776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59791469573975</t>
+    <t xml:space="preserve">2.49066162109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53435730934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59791493415833</t>
   </si>
   <si>
     <t xml:space="preserve">2.55024671554565</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">2.5144956111908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48271679878235</t>
+    <t xml:space="preserve">2.48271703720093</t>
   </si>
   <si>
     <t xml:space="preserve">2.43902087211609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57010841369629</t>
+    <t xml:space="preserve">2.57010817527771</t>
   </si>
   <si>
     <t xml:space="preserve">2.49860620498657</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">2.391352891922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38340830802917</t>
+    <t xml:space="preserve">2.3834080696106</t>
   </si>
   <si>
     <t xml:space="preserve">2.39532518386841</t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">2.28409934043884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30793380737305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28807187080383</t>
+    <t xml:space="preserve">2.30793356895447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28807163238525</t>
   </si>
   <si>
     <t xml:space="preserve">2.25232076644897</t>
@@ -2678,19 +2678,19 @@
     <t xml:space="preserve">2.14506721496582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11328840255737</t>
+    <t xml:space="preserve">2.11328864097595</t>
   </si>
   <si>
     <t xml:space="preserve">2.05767560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96631169319153</t>
+    <t xml:space="preserve">1.96631157398224</t>
   </si>
   <si>
     <t xml:space="preserve">1.97822856903076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98220098018646</t>
+    <t xml:space="preserve">1.98220109939575</t>
   </si>
   <si>
     <t xml:space="preserve">2.08548212051392</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">2.09342670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0815098285675</t>
+    <t xml:space="preserve">2.08150959014893</t>
   </si>
   <si>
     <t xml:space="preserve">2.15301203727722</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">2.72900223731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71311283111572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88392376899719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8362557888031</t>
+    <t xml:space="preserve">2.7131130695343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88392400741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83625555038452</t>
   </si>
   <si>
     <t xml:space="preserve">2.81242156028748</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">2.70119595527649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82036638259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84420037269592</t>
+    <t xml:space="preserve">2.8203661441803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84420013427734</t>
   </si>
   <si>
     <t xml:space="preserve">2.86406207084656</t>
@@ -2753,22 +2753,22 @@
     <t xml:space="preserve">2.85611748695374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78461503982544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87200689315796</t>
+    <t xml:space="preserve">2.78461527824402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87200665473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.85214519500732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93556451797485</t>
+    <t xml:space="preserve">2.93556427955627</t>
   </si>
   <si>
     <t xml:space="preserve">2.96337080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87597894668579</t>
+    <t xml:space="preserve">2.87597918510437</t>
   </si>
   <si>
     <t xml:space="preserve">2.9514536857605</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">2.91967487335205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91173028945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78064298629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83228325843811</t>
+    <t xml:space="preserve">2.91173005104065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78064274787903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83228349685669</t>
   </si>
   <si>
     <t xml:space="preserve">2.94748163223267</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">2.95939826965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99912190437317</t>
+    <t xml:space="preserve">2.99912214279175</t>
   </si>
   <si>
     <t xml:space="preserve">2.96734309196472</t>
@@ -2834,16 +2834,16 @@
     <t xml:space="preserve">2.82433867454529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80844926834106</t>
+    <t xml:space="preserve">2.80844950675964</t>
   </si>
   <si>
     <t xml:space="preserve">2.89186859130859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90775775909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92364716529846</t>
+    <t xml:space="preserve">2.90775799751282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92364740371704</t>
   </si>
   <si>
     <t xml:space="preserve">2.98323249816895</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">3.30896496772766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17787742614746</t>
+    <t xml:space="preserve">3.17787766456604</t>
   </si>
   <si>
     <t xml:space="preserve">3.05473470687866</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">3.04281759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10637545585632</t>
+    <t xml:space="preserve">3.10637521743774</t>
   </si>
   <si>
     <t xml:space="preserve">3.02692818641663</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">2.84022808074951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79255986213684</t>
+    <t xml:space="preserve">2.79256010055542</t>
   </si>
   <si>
     <t xml:space="preserve">2.80050468444824</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">2.99514961242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15404367446899</t>
+    <t xml:space="preserve">3.15404343605042</t>
   </si>
   <si>
     <t xml:space="preserve">3.07459616661072</t>
@@ -2930,28 +2930,28 @@
     <t xml:space="preserve">3.13815426826477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0825412273407</t>
+    <t xml:space="preserve">3.08254098892212</t>
   </si>
   <si>
     <t xml:space="preserve">3.14609885215759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09843063354492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18582224845886</t>
+    <t xml:space="preserve">3.09843039512634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18582248687744</t>
   </si>
   <si>
     <t xml:space="preserve">3.13020944595337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25335192680359</t>
+    <t xml:space="preserve">3.25335216522217</t>
   </si>
   <si>
     <t xml:space="preserve">3.26924133300781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30102038383484</t>
+    <t xml:space="preserve">3.30102062225342</t>
   </si>
   <si>
     <t xml:space="preserve">3.3288266658783</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">3.29307556152344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23746252059937</t>
+    <t xml:space="preserve">3.23746228218079</t>
   </si>
   <si>
     <t xml:space="preserve">3.23349046707153</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">3.20568370819092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2136287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22554540634155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19773936271667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20171165466309</t>
+    <t xml:space="preserve">3.21362853050232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22554564476013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1977391242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20171189308167</t>
   </si>
   <si>
     <t xml:space="preserve">3.2652690410614</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">3.34471607208252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41224575042725</t>
+    <t xml:space="preserve">3.41224598884583</t>
   </si>
   <si>
     <t xml:space="preserve">3.40827345848083</t>
@@ -3014,10 +3014,10 @@
     <t xml:space="preserve">3.55922269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67044854164124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69031023979187</t>
+    <t xml:space="preserve">3.67044878005981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69031047821045</t>
   </si>
   <si>
     <t xml:space="preserve">3.69428277015686</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">3.66647601127625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63866949081421</t>
+    <t xml:space="preserve">3.63866925239563</t>
   </si>
   <si>
     <t xml:space="preserve">3.51949906349182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45594191551208</t>
+    <t xml:space="preserve">3.45594167709351</t>
   </si>
   <si>
     <t xml:space="preserve">3.52347159385681</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">3.49169278144836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40430116653442</t>
+    <t xml:space="preserve">3.40430092811584</t>
   </si>
   <si>
     <t xml:space="preserve">3.45196914672852</t>
@@ -3050,13 +3050,13 @@
     <t xml:space="preserve">3.44005250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34074354171753</t>
+    <t xml:space="preserve">3.34074378013611</t>
   </si>
   <si>
     <t xml:space="preserve">3.24540734291077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26129674911499</t>
+    <t xml:space="preserve">3.26129698753357</t>
   </si>
   <si>
     <t xml:space="preserve">3.33677101135254</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">3.22157311439514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30499267578125</t>
+    <t xml:space="preserve">3.30499243736267</t>
   </si>
   <si>
     <t xml:space="preserve">3.2811586856842</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">3.19376683235168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27718615531921</t>
+    <t xml:space="preserve">3.27718639373779</t>
   </si>
   <si>
     <t xml:space="preserve">3.36457800865173</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">3.16198825836182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07856893539429</t>
+    <t xml:space="preserve">3.07856869697571</t>
   </si>
   <si>
     <t xml:space="preserve">2.97131562232971</t>
@@ -3128,13 +3128,13 @@
     <t xml:space="preserve">2.99117732048035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.895840883255</t>
+    <t xml:space="preserve">2.89584064483643</t>
   </si>
   <si>
     <t xml:space="preserve">3.0189836025238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31293749809265</t>
+    <t xml:space="preserve">3.31293725967407</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596031188965</t>
@@ -3149,19 +3149,19 @@
     <t xml:space="preserve">3.18184995651245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17390513420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22951817512512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03884530067444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00309443473816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01103901863098</t>
+    <t xml:space="preserve">3.17390489578247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22951793670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03884553909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00309419631958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0110387802124</t>
   </si>
   <si>
     <t xml:space="preserve">3.05076217651367</t>
@@ -3173,16 +3173,16 @@
     <t xml:space="preserve">3.21760106086731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92761969566345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79653239250183</t>
+    <t xml:space="preserve">2.92761945724487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79653215408325</t>
   </si>
   <si>
     <t xml:space="preserve">2.87995147705078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98720502853394</t>
+    <t xml:space="preserve">2.98720479011536</t>
   </si>
   <si>
     <t xml:space="preserve">3.03487277030945</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">2.91570258140564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28513097763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36060547828674</t>
+    <t xml:space="preserve">3.28513121604919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36060523986816</t>
   </si>
   <si>
     <t xml:space="preserve">3.37649464607239</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">3.53141665458679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57908463478088</t>
+    <t xml:space="preserve">3.57908487319946</t>
   </si>
   <si>
     <t xml:space="preserve">3.42416310310364</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">3.40032911300659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39238405227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38443970680237</t>
+    <t xml:space="preserve">3.39238429069519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38443946838379</t>
   </si>
   <si>
     <t xml:space="preserve">3.46388673782349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48772025108337</t>
+    <t xml:space="preserve">3.48772048950195</t>
   </si>
   <si>
     <t xml:space="preserve">3.47183108329773</t>
@@ -3248,19 +3248,19 @@
     <t xml:space="preserve">3.55127787590027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63072514533997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59100151062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67442083358765</t>
+    <t xml:space="preserve">3.63072490692139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59100127220154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67442107200623</t>
   </si>
   <si>
     <t xml:space="preserve">3.61086344718933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62278032302856</t>
+    <t xml:space="preserve">3.62278008460999</t>
   </si>
   <si>
     <t xml:space="preserve">3.67839336395264</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">3.65058660507202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61880779266357</t>
+    <t xml:space="preserve">3.61880803108215</t>
   </si>
   <si>
     <t xml:space="preserve">3.6346971988678</t>
@@ -8811,7 +8811,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G144" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8837,7 +8837,7 @@
         <v>7.24187612533569</v>
       </c>
       <c r="G145" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -9149,7 +9149,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G157" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -12425,7 +12425,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G283" t="s">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12451,7 +12451,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G284" t="s">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12555,7 +12555,7 @@
         <v>6.81424283981323</v>
       </c>
       <c r="G288" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12633,7 +12633,7 @@
         <v>6.95833683013916</v>
       </c>
       <c r="G291" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12815,7 +12815,7 @@
         <v>6.70268678665161</v>
       </c>
       <c r="G298" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12867,7 +12867,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G300" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12945,7 +12945,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G303" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -12971,7 +12971,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G304" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -13101,7 +13101,7 @@
         <v>7.06989288330078</v>
       </c>
       <c r="G309" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13127,7 +13127,7 @@
         <v>7.17680215835571</v>
       </c>
       <c r="G310" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13179,7 +13179,7 @@
         <v>7.41850709915161</v>
       </c>
       <c r="G312" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13205,7 +13205,7 @@
         <v>7.46963787078857</v>
       </c>
       <c r="G313" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13257,7 +13257,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G315" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13309,7 +13309,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G317" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13335,7 +13335,7 @@
         <v>7.60443496704102</v>
       </c>
       <c r="G318" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13361,7 +13361,7 @@
         <v>7.75782489776611</v>
       </c>
       <c r="G319" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13387,7 +13387,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G320" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13439,7 +13439,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G322" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13465,7 +13465,7 @@
         <v>7.59978723526001</v>
       </c>
       <c r="G323" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13491,7 +13491,7 @@
         <v>7.59513902664185</v>
       </c>
       <c r="G324" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13595,7 +13595,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G328" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13621,7 +13621,7 @@
         <v>7.46498918533325</v>
       </c>
       <c r="G329" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13673,7 +13673,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G331" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13699,7 +13699,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G332" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13725,7 +13725,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G333" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13751,7 +13751,7 @@
         <v>7.311598777771</v>
       </c>
       <c r="G334" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13777,7 +13777,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G335" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13803,7 +13803,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G336" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13829,7 +13829,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G337" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13855,7 +13855,7 @@
         <v>7.53471183776855</v>
       </c>
       <c r="G338" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13881,7 +13881,7 @@
         <v>7.66486120223999</v>
       </c>
       <c r="G339" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13907,7 +13907,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G340" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13933,7 +13933,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G341" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -13959,7 +13959,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G342" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -13985,7 +13985,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G343" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -14011,7 +14011,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G344" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -14037,7 +14037,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G345" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -14063,7 +14063,7 @@
         <v>7.95769691467285</v>
       </c>
       <c r="G346" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -14089,7 +14089,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G347" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -14115,7 +14115,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G348" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14141,7 +14141,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G349" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14167,7 +14167,7 @@
         <v>8.16686630249023</v>
       </c>
       <c r="G350" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14193,7 +14193,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G351" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14219,7 +14219,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G352" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14245,7 +14245,7 @@
         <v>7.8554368019104</v>
       </c>
       <c r="G353" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14271,7 +14271,7 @@
         <v>7.79965877532959</v>
       </c>
       <c r="G354" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14297,7 +14297,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G355" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14323,7 +14323,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G356" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14349,7 +14349,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G357" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14375,7 +14375,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G358" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14401,7 +14401,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G359" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14427,7 +14427,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G360" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14453,7 +14453,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G361" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14479,7 +14479,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G362" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14505,7 +14505,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G363" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14531,7 +14531,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G364" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14557,7 +14557,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G365" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14583,7 +14583,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G366" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14609,7 +14609,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G367" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14635,7 +14635,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G368" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14661,7 +14661,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G369" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14687,7 +14687,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G370" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14713,7 +14713,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G371" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14739,7 +14739,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G372" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14765,7 +14765,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G373" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14791,7 +14791,7 @@
         <v>7.59048986434937</v>
       </c>
       <c r="G374" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14817,7 +14817,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G375" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14843,7 +14843,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G376" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14869,7 +14869,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G377" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14895,7 +14895,7 @@
         <v>7.4278039932251</v>
       </c>
       <c r="G378" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14921,7 +14921,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G379" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14947,7 +14947,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G380" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -14973,7 +14973,7 @@
         <v>7.39991521835327</v>
       </c>
       <c r="G381" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -14999,7 +14999,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G382" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -15025,7 +15025,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G383" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -15051,7 +15051,7 @@
         <v>7.16750478744507</v>
       </c>
       <c r="G384" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -15077,7 +15077,7 @@
         <v>7.21863508224487</v>
       </c>
       <c r="G385" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -15103,7 +15103,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G386" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15129,7 +15129,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G387" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15155,7 +15155,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G388" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15181,7 +15181,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G389" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15207,7 +15207,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G390" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15233,7 +15233,7 @@
         <v>7.59048986434937</v>
       </c>
       <c r="G391" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15259,7 +15259,7 @@
         <v>7.55330514907837</v>
       </c>
       <c r="G392" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15285,7 +15285,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G393" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15311,7 +15311,7 @@
         <v>7.72064018249512</v>
       </c>
       <c r="G394" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15337,7 +15337,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G395" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15363,7 +15363,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G396" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15389,7 +15389,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G397" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15415,7 +15415,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G398" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15441,7 +15441,7 @@
         <v>7.72993612289429</v>
       </c>
       <c r="G399" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15467,7 +15467,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G400" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15493,7 +15493,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G401" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15519,7 +15519,7 @@
         <v>7.74388122558594</v>
       </c>
       <c r="G402" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15545,7 +15545,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G403" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15571,7 +15571,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G404" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15597,7 +15597,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G405" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15623,7 +15623,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G406" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15649,7 +15649,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G407" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15675,7 +15675,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G408" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15701,7 +15701,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G409" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15727,7 +15727,7 @@
         <v>7.82289981842041</v>
       </c>
       <c r="G410" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15753,7 +15753,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G411" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15779,7 +15779,7 @@
         <v>7.89262294769287</v>
       </c>
       <c r="G412" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15805,7 +15805,7 @@
         <v>7.81360292434692</v>
       </c>
       <c r="G413" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15831,7 +15831,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G414" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15857,7 +15857,7 @@
         <v>7.79501104354858</v>
       </c>
       <c r="G415" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15883,7 +15883,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G416" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15909,7 +15909,7 @@
         <v>8.01347637176514</v>
       </c>
       <c r="G417" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15935,7 +15935,7 @@
         <v>7.99023485183716</v>
       </c>
       <c r="G418" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -15961,7 +15961,7 @@
         <v>7.93445587158203</v>
       </c>
       <c r="G419" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -15987,7 +15987,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G420" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -16013,7 +16013,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G421" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -16039,7 +16039,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G422" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -16065,7 +16065,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G423" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -16091,7 +16091,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G424" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -16117,7 +16117,7 @@
         <v>7.86008501052856</v>
       </c>
       <c r="G425" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -16143,7 +16143,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G426" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16169,7 +16169,7 @@
         <v>7.78106594085693</v>
       </c>
       <c r="G427" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16195,7 +16195,7 @@
         <v>7.89727115631104</v>
       </c>
       <c r="G428" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16221,7 +16221,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G429" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16247,7 +16247,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G430" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16273,7 +16273,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G431" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16299,7 +16299,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G432" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16325,7 +16325,7 @@
         <v>7.84149312973022</v>
       </c>
       <c r="G433" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16351,7 +16351,7 @@
         <v>7.92051219940186</v>
       </c>
       <c r="G434" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16377,7 +16377,7 @@
         <v>8.03206825256348</v>
       </c>
       <c r="G435" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16403,7 +16403,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G436" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16429,7 +16429,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G437" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16455,7 +16455,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G438" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16481,7 +16481,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G439" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16507,7 +16507,7 @@
         <v>8.19010734558105</v>
       </c>
       <c r="G440" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16533,7 +16533,7 @@
         <v>8.12503242492676</v>
       </c>
       <c r="G441" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16559,7 +16559,7 @@
         <v>8.08784675598145</v>
       </c>
       <c r="G442" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16585,7 +16585,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G443" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16611,7 +16611,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G444" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16637,7 +16637,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G445" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16663,7 +16663,7 @@
         <v>8.14362525939941</v>
       </c>
       <c r="G446" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16689,7 +16689,7 @@
         <v>8.12038421630859</v>
       </c>
       <c r="G447" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16715,7 +16715,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G448" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16741,7 +16741,7 @@
         <v>8.20869922637939</v>
       </c>
       <c r="G449" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16767,7 +16767,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G450" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16793,7 +16793,7 @@
         <v>8.22729206085205</v>
       </c>
       <c r="G451" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16819,7 +16819,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G452" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16845,7 +16845,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G453" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16871,7 +16871,7 @@
         <v>8.07390213012695</v>
       </c>
       <c r="G454" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16897,7 +16897,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G455" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16923,7 +16923,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G456" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16949,7 +16949,7 @@
         <v>8.36673831939697</v>
       </c>
       <c r="G457" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -16975,7 +16975,7 @@
         <v>8.50618267059326</v>
       </c>
       <c r="G458" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -17001,7 +17001,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G459" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -17027,7 +17027,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G460" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -17053,7 +17053,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -17079,7 +17079,7 @@
         <v>8.5526647567749</v>
       </c>
       <c r="G462" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -17105,7 +17105,7 @@
         <v>8.54801654815674</v>
       </c>
       <c r="G463" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -17131,7 +17131,7 @@
         <v>8.69211101531982</v>
       </c>
       <c r="G464" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -17157,7 +17157,7 @@
         <v>8.74788856506348</v>
       </c>
       <c r="G465" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -17183,7 +17183,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G466" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17209,7 +17209,7 @@
         <v>8.60379505157471</v>
       </c>
       <c r="G467" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17235,7 +17235,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G468" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17261,7 +17261,7 @@
         <v>8.98959541320801</v>
       </c>
       <c r="G469" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17287,7 +17287,7 @@
         <v>9.22665309906006</v>
       </c>
       <c r="G470" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17313,7 +17313,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G471" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17339,7 +17339,7 @@
         <v>9.696120262146</v>
       </c>
       <c r="G472" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17365,7 +17365,7 @@
         <v>9.67752742767334</v>
       </c>
       <c r="G473" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17391,7 +17391,7 @@
         <v>9.55667400360107</v>
       </c>
       <c r="G474" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17417,7 +17417,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G475" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17443,7 +17443,7 @@
         <v>9.62174892425537</v>
       </c>
       <c r="G476" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17469,7 +17469,7 @@
         <v>9.43582057952881</v>
       </c>
       <c r="G477" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17495,7 +17495,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G478" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17521,7 +17521,7 @@
         <v>9.34285736083984</v>
       </c>
       <c r="G479" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17547,7 +17547,7 @@
         <v>9.2080602645874</v>
       </c>
       <c r="G480" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17573,7 +17573,7 @@
         <v>9.38933944702148</v>
       </c>
       <c r="G481" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17599,7 +17599,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G482" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17625,7 +17625,7 @@
         <v>9.91923332214355</v>
       </c>
       <c r="G483" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17651,7 +17651,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G484" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17677,7 +17677,7 @@
         <v>9.65893363952637</v>
       </c>
       <c r="G485" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17703,7 +17703,7 @@
         <v>10.0029001235962</v>
       </c>
       <c r="G486" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17729,7 +17729,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G487" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17755,7 +17755,7 @@
         <v>9.90063953399658</v>
       </c>
       <c r="G488" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17781,7 +17781,7 @@
         <v>10.0586776733398</v>
       </c>
       <c r="G489" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17807,7 +17807,7 @@
         <v>10.1144561767578</v>
       </c>
       <c r="G490" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17833,7 +17833,7 @@
         <v>10.0307893753052</v>
       </c>
       <c r="G491" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17859,7 +17859,7 @@
         <v>10.0121955871582</v>
       </c>
       <c r="G492" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17885,7 +17885,7 @@
         <v>9.76119422912598</v>
       </c>
       <c r="G493" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17911,7 +17911,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G494" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17937,7 +17937,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G495" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -17963,7 +17963,7 @@
         <v>9.93782520294189</v>
       </c>
       <c r="G496" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -17989,7 +17989,7 @@
         <v>10.0772714614868</v>
       </c>
       <c r="G497" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -18015,7 +18015,7 @@
         <v>10.318977355957</v>
       </c>
       <c r="G498" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -18041,7 +18041,7 @@
         <v>10.3003835678101</v>
       </c>
       <c r="G499" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -18067,7 +18067,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G500" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -18093,7 +18093,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G501" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -18119,7 +18119,7 @@
         <v>10.411940574646</v>
       </c>
       <c r="G502" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18145,7 +18145,7 @@
         <v>10.1330490112305</v>
       </c>
       <c r="G503" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18171,7 +18171,7 @@
         <v>9.49159908294678</v>
       </c>
       <c r="G504" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18197,7 +18197,7 @@
         <v>9.11044788360596</v>
       </c>
       <c r="G505" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18223,7 +18223,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G506" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18249,7 +18249,7 @@
         <v>9.08255863189697</v>
       </c>
       <c r="G507" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18275,7 +18275,7 @@
         <v>8.88268661499023</v>
       </c>
       <c r="G508" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18301,7 +18301,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G509" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18327,7 +18327,7 @@
         <v>9.09650325775146</v>
       </c>
       <c r="G510" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18353,7 +18353,7 @@
         <v>8.96170616149902</v>
       </c>
       <c r="G511" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18379,7 +18379,7 @@
         <v>8.95240879058838</v>
       </c>
       <c r="G512" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18405,7 +18405,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G513" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18431,7 +18431,7 @@
         <v>9.1569299697876</v>
       </c>
       <c r="G514" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18457,7 +18457,7 @@
         <v>9.16622638702393</v>
       </c>
       <c r="G515" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18483,7 +18483,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G516" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18509,7 +18509,7 @@
         <v>9.31496810913086</v>
       </c>
       <c r="G517" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18535,7 +18535,7 @@
         <v>9.26848602294922</v>
       </c>
       <c r="G518" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18561,7 +18561,7 @@
         <v>9.00818824768066</v>
       </c>
       <c r="G519" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18587,7 +18587,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G520" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18613,7 +18613,7 @@
         <v>9.06396579742432</v>
       </c>
       <c r="G521" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18639,7 +18639,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G522" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18665,7 +18665,7 @@
         <v>8.8873348236084</v>
       </c>
       <c r="G523" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18691,7 +18691,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G524" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18717,7 +18717,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G525" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18743,7 +18743,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G526" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18769,7 +18769,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G527" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18795,7 +18795,7 @@
         <v>8.90592765808105</v>
       </c>
       <c r="G528" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18821,7 +18821,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18847,7 +18847,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G530" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18873,7 +18873,7 @@
         <v>8.85014915466309</v>
       </c>
       <c r="G531" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18899,7 +18899,7 @@
         <v>8.60844421386719</v>
       </c>
       <c r="G532" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18925,7 +18925,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G533" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18951,7 +18951,7 @@
         <v>8.53407287597656</v>
       </c>
       <c r="G534" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -18977,7 +18977,7 @@
         <v>8.34814453125</v>
       </c>
       <c r="G535" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -19003,7 +19003,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G536" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -19029,7 +19029,7 @@
         <v>8.05995655059814</v>
       </c>
       <c r="G537" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -19055,7 +19055,7 @@
         <v>8.30166339874268</v>
       </c>
       <c r="G538" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -19081,7 +19081,7 @@
         <v>7.87403011322021</v>
       </c>
       <c r="G539" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -19107,7 +19107,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G540" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -19133,7 +19133,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G541" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19159,7 +19159,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G542" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19185,7 +19185,7 @@
         <v>7.68810176849365</v>
       </c>
       <c r="G543" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19211,7 +19211,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G544" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19237,7 +19237,7 @@
         <v>7.8182520866394</v>
       </c>
       <c r="G545" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19263,7 +19263,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G546" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19289,7 +19289,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G547" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19315,7 +19315,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G548" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19341,7 +19341,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G549" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19367,7 +19367,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G550" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19393,7 +19393,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G551" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19419,7 +19419,7 @@
         <v>7.49566698074341</v>
       </c>
       <c r="G552" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19445,7 +19445,7 @@
         <v>7.36086988449097</v>
       </c>
       <c r="G553" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19471,7 +19471,7 @@
         <v>7.17308282852173</v>
       </c>
       <c r="G554" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19497,7 +19497,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G555" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19523,7 +19523,7 @@
         <v>6.98622608184814</v>
       </c>
       <c r="G556" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19549,7 +19549,7 @@
         <v>7.08383798599243</v>
       </c>
       <c r="G557" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19575,7 +19575,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G558" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19601,7 +19601,7 @@
         <v>7.298583984375</v>
       </c>
       <c r="G559" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19627,7 +19627,7 @@
         <v>7.12102317810059</v>
       </c>
       <c r="G560" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19653,7 +19653,7 @@
         <v>7.03177785873413</v>
       </c>
       <c r="G561" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19679,7 +19679,7 @@
         <v>7.05501890182495</v>
       </c>
       <c r="G562" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19705,7 +19705,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G563" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19731,7 +19731,7 @@
         <v>6.82911682128906</v>
       </c>
       <c r="G564" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19757,7 +19757,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G565" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19783,7 +19783,7 @@
         <v>7.01225614547729</v>
       </c>
       <c r="G566" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19809,7 +19809,7 @@
         <v>6.98064804077148</v>
       </c>
       <c r="G567" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19835,7 +19835,7 @@
         <v>6.94439220428467</v>
       </c>
       <c r="G568" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19861,7 +19861,7 @@
         <v>6.71291303634644</v>
       </c>
       <c r="G569" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19887,7 +19887,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G570" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19913,7 +19913,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G571" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19939,7 +19939,7 @@
         <v>7.27699995040894</v>
       </c>
       <c r="G572" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -19965,7 +19965,7 @@
         <v>7.97800016403198</v>
       </c>
       <c r="G573" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -19991,7 +19991,7 @@
         <v>7.58799982070923</v>
       </c>
       <c r="G574" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -20017,7 +20017,7 @@
         <v>7.75</v>
       </c>
       <c r="G575" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -20043,7 +20043,7 @@
         <v>8.04199981689453</v>
       </c>
       <c r="G576" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -20069,7 +20069,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G577" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -20095,7 +20095,7 @@
         <v>8.25899982452393</v>
       </c>
       <c r="G578" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -20121,7 +20121,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G579" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -20147,7 +20147,7 @@
         <v>7.83699989318848</v>
       </c>
       <c r="G580" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20173,7 +20173,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G581" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20199,7 +20199,7 @@
         <v>7.89900016784668</v>
       </c>
       <c r="G582" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20225,7 +20225,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G583" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20251,7 +20251,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G584" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20277,7 +20277,7 @@
         <v>7.86700010299683</v>
       </c>
       <c r="G585" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20303,7 +20303,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G586" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20329,7 +20329,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G587" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20355,7 +20355,7 @@
         <v>7.85799980163574</v>
       </c>
       <c r="G588" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20381,7 +20381,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G589" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20407,7 +20407,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G590" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20433,7 +20433,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G591" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20459,7 +20459,7 @@
         <v>7.71600008010864</v>
       </c>
       <c r="G592" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20485,7 +20485,7 @@
         <v>7.70100021362305</v>
       </c>
       <c r="G593" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20511,7 +20511,7 @@
         <v>7.76300001144409</v>
       </c>
       <c r="G594" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20537,7 +20537,7 @@
         <v>7.85699987411499</v>
       </c>
       <c r="G595" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20563,7 +20563,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G596" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20589,7 +20589,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20615,7 +20615,7 @@
         <v>8</v>
       </c>
       <c r="G598" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20641,7 +20641,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G599" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20667,7 +20667,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G600" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20693,7 +20693,7 @@
         <v>7.92600011825562</v>
       </c>
       <c r="G601" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20719,7 +20719,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G602" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20745,7 +20745,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G603" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20771,7 +20771,7 @@
         <v>8</v>
       </c>
       <c r="G604" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20797,7 +20797,7 @@
         <v>7.78399991989136</v>
       </c>
       <c r="G605" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20823,7 +20823,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G606" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20849,7 +20849,7 @@
         <v>7.44899988174438</v>
       </c>
       <c r="G607" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20875,7 +20875,7 @@
         <v>7.55900001525879</v>
       </c>
       <c r="G608" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -20901,7 +20901,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G609" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -20927,7 +20927,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G610" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -20953,7 +20953,7 @@
         <v>7.37099981307983</v>
       </c>
       <c r="G611" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -20979,7 +20979,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G612" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -21005,7 +21005,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G613" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -21031,7 +21031,7 @@
         <v>6.7649998664856</v>
       </c>
       <c r="G614" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -21057,7 +21057,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G615" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -21083,7 +21083,7 @@
         <v>7.27400016784668</v>
       </c>
       <c r="G616" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -21109,7 +21109,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G617" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -21135,7 +21135,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G618" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -21161,7 +21161,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G619" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21187,7 +21187,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G620" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21213,7 +21213,7 @@
         <v>7.32299995422363</v>
       </c>
       <c r="G621" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21239,7 +21239,7 @@
         <v>7.1710000038147</v>
       </c>
       <c r="G622" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21265,7 +21265,7 @@
         <v>7.08900022506714</v>
       </c>
       <c r="G623" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21291,7 +21291,7 @@
         <v>7.25899982452393</v>
       </c>
       <c r="G624" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21317,7 +21317,7 @@
         <v>7.11100006103516</v>
       </c>
       <c r="G625" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21343,7 +21343,7 @@
         <v>7.24900007247925</v>
       </c>
       <c r="G626" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21369,7 +21369,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G627" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21395,7 +21395,7 @@
         <v>6.97200012207031</v>
       </c>
       <c r="G628" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21421,7 +21421,7 @@
         <v>6.97399997711182</v>
       </c>
       <c r="G629" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21447,7 +21447,7 @@
         <v>6.92399978637695</v>
       </c>
       <c r="G630" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21473,7 +21473,7 @@
         <v>6.90299987792969</v>
       </c>
       <c r="G631" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21499,7 +21499,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G632" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21525,7 +21525,7 @@
         <v>6.96700000762939</v>
       </c>
       <c r="G633" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21551,7 +21551,7 @@
         <v>7</v>
       </c>
       <c r="G634" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21577,7 +21577,7 @@
         <v>6.875</v>
       </c>
       <c r="G635" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21603,7 +21603,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G636" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21629,7 +21629,7 @@
         <v>6.88199996948242</v>
       </c>
       <c r="G637" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21655,7 +21655,7 @@
         <v>7.04699993133545</v>
       </c>
       <c r="G638" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21681,7 +21681,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G639" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21707,7 +21707,7 @@
         <v>7</v>
       </c>
       <c r="G640" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21733,7 +21733,7 @@
         <v>6.93699979782104</v>
       </c>
       <c r="G641" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21759,7 +21759,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G642" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21785,7 +21785,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G643" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21811,7 +21811,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G644" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21837,7 +21837,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G645" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21863,7 +21863,7 @@
         <v>7.05399990081787</v>
       </c>
       <c r="G646" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21889,7 +21889,7 @@
         <v>7.06899976730347</v>
       </c>
       <c r="G647" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -21915,7 +21915,7 @@
         <v>7.12599992752075</v>
       </c>
       <c r="G648" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -21941,7 +21941,7 @@
         <v>7.17700004577637</v>
       </c>
       <c r="G649" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -21967,7 +21967,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G650" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -21993,7 +21993,7 @@
         <v>7.35099983215332</v>
       </c>
       <c r="G651" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22019,7 +22019,7 @@
         <v>7.21600008010864</v>
       </c>
       <c r="G652" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -22045,7 +22045,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G653" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -22071,7 +22071,7 @@
         <v>7.26100015640259</v>
       </c>
       <c r="G654" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22097,7 +22097,7 @@
         <v>7.06599998474121</v>
       </c>
       <c r="G655" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22123,7 +22123,7 @@
         <v>7.25</v>
       </c>
       <c r="G656" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22149,7 +22149,7 @@
         <v>7.05700016021729</v>
       </c>
       <c r="G657" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22175,7 +22175,7 @@
         <v>7.13100004196167</v>
       </c>
       <c r="G658" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22201,7 +22201,7 @@
         <v>7.23099994659424</v>
       </c>
       <c r="G659" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22227,7 +22227,7 @@
         <v>7.18300008773804</v>
       </c>
       <c r="G660" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22253,7 +22253,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G661" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22279,7 +22279,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G662" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22305,7 +22305,7 @@
         <v>6.93100023269653</v>
       </c>
       <c r="G663" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22331,7 +22331,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G664" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22357,7 +22357,7 @@
         <v>6.9210000038147</v>
       </c>
       <c r="G665" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22383,7 +22383,7 @@
         <v>6.90899991989136</v>
       </c>
       <c r="G666" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22409,7 +22409,7 @@
         <v>6.79300022125244</v>
       </c>
       <c r="G667" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22435,7 +22435,7 @@
         <v>6.66300010681152</v>
       </c>
       <c r="G668" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22461,7 +22461,7 @@
         <v>6.60699987411499</v>
       </c>
       <c r="G669" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22487,7 +22487,7 @@
         <v>6.49100017547607</v>
       </c>
       <c r="G670" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22513,7 +22513,7 @@
         <v>6.51900005340576</v>
       </c>
       <c r="G671" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22539,7 +22539,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22565,7 +22565,7 @@
         <v>6.69899988174438</v>
       </c>
       <c r="G673" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22591,7 +22591,7 @@
         <v>6.68699979782104</v>
       </c>
       <c r="G674" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22617,7 +22617,7 @@
         <v>6.58799982070923</v>
       </c>
       <c r="G675" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22643,7 +22643,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G676" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22669,7 +22669,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G677" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22695,7 +22695,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G678" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22721,7 +22721,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G679" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22747,7 +22747,7 @@
         <v>6.62099981307983</v>
       </c>
       <c r="G680" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22773,7 +22773,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G681" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22799,7 +22799,7 @@
         <v>6.56799983978271</v>
       </c>
       <c r="G682" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22825,7 +22825,7 @@
         <v>6.5310001373291</v>
       </c>
       <c r="G683" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22851,7 +22851,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G684" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22877,7 +22877,7 @@
         <v>6.57200002670288</v>
       </c>
       <c r="G685" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -22903,7 +22903,7 @@
         <v>6.58900022506714</v>
       </c>
       <c r="G686" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -22929,7 +22929,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G687" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -22955,7 +22955,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G688" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -22981,7 +22981,7 @@
         <v>6.58099985122681</v>
       </c>
       <c r="G689" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23007,7 +23007,7 @@
         <v>6.52299976348877</v>
       </c>
       <c r="G690" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -23033,7 +23033,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G691" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -23059,7 +23059,7 @@
         <v>6.95800018310547</v>
       </c>
       <c r="G692" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -23085,7 +23085,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G693" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -23111,7 +23111,7 @@
         <v>6.76900005340576</v>
       </c>
       <c r="G694" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -23137,7 +23137,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G695" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23163,7 +23163,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G696" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23189,7 +23189,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G697" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23215,7 +23215,7 @@
         <v>6.85099983215332</v>
       </c>
       <c r="G698" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23241,7 +23241,7 @@
         <v>6.75799989700317</v>
       </c>
       <c r="G699" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23267,7 +23267,7 @@
         <v>6.73899984359741</v>
       </c>
       <c r="G700" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23293,7 +23293,7 @@
         <v>6.61800003051758</v>
       </c>
       <c r="G701" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23319,7 +23319,7 @@
         <v>6.55700016021729</v>
       </c>
       <c r="G702" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23345,7 +23345,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G703" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23371,7 +23371,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G704" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23397,7 +23397,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G705" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23423,7 +23423,7 @@
         <v>6.30100011825562</v>
       </c>
       <c r="G706" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23449,7 +23449,7 @@
         <v>6.14099979400635</v>
       </c>
       <c r="G707" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23475,7 +23475,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G708" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23501,7 +23501,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G709" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23527,7 +23527,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G710" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23553,7 +23553,7 @@
         <v>5.95300006866455</v>
       </c>
       <c r="G711" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23579,7 +23579,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G712" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23605,7 +23605,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G713" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23631,7 +23631,7 @@
         <v>5.95900011062622</v>
       </c>
       <c r="G714" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23657,7 +23657,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G715" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23683,7 +23683,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G716" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23709,7 +23709,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G717" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23735,7 +23735,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G718" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23761,7 +23761,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G719" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23787,7 +23787,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G720" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23813,7 +23813,7 @@
         <v>6.00899982452393</v>
       </c>
       <c r="G721" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23839,7 +23839,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G722" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23865,7 +23865,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G723" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23891,7 +23891,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G724" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -23917,7 +23917,7 @@
         <v>6.25</v>
       </c>
       <c r="G725" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -23943,7 +23943,7 @@
         <v>6.23899984359741</v>
       </c>
       <c r="G726" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -23969,7 +23969,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G727" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -23995,7 +23995,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G728" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -24021,7 +24021,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G729" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -24047,7 +24047,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G730" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -24073,7 +24073,7 @@
         <v>6.2189998626709</v>
       </c>
       <c r="G731" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -24099,7 +24099,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G732" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -24125,7 +24125,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G733" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24151,7 +24151,7 @@
         <v>6.00299978256226</v>
       </c>
       <c r="G734" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24177,7 +24177,7 @@
         <v>6.03900003433228</v>
       </c>
       <c r="G735" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24203,7 +24203,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G736" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24229,7 +24229,7 @@
         <v>5.95100021362305</v>
       </c>
       <c r="G737" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24255,7 +24255,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G738" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24281,7 +24281,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G739" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24307,7 +24307,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G740" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24333,7 +24333,7 @@
         <v>6.02899980545044</v>
       </c>
       <c r="G741" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24359,7 +24359,7 @@
         <v>6.14300012588501</v>
       </c>
       <c r="G742" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24385,7 +24385,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G743" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24411,7 +24411,7 @@
         <v>6.10699987411499</v>
       </c>
       <c r="G744" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24437,7 +24437,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G745" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24463,7 +24463,7 @@
         <v>5.98299980163574</v>
       </c>
       <c r="G746" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24489,7 +24489,7 @@
         <v>5.88199996948242</v>
       </c>
       <c r="G747" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24515,7 +24515,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G748" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24541,7 +24541,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G749" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24567,7 +24567,7 @@
         <v>5.80700016021729</v>
       </c>
       <c r="G750" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24593,7 +24593,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G751" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24619,7 +24619,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G752" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24645,7 +24645,7 @@
         <v>5.65299987792969</v>
       </c>
       <c r="G753" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24671,7 +24671,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G754" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24697,7 +24697,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G755" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24723,7 +24723,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G756" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24749,7 +24749,7 @@
         <v>5.5</v>
       </c>
       <c r="G757" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24775,7 +24775,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G758" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24801,7 +24801,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G759" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24827,7 +24827,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G760" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24853,7 +24853,7 @@
         <v>5.4229998588562</v>
       </c>
       <c r="G761" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24879,7 +24879,7 @@
         <v>5.30700016021729</v>
       </c>
       <c r="G762" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -24905,7 +24905,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G763" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -24931,7 +24931,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G764" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -24957,7 +24957,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G765" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -24983,7 +24983,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G766" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -25009,7 +25009,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G767" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -25035,7 +25035,7 @@
         <v>5.90899991989136</v>
       </c>
       <c r="G768" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25061,7 +25061,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G769" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -25087,7 +25087,7 @@
         <v>5.91599988937378</v>
       </c>
       <c r="G770" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25113,7 +25113,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G771" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -25139,7 +25139,7 @@
         <v>5.81099987030029</v>
       </c>
       <c r="G772" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -25165,7 +25165,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G773" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25191,7 +25191,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G774" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25217,7 +25217,7 @@
         <v>5.84899997711182</v>
       </c>
       <c r="G775" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25243,7 +25243,7 @@
         <v>5.90199995040894</v>
       </c>
       <c r="G776" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25269,7 +25269,7 @@
         <v>5.83699989318848</v>
       </c>
       <c r="G777" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25295,7 +25295,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G778" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25321,7 +25321,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G779" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25347,7 +25347,7 @@
         <v>5.98899984359741</v>
       </c>
       <c r="G780" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25373,7 +25373,7 @@
         <v>6.14900016784668</v>
       </c>
       <c r="G781" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25399,7 +25399,7 @@
         <v>6.2810001373291</v>
       </c>
       <c r="G782" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25425,7 +25425,7 @@
         <v>6.23799991607666</v>
       </c>
       <c r="G783" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25451,7 +25451,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G784" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25477,7 +25477,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G785" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25503,7 +25503,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G786" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25529,7 +25529,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G787" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25555,7 +25555,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25581,7 +25581,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G789" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25607,7 +25607,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G790" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25633,7 +25633,7 @@
         <v>5.89599990844727</v>
       </c>
       <c r="G791" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25659,7 +25659,7 @@
         <v>6</v>
       </c>
       <c r="G792" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25685,7 +25685,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G793" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25711,7 +25711,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G794" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -25737,7 +25737,7 @@
         <v>6.06699991226196</v>
       </c>
       <c r="G795" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25763,7 +25763,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G796" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25789,7 +25789,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G797" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25815,7 +25815,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G798" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25841,7 +25841,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G799" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25867,7 +25867,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G800" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25893,7 +25893,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G801" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25919,7 +25919,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G802" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25945,7 +25945,7 @@
         <v>6.31899976730347</v>
       </c>
       <c r="G803" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -25971,7 +25971,7 @@
         <v>6.18699979782104</v>
       </c>
       <c r="G804" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -25997,7 +25997,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G805" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26023,7 +26023,7 @@
         <v>6.30800008773804</v>
       </c>
       <c r="G806" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26049,7 +26049,7 @@
         <v>6.36199998855591</v>
       </c>
       <c r="G807" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26075,7 +26075,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G808" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26101,7 +26101,7 @@
         <v>6.65299987792969</v>
       </c>
       <c r="G809" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26127,7 +26127,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G810" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26153,7 +26153,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G811" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26179,7 +26179,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26205,7 +26205,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G813" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26231,7 +26231,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G814" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26257,7 +26257,7 @@
         <v>6.65799999237061</v>
       </c>
       <c r="G815" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26283,7 +26283,7 @@
         <v>6.7039999961853</v>
       </c>
       <c r="G816" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26309,7 +26309,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G817" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26335,7 +26335,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G818" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26361,7 +26361,7 @@
         <v>6.64799976348877</v>
       </c>
       <c r="G819" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26387,7 +26387,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G820" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26413,7 +26413,7 @@
         <v>6.55600023269653</v>
       </c>
       <c r="G821" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26439,7 +26439,7 @@
         <v>6.48299980163574</v>
       </c>
       <c r="G822" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26465,7 +26465,7 @@
         <v>6.42799997329712</v>
       </c>
       <c r="G823" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26491,7 +26491,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G824" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26517,7 +26517,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G825" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26543,7 +26543,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G826" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26569,7 +26569,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G827" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26595,7 +26595,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G828" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26621,7 +26621,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G829" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26647,7 +26647,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G830" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26673,7 +26673,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G831" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26699,7 +26699,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G832" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26725,7 +26725,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G833" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26751,7 +26751,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G834" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26777,7 +26777,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G835" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26803,7 +26803,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G836" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26829,7 +26829,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G837" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26855,7 +26855,7 @@
         <v>6.75</v>
       </c>
       <c r="G838" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26881,7 +26881,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26907,7 +26907,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26933,7 +26933,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G841" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -26959,7 +26959,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G842" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -26985,7 +26985,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G843" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27011,7 +27011,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G844" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27037,7 +27037,7 @@
         <v>6.75</v>
       </c>
       <c r="G845" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27063,7 +27063,7 @@
         <v>6.75</v>
       </c>
       <c r="G846" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -27089,7 +27089,7 @@
         <v>6.75</v>
       </c>
       <c r="G847" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27115,7 +27115,7 @@
         <v>6.75</v>
       </c>
       <c r="G848" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -27141,7 +27141,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G849" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -27167,7 +27167,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G850" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27193,7 +27193,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G851" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27219,7 +27219,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G852" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27245,7 +27245,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G853" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27271,7 +27271,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G854" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27297,7 +27297,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27323,7 +27323,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G856" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27713,7 +27713,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G871" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28285,7 +28285,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G893" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -30911,7 +30911,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G994" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31197,7 +31197,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1005" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -31301,7 +31301,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1009" t="s">
-        <v>685</v>
+        <v>668</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -31457,7 +31457,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1015" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -31821,7 +31821,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1029" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -31873,7 +31873,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1031" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32081,7 +32081,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1039" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -69841,7 +69841,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6496064815</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>133316</v>
@@ -69862,6 +69862,32 @@
         <v>1574</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6494444444</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>99745</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>3.54500007629395</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>1571</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="1575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="1576">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">4.53839159011841</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56573057174683</t>
+    <t xml:space="preserve">4.56573152542114</t>
   </si>
   <si>
     <t xml:space="preserve">4.67235612869263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55206060409546</t>
+    <t xml:space="preserve">4.55206108093262</t>
   </si>
   <si>
     <t xml:space="preserve">4.33334350585938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16383743286133</t>
+    <t xml:space="preserve">4.16383790969849</t>
   </si>
   <si>
     <t xml:space="preserve">4.04627704620361</t>
@@ -80,16 +80,16 @@
     <t xml:space="preserve">3.60884189605713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88223814964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95605540275574</t>
+    <t xml:space="preserve">3.88223838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95605516433716</t>
   </si>
   <si>
     <t xml:space="preserve">4.0380744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97519373893738</t>
+    <t xml:space="preserve">3.9751935005188</t>
   </si>
   <si>
     <t xml:space="preserve">3.94785380363464</t>
@@ -98,25 +98,25 @@
     <t xml:space="preserve">3.813889503479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96425747871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07088232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92051362991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69632863998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78654909133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45573830604553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49948263168335</t>
+    <t xml:space="preserve">3.96425700187683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07088279724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92051434516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69632911682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78655004501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45573902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49948239326477</t>
   </si>
   <si>
     <t xml:space="preserve">3.69086003303528</t>
@@ -125,103 +125,103 @@
     <t xml:space="preserve">3.56783175468445</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63891506195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497281074524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755899429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93691802024841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87130284309387</t>
+    <t xml:space="preserve">3.63891530036926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755923271179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93691778182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87130236625671</t>
   </si>
   <si>
     <t xml:space="preserve">4.05994653701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00800132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95332169532776</t>
+    <t xml:space="preserve">4.00800085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95332145690918</t>
   </si>
   <si>
     <t xml:space="preserve">3.98612952232361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99159717559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03260660171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05447864532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2403883934021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21031522750854</t>
+    <t xml:space="preserve">3.99159693717957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0326075553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05447816848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24038887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21031427383423</t>
   </si>
   <si>
     <t xml:space="preserve">4.37435340881348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33607816696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34701299667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33881187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42903327941895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52745532989502</t>
+    <t xml:space="preserve">4.33607769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34701347351074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33881139755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42903232574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52745628356934</t>
   </si>
   <si>
     <t xml:space="preserve">4.51105165481567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46184015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57119941711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67509078979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60947370529175</t>
+    <t xml:space="preserve">4.46184062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5711989402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67509031295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60947418212891</t>
   </si>
   <si>
     <t xml:space="preserve">4.54932737350464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48371171951294</t>
+    <t xml:space="preserve">4.48371124267578</t>
   </si>
   <si>
     <t xml:space="preserve">4.34974765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42083072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42356491088867</t>
+    <t xml:space="preserve">4.42083024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42356538772583</t>
   </si>
   <si>
     <t xml:space="preserve">4.2649941444397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25405836105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22398471832275</t>
+    <t xml:space="preserve">4.25405883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2239842414856</t>
   </si>
   <si>
     <t xml:space="preserve">4.22671890258789</t>
@@ -233,37 +233,37 @@
     <t xml:space="preserve">4.3306097984314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40169286727905</t>
+    <t xml:space="preserve">4.40169334411621</t>
   </si>
   <si>
     <t xml:space="preserve">4.31967353820801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30600452423096</t>
+    <t xml:space="preserve">4.3060040473938</t>
   </si>
   <si>
     <t xml:space="preserve">4.36615133285522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26772832870483</t>
+    <t xml:space="preserve">4.26772880554199</t>
   </si>
   <si>
     <t xml:space="preserve">4.32514190673828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29233455657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27046203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29506826400757</t>
+    <t xml:space="preserve">4.29233407974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27046155929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29506778717041</t>
   </si>
   <si>
     <t xml:space="preserve">4.39895868301392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30873727798462</t>
+    <t xml:space="preserve">4.30873823165894</t>
   </si>
   <si>
     <t xml:space="preserve">4.38802289962769</t>
@@ -275,31 +275,31 @@
     <t xml:space="preserve">4.34427928924561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39075708389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3032693862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49522304534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57292556762695</t>
+    <t xml:space="preserve">4.39075660705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30326986312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49522352218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57292604446411</t>
   </si>
   <si>
     <t xml:space="preserve">4.65062808990479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69091892242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67940664291382</t>
+    <t xml:space="preserve">4.69091844558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67940616607666</t>
   </si>
   <si>
     <t xml:space="preserve">4.69379615783691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66213941574097</t>
+    <t xml:space="preserve">4.66213989257812</t>
   </si>
   <si>
     <t xml:space="preserve">4.61609363555908</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">4.57580327987671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63623905181885</t>
+    <t xml:space="preserve">4.63623809814453</t>
   </si>
   <si>
     <t xml:space="preserve">4.63048267364502</t>
@@ -320,76 +320,79 @@
     <t xml:space="preserve">4.63911628723145</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56429243087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35133075714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066560745239</t>
+    <t xml:space="preserve">4.56429290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35133028030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066608428955</t>
   </si>
   <si>
     <t xml:space="preserve">4.08368873596191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95130729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97145247459412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16139125823975</t>
+    <t xml:space="preserve">3.95130753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9714527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16139078140259</t>
   </si>
   <si>
     <t xml:space="preserve">4.20168161392212</t>
   </si>
   <si>
-    <t xml:space="preserve">4.247727394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27650547027588</t>
+    <t xml:space="preserve">4.24772691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27650594711304</t>
   </si>
   <si>
     <t xml:space="preserve">4.03476572036743</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84482622146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633730888367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470378875732</t>
+    <t xml:space="preserve">3.82755875587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84482669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633754730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470426559448</t>
   </si>
   <si>
     <t xml:space="preserve">4.15851306915283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01749897003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784887313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83619260787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96281886100769</t>
+    <t xml:space="preserve">4.01749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784958839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8361930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96281814575195</t>
   </si>
   <si>
     <t xml:space="preserve">4.05778837203979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09232234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25636005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40313196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33406352996826</t>
+    <t xml:space="preserve">4.0923228263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25636053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40313243865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33406400680542</t>
   </si>
   <si>
     <t xml:space="preserve">4.5182466506958</t>
@@ -401,10 +404,10 @@
     <t xml:space="preserve">4.45493316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45781135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52975749969482</t>
+    <t xml:space="preserve">4.45781183242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52975702285767</t>
   </si>
   <si>
     <t xml:space="preserve">4.48946809768677</t>
@@ -428,19 +431,19 @@
     <t xml:space="preserve">4.36571979522705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41464328765869</t>
+    <t xml:space="preserve">4.41464376449585</t>
   </si>
   <si>
     <t xml:space="preserve">4.35996389389038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33694124221802</t>
+    <t xml:space="preserve">4.33694171905518</t>
   </si>
   <si>
     <t xml:space="preserve">4.29377269744873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3139181137085</t>
+    <t xml:space="preserve">4.31391763687134</t>
   </si>
   <si>
     <t xml:space="preserve">4.19016981124878</t>
@@ -449,34 +452,34 @@
     <t xml:space="preserve">4.19880342483521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22182655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26211643218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25348281860352</t>
+    <t xml:space="preserve">4.22182607650757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2621169090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25348329544067</t>
   </si>
   <si>
     <t xml:space="preserve">4.23046016693115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14412450790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19592618942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16714668273926</t>
+    <t xml:space="preserve">4.14412403106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19592571258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16714763641357</t>
   </si>
   <si>
     <t xml:space="preserve">4.15563583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1153450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20743656158447</t>
+    <t xml:space="preserve">4.11534452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20743703842163</t>
   </si>
   <si>
     <t xml:space="preserve">4.14700222015381</t>
@@ -485,67 +488,67 @@
     <t xml:space="preserve">4.1786584854126</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0750560760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9426736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497092247009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79878115653992</t>
+    <t xml:space="preserve">4.07505559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94267392158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497139930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79878091812134</t>
   </si>
   <si>
     <t xml:space="preserve">3.77575755119324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83907055854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74697828292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74985647201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85921621322632</t>
+    <t xml:space="preserve">3.83907032012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74697852134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74985671043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85921597480774</t>
   </si>
   <si>
     <t xml:space="preserve">3.82468104362488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79590225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87936091423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81029200553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439116477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76424646377563</t>
+    <t xml:space="preserve">3.79590201377869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87936067581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81029176712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439164161682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76424598693848</t>
   </si>
   <si>
     <t xml:space="preserve">3.72971200942993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71244502067566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72395610809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84194827079773</t>
+    <t xml:space="preserve">3.7124445438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72395658493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84194803237915</t>
   </si>
   <si>
     <t xml:space="preserve">3.99735307693481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06354379653931</t>
+    <t xml:space="preserve">4.06354427337646</t>
   </si>
   <si>
     <t xml:space="preserve">4.10958957672119</t>
@@ -554,10 +557,10 @@
     <t xml:space="preserve">4.11822271347046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08656644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03764247894287</t>
+    <t xml:space="preserve">4.08656692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03764343261719</t>
   </si>
   <si>
     <t xml:space="preserve">4.00310897827148</t>
@@ -572,58 +575,58 @@
     <t xml:space="preserve">3.93979620933533</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92540693283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92828440666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89662766456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8477041721344</t>
+    <t xml:space="preserve">3.92540597915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92828464508057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89662742614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84770393371582</t>
   </si>
   <si>
     <t xml:space="preserve">3.75273489952087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75848984718323</t>
+    <t xml:space="preserve">3.75849008560181</t>
   </si>
   <si>
     <t xml:space="preserve">3.55703997612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64337539672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66927599906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65776467323303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5800621509552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59732961654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60308575630188</t>
+    <t xml:space="preserve">3.64337515830994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66927695274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65776491165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58006238937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59732937812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60308599472046</t>
   </si>
   <si>
     <t xml:space="preserve">3.63186430931091</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6261088848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66064310073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61459684371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80453634262085</t>
+    <t xml:space="preserve">3.62610840797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66064286231995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61459732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80453586578369</t>
   </si>
   <si>
     <t xml:space="preserve">3.9599404335022</t>
@@ -650,46 +653,43 @@
     <t xml:space="preserve">4.28226137161255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33981943130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34845209121704</t>
+    <t xml:space="preserve">4.33981895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3484525680542</t>
   </si>
   <si>
     <t xml:space="preserve">4.33118486404419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30240631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27075004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22758293151855</t>
+    <t xml:space="preserve">4.30240678787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27074956893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22758197784424</t>
   </si>
   <si>
     <t xml:space="preserve">4.2131929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18153619766235</t>
+    <t xml:space="preserve">4.18153715133667</t>
   </si>
   <si>
     <t xml:space="preserve">4.09807872772217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00598621368408</t>
+    <t xml:space="preserve">4.00598573684692</t>
   </si>
   <si>
     <t xml:space="preserve">4.10383415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02900981903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06929874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04627656936646</t>
+    <t xml:space="preserve">4.0290093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06929922103882</t>
   </si>
   <si>
     <t xml:space="preserve">4.21894836425781</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">4.59307050704956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62472820281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57004880905151</t>
+    <t xml:space="preserve">4.62472772598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57004833221436</t>
   </si>
   <si>
     <t xml:space="preserve">4.71969652175903</t>
@@ -728,31 +728,31 @@
     <t xml:space="preserve">4.70818567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80315494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73120880126953</t>
+    <t xml:space="preserve">4.80315446853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73120784759521</t>
   </si>
   <si>
     <t xml:space="preserve">4.70530796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70242977142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64487171173096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62184906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54702472686768</t>
+    <t xml:space="preserve">4.7024302482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64487218856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62185001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54702520370483</t>
   </si>
   <si>
     <t xml:space="preserve">4.52687978744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46068906784058</t>
+    <t xml:space="preserve">4.46068954467773</t>
   </si>
   <si>
     <t xml:space="preserve">4.6045823097229</t>
@@ -761,13 +761,13 @@
     <t xml:space="preserve">4.71394109725952</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66501665115356</t>
+    <t xml:space="preserve">4.66501760482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.74559783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76574277877808</t>
+    <t xml:space="preserve">4.76574325561523</t>
   </si>
   <si>
     <t xml:space="preserve">4.74847555160522</t>
@@ -776,16 +776,16 @@
     <t xml:space="preserve">4.78301000595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77149868011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82329988479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92690324783325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94992589950562</t>
+    <t xml:space="preserve">4.77149820327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8233003616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92690277099609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94992637634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.98446035385132</t>
@@ -797,7 +797,7 @@
     <t xml:space="preserve">5.05640745162964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89236879348755</t>
+    <t xml:space="preserve">4.89236831665039</t>
   </si>
   <si>
     <t xml:space="preserve">4.86358976364136</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">4.82905578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87592363357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91160106658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93538618087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89970827102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92052125930786</t>
+    <t xml:space="preserve">4.8759241104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91160154342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93538570404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89970874786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9205207824707</t>
   </si>
   <si>
     <t xml:space="preserve">5.01268720626831</t>
@@ -830,64 +830,64 @@
     <t xml:space="preserve">4.97106409072876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89376258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94727849960327</t>
+    <t xml:space="preserve">4.89376306533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94727897644043</t>
   </si>
   <si>
     <t xml:space="preserve">4.94133281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92944049835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88781642913818</t>
+    <t xml:space="preserve">4.92944002151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88781595230103</t>
   </si>
   <si>
     <t xml:space="preserve">4.85511159896851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79862213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77186441421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75105285644531</t>
+    <t xml:space="preserve">4.79862260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77186489105225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75105237960815</t>
   </si>
   <si>
     <t xml:space="preserve">4.78673028945923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73321390151978</t>
+    <t xml:space="preserve">4.73321437835693</t>
   </si>
   <si>
     <t xml:space="preserve">4.66185855865479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53401470184326</t>
+    <t xml:space="preserve">4.5340142250061</t>
   </si>
   <si>
     <t xml:space="preserve">4.584557056427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61726093292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70348310470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72132205963135</t>
+    <t xml:space="preserve">4.61726188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70348262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72132158279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.63807392120361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72726726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81646108627319</t>
+    <t xml:space="preserve">4.72726678848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81646156311035</t>
   </si>
   <si>
     <t xml:space="preserve">4.83132696151733</t>
@@ -896,46 +896,46 @@
     <t xml:space="preserve">4.93835973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94430541992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98295640945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95322561264038</t>
+    <t xml:space="preserve">4.94430637359619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9829568862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95322513580322</t>
   </si>
   <si>
     <t xml:space="preserve">4.90565490722656</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84619331359863</t>
+    <t xml:space="preserve">4.84619283676147</t>
   </si>
   <si>
     <t xml:space="preserve">4.89078950881958</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00376844406128</t>
+    <t xml:space="preserve">5.00376796722412</t>
   </si>
   <si>
     <t xml:space="preserve">5.05431127548218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04836559295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99782133102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9859299659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15837097167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12566661834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11080121994019</t>
+    <t xml:space="preserve">5.04836511611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99782180786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98592948913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15837049484253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12566709518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11080074310303</t>
   </si>
   <si>
     <t xml:space="preserve">5.07512283325195</t>
@@ -944,52 +944,52 @@
     <t xml:space="preserve">5.0810694694519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09593486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11377382278442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03944540023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02755355834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97701072692871</t>
+    <t xml:space="preserve">5.09593534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11377429962158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0394458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02755260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97700977325439</t>
   </si>
   <si>
     <t xml:space="preserve">5.05133819580078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99484920501709</t>
+    <t xml:space="preserve">4.99484872817993</t>
   </si>
   <si>
     <t xml:space="preserve">5.01566123962402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06620454788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1375584602356</t>
+    <t xml:space="preserve">5.06620407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13755893707275</t>
   </si>
   <si>
     <t xml:space="preserve">5.2326979637146</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24459075927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23864555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19702196121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17323637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1851282119751</t>
+    <t xml:space="preserve">5.2445912361145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23864507675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.197021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17323589324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18512868881226</t>
   </si>
   <si>
     <t xml:space="preserve">5.20891427993774</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">5.1940484046936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24756479263306</t>
+    <t xml:space="preserve">5.2475643157959</t>
   </si>
   <si>
     <t xml:space="preserve">5.25053739547729</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">5.26242971420288</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1494517326355</t>
+    <t xml:space="preserve">5.14945125579834</t>
   </si>
   <si>
     <t xml:space="preserve">5.16431713104248</t>
@@ -1016,25 +1016,25 @@
     <t xml:space="preserve">5.21485996246338</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35162353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.44081687927246</t>
+    <t xml:space="preserve">5.35162448883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44081735610962</t>
   </si>
   <si>
     <t xml:space="preserve">5.64893627166748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6786675453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47054767608643</t>
+    <t xml:space="preserve">5.67866706848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47054862976074</t>
   </si>
   <si>
     <t xml:space="preserve">5.46757555007935</t>
   </si>
   <si>
-    <t xml:space="preserve">5.55974197387695</t>
+    <t xml:space="preserve">5.55974292755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.59541940689087</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">5.57758140563965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75002288818359</t>
+    <t xml:space="preserve">5.75002241134644</t>
   </si>
   <si>
     <t xml:space="preserve">5.90165185928345</t>
@@ -1064,58 +1064,58 @@
     <t xml:space="preserve">6.19004535675049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11274337768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12463569641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15436792373657</t>
+    <t xml:space="preserve">6.11274385452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12463665008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15436744689941</t>
   </si>
   <si>
     <t xml:space="preserve">6.03544235229492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.97597932815552</t>
+    <t xml:space="preserve">5.97597980499268</t>
   </si>
   <si>
     <t xml:space="preserve">5.88976001739502</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00571203231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29113101959229</t>
+    <t xml:space="preserve">6.00571155548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29113054275513</t>
   </si>
   <si>
     <t xml:space="preserve">6.3446478843689</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17815256118774</t>
+    <t xml:space="preserve">6.1781530380249</t>
   </si>
   <si>
     <t xml:space="preserve">6.39816379547119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38627147674561</t>
+    <t xml:space="preserve">6.38627052307129</t>
   </si>
   <si>
     <t xml:space="preserve">6.33275461196899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43384027481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46951913833618</t>
+    <t xml:space="preserve">6.43384122848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46951866149902</t>
   </si>
   <si>
     <t xml:space="preserve">6.41600227355957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40410995483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24356126785278</t>
+    <t xml:space="preserve">6.40411043167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24356174468994</t>
   </si>
   <si>
     <t xml:space="preserve">6.35653972625732</t>
@@ -1124,34 +1124,34 @@
     <t xml:space="preserve">6.44573402404785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6003360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5884428024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71926164627075</t>
+    <t xml:space="preserve">6.60033702850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58844375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71926116943359</t>
   </si>
   <si>
     <t xml:space="preserve">6.65979862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48141098022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07111978530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82732439041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76786136627197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80948448181152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68164014816284</t>
+    <t xml:space="preserve">6.48141050338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07111930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82732343673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76786088943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80948495864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.681640625</t>
   </si>
   <si>
     <t xml:space="preserve">5.73812961578369</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">5.81840419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7321834564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72623682022095</t>
+    <t xml:space="preserve">5.73218393325806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72623634338379</t>
   </si>
   <si>
     <t xml:space="preserve">5.85705518722534</t>
@@ -1178,7 +1178,7 @@
     <t xml:space="preserve">5.92841005325317</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76191568374634</t>
+    <t xml:space="preserve">5.76191473007202</t>
   </si>
   <si>
     <t xml:space="preserve">5.70839834213257</t>
@@ -1187,7 +1187,7 @@
     <t xml:space="preserve">5.79759216308594</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75596904754639</t>
+    <t xml:space="preserve">5.75596857070923</t>
   </si>
   <si>
     <t xml:space="preserve">5.6846137046814</t>
@@ -1202,37 +1202,37 @@
     <t xml:space="preserve">5.50622701644897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.458655834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33973073959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15539693832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3100004196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0364727973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91754674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00079488754272</t>
+    <t xml:space="preserve">5.45865631103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33973121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15539741516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.31000089645386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03647232055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91754722595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00079536437988</t>
   </si>
   <si>
     <t xml:space="preserve">4.86997747421265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85213899612427</t>
+    <t xml:space="preserve">4.85213851928711</t>
   </si>
   <si>
     <t xml:space="preserve">5.14350509643555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75699901580811</t>
+    <t xml:space="preserve">4.75699853897095</t>
   </si>
   <si>
     <t xml:space="preserve">4.79446029663086</t>
@@ -1244,19 +1244,19 @@
     <t xml:space="preserve">4.58812522888184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47752571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46860551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53104114532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66483211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66839933395386</t>
+    <t xml:space="preserve">4.47752618789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46860599517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53104066848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66483163833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66839981079102</t>
   </si>
   <si>
     <t xml:space="preserve">4.55482625961304</t>
@@ -1265,7 +1265,7 @@
     <t xml:space="preserve">4.49774217605591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51260757446289</t>
+    <t xml:space="preserve">4.51260805130005</t>
   </si>
   <si>
     <t xml:space="preserve">4.41211652755737</t>
@@ -1277,34 +1277,34 @@
     <t xml:space="preserve">4.29913759231567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4852557182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46503829956055</t>
+    <t xml:space="preserve">4.48525524139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46503782272339</t>
   </si>
   <si>
     <t xml:space="preserve">4.4418478012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29378652572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19210529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57336091995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6545934677124</t>
+    <t xml:space="preserve">4.29378700256348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19210577011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57336044311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65459442138672</t>
   </si>
   <si>
     <t xml:space="preserve">5.10297536849976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85351848602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95713901519775</t>
+    <t xml:space="preserve">4.85351943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95713949203491</t>
   </si>
   <si>
     <t xml:space="preserve">5.14391136169434</t>
@@ -1340,28 +1340,28 @@
     <t xml:space="preserve">5.01598501205444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02621936798096</t>
+    <t xml:space="preserve">5.0262188911438</t>
   </si>
   <si>
     <t xml:space="preserve">5.01470613479614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08506488800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93539190292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92579746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96545505523682</t>
+    <t xml:space="preserve">5.08506536483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93539142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92579793930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96545457839966</t>
   </si>
   <si>
     <t xml:space="preserve">5.02557945251465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04029178619385</t>
+    <t xml:space="preserve">5.04029130935669</t>
   </si>
   <si>
     <t xml:space="preserve">5.02110242843628</t>
@@ -1376,13 +1376,13 @@
     <t xml:space="preserve">5.06971454620361</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24497270584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14135313034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97888708114624</t>
+    <t xml:space="preserve">5.24497318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14135265350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97888660430908</t>
   </si>
   <si>
     <t xml:space="preserve">4.76461029052734</t>
@@ -1394,13 +1394,13 @@
     <t xml:space="preserve">4.78124046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73326873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71471929550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66290903091431</t>
+    <t xml:space="preserve">4.73326826095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71471881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66290950775146</t>
   </si>
   <si>
     <t xml:space="preserve">4.55097341537476</t>
@@ -1409,34 +1409,34 @@
     <t xml:space="preserve">4.32710313796997</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57399988174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65267467498779</t>
+    <t xml:space="preserve">4.57400035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65267515182495</t>
   </si>
   <si>
     <t xml:space="preserve">4.63092708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72943067550659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81961870193481</t>
+    <t xml:space="preserve">4.72943115234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81961822509766</t>
   </si>
   <si>
     <t xml:space="preserve">4.79403352737427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68401670455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58679342269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87419843673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99108505249023</t>
+    <t xml:space="preserve">4.68401622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58679294586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8741979598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99108457565308</t>
   </si>
   <si>
     <t xml:space="preserve">4.88932466506958</t>
@@ -1445,10 +1445,10 @@
     <t xml:space="preserve">4.9842095375061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03165149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79375219345093</t>
+    <t xml:space="preserve">5.03165197372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79375267028809</t>
   </si>
   <si>
     <t xml:space="preserve">4.79512739181519</t>
@@ -1460,13 +1460,13 @@
     <t xml:space="preserve">4.74630928039551</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86113452911377</t>
+    <t xml:space="preserve">4.86113405227661</t>
   </si>
   <si>
     <t xml:space="preserve">4.79031419754028</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81300401687622</t>
+    <t xml:space="preserve">4.81300449371338</t>
   </si>
   <si>
     <t xml:space="preserve">4.72705745697021</t>
@@ -1481,10 +1481,10 @@
     <t xml:space="preserve">4.84532022476196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7868766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76968669891357</t>
+    <t xml:space="preserve">4.78687620162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76968717575073</t>
   </si>
   <si>
     <t xml:space="preserve">4.91614007949829</t>
@@ -1499,31 +1499,31 @@
     <t xml:space="preserve">4.82675552368164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85013246536255</t>
+    <t xml:space="preserve">4.85013294219971</t>
   </si>
   <si>
     <t xml:space="preserve">4.86044645309448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8996376991272</t>
+    <t xml:space="preserve">4.89963817596436</t>
   </si>
   <si>
     <t xml:space="preserve">4.93470430374146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99177265167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05434131622314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96152019500732</t>
+    <t xml:space="preserve">4.99177312850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0543417930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96151971817017</t>
   </si>
   <si>
     <t xml:space="preserve">4.97939682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99246072769165</t>
+    <t xml:space="preserve">4.99246025085449</t>
   </si>
   <si>
     <t xml:space="preserve">4.8583836555481</t>
@@ -1532,34 +1532,34 @@
     <t xml:space="preserve">4.98489713668823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85219621658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90307664871216</t>
+    <t xml:space="preserve">4.85219573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.903076171875</t>
   </si>
   <si>
     <t xml:space="preserve">4.97183322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93882989883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91682720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83363151550293</t>
+    <t xml:space="preserve">4.93883037567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91682767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83363199234009</t>
   </si>
   <si>
     <t xml:space="preserve">4.76556158065796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75868558883667</t>
+    <t xml:space="preserve">4.75868606567383</t>
   </si>
   <si>
     <t xml:space="preserve">4.75043487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67067670822144</t>
+    <t xml:space="preserve">4.67067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.58129262924194</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">4.5427885055542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46303033828735</t>
+    <t xml:space="preserve">4.4630298614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.48228216171265</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">4.60604524612427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59779405593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52972412109375</t>
+    <t xml:space="preserve">4.59779357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52972459793091</t>
   </si>
   <si>
     <t xml:space="preserve">4.5379753112793</t>
@@ -1592,28 +1592,28 @@
     <t xml:space="preserve">4.57922983169556</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55172634124756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57235383987427</t>
+    <t xml:space="preserve">4.55172681808472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57235431671143</t>
   </si>
   <si>
     <t xml:space="preserve">4.55241394042969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50634670257568</t>
+    <t xml:space="preserve">4.50634717941284</t>
   </si>
   <si>
     <t xml:space="preserve">4.51597309112549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49053335189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52078628540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.518723487854</t>
+    <t xml:space="preserve">4.49053287506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52078580856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51872301101685</t>
   </si>
   <si>
     <t xml:space="preserve">4.53041219711304</t>
@@ -1622,7 +1622,7 @@
     <t xml:space="preserve">4.51047229766846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52491092681885</t>
+    <t xml:space="preserve">4.52491140365601</t>
   </si>
   <si>
     <t xml:space="preserve">4.485032081604</t>
@@ -1631,28 +1631,28 @@
     <t xml:space="preserve">4.47746896743774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78412580490112</t>
+    <t xml:space="preserve">4.78412628173828</t>
   </si>
   <si>
     <t xml:space="preserve">4.6651759147644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6541748046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70299291610718</t>
+    <t xml:space="preserve">4.65417432785034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70299243927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.73049545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71055555343628</t>
+    <t xml:space="preserve">4.71055603027344</t>
   </si>
   <si>
     <t xml:space="preserve">4.64661169052124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63354778289795</t>
+    <t xml:space="preserve">4.63354730606079</t>
   </si>
   <si>
     <t xml:space="preserve">4.55035161972046</t>
@@ -1664,43 +1664,43 @@
     <t xml:space="preserve">4.41558742523193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42727661132812</t>
+    <t xml:space="preserve">4.42727613449097</t>
   </si>
   <si>
     <t xml:space="preserve">4.40046072006226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3323917388916</t>
+    <t xml:space="preserve">4.33239126205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.22237968444824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20450258255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16256046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0663013458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09311676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98791790008545</t>
+    <t xml:space="preserve">4.20450305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16256093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06630086898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09311580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98791766166687</t>
   </si>
   <si>
     <t xml:space="preserve">4.05942487716675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09724140167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0497989654541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05323648452759</t>
+    <t xml:space="preserve">4.09724187850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04979848861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05323696136475</t>
   </si>
   <si>
     <t xml:space="preserve">4.10480499267578</t>
@@ -1709,19 +1709,19 @@
     <t xml:space="preserve">4.09105348587036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08830308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13162040710449</t>
+    <t xml:space="preserve">4.088303565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13161993026733</t>
   </si>
   <si>
     <t xml:space="preserve">4.21962976455688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28563594818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29732465744019</t>
+    <t xml:space="preserve">4.28563642501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29732513427734</t>
   </si>
   <si>
     <t xml:space="preserve">4.28976202011108</t>
@@ -1730,22 +1730,22 @@
     <t xml:space="preserve">4.22100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15293502807617</t>
+    <t xml:space="preserve">4.15293455123901</t>
   </si>
   <si>
     <t xml:space="preserve">4.36608219146729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27601003646851</t>
+    <t xml:space="preserve">4.27601051330566</t>
   </si>
   <si>
     <t xml:space="preserve">4.22513008117676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1948766708374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12749481201172</t>
+    <t xml:space="preserve">4.19487619400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12749433517456</t>
   </si>
   <si>
     <t xml:space="preserve">4.15224742889404</t>
@@ -1766,25 +1766,25 @@
     <t xml:space="preserve">4.054612159729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14537143707275</t>
+    <t xml:space="preserve">4.14537191390991</t>
   </si>
   <si>
     <t xml:space="preserve">4.22375535964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23544311523438</t>
+    <t xml:space="preserve">4.23544359207153</t>
   </si>
   <si>
     <t xml:space="preserve">4.19900226593018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1886887550354</t>
+    <t xml:space="preserve">4.18868827819824</t>
   </si>
   <si>
     <t xml:space="preserve">4.1137433052063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04429912567139</t>
+    <t xml:space="preserve">4.04429864883423</t>
   </si>
   <si>
     <t xml:space="preserve">4.02917194366455</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">3.99273061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99891924858093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96316528320312</t>
+    <t xml:space="preserve">3.9989185333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96316480636597</t>
   </si>
   <si>
     <t xml:space="preserve">3.88684463500977</t>
@@ -1805,16 +1805,16 @@
     <t xml:space="preserve">3.98241686820984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90540885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87378072738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78164649009705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71013879776001</t>
+    <t xml:space="preserve">3.90540909767151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8737804889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78164601325989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71013903617859</t>
   </si>
   <si>
     <t xml:space="preserve">3.69501209259033</t>
@@ -1829,64 +1829,64 @@
     <t xml:space="preserve">3.64894461631775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70051264762878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83115148544312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990830421448</t>
+    <t xml:space="preserve">3.70051240921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83115100860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990854263306</t>
   </si>
   <si>
     <t xml:space="preserve">3.99341821670532</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9782919883728</t>
+    <t xml:space="preserve">3.97829174995422</t>
   </si>
   <si>
     <t xml:space="preserve">4.06286287307739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.048424243927</t>
+    <t xml:space="preserve">4.04842376708984</t>
   </si>
   <si>
     <t xml:space="preserve">4.06767606735229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04292345046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99548077583313</t>
+    <t xml:space="preserve">4.04292392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99548053741455</t>
   </si>
   <si>
     <t xml:space="preserve">3.95491409301758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04086112976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02160882949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05804967880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0133581161499</t>
+    <t xml:space="preserve">4.04086065292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02160835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05805015563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01335763931274</t>
   </si>
   <si>
     <t xml:space="preserve">3.97004103660583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07180166244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11786842346191</t>
+    <t xml:space="preserve">4.07180118560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11786890029907</t>
   </si>
   <si>
     <t xml:space="preserve">4.22788047790527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31864023208618</t>
+    <t xml:space="preserve">4.31863975524902</t>
   </si>
   <si>
     <t xml:space="preserve">4.2890739440918</t>
@@ -1895,7 +1895,7 @@
     <t xml:space="preserve">4.29044914245605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25057029724121</t>
+    <t xml:space="preserve">4.25056982040405</t>
   </si>
   <si>
     <t xml:space="preserve">4.24919462203979</t>
@@ -1907,19 +1907,19 @@
     <t xml:space="preserve">4.26294660568237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24231910705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13643360137939</t>
+    <t xml:space="preserve">4.24232006072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13643312454224</t>
   </si>
   <si>
     <t xml:space="preserve">4.05392456054688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12543201446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0896782875061</t>
+    <t xml:space="preserve">4.12543249130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08967876434326</t>
   </si>
   <si>
     <t xml:space="preserve">4.13230800628662</t>
@@ -1934,22 +1934,22 @@
     <t xml:space="preserve">4.22169208526611</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21894216537476</t>
+    <t xml:space="preserve">4.2189416885376</t>
   </si>
   <si>
     <t xml:space="preserve">4.21481657028198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16324806213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28494882583618</t>
+    <t xml:space="preserve">4.16324853897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28494834899902</t>
   </si>
   <si>
     <t xml:space="preserve">4.34476757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2540078163147</t>
+    <t xml:space="preserve">4.25400829315186</t>
   </si>
   <si>
     <t xml:space="preserve">4.33720397949219</t>
@@ -1970,31 +1970,31 @@
     <t xml:space="preserve">4.44171571731567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4485912322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55653953552246</t>
+    <t xml:space="preserve">4.44859075546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55654001235962</t>
   </si>
   <si>
     <t xml:space="preserve">4.5778546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60948276519775</t>
+    <t xml:space="preserve">4.60948324203491</t>
   </si>
   <si>
     <t xml:space="preserve">4.66173839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6067328453064</t>
+    <t xml:space="preserve">4.60673236846924</t>
   </si>
   <si>
     <t xml:space="preserve">4.57097864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57166624069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5077223777771</t>
+    <t xml:space="preserve">4.5716667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50772285461426</t>
   </si>
   <si>
     <t xml:space="preserve">4.45752906799316</t>
@@ -2003,58 +2003,58 @@
     <t xml:space="preserve">4.41971302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46234226226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42796421051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54485082626343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52422380447388</t>
+    <t xml:space="preserve">4.46234273910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4279637336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54485130310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52422332763672</t>
   </si>
   <si>
     <t xml:space="preserve">4.55860233306885</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58610582351685</t>
+    <t xml:space="preserve">4.58610486984253</t>
   </si>
   <si>
     <t xml:space="preserve">4.45546674728394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48296976089478</t>
+    <t xml:space="preserve">4.48296928405762</t>
   </si>
   <si>
     <t xml:space="preserve">4.53109979629517</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56547784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59985733032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64111089706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61360883712769</t>
+    <t xml:space="preserve">4.56547832489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59985685348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64111137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61360836029053</t>
   </si>
   <si>
     <t xml:space="preserve">4.62048387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62735986709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71674394607544</t>
+    <t xml:space="preserve">4.62735939025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7167444229126</t>
   </si>
   <si>
     <t xml:space="preserve">4.65486240386963</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49672079086304</t>
+    <t xml:space="preserve">4.4967212677002</t>
   </si>
   <si>
     <t xml:space="preserve">4.5522894859314</t>
@@ -2063,25 +2063,25 @@
     <t xml:space="preserve">4.61179637908936</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60435771942139</t>
+    <t xml:space="preserve">4.60435819625854</t>
   </si>
   <si>
     <t xml:space="preserve">4.62667322158813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6936182975769</t>
+    <t xml:space="preserve">4.69361877441406</t>
   </si>
   <si>
     <t xml:space="preserve">4.73824882507324</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71593332290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6341118812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65642690658569</t>
+    <t xml:space="preserve">4.71593379974365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63411140441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65642642974854</t>
   </si>
   <si>
     <t xml:space="preserve">4.58948135375977</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">4.51509761810303</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57460403442383</t>
+    <t xml:space="preserve">4.57460451126099</t>
   </si>
   <si>
     <t xml:space="preserve">4.56716585159302</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">4.5820426940918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52997446060181</t>
+    <t xml:space="preserve">4.52997398376465</t>
   </si>
   <si>
     <t xml:space="preserve">4.4481520652771</t>
@@ -2123,28 +2123,28 @@
     <t xml:space="preserve">4.37376832962036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41839838027954</t>
+    <t xml:space="preserve">4.4183988571167</t>
   </si>
   <si>
     <t xml:space="preserve">4.35889148712158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32913827896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32169914245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31426095962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33657646179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59691905975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50765895843506</t>
+    <t xml:space="preserve">4.32913780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32169961929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3142614364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33657598495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59691953659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5076584815979</t>
   </si>
   <si>
     <t xml:space="preserve">4.49278211593628</t>
@@ -2156,19 +2156,19 @@
     <t xml:space="preserve">4.43327522277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40352201461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38864469528198</t>
+    <t xml:space="preserve">4.40352153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38864517211914</t>
   </si>
   <si>
     <t xml:space="preserve">4.39608287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35145282745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24731540679932</t>
+    <t xml:space="preserve">4.35145330429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24731588363647</t>
   </si>
   <si>
     <t xml:space="preserve">4.20268535614014</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">4.19524669647217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10598707199097</t>
+    <t xml:space="preserve">4.10598659515381</t>
   </si>
   <si>
     <t xml:space="preserve">4.13573980331421</t>
@@ -2186,22 +2186,22 @@
     <t xml:space="preserve">4.01672554016113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02416372299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93490362167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90514993667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95721936225891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89771127700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98697257041931</t>
+    <t xml:space="preserve">4.0241641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93490409851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90515065193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95721888542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89771151542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98697233200073</t>
   </si>
   <si>
     <t xml:space="preserve">3.92002701759338</t>
@@ -2210,13 +2210,13 @@
     <t xml:space="preserve">3.94234228134155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97953414916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97209596633911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04647922515869</t>
+    <t xml:space="preserve">3.97953391075134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97209572792053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04647970199585</t>
   </si>
   <si>
     <t xml:space="preserve">4.06879425048828</t>
@@ -2225,7 +2225,7 @@
     <t xml:space="preserve">4.098548412323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16549301147461</t>
+    <t xml:space="preserve">4.16549348831177</t>
   </si>
   <si>
     <t xml:space="preserve">4.18780851364136</t>
@@ -2234,7 +2234,7 @@
     <t xml:space="preserve">4.18037033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17293167114258</t>
+    <t xml:space="preserve">4.17293214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.11342525482178</t>
@@ -2243,22 +2243,22 @@
     <t xml:space="preserve">4.14317846298218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12830209732056</t>
+    <t xml:space="preserve">4.1283016204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.15805530548096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03904056549072</t>
+    <t xml:space="preserve">4.03904104232788</t>
   </si>
   <si>
     <t xml:space="preserve">4.2324390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23987674713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26963090896606</t>
+    <t xml:space="preserve">4.23987722396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26963043212891</t>
   </si>
   <si>
     <t xml:space="preserve">4.30682277679443</t>
@@ -2270,7 +2270,7 @@
     <t xml:space="preserve">4.2621922492981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27706956863403</t>
+    <t xml:space="preserve">4.27706909179688</t>
   </si>
   <si>
     <t xml:space="preserve">4.29938459396362</t>
@@ -2297,55 +2297,55 @@
     <t xml:space="preserve">4.6638650894165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74568700790405</t>
+    <t xml:space="preserve">4.74568748474121</t>
   </si>
   <si>
     <t xml:space="preserve">4.79031753540039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70105743408203</t>
+    <t xml:space="preserve">4.70105695724487</t>
   </si>
   <si>
     <t xml:space="preserve">4.67874193191528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61923456192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75312519073486</t>
+    <t xml:space="preserve">4.61923503875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75312566757202</t>
   </si>
   <si>
     <t xml:space="preserve">4.67130374908447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70849561691284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7233715057373</t>
+    <t xml:space="preserve">4.70849514007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72337198257446</t>
   </si>
   <si>
     <t xml:space="preserve">4.68618059158325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08367156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06135559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96465730667114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92746567726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48116230964661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38446354866028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37702488899231</t>
+    <t xml:space="preserve">4.0836706161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06135606765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96465754508972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92746543884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48116254806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38446378707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37702512741089</t>
   </si>
   <si>
     <t xml:space="preserve">2.7187283039093</t>
@@ -2354,13 +2354,13 @@
     <t xml:space="preserve">2.76335859298706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54020714759827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57368016242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7038516998291</t>
+    <t xml:space="preserve">2.54020690917969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57367992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70385146141052</t>
   </si>
   <si>
     <t xml:space="preserve">2.64806365966797</t>
@@ -2369,7 +2369,7 @@
     <t xml:space="preserve">2.77451610565186</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70757102966309</t>
+    <t xml:space="preserve">2.70757079124451</t>
   </si>
   <si>
     <t xml:space="preserve">2.88609194755554</t>
@@ -2378,13 +2378,13 @@
     <t xml:space="preserve">2.80798888206482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83402347564697</t>
+    <t xml:space="preserve">2.83402299880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.826584815979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68525552749634</t>
+    <t xml:space="preserve">2.68525576591492</t>
   </si>
   <si>
     <t xml:space="preserve">2.78939294815063</t>
@@ -2396,13 +2396,13 @@
     <t xml:space="preserve">2.75220108032227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70013236999512</t>
+    <t xml:space="preserve">2.7001326084137</t>
   </si>
   <si>
     <t xml:space="preserve">2.7150092124939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76707792282104</t>
+    <t xml:space="preserve">2.76707768440247</t>
   </si>
   <si>
     <t xml:space="preserve">2.73732423782349</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">2.69641304016113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60343337059021</t>
+    <t xml:space="preserve">2.60343360900879</t>
   </si>
   <si>
     <t xml:space="preserve">2.66294050216675</t>
@@ -2420,37 +2420,37 @@
     <t xml:space="preserve">2.69269394874573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62946796417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6257483959198</t>
+    <t xml:space="preserve">2.62946772575378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62574863433838</t>
   </si>
   <si>
     <t xml:space="preserve">2.64062523841858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65550208091736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61459112167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60715270042419</t>
+    <t xml:space="preserve">2.65550231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.614590883255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60715246200562</t>
   </si>
   <si>
     <t xml:space="preserve">2.63318705558777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59227585792542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55508399009705</t>
+    <t xml:space="preserve">2.59227561950684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55508375167847</t>
   </si>
   <si>
     <t xml:space="preserve">2.45466566085815</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42491245269775</t>
+    <t xml:space="preserve">2.42491221427917</t>
   </si>
   <si>
     <t xml:space="preserve">2.3951587677002</t>
@@ -2471,22 +2471,22 @@
     <t xml:space="preserve">2.25754880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44722723960876</t>
+    <t xml:space="preserve">2.44722747802734</t>
   </si>
   <si>
     <t xml:space="preserve">2.38400101661682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41747403144836</t>
+    <t xml:space="preserve">2.41747379302979</t>
   </si>
   <si>
     <t xml:space="preserve">2.41375470161438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43978881835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51417279243469</t>
+    <t xml:space="preserve">2.43978905677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51417303085327</t>
   </si>
   <si>
     <t xml:space="preserve">2.6108717918396</t>
@@ -2498,7 +2498,7 @@
     <t xml:space="preserve">2.77823543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9158456325531</t>
+    <t xml:space="preserve">2.91584539413452</t>
   </si>
   <si>
     <t xml:space="preserve">2.54392647743225</t>
@@ -2507,19 +2507,19 @@
     <t xml:space="preserve">2.54764533042908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56624150276184</t>
+    <t xml:space="preserve">2.56624174118042</t>
   </si>
   <si>
     <t xml:space="preserve">2.49929618835449</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52904963493347</t>
+    <t xml:space="preserve">2.52904987335205</t>
   </si>
   <si>
     <t xml:space="preserve">2.51045346260071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58483719825745</t>
+    <t xml:space="preserve">2.58483743667603</t>
   </si>
   <si>
     <t xml:space="preserve">2.58111834526062</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">2.63690614700317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68530631065369</t>
+    <t xml:space="preserve">2.68530678749084</t>
   </si>
   <si>
     <t xml:space="preserve">2.66147232055664</t>
@@ -2540,16 +2540,16 @@
     <t xml:space="preserve">2.62969350814819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57408094406128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51846790313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46285486221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45491027832031</t>
+    <t xml:space="preserve">2.5740807056427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51846814155579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46285510063171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45491051673889</t>
   </si>
   <si>
     <t xml:space="preserve">2.42710399627686</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">2.53435730934143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59791493415833</t>
+    <t xml:space="preserve">2.59791469573975</t>
   </si>
   <si>
     <t xml:space="preserve">2.55024671554565</t>
@@ -2576,7 +2576,7 @@
     <t xml:space="preserve">2.49463391304016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47874450683594</t>
+    <t xml:space="preserve">2.47874426841736</t>
   </si>
   <si>
     <t xml:space="preserve">2.4588828086853</t>
@@ -2585,13 +2585,13 @@
     <t xml:space="preserve">2.39929747581482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41121482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40724205970764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4429931640625</t>
+    <t xml:space="preserve">2.41121459007263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40724229812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44299340248108</t>
   </si>
   <si>
     <t xml:space="preserve">2.42313146591187</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">2.48271679878235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43902111053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57010817527771</t>
+    <t xml:space="preserve">2.43902087211609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57010841369629</t>
   </si>
   <si>
     <t xml:space="preserve">2.49860620498657</t>
@@ -2621,7 +2621,7 @@
     <t xml:space="preserve">2.3834080696106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39532518386841</t>
+    <t xml:space="preserve">2.39532542228699</t>
   </si>
   <si>
     <t xml:space="preserve">2.33176755905151</t>
@@ -2630,7 +2630,7 @@
     <t xml:space="preserve">2.37149095535278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33573985099792</t>
+    <t xml:space="preserve">2.3357400894165</t>
   </si>
   <si>
     <t xml:space="preserve">2.35560154914856</t>
@@ -2639,25 +2639,25 @@
     <t xml:space="preserve">2.44696545600891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50257873535156</t>
+    <t xml:space="preserve">2.50257849693298</t>
   </si>
   <si>
     <t xml:space="preserve">2.56613612174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52243995666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30396127700806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28409957885742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30793333053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28807163238525</t>
+    <t xml:space="preserve">2.5224404335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30396151542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28409934043884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30793356895447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28807187080383</t>
   </si>
   <si>
     <t xml:space="preserve">2.25232076644897</t>
@@ -2666,31 +2666,31 @@
     <t xml:space="preserve">2.18479084968567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14506721496582</t>
+    <t xml:space="preserve">2.1450674533844</t>
   </si>
   <si>
     <t xml:space="preserve">2.11328864097595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0576753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96631157398224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97822856903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98220086097717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08548212051392</t>
+    <t xml:space="preserve">2.05767560005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96631169319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97822892665863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98220121860504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0854823589325</t>
   </si>
   <si>
     <t xml:space="preserve">2.09342670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08150959014893</t>
+    <t xml:space="preserve">2.0815098285675</t>
   </si>
   <si>
     <t xml:space="preserve">2.15301203727722</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">2.05370330810547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2602653503418</t>
+    <t xml:space="preserve">2.26026511192322</t>
   </si>
   <si>
     <t xml:space="preserve">2.58997011184692</t>
@@ -2708,40 +2708,40 @@
     <t xml:space="preserve">2.72900223731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7131130695343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88392400741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83625555038452</t>
+    <t xml:space="preserve">2.71311283111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88392376899719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8362557888031</t>
   </si>
   <si>
     <t xml:space="preserve">2.81242156028748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77269792556763</t>
+    <t xml:space="preserve">2.77269816398621</t>
   </si>
   <si>
     <t xml:space="preserve">2.74091958999634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70119595527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82036638259888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84420013427734</t>
+    <t xml:space="preserve">2.70119571685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8203661441803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84420037269592</t>
   </si>
   <si>
     <t xml:space="preserve">2.86406207084656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84817266464233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85611748695374</t>
+    <t xml:space="preserve">2.84817290306091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85611724853516</t>
   </si>
   <si>
     <t xml:space="preserve">2.78461527824402</t>
@@ -2759,7 +2759,7 @@
     <t xml:space="preserve">2.96337080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87597918510437</t>
+    <t xml:space="preserve">2.87597894668579</t>
   </si>
   <si>
     <t xml:space="preserve">2.9514536857605</t>
@@ -2774,19 +2774,19 @@
     <t xml:space="preserve">2.78064274787903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83228325843811</t>
+    <t xml:space="preserve">2.83228349685669</t>
   </si>
   <si>
     <t xml:space="preserve">2.94748139381409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97926020622253</t>
+    <t xml:space="preserve">2.97925996780396</t>
   </si>
   <si>
     <t xml:space="preserve">2.93159198760986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86008954048157</t>
+    <t xml:space="preserve">2.86008977890015</t>
   </si>
   <si>
     <t xml:space="preserve">2.8283109664917</t>
@@ -2795,7 +2795,7 @@
     <t xml:space="preserve">2.90378570556641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93953657150269</t>
+    <t xml:space="preserve">2.93953680992126</t>
   </si>
   <si>
     <t xml:space="preserve">2.9435088634491</t>
@@ -2804,28 +2804,28 @@
     <t xml:space="preserve">2.95542621612549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97528791427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95939826965332</t>
+    <t xml:space="preserve">2.97528767585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9593985080719</t>
   </si>
   <si>
     <t xml:space="preserve">2.99912190437317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96734309196472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88789629936218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80447697639465</t>
+    <t xml:space="preserve">2.96734285354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8878960609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80447673797607</t>
   </si>
   <si>
     <t xml:space="preserve">2.82433867454529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80844950675964</t>
+    <t xml:space="preserve">2.80844926834106</t>
   </si>
   <si>
     <t xml:space="preserve">2.89186859130859</t>
@@ -2840,25 +2840,25 @@
     <t xml:space="preserve">2.98323249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02295613288879</t>
+    <t xml:space="preserve">3.02295589447021</t>
   </si>
   <si>
     <t xml:space="preserve">3.04679012298584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30896472930908</t>
+    <t xml:space="preserve">3.30896496772766</t>
   </si>
   <si>
     <t xml:space="preserve">3.17787766456604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05473470687866</t>
+    <t xml:space="preserve">3.05473494529724</t>
   </si>
   <si>
     <t xml:space="preserve">3.11829233169556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04281783103943</t>
+    <t xml:space="preserve">3.04281759262085</t>
   </si>
   <si>
     <t xml:space="preserve">3.10637521743774</t>
@@ -2867,13 +2867,13 @@
     <t xml:space="preserve">3.02692818641663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0666515827179</t>
+    <t xml:space="preserve">3.06665182113647</t>
   </si>
   <si>
     <t xml:space="preserve">3.07062411308289</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76078104972839</t>
+    <t xml:space="preserve">2.76078081130981</t>
   </si>
   <si>
     <t xml:space="preserve">2.78858757019043</t>
@@ -2891,10 +2891,10 @@
     <t xml:space="preserve">2.76872563362122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74886417388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69325137138367</t>
+    <t xml:space="preserve">2.74886393547058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69325113296509</t>
   </si>
   <si>
     <t xml:space="preserve">2.7568085193634</t>
@@ -2906,7 +2906,7 @@
     <t xml:space="preserve">2.75283622741699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81639409065247</t>
+    <t xml:space="preserve">2.81639385223389</t>
   </si>
   <si>
     <t xml:space="preserve">2.99514961242676</t>
@@ -2915,25 +2915,25 @@
     <t xml:space="preserve">3.15404343605042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07459616661072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13815426826477</t>
+    <t xml:space="preserve">3.0745964050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13815402984619</t>
   </si>
   <si>
     <t xml:space="preserve">3.0825412273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14609861373901</t>
+    <t xml:space="preserve">3.14609885215759</t>
   </si>
   <si>
     <t xml:space="preserve">3.09843063354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18582248687744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13020944595337</t>
+    <t xml:space="preserve">3.18582224845886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13020920753479</t>
   </si>
   <si>
     <t xml:space="preserve">3.25335192680359</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">3.2732138633728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29307556152344</t>
+    <t xml:space="preserve">3.29307532310486</t>
   </si>
   <si>
     <t xml:space="preserve">3.23746252059937</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">3.20965623855591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25732445716858</t>
+    <t xml:space="preserve">3.25732421875</t>
   </si>
   <si>
     <t xml:space="preserve">3.2056839466095</t>
@@ -2978,10 +2978,10 @@
     <t xml:space="preserve">3.22554564476013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19773936271667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20171189308167</t>
+    <t xml:space="preserve">3.1977391242981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20171165466309</t>
   </si>
   <si>
     <t xml:space="preserve">3.26526927947998</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">3.40827345848083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55922269821167</t>
+    <t xml:space="preserve">3.55922293663025</t>
   </si>
   <si>
     <t xml:space="preserve">3.67044830322266</t>
@@ -3011,16 +3011,16 @@
     <t xml:space="preserve">3.69031047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69428277015686</t>
+    <t xml:space="preserve">3.69428253173828</t>
   </si>
   <si>
     <t xml:space="preserve">3.66647601127625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63866972923279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51949906349182</t>
+    <t xml:space="preserve">3.63866996765137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5194993019104</t>
   </si>
   <si>
     <t xml:space="preserve">3.45594167709351</t>
@@ -3032,13 +3032,13 @@
     <t xml:space="preserve">3.49169278144836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40430116653442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45196914672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.44005250930786</t>
+    <t xml:space="preserve">3.40430092811584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45196938514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.44005227088928</t>
   </si>
   <si>
     <t xml:space="preserve">3.34074378013611</t>
@@ -3050,16 +3050,16 @@
     <t xml:space="preserve">3.26129674911499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33677101135254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32485437393188</t>
+    <t xml:space="preserve">3.33677124977112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32485413551331</t>
   </si>
   <si>
     <t xml:space="preserve">3.22157311439514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30499267578125</t>
+    <t xml:space="preserve">3.30499243736267</t>
   </si>
   <si>
     <t xml:space="preserve">3.2811586856842</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">3.08651351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18979454040527</t>
+    <t xml:space="preserve">3.18979430198669</t>
   </si>
   <si>
     <t xml:space="preserve">3.24937987327576</t>
@@ -3086,10 +3086,10 @@
     <t xml:space="preserve">3.36457800865173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37252259254456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24143481254578</t>
+    <t xml:space="preserve">3.37252235412598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24143505096436</t>
   </si>
   <si>
     <t xml:space="preserve">3.15007090568542</t>
@@ -3110,10 +3110,10 @@
     <t xml:space="preserve">3.16198801994324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07856869697571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97131562232971</t>
+    <t xml:space="preserve">3.07856893539429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97131538391113</t>
   </si>
   <si>
     <t xml:space="preserve">2.99117732048035</t>
@@ -3125,7 +3125,7 @@
     <t xml:space="preserve">3.0189836025238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31293749809265</t>
+    <t xml:space="preserve">3.31293725967407</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596031188965</t>
@@ -3134,19 +3134,19 @@
     <t xml:space="preserve">3.11432003974915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14212608337402</t>
+    <t xml:space="preserve">3.1421263217926</t>
   </si>
   <si>
     <t xml:space="preserve">3.18184995651245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17390489578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22951793670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03884553909302</t>
+    <t xml:space="preserve">3.17390513420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22951817512512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03884530067444</t>
   </si>
   <si>
     <t xml:space="preserve">3.00309419631958</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">2.87995147705078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98720455169678</t>
+    <t xml:space="preserve">2.98720502853394</t>
   </si>
   <si>
     <t xml:space="preserve">3.03487277030945</t>
@@ -3185,31 +3185,31 @@
     <t xml:space="preserve">3.28513121604919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36060523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37649464607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36854982376099</t>
+    <t xml:space="preserve">3.36060547828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37649488449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36855006217957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53141665458679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5790843963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42416286468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34868860244751</t>
+    <t xml:space="preserve">3.57908463478088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42416310310364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34868836402893</t>
   </si>
   <si>
     <t xml:space="preserve">3.35663294792175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32088208198547</t>
+    <t xml:space="preserve">3.32088184356689</t>
   </si>
   <si>
     <t xml:space="preserve">3.40032911300659</t>
@@ -3218,22 +3218,22 @@
     <t xml:space="preserve">3.39238429069519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38443946838379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46388673782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48772072792053</t>
+    <t xml:space="preserve">3.38443970680237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46388649940491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48772048950195</t>
   </si>
   <si>
     <t xml:space="preserve">3.47183108329773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54333329200745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54730606079102</t>
+    <t xml:space="preserve">3.54333353042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54730582237244</t>
   </si>
   <si>
     <t xml:space="preserve">3.55127787590027</t>
@@ -3242,7 +3242,7 @@
     <t xml:space="preserve">3.63072538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59100151062012</t>
+    <t xml:space="preserve">3.5910017490387</t>
   </si>
   <si>
     <t xml:space="preserve">3.67442107200623</t>
@@ -3251,25 +3251,25 @@
     <t xml:space="preserve">3.61086320877075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62278056144714</t>
+    <t xml:space="preserve">3.62278032302856</t>
   </si>
   <si>
     <t xml:space="preserve">3.67839336395264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65058660507202</t>
+    <t xml:space="preserve">3.6505868434906</t>
   </si>
   <si>
     <t xml:space="preserve">3.61880779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6346971988678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58702898025513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53936100006104</t>
+    <t xml:space="preserve">3.63469696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58702921867371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53936076164246</t>
   </si>
   <si>
     <t xml:space="preserve">3.55525064468384</t>
@@ -4737,6 +4737,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.49000000953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54500007629395</t>
   </si>
 </sst>
 </file>
@@ -8317,7 +8320,7 @@
         <v>6.18208885192871</v>
       </c>
       <c r="G125" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -8343,7 +8346,7 @@
         <v>6.20997905731201</v>
       </c>
       <c r="G126" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8369,7 +8372,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G127" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8395,7 +8398,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G128" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8421,7 +8424,7 @@
         <v>6.71663093566895</v>
       </c>
       <c r="G129" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8447,7 +8450,7 @@
         <v>6.48887014389038</v>
       </c>
       <c r="G130" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -8473,7 +8476,7 @@
         <v>6.24716377258301</v>
       </c>
       <c r="G131" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H131" t="s">
         <v>9</v>
@@ -8499,7 +8502,7 @@
         <v>6.19603395462036</v>
       </c>
       <c r="G132" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -8525,7 +8528,7 @@
         <v>6.40055418014526</v>
       </c>
       <c r="G133" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8551,7 +8554,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G134" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8577,7 +8580,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G135" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -8629,7 +8632,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G137" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -8655,7 +8658,7 @@
         <v>7.11172723770142</v>
       </c>
       <c r="G138" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8681,7 +8684,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G139" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8707,7 +8710,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G140" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8733,7 +8736,7 @@
         <v>7.13496780395508</v>
       </c>
       <c r="G141" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8759,7 +8762,7 @@
         <v>7.19539403915405</v>
       </c>
       <c r="G142" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8863,7 +8866,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G146" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8915,7 +8918,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G148" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8941,7 +8944,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G149" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -8967,7 +8970,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -9019,7 +9022,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G152" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -9045,7 +9048,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G153" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -9071,7 +9074,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9097,7 +9100,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G155" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9123,7 +9126,7 @@
         <v>7.05130100250244</v>
       </c>
       <c r="G156" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -9175,7 +9178,7 @@
         <v>7.13032007217407</v>
       </c>
       <c r="G158" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9201,7 +9204,7 @@
         <v>7.04200410842896</v>
       </c>
       <c r="G159" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9227,7 +9230,7 @@
         <v>7.0048189163208</v>
       </c>
       <c r="G160" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9253,7 +9256,7 @@
         <v>6.93509578704834</v>
       </c>
       <c r="G161" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9279,7 +9282,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G162" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9305,7 +9308,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G163" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9331,7 +9334,7 @@
         <v>6.78170585632324</v>
       </c>
       <c r="G164" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9357,7 +9360,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G165" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9383,7 +9386,7 @@
         <v>6.88396596908569</v>
       </c>
       <c r="G166" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9409,7 +9412,7 @@
         <v>6.87002086639404</v>
       </c>
       <c r="G167" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9435,7 +9438,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9461,7 +9464,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9487,7 +9490,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G170" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9513,7 +9516,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G171" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9539,7 +9542,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G172" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9565,7 +9568,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9591,7 +9594,7 @@
         <v>6.79565000534058</v>
       </c>
       <c r="G174" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9617,7 +9620,7 @@
         <v>6.69803810119629</v>
       </c>
       <c r="G175" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9669,7 +9672,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9695,7 +9698,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G178" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9721,7 +9724,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G179" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9747,7 +9750,7 @@
         <v>6.242516040802</v>
       </c>
       <c r="G180" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9773,7 +9776,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G181" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -9799,7 +9802,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G182" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9825,7 +9828,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9851,7 +9854,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9877,7 +9880,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9903,7 +9906,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G186" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9929,7 +9932,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G187" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9955,7 +9958,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -9981,7 +9984,7 @@
         <v>6.13095903396606</v>
       </c>
       <c r="G189" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -10007,7 +10010,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G190" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -10033,7 +10036,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -10059,7 +10062,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G192" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -10085,7 +10088,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G193" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10111,7 +10114,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G194" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10137,7 +10140,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G195" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10163,7 +10166,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10189,7 +10192,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G197" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10215,7 +10218,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G198" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10241,7 +10244,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10267,7 +10270,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10293,7 +10296,7 @@
         <v>5.99616193771362</v>
       </c>
       <c r="G201" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10319,7 +10322,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G202" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10345,7 +10348,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G203" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10371,7 +10374,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G204" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10397,7 +10400,7 @@
         <v>6.20532989501953</v>
       </c>
       <c r="G205" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10423,7 +10426,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10449,7 +10452,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10475,7 +10478,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G208" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10501,7 +10504,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10527,7 +10530,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G210" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10553,7 +10556,7 @@
         <v>6.65155601501465</v>
       </c>
       <c r="G211" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10579,7 +10582,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G212" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10605,7 +10608,7 @@
         <v>6.52140712738037</v>
       </c>
       <c r="G213" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10657,7 +10660,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10683,7 +10686,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G216" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10709,7 +10712,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10735,7 +10738,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G218" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10761,7 +10764,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10787,7 +10790,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G220" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10813,7 +10816,7 @@
         <v>6.34477615356445</v>
       </c>
       <c r="G221" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10839,7 +10842,7 @@
         <v>6.29364585876465</v>
       </c>
       <c r="G222" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10865,7 +10868,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G223" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10891,7 +10894,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10917,7 +10920,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10943,7 +10946,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -10969,7 +10972,7 @@
         <v>6.07053279876709</v>
       </c>
       <c r="G227" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -10995,7 +10998,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G228" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -11021,7 +11024,7 @@
         <v>5.74516010284424</v>
       </c>
       <c r="G229" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -11047,7 +11050,7 @@
         <v>5.88460493087769</v>
       </c>
       <c r="G230" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11073,7 +11076,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11099,7 +11102,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11125,7 +11128,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11151,7 +11154,7 @@
         <v>5.81023406982422</v>
       </c>
       <c r="G234" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11177,7 +11180,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11203,7 +11206,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11229,7 +11232,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11255,7 +11258,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11281,7 +11284,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11307,7 +11310,7 @@
         <v>6.14490413665771</v>
       </c>
       <c r="G240" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11333,7 +11336,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11359,7 +11362,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11385,7 +11388,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G243" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11411,7 +11414,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G244" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11463,7 +11466,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G246" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11541,7 +11544,7 @@
         <v>6.57718515396118</v>
       </c>
       <c r="G249" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11567,7 +11570,7 @@
         <v>6.53070402145386</v>
       </c>
       <c r="G250" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11593,7 +11596,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G251" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11619,7 +11622,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11645,7 +11648,7 @@
         <v>6.67479705810547</v>
       </c>
       <c r="G253" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11671,7 +11674,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G254" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11697,7 +11700,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11723,7 +11726,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11749,7 +11752,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G257" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11775,7 +11778,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G258" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11801,7 +11804,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G259" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11853,7 +11856,7 @@
         <v>7.05594921112061</v>
       </c>
       <c r="G261" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11879,7 +11882,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G262" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11905,7 +11908,7 @@
         <v>6.91650295257568</v>
       </c>
       <c r="G263" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11931,7 +11934,7 @@
         <v>7.00946712493896</v>
       </c>
       <c r="G264" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11957,7 +11960,7 @@
         <v>7.02341079711914</v>
       </c>
       <c r="G265" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12009,7 +12012,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G267" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12035,7 +12038,7 @@
         <v>6.94903993606567</v>
       </c>
       <c r="G268" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -12113,7 +12116,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G271" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12139,7 +12142,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G272" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12165,7 +12168,7 @@
         <v>6.82818794250488</v>
       </c>
       <c r="G273" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12191,7 +12194,7 @@
         <v>6.80494689941406</v>
       </c>
       <c r="G274" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12217,7 +12220,7 @@
         <v>6.75381708145142</v>
       </c>
       <c r="G275" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12243,7 +12246,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G276" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12269,7 +12272,7 @@
         <v>6.61901903152466</v>
       </c>
       <c r="G277" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12295,7 +12298,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12321,7 +12324,7 @@
         <v>6.47027683258057</v>
       </c>
       <c r="G279" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12347,7 +12350,7 @@
         <v>6.62831592559814</v>
       </c>
       <c r="G280" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12373,7 +12376,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G281" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12399,7 +12402,7 @@
         <v>6.57253694534302</v>
       </c>
       <c r="G282" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12425,7 +12428,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G283" t="s">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12451,7 +12454,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G284" t="s">
-        <v>225</v>
+        <v>20</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12477,7 +12480,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12503,7 +12506,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G286" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12581,7 +12584,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G289" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12607,7 +12610,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G290" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12659,7 +12662,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G292" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12685,7 +12688,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G293" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12711,7 +12714,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G294" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12737,7 +12740,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G295" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12763,7 +12766,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G296" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12789,7 +12792,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G297" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12841,7 +12844,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G299" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12893,7 +12896,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G301" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12997,7 +13000,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G305" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -13023,7 +13026,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G306" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -13049,7 +13052,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13075,7 +13078,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G308" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13153,7 +13156,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -69997,7 +70000,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6910300926</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>87888</v>
@@ -70018,6 +70021,32 @@
         <v>1574</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6912731481</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>84394</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>3.57500004768372</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>3.45000004768372</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>3.45000004768372</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>3.54500007629395</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>1575</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1576" uniqueCount="1576">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="1577">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72976970672607</t>
+    <t xml:space="preserve">4.72976922988892</t>
   </si>
   <si>
     <t xml:space="preserve">IGD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8117880821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76804494857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76531076431274</t>
+    <t xml:space="preserve">4.81178855895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76804447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7653112411499</t>
   </si>
   <si>
     <t xml:space="preserve">4.64775037765503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53839159011841</t>
+    <t xml:space="preserve">4.53839206695557</t>
   </si>
   <si>
     <t xml:space="preserve">4.56573104858398</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">4.55206108093262</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33334350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16383790969849</t>
+    <t xml:space="preserve">4.33334302902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16383743286133</t>
   </si>
   <si>
     <t xml:space="preserve">4.04627704620361</t>
@@ -83,46 +83,46 @@
     <t xml:space="preserve">3.88223838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95605564117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03807401657104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97519326210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785404205322</t>
+    <t xml:space="preserve">3.95605516433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0380744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97519397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785380363464</t>
   </si>
   <si>
     <t xml:space="preserve">3.813889503479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96425700187683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07088279724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92051458358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69632887840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78654980659485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45573878288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49948287010193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69086050987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56783151626587</t>
+    <t xml:space="preserve">3.96425724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07088232040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92051434516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69632863998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78654885292053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45573902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49948239326477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69086098670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56783199310303</t>
   </si>
   <si>
     <t xml:space="preserve">3.63891506195068</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">3.88497257232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82755923271179</t>
+    <t xml:space="preserve">3.82755970954895</t>
   </si>
   <si>
     <t xml:space="preserve">3.93691778182983</t>
@@ -140,28 +140,28 @@
     <t xml:space="preserve">3.87130260467529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05994701385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00800085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95332169532776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98612952232361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99159717559814</t>
+    <t xml:space="preserve">4.05994749069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00800132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95332193374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98613023757935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99159789085388</t>
   </si>
   <si>
     <t xml:space="preserve">4.03260707855225</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05447864532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24038887023926</t>
+    <t xml:space="preserve">4.05447816848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2403883934021</t>
   </si>
   <si>
     <t xml:space="preserve">4.21031475067139</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">4.33607769012451</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34701347351074</t>
+    <t xml:space="preserve">4.34701251983643</t>
   </si>
   <si>
     <t xml:space="preserve">4.33881139755249</t>
@@ -182,37 +182,37 @@
     <t xml:space="preserve">4.42903232574463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52745628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51105117797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46184062957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5711989402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67509031295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60947465896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54932689666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48371171951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34974765777588</t>
+    <t xml:space="preserve">4.52745580673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51105165481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46184015274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57119941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67508983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60947418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54932737350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4837121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34974718093872</t>
   </si>
   <si>
     <t xml:space="preserve">4.42083072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42356491088867</t>
+    <t xml:space="preserve">4.42356538772583</t>
   </si>
   <si>
     <t xml:space="preserve">4.2649941444397</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">4.23765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33060932159424</t>
+    <t xml:space="preserve">4.3306097984314</t>
   </si>
   <si>
     <t xml:space="preserve">4.40169286727905</t>
@@ -245,28 +245,28 @@
     <t xml:space="preserve">4.36615133285522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26772880554199</t>
+    <t xml:space="preserve">4.26772832870483</t>
   </si>
   <si>
     <t xml:space="preserve">4.32514190673828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29233407974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27046203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29506826400757</t>
+    <t xml:space="preserve">4.29233455657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27046251296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29506778717041</t>
   </si>
   <si>
     <t xml:space="preserve">4.39895868301392</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30873870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38802242279053</t>
+    <t xml:space="preserve">4.30873775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38802289962769</t>
   </si>
   <si>
     <t xml:space="preserve">4.42629909515381</t>
@@ -278,10 +278,10 @@
     <t xml:space="preserve">4.39075708389282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30326986312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49522352218628</t>
+    <t xml:space="preserve">4.30327033996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49522399902344</t>
   </si>
   <si>
     <t xml:space="preserve">4.57292604446411</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">4.66213989257812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61609363555908</t>
+    <t xml:space="preserve">4.61609315872192</t>
   </si>
   <si>
     <t xml:space="preserve">4.57580327987671</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63623905181885</t>
+    <t xml:space="preserve">4.63623857498169</t>
   </si>
   <si>
     <t xml:space="preserve">4.63048315048218</t>
@@ -317,31 +317,31 @@
     <t xml:space="preserve">4.63336086273193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6391167640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56429243087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35133028030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066656112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08368921279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95130681991577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9714527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16139125823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20168161392212</t>
+    <t xml:space="preserve">4.63911628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56429290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35133075714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08368873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95130753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97145223617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1613917350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20168113708496</t>
   </si>
   <si>
     <t xml:space="preserve">4.24772691726685</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">3.82755875587463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84482645988464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633730888367</t>
+    <t xml:space="preserve">3.8448269367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633778572083</t>
   </si>
   <si>
     <t xml:space="preserve">4.22470378875732</t>
@@ -368,7 +368,7 @@
     <t xml:space="preserve">4.15851306915283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01749801635742</t>
+    <t xml:space="preserve">4.01749849319458</t>
   </si>
   <si>
     <t xml:space="preserve">3.86784887313843</t>
@@ -386,10 +386,10 @@
     <t xml:space="preserve">4.0923228263855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25636005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40313148498535</t>
+    <t xml:space="preserve">4.25636053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40313196182251</t>
   </si>
   <si>
     <t xml:space="preserve">4.33406352996826</t>
@@ -398,142 +398,142 @@
     <t xml:space="preserve">4.5182466506958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41752147674561</t>
+    <t xml:space="preserve">4.41752099990845</t>
   </si>
   <si>
     <t xml:space="preserve">4.45493316650391</t>
   </si>
   <si>
+    <t xml:space="preserve">4.37435340881348</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.45781183242798</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53839206695557</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.52975797653198</t>
   </si>
   <si>
     <t xml:space="preserve">4.48946762084961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51536798477173</t>
+    <t xml:space="preserve">4.51536846160889</t>
   </si>
   <si>
     <t xml:space="preserve">4.25923919677734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38874244689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46644449234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3829870223999</t>
+    <t xml:space="preserve">4.38874292373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46644496917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38298654556274</t>
   </si>
   <si>
     <t xml:space="preserve">4.36571979522705</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41464328765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35996341705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33694171905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29377317428589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31391763687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19016981124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19880342483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22182607650757</t>
+    <t xml:space="preserve">4.41464281082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35996389389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33694124221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29377269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3139181137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19017028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19880390167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22182655334473</t>
   </si>
   <si>
     <t xml:space="preserve">4.26211643218994</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25348281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23046016693115</t>
+    <t xml:space="preserve">4.25348234176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23046064376831</t>
   </si>
   <si>
     <t xml:space="preserve">4.14412403106689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19592571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16714715957642</t>
+    <t xml:space="preserve">4.19592618942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16714763641357</t>
   </si>
   <si>
     <t xml:space="preserve">4.15563583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11534547805786</t>
+    <t xml:space="preserve">4.1153450012207</t>
   </si>
   <si>
     <t xml:space="preserve">4.20743703842163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14700222015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17865753173828</t>
+    <t xml:space="preserve">4.14700174331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1786584854126</t>
   </si>
   <si>
     <t xml:space="preserve">4.07505512237549</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94267392158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497139930725</t>
+    <t xml:space="preserve">3.94267320632935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497116088867</t>
   </si>
   <si>
     <t xml:space="preserve">3.79878067970276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77575755119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83907032012939</t>
+    <t xml:space="preserve">3.77575731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83907055854797</t>
   </si>
   <si>
     <t xml:space="preserve">3.74697875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74985647201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85921597480774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82468152046204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79590249061584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87936091423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81029152870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76424551010132</t>
+    <t xml:space="preserve">3.7498562335968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85921549797058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82468104362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79590201377869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87936115264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81029200553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7642457485199</t>
   </si>
   <si>
     <t xml:space="preserve">3.72971153259277</t>
@@ -545,19 +545,19 @@
     <t xml:space="preserve">3.72395586967468</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84194779396057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735283851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06354379653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10958957672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11822319030762</t>
+    <t xml:space="preserve">3.84194827079773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735331535339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06354427337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10958909988403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11822271347046</t>
   </si>
   <si>
     <t xml:space="preserve">4.08656644821167</t>
@@ -566,94 +566,94 @@
     <t xml:space="preserve">4.03764295578003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00310945510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97432971000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91389536857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93979549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92540669441223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92828440666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89662718772888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84770393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273466110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75848984718323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55704021453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64337491989136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66927623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65776467323303</t>
+    <t xml:space="preserve">4.00310897827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97432994842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91389513015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93979597091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92540645599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92828416824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89662790298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84770441055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273442268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75849056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55703997612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64337587356567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66927647590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65776443481445</t>
   </si>
   <si>
     <t xml:space="preserve">3.58006238937378</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59732985496521</t>
+    <t xml:space="preserve">3.59732961654663</t>
   </si>
   <si>
     <t xml:space="preserve">3.60308575630188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63186478614807</t>
+    <t xml:space="preserve">3.63186454772949</t>
   </si>
   <si>
     <t xml:space="preserve">3.62610840797424</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66064286231995</t>
+    <t xml:space="preserve">3.66064357757568</t>
   </si>
   <si>
     <t xml:space="preserve">3.61459732055664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80453634262085</t>
+    <t xml:space="preserve">3.80453586578369</t>
   </si>
   <si>
     <t xml:space="preserve">3.95994067192078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07217693328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0433988571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12685680389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13261222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12110185623169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36859750747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28226089477539</t>
+    <t xml:space="preserve">4.07217741012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04339933395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12685632705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13261270523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12110137939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36859798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28226137161255</t>
   </si>
   <si>
     <t xml:space="preserve">4.33981895446777</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">4.34845209121704</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33118486404419</t>
+    <t xml:space="preserve">4.33118534088135</t>
   </si>
   <si>
     <t xml:space="preserve">4.30240631103516</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">4.2275824546814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2131929397583</t>
+    <t xml:space="preserve">4.21319341659546</t>
   </si>
   <si>
     <t xml:space="preserve">4.18153667449951</t>
@@ -683,28 +683,28 @@
     <t xml:space="preserve">4.09807825088501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0059871673584</t>
+    <t xml:space="preserve">4.00598621368408</t>
   </si>
   <si>
     <t xml:space="preserve">4.10383462905884</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0290093421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06929969787598</t>
+    <t xml:space="preserve">4.02900981903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06929922103882</t>
   </si>
   <si>
     <t xml:space="preserve">4.21894788742065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30816221237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14988040924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47220087051392</t>
+    <t xml:space="preserve">4.30816173553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14987993240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4721999168396</t>
   </si>
   <si>
     <t xml:space="preserve">4.51249074935913</t>
@@ -713,19 +713,19 @@
     <t xml:space="preserve">4.37723064422607</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44342231750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59307098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62472772598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5700478553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71969652175903</t>
+    <t xml:space="preserve">4.44342184066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59307050704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62472724914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57004833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71969747543335</t>
   </si>
   <si>
     <t xml:space="preserve">4.70818567276001</t>
@@ -734,55 +734,55 @@
     <t xml:space="preserve">4.80315446853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73120832443237</t>
+    <t xml:space="preserve">4.73120784759521</t>
   </si>
   <si>
     <t xml:space="preserve">4.70530796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70242977142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64487314224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62184906005859</t>
+    <t xml:space="preserve">4.7024302482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64487266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62184953689575</t>
   </si>
   <si>
     <t xml:space="preserve">4.54702520370483</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52688026428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46068954467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6045823097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71394062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66501712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74559736251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76574277877808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74847602844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78301000595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77149868011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82329988479614</t>
+    <t xml:space="preserve">4.52687978744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46068906784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60458278656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71394109725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66501760482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74559783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76574325561523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74847555160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78301048278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77149820327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8233003616333</t>
   </si>
   <si>
     <t xml:space="preserve">4.92690324783325</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">4.98446035385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02475070953369</t>
+    <t xml:space="preserve">5.02475118637085</t>
   </si>
   <si>
     <t xml:space="preserve">5.05640745162964</t>
@@ -803,19 +803,19 @@
     <t xml:space="preserve">4.89236879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86359071731567</t>
+    <t xml:space="preserve">4.86358976364136</t>
   </si>
   <si>
     <t xml:space="preserve">4.82905578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8759241104126</t>
+    <t xml:space="preserve">4.87592363357544</t>
   </si>
   <si>
     <t xml:space="preserve">4.91160154342651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93538618087769</t>
+    <t xml:space="preserve">4.93538665771484</t>
   </si>
   <si>
     <t xml:space="preserve">4.89970874786377</t>
@@ -830,13 +830,13 @@
     <t xml:space="preserve">4.96809101104736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97106456756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89376211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94727849960327</t>
+    <t xml:space="preserve">4.9710636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89376258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94727897644043</t>
   </si>
   <si>
     <t xml:space="preserve">4.94133281707764</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">4.75105285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78672981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73321437835693</t>
+    <t xml:space="preserve">4.78673076629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73321485519409</t>
   </si>
   <si>
     <t xml:space="preserve">4.66185855865479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53401517868042</t>
+    <t xml:space="preserve">4.5340142250061</t>
   </si>
   <si>
     <t xml:space="preserve">4.58455753326416</t>
@@ -878,25 +878,25 @@
     <t xml:space="preserve">4.61726236343384</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70348310470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72132110595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63807392120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72726726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81646108627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83132743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9383602142334</t>
+    <t xml:space="preserve">4.70348262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72132158279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63807439804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72726678848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81646203994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83132696151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93835926055908</t>
   </si>
   <si>
     <t xml:space="preserve">4.94430589675903</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">4.9829568862915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95322513580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90565538406372</t>
+    <t xml:space="preserve">4.95322561264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9056544303894</t>
   </si>
   <si>
     <t xml:space="preserve">4.84619283676147</t>
@@ -920,10 +920,10 @@
     <t xml:space="preserve">5.00376796722412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05431175231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04836511611938</t>
+    <t xml:space="preserve">5.05431079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04836559295654</t>
   </si>
   <si>
     <t xml:space="preserve">4.99782180786133</t>
@@ -932,13 +932,13 @@
     <t xml:space="preserve">4.98592948913574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15837049484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12566661834717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11080121994019</t>
+    <t xml:space="preserve">5.15837097167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12566709518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11080074310303</t>
   </si>
   <si>
     <t xml:space="preserve">5.07512283325195</t>
@@ -947,28 +947,28 @@
     <t xml:space="preserve">5.0810694694519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09593534469604</t>
+    <t xml:space="preserve">5.09593486785889</t>
   </si>
   <si>
     <t xml:space="preserve">5.11377429962158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03944492340088</t>
+    <t xml:space="preserve">5.0394458770752</t>
   </si>
   <si>
     <t xml:space="preserve">5.02755308151245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97701025009155</t>
+    <t xml:space="preserve">4.97701072692871</t>
   </si>
   <si>
     <t xml:space="preserve">5.05133867263794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99484872817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01566076278687</t>
+    <t xml:space="preserve">4.99484825134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01566123962402</t>
   </si>
   <si>
     <t xml:space="preserve">5.06620407104492</t>
@@ -977,19 +977,19 @@
     <t xml:space="preserve">5.13755941390991</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23269844055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24459075927734</t>
+    <t xml:space="preserve">5.23269891738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2445912361145</t>
   </si>
   <si>
     <t xml:space="preserve">5.23864555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19702196121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17323684692383</t>
+    <t xml:space="preserve">5.197021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17323637008667</t>
   </si>
   <si>
     <t xml:space="preserve">5.1851282119751</t>
@@ -1001,82 +1001,82 @@
     <t xml:space="preserve">5.1940484046936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2475643157959</t>
+    <t xml:space="preserve">5.24756383895874</t>
   </si>
   <si>
     <t xml:space="preserve">5.25053739547729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26242971420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1494517326355</t>
+    <t xml:space="preserve">5.26243019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14945077896118</t>
   </si>
   <si>
     <t xml:space="preserve">5.16431713104248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21485948562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35162448883057</t>
+    <t xml:space="preserve">5.21485900878906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35162401199341</t>
   </si>
   <si>
     <t xml:space="preserve">5.44081687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64893674850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6786675453186</t>
+    <t xml:space="preserve">5.64893627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67866706848145</t>
   </si>
   <si>
     <t xml:space="preserve">5.47054815292358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46757555007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55974197387695</t>
+    <t xml:space="preserve">5.46757507324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55974292755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.59541940689087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58947420120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5032525062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57758140563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75002193450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90165233612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91651725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20193767547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19004535675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11274385452271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12463665008545</t>
+    <t xml:space="preserve">5.58947467803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50325298309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57758092880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75002288818359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90165185928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91651773452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20193719863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19004487991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11274433135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12463617324829</t>
   </si>
   <si>
     <t xml:space="preserve">6.15436744689941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03544235229492</t>
+    <t xml:space="preserve">6.03544139862061</t>
   </si>
   <si>
     <t xml:space="preserve">5.97598028182983</t>
@@ -1088,10 +1088,10 @@
     <t xml:space="preserve">6.00571155548096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29113101959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34464836120605</t>
+    <t xml:space="preserve">6.29113054275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3446478843689</t>
   </si>
   <si>
     <t xml:space="preserve">6.17815256118774</t>
@@ -1100,67 +1100,67 @@
     <t xml:space="preserve">6.39816379547119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38627099990845</t>
+    <t xml:space="preserve">6.38627147674561</t>
   </si>
   <si>
     <t xml:space="preserve">6.33275461196899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43384027481079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46951818466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41600227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40410995483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24356079101562</t>
+    <t xml:space="preserve">6.43384075164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46951866149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41600275039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40410900115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24356126785278</t>
   </si>
   <si>
     <t xml:space="preserve">6.35653972625732</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44573402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6003360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58844327926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71926021575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65979862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48141050338745</t>
+    <t xml:space="preserve">6.44573354721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60033655166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58844470977783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71926164627075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65979766845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48141098022461</t>
   </si>
   <si>
     <t xml:space="preserve">6.07111978530884</t>
   </si>
   <si>
-    <t xml:space="preserve">5.82732439041138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76786088943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80948495864868</t>
+    <t xml:space="preserve">5.82732391357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76786041259766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80948448181152</t>
   </si>
   <si>
     <t xml:space="preserve">5.681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73812913894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81840419769287</t>
+    <t xml:space="preserve">5.73812961578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81840372085571</t>
   </si>
   <si>
     <t xml:space="preserve">5.7321834564209</t>
@@ -1169,25 +1169,25 @@
     <t xml:space="preserve">5.72623682022095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85705471038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86300182342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.95814180374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92840909957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76191520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79759168624878</t>
+    <t xml:space="preserve">5.85705518722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86300134658813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95814085006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92841005325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76191568374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70839881896973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79759216308594</t>
   </si>
   <si>
     <t xml:space="preserve">5.75596857070923</t>
@@ -1196,16 +1196,16 @@
     <t xml:space="preserve">5.6846137046814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69650650024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66082906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50622653961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45865678787231</t>
+    <t xml:space="preserve">5.69650602340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66082811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50622701644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45865631103516</t>
   </si>
   <si>
     <t xml:space="preserve">5.33973121643066</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">5.15539693832397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.3100004196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0364727973938</t>
+    <t xml:space="preserve">5.30999994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03647232055664</t>
   </si>
   <si>
     <t xml:space="preserve">4.91754722595215</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">5.00079536437988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86997699737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85213947296143</t>
+    <t xml:space="preserve">4.86997747421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85213899612427</t>
   </si>
   <si>
     <t xml:space="preserve">5.14350509643555</t>
@@ -1241,37 +1241,37 @@
     <t xml:space="preserve">4.7944598197937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70823955535889</t>
+    <t xml:space="preserve">4.70824003219604</t>
   </si>
   <si>
     <t xml:space="preserve">4.58812522888184</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47752523422241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46860551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53104114532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66483211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66839981079102</t>
+    <t xml:space="preserve">4.47752618789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46860599517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53104209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66483163833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66839933395386</t>
   </si>
   <si>
     <t xml:space="preserve">4.55482625961304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49774169921875</t>
+    <t xml:space="preserve">4.49774265289307</t>
   </si>
   <si>
     <t xml:space="preserve">4.51260805130005</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41211605072021</t>
+    <t xml:space="preserve">4.41211652755737</t>
   </si>
   <si>
     <t xml:space="preserve">4.36811399459839</t>
@@ -1286,7 +1286,7 @@
     <t xml:space="preserve">4.46503829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4418478012085</t>
+    <t xml:space="preserve">4.44184732437134</t>
   </si>
   <si>
     <t xml:space="preserve">4.29378652572632</t>
@@ -1304,19 +1304,19 @@
     <t xml:space="preserve">5.1029748916626</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85351896286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95713949203491</t>
+    <t xml:space="preserve">4.85351943969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95713901519775</t>
   </si>
   <si>
     <t xml:space="preserve">5.14391183853149</t>
   </si>
   <si>
-    <t xml:space="preserve">5.34731340408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28271055221558</t>
+    <t xml:space="preserve">5.34731388092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28271102905273</t>
   </si>
   <si>
     <t xml:space="preserve">5.17781209945679</t>
@@ -1331,7 +1331,7 @@
     <t xml:space="preserve">5.05244445800781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98912143707275</t>
+    <t xml:space="preserve">4.9891209602356</t>
   </si>
   <si>
     <t xml:space="preserve">4.94498634338379</t>
@@ -1364,16 +1364,16 @@
     <t xml:space="preserve">5.02557945251465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04029178619385</t>
+    <t xml:space="preserve">5.04029130935669</t>
   </si>
   <si>
     <t xml:space="preserve">5.02110242843628</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11704730987549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0594801902771</t>
+    <t xml:space="preserve">5.11704778671265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05947971343994</t>
   </si>
   <si>
     <t xml:space="preserve">5.06971406936646</t>
@@ -1382,28 +1382,28 @@
     <t xml:space="preserve">5.24497270584106</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14135265350342</t>
+    <t xml:space="preserve">5.14135313034058</t>
   </si>
   <si>
     <t xml:space="preserve">4.97888708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7646107673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83496952056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78124094009399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73326826095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71471881866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66290855407715</t>
+    <t xml:space="preserve">4.76461029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83496999740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78124046325684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73326873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71471834182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66290950775146</t>
   </si>
   <si>
     <t xml:space="preserve">4.55097341537476</t>
@@ -1412,16 +1412,16 @@
     <t xml:space="preserve">4.32710313796997</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57400035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65267467498779</t>
+    <t xml:space="preserve">4.57399988174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65267562866211</t>
   </si>
   <si>
     <t xml:space="preserve">4.63092708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72943115234375</t>
+    <t xml:space="preserve">4.72943067550659</t>
   </si>
   <si>
     <t xml:space="preserve">4.81961870193481</t>
@@ -1430,16 +1430,16 @@
     <t xml:space="preserve">4.79403352737427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68401670455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58679294586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8741979598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99108505249023</t>
+    <t xml:space="preserve">4.68401718139648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58679246902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87419843673706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99108457565308</t>
   </si>
   <si>
     <t xml:space="preserve">4.88932466506958</t>
@@ -1448,37 +1448,37 @@
     <t xml:space="preserve">4.9842095375061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03165149688721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79375267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79512691497803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76074838638306</t>
+    <t xml:space="preserve">5.03165245056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79375219345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79512739181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76074886322021</t>
   </si>
   <si>
     <t xml:space="preserve">4.74630975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86113405227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79031467437744</t>
+    <t xml:space="preserve">4.86113452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79031419754028</t>
   </si>
   <si>
     <t xml:space="preserve">4.81300401687622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72705745697021</t>
+    <t xml:space="preserve">4.72705793380737</t>
   </si>
   <si>
     <t xml:space="preserve">4.77174997329712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73187065124512</t>
+    <t xml:space="preserve">4.73187112808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.84532022476196</t>
@@ -1487,13 +1487,13 @@
     <t xml:space="preserve">4.78687620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76968669891357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91614055633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97802066802979</t>
+    <t xml:space="preserve">4.76968717575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91614007949829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97802114486694</t>
   </si>
   <si>
     <t xml:space="preserve">4.96770763397217</t>
@@ -1508,34 +1508,34 @@
     <t xml:space="preserve">4.86044645309448</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89963817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93470430374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99177360534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05434226989746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96151971817017</t>
+    <t xml:space="preserve">4.8996376991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93470478057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99177265167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0543417930603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96152019500732</t>
   </si>
   <si>
     <t xml:space="preserve">4.97939682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99246025085449</t>
+    <t xml:space="preserve">4.99246072769165</t>
   </si>
   <si>
     <t xml:space="preserve">4.8583836555481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98489713668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85219573974609</t>
+    <t xml:space="preserve">4.98489761352539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85219621658325</t>
   </si>
   <si>
     <t xml:space="preserve">4.903076171875</t>
@@ -1544,25 +1544,25 @@
     <t xml:space="preserve">4.97183322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93882989883423</t>
+    <t xml:space="preserve">4.93883037567139</t>
   </si>
   <si>
     <t xml:space="preserve">4.91682767868042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83363151550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76556205749512</t>
+    <t xml:space="preserve">4.83363199234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76556158065796</t>
   </si>
   <si>
     <t xml:space="preserve">4.75868606567383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75043487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67067718505859</t>
+    <t xml:space="preserve">4.75043535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.58129262924194</t>
@@ -1571,7 +1571,7 @@
     <t xml:space="preserve">4.5427885055542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46303033828735</t>
+    <t xml:space="preserve">4.4630298614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.48228216171265</t>
@@ -1580,13 +1580,13 @@
     <t xml:space="preserve">4.51941108703613</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60604524612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59779405593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52972412109375</t>
+    <t xml:space="preserve">4.60604476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59779357910156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52972459793091</t>
   </si>
   <si>
     <t xml:space="preserve">4.5379753112793</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">4.57235383987427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55241441726685</t>
+    <t xml:space="preserve">4.55241394042969</t>
   </si>
   <si>
     <t xml:space="preserve">4.50634670257568</t>
@@ -1613,7 +1613,7 @@
     <t xml:space="preserve">4.49053239822388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52078628540039</t>
+    <t xml:space="preserve">4.52078580856323</t>
   </si>
   <si>
     <t xml:space="preserve">4.51872301101685</t>
@@ -1622,16 +1622,16 @@
     <t xml:space="preserve">4.5304126739502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51047277450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52491140365601</t>
+    <t xml:space="preserve">4.51047229766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52491188049316</t>
   </si>
   <si>
     <t xml:space="preserve">4.485032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47746896743774</t>
+    <t xml:space="preserve">4.47746849060059</t>
   </si>
   <si>
     <t xml:space="preserve">4.78412580490112</t>
@@ -1640,7 +1640,7 @@
     <t xml:space="preserve">4.6651759147644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6541748046875</t>
+    <t xml:space="preserve">4.65417528152466</t>
   </si>
   <si>
     <t xml:space="preserve">4.70299291610718</t>
@@ -1652,19 +1652,19 @@
     <t xml:space="preserve">4.71055555343628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64661169052124</t>
+    <t xml:space="preserve">4.64661121368408</t>
   </si>
   <si>
     <t xml:space="preserve">4.63354778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5503511428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50840997695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41558742523193</t>
+    <t xml:space="preserve">4.55035161972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50840950012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41558790206909</t>
   </si>
   <si>
     <t xml:space="preserve">4.42727613449097</t>
@@ -1679,28 +1679,28 @@
     <t xml:space="preserve">4.22237968444824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20450258255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16256046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06630086898804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09311676025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98791742324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05942535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09724187850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0497989654541</t>
+    <t xml:space="preserve">4.20450305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16256141662598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0663013458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09311580657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98791766166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05942487716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09724235534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04979848861694</t>
   </si>
   <si>
     <t xml:space="preserve">4.05323696136475</t>
@@ -1709,13 +1709,13 @@
     <t xml:space="preserve">4.10480499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09105348587036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08830308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13162040710449</t>
+    <t xml:space="preserve">4.0910530090332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.088303565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13161993026733</t>
   </si>
   <si>
     <t xml:space="preserve">4.21962976455688</t>
@@ -1733,22 +1733,22 @@
     <t xml:space="preserve">4.22100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15293455123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36608219146729</t>
+    <t xml:space="preserve">4.15293550491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36608171463013</t>
   </si>
   <si>
     <t xml:space="preserve">4.27601051330566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2251296043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19487714767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12749481201172</t>
+    <t xml:space="preserve">4.22513008117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1948766708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12749433517456</t>
   </si>
   <si>
     <t xml:space="preserve">4.15224742889404</t>
@@ -1778,76 +1778,76 @@
     <t xml:space="preserve">4.23544359207153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19900226593018</t>
+    <t xml:space="preserve">4.19900274276733</t>
   </si>
   <si>
     <t xml:space="preserve">4.1886887550354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11374282836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04429864883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02917194366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99273061752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99891877174377</t>
+    <t xml:space="preserve">4.1137433052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04429817199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02917242050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99273085594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9989185333252</t>
   </si>
   <si>
     <t xml:space="preserve">3.96316480636597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88684511184692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.982417345047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90540885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87378072738647</t>
+    <t xml:space="preserve">3.88684439659119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98241710662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90540909767151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8737804889679</t>
   </si>
   <si>
     <t xml:space="preserve">3.78164601325989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71013879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69501256942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73351573944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72870302200317</t>
+    <t xml:space="preserve">3.71013832092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69501233100891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7335159778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72870278358459</t>
   </si>
   <si>
     <t xml:space="preserve">3.64894485473633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70051264762878</t>
+    <t xml:space="preserve">3.70051288604736</t>
   </si>
   <si>
     <t xml:space="preserve">3.83115100860596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89990878105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99341869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97829151153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06286334991455</t>
+    <t xml:space="preserve">3.89990854263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9934184551239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97829127311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06286239624023</t>
   </si>
   <si>
     <t xml:space="preserve">4.04842376708984</t>
@@ -1859,19 +1859,19 @@
     <t xml:space="preserve">4.04292345046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99548029899597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95491433143616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04086112976074</t>
+    <t xml:space="preserve">3.99548101425171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95491409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04086065292358</t>
   </si>
   <si>
     <t xml:space="preserve">4.02160835266113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05804967880249</t>
+    <t xml:space="preserve">4.05805015563965</t>
   </si>
   <si>
     <t xml:space="preserve">4.01335763931274</t>
@@ -1880,19 +1880,19 @@
     <t xml:space="preserve">3.97004103660583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07180166244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11786890029907</t>
+    <t xml:space="preserve">4.07180118560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11786842346191</t>
   </si>
   <si>
     <t xml:space="preserve">4.22788047790527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31863975524902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2890739440918</t>
+    <t xml:space="preserve">4.31864023208618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28907346725464</t>
   </si>
   <si>
     <t xml:space="preserve">4.29044914245605</t>
@@ -1901,19 +1901,19 @@
     <t xml:space="preserve">4.25057029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24919462203979</t>
+    <t xml:space="preserve">4.24919509887695</t>
   </si>
   <si>
     <t xml:space="preserve">4.2698221206665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26294708251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24231910705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13643264770508</t>
+    <t xml:space="preserve">4.26294660568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24231958389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13643312454224</t>
   </si>
   <si>
     <t xml:space="preserve">4.05392456054688</t>
@@ -1922,19 +1922,19 @@
     <t xml:space="preserve">4.12543249130249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08967876434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13230752944946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17149925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23819398880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22169208526611</t>
+    <t xml:space="preserve">4.0896782875061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13230800628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17149972915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23819351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22169256210327</t>
   </si>
   <si>
     <t xml:space="preserve">4.2189416885376</t>
@@ -1958,10 +1958,10 @@
     <t xml:space="preserve">4.33720445632935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37433290481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50359678268433</t>
+    <t xml:space="preserve">4.37433338165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50359630584717</t>
   </si>
   <si>
     <t xml:space="preserve">4.57441663742065</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">4.47609376907349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44171571731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4485912322998</t>
+    <t xml:space="preserve">4.44171524047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44859027862549</t>
   </si>
   <si>
     <t xml:space="preserve">4.55653953552246</t>
@@ -1994,13 +1994,13 @@
     <t xml:space="preserve">4.57097864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57166624069214</t>
+    <t xml:space="preserve">4.57166719436646</t>
   </si>
   <si>
     <t xml:space="preserve">4.5077223777771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45752954483032</t>
+    <t xml:space="preserve">4.45752906799316</t>
   </si>
   <si>
     <t xml:space="preserve">4.41971302032471</t>
@@ -2009,7 +2009,7 @@
     <t xml:space="preserve">4.46234226226807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4279637336731</t>
+    <t xml:space="preserve">4.42796421051025</t>
   </si>
   <si>
     <t xml:space="preserve">4.54485082626343</t>
@@ -2030,16 +2030,16 @@
     <t xml:space="preserve">4.48296928405762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53109979629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56547737121582</t>
+    <t xml:space="preserve">4.53109931945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56547784805298</t>
   </si>
   <si>
     <t xml:space="preserve">4.59985685348511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64111042022705</t>
+    <t xml:space="preserve">4.64111089706421</t>
   </si>
   <si>
     <t xml:space="preserve">4.61360836029053</t>
@@ -2054,16 +2054,16 @@
     <t xml:space="preserve">4.71674394607544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65486240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49672079086304</t>
+    <t xml:space="preserve">4.65486288070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4967212677002</t>
   </si>
   <si>
     <t xml:space="preserve">4.5522894859314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61179637908936</t>
+    <t xml:space="preserve">4.6117959022522</t>
   </si>
   <si>
     <t xml:space="preserve">4.60435819625854</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">4.62667322158813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6936182975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73824882507324</t>
+    <t xml:space="preserve">4.69361877441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73824834823608</t>
   </si>
   <si>
     <t xml:space="preserve">4.71593379974365</t>
@@ -2090,16 +2090,16 @@
     <t xml:space="preserve">4.58948135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51509761810303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57460451126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56716537475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55972766876221</t>
+    <t xml:space="preserve">4.51509809494019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57460403442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56716632843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55972814559937</t>
   </si>
   <si>
     <t xml:space="preserve">4.64898824691772</t>
@@ -2108,43 +2108,43 @@
     <t xml:space="preserve">4.64155006408691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52997398376465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4481520652771</t>
+    <t xml:space="preserve">4.58204221725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52997446060181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44815158843994</t>
   </si>
   <si>
     <t xml:space="preserve">4.38120651245117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42583656311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37376832962036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4183988571167</t>
+    <t xml:space="preserve">4.42583703994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3737678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41839838027954</t>
   </si>
   <si>
     <t xml:space="preserve">4.35889148712158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32913827896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32169961929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31426095962524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33657646179199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59691905975342</t>
+    <t xml:space="preserve">4.32913780212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32169914245605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3142614364624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33657598495483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59691953659058</t>
   </si>
   <si>
     <t xml:space="preserve">4.50765895843506</t>
@@ -2153,19 +2153,19 @@
     <t xml:space="preserve">4.49278211593628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48534440994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43327474594116</t>
+    <t xml:space="preserve">4.48534393310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43327522277832</t>
   </si>
   <si>
     <t xml:space="preserve">4.40352201461792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38864517211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39608287811279</t>
+    <t xml:space="preserve">4.3886456489563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39608335494995</t>
   </si>
   <si>
     <t xml:space="preserve">4.35145330429077</t>
@@ -2195,34 +2195,34 @@
     <t xml:space="preserve">3.93490362167358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90514993667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95721888542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89771175384521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98697209358215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92002654075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94234180450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97953367233276</t>
+    <t xml:space="preserve">3.9051501750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95721912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89771151542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98697257041931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9200267791748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94234204292297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97953391075134</t>
   </si>
   <si>
     <t xml:space="preserve">3.97209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04647970199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06879472732544</t>
+    <t xml:space="preserve">4.04647922515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06879425048828</t>
   </si>
   <si>
     <t xml:space="preserve">4.098548412323</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">4.17293167114258</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11342477798462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14317846298218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1283016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15805530548096</t>
+    <t xml:space="preserve">4.11342525482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14317798614502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12830209732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1580548286438</t>
   </si>
   <si>
     <t xml:space="preserve">4.03904104232788</t>
@@ -2258,55 +2258,55 @@
     <t xml:space="preserve">4.2324390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23987674713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26963043212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30682229995728</t>
+    <t xml:space="preserve">4.23987722396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26963090896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30682277679443</t>
   </si>
   <si>
     <t xml:space="preserve">4.29194593429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2621922492981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27706861495972</t>
+    <t xml:space="preserve">4.26219272613525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27706956863403</t>
   </si>
   <si>
     <t xml:space="preserve">4.29938459396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28450775146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41096019744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44071388244629</t>
+    <t xml:space="preserve">4.28450727462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41095972061157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44071340560913</t>
   </si>
   <si>
     <t xml:space="preserve">4.46302843093872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47046709060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45559024810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6638650894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74568748474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79031753540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70105743408203</t>
+    <t xml:space="preserve">4.47046756744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45558977127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66386461257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74568700790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79031801223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70105695724487</t>
   </si>
   <si>
     <t xml:space="preserve">4.67874193191528</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">4.61923456192017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75312519073486</t>
+    <t xml:space="preserve">4.75312566757202</t>
   </si>
   <si>
     <t xml:space="preserve">4.67130374908447</t>
@@ -2324,10 +2324,10 @@
     <t xml:space="preserve">4.70849561691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337198257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68618011474609</t>
+    <t xml:space="preserve">4.7233715057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68618059158325</t>
   </si>
   <si>
     <t xml:space="preserve">4.08367109298706</t>
@@ -2345,34 +2345,34 @@
     <t xml:space="preserve">3.48116254806519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38446354866028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37702488899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7187283039093</t>
+    <t xml:space="preserve">3.38446378707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37702512741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71872854232788</t>
   </si>
   <si>
     <t xml:space="preserve">2.76335859298706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54020714759827</t>
+    <t xml:space="preserve">2.54020738601685</t>
   </si>
   <si>
     <t xml:space="preserve">2.57367992401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70385146141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64806389808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77451610565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70757102966309</t>
+    <t xml:space="preserve">2.7038516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64806365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77451634407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70757079124451</t>
   </si>
   <si>
     <t xml:space="preserve">2.88609194755554</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">2.80798888206482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83402347564697</t>
+    <t xml:space="preserve">2.83402323722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.826584815979</t>
@@ -2399,25 +2399,25 @@
     <t xml:space="preserve">2.75220084190369</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70013236999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71500897407532</t>
+    <t xml:space="preserve">2.7001326084137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71500945091248</t>
   </si>
   <si>
     <t xml:space="preserve">2.76707792282104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73732423782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69641304016113</t>
+    <t xml:space="preserve">2.73732447624207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69641327857971</t>
   </si>
   <si>
     <t xml:space="preserve">2.60343337059021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66294050216675</t>
+    <t xml:space="preserve">2.66294026374817</t>
   </si>
   <si>
     <t xml:space="preserve">2.69269394874573</t>
@@ -2432,19 +2432,19 @@
     <t xml:space="preserve">2.64062547683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65550184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61459136009216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60715246200562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63318705558777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59227585792542</t>
+    <t xml:space="preserve">2.65550208091736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61459112167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60715270042419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63318681716919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59227561950684</t>
   </si>
   <si>
     <t xml:space="preserve">2.55508399009705</t>
@@ -2456,43 +2456,43 @@
     <t xml:space="preserve">2.42491221427917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3951587677002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40259695053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46954250335693</t>
+    <t xml:space="preserve">2.39515900611877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40259718894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46954226493835</t>
   </si>
   <si>
     <t xml:space="preserve">2.33937096595764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23523354530334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25754880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44722747802734</t>
+    <t xml:space="preserve">2.23523378372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25754904747009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44722723960876</t>
   </si>
   <si>
     <t xml:space="preserve">2.38400101661682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41747379302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41375470161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43978881835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51417303085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61087203025818</t>
+    <t xml:space="preserve">2.41747403144836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41375494003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43978905677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51417279243469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6108717918396</t>
   </si>
   <si>
     <t xml:space="preserve">2.61831021308899</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">2.54764556884766</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56624150276184</t>
+    <t xml:space="preserve">2.56624174118042</t>
   </si>
   <si>
     <t xml:space="preserve">2.49929618835449</t>
@@ -2522,40 +2522,40 @@
     <t xml:space="preserve">2.51045346260071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58483719825745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58111834526062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5997142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63690614700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68530654907227</t>
+    <t xml:space="preserve">2.58483743667603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58111810684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59971404075623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63690638542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68530631065369</t>
   </si>
   <si>
     <t xml:space="preserve">2.66147232055664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62969374656677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5740807056427</t>
+    <t xml:space="preserve">2.62969350814819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57408094406128</t>
   </si>
   <si>
     <t xml:space="preserve">2.51846790313721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46285510063171</t>
+    <t xml:space="preserve">2.46285486221313</t>
   </si>
   <si>
     <t xml:space="preserve">2.45491027832031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42710375785828</t>
+    <t xml:space="preserve">2.42710399627686</t>
   </si>
   <si>
     <t xml:space="preserve">2.51052331924438</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">2.47079968452454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49066162109375</t>
+    <t xml:space="preserve">2.49066138267517</t>
   </si>
   <si>
     <t xml:space="preserve">2.53435730934143</t>
@@ -2588,13 +2588,13 @@
     <t xml:space="preserve">2.39929747581482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41121459007263</t>
+    <t xml:space="preserve">2.41121482849121</t>
   </si>
   <si>
     <t xml:space="preserve">2.40724205970764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44299340248108</t>
+    <t xml:space="preserve">2.4429931640625</t>
   </si>
   <si>
     <t xml:space="preserve">2.42313146591187</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">2.5144956111908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48271703720093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43902087211609</t>
+    <t xml:space="preserve">2.48271679878235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43902111053467</t>
   </si>
   <si>
     <t xml:space="preserve">2.57010817527771</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">2.37149095535278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3357400894165</t>
+    <t xml:space="preserve">2.33573985099792</t>
   </si>
   <si>
     <t xml:space="preserve">2.35560154914856</t>
@@ -2645,19 +2645,19 @@
     <t xml:space="preserve">2.50257873535156</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5661358833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52244019508362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30396103858948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28409934043884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30793356895447</t>
+    <t xml:space="preserve">2.56613612174988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52243995666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30396127700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28409957885742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30793333053589</t>
   </si>
   <si>
     <t xml:space="preserve">2.28807163238525</t>
@@ -2675,7 +2675,7 @@
     <t xml:space="preserve">2.11328864097595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05767560005188</t>
+    <t xml:space="preserve">2.0576753616333</t>
   </si>
   <si>
     <t xml:space="preserve">1.96631157398224</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">1.97822856903076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98220109939575</t>
+    <t xml:space="preserve">1.98220086097717</t>
   </si>
   <si>
     <t xml:space="preserve">2.08548212051392</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">2.77269792556763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74091935157776</t>
+    <t xml:space="preserve">2.74091958999634</t>
   </si>
   <si>
     <t xml:space="preserve">2.70119595527649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8203661441803</t>
+    <t xml:space="preserve">2.82036638259888</t>
   </si>
   <si>
     <t xml:space="preserve">2.84420013427734</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">2.87200665473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85214519500732</t>
+    <t xml:space="preserve">2.85214495658875</t>
   </si>
   <si>
     <t xml:space="preserve">2.93556427955627</t>
@@ -2777,10 +2777,10 @@
     <t xml:space="preserve">2.78064274787903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83228349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94748163223267</t>
+    <t xml:space="preserve">2.83228325843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94748139381409</t>
   </si>
   <si>
     <t xml:space="preserve">2.97926020622253</t>
@@ -2789,13 +2789,13 @@
     <t xml:space="preserve">2.93159198760986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86008977890015</t>
+    <t xml:space="preserve">2.86008954048157</t>
   </si>
   <si>
     <t xml:space="preserve">2.8283109664917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90378546714783</t>
+    <t xml:space="preserve">2.90378570556641</t>
   </si>
   <si>
     <t xml:space="preserve">2.93953657150269</t>
@@ -2807,19 +2807,19 @@
     <t xml:space="preserve">2.95542621612549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97528767585754</t>
+    <t xml:space="preserve">2.97528791427612</t>
   </si>
   <si>
     <t xml:space="preserve">2.95939826965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99912214279175</t>
+    <t xml:space="preserve">2.99912190437317</t>
   </si>
   <si>
     <t xml:space="preserve">2.96734309196472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8878960609436</t>
+    <t xml:space="preserve">2.88789629936218</t>
   </si>
   <si>
     <t xml:space="preserve">2.80447697639465</t>
@@ -2849,7 +2849,7 @@
     <t xml:space="preserve">3.04679012298584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30896496772766</t>
+    <t xml:space="preserve">3.30896472930908</t>
   </si>
   <si>
     <t xml:space="preserve">3.17787766456604</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">3.11829233169556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04281759262085</t>
+    <t xml:space="preserve">3.04281783103943</t>
   </si>
   <si>
     <t xml:space="preserve">3.10637521743774</t>
@@ -2885,7 +2885,7 @@
     <t xml:space="preserve">2.84022808074951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79256010055542</t>
+    <t xml:space="preserve">2.79255986213684</t>
   </si>
   <si>
     <t xml:space="preserve">2.80050468444824</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">2.76872563362122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74886393547058</t>
+    <t xml:space="preserve">2.74886417388916</t>
   </si>
   <si>
     <t xml:space="preserve">2.69325137138367</t>
@@ -2924,13 +2924,13 @@
     <t xml:space="preserve">3.13815426826477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08254098892212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14609885215759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09843039512634</t>
+    <t xml:space="preserve">3.0825412273407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14609861373901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09843063354492</t>
   </si>
   <si>
     <t xml:space="preserve">3.18582248687744</t>
@@ -2939,19 +2939,19 @@
     <t xml:space="preserve">3.13020944595337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25335216522217</t>
+    <t xml:space="preserve">3.25335192680359</t>
   </si>
   <si>
     <t xml:space="preserve">3.26924133300781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30102062225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3288266658783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3963565826416</t>
+    <t xml:space="preserve">3.30102038383484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32882690429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39635682106018</t>
   </si>
   <si>
     <t xml:space="preserve">3.2732138633728</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">3.29307556152344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23746228218079</t>
+    <t xml:space="preserve">3.23746252059937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23349046707153</t>
@@ -2972,22 +2972,22 @@
     <t xml:space="preserve">3.25732445716858</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20568370819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21362853050232</t>
+    <t xml:space="preserve">3.2056839466095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2136287689209</t>
   </si>
   <si>
     <t xml:space="preserve">3.22554564476013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1977391242981</t>
+    <t xml:space="preserve">3.19773936271667</t>
   </si>
   <si>
     <t xml:space="preserve">3.20171189308167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2652690410614</t>
+    <t xml:space="preserve">3.26526927947998</t>
   </si>
   <si>
     <t xml:space="preserve">3.31690979003906</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">3.55922269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67044878005981</t>
+    <t xml:space="preserve">3.67044830322266</t>
   </si>
   <si>
     <t xml:space="preserve">3.69031047821045</t>
@@ -3020,7 +3020,7 @@
     <t xml:space="preserve">3.66647601127625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63866925239563</t>
+    <t xml:space="preserve">3.63866972923279</t>
   </si>
   <si>
     <t xml:space="preserve">3.51949906349182</t>
@@ -3035,7 +3035,7 @@
     <t xml:space="preserve">3.49169278144836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40430092811584</t>
+    <t xml:space="preserve">3.40430116653442</t>
   </si>
   <si>
     <t xml:space="preserve">3.45196914672852</t>
@@ -3050,7 +3050,7 @@
     <t xml:space="preserve">3.24540734291077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26129698753357</t>
+    <t xml:space="preserve">3.26129674911499</t>
   </si>
   <si>
     <t xml:space="preserve">3.33677101135254</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">3.22157311439514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30499243736267</t>
+    <t xml:space="preserve">3.30499267578125</t>
   </si>
   <si>
     <t xml:space="preserve">3.2811586856842</t>
@@ -3074,7 +3074,7 @@
     <t xml:space="preserve">3.08651351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18979430198669</t>
+    <t xml:space="preserve">3.18979454040527</t>
   </si>
   <si>
     <t xml:space="preserve">3.24937987327576</t>
@@ -3083,13 +3083,13 @@
     <t xml:space="preserve">3.19376683235168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27718639373779</t>
+    <t xml:space="preserve">3.27718615531921</t>
   </si>
   <si>
     <t xml:space="preserve">3.36457800865173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37252235412598</t>
+    <t xml:space="preserve">3.37252259254456</t>
   </si>
   <si>
     <t xml:space="preserve">3.24143481254578</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">3.09445810317993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09048581123352</t>
+    <t xml:space="preserve">3.0904860496521</t>
   </si>
   <si>
     <t xml:space="preserve">3.16993284225464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16198825836182</t>
+    <t xml:space="preserve">3.16198801994324</t>
   </si>
   <si>
     <t xml:space="preserve">3.07856869697571</t>
@@ -3122,13 +3122,13 @@
     <t xml:space="preserve">2.99117732048035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89584064483643</t>
+    <t xml:space="preserve">2.895840883255</t>
   </si>
   <si>
     <t xml:space="preserve">3.0189836025238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31293725967407</t>
+    <t xml:space="preserve">3.31293749809265</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596031188965</t>
@@ -3137,7 +3137,7 @@
     <t xml:space="preserve">3.11432003974915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1421263217926</t>
+    <t xml:space="preserve">3.14212608337402</t>
   </si>
   <si>
     <t xml:space="preserve">3.18184995651245</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">3.0110387802124</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05076217651367</t>
+    <t xml:space="preserve">3.05076241493225</t>
   </si>
   <si>
     <t xml:space="preserve">3.15801572799683</t>
@@ -3167,7 +3167,7 @@
     <t xml:space="preserve">3.21760106086731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92761945724487</t>
+    <t xml:space="preserve">2.92761969566345</t>
   </si>
   <si>
     <t xml:space="preserve">2.79653215408325</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">2.87995147705078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98720479011536</t>
+    <t xml:space="preserve">2.98720455169678</t>
   </si>
   <si>
     <t xml:space="preserve">3.03487277030945</t>
@@ -3200,10 +3200,10 @@
     <t xml:space="preserve">3.53141665458679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57908487319946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42416310310364</t>
+    <t xml:space="preserve">3.5790843963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42416286468506</t>
   </si>
   <si>
     <t xml:space="preserve">3.34868860244751</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">3.35663294792175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32088184356689</t>
+    <t xml:space="preserve">3.32088208198547</t>
   </si>
   <si>
     <t xml:space="preserve">3.40032911300659</t>
@@ -3227,7 +3227,7 @@
     <t xml:space="preserve">3.46388673782349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48772048950195</t>
+    <t xml:space="preserve">3.48772072792053</t>
   </si>
   <si>
     <t xml:space="preserve">3.47183108329773</t>
@@ -3242,19 +3242,19 @@
     <t xml:space="preserve">3.55127787590027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63072490692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59100127220154</t>
+    <t xml:space="preserve">3.63072538375854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59100151062012</t>
   </si>
   <si>
     <t xml:space="preserve">3.67442107200623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61086344718933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62278008460999</t>
+    <t xml:space="preserve">3.61086320877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62278056144714</t>
   </si>
   <si>
     <t xml:space="preserve">3.67839336395264</t>
@@ -3263,13 +3263,13 @@
     <t xml:space="preserve">3.65058660507202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61880803108215</t>
+    <t xml:space="preserve">3.61880779266357</t>
   </si>
   <si>
     <t xml:space="preserve">3.6346971988678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58702921867371</t>
+    <t xml:space="preserve">3.58702898025513</t>
   </si>
   <si>
     <t xml:space="preserve">3.53936100006104</t>
@@ -3281,7 +3281,7 @@
     <t xml:space="preserve">3.33100271224976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32667088508606</t>
+    <t xml:space="preserve">3.32667112350464</t>
   </si>
   <si>
     <t xml:space="preserve">3.34399724006653</t>
@@ -3299,13 +3299,13 @@
     <t xml:space="preserve">3.49127221107483</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49560332298279</t>
+    <t xml:space="preserve">3.49560356140137</t>
   </si>
   <si>
     <t xml:space="preserve">3.42196655273438</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38298201560974</t>
+    <t xml:space="preserve">3.38298177719116</t>
   </si>
   <si>
     <t xml:space="preserve">3.48260879516602</t>
@@ -3314,22 +3314,22 @@
     <t xml:space="preserve">3.45228743553162</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48694038391113</t>
+    <t xml:space="preserve">3.48694062232971</t>
   </si>
   <si>
     <t xml:space="preserve">3.51292967796326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5042667388916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43062973022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.43929290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37865018844604</t>
+    <t xml:space="preserve">3.50426697731018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43062949180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.43929266929626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37865042686462</t>
   </si>
   <si>
     <t xml:space="preserve">3.29635000228882</t>
@@ -3341,7 +3341,7 @@
     <t xml:space="preserve">3.05811166763306</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04511713981628</t>
+    <t xml:space="preserve">3.04511690139771</t>
   </si>
   <si>
     <t xml:space="preserve">3.05378031730652</t>
@@ -3371,7 +3371,7 @@
     <t xml:space="preserve">3.17073345184326</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07543802261353</t>
+    <t xml:space="preserve">3.0754382610321</t>
   </si>
   <si>
     <t xml:space="preserve">2.98447442054749</t>
@@ -3389,13 +3389,13 @@
     <t xml:space="preserve">3.20105457305908</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11875414848328</t>
+    <t xml:space="preserve">3.1187539100647</t>
   </si>
   <si>
     <t xml:space="preserve">3.14041209220886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08410120010376</t>
+    <t xml:space="preserve">3.08410143852234</t>
   </si>
   <si>
     <t xml:space="preserve">3.02345871925354</t>
@@ -3404,7 +3404,7 @@
     <t xml:space="preserve">3.07110667228699</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08843302726746</t>
+    <t xml:space="preserve">3.08843278884888</t>
   </si>
   <si>
     <t xml:space="preserve">3.12741732597351</t>
@@ -3422,7 +3422,7 @@
     <t xml:space="preserve">3.14474391937256</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26169729232788</t>
+    <t xml:space="preserve">3.2616970539093</t>
   </si>
   <si>
     <t xml:space="preserve">3.18372797966003</t>
@@ -3431,13 +3431,13 @@
     <t xml:space="preserve">3.19672298431396</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21404957771301</t>
+    <t xml:space="preserve">3.21404933929443</t>
   </si>
   <si>
     <t xml:space="preserve">3.28335499763489</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27902364730835</t>
+    <t xml:space="preserve">3.27902340888977</t>
   </si>
   <si>
     <t xml:space="preserve">3.24870228767395</t>
@@ -3452,7 +3452,7 @@
     <t xml:space="preserve">3.06244349479675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99746918678284</t>
+    <t xml:space="preserve">2.99746942520142</t>
   </si>
   <si>
     <t xml:space="preserve">2.9324951171875</t>
@@ -3467,7 +3467,7 @@
     <t xml:space="preserve">2.88051605224609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85885810852051</t>
+    <t xml:space="preserve">2.85885787010193</t>
   </si>
   <si>
     <t xml:space="preserve">2.84153151512146</t>
@@ -3479,13 +3479,13 @@
     <t xml:space="preserve">2.9368269443512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86318945884705</t>
+    <t xml:space="preserve">2.86318969726562</t>
   </si>
   <si>
     <t xml:space="preserve">2.85019469261169</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79821538925171</t>
+    <t xml:space="preserve">2.79821562767029</t>
   </si>
   <si>
     <t xml:space="preserve">2.83286833763123</t>
@@ -3500,7 +3500,7 @@
     <t xml:space="preserve">2.60329341888428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49067163467407</t>
+    <t xml:space="preserve">2.49067187309265</t>
   </si>
   <si>
     <t xml:space="preserve">2.45601892471313</t>
@@ -3518,16 +3518,16 @@
     <t xml:space="preserve">2.3910448551178</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46035027503967</t>
+    <t xml:space="preserve">2.46035051345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.35206031799316</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32173919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35639214515686</t>
+    <t xml:space="preserve">2.32173943519592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35639190673828</t>
   </si>
   <si>
     <t xml:space="preserve">2.36505532264709</t>
@@ -3539,25 +3539,25 @@
     <t xml:space="preserve">2.28275465965271</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29141783714294</t>
+    <t xml:space="preserve">2.29141807556152</t>
   </si>
   <si>
     <t xml:space="preserve">2.23943877220154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30874419212341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36938691139221</t>
+    <t xml:space="preserve">2.30874443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36938667297363</t>
   </si>
   <si>
     <t xml:space="preserve">2.38238167762756</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51666140556335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54698276519775</t>
+    <t xml:space="preserve">2.51666116714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54698252677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.54265093803406</t>
@@ -3578,7 +3578,7 @@
     <t xml:space="preserve">2.59896183013916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6639358997345</t>
+    <t xml:space="preserve">2.66393566131592</t>
   </si>
   <si>
     <t xml:space="preserve">2.69425702095032</t>
@@ -3587,28 +3587,28 @@
     <t xml:space="preserve">2.67259907722473</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75056791305542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68559384346008</t>
+    <t xml:space="preserve">2.75056767463684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6855936050415</t>
   </si>
   <si>
     <t xml:space="preserve">2.68126225471497</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63794612884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65094089508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68992567062378</t>
+    <t xml:space="preserve">2.63794636726379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65094113349915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6899254322052</t>
   </si>
   <si>
     <t xml:space="preserve">2.72457838058472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71591520309448</t>
+    <t xml:space="preserve">2.7159149646759</t>
   </si>
   <si>
     <t xml:space="preserve">2.76789426803589</t>
@@ -3620,7 +3620,7 @@
     <t xml:space="preserve">2.78522062301636</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81987357139587</t>
+    <t xml:space="preserve">2.81987380981445</t>
   </si>
   <si>
     <t xml:space="preserve">2.72890996932983</t>
@@ -3632,13 +3632,13 @@
     <t xml:space="preserve">2.82420516014099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81121015548706</t>
+    <t xml:space="preserve">2.81121039390564</t>
   </si>
   <si>
     <t xml:space="preserve">2.75489950180054</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78955221176147</t>
+    <t xml:space="preserve">2.78955245018005</t>
   </si>
   <si>
     <t xml:space="preserve">2.73324155807495</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">2.67693042755127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69858884811401</t>
+    <t xml:space="preserve">2.69858860969543</t>
   </si>
   <si>
     <t xml:space="preserve">2.73757314682007</t>
@@ -3662,7 +3662,7 @@
     <t xml:space="preserve">2.81554198265076</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82853674888611</t>
+    <t xml:space="preserve">2.82853698730469</t>
   </si>
   <si>
     <t xml:space="preserve">2.83719992637634</t>
@@ -3671,13 +3671,13 @@
     <t xml:space="preserve">2.87185287475586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91950035095215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91516876220703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9888060092926</t>
+    <t xml:space="preserve">2.91950011253357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91516900062561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98880624771118</t>
   </si>
   <si>
     <t xml:space="preserve">3.01479554176331</t>
@@ -3695,7 +3695,7 @@
     <t xml:space="preserve">2.43869256973267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48200845718384</t>
+    <t xml:space="preserve">2.48200869560242</t>
   </si>
   <si>
     <t xml:space="preserve">2.4473557472229</t>
@@ -3707,7 +3707,7 @@
     <t xml:space="preserve">2.45168709754944</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43002939224243</t>
+    <t xml:space="preserve">2.43002915382385</t>
   </si>
   <si>
     <t xml:space="preserve">2.39970803260803</t>
@@ -3716,28 +3716,28 @@
     <t xml:space="preserve">2.40837121009827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48633980751038</t>
+    <t xml:space="preserve">2.48634004592896</t>
   </si>
   <si>
     <t xml:space="preserve">2.50799798965454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51232957839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46901345252991</t>
+    <t xml:space="preserve">2.51232981681824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46901369094849</t>
   </si>
   <si>
     <t xml:space="preserve">2.4733452796936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37805008888245</t>
+    <t xml:space="preserve">2.37804985046387</t>
   </si>
   <si>
     <t xml:space="preserve">2.3607234954834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47767663002014</t>
+    <t xml:space="preserve">2.47767686843872</t>
   </si>
   <si>
     <t xml:space="preserve">2.55564594268799</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">2.55131411552429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52965641021729</t>
+    <t xml:space="preserve">2.52965617179871</t>
   </si>
   <si>
     <t xml:space="preserve">2.57297229766846</t>
@@ -3758,16 +3758,19 @@
     <t xml:space="preserve">2.49933481216431</t>
   </si>
   <si>
+    <t xml:space="preserve">2.503666639328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55200004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46499991416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51816654205322</t>
+  </si>
+  <si>
     <t xml:space="preserve">2.50366640090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55200004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46499991416931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51816654205322</t>
   </si>
   <si>
     <t xml:space="preserve">2.5278332233429</t>
@@ -8814,7 +8817,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G144" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8866,7 +8869,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G146" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8892,7 +8895,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -9152,7 +9155,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G157" t="s">
-        <v>51</v>
+        <v>130</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -13078,7 +13081,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G308" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -53768,7 +53771,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1873" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -53794,7 +53797,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1874" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -53820,7 +53823,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G1875" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -53846,7 +53849,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1876" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -53872,7 +53875,7 @@
         <v>2.59500002861023</v>
       </c>
       <c r="G1877" t="s">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -53898,7 +53901,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1878" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -53924,7 +53927,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1879" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -53950,7 +53953,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1880" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -53976,7 +53979,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1881" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -54002,7 +54005,7 @@
         <v>2.53999996185303</v>
       </c>
       <c r="G1882" t="s">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -54028,7 +54031,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1883" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -54054,7 +54057,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1884" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -54080,7 +54083,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1885" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -54106,7 +54109,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1886" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -54132,7 +54135,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1887" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -54158,7 +54161,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G1888" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -54184,7 +54187,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G1889" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -54210,7 +54213,7 @@
         <v>2.59999990463257</v>
       </c>
       <c r="G1890" t="s">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -54236,7 +54239,7 @@
         <v>2.60999989509583</v>
       </c>
       <c r="G1891" t="s">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -54262,7 +54265,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1892" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -54288,7 +54291,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G1893" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -54314,7 +54317,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G1894" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -54340,7 +54343,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1895" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -54366,7 +54369,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1896" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -54392,7 +54395,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1897" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -54418,7 +54421,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1898" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -54444,7 +54447,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1899" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -54470,7 +54473,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G1900" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -54496,7 +54499,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1901" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -54522,7 +54525,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1902" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -54548,7 +54551,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1903" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -54574,7 +54577,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1904" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -54600,7 +54603,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1905" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -54626,7 +54629,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1906" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -54652,7 +54655,7 @@
         <v>2.43499994277954</v>
       </c>
       <c r="G1907" t="s">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -54678,7 +54681,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G1908" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -54704,7 +54707,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1909" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -54730,7 +54733,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G1910" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -54756,7 +54759,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1911" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -54782,7 +54785,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G1912" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -54808,7 +54811,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1913" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -54834,7 +54837,7 @@
         <v>2.40499997138977</v>
       </c>
       <c r="G1914" t="s">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -54860,7 +54863,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G1915" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -54886,7 +54889,7 @@
         <v>2.4449999332428</v>
       </c>
       <c r="G1916" t="s">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -54912,7 +54915,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1917" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -54938,7 +54941,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G1918" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -54964,7 +54967,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G1919" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -54990,7 +54993,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G1920" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -55016,7 +55019,7 @@
         <v>2.5</v>
       </c>
       <c r="G1921" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -55042,7 +55045,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1922" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -55094,7 +55097,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G1924" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -55120,7 +55123,7 @@
         <v>2.57999992370605</v>
       </c>
       <c r="G1925" t="s">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -55172,7 +55175,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G1927" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -55198,7 +55201,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G1928" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -55224,7 +55227,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G1929" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -55250,7 +55253,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G1930" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -55276,7 +55279,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G1931" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -55302,7 +55305,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G1932" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -55328,7 +55331,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G1933" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -55354,7 +55357,7 @@
         <v>2.42000007629395</v>
       </c>
       <c r="G1934" t="s">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -55380,7 +55383,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1935" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -55406,7 +55409,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1936" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -55432,7 +55435,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G1937" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -55458,7 +55461,7 @@
         <v>2.4300000667572</v>
       </c>
       <c r="G1938" t="s">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -55484,7 +55487,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G1939" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -55510,7 +55513,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G1940" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -55536,7 +55539,7 @@
         <v>2.375</v>
       </c>
       <c r="G1941" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -55562,7 +55565,7 @@
         <v>2.32500004768372</v>
       </c>
       <c r="G1942" t="s">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -55588,7 +55591,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G1943" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -55614,7 +55617,7 @@
         <v>2.27500009536743</v>
       </c>
       <c r="G1944" t="s">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -55640,7 +55643,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1945" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -55666,7 +55669,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1946" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -55692,7 +55695,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -55718,7 +55721,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G1948" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -55744,7 +55747,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G1949" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -55770,7 +55773,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1950" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -55796,7 +55799,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1951" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -55822,7 +55825,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G1952" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -55848,7 +55851,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G1953" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -55874,7 +55877,7 @@
         <v>2.25</v>
       </c>
       <c r="G1954" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -55900,7 +55903,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G1955" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -55926,7 +55929,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G1956" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -55952,7 +55955,7 @@
         <v>2.25</v>
       </c>
       <c r="G1957" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -55978,7 +55981,7 @@
         <v>2.25</v>
       </c>
       <c r="G1958" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -56004,7 +56007,7 @@
         <v>2.25</v>
       </c>
       <c r="G1959" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -56030,7 +56033,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1960" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -56056,7 +56059,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G1961" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -56082,7 +56085,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G1962" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -56108,7 +56111,7 @@
         <v>2.25500011444092</v>
       </c>
       <c r="G1963" t="s">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -56134,7 +56137,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1964" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -56160,7 +56163,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G1965" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -56186,7 +56189,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G1966" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -56212,7 +56215,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1967" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -56238,7 +56241,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G1968" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -56264,7 +56267,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1969" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -56290,7 +56293,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1970" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -56316,7 +56319,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1971" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -56342,7 +56345,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1972" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -56368,7 +56371,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1973" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -56394,7 +56397,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G1974" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -56420,7 +56423,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1975" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -56446,7 +56449,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1976" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -56472,7 +56475,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G1977" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -56498,7 +56501,7 @@
         <v>2.04999995231628</v>
       </c>
       <c r="G1978" t="s">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -56524,7 +56527,7 @@
         <v>2.07500004768372</v>
       </c>
       <c r="G1979" t="s">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -56550,7 +56553,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G1980" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -56576,7 +56579,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G1981" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -56602,7 +56605,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1982" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -56628,7 +56631,7 @@
         <v>2.07999992370605</v>
       </c>
       <c r="G1983" t="s">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -56654,7 +56657,7 @@
         <v>2.03999996185303</v>
       </c>
       <c r="G1984" t="s">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -56680,7 +56683,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G1985" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -56706,7 +56709,7 @@
         <v>2.02999997138977</v>
       </c>
       <c r="G1986" t="s">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -56732,7 +56735,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G1987" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -56758,7 +56761,7 @@
         <v>1.97800004482269</v>
       </c>
       <c r="G1988" t="s">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -56784,7 +56787,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G1989" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -56810,7 +56813,7 @@
         <v>1.91400003433228</v>
       </c>
       <c r="G1990" t="s">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -56836,7 +56839,7 @@
         <v>1.83000004291534</v>
       </c>
       <c r="G1991" t="s">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -56862,7 +56865,7 @@
         <v>1.85199999809265</v>
       </c>
       <c r="G1992" t="s">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -56888,7 +56891,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G1993" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -56914,7 +56917,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G1994" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -56940,7 +56943,7 @@
         <v>1.94000005722046</v>
       </c>
       <c r="G1995" t="s">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -56966,7 +56969,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G1996" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -56992,7 +56995,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G1997" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -57018,7 +57021,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G1998" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -57044,7 +57047,7 @@
         <v>2.125</v>
       </c>
       <c r="G1999" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -57070,7 +57073,7 @@
         <v>2.15000009536743</v>
       </c>
       <c r="G2000" t="s">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -57096,7 +57099,7 @@
         <v>2.08500003814697</v>
       </c>
       <c r="G2001" t="s">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -57122,7 +57125,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2002" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -57148,7 +57151,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G2003" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -57174,7 +57177,7 @@
         <v>2.13499999046326</v>
       </c>
       <c r="G2004" t="s">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -57200,7 +57203,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2005" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -57226,7 +57229,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2006" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -57252,7 +57255,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2007" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -57278,7 +57281,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2008" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -57304,7 +57307,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G2009" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -57330,7 +57333,7 @@
         <v>2.125</v>
       </c>
       <c r="G2010" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -57356,7 +57359,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2011" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -57382,7 +57385,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2012" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -57408,7 +57411,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -57434,7 +57437,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2014" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -57460,7 +57463,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2015" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -57486,7 +57489,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2016" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -57512,7 +57515,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G2017" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -57538,7 +57541,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2018" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -57564,7 +57567,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G2019" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -57590,7 +57593,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2020" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -57616,7 +57619,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G2021" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -57642,7 +57645,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G2022" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -57668,7 +57671,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G2023" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -57694,7 +57697,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G2024" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -57720,7 +57723,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2025" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -57746,7 +57749,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2026" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57772,7 +57775,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2027" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -57798,7 +57801,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2028" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -57824,7 +57827,7 @@
         <v>2.26999998092651</v>
       </c>
       <c r="G2029" t="s">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -57850,7 +57853,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2030" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -57876,7 +57879,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G2031" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -57902,7 +57905,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2032" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -57928,7 +57931,7 @@
         <v>2.29500007629395</v>
       </c>
       <c r="G2033" t="s">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -57954,7 +57957,7 @@
         <v>2.30999994277954</v>
       </c>
       <c r="G2034" t="s">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -57980,7 +57983,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2035" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -58006,7 +58009,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2036" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -58032,7 +58035,7 @@
         <v>2.34500002861023</v>
       </c>
       <c r="G2037" t="s">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -58058,7 +58061,7 @@
         <v>2.28999996185303</v>
       </c>
       <c r="G2038" t="s">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -58084,7 +58087,7 @@
         <v>2.3199999332428</v>
       </c>
       <c r="G2039" t="s">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -58110,7 +58113,7 @@
         <v>2.31500005722046</v>
       </c>
       <c r="G2040" t="s">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -58136,7 +58139,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2041" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -58162,7 +58165,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G2042" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -58188,7 +58191,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2043" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -58214,7 +58217,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2044" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -58240,7 +58243,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G2045" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -58266,7 +58269,7 @@
         <v>2.25</v>
       </c>
       <c r="G2046" t="s">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -58292,7 +58295,7 @@
         <v>2.22000002861023</v>
       </c>
       <c r="G2047" t="s">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -58318,7 +58321,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2048" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -58344,7 +58347,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2049" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -58370,7 +58373,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2050" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -58396,7 +58399,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2051" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -58422,7 +58425,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2052" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -58448,7 +58451,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2053" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -58474,7 +58477,7 @@
         <v>2.22499990463257</v>
       </c>
       <c r="G2054" t="s">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -58500,7 +58503,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2055" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -58526,7 +58529,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2056" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -58552,7 +58555,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2057" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -58578,7 +58581,7 @@
         <v>2.20499992370605</v>
       </c>
       <c r="G2058" t="s">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -58604,7 +58607,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2059" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -58630,7 +58633,7 @@
         <v>2.21000003814697</v>
       </c>
       <c r="G2060" t="s">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -58656,7 +58659,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2061" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -58682,7 +58685,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2062" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -58708,7 +58711,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G2063" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -58734,7 +58737,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G2064" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -58760,7 +58763,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2065" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -58786,7 +58789,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2066" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -58812,7 +58815,7 @@
         <v>2.13000011444092</v>
       </c>
       <c r="G2067" t="s">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -58838,7 +58841,7 @@
         <v>2.125</v>
       </c>
       <c r="G2068" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -58864,7 +58867,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G2069" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -58890,7 +58893,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G2070" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -58916,7 +58919,7 @@
         <v>2.1800000667572</v>
       </c>
       <c r="G2071" t="s">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -58942,7 +58945,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G2072" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -58968,7 +58971,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2073" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -58994,7 +58997,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G2074" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -59020,7 +59023,7 @@
         <v>2.17000007629395</v>
       </c>
       <c r="G2075" t="s">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -59046,7 +59049,7 @@
         <v>2.25999999046326</v>
       </c>
       <c r="G2076" t="s">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -59072,7 +59075,7 @@
         <v>1.87999999523163</v>
       </c>
       <c r="G2077" t="s">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -59098,7 +59101,7 @@
         <v>1.76999998092651</v>
       </c>
       <c r="G2078" t="s">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -59124,7 +59127,7 @@
         <v>1.69799995422363</v>
       </c>
       <c r="G2079" t="s">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -59150,7 +59153,7 @@
         <v>1.7059999704361</v>
       </c>
       <c r="G2080" t="s">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -59176,7 +59179,7 @@
         <v>1.66199994087219</v>
       </c>
       <c r="G2081" t="s">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -59202,7 +59205,7 @@
         <v>1.67599999904633</v>
       </c>
       <c r="G2082" t="s">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -59228,7 +59231,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G2083" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -59254,7 +59257,7 @@
         <v>1.64199995994568</v>
       </c>
       <c r="G2084" t="s">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -59280,7 +59283,7 @@
         <v>1.62999999523163</v>
       </c>
       <c r="G2085" t="s">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -59306,7 +59309,7 @@
         <v>1.61000001430511</v>
       </c>
       <c r="G2086" t="s">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -59332,7 +59335,7 @@
         <v>1.58200001716614</v>
       </c>
       <c r="G2087" t="s">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -59358,7 +59361,7 @@
         <v>1.50800001621246</v>
       </c>
       <c r="G2088" t="s">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -59384,7 +59387,7 @@
         <v>1.5</v>
       </c>
       <c r="G2089" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -59410,7 +59413,7 @@
         <v>1.4559999704361</v>
       </c>
       <c r="G2090" t="s">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -59436,7 +59439,7 @@
         <v>1.41799998283386</v>
       </c>
       <c r="G2091" t="s">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -59462,7 +59465,7 @@
         <v>1.42799997329712</v>
       </c>
       <c r="G2092" t="s">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -59488,7 +59491,7 @@
         <v>1.42200005054474</v>
       </c>
       <c r="G2093" t="s">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -59514,7 +59517,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G2094" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -59540,7 +59543,7 @@
         <v>1.432000041008</v>
       </c>
       <c r="G2095" t="s">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -59566,7 +59569,7 @@
         <v>1.48399996757507</v>
       </c>
       <c r="G2096" t="s">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -59592,7 +59595,7 @@
         <v>1.50399994850159</v>
       </c>
       <c r="G2097" t="s">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -59618,7 +59621,7 @@
         <v>1.5</v>
       </c>
       <c r="G2098" t="s">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -59644,7 +59647,7 @@
         <v>1.51800000667572</v>
       </c>
       <c r="G2099" t="s">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -59670,7 +59673,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G2100" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -59696,7 +59699,7 @@
         <v>1.42599999904633</v>
       </c>
       <c r="G2101" t="s">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -59722,7 +59725,7 @@
         <v>1.44000005722046</v>
       </c>
       <c r="G2102" t="s">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -59748,7 +59751,7 @@
         <v>1.40600001811981</v>
       </c>
       <c r="G2103" t="s">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -59774,7 +59777,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G2104" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -59800,7 +59803,7 @@
         <v>1.47800004482269</v>
       </c>
       <c r="G2105" t="s">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -59826,7 +59829,7 @@
         <v>1.46800005435944</v>
       </c>
       <c r="G2106" t="s">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -59852,7 +59855,7 @@
         <v>1.47000002861023</v>
       </c>
       <c r="G2107" t="s">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -59878,7 +59881,7 @@
         <v>1.45000004768372</v>
       </c>
       <c r="G2108" t="s">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -59904,7 +59907,7 @@
         <v>1.44599997997284</v>
       </c>
       <c r="G2109" t="s">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -59930,7 +59933,7 @@
         <v>1.45200002193451</v>
       </c>
       <c r="G2110" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -59956,7 +59959,7 @@
         <v>1.47200000286102</v>
       </c>
       <c r="G2111" t="s">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -59982,7 +59985,7 @@
         <v>1.52999997138977</v>
       </c>
       <c r="G2112" t="s">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -60008,7 +60011,7 @@
         <v>1.52600002288818</v>
       </c>
       <c r="G2113" t="s">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -60034,7 +60037,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2114" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -60060,7 +60063,7 @@
         <v>1.66600000858307</v>
       </c>
       <c r="G2115" t="s">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -60086,7 +60089,7 @@
         <v>1.58599996566772</v>
       </c>
       <c r="G2116" t="s">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -60112,7 +60115,7 @@
         <v>1.5460000038147</v>
       </c>
       <c r="G2117" t="s">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -60138,7 +60141,7 @@
         <v>1.62000000476837</v>
       </c>
       <c r="G2118" t="s">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -60164,7 +60167,7 @@
         <v>1.65600001811981</v>
       </c>
       <c r="G2119" t="s">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -60190,7 +60193,7 @@
         <v>1.64600002765656</v>
       </c>
       <c r="G2120" t="s">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -60216,7 +60219,7 @@
         <v>1.67200005054474</v>
       </c>
       <c r="G2121" t="s">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -60242,7 +60245,7 @@
         <v>1.69400000572205</v>
       </c>
       <c r="G2122" t="s">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -60268,7 +60271,7 @@
         <v>1.69599997997284</v>
       </c>
       <c r="G2123" t="s">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -60294,7 +60297,7 @@
         <v>1.68799996376038</v>
       </c>
       <c r="G2124" t="s">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -60320,7 +60323,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G2125" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -60346,7 +60349,7 @@
         <v>1.73599994182587</v>
       </c>
       <c r="G2126" t="s">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -60372,7 +60375,7 @@
         <v>1.7940000295639</v>
       </c>
       <c r="G2127" t="s">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -60398,7 +60401,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G2128" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -60424,7 +60427,7 @@
         <v>1.8400000333786</v>
       </c>
       <c r="G2129" t="s">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -60450,7 +60453,7 @@
         <v>1.86000001430511</v>
       </c>
       <c r="G2130" t="s">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -60476,7 +60479,7 @@
         <v>1.83399999141693</v>
       </c>
       <c r="G2131" t="s">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -60502,7 +60505,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G2132" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -60528,7 +60531,7 @@
         <v>1.82799994945526</v>
       </c>
       <c r="G2133" t="s">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -60554,7 +60557,7 @@
         <v>1.85800004005432</v>
       </c>
       <c r="G2134" t="s">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -60580,7 +60583,7 @@
         <v>1.86199998855591</v>
       </c>
       <c r="G2135" t="s">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -60606,7 +60609,7 @@
         <v>1.86600005626678</v>
       </c>
       <c r="G2136" t="s">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -60632,7 +60635,7 @@
         <v>1.85000002384186</v>
       </c>
       <c r="G2137" t="s">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -60658,7 +60661,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G2138" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -60684,7 +60687,7 @@
         <v>1.9099999666214</v>
       </c>
       <c r="G2139" t="s">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -60710,7 +60713,7 @@
         <v>1.88199996948242</v>
       </c>
       <c r="G2140" t="s">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -60736,7 +60739,7 @@
         <v>1.98599994182587</v>
       </c>
       <c r="G2141" t="s">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -60762,7 +60765,7 @@
         <v>1.95000004768372</v>
       </c>
       <c r="G2142" t="s">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -60788,7 +60791,7 @@
         <v>1.99800002574921</v>
       </c>
       <c r="G2143" t="s">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -60814,7 +60817,7 @@
         <v>1.98399996757507</v>
       </c>
       <c r="G2144" t="s">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -60840,7 +60843,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2145" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -60866,7 +60869,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2146" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -60892,7 +60895,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G2147" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -60918,7 +60921,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G2148" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -60944,7 +60947,7 @@
         <v>1.8639999628067</v>
       </c>
       <c r="G2149" t="s">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -60970,7 +60973,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G2150" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -60996,7 +60999,7 @@
         <v>1.83200001716614</v>
       </c>
       <c r="G2151" t="s">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -61022,7 +61025,7 @@
         <v>1.82400000095367</v>
       </c>
       <c r="G2152" t="s">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -61048,7 +61051,7 @@
         <v>1.817999958992</v>
       </c>
       <c r="G2153" t="s">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -61074,7 +61077,7 @@
         <v>1.78400003910065</v>
       </c>
       <c r="G2154" t="s">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -61100,7 +61103,7 @@
         <v>1.70200002193451</v>
       </c>
       <c r="G2155" t="s">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -61126,7 +61129,7 @@
         <v>1.74800002574921</v>
       </c>
       <c r="G2156" t="s">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -61152,7 +61155,7 @@
         <v>1.75</v>
       </c>
       <c r="G2157" t="s">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -61178,7 +61181,7 @@
         <v>1.78799998760223</v>
       </c>
       <c r="G2158" t="s">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -61204,7 +61207,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G2159" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -61230,7 +61233,7 @@
         <v>1.73800003528595</v>
       </c>
       <c r="G2160" t="s">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -61256,7 +61259,7 @@
         <v>1.76199996471405</v>
       </c>
       <c r="G2161" t="s">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -61282,7 +61285,7 @@
         <v>1.72399997711182</v>
       </c>
       <c r="G2162" t="s">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -61308,7 +61311,7 @@
         <v>1.76600003242493</v>
       </c>
       <c r="G2163" t="s">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -61334,7 +61337,7 @@
         <v>1.75600004196167</v>
       </c>
       <c r="G2164" t="s">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -61360,7 +61363,7 @@
         <v>1.79999995231628</v>
       </c>
       <c r="G2165" t="s">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -61386,7 +61389,7 @@
         <v>1.89400005340576</v>
       </c>
       <c r="G2166" t="s">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -61412,7 +61415,7 @@
         <v>1.91799998283386</v>
       </c>
       <c r="G2167" t="s">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -61438,7 +61441,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G2168" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -61464,7 +61467,7 @@
         <v>1.87199997901917</v>
       </c>
       <c r="G2169" t="s">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -61490,7 +61493,7 @@
         <v>1.93400001525879</v>
       </c>
       <c r="G2170" t="s">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -61516,7 +61519,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G2171" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -61542,7 +61545,7 @@
         <v>1.90199995040894</v>
       </c>
       <c r="G2172" t="s">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -61568,7 +61571,7 @@
         <v>1.90600001811981</v>
       </c>
       <c r="G2173" t="s">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -61594,7 +61597,7 @@
         <v>1.89600002765656</v>
       </c>
       <c r="G2174" t="s">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -61620,7 +61623,7 @@
         <v>1.90799999237061</v>
       </c>
       <c r="G2175" t="s">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -61646,7 +61649,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G2176" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -61672,7 +61675,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G2177" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -61698,7 +61701,7 @@
         <v>1.92599999904633</v>
       </c>
       <c r="G2178" t="s">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -61724,7 +61727,7 @@
         <v>1.932000041008</v>
       </c>
       <c r="G2179" t="s">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -61750,7 +61753,7 @@
         <v>1.93799996376038</v>
       </c>
       <c r="G2180" t="s">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -61776,7 +61779,7 @@
         <v>1.92200005054474</v>
       </c>
       <c r="G2181" t="s">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -61802,7 +61805,7 @@
         <v>1.94200003147125</v>
       </c>
       <c r="G2182" t="s">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -61828,7 +61831,7 @@
         <v>1.99000000953674</v>
       </c>
       <c r="G2183" t="s">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -61854,7 +61857,7 @@
         <v>2.02500009536743</v>
       </c>
       <c r="G2184" t="s">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -61880,7 +61883,7 @@
         <v>2.01999998092651</v>
       </c>
       <c r="G2185" t="s">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -61906,7 +61909,7 @@
         <v>1.96599996089935</v>
       </c>
       <c r="G2186" t="s">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -61932,7 +61935,7 @@
         <v>2.00999999046326</v>
       </c>
       <c r="G2187" t="s">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -61958,7 +61961,7 @@
         <v>1.94799995422363</v>
       </c>
       <c r="G2188" t="s">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -61984,7 +61987,7 @@
         <v>1.98800003528595</v>
       </c>
       <c r="G2189" t="s">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -62010,7 +62013,7 @@
         <v>2.05999994277954</v>
       </c>
       <c r="G2190" t="s">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -62036,7 +62039,7 @@
         <v>2.0699999332428</v>
       </c>
       <c r="G2191" t="s">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -62062,7 +62065,7 @@
         <v>2.11500000953674</v>
       </c>
       <c r="G2192" t="s">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -62088,7 +62091,7 @@
         <v>2.11999988555908</v>
       </c>
       <c r="G2193" t="s">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -62114,7 +62117,7 @@
         <v>2.08999991416931</v>
       </c>
       <c r="G2194" t="s">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -62140,7 +62143,7 @@
         <v>2.09500002861023</v>
       </c>
       <c r="G2195" t="s">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -62166,7 +62169,7 @@
         <v>2.09999990463257</v>
       </c>
       <c r="G2196" t="s">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -62192,7 +62195,7 @@
         <v>2.125</v>
       </c>
       <c r="G2197" t="s">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -62218,7 +62221,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2198" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -62244,7 +62247,7 @@
         <v>2.1949999332428</v>
       </c>
       <c r="G2199" t="s">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -62270,7 +62273,7 @@
         <v>2.23000001907349</v>
       </c>
       <c r="G2200" t="s">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -62296,7 +62299,7 @@
         <v>2.24000000953674</v>
       </c>
       <c r="G2201" t="s">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -62322,7 +62325,7 @@
         <v>2.26500010490417</v>
       </c>
       <c r="G2202" t="s">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -62348,7 +62351,7 @@
         <v>2.28500008583069</v>
       </c>
       <c r="G2203" t="s">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -62374,7 +62377,7 @@
         <v>2.36500000953674</v>
       </c>
       <c r="G2204" t="s">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -62400,7 +62403,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G2205" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -62426,7 +62429,7 @@
         <v>2.5</v>
       </c>
       <c r="G2206" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -62452,7 +62455,7 @@
         <v>2.50500011444092</v>
       </c>
       <c r="G2207" t="s">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -62478,7 +62481,7 @@
         <v>2.41000008583069</v>
       </c>
       <c r="G2208" t="s">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -62504,7 +62507,7 @@
         <v>2.5</v>
       </c>
       <c r="G2209" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -62530,7 +62533,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G2210" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -62556,7 +62559,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G2211" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -62582,7 +62585,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2212" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -62608,7 +62611,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G2213" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -62634,7 +62637,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G2214" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -62660,7 +62663,7 @@
         <v>2.54500007629395</v>
       </c>
       <c r="G2215" t="s">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -62686,7 +62689,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G2216" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -62712,7 +62715,7 @@
         <v>2.61999988555908</v>
       </c>
       <c r="G2217" t="s">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -62764,7 +62767,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2219" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -62816,7 +62819,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G2221" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -62842,7 +62845,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G2222" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -62868,7 +62871,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2223" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -62894,7 +62897,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G2224" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -62920,7 +62923,7 @@
         <v>2.53500008583069</v>
       </c>
       <c r="G2225" t="s">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -62946,7 +62949,7 @@
         <v>2.56500005722046</v>
       </c>
       <c r="G2226" t="s">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -62972,7 +62975,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G2227" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -62998,7 +63001,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G2228" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -63024,7 +63027,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2229" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -63050,7 +63053,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2230" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -63076,7 +63079,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2231" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -63102,7 +63105,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2232" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -63128,7 +63131,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G2233" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -63154,7 +63157,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G2234" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -63180,7 +63183,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G2235" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -63206,7 +63209,7 @@
         <v>2.50999999046326</v>
       </c>
       <c r="G2236" t="s">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -63232,7 +63235,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G2237" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -63258,7 +63261,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G2238" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -63284,7 +63287,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G2239" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -63310,7 +63313,7 @@
         <v>2.48499989509583</v>
       </c>
       <c r="G2240" t="s">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -63336,7 +63339,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G2241" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -63362,7 +63365,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2242" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -63388,7 +63391,7 @@
         <v>2.41499996185303</v>
       </c>
       <c r="G2243" t="s">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -63414,7 +63417,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G2244" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -63440,7 +63443,7 @@
         <v>2.5</v>
       </c>
       <c r="G2245" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -63466,7 +63469,7 @@
         <v>2.5</v>
       </c>
       <c r="G2246" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -63492,7 +63495,7 @@
         <v>2.58500003814697</v>
       </c>
       <c r="G2247" t="s">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -63518,7 +63521,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2248" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -63544,7 +63547,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G2249" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -63570,7 +63573,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G2250" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -63596,7 +63599,7 @@
         <v>2.52999997138977</v>
       </c>
       <c r="G2251" t="s">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -63622,7 +63625,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G2252" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -63648,7 +63651,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G2253" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -63674,7 +63677,7 @@
         <v>2.39499998092651</v>
       </c>
       <c r="G2254" t="s">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -63700,7 +63703,7 @@
         <v>2.35500001907349</v>
       </c>
       <c r="G2255" t="s">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -63726,7 +63729,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G2256" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -63752,7 +63755,7 @@
         <v>2.23499989509583</v>
       </c>
       <c r="G2257" t="s">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -63778,7 +63781,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G2258" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -63804,7 +63807,7 @@
         <v>2.16499996185303</v>
       </c>
       <c r="G2259" t="s">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -63830,7 +63833,7 @@
         <v>2.19000005722046</v>
       </c>
       <c r="G2260" t="s">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -63856,7 +63859,7 @@
         <v>2.18499994277954</v>
       </c>
       <c r="G2261" t="s">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -63882,7 +63885,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2262" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -63908,7 +63911,7 @@
         <v>2.17499995231628</v>
       </c>
       <c r="G2263" t="s">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -63934,7 +63937,7 @@
         <v>2.15499997138977</v>
       </c>
       <c r="G2264" t="s">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -63960,7 +63963,7 @@
         <v>2.16000008583069</v>
       </c>
       <c r="G2265" t="s">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -63986,7 +63989,7 @@
         <v>2.24499988555908</v>
       </c>
       <c r="G2266" t="s">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -64012,7 +64015,7 @@
         <v>2.27999997138977</v>
       </c>
       <c r="G2267" t="s">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -64038,7 +64041,7 @@
         <v>2.21499991416931</v>
       </c>
       <c r="G2268" t="s">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -64064,7 +64067,7 @@
         <v>2.3050000667572</v>
       </c>
       <c r="G2269" t="s">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -64090,7 +64093,7 @@
         <v>2.36999988555908</v>
       </c>
       <c r="G2270" t="s">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -64116,7 +64119,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G2271" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -64142,7 +64145,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G2272" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -64168,7 +64171,7 @@
         <v>2.5</v>
       </c>
       <c r="G2273" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -64194,7 +64197,7 @@
         <v>2.52500009536743</v>
       </c>
       <c r="G2274" t="s">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -64220,7 +64223,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2275" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -64246,7 +64249,7 @@
         <v>2.625</v>
       </c>
       <c r="G2276" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -64272,7 +64275,7 @@
         <v>2.58999991416931</v>
       </c>
       <c r="G2277" t="s">
-        <v>1248</v>
+        <v>1252</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -64298,7 +64301,7 @@
         <v>2.57500004768372</v>
       </c>
       <c r="G2278" t="s">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -64324,7 +64327,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2279" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -64350,7 +64353,7 @@
         <v>2.75</v>
       </c>
       <c r="G2280" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -64376,7 +64379,7 @@
         <v>2.63000011444092</v>
       </c>
       <c r="G2281" t="s">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -64428,7 +64431,7 @@
         <v>2.63499999046326</v>
       </c>
       <c r="G2283" t="s">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -64454,7 +64457,7 @@
         <v>2.5699999332428</v>
       </c>
       <c r="G2284" t="s">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -64480,7 +64483,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2285" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -64506,7 +64509,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G2286" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -64532,7 +64535,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G2287" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -64558,7 +64561,7 @@
         <v>2.48000001907349</v>
       </c>
       <c r="G2288" t="s">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -64584,7 +64587,7 @@
         <v>2.5</v>
       </c>
       <c r="G2289" t="s">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -64610,7 +64613,7 @@
         <v>2.47499990463257</v>
       </c>
       <c r="G2290" t="s">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -64636,7 +64639,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2291" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -64662,7 +64665,7 @@
         <v>2.45499992370605</v>
       </c>
       <c r="G2292" t="s">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -64688,7 +64691,7 @@
         <v>2.42499995231628</v>
       </c>
       <c r="G2293" t="s">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -64714,7 +64717,7 @@
         <v>2.40000009536743</v>
       </c>
       <c r="G2294" t="s">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -64740,7 +64743,7 @@
         <v>2.38499999046326</v>
       </c>
       <c r="G2295" t="s">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -64766,7 +64769,7 @@
         <v>2.375</v>
       </c>
       <c r="G2296" t="s">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -64792,7 +64795,7 @@
         <v>2.35999989509583</v>
       </c>
       <c r="G2297" t="s">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -64818,7 +64821,7 @@
         <v>2.38000011444092</v>
       </c>
       <c r="G2298" t="s">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -64844,7 +64847,7 @@
         <v>2.44000005722046</v>
       </c>
       <c r="G2299" t="s">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -64870,7 +64873,7 @@
         <v>2.46499991416931</v>
       </c>
       <c r="G2300" t="s">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -64896,7 +64899,7 @@
         <v>2.49000000953674</v>
       </c>
       <c r="G2301" t="s">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -64922,7 +64925,7 @@
         <v>2.47000002861023</v>
       </c>
       <c r="G2302" t="s">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -64948,7 +64951,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G2303" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -64974,7 +64977,7 @@
         <v>2.46000003814697</v>
       </c>
       <c r="G2304" t="s">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -65000,7 +65003,7 @@
         <v>2.45000004768372</v>
       </c>
       <c r="G2305" t="s">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -65026,7 +65029,7 @@
         <v>2.49499988555908</v>
       </c>
       <c r="G2306" t="s">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -65052,7 +65055,7 @@
         <v>2.51500010490417</v>
       </c>
       <c r="G2307" t="s">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -65104,7 +65107,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G2309" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -65130,7 +65133,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G2310" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -65156,7 +65159,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G2311" t="s">
-        <v>1455</v>
+        <v>1456</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -65182,7 +65185,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2312" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -65208,7 +65211,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2313" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -65234,7 +65237,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2314" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -65260,7 +65263,7 @@
         <v>2.86500000953674</v>
       </c>
       <c r="G2315" t="s">
-        <v>1458</v>
+        <v>1459</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -65286,7 +65289,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G2316" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -65312,7 +65315,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G2317" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -65338,7 +65341,7 @@
         <v>2.78999996185303</v>
       </c>
       <c r="G2318" t="s">
-        <v>1461</v>
+        <v>1462</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -65364,7 +65367,7 @@
         <v>2.875</v>
       </c>
       <c r="G2319" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -65390,7 +65393,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G2320" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -65416,7 +65419,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2321" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -65442,7 +65445,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2322" t="s">
-        <v>1457</v>
+        <v>1458</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -65468,7 +65471,7 @@
         <v>2.82500004768372</v>
       </c>
       <c r="G2323" t="s">
-        <v>1465</v>
+        <v>1466</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -65494,7 +65497,7 @@
         <v>2.76500010490417</v>
       </c>
       <c r="G2324" t="s">
-        <v>1460</v>
+        <v>1461</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -65520,7 +65523,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G2325" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -65546,7 +65549,7 @@
         <v>2.90000009536743</v>
       </c>
       <c r="G2326" t="s">
-        <v>1456</v>
+        <v>1457</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -65572,7 +65575,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2327" t="s">
-        <v>1466</v>
+        <v>1467</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -65598,7 +65601,7 @@
         <v>2.875</v>
       </c>
       <c r="G2328" t="s">
-        <v>1462</v>
+        <v>1463</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -65624,7 +65627,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G2329" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -65650,7 +65653,7 @@
         <v>2.89000010490417</v>
       </c>
       <c r="G2330" t="s">
-        <v>1468</v>
+        <v>1469</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -65676,7 +65679,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2331" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -65702,7 +65705,7 @@
         <v>2.9300000667572</v>
       </c>
       <c r="G2332" t="s">
-        <v>1467</v>
+        <v>1468</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -65728,7 +65731,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G2333" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -65754,7 +65757,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G2334" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -65780,7 +65783,7 @@
         <v>2.625</v>
       </c>
       <c r="G2335" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -65806,7 +65809,7 @@
         <v>2.51999998092651</v>
       </c>
       <c r="G2336" t="s">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -65832,7 +65835,7 @@
         <v>2.5550000667572</v>
       </c>
       <c r="G2337" t="s">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -65858,7 +65861,7 @@
         <v>2.625</v>
       </c>
       <c r="G2338" t="s">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -65884,7 +65887,7 @@
         <v>2.70000004768372</v>
       </c>
       <c r="G2339" t="s">
-        <v>1471</v>
+        <v>1472</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -65910,7 +65913,7 @@
         <v>2.61500000953674</v>
       </c>
       <c r="G2340" t="s">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -65936,7 +65939,7 @@
         <v>2.65000009536743</v>
       </c>
       <c r="G2341" t="s">
-        <v>1472</v>
+        <v>1473</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -65962,7 +65965,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2342" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -65988,7 +65991,7 @@
         <v>2.73000001907349</v>
       </c>
       <c r="G2343" t="s">
-        <v>1474</v>
+        <v>1475</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -66014,7 +66017,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G2344" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -66040,7 +66043,7 @@
         <v>2.8199999332428</v>
       </c>
       <c r="G2345" t="s">
-        <v>1475</v>
+        <v>1476</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -66066,7 +66069,7 @@
         <v>2.75</v>
       </c>
       <c r="G2346" t="s">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -66092,7 +66095,7 @@
         <v>2.81500005722046</v>
       </c>
       <c r="G2347" t="s">
-        <v>1476</v>
+        <v>1477</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -66118,7 +66121,7 @@
         <v>2.82999992370605</v>
       </c>
       <c r="G2348" t="s">
-        <v>1470</v>
+        <v>1471</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -66144,7 +66147,7 @@
         <v>2.79500007629395</v>
       </c>
       <c r="G2349" t="s">
-        <v>1469</v>
+        <v>1470</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -66170,7 +66173,7 @@
         <v>2.86999988555908</v>
       </c>
       <c r="G2350" t="s">
-        <v>1477</v>
+        <v>1478</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -66196,7 +66199,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2351" t="s">
-        <v>1478</v>
+        <v>1479</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -66222,7 +66225,7 @@
         <v>2.80999994277954</v>
       </c>
       <c r="G2352" t="s">
-        <v>1479</v>
+        <v>1480</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -66248,7 +66251,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2353" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -66274,7 +66277,7 @@
         <v>2.95499992370605</v>
       </c>
       <c r="G2354" t="s">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -66300,7 +66303,7 @@
         <v>2.88499999046326</v>
       </c>
       <c r="G2355" t="s">
-        <v>1482</v>
+        <v>1483</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -66326,7 +66329,7 @@
         <v>2.77500009536743</v>
       </c>
       <c r="G2356" t="s">
-        <v>1483</v>
+        <v>1484</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -66352,7 +66355,7 @@
         <v>2.69000005722046</v>
       </c>
       <c r="G2357" t="s">
-        <v>1484</v>
+        <v>1485</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -66378,7 +66381,7 @@
         <v>2.75500011444092</v>
       </c>
       <c r="G2358" t="s">
-        <v>1454</v>
+        <v>1455</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -66404,7 +66407,7 @@
         <v>2.67000007629395</v>
       </c>
       <c r="G2359" t="s">
-        <v>1473</v>
+        <v>1474</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -66430,7 +66433,7 @@
         <v>2.78500008583069</v>
       </c>
       <c r="G2360" t="s">
-        <v>1459</v>
+        <v>1460</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -66456,7 +66459,7 @@
         <v>2.75999999046326</v>
       </c>
       <c r="G2361" t="s">
-        <v>1485</v>
+        <v>1486</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -66482,7 +66485,7 @@
         <v>2.85999989509583</v>
       </c>
       <c r="G2362" t="s">
-        <v>1464</v>
+        <v>1465</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -66508,7 +66511,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G2363" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -66534,7 +66537,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2364" t="s">
-        <v>1480</v>
+        <v>1481</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -66560,7 +66563,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G2365" t="s">
-        <v>1463</v>
+        <v>1464</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -66586,7 +66589,7 @@
         <v>2.95000004768372</v>
       </c>
       <c r="G2366" t="s">
-        <v>1486</v>
+        <v>1487</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -66612,7 +66615,7 @@
         <v>2.98499989509583</v>
       </c>
       <c r="G2367" t="s">
-        <v>1487</v>
+        <v>1488</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -66638,7 +66641,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G2368" t="s">
-        <v>1488</v>
+        <v>1489</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -66664,7 +66667,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2369" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -66690,7 +66693,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2370" t="s">
-        <v>1489</v>
+        <v>1490</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -66716,7 +66719,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2371" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -66742,7 +66745,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G2372" t="s">
-        <v>1491</v>
+        <v>1492</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -66768,7 +66771,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2373" t="s">
-        <v>1490</v>
+        <v>1491</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -66794,7 +66797,7 @@
         <v>3.02999997138977</v>
       </c>
       <c r="G2374" t="s">
-        <v>1492</v>
+        <v>1493</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -66820,7 +66823,7 @@
         <v>3.01500010490417</v>
       </c>
       <c r="G2375" t="s">
-        <v>1493</v>
+        <v>1494</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -66846,7 +66849,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2376" t="s">
-        <v>1494</v>
+        <v>1495</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -66872,7 +66875,7 @@
         <v>3.08500003814697</v>
       </c>
       <c r="G2377" t="s">
-        <v>1495</v>
+        <v>1496</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -66898,7 +66901,7 @@
         <v>3</v>
       </c>
       <c r="G2378" t="s">
-        <v>1496</v>
+        <v>1497</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -66924,7 +66927,7 @@
         <v>2.92000007629395</v>
       </c>
       <c r="G2379" t="s">
-        <v>1497</v>
+        <v>1498</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -66950,7 +66953,7 @@
         <v>2.9449999332428</v>
       </c>
       <c r="G2380" t="s">
-        <v>1498</v>
+        <v>1499</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -66976,7 +66979,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G2381" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -67002,7 +67005,7 @@
         <v>2.91499996185303</v>
       </c>
       <c r="G2382" t="s">
-        <v>1500</v>
+        <v>1501</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -67028,7 +67031,7 @@
         <v>2.91000008583069</v>
       </c>
       <c r="G2383" t="s">
-        <v>1501</v>
+        <v>1502</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -67054,7 +67057,7 @@
         <v>2.94000005722046</v>
       </c>
       <c r="G2384" t="s">
-        <v>1502</v>
+        <v>1503</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -67080,7 +67083,7 @@
         <v>2.93499994277954</v>
       </c>
       <c r="G2385" t="s">
-        <v>1503</v>
+        <v>1504</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -67106,7 +67109,7 @@
         <v>2.88000011444092</v>
       </c>
       <c r="G2386" t="s">
-        <v>1504</v>
+        <v>1505</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -67132,7 +67135,7 @@
         <v>2.84999990463257</v>
       </c>
       <c r="G2387" t="s">
-        <v>1505</v>
+        <v>1506</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -67158,7 +67161,7 @@
         <v>2.84500002861023</v>
       </c>
       <c r="G2388" t="s">
-        <v>1506</v>
+        <v>1507</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -67184,7 +67187,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G2389" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -67210,7 +67213,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2390" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -67236,7 +67239,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2391" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -67262,7 +67265,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G2392" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -67288,7 +67291,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G2393" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -67314,7 +67317,7 @@
         <v>3.10500001907349</v>
       </c>
       <c r="G2394" t="s">
-        <v>1510</v>
+        <v>1511</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -67340,7 +67343,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2395" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -67366,7 +67369,7 @@
         <v>3.05999994277954</v>
       </c>
       <c r="G2396" t="s">
-        <v>1511</v>
+        <v>1512</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -67392,7 +67395,7 @@
         <v>3.07999992370605</v>
       </c>
       <c r="G2397" t="s">
-        <v>1512</v>
+        <v>1513</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -67418,7 +67421,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2398" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -67444,7 +67447,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2399" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -67470,7 +67473,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2400" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -67496,7 +67499,7 @@
         <v>3.07500004768372</v>
       </c>
       <c r="G2401" t="s">
-        <v>1515</v>
+        <v>1516</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -67522,7 +67525,7 @@
         <v>3</v>
       </c>
       <c r="G2402" t="s">
-        <v>1516</v>
+        <v>1517</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -67548,7 +67551,7 @@
         <v>2.90499997138977</v>
       </c>
       <c r="G2403" t="s">
-        <v>1517</v>
+        <v>1518</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -67574,7 +67577,7 @@
         <v>2.98000001907349</v>
       </c>
       <c r="G2404" t="s">
-        <v>1518</v>
+        <v>1519</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -67600,7 +67603,7 @@
         <v>2.97000002861023</v>
       </c>
       <c r="G2405" t="s">
-        <v>1519</v>
+        <v>1520</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -67626,7 +67629,7 @@
         <v>3.0550000667572</v>
       </c>
       <c r="G2406" t="s">
-        <v>1520</v>
+        <v>1521</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -67652,7 +67655,7 @@
         <v>3.02500009536743</v>
       </c>
       <c r="G2407" t="s">
-        <v>1521</v>
+        <v>1522</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -67678,7 +67681,7 @@
         <v>3.03999996185303</v>
       </c>
       <c r="G2408" t="s">
-        <v>1508</v>
+        <v>1509</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -67704,7 +67707,7 @@
         <v>2.97499990463257</v>
       </c>
       <c r="G2409" t="s">
-        <v>1499</v>
+        <v>1500</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -67730,7 +67733,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2410" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -67756,7 +67759,7 @@
         <v>3.04500007629395</v>
       </c>
       <c r="G2411" t="s">
-        <v>1509</v>
+        <v>1510</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -67782,7 +67785,7 @@
         <v>3.04999995231628</v>
       </c>
       <c r="G2412" t="s">
-        <v>1507</v>
+        <v>1508</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -67808,7 +67811,7 @@
         <v>3.0699999332428</v>
       </c>
       <c r="G2413" t="s">
-        <v>1513</v>
+        <v>1514</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -67834,7 +67837,7 @@
         <v>3.09999990463257</v>
       </c>
       <c r="G2414" t="s">
-        <v>1514</v>
+        <v>1515</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -67860,7 +67863,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G2415" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -67886,7 +67889,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2416" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -67912,7 +67915,7 @@
         <v>3.125</v>
       </c>
       <c r="G2417" t="s">
-        <v>1524</v>
+        <v>1525</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -67938,7 +67941,7 @@
         <v>3.16000008583069</v>
       </c>
       <c r="G2418" t="s">
-        <v>1525</v>
+        <v>1526</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -67964,7 +67967,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2419" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -67990,7 +67993,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G2420" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -68016,7 +68019,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2421" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -68042,7 +68045,7 @@
         <v>3.14499998092651</v>
       </c>
       <c r="G2422" t="s">
-        <v>1528</v>
+        <v>1529</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -68068,7 +68071,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2423" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -68094,7 +68097,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2424" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -68120,7 +68123,7 @@
         <v>3.15499997138977</v>
       </c>
       <c r="G2425" t="s">
-        <v>1522</v>
+        <v>1523</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -68146,7 +68149,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2426" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -68172,7 +68175,7 @@
         <v>3.13499999046326</v>
       </c>
       <c r="G2427" t="s">
-        <v>1526</v>
+        <v>1527</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -68198,7 +68201,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2428" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -68224,7 +68227,7 @@
         <v>3.14000010490417</v>
       </c>
       <c r="G2429" t="s">
-        <v>1523</v>
+        <v>1524</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -68250,7 +68253,7 @@
         <v>3.13000011444092</v>
       </c>
       <c r="G2430" t="s">
-        <v>1531</v>
+        <v>1532</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -68276,7 +68279,7 @@
         <v>3.17000007629395</v>
       </c>
       <c r="G2431" t="s">
-        <v>1529</v>
+        <v>1530</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -68302,7 +68305,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G2432" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -68328,7 +68331,7 @@
         <v>3.15000009536743</v>
       </c>
       <c r="G2433" t="s">
-        <v>1527</v>
+        <v>1528</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -68354,7 +68357,7 @@
         <v>3.10999989509583</v>
       </c>
       <c r="G2434" t="s">
-        <v>1533</v>
+        <v>1534</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -68380,7 +68383,7 @@
         <v>3.18499994277954</v>
       </c>
       <c r="G2435" t="s">
-        <v>1534</v>
+        <v>1535</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -68406,7 +68409,7 @@
         <v>3.23000001907349</v>
       </c>
       <c r="G2436" t="s">
-        <v>1535</v>
+        <v>1536</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -68432,7 +68435,7 @@
         <v>3.29500007629395</v>
       </c>
       <c r="G2437" t="s">
-        <v>1536</v>
+        <v>1537</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -68458,7 +68461,7 @@
         <v>3.11999988555908</v>
       </c>
       <c r="G2438" t="s">
-        <v>1530</v>
+        <v>1531</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -68484,7 +68487,7 @@
         <v>3.16499996185303</v>
       </c>
       <c r="G2439" t="s">
-        <v>1537</v>
+        <v>1538</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -68510,7 +68513,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G2440" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -68536,7 +68539,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G2441" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -68562,7 +68565,7 @@
         <v>3.27999997138977</v>
       </c>
       <c r="G2442" t="s">
-        <v>1539</v>
+        <v>1540</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -68588,7 +68591,7 @@
         <v>3.24000000953674</v>
       </c>
       <c r="G2443" t="s">
-        <v>1540</v>
+        <v>1541</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -68614,7 +68617,7 @@
         <v>3.22499990463257</v>
       </c>
       <c r="G2444" t="s">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -68640,7 +68643,7 @@
         <v>3.17499995231628</v>
       </c>
       <c r="G2445" t="s">
-        <v>1532</v>
+        <v>1533</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -68666,7 +68669,7 @@
         <v>3.1949999332428</v>
       </c>
       <c r="G2446" t="s">
-        <v>1542</v>
+        <v>1543</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -68692,7 +68695,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2447" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -68718,7 +68721,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2448" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -68744,7 +68747,7 @@
         <v>3.20000004768372</v>
       </c>
       <c r="G2449" t="s">
-        <v>1543</v>
+        <v>1544</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -68770,7 +68773,7 @@
         <v>3.25999999046326</v>
       </c>
       <c r="G2450" t="s">
-        <v>1544</v>
+        <v>1545</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -68796,7 +68799,7 @@
         <v>3.28500008583069</v>
       </c>
       <c r="G2451" t="s">
-        <v>1545</v>
+        <v>1546</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -68822,7 +68825,7 @@
         <v>3.31500005722046</v>
       </c>
       <c r="G2452" t="s">
-        <v>1546</v>
+        <v>1547</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -68848,7 +68851,7 @@
         <v>3.375</v>
       </c>
       <c r="G2453" t="s">
-        <v>1547</v>
+        <v>1548</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -68874,7 +68877,7 @@
         <v>3.28999996185303</v>
       </c>
       <c r="G2454" t="s">
-        <v>1548</v>
+        <v>1549</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -68900,7 +68903,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2455" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -68926,7 +68929,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2456" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -68952,7 +68955,7 @@
         <v>3.3050000667572</v>
       </c>
       <c r="G2457" t="s">
-        <v>1551</v>
+        <v>1552</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -68978,7 +68981,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G2458" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -69004,7 +69007,7 @@
         <v>3.24499988555908</v>
       </c>
       <c r="G2459" t="s">
-        <v>1553</v>
+        <v>1554</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -69030,7 +69033,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2460" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -69056,7 +69059,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2461" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -69082,7 +69085,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2462" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -69108,7 +69111,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2463" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -69134,7 +69137,7 @@
         <v>3.32500004768372</v>
       </c>
       <c r="G2464" t="s">
-        <v>1538</v>
+        <v>1539</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -69160,7 +69163,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2465" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -69186,7 +69189,7 @@
         <v>3.35500001907349</v>
       </c>
       <c r="G2466" t="s">
-        <v>1552</v>
+        <v>1553</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -69212,7 +69215,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G2467" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -69238,7 +69241,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2468" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -69264,7 +69267,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2469" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -69290,7 +69293,7 @@
         <v>3.35999989509583</v>
       </c>
       <c r="G2470" t="s">
-        <v>1558</v>
+        <v>1559</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -69316,7 +69319,7 @@
         <v>3.36999988555908</v>
       </c>
       <c r="G2471" t="s">
-        <v>1557</v>
+        <v>1558</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -69342,7 +69345,7 @@
         <v>3.40000009536743</v>
       </c>
       <c r="G2472" t="s">
-        <v>1559</v>
+        <v>1560</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -69368,7 +69371,7 @@
         <v>3.34999990463257</v>
       </c>
       <c r="G2473" t="s">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -69394,7 +69397,7 @@
         <v>3.32999992370605</v>
       </c>
       <c r="G2474" t="s">
-        <v>1549</v>
+        <v>1550</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -69420,7 +69423,7 @@
         <v>3.33999991416931</v>
       </c>
       <c r="G2475" t="s">
-        <v>1555</v>
+        <v>1556</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -69446,7 +69449,7 @@
         <v>3.27500009536743</v>
       </c>
       <c r="G2476" t="s">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -69472,7 +69475,7 @@
         <v>3.3199999332428</v>
       </c>
       <c r="G2477" t="s">
-        <v>1556</v>
+        <v>1557</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -69498,7 +69501,7 @@
         <v>3.36500000953674</v>
       </c>
       <c r="G2478" t="s">
-        <v>1560</v>
+        <v>1561</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -69524,7 +69527,7 @@
         <v>3.45000004768372</v>
       </c>
       <c r="G2479" t="s">
-        <v>1561</v>
+        <v>1562</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -69550,7 +69553,7 @@
         <v>3.5</v>
       </c>
       <c r="G2480" t="s">
-        <v>1562</v>
+        <v>1563</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -69576,7 +69579,7 @@
         <v>3.47000002861023</v>
       </c>
       <c r="G2481" t="s">
-        <v>1563</v>
+        <v>1564</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -69602,7 +69605,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G2482" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -69628,7 +69631,7 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G2483" t="s">
-        <v>1565</v>
+        <v>1566</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -69654,7 +69657,7 @@
         <v>3.45499992370605</v>
       </c>
       <c r="G2484" t="s">
-        <v>1566</v>
+        <v>1567</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -69680,7 +69683,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2485" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -69706,7 +69709,7 @@
         <v>3.47499990463257</v>
       </c>
       <c r="G2486" t="s">
-        <v>1568</v>
+        <v>1569</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -69732,7 +69735,7 @@
         <v>3.46000003814697</v>
       </c>
       <c r="G2487" t="s">
-        <v>1567</v>
+        <v>1568</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -69758,7 +69761,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2488" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -69784,7 +69787,7 @@
         <v>3.50500011444092</v>
       </c>
       <c r="G2489" t="s">
-        <v>1570</v>
+        <v>1571</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -69810,7 +69813,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2490" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -69836,7 +69839,7 @@
         <v>3.5699999332428</v>
       </c>
       <c r="G2491" t="s">
-        <v>1571</v>
+        <v>1572</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -69862,7 +69865,7 @@
         <v>3.49499988555908</v>
       </c>
       <c r="G2492" t="s">
-        <v>1572</v>
+        <v>1573</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -69888,7 +69891,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2493" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -69914,7 +69917,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2494" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -69940,7 +69943,7 @@
         <v>3.55999994277954</v>
       </c>
       <c r="G2495" t="s">
-        <v>1573</v>
+        <v>1574</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -69966,7 +69969,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2496" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -69992,7 +69995,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2497" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -70018,7 +70021,7 @@
         <v>3.49000000953674</v>
       </c>
       <c r="G2498" t="s">
-        <v>1574</v>
+        <v>1575</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -70044,7 +70047,7 @@
         <v>3.54500007629395</v>
       </c>
       <c r="G2499" t="s">
-        <v>1575</v>
+        <v>1576</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -70070,7 +70073,7 @@
         <v>3.53999996185303</v>
       </c>
       <c r="G2500" t="s">
-        <v>1569</v>
+        <v>1570</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -70096,7 +70099,7 @@
         <v>3.52500009536743</v>
       </c>
       <c r="G2501" t="s">
-        <v>1564</v>
+        <v>1565</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -70104,7 +70107,7 @@
     </row>
     <row r="2502">
       <c r="A2502" s="1" t="n">
-        <v>45961.6911574074</v>
+        <v>45961.3333333333</v>
       </c>
       <c r="B2502" t="n">
         <v>49818</v>
@@ -70122,9 +70125,35 @@
         <v>3.51500010490417</v>
       </c>
       <c r="G2502" t="s">
+        <v>1566</v>
+      </c>
+      <c r="H2502" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2503">
+      <c r="A2503" s="1" t="n">
+        <v>45964.6910763889</v>
+      </c>
+      <c r="B2503" t="n">
+        <v>69645</v>
+      </c>
+      <c r="C2503" t="n">
+        <v>3.54999995231628</v>
+      </c>
+      <c r="D2503" t="n">
+        <v>3.50500011444092</v>
+      </c>
+      <c r="E2503" t="n">
+        <v>3.53500008583069</v>
+      </c>
+      <c r="F2503" t="n">
+        <v>3.52500009536743</v>
+      </c>
+      <c r="G2503" t="s">
         <v>1565</v>
       </c>
-      <c r="H2502" t="s">
+      <c r="H2503" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1582" uniqueCount="1582">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1583" uniqueCount="1583">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,16 +44,16 @@
     <t xml:space="preserve">IGD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81178855895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76804447174072</t>
+    <t xml:space="preserve">4.8117880821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76804494857788</t>
   </si>
   <si>
     <t xml:space="preserve">4.7653112411499</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64774990081787</t>
+    <t xml:space="preserve">4.64775037765503</t>
   </si>
   <si>
     <t xml:space="preserve">4.53839111328125</t>
@@ -62,22 +62,22 @@
     <t xml:space="preserve">4.56573104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67235565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55206060409546</t>
+    <t xml:space="preserve">4.67235660552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55206155776978</t>
   </si>
   <si>
     <t xml:space="preserve">4.33334302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16383790969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04627752304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60884141921997</t>
+    <t xml:space="preserve">4.16383743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04627656936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60884118080139</t>
   </si>
   <si>
     <t xml:space="preserve">3.88223814964294</t>
@@ -86,58 +86,58 @@
     <t xml:space="preserve">3.95605540275574</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03807497024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97519397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785404205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81388926506042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96425747871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07088184356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92051458358765</t>
+    <t xml:space="preserve">4.0380744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97519373893738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785380363464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81388878822327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96425724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07088232040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92051386833191</t>
   </si>
   <si>
     <t xml:space="preserve">3.69632863998413</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78654932975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45573925971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49948239326477</t>
+    <t xml:space="preserve">3.78654956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45573902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49948287010193</t>
   </si>
   <si>
     <t xml:space="preserve">3.69086050987244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56783199310303</t>
+    <t xml:space="preserve">3.56783270835876</t>
   </si>
   <si>
     <t xml:space="preserve">3.63891506195068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88497281074524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755923271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93691754341125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87130284309387</t>
+    <t xml:space="preserve">3.88497233390808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755899429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93691778182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87130236625671</t>
   </si>
   <si>
     <t xml:space="preserve">4.05994653701782</t>
@@ -146,16 +146,16 @@
     <t xml:space="preserve">4.00800085067749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95332169532776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98612976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99159741401672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03260707855225</t>
+    <t xml:space="preserve">3.95332145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98612952232361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99159717559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03260660171509</t>
   </si>
   <si>
     <t xml:space="preserve">4.05447816848755</t>
@@ -164,19 +164,19 @@
     <t xml:space="preserve">4.2403883934021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21031475067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37435293197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33607769012451</t>
+    <t xml:space="preserve">4.21031522750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37435340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33607864379883</t>
   </si>
   <si>
     <t xml:space="preserve">4.34701347351074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33881092071533</t>
+    <t xml:space="preserve">4.33881139755249</t>
   </si>
   <si>
     <t xml:space="preserve">4.42903280258179</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">4.51105165481567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46184062957764</t>
+    <t xml:space="preserve">4.46184015274048</t>
   </si>
   <si>
     <t xml:space="preserve">4.57119941711426</t>
@@ -197,223 +197,223 @@
     <t xml:space="preserve">4.67509031295776</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60947513580322</t>
+    <t xml:space="preserve">4.60947418212891</t>
   </si>
   <si>
     <t xml:space="preserve">4.54932689666748</t>
   </si>
   <si>
+    <t xml:space="preserve">4.48371171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34974813461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42083024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42356491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26499462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22398471832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22671842575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33060884475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40169334411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30600452423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36615133285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26772832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32514190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29233407974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27046203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29506778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39895868301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30873775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38802289962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42629909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34427928924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39075708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30326986312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49522352218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57292604446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65062808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67940664291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69379615783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66213941574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61609363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57580327987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63623905181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63048362731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63336086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6391167640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56429290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35133028030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08368873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95130705833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9714527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16139125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20168209075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.247727394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27650594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03476524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755851745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8448269367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633730888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470474243164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15851354598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784887313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83619284629822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96281862258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05778789520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0923228263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25636100769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40313196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33406352996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5182466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41752099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45493316650391</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.4837121963501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34974718093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42083072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42356491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26499462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25405883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22398471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22671842575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23765468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3306097984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40169286727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31967401504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3060040473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36615133285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26772832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32514190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29233407974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27046203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29506778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39895915985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30873775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38802289962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42629957199097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34427976608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39075660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3032693862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49522304534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57292604446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65062808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091844558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67940664291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69379615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66213989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61609363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57580327987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63623905181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63048362731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63336086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6391167640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56429243087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35133028030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08368873596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95130777359009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97145223617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16139125823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20168161392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24772691726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27650594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03476524353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755875587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84482622146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633778572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15851306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01749849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784887313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83619284629822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96281838417053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05778837203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09232330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25636053085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40313243865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33406352996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5182466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41752052307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45493316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37435340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45781230926514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53839159011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52975749969482</t>
+    <t xml:space="preserve">4.45781135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53839206695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52975797653198</t>
   </si>
   <si>
     <t xml:space="preserve">4.48946809768677</t>
@@ -431,31 +431,31 @@
     <t xml:space="preserve">4.46644449234009</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3829870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36572027206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41464376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35996389389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33694124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29377269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3139181137085</t>
+    <t xml:space="preserve">4.38298654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36571979522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41464328765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35996294021606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33694076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29377317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31391763687134</t>
   </si>
   <si>
     <t xml:space="preserve">4.19016981124878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19880342483521</t>
+    <t xml:space="preserve">4.19880390167236</t>
   </si>
   <si>
     <t xml:space="preserve">4.22182655334473</t>
@@ -476,22 +476,22 @@
     <t xml:space="preserve">4.19592618942261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16714763641357</t>
+    <t xml:space="preserve">4.16714811325073</t>
   </si>
   <si>
     <t xml:space="preserve">4.15563583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11534547805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20743656158447</t>
+    <t xml:space="preserve">4.1153450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20743703842163</t>
   </si>
   <si>
     <t xml:space="preserve">4.14700174331665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1786584854126</t>
+    <t xml:space="preserve">4.17865800857544</t>
   </si>
   <si>
     <t xml:space="preserve">4.07505559921265</t>
@@ -506,55 +506,55 @@
     <t xml:space="preserve">3.79878067970276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77575755119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83907079696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74697852134705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74985671043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85921597480774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82468152046204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79590225219727</t>
+    <t xml:space="preserve">3.77575731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83906984329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74697923660278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7498562335968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85921621322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82468104362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79590272903442</t>
   </si>
   <si>
     <t xml:space="preserve">3.87936091423035</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81029200553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439116477966</t>
+    <t xml:space="preserve">3.81029224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439140319824</t>
   </si>
   <si>
     <t xml:space="preserve">3.76424598693848</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72971129417419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71244478225708</t>
+    <t xml:space="preserve">3.72971177101135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71244406700134</t>
   </si>
   <si>
     <t xml:space="preserve">3.72395634651184</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84194755554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735307693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06354427337646</t>
+    <t xml:space="preserve">3.84194827079773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735355377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06354379653931</t>
   </si>
   <si>
     <t xml:space="preserve">4.10958957672119</t>
@@ -569,76 +569,76 @@
     <t xml:space="preserve">4.03764295578003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00310850143433</t>
+    <t xml:space="preserve">4.00310897827148</t>
   </si>
   <si>
     <t xml:space="preserve">3.97432994842529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91389536857605</t>
+    <t xml:space="preserve">3.91389513015747</t>
   </si>
   <si>
     <t xml:space="preserve">3.93979597091675</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92540645599365</t>
+    <t xml:space="preserve">3.92540621757507</t>
   </si>
   <si>
     <t xml:space="preserve">3.92828440666199</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89662742614746</t>
+    <t xml:space="preserve">3.89662790298462</t>
   </si>
   <si>
     <t xml:space="preserve">3.84770393371582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75273489952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75849008560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55703973770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64337539672852</t>
+    <t xml:space="preserve">3.75273466110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75849032402039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55703997612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64337515830994</t>
   </si>
   <si>
     <t xml:space="preserve">3.66927647590637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65776491165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58006262779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59732985496521</t>
+    <t xml:space="preserve">3.65776467323303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5800621509552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59732961654663</t>
   </si>
   <si>
     <t xml:space="preserve">3.6030855178833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63186454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62610864639282</t>
+    <t xml:space="preserve">3.63186430931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62610840797424</t>
   </si>
   <si>
     <t xml:space="preserve">3.6606433391571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61459708213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80453610420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95994067192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07217693328857</t>
+    <t xml:space="preserve">3.61459732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80453658103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95994019508362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07217741012573</t>
   </si>
   <si>
     <t xml:space="preserve">4.0433988571167</t>
@@ -650,73 +650,73 @@
     <t xml:space="preserve">4.13261222839355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12110233306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36859703063965</t>
+    <t xml:space="preserve">4.12110137939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36859750747681</t>
   </si>
   <si>
     <t xml:space="preserve">4.28226137161255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33981847763062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3484525680542</t>
+    <t xml:space="preserve">4.33981895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34845161437988</t>
   </si>
   <si>
     <t xml:space="preserve">4.33118534088135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30240678787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2649941444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27074956893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22758197784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21319246292114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18153619766235</t>
+    <t xml:space="preserve">4.30240631103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27075004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2275824546814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2131929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18153667449951</t>
   </si>
   <si>
     <t xml:space="preserve">4.09807825088501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00598669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10383415222168</t>
+    <t xml:space="preserve">4.00598621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.103835105896</t>
   </si>
   <si>
     <t xml:space="preserve">4.02900981903076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06929922103882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21894836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30816268920898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14988088607788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47220039367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51249122619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37723159790039</t>
+    <t xml:space="preserve">4.06929969787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04627704620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21894788742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30816221237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14988040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47220087051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51249074935913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37723064422607</t>
   </si>
   <si>
     <t xml:space="preserve">4.44342184066772</t>
@@ -725,7 +725,7 @@
     <t xml:space="preserve">4.59307050704956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62472724914551</t>
+    <t xml:space="preserve">4.62472820281982</t>
   </si>
   <si>
     <t xml:space="preserve">4.57004833221436</t>
@@ -737,43 +737,43 @@
     <t xml:space="preserve">4.70818567276001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80315399169922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73120832443237</t>
+    <t xml:space="preserve">4.80315446853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73120784759521</t>
   </si>
   <si>
     <t xml:space="preserve">4.70530796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70242977142334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64487218856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62184906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54702520370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52688026428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46068954467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6045823097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71394109725952</t>
+    <t xml:space="preserve">4.7024302482605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64487314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62185001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54702568054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52687978744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46068906784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60458278656006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71394062042236</t>
   </si>
   <si>
     <t xml:space="preserve">4.66501712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74559783935547</t>
+    <t xml:space="preserve">4.74559736251831</t>
   </si>
   <si>
     <t xml:space="preserve">4.76574277877808</t>
@@ -785,16 +785,16 @@
     <t xml:space="preserve">4.78301000595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77149868011475</t>
+    <t xml:space="preserve">4.77149820327759</t>
   </si>
   <si>
     <t xml:space="preserve">4.8233003616333</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92690277099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94992685317993</t>
+    <t xml:space="preserve">4.92690372467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94992637634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.98446035385132</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">4.86359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82905626296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8759241104126</t>
+    <t xml:space="preserve">4.82905578613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87592363357544</t>
   </si>
   <si>
     <t xml:space="preserve">4.91160154342651</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">4.93538570404053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89970922470093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9205207824707</t>
+    <t xml:space="preserve">4.89970874786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92052030563354</t>
   </si>
   <si>
     <t xml:space="preserve">5.01268720626831</t>
@@ -836,37 +836,37 @@
     <t xml:space="preserve">4.96809101104736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9710636138916</t>
+    <t xml:space="preserve">4.97106409072876</t>
   </si>
   <si>
     <t xml:space="preserve">4.89376258850098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94727802276611</t>
+    <t xml:space="preserve">4.94727849960327</t>
   </si>
   <si>
     <t xml:space="preserve">4.94133281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92944002151489</t>
+    <t xml:space="preserve">4.92943954467773</t>
   </si>
   <si>
     <t xml:space="preserve">4.88781595230103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85511112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79862213134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77186441421509</t>
+    <t xml:space="preserve">4.85511207580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79862260818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77186489105225</t>
   </si>
   <si>
     <t xml:space="preserve">4.75105285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78672981262207</t>
+    <t xml:space="preserve">4.78673028945923</t>
   </si>
   <si>
     <t xml:space="preserve">4.73321437835693</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">4.53401470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.584557056427</t>
+    <t xml:space="preserve">4.58455753326416</t>
   </si>
   <si>
     <t xml:space="preserve">4.61726188659668</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">4.72726726531982</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81646156311035</t>
+    <t xml:space="preserve">4.81646108627319</t>
   </si>
   <si>
     <t xml:space="preserve">4.83132696151733</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">4.94430541992188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98295593261719</t>
+    <t xml:space="preserve">4.9829568862915</t>
   </si>
   <si>
     <t xml:space="preserve">4.95322513580322</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">4.90565538406372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84619235992432</t>
+    <t xml:space="preserve">4.84619283676147</t>
   </si>
   <si>
     <t xml:space="preserve">4.89078950881958</t>
@@ -938,13 +938,13 @@
     <t xml:space="preserve">4.98592948913574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15837049484253</t>
+    <t xml:space="preserve">5.15837097167969</t>
   </si>
   <si>
     <t xml:space="preserve">5.12566661834717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11080121994019</t>
+    <t xml:space="preserve">5.11080026626587</t>
   </si>
   <si>
     <t xml:space="preserve">5.07512283325195</t>
@@ -959,40 +959,40 @@
     <t xml:space="preserve">5.11377429962158</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0394458770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02755308151245</t>
+    <t xml:space="preserve">5.03944540023804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02755260467529</t>
   </si>
   <si>
     <t xml:space="preserve">4.97701025009155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05133819580078</t>
+    <t xml:space="preserve">5.05133771896362</t>
   </si>
   <si>
     <t xml:space="preserve">4.99484872817993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01566171646118</t>
+    <t xml:space="preserve">5.01566123962402</t>
   </si>
   <si>
     <t xml:space="preserve">5.06620407104492</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1375584602356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23269891738892</t>
+    <t xml:space="preserve">5.13755893707275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23269844055176</t>
   </si>
   <si>
     <t xml:space="preserve">5.2445912361145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23864555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19702100753784</t>
+    <t xml:space="preserve">5.23864507675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19702196121216</t>
   </si>
   <si>
     <t xml:space="preserve">5.17323637008667</t>
@@ -1001,55 +1001,55 @@
     <t xml:space="preserve">5.18512868881226</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20891380310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19404888153076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2475643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25053787231445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26242971420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14945077896118</t>
+    <t xml:space="preserve">5.20891427993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1940484046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24756383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25053739547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26243019104004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1494517326355</t>
   </si>
   <si>
     <t xml:space="preserve">5.16431713104248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21485996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35162353515625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.4408164024353</t>
+    <t xml:space="preserve">5.21485948562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35162401199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.44081687927246</t>
   </si>
   <si>
     <t xml:space="preserve">5.64893674850464</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6786675453186</t>
+    <t xml:space="preserve">5.67866706848145</t>
   </si>
   <si>
     <t xml:space="preserve">5.47054862976074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.4675760269165</t>
+    <t xml:space="preserve">5.46757555007935</t>
   </si>
   <si>
     <t xml:space="preserve">5.55974245071411</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59541988372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58947420120239</t>
+    <t xml:space="preserve">5.59541940689087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58947467803955</t>
   </si>
   <si>
     <t xml:space="preserve">5.50325298309326</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">5.75002288818359</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90165185928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91651821136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20193719863892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19004487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11274337768555</t>
+    <t xml:space="preserve">5.90165233612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91651773452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20193815231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19004583358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11274385452271</t>
   </si>
   <si>
     <t xml:space="preserve">6.12463617324829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15436792373657</t>
+    <t xml:space="preserve">6.15436744689941</t>
   </si>
   <si>
     <t xml:space="preserve">6.03544187545776</t>
@@ -1088,22 +1088,22 @@
     <t xml:space="preserve">5.97597980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8897590637207</t>
+    <t xml:space="preserve">5.88975954055786</t>
   </si>
   <si>
     <t xml:space="preserve">6.0057110786438</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29113054275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3446478843689</t>
+    <t xml:space="preserve">6.29113101959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34464740753174</t>
   </si>
   <si>
     <t xml:space="preserve">6.17815160751343</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39816331863403</t>
+    <t xml:space="preserve">6.39816379547119</t>
   </si>
   <si>
     <t xml:space="preserve">6.38627147674561</t>
@@ -1112,25 +1112,25 @@
     <t xml:space="preserve">6.33275508880615</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43384170532227</t>
+    <t xml:space="preserve">6.43384075164795</t>
   </si>
   <si>
     <t xml:space="preserve">6.46951866149902</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41600179672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40410947799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24356079101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35653972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44573354721069</t>
+    <t xml:space="preserve">6.41600227355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40410995483398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24356126785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35654020309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44573402404785</t>
   </si>
   <si>
     <t xml:space="preserve">6.60033655166626</t>
@@ -1139,70 +1139,70 @@
     <t xml:space="preserve">6.58844327926636</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71926069259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65979862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48141050338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07111978530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82732343673706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76786088943481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80948543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73813009262085</t>
+    <t xml:space="preserve">6.71926116943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65979766845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48141098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07111930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82732391357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76786136627197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80948448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68164014816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73812913894653</t>
   </si>
   <si>
     <t xml:space="preserve">5.81840419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7321834564209</t>
+    <t xml:space="preserve">5.73218393325806</t>
   </si>
   <si>
     <t xml:space="preserve">5.72623634338379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8570556640625</t>
+    <t xml:space="preserve">5.85705423355103</t>
   </si>
   <si>
     <t xml:space="preserve">5.86300134658813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95814085006714</t>
+    <t xml:space="preserve">5.9581413269043</t>
   </si>
   <si>
     <t xml:space="preserve">5.92840957641602</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76191520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7975926399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75596809387207</t>
+    <t xml:space="preserve">5.76191473007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70839834213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79759168624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75596857070923</t>
   </si>
   <si>
     <t xml:space="preserve">5.6846137046814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69650650024414</t>
+    <t xml:space="preserve">5.69650602340698</t>
   </si>
   <si>
     <t xml:space="preserve">5.66082859039307</t>
@@ -1211,25 +1211,25 @@
     <t xml:space="preserve">5.50622701644897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45865631103516</t>
+    <t xml:space="preserve">5.45865678787231</t>
   </si>
   <si>
     <t xml:space="preserve">5.33973121643066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15539741516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3100004196167</t>
+    <t xml:space="preserve">5.15539693832397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30999994277954</t>
   </si>
   <si>
     <t xml:space="preserve">5.0364727973938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91754770278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00079488754272</t>
+    <t xml:space="preserve">4.91754722595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00079536437988</t>
   </si>
   <si>
     <t xml:space="preserve">4.86997699737549</t>
@@ -1238,16 +1238,16 @@
     <t xml:space="preserve">4.85213899612427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14350557327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75699853897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7944598197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70823907852173</t>
+    <t xml:space="preserve">5.14350461959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75699901580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79446029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70824003219604</t>
   </si>
   <si>
     <t xml:space="preserve">4.58812522888184</t>
@@ -1256,10 +1256,10 @@
     <t xml:space="preserve">4.47752618789673</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46860551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53104114532471</t>
+    <t xml:space="preserve">4.46860599517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53104162216187</t>
   </si>
   <si>
     <t xml:space="preserve">4.66483211517334</t>
@@ -1268,19 +1268,19 @@
     <t xml:space="preserve">4.66839933395386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55482625961304</t>
+    <t xml:space="preserve">4.55482578277588</t>
   </si>
   <si>
     <t xml:space="preserve">4.49774217605591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51260805130005</t>
+    <t xml:space="preserve">4.51260852813721</t>
   </si>
   <si>
     <t xml:space="preserve">4.41211652755737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36811351776123</t>
+    <t xml:space="preserve">4.36811399459839</t>
   </si>
   <si>
     <t xml:space="preserve">4.29913759231567</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">4.48525524139404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46503782272339</t>
+    <t xml:space="preserve">4.46503829956055</t>
   </si>
   <si>
     <t xml:space="preserve">4.44184732437134</t>
@@ -1298,22 +1298,22 @@
     <t xml:space="preserve">4.29378652572632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19210529327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57336139678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65459394454956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.10297441482544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85351848602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95713901519775</t>
+    <t xml:space="preserve">4.19210577011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57336091995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6545934677124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1029748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85351896286011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95713949203491</t>
   </si>
   <si>
     <t xml:space="preserve">5.14391183853149</t>
@@ -1328,37 +1328,37 @@
     <t xml:space="preserve">5.17781209945679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01278734207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96993207931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05244445800781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9891209602356</t>
+    <t xml:space="preserve">5.01278686523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96993160247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05244398117065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98912048339844</t>
   </si>
   <si>
     <t xml:space="preserve">4.94498634338379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03197622299194</t>
+    <t xml:space="preserve">5.03197574615479</t>
   </si>
   <si>
     <t xml:space="preserve">5.01598501205444</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02621984481812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0147066116333</t>
+    <t xml:space="preserve">5.0262188911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01470613479614</t>
   </si>
   <si>
     <t xml:space="preserve">5.08506536483765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93539142608643</t>
+    <t xml:space="preserve">4.93539190292358</t>
   </si>
   <si>
     <t xml:space="preserve">4.92579793930054</t>
@@ -1367,22 +1367,22 @@
     <t xml:space="preserve">4.96545457839966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02557992935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04029130935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02110242843628</t>
+    <t xml:space="preserve">5.02557945251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04029083251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02110195159912</t>
   </si>
   <si>
     <t xml:space="preserve">5.11704683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0594801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06971454620361</t>
+    <t xml:space="preserve">5.05947971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06971406936646</t>
   </si>
   <si>
     <t xml:space="preserve">5.24497270584106</t>
@@ -1391,22 +1391,22 @@
     <t xml:space="preserve">5.14135313034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97888708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76460981369019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83496952056885</t>
+    <t xml:space="preserve">4.97888660430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76461029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83496999740601</t>
   </si>
   <si>
     <t xml:space="preserve">4.78124046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73326778411865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71471929550171</t>
+    <t xml:space="preserve">4.73326873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71471881866455</t>
   </si>
   <si>
     <t xml:space="preserve">4.66290950775146</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">4.55097341537476</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32710266113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57399988174438</t>
+    <t xml:space="preserve">4.32710313796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57400035858154</t>
   </si>
   <si>
     <t xml:space="preserve">4.65267515182495</t>
@@ -1430,13 +1430,13 @@
     <t xml:space="preserve">4.72943115234375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81961870193481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79403352737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.68401670455933</t>
+    <t xml:space="preserve">4.81961822509766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79403305053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.68401622772217</t>
   </si>
   <si>
     <t xml:space="preserve">4.58679294586182</t>
@@ -1448,16 +1448,16 @@
     <t xml:space="preserve">4.99108505249023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88932418823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9842095375061</t>
+    <t xml:space="preserve">4.88932466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98421001434326</t>
   </si>
   <si>
     <t xml:space="preserve">5.03165197372437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79375219345093</t>
+    <t xml:space="preserve">4.79375267028809</t>
   </si>
   <si>
     <t xml:space="preserve">4.79512691497803</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">4.74630975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86113452911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79031467437744</t>
+    <t xml:space="preserve">4.86113405227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79031419754028</t>
   </si>
   <si>
     <t xml:space="preserve">4.81300401687622</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">4.73187112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84532022476196</t>
+    <t xml:space="preserve">4.84532070159912</t>
   </si>
   <si>
     <t xml:space="preserve">4.78687620162964</t>
@@ -1499,19 +1499,19 @@
     <t xml:space="preserve">4.91614007949829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97802114486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96770763397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8267560005188</t>
+    <t xml:space="preserve">4.97802066802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96770811080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82675552368164</t>
   </si>
   <si>
     <t xml:space="preserve">4.85013294219971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86044645309448</t>
+    <t xml:space="preserve">4.86044692993164</t>
   </si>
   <si>
     <t xml:space="preserve">4.89963817596436</t>
@@ -1520,31 +1520,31 @@
     <t xml:space="preserve">4.93470430374146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99177265167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0543417930603</t>
+    <t xml:space="preserve">4.99177360534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05434226989746</t>
   </si>
   <si>
     <t xml:space="preserve">4.96151971817017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9793963432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99245977401733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8583836555481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98489665985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85219621658325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90307569503784</t>
+    <t xml:space="preserve">4.97939682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99246025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85838413238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98489713668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85219573974609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.903076171875</t>
   </si>
   <si>
     <t xml:space="preserve">4.97183322906494</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">4.93882989883423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91682720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83363199234009</t>
+    <t xml:space="preserve">4.91682767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83363151550293</t>
   </si>
   <si>
     <t xml:space="preserve">4.76556205749512</t>
@@ -1565,31 +1565,31 @@
     <t xml:space="preserve">4.75868654251099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75043535232544</t>
+    <t xml:space="preserve">4.75043487548828</t>
   </si>
   <si>
     <t xml:space="preserve">4.67067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58129215240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5427885055542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4630298614502</t>
+    <t xml:space="preserve">4.58129262924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54278802871704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46303033828735</t>
   </si>
   <si>
     <t xml:space="preserve">4.48228216171265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51941013336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60604476928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59779405593872</t>
+    <t xml:space="preserve">4.51941108703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60604524612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59779453277588</t>
   </si>
   <si>
     <t xml:space="preserve">4.52972412109375</t>
@@ -1607,49 +1607,49 @@
     <t xml:space="preserve">4.57235383987427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55241441726685</t>
+    <t xml:space="preserve">4.55241394042969</t>
   </si>
   <si>
     <t xml:space="preserve">4.50634717941284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51597309112549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49053335189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52078533172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51872301101685</t>
+    <t xml:space="preserve">4.51597261428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49053239822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52078580856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.518723487854</t>
   </si>
   <si>
     <t xml:space="preserve">4.53041219711304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5104718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52491140365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48503160476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47746849060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78412675857544</t>
+    <t xml:space="preserve">4.51047277450562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52491188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.485032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47746896743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78412580490112</t>
   </si>
   <si>
     <t xml:space="preserve">4.6651759147644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65417575836182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70299291610718</t>
+    <t xml:space="preserve">4.6541748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70299243927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.73049545288086</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">4.71055555343628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64661169052124</t>
+    <t xml:space="preserve">4.64661121368408</t>
   </si>
   <si>
     <t xml:space="preserve">4.63354778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55035161972046</t>
+    <t xml:space="preserve">4.5503511428833</t>
   </si>
   <si>
     <t xml:space="preserve">4.50840950012207</t>
@@ -1673,19 +1673,19 @@
     <t xml:space="preserve">4.41558742523193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42727613449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40046072006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33239126205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2223801612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20450305938721</t>
+    <t xml:space="preserve">4.42727661132812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40046119689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22237968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20450258255005</t>
   </si>
   <si>
     <t xml:space="preserve">4.16256093978882</t>
@@ -1694,10 +1694,10 @@
     <t xml:space="preserve">4.06630086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09311628341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98791766166687</t>
+    <t xml:space="preserve">4.09311676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98791742324829</t>
   </si>
   <si>
     <t xml:space="preserve">4.05942487716675</t>
@@ -1718,13 +1718,13 @@
     <t xml:space="preserve">4.09105348587036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08830308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13162040710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21962928771973</t>
+    <t xml:space="preserve">4.088303565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13161993026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21962976455688</t>
   </si>
   <si>
     <t xml:space="preserve">4.28563642501831</t>
@@ -1733,13 +1733,13 @@
     <t xml:space="preserve">4.29732513427734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28976154327393</t>
+    <t xml:space="preserve">4.28976202011108</t>
   </si>
   <si>
     <t xml:space="preserve">4.22100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15293502807617</t>
+    <t xml:space="preserve">4.15293455123901</t>
   </si>
   <si>
     <t xml:space="preserve">4.36608219146729</t>
@@ -1748,34 +1748,34 @@
     <t xml:space="preserve">4.27601051330566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22513055801392</t>
+    <t xml:space="preserve">4.2251296043396</t>
   </si>
   <si>
     <t xml:space="preserve">4.19487714767456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12749481201172</t>
+    <t xml:space="preserve">4.12749528884888</t>
   </si>
   <si>
     <t xml:space="preserve">4.1522479057312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13505792617798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09174108505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03260946273804</t>
+    <t xml:space="preserve">4.13505840301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09174156188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0326099395752</t>
   </si>
   <si>
     <t xml:space="preserve">4.03467273712158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05461168289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14537191390991</t>
+    <t xml:space="preserve">4.054612159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14537143707275</t>
   </si>
   <si>
     <t xml:space="preserve">4.2237548828125</t>
@@ -1787,31 +1787,31 @@
     <t xml:space="preserve">4.19900226593018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18868923187256</t>
+    <t xml:space="preserve">4.1886887550354</t>
   </si>
   <si>
     <t xml:space="preserve">4.1137433052063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04429864883423</t>
+    <t xml:space="preserve">4.04429817199707</t>
   </si>
   <si>
     <t xml:space="preserve">4.02917194366455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99273109436035</t>
+    <t xml:space="preserve">3.99273061752319</t>
   </si>
   <si>
     <t xml:space="preserve">3.99891877174377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96316528320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88684463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98241710662842</t>
+    <t xml:space="preserve">3.96316480636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88684487342834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98241758346558</t>
   </si>
   <si>
     <t xml:space="preserve">3.90540885925293</t>
@@ -1823,19 +1823,19 @@
     <t xml:space="preserve">3.78164625167847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71013855934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69501233100891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7335159778595</t>
+    <t xml:space="preserve">3.71013879776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69501256942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73351573944092</t>
   </si>
   <si>
     <t xml:space="preserve">3.72870302200317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64894485473633</t>
+    <t xml:space="preserve">3.64894461631775</t>
   </si>
   <si>
     <t xml:space="preserve">3.70051264762878</t>
@@ -1844,19 +1844,19 @@
     <t xml:space="preserve">3.83115148544312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8999080657959</t>
+    <t xml:space="preserve">3.89990830421448</t>
   </si>
   <si>
     <t xml:space="preserve">3.9934184551239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97829174995422</t>
+    <t xml:space="preserve">3.97829127311707</t>
   </si>
   <si>
     <t xml:space="preserve">4.06286287307739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04842376708984</t>
+    <t xml:space="preserve">4.048424243927</t>
   </si>
   <si>
     <t xml:space="preserve">4.06767559051514</t>
@@ -1865,13 +1865,13 @@
     <t xml:space="preserve">4.04292345046997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99548077583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95491409301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04086065292358</t>
+    <t xml:space="preserve">3.99548053741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95491456985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04086112976074</t>
   </si>
   <si>
     <t xml:space="preserve">4.02160835266113</t>
@@ -1883,34 +1883,34 @@
     <t xml:space="preserve">4.01335763931274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97004079818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07180118560791</t>
+    <t xml:space="preserve">3.97004127502441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07180166244507</t>
   </si>
   <si>
     <t xml:space="preserve">4.11786890029907</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22788000106812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31864023208618</t>
+    <t xml:space="preserve">4.22788047790527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31863975524902</t>
   </si>
   <si>
     <t xml:space="preserve">4.2890739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29044961929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25057077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24919462203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2698221206665</t>
+    <t xml:space="preserve">4.2904486656189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25057029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24919509887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26982164382935</t>
   </si>
   <si>
     <t xml:space="preserve">4.26294660568237</t>
@@ -1919,43 +1919,43 @@
     <t xml:space="preserve">4.24231958389282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13643360137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05392456054688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12543201446533</t>
+    <t xml:space="preserve">4.13643264770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05392503738403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12543249130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.0896782875061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13230800628662</t>
+    <t xml:space="preserve">4.13230752944946</t>
   </si>
   <si>
     <t xml:space="preserve">4.17149925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23819446563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22169160842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21894216537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21481657028198</t>
+    <t xml:space="preserve">4.23819351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22169256210327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2189416885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21481704711914</t>
   </si>
   <si>
     <t xml:space="preserve">4.16324853897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28494882583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34476757049561</t>
+    <t xml:space="preserve">4.28494834899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34476709365845</t>
   </si>
   <si>
     <t xml:space="preserve">4.25400829315186</t>
@@ -1964,34 +1964,34 @@
     <t xml:space="preserve">4.33720445632935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37433338165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50359630584717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57441663742065</t>
+    <t xml:space="preserve">4.37433290481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50359678268433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5744161605835</t>
   </si>
   <si>
     <t xml:space="preserve">4.47609376907349</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44171476364136</t>
+    <t xml:space="preserve">4.44171524047852</t>
   </si>
   <si>
     <t xml:space="preserve">4.44859075546265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55653953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5778546333313</t>
+    <t xml:space="preserve">4.55654001235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57785415649414</t>
   </si>
   <si>
     <t xml:space="preserve">4.60948276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66173887252808</t>
+    <t xml:space="preserve">4.66173791885376</t>
   </si>
   <si>
     <t xml:space="preserve">4.60673236846924</t>
@@ -2000,19 +2000,19 @@
     <t xml:space="preserve">4.57097864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57166624069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50772190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45752906799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41971254348755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46234226226807</t>
+    <t xml:space="preserve">4.5716667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5077223777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45752954483032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41971302032471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46234273910522</t>
   </si>
   <si>
     <t xml:space="preserve">4.4279637336731</t>
@@ -2027,16 +2027,16 @@
     <t xml:space="preserve">4.55860280990601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58610582351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45546627044678</t>
+    <t xml:space="preserve">4.58610534667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45546674728394</t>
   </si>
   <si>
     <t xml:space="preserve">4.48296928405762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53109931945801</t>
+    <t xml:space="preserve">4.53109979629517</t>
   </si>
   <si>
     <t xml:space="preserve">4.56547784805298</t>
@@ -2057,16 +2057,16 @@
     <t xml:space="preserve">4.62735986709595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71674394607544</t>
+    <t xml:space="preserve">4.7167444229126</t>
   </si>
   <si>
     <t xml:space="preserve">4.65486288070679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49672079086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5522894859314</t>
+    <t xml:space="preserve">4.4967212677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55228900909424</t>
   </si>
   <si>
     <t xml:space="preserve">4.61179637908936</t>
@@ -2075,7 +2075,7 @@
     <t xml:space="preserve">4.60435819625854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62667322158813</t>
+    <t xml:space="preserve">4.62667274475098</t>
   </si>
   <si>
     <t xml:space="preserve">4.6936182975769</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">4.56716537475586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55972766876221</t>
+    <t xml:space="preserve">4.55972719192505</t>
   </si>
   <si>
     <t xml:space="preserve">4.64898824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64155006408691</t>
+    <t xml:space="preserve">4.64154958724976</t>
   </si>
   <si>
     <t xml:space="preserve">4.5820426940918</t>
@@ -2126,7 +2126,7 @@
     <t xml:space="preserve">4.38120651245117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42583656311035</t>
+    <t xml:space="preserve">4.42583703994751</t>
   </si>
   <si>
     <t xml:space="preserve">4.37376832962036</t>
@@ -2153,19 +2153,19 @@
     <t xml:space="preserve">4.59691905975342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50765895843506</t>
+    <t xml:space="preserve">4.50765943527222</t>
   </si>
   <si>
     <t xml:space="preserve">4.49278211593628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48534440994263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43327474594116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40352201461792</t>
+    <t xml:space="preserve">4.48534393310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43327522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40352153778076</t>
   </si>
   <si>
     <t xml:space="preserve">4.38864517211914</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">4.35145330429077</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24731540679932</t>
+    <t xml:space="preserve">4.24731588363647</t>
   </si>
   <si>
     <t xml:space="preserve">4.20268535614014</t>
@@ -2195,19 +2195,19 @@
     <t xml:space="preserve">4.01672554016113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0241641998291</t>
+    <t xml:space="preserve">4.02416467666626</t>
   </si>
   <si>
     <t xml:space="preserve">3.93490362167358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90514993667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95721888542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89771175384521</t>
+    <t xml:space="preserve">3.9051501750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95721912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89771151542664</t>
   </si>
   <si>
     <t xml:space="preserve">3.98697209358215</t>
@@ -2216,19 +2216,19 @@
     <t xml:space="preserve">3.92002654075623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94234180450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97953367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97209548950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04647970199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06879472732544</t>
+    <t xml:space="preserve">3.94234228134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97953343391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97209572792053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04647922515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06879425048828</t>
   </si>
   <si>
     <t xml:space="preserve">4.098548412323</t>
@@ -2243,28 +2243,28 @@
     <t xml:space="preserve">4.18036985397339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17293167114258</t>
+    <t xml:space="preserve">4.17293214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.11342477798462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14317846298218</t>
+    <t xml:space="preserve">4.14317798614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.1283016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15805530548096</t>
+    <t xml:space="preserve">4.15805578231812</t>
   </si>
   <si>
     <t xml:space="preserve">4.03904104232788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2324390411377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23987674713135</t>
+    <t xml:space="preserve">4.23243856430054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23987722396851</t>
   </si>
   <si>
     <t xml:space="preserve">4.26963043212891</t>
@@ -2279,10 +2279,10 @@
     <t xml:space="preserve">4.2621922492981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27706861495972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29938459396362</t>
+    <t xml:space="preserve">4.27706909179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29938411712646</t>
   </si>
   <si>
     <t xml:space="preserve">4.28450775146484</t>
@@ -2318,22 +2318,22 @@
     <t xml:space="preserve">4.67874193191528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61923456192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75312519073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67130374908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70849561691284</t>
+    <t xml:space="preserve">4.61923503875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75312566757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67130422592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70849514007568</t>
   </si>
   <si>
     <t xml:space="preserve">4.72337198257446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68618011474609</t>
+    <t xml:space="preserve">4.68618059158325</t>
   </si>
   <si>
     <t xml:space="preserve">4.08367109298706</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">4.06135606765747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96465730667114</t>
+    <t xml:space="preserve">3.96465706825256</t>
   </si>
   <si>
     <t xml:space="preserve">3.92746543884277</t>
@@ -2366,16 +2366,16 @@
     <t xml:space="preserve">2.54020714759827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57367992401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70385146141052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64806389808655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77451610565186</t>
+    <t xml:space="preserve">2.57367968559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70385122299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64806365966797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77451634407043</t>
   </si>
   <si>
     <t xml:space="preserve">2.70757102966309</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">2.88609194755554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80798888206482</t>
+    <t xml:space="preserve">2.8079891204834</t>
   </si>
   <si>
     <t xml:space="preserve">2.83402347564697</t>
@@ -2402,13 +2402,13 @@
     <t xml:space="preserve">2.80426979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75220084190369</t>
+    <t xml:space="preserve">2.75220108032227</t>
   </si>
   <si>
     <t xml:space="preserve">2.70013236999512</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71500897407532</t>
+    <t xml:space="preserve">2.7150092124939</t>
   </si>
   <si>
     <t xml:space="preserve">2.76707792282104</t>
@@ -2423,7 +2423,7 @@
     <t xml:space="preserve">2.60343337059021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66294050216675</t>
+    <t xml:space="preserve">2.66294026374817</t>
   </si>
   <si>
     <t xml:space="preserve">2.69269394874573</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">2.62946796417236</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62574863433838</t>
+    <t xml:space="preserve">2.62574887275696</t>
   </si>
   <si>
     <t xml:space="preserve">2.64062547683716</t>
@@ -2441,7 +2441,7 @@
     <t xml:space="preserve">2.65550184249878</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61459136009216</t>
+    <t xml:space="preserve">2.61459112167358</t>
   </si>
   <si>
     <t xml:space="preserve">2.60715246200562</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">2.59227585792542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55508399009705</t>
+    <t xml:space="preserve">2.55508375167847</t>
   </si>
   <si>
     <t xml:space="preserve">2.45466589927673</t>
@@ -2465,10 +2465,10 @@
     <t xml:space="preserve">2.3951587677002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40259695053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46954250335693</t>
+    <t xml:space="preserve">2.40259718894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46954274177551</t>
   </si>
   <si>
     <t xml:space="preserve">2.33937096595764</t>
@@ -2480,13 +2480,13 @@
     <t xml:space="preserve">2.25754880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44722747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38400101661682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41747379302979</t>
+    <t xml:space="preserve">2.44722723960876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3840012550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41747403144836</t>
   </si>
   <si>
     <t xml:space="preserve">2.41375470161438</t>
@@ -2504,13 +2504,13 @@
     <t xml:space="preserve">2.61831021308899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77823543548584</t>
+    <t xml:space="preserve">2.77823519706726</t>
   </si>
   <si>
     <t xml:space="preserve">2.9158456325531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54392647743225</t>
+    <t xml:space="preserve">2.54392671585083</t>
   </si>
   <si>
     <t xml:space="preserve">2.54764556884766</t>
@@ -2525,10 +2525,10 @@
     <t xml:space="preserve">2.52904963493347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51045346260071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58483719825745</t>
+    <t xml:space="preserve">2.51045370101929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58483743667603</t>
   </si>
   <si>
     <t xml:space="preserve">2.58111834526062</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">2.63690614700317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68530654907227</t>
+    <t xml:space="preserve">2.68530678749084</t>
   </si>
   <si>
     <t xml:space="preserve">2.66147232055664</t>
@@ -2552,16 +2552,16 @@
     <t xml:space="preserve">2.5740807056427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51846790313721</t>
+    <t xml:space="preserve">2.51846814155579</t>
   </si>
   <si>
     <t xml:space="preserve">2.46285510063171</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45491027832031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42710375785828</t>
+    <t xml:space="preserve">2.45491003990173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42710399627686</t>
   </si>
   <si>
     <t xml:space="preserve">2.51052331924438</t>
@@ -2570,13 +2570,13 @@
     <t xml:space="preserve">2.47079968452454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49066162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53435730934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59791493415833</t>
+    <t xml:space="preserve">2.49066138267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53435754776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59791469573975</t>
   </si>
   <si>
     <t xml:space="preserve">2.55024671554565</t>
@@ -2612,13 +2612,13 @@
     <t xml:space="preserve">2.5144956111908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48271703720093</t>
+    <t xml:space="preserve">2.48271679878235</t>
   </si>
   <si>
     <t xml:space="preserve">2.43902087211609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57010817527771</t>
+    <t xml:space="preserve">2.57010841369629</t>
   </si>
   <si>
     <t xml:space="preserve">2.49860620498657</t>
@@ -2627,7 +2627,7 @@
     <t xml:space="preserve">2.391352891922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3834080696106</t>
+    <t xml:space="preserve">2.38340830802917</t>
   </si>
   <si>
     <t xml:space="preserve">2.39532518386841</t>
@@ -2663,10 +2663,10 @@
     <t xml:space="preserve">2.28409934043884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30793356895447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28807163238525</t>
+    <t xml:space="preserve">2.30793380737305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28807187080383</t>
   </si>
   <si>
     <t xml:space="preserve">2.25232076644897</t>
@@ -2678,19 +2678,19 @@
     <t xml:space="preserve">2.14506721496582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11328864097595</t>
+    <t xml:space="preserve">2.11328840255737</t>
   </si>
   <si>
     <t xml:space="preserve">2.05767560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96631157398224</t>
+    <t xml:space="preserve">1.96631169319153</t>
   </si>
   <si>
     <t xml:space="preserve">1.97822856903076</t>
   </si>
   <si>
-    <t xml:space="preserve">1.98220109939575</t>
+    <t xml:space="preserve">1.98220098018646</t>
   </si>
   <si>
     <t xml:space="preserve">2.08548212051392</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">2.09342670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08150959014893</t>
+    <t xml:space="preserve">2.0815098285675</t>
   </si>
   <si>
     <t xml:space="preserve">2.15301203727722</t>
@@ -2717,13 +2717,13 @@
     <t xml:space="preserve">2.72900223731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7131130695343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88392400741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83625555038452</t>
+    <t xml:space="preserve">2.71311283111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88392376899719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8362557888031</t>
   </si>
   <si>
     <t xml:space="preserve">2.81242156028748</t>
@@ -2738,10 +2738,10 @@
     <t xml:space="preserve">2.70119595527649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8203661441803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84420013427734</t>
+    <t xml:space="preserve">2.82036638259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84420037269592</t>
   </si>
   <si>
     <t xml:space="preserve">2.86406207084656</t>
@@ -2753,22 +2753,22 @@
     <t xml:space="preserve">2.85611748695374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78461527824402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87200665473938</t>
+    <t xml:space="preserve">2.78461503982544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87200689315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.85214519500732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93556427955627</t>
+    <t xml:space="preserve">2.93556451797485</t>
   </si>
   <si>
     <t xml:space="preserve">2.96337080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87597918510437</t>
+    <t xml:space="preserve">2.87597894668579</t>
   </si>
   <si>
     <t xml:space="preserve">2.9514536857605</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">2.91967487335205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91173005104065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78064274787903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83228349685669</t>
+    <t xml:space="preserve">2.91173028945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78064298629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83228325843811</t>
   </si>
   <si>
     <t xml:space="preserve">2.94748163223267</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">2.95939826965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99912214279175</t>
+    <t xml:space="preserve">2.99912190437317</t>
   </si>
   <si>
     <t xml:space="preserve">2.96734309196472</t>
@@ -2834,16 +2834,16 @@
     <t xml:space="preserve">2.82433867454529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80844950675964</t>
+    <t xml:space="preserve">2.80844926834106</t>
   </si>
   <si>
     <t xml:space="preserve">2.89186859130859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90775799751282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92364740371704</t>
+    <t xml:space="preserve">2.90775775909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92364716529846</t>
   </si>
   <si>
     <t xml:space="preserve">2.98323249816895</t>
@@ -2858,7 +2858,7 @@
     <t xml:space="preserve">3.30896496772766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17787766456604</t>
+    <t xml:space="preserve">3.17787742614746</t>
   </si>
   <si>
     <t xml:space="preserve">3.05473470687866</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">3.04281759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10637521743774</t>
+    <t xml:space="preserve">3.10637545585632</t>
   </si>
   <si>
     <t xml:space="preserve">3.02692818641663</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">2.84022808074951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79256010055542</t>
+    <t xml:space="preserve">2.79255986213684</t>
   </si>
   <si>
     <t xml:space="preserve">2.80050468444824</t>
@@ -2921,7 +2921,7 @@
     <t xml:space="preserve">2.99514961242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15404343605042</t>
+    <t xml:space="preserve">3.15404367446899</t>
   </si>
   <si>
     <t xml:space="preserve">3.07459616661072</t>
@@ -2930,28 +2930,28 @@
     <t xml:space="preserve">3.13815426826477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.08254098892212</t>
+    <t xml:space="preserve">3.0825412273407</t>
   </si>
   <si>
     <t xml:space="preserve">3.14609885215759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09843039512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18582248687744</t>
+    <t xml:space="preserve">3.09843063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18582224845886</t>
   </si>
   <si>
     <t xml:space="preserve">3.13020944595337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25335216522217</t>
+    <t xml:space="preserve">3.25335192680359</t>
   </si>
   <si>
     <t xml:space="preserve">3.26924133300781</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30102062225342</t>
+    <t xml:space="preserve">3.30102038383484</t>
   </si>
   <si>
     <t xml:space="preserve">3.3288266658783</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">3.29307556152344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23746228218079</t>
+    <t xml:space="preserve">3.23746252059937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23349046707153</t>
@@ -2981,16 +2981,16 @@
     <t xml:space="preserve">3.20568370819092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.21362853050232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22554564476013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1977391242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20171189308167</t>
+    <t xml:space="preserve">3.2136287689209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22554540634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19773936271667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20171165466309</t>
   </si>
   <si>
     <t xml:space="preserve">3.2652690410614</t>
@@ -3005,7 +3005,7 @@
     <t xml:space="preserve">3.34471607208252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41224598884583</t>
+    <t xml:space="preserve">3.41224575042725</t>
   </si>
   <si>
     <t xml:space="preserve">3.40827345848083</t>
@@ -3014,10 +3014,10 @@
     <t xml:space="preserve">3.55922269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67044878005981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69031047821045</t>
+    <t xml:space="preserve">3.67044854164124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69031023979187</t>
   </si>
   <si>
     <t xml:space="preserve">3.69428277015686</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">3.66647601127625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63866925239563</t>
+    <t xml:space="preserve">3.63866949081421</t>
   </si>
   <si>
     <t xml:space="preserve">3.51949906349182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45594167709351</t>
+    <t xml:space="preserve">3.45594191551208</t>
   </si>
   <si>
     <t xml:space="preserve">3.52347159385681</t>
@@ -3041,7 +3041,7 @@
     <t xml:space="preserve">3.49169278144836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40430092811584</t>
+    <t xml:space="preserve">3.40430116653442</t>
   </si>
   <si>
     <t xml:space="preserve">3.45196914672852</t>
@@ -3050,13 +3050,13 @@
     <t xml:space="preserve">3.44005250930786</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34074378013611</t>
+    <t xml:space="preserve">3.34074354171753</t>
   </si>
   <si>
     <t xml:space="preserve">3.24540734291077</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26129698753357</t>
+    <t xml:space="preserve">3.26129674911499</t>
   </si>
   <si>
     <t xml:space="preserve">3.33677101135254</t>
@@ -3068,7 +3068,7 @@
     <t xml:space="preserve">3.22157311439514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30499243736267</t>
+    <t xml:space="preserve">3.30499267578125</t>
   </si>
   <si>
     <t xml:space="preserve">3.2811586856842</t>
@@ -3089,7 +3089,7 @@
     <t xml:space="preserve">3.19376683235168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27718639373779</t>
+    <t xml:space="preserve">3.27718615531921</t>
   </si>
   <si>
     <t xml:space="preserve">3.36457800865173</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">3.16198825836182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07856869697571</t>
+    <t xml:space="preserve">3.07856893539429</t>
   </si>
   <si>
     <t xml:space="preserve">2.97131562232971</t>
@@ -3128,13 +3128,13 @@
     <t xml:space="preserve">2.99117732048035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89584064483643</t>
+    <t xml:space="preserve">2.895840883255</t>
   </si>
   <si>
     <t xml:space="preserve">3.0189836025238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31293725967407</t>
+    <t xml:space="preserve">3.31293749809265</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596031188965</t>
@@ -3149,19 +3149,19 @@
     <t xml:space="preserve">3.18184995651245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17390489578247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22951793670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03884553909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00309419631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0110387802124</t>
+    <t xml:space="preserve">3.17390513420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22951817512512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03884530067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00309443473816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01103901863098</t>
   </si>
   <si>
     <t xml:space="preserve">3.05076217651367</t>
@@ -3173,16 +3173,16 @@
     <t xml:space="preserve">3.21760106086731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92761945724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79653215408325</t>
+    <t xml:space="preserve">2.92761969566345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79653239250183</t>
   </si>
   <si>
     <t xml:space="preserve">2.87995147705078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98720479011536</t>
+    <t xml:space="preserve">2.98720502853394</t>
   </si>
   <si>
     <t xml:space="preserve">3.03487277030945</t>
@@ -3191,10 +3191,10 @@
     <t xml:space="preserve">2.91570258140564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28513121604919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36060523986816</t>
+    <t xml:space="preserve">3.28513097763062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36060547828674</t>
   </si>
   <si>
     <t xml:space="preserve">3.37649464607239</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">3.53141665458679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57908487319946</t>
+    <t xml:space="preserve">3.57908463478088</t>
   </si>
   <si>
     <t xml:space="preserve">3.42416310310364</t>
@@ -3224,16 +3224,16 @@
     <t xml:space="preserve">3.40032911300659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39238429069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38443946838379</t>
+    <t xml:space="preserve">3.39238405227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38443970680237</t>
   </si>
   <si>
     <t xml:space="preserve">3.46388673782349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48772048950195</t>
+    <t xml:space="preserve">3.48772025108337</t>
   </si>
   <si>
     <t xml:space="preserve">3.47183108329773</t>
@@ -3248,19 +3248,19 @@
     <t xml:space="preserve">3.55127787590027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63072490692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59100127220154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67442107200623</t>
+    <t xml:space="preserve">3.63072514533997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59100151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67442083358765</t>
   </si>
   <si>
     <t xml:space="preserve">3.61086344718933</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62278008460999</t>
+    <t xml:space="preserve">3.62278032302856</t>
   </si>
   <si>
     <t xml:space="preserve">3.67839336395264</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">3.65058660507202</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61880803108215</t>
+    <t xml:space="preserve">3.61880779266357</t>
   </si>
   <si>
     <t xml:space="preserve">3.6346971988678</t>
@@ -4758,6 +4758,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.66000008583069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57500004768372</t>
   </si>
 </sst>
 </file>
@@ -8832,7 +8835,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G144" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8858,7 +8861,7 @@
         <v>7.24187612533569</v>
       </c>
       <c r="G145" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -9170,7 +9173,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G157" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -12082,7 +12085,7 @@
         <v>6.88861417770386</v>
       </c>
       <c r="G269" t="s">
-        <v>219</v>
+        <v>67</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -12134,7 +12137,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G271" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12186,7 +12189,7 @@
         <v>6.82818794250488</v>
       </c>
       <c r="G273" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12212,7 +12215,7 @@
         <v>6.80494689941406</v>
       </c>
       <c r="G274" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12238,7 +12241,7 @@
         <v>6.75381708145142</v>
       </c>
       <c r="G275" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12290,7 +12293,7 @@
         <v>6.61901903152466</v>
       </c>
       <c r="G277" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12342,7 +12345,7 @@
         <v>6.47027683258057</v>
       </c>
       <c r="G279" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12368,7 +12371,7 @@
         <v>6.62831592559814</v>
       </c>
       <c r="G280" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12394,7 +12397,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G281" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12420,7 +12423,7 @@
         <v>6.57253694534302</v>
       </c>
       <c r="G282" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12446,7 +12449,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G283" t="s">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12472,7 +12475,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G284" t="s">
-        <v>20</v>
+        <v>228</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12758,7 +12761,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G295" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12784,7 +12787,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G296" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -70330,7 +70333,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.6911805556</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>389891</v>
@@ -70351,6 +70354,32 @@
         <v>1581</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6911689815</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>87222</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>3.69000005722046</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>3.5699999332428</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>3.6800000667572</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>3.57500004768372</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>1582</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">IGD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8117880821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76804447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7653112411499</t>
+    <t xml:space="preserve">4.81178760528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76804494857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76531076431274</t>
   </si>
   <si>
     <t xml:space="preserve">4.64775037765503</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">4.53839111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56573104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67235660552979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55206155776978</t>
+    <t xml:space="preserve">4.56573057174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67235612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55206108093262</t>
   </si>
   <si>
     <t xml:space="preserve">4.33334302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16383695602417</t>
+    <t xml:space="preserve">4.16383743286133</t>
   </si>
   <si>
     <t xml:space="preserve">4.04627704620361</t>
@@ -83,49 +83,49 @@
     <t xml:space="preserve">3.88223814964294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9560558795929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03807497024536</t>
+    <t xml:space="preserve">3.95605540275574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0380744934082</t>
   </si>
   <si>
     <t xml:space="preserve">3.97519326210022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9478542804718</t>
+    <t xml:space="preserve">3.94785380363464</t>
   </si>
   <si>
     <t xml:space="preserve">3.81388926506042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96425819396973</t>
+    <t xml:space="preserve">3.96425771713257</t>
   </si>
   <si>
     <t xml:space="preserve">4.07088232040405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92051434516907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69632863998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78654909133911</t>
+    <t xml:space="preserve">3.92051339149475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69632887840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78654932975769</t>
   </si>
   <si>
     <t xml:space="preserve">3.45573902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49948239326477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69086098670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56783223152161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6389148235321</t>
+    <t xml:space="preserve">3.49948215484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69086050987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56783199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63891553878784</t>
   </si>
   <si>
     <t xml:space="preserve">3.88497233390808</t>
@@ -134,16 +134,16 @@
     <t xml:space="preserve">3.82755899429321</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93691754341125</t>
+    <t xml:space="preserve">3.9369170665741</t>
   </si>
   <si>
     <t xml:space="preserve">3.87130260467529</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05994701385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00800037384033</t>
+    <t xml:space="preserve">4.05994653701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00800132751465</t>
   </si>
   <si>
     <t xml:space="preserve">3.95332193374634</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">3.9915976524353</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03260707855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05447864532471</t>
+    <t xml:space="preserve">4.03260660171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05447816848755</t>
   </si>
   <si>
     <t xml:space="preserve">4.24038887023926</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">4.21031427383423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37435340881348</t>
+    <t xml:space="preserve">4.37435293197632</t>
   </si>
   <si>
     <t xml:space="preserve">4.33607816696167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34701347351074</t>
+    <t xml:space="preserve">4.3470139503479</t>
   </si>
   <si>
     <t xml:space="preserve">4.33881235122681</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">4.42903280258179</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52745580673218</t>
+    <t xml:space="preserve">4.52745628356934</t>
   </si>
   <si>
     <t xml:space="preserve">4.51105213165283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46183967590332</t>
+    <t xml:space="preserve">4.46184015274048</t>
   </si>
   <si>
     <t xml:space="preserve">4.57119989395142</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">4.42083072662354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42356443405151</t>
+    <t xml:space="preserve">4.42356491088867</t>
   </si>
   <si>
     <t xml:space="preserve">4.26499462127686</t>
@@ -224,25 +224,25 @@
     <t xml:space="preserve">4.22398519515991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22671937942505</t>
+    <t xml:space="preserve">4.22671842575073</t>
   </si>
   <si>
     <t xml:space="preserve">4.23765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3306097984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40169286727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31967353820801</t>
+    <t xml:space="preserve">4.33060932159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40169334411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31967306137085</t>
   </si>
   <si>
     <t xml:space="preserve">4.30600452423096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36615133285522</t>
+    <t xml:space="preserve">4.36615085601807</t>
   </si>
   <si>
     <t xml:space="preserve">4.26772832870483</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">4.32514190673828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29233455657959</t>
+    <t xml:space="preserve">4.29233407974243</t>
   </si>
   <si>
     <t xml:space="preserve">4.27046251296997</t>
@@ -260,67 +260,67 @@
     <t xml:space="preserve">4.29506778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39895915985107</t>
+    <t xml:space="preserve">4.39895868301392</t>
   </si>
   <si>
     <t xml:space="preserve">4.30873775482178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38802289962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42629814147949</t>
+    <t xml:space="preserve">4.38802337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42629861831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.34427976608276</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39075756072998</t>
+    <t xml:space="preserve">4.39075660705566</t>
   </si>
   <si>
     <t xml:space="preserve">4.3032693862915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49522352218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57292556762695</t>
+    <t xml:space="preserve">4.49522399902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57292604446411</t>
   </si>
   <si>
     <t xml:space="preserve">4.65062808990479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69091844558716</t>
+    <t xml:space="preserve">4.69091796875</t>
   </si>
   <si>
     <t xml:space="preserve">4.67940664291382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69379615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66213989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61609315872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57580327987671</t>
+    <t xml:space="preserve">4.69379663467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66213941574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61609411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57580423355103</t>
   </si>
   <si>
     <t xml:space="preserve">4.63623857498169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63048362731934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63336086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63911628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56429243087769</t>
+    <t xml:space="preserve">4.63048315048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63336133956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63911581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56429290771484</t>
   </si>
   <si>
     <t xml:space="preserve">4.35133075714111</t>
@@ -329,16 +329,16 @@
     <t xml:space="preserve">4.06066560745239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08368921279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95130705833435</t>
+    <t xml:space="preserve">4.08368873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95130753517151</t>
   </si>
   <si>
     <t xml:space="preserve">3.97145223617554</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16139078140259</t>
+    <t xml:space="preserve">4.1613917350769</t>
   </si>
   <si>
     <t xml:space="preserve">4.20168161392212</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">4.247727394104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2765064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03476524353027</t>
+    <t xml:space="preserve">4.27650594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03476572036743</t>
   </si>
   <si>
     <t xml:space="preserve">3.82755851745605</t>
@@ -359,22 +359,22 @@
     <t xml:space="preserve">3.84482645988464</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85633730888367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470331192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15851259231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01749801635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784887313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83619236946106</t>
+    <t xml:space="preserve">3.85633683204651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470426559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784839630127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83619260787964</t>
   </si>
   <si>
     <t xml:space="preserve">3.96281814575195</t>
@@ -386,37 +386,40 @@
     <t xml:space="preserve">4.0923228263855</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25636053085327</t>
+    <t xml:space="preserve">4.25636100769043</t>
   </si>
   <si>
     <t xml:space="preserve">4.40313196182251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3340630531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51824712753296</t>
+    <t xml:space="preserve">4.33406352996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5182466506958</t>
   </si>
   <si>
     <t xml:space="preserve">4.41752099990845</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45493316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37435388565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45781135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52975749969482</t>
+    <t xml:space="preserve">4.45493364334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48371124267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45781087875366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53839159011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52975797653198</t>
   </si>
   <si>
     <t xml:space="preserve">4.48946809768677</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51536798477173</t>
+    <t xml:space="preserve">4.51536846160889</t>
   </si>
   <si>
     <t xml:space="preserve">4.25923871994019</t>
@@ -431,16 +434,16 @@
     <t xml:space="preserve">4.38298654556274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36571979522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41464328765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35996389389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33694124221802</t>
+    <t xml:space="preserve">4.36571931838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41464281082153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35996341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33694076538086</t>
   </si>
   <si>
     <t xml:space="preserve">4.29377269744873</t>
@@ -449,7 +452,7 @@
     <t xml:space="preserve">4.31391763687134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19016933441162</t>
+    <t xml:space="preserve">4.19017028808594</t>
   </si>
   <si>
     <t xml:space="preserve">4.19880390167236</t>
@@ -458,19 +461,19 @@
     <t xml:space="preserve">4.22182607650757</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26211643218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25348281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23046016693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14412403106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19592571258545</t>
+    <t xml:space="preserve">4.26211595535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25348234176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23046064376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14412355422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19592618942261</t>
   </si>
   <si>
     <t xml:space="preserve">4.16714715957642</t>
@@ -479,13 +482,13 @@
     <t xml:space="preserve">4.15563583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1153450012207</t>
+    <t xml:space="preserve">4.11534452438354</t>
   </si>
   <si>
     <t xml:space="preserve">4.20743656158447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14700174331665</t>
+    <t xml:space="preserve">4.14700222015381</t>
   </si>
   <si>
     <t xml:space="preserve">4.1786584854126</t>
@@ -494,22 +497,22 @@
     <t xml:space="preserve">4.07505559921265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9426736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497092247009</t>
+    <t xml:space="preserve">3.94267416000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497116088867</t>
   </si>
   <si>
     <t xml:space="preserve">3.79878067970276</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77575755119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83907032012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74697852134705</t>
+    <t xml:space="preserve">3.77575731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83906984329224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74697923660278</t>
   </si>
   <si>
     <t xml:space="preserve">3.74985647201538</t>
@@ -521,31 +524,31 @@
     <t xml:space="preserve">3.82468128204346</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79590249061584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87936043739319</t>
+    <t xml:space="preserve">3.79590225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87936091423035</t>
   </si>
   <si>
     <t xml:space="preserve">3.81029176712036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78439164161682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7642457485199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72971153259277</t>
+    <t xml:space="preserve">3.78439140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76424598693848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72971177101135</t>
   </si>
   <si>
     <t xml:space="preserve">3.71244406700134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72395586967468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84194803237915</t>
+    <t xml:space="preserve">3.72395539283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84194779396057</t>
   </si>
   <si>
     <t xml:space="preserve">3.99735355377197</t>
@@ -572,7 +575,7 @@
     <t xml:space="preserve">3.97432994842529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91389465332031</t>
+    <t xml:space="preserve">3.91389513015747</t>
   </si>
   <si>
     <t xml:space="preserve">3.93979597091675</t>
@@ -581,67 +584,67 @@
     <t xml:space="preserve">3.92540669441223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92828392982483</t>
+    <t xml:space="preserve">3.92828440666199</t>
   </si>
   <si>
     <t xml:space="preserve">3.89662790298462</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84770464897156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273537635803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75849032402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55703997612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64337587356567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66927599906921</t>
+    <t xml:space="preserve">3.84770393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273489952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75849056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55704021453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64337515830994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66927623748779</t>
   </si>
   <si>
     <t xml:space="preserve">3.65776467323303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58006262779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59732961654663</t>
+    <t xml:space="preserve">3.58006238937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59732985496521</t>
   </si>
   <si>
     <t xml:space="preserve">3.60308599472046</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63186407089233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62610840797424</t>
+    <t xml:space="preserve">3.63186502456665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62610864639282</t>
   </si>
   <si>
     <t xml:space="preserve">3.66064310073853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61459708213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80453562736511</t>
+    <t xml:space="preserve">3.61459755897522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80453658103943</t>
   </si>
   <si>
     <t xml:space="preserve">3.95994067192078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07217741012573</t>
+    <t xml:space="preserve">4.07217693328857</t>
   </si>
   <si>
     <t xml:space="preserve">4.04339933395386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1268572807312</t>
+    <t xml:space="preserve">4.12685680389404</t>
   </si>
   <si>
     <t xml:space="preserve">4.13261222839355</t>
@@ -650,7 +653,7 @@
     <t xml:space="preserve">4.12110137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36859750747681</t>
+    <t xml:space="preserve">4.36859798431396</t>
   </si>
   <si>
     <t xml:space="preserve">4.28226137161255</t>
@@ -659,7 +662,7 @@
     <t xml:space="preserve">4.33981895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34845209121704</t>
+    <t xml:space="preserve">4.34845161437988</t>
   </si>
   <si>
     <t xml:space="preserve">4.33118534088135</t>
@@ -668,13 +671,13 @@
     <t xml:space="preserve">4.30240678787231</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27075004577637</t>
+    <t xml:space="preserve">4.27074956893921</t>
   </si>
   <si>
     <t xml:space="preserve">4.2275824546814</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2131929397583</t>
+    <t xml:space="preserve">4.21319341659546</t>
   </si>
   <si>
     <t xml:space="preserve">4.18153619766235</t>
@@ -683,10 +686,10 @@
     <t xml:space="preserve">4.09807825088501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00598669052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10383415222168</t>
+    <t xml:space="preserve">4.00598621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10383462905884</t>
   </si>
   <si>
     <t xml:space="preserve">4.02900981903076</t>
@@ -698,16 +701,16 @@
     <t xml:space="preserve">4.21894836425781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30816268920898</t>
+    <t xml:space="preserve">4.30816221237183</t>
   </si>
   <si>
     <t xml:space="preserve">4.14988040924072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47220087051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51248979568481</t>
+    <t xml:space="preserve">4.47220039367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51249074935913</t>
   </si>
   <si>
     <t xml:space="preserve">4.37723112106323</t>
@@ -722,13 +725,13 @@
     <t xml:space="preserve">4.62472772598267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57004833221436</t>
+    <t xml:space="preserve">4.5700478553772</t>
   </si>
   <si>
     <t xml:space="preserve">4.71969699859619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70818519592285</t>
+    <t xml:space="preserve">4.70818567276001</t>
   </si>
   <si>
     <t xml:space="preserve">4.80315494537354</t>
@@ -743,43 +746,43 @@
     <t xml:space="preserve">4.7024302482605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64487218856812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62184953689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54702520370483</t>
+    <t xml:space="preserve">4.64487266540527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62184906005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54702472686768</t>
   </si>
   <si>
     <t xml:space="preserve">4.52687978744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46068954467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60458278656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71394109725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66501760482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74559736251831</t>
+    <t xml:space="preserve">4.46068906784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6045823097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71394062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66501665115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74559783935547</t>
   </si>
   <si>
     <t xml:space="preserve">4.76574325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74847555160522</t>
+    <t xml:space="preserve">4.74847602844238</t>
   </si>
   <si>
     <t xml:space="preserve">4.78301048278809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77149820327759</t>
+    <t xml:space="preserve">4.77149868011475</t>
   </si>
   <si>
     <t xml:space="preserve">4.8233003616333</t>
@@ -788,22 +791,22 @@
     <t xml:space="preserve">4.92690277099609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94992589950562</t>
+    <t xml:space="preserve">4.94992637634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.98446035385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02475118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0564079284668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89236831665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86358976364136</t>
+    <t xml:space="preserve">5.02475070953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05640697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89236879348755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86359024047852</t>
   </si>
   <si>
     <t xml:space="preserve">4.82905578613281</t>
@@ -818,7 +821,7 @@
     <t xml:space="preserve">4.93538570404053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89970827102661</t>
+    <t xml:space="preserve">4.89970874786377</t>
   </si>
   <si>
     <t xml:space="preserve">4.9205207824707</t>
@@ -830,7 +833,7 @@
     <t xml:space="preserve">4.96809053421021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9710636138916</t>
+    <t xml:space="preserve">4.97106409072876</t>
   </si>
   <si>
     <t xml:space="preserve">4.89376258850098</t>
@@ -842,13 +845,13 @@
     <t xml:space="preserve">4.94133281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92943954467773</t>
+    <t xml:space="preserve">4.92944002151489</t>
   </si>
   <si>
     <t xml:space="preserve">4.88781595230103</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85511112213135</t>
+    <t xml:space="preserve">4.85511159896851</t>
   </si>
   <si>
     <t xml:space="preserve">4.79862260818481</t>
@@ -863,16 +866,16 @@
     <t xml:space="preserve">4.78673028945923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73321437835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66185855865479</t>
+    <t xml:space="preserve">4.73321390151978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66185903549194</t>
   </si>
   <si>
     <t xml:space="preserve">4.53401470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58455753326416</t>
+    <t xml:space="preserve">4.58455801010132</t>
   </si>
   <si>
     <t xml:space="preserve">4.61726188659668</t>
@@ -884,13 +887,13 @@
     <t xml:space="preserve">4.72132158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63807392120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72726726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81646156311035</t>
+    <t xml:space="preserve">4.63807439804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72726821899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81646108627319</t>
   </si>
   <si>
     <t xml:space="preserve">4.83132696151733</t>
@@ -899,7 +902,7 @@
     <t xml:space="preserve">4.93835973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94430589675903</t>
+    <t xml:space="preserve">4.94430541992188</t>
   </si>
   <si>
     <t xml:space="preserve">4.98295640945435</t>
@@ -908,10 +911,10 @@
     <t xml:space="preserve">4.95322513580322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90565490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84619283676147</t>
+    <t xml:space="preserve">4.90565538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84619235992432</t>
   </si>
   <si>
     <t xml:space="preserve">4.89078950881958</t>
@@ -920,7 +923,7 @@
     <t xml:space="preserve">5.00376796722412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05431079864502</t>
+    <t xml:space="preserve">5.05431127548218</t>
   </si>
   <si>
     <t xml:space="preserve">5.04836511611938</t>
@@ -929,16 +932,16 @@
     <t xml:space="preserve">4.99782180786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98592948913574</t>
+    <t xml:space="preserve">4.9859299659729</t>
   </si>
   <si>
     <t xml:space="preserve">5.15837049484253</t>
   </si>
   <si>
-    <t xml:space="preserve">5.12566614151001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11080121994019</t>
+    <t xml:space="preserve">5.12566709518433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11080074310303</t>
   </si>
   <si>
     <t xml:space="preserve">5.07512283325195</t>
@@ -956,22 +959,22 @@
     <t xml:space="preserve">5.03944540023804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02755260467529</t>
+    <t xml:space="preserve">5.02755308151245</t>
   </si>
   <si>
     <t xml:space="preserve">4.97700977325439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05133771896362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99484872817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01566123962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06620407104492</t>
+    <t xml:space="preserve">5.05133867263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99484825134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01566076278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06620454788208</t>
   </si>
   <si>
     <t xml:space="preserve">5.13755893707275</t>
@@ -986,13 +989,13 @@
     <t xml:space="preserve">5.23864555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.197021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17323684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1851282119751</t>
+    <t xml:space="preserve">5.19702196121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17323637008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18512868881226</t>
   </si>
   <si>
     <t xml:space="preserve">5.20891427993774</t>
@@ -1001,34 +1004,34 @@
     <t xml:space="preserve">5.1940484046936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24756479263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25053787231445</t>
+    <t xml:space="preserve">5.2475643157959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25053691864014</t>
   </si>
   <si>
     <t xml:space="preserve">5.26242971420288</t>
   </si>
   <si>
-    <t xml:space="preserve">5.1494517326355</t>
+    <t xml:space="preserve">5.14945125579834</t>
   </si>
   <si>
     <t xml:space="preserve">5.16431665420532</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21485996246338</t>
+    <t xml:space="preserve">5.21486043930054</t>
   </si>
   <si>
     <t xml:space="preserve">5.35162448883057</t>
   </si>
   <si>
-    <t xml:space="preserve">5.44081735610962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.64893674850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6786675453186</t>
+    <t xml:space="preserve">5.44081687927246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.64893627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.67866706848145</t>
   </si>
   <si>
     <t xml:space="preserve">5.47054862976074</t>
@@ -1040,34 +1043,34 @@
     <t xml:space="preserve">5.55974245071411</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59541893005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.58947420120239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50325345993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57758188247681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75002193450928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90165185928345</t>
+    <t xml:space="preserve">5.59541988372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.58947372436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50325298309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57758140563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75002241134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90165233612061</t>
   </si>
   <si>
     <t xml:space="preserve">5.91651821136475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20193767547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19004487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11274337768555</t>
+    <t xml:space="preserve">6.20193815231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19004583358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11274385452271</t>
   </si>
   <si>
     <t xml:space="preserve">6.12463617324829</t>
@@ -1085,106 +1088,106 @@
     <t xml:space="preserve">5.88975954055786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00571155548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29113101959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34464836120605</t>
+    <t xml:space="preserve">6.0057110786438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29113149642944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3446478843689</t>
   </si>
   <si>
     <t xml:space="preserve">6.17815256118774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39816331863403</t>
+    <t xml:space="preserve">6.39816427230835</t>
   </si>
   <si>
     <t xml:space="preserve">6.38627147674561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33275508880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43384122848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46951866149902</t>
+    <t xml:space="preserve">6.33275461196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43384075164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46951818466187</t>
   </si>
   <si>
     <t xml:space="preserve">6.41600227355957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40410947799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24356126785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35654020309448</t>
+    <t xml:space="preserve">6.40411043167114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24356079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35653924942017</t>
   </si>
   <si>
     <t xml:space="preserve">6.44573402404785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60033559799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58844375610352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71926116943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65979909896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48141098022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.071120262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82732391357422</t>
+    <t xml:space="preserve">6.60033655166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58844327926636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71926069259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65979862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48141145706177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07111930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82732343673706</t>
   </si>
   <si>
     <t xml:space="preserve">5.76786088943481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80948495864868</t>
+    <t xml:space="preserve">5.80948448181152</t>
   </si>
   <si>
     <t xml:space="preserve">5.681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73812961578369</t>
+    <t xml:space="preserve">5.73812913894653</t>
   </si>
   <si>
     <t xml:space="preserve">5.81840419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73218297958374</t>
+    <t xml:space="preserve">5.73218393325806</t>
   </si>
   <si>
     <t xml:space="preserve">5.72623634338379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85705471038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86300134658813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.9581413269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.92840957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76191520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70839786529541</t>
+    <t xml:space="preserve">5.85705518722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86300086975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.95814085006714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.92841005325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76191473007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70839834213257</t>
   </si>
   <si>
     <t xml:space="preserve">5.79759168624878</t>
@@ -1193,40 +1196,40 @@
     <t xml:space="preserve">5.75596857070923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6846137046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69650602340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66082859039307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50622701644897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45865631103516</t>
+    <t xml:space="preserve">5.68461322784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69650650024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66082811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50622653961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45865678787231</t>
   </si>
   <si>
     <t xml:space="preserve">5.33973121643066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15539693832397</t>
+    <t xml:space="preserve">5.15539741516113</t>
   </si>
   <si>
     <t xml:space="preserve">5.30999994277954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0364727973938</t>
+    <t xml:space="preserve">5.03647232055664</t>
   </si>
   <si>
     <t xml:space="preserve">4.91754722595215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00079488754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86997747421265</t>
+    <t xml:space="preserve">5.00079584121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86997699737549</t>
   </si>
   <si>
     <t xml:space="preserve">4.85213851928711</t>
@@ -1241,16 +1244,16 @@
     <t xml:space="preserve">4.79446029663086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70824003219604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58812570571899</t>
+    <t xml:space="preserve">4.70823955535889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58812522888184</t>
   </si>
   <si>
     <t xml:space="preserve">4.47752571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46860599517822</t>
+    <t xml:space="preserve">4.46860551834106</t>
   </si>
   <si>
     <t xml:space="preserve">4.53104162216187</t>
@@ -1259,61 +1262,61 @@
     <t xml:space="preserve">4.66483211517334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66839933395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5548267364502</t>
+    <t xml:space="preserve">4.66840028762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55482625961304</t>
   </si>
   <si>
     <t xml:space="preserve">4.49774217605591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51260805130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41211652755737</t>
+    <t xml:space="preserve">4.51260757446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41211605072021</t>
   </si>
   <si>
     <t xml:space="preserve">4.36811399459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29913759231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48525524139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46503829956055</t>
+    <t xml:space="preserve">4.29913806915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48525619506836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46503782272339</t>
   </si>
   <si>
     <t xml:space="preserve">4.4418478012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29378652572632</t>
+    <t xml:space="preserve">4.29378700256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.19210577011108</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57336044311523</t>
+    <t xml:space="preserve">4.57335996627808</t>
   </si>
   <si>
     <t xml:space="preserve">4.65459394454956</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10297536849976</t>
+    <t xml:space="preserve">5.10297584533691</t>
   </si>
   <si>
     <t xml:space="preserve">4.85351896286011</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95713949203491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14391183853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34731435775757</t>
+    <t xml:space="preserve">4.95713901519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14391136169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34731388092041</t>
   </si>
   <si>
     <t xml:space="preserve">5.28271150588989</t>
@@ -1322,7 +1325,7 @@
     <t xml:space="preserve">5.17781209945679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01278734207153</t>
+    <t xml:space="preserve">5.01278686523438</t>
   </si>
   <si>
     <t xml:space="preserve">4.96993160247803</t>
@@ -1331,40 +1334,40 @@
     <t xml:space="preserve">5.05244445800781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98912048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94498634338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03197622299194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01598501205444</t>
+    <t xml:space="preserve">4.9891209602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94498586654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03197574615479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0159854888916</t>
   </si>
   <si>
     <t xml:space="preserve">5.02621936798096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01470613479614</t>
+    <t xml:space="preserve">5.01470565795898</t>
   </si>
   <si>
     <t xml:space="preserve">5.08506488800049</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93539190292358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92579746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96545457839966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02557945251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04029083251953</t>
+    <t xml:space="preserve">4.93539142608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92579793930054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9654541015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02557992935181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04029130935669</t>
   </si>
   <si>
     <t xml:space="preserve">5.02110242843628</t>
@@ -1373,25 +1376,25 @@
     <t xml:space="preserve">5.11704683303833</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05947971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06971454620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24497270584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14135313034058</t>
+    <t xml:space="preserve">5.0594801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06971406936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24497318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14135265350342</t>
   </si>
   <si>
     <t xml:space="preserve">4.97888708114624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7646107673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83496999740601</t>
+    <t xml:space="preserve">4.76461029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83496952056885</t>
   </si>
   <si>
     <t xml:space="preserve">4.78124046325684</t>
@@ -1400,13 +1403,13 @@
     <t xml:space="preserve">4.73326873779297</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71471881866455</t>
+    <t xml:space="preserve">4.71471929550171</t>
   </si>
   <si>
     <t xml:space="preserve">4.66290903091431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55097341537476</t>
+    <t xml:space="preserve">4.5509729385376</t>
   </si>
   <si>
     <t xml:space="preserve">4.32710266113281</t>
@@ -1421,7 +1424,7 @@
     <t xml:space="preserve">4.63092708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72943067550659</t>
+    <t xml:space="preserve">4.72943019866943</t>
   </si>
   <si>
     <t xml:space="preserve">4.81961822509766</t>
@@ -1439,13 +1442,13 @@
     <t xml:space="preserve">4.8741979598999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99108457565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88932514190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9842095375061</t>
+    <t xml:space="preserve">4.99108505249023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88932466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98421001434326</t>
   </si>
   <si>
     <t xml:space="preserve">5.03165197372437</t>
@@ -1457,13 +1460,13 @@
     <t xml:space="preserve">4.79512739181519</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76074838638306</t>
+    <t xml:space="preserve">4.7607479095459</t>
   </si>
   <si>
     <t xml:space="preserve">4.74630975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86113452911377</t>
+    <t xml:space="preserve">4.86113405227661</t>
   </si>
   <si>
     <t xml:space="preserve">4.79031372070312</t>
@@ -1487,7 +1490,7 @@
     <t xml:space="preserve">4.78687620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76968669891357</t>
+    <t xml:space="preserve">4.76968717575073</t>
   </si>
   <si>
     <t xml:space="preserve">4.91613960266113</t>
@@ -1496,16 +1499,16 @@
     <t xml:space="preserve">4.97802114486694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96770763397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82675552368164</t>
+    <t xml:space="preserve">4.96770811080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8267560005188</t>
   </si>
   <si>
     <t xml:space="preserve">4.85013294219971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86044692993164</t>
+    <t xml:space="preserve">4.86044645309448</t>
   </si>
   <si>
     <t xml:space="preserve">4.89963817596436</t>
@@ -1517,7 +1520,7 @@
     <t xml:space="preserve">4.99177312850952</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0543417930603</t>
+    <t xml:space="preserve">5.05434131622314</t>
   </si>
   <si>
     <t xml:space="preserve">4.96151971817017</t>
@@ -1526,10 +1529,10 @@
     <t xml:space="preserve">4.97939682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99246072769165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85838413238525</t>
+    <t xml:space="preserve">4.99246025085449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85838460922241</t>
   </si>
   <si>
     <t xml:space="preserve">4.98489713668823</t>
@@ -1538,22 +1541,22 @@
     <t xml:space="preserve">4.85219573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90307569503784</t>
+    <t xml:space="preserve">4.90307664871216</t>
   </si>
   <si>
     <t xml:space="preserve">4.97183322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93882989883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91682767868042</t>
+    <t xml:space="preserve">4.93882942199707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91682720184326</t>
   </si>
   <si>
     <t xml:space="preserve">4.83363151550293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76556158065796</t>
+    <t xml:space="preserve">4.76556205749512</t>
   </si>
   <si>
     <t xml:space="preserve">4.75868606567383</t>
@@ -1562,7 +1565,7 @@
     <t xml:space="preserve">4.75043487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67067718505859</t>
+    <t xml:space="preserve">4.67067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.58129262924194</t>
@@ -1571,22 +1574,22 @@
     <t xml:space="preserve">4.5427885055542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4630298614502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48228168487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51941108703613</t>
+    <t xml:space="preserve">4.46303033828735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48228216171265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51941061019897</t>
   </si>
   <si>
     <t xml:space="preserve">4.60604524612427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59779405593872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52972459793091</t>
+    <t xml:space="preserve">4.59779453277588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52972412109375</t>
   </si>
   <si>
     <t xml:space="preserve">4.53797483444214</t>
@@ -1607,7 +1610,7 @@
     <t xml:space="preserve">4.50634717941284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51597261428833</t>
+    <t xml:space="preserve">4.51597309112549</t>
   </si>
   <si>
     <t xml:space="preserve">4.49053287506104</t>
@@ -1619,19 +1622,19 @@
     <t xml:space="preserve">4.518723487854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53041219711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5104718208313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52491092681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48503160476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47746896743774</t>
+    <t xml:space="preserve">4.53041172027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51047229766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52491140365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.485032081604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47746849060059</t>
   </si>
   <si>
     <t xml:space="preserve">4.78412628173828</t>
@@ -1640,25 +1643,25 @@
     <t xml:space="preserve">4.66517639160156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6541748046875</t>
+    <t xml:space="preserve">4.65417432785034</t>
   </si>
   <si>
     <t xml:space="preserve">4.70299291610718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73049545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71055603027344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64661121368408</t>
+    <t xml:space="preserve">4.7304949760437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71055555343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64661169052124</t>
   </si>
   <si>
     <t xml:space="preserve">4.63354778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5503511428833</t>
+    <t xml:space="preserve">4.55035161972046</t>
   </si>
   <si>
     <t xml:space="preserve">4.50840950012207</t>
@@ -1670,16 +1673,16 @@
     <t xml:space="preserve">4.42727661132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40046072006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33239126205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22237968444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20450305938721</t>
+    <t xml:space="preserve">4.40046119689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2223801612854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20450258255005</t>
   </si>
   <si>
     <t xml:space="preserve">4.16256093978882</t>
@@ -1688,7 +1691,7 @@
     <t xml:space="preserve">4.06630086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09311676025391</t>
+    <t xml:space="preserve">4.09311628341675</t>
   </si>
   <si>
     <t xml:space="preserve">3.98791790008545</t>
@@ -1697,7 +1700,7 @@
     <t xml:space="preserve">4.05942487716675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09724140167236</t>
+    <t xml:space="preserve">4.09724187850952</t>
   </si>
   <si>
     <t xml:space="preserve">4.0497989654541</t>
@@ -1706,10 +1709,10 @@
     <t xml:space="preserve">4.0532374382019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10480499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09105348587036</t>
+    <t xml:space="preserve">4.10480451583862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09105396270752</t>
   </si>
   <si>
     <t xml:space="preserve">4.088303565979</t>
@@ -1718,25 +1721,25 @@
     <t xml:space="preserve">4.13161993026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21962928771973</t>
+    <t xml:space="preserve">4.21962976455688</t>
   </si>
   <si>
     <t xml:space="preserve">4.28563594818115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29732513427734</t>
+    <t xml:space="preserve">4.29732465744019</t>
   </si>
   <si>
     <t xml:space="preserve">4.28976154327393</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22100448608398</t>
+    <t xml:space="preserve">4.22100496292114</t>
   </si>
   <si>
     <t xml:space="preserve">4.15293502807617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36608219146729</t>
+    <t xml:space="preserve">4.36608266830444</t>
   </si>
   <si>
     <t xml:space="preserve">4.27601051330566</t>
@@ -1754,10 +1757,10 @@
     <t xml:space="preserve">4.15224742889404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13505840301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09174108505249</t>
+    <t xml:space="preserve">4.13505792617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09174060821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.03260946273804</t>
@@ -1769,7 +1772,7 @@
     <t xml:space="preserve">4.054612159729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14537191390991</t>
+    <t xml:space="preserve">4.14537143707275</t>
   </si>
   <si>
     <t xml:space="preserve">4.2237548828125</t>
@@ -1790,13 +1793,13 @@
     <t xml:space="preserve">4.04429864883423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02917194366455</t>
+    <t xml:space="preserve">4.02917289733887</t>
   </si>
   <si>
     <t xml:space="preserve">3.99273061752319</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99891924858093</t>
+    <t xml:space="preserve">3.99891877174377</t>
   </si>
   <si>
     <t xml:space="preserve">3.96316480636597</t>
@@ -1817,25 +1820,25 @@
     <t xml:space="preserve">3.78164625167847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71013879776001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69501233100891</t>
+    <t xml:space="preserve">3.71013855934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69501209259033</t>
   </si>
   <si>
     <t xml:space="preserve">3.73351573944092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72870278358459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64894461631775</t>
+    <t xml:space="preserve">3.72870326042175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64894437789917</t>
   </si>
   <si>
     <t xml:space="preserve">3.70051240921021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83115148544312</t>
+    <t xml:space="preserve">3.83115124702454</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990830421448</t>
@@ -1847,25 +1850,25 @@
     <t xml:space="preserve">3.97829174995422</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06286287307739</t>
+    <t xml:space="preserve">4.06286239624023</t>
   </si>
   <si>
     <t xml:space="preserve">4.048424243927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06767606735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04292392730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99548101425171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95491456985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04086065292358</t>
+    <t xml:space="preserve">4.06767559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04292345046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99548053741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95491409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04086112976074</t>
   </si>
   <si>
     <t xml:space="preserve">4.02160882949829</t>
@@ -1880,31 +1883,31 @@
     <t xml:space="preserve">3.97004127502441</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07180118560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11786937713623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22788095474243</t>
+    <t xml:space="preserve">4.07180166244507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11786890029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22788000106812</t>
   </si>
   <si>
     <t xml:space="preserve">4.31864023208618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28907442092896</t>
+    <t xml:space="preserve">4.2890739440918</t>
   </si>
   <si>
     <t xml:space="preserve">4.29044914245605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25056982040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24919462203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2698221206665</t>
+    <t xml:space="preserve">4.25057029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24919557571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26982259750366</t>
   </si>
   <si>
     <t xml:space="preserve">4.26294612884521</t>
@@ -1913,7 +1916,7 @@
     <t xml:space="preserve">4.24231958389282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13643312454224</t>
+    <t xml:space="preserve">4.13643264770508</t>
   </si>
   <si>
     <t xml:space="preserve">4.05392456054688</t>
@@ -1940,7 +1943,7 @@
     <t xml:space="preserve">4.2189416885376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21481704711914</t>
+    <t xml:space="preserve">4.21481657028198</t>
   </si>
   <si>
     <t xml:space="preserve">4.16324853897095</t>
@@ -1949,7 +1952,7 @@
     <t xml:space="preserve">4.28494882583618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34476709365845</t>
+    <t xml:space="preserve">4.34476757049561</t>
   </si>
   <si>
     <t xml:space="preserve">4.25400829315186</t>
@@ -1982,22 +1985,22 @@
     <t xml:space="preserve">4.57785415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6094822883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66173839569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60673189163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57097911834717</t>
+    <t xml:space="preserve">4.60948276519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66173791885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60673236846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57097864151001</t>
   </si>
   <si>
     <t xml:space="preserve">4.57166624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5077223777771</t>
+    <t xml:space="preserve">4.50772190093994</t>
   </si>
   <si>
     <t xml:space="preserve">4.45752906799316</t>
@@ -2006,28 +2009,28 @@
     <t xml:space="preserve">4.41971302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46234273910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4279637336731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54485130310059</t>
+    <t xml:space="preserve">4.46234226226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42796421051025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54485082626343</t>
   </si>
   <si>
     <t xml:space="preserve">4.52422380447388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55860280990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58610534667969</t>
+    <t xml:space="preserve">4.55860233306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58610582351685</t>
   </si>
   <si>
     <t xml:space="preserve">4.45546674728394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48296976089478</t>
+    <t xml:space="preserve">4.48296928405762</t>
   </si>
   <si>
     <t xml:space="preserve">4.53109979629517</t>
@@ -2042,10 +2045,10 @@
     <t xml:space="preserve">4.64111089706421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61360788345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62048435211182</t>
+    <t xml:space="preserve">4.61360836029053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62048387527466</t>
   </si>
   <si>
     <t xml:space="preserve">4.62735939025879</t>
@@ -2057,16 +2060,13 @@
     <t xml:space="preserve">4.65486288070679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49672079086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55228900909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61179637908936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54485082626343</t>
+    <t xml:space="preserve">4.4967212677002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5522894859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6117959022522</t>
   </si>
   <si>
     <t xml:space="preserve">4.60435819625854</t>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">4.69361877441406</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73824882507324</t>
+    <t xml:space="preserve">4.73824834823608</t>
   </si>
   <si>
     <t xml:space="preserve">4.71593379974365</t>
@@ -2087,10 +2087,10 @@
     <t xml:space="preserve">4.63411140441895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65642642974854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58948135375977</t>
+    <t xml:space="preserve">4.65642690658569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58948183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.51509761810303</t>
@@ -2102,16 +2102,16 @@
     <t xml:space="preserve">4.56716585159302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55972766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64898824691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64154958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58204317092896</t>
+    <t xml:space="preserve">4.55972719192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64898777008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64155006408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5820426940918</t>
   </si>
   <si>
     <t xml:space="preserve">4.52997446060181</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">4.37376832962036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4183988571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35889148712158</t>
+    <t xml:space="preserve">4.41839838027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35889196395874</t>
   </si>
   <si>
     <t xml:space="preserve">4.32913827896118</t>
@@ -2159,7 +2159,7 @@
     <t xml:space="preserve">4.48534393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43327522277832</t>
+    <t xml:space="preserve">4.43327569961548</t>
   </si>
   <si>
     <t xml:space="preserve">4.40352153778076</t>
@@ -2168,7 +2168,7 @@
     <t xml:space="preserve">4.38864469528198</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39608287811279</t>
+    <t xml:space="preserve">4.39608335494995</t>
   </si>
   <si>
     <t xml:space="preserve">4.35145282745361</t>
@@ -2177,13 +2177,13 @@
     <t xml:space="preserve">4.24731588363647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20268535614014</t>
+    <t xml:space="preserve">4.20268583297729</t>
   </si>
   <si>
     <t xml:space="preserve">4.19524669647217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10598659515381</t>
+    <t xml:space="preserve">4.10598611831665</t>
   </si>
   <si>
     <t xml:space="preserve">4.13573980331421</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">4.0241641998291</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93490409851074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90515065193176</t>
+    <t xml:space="preserve">3.93490362167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9051501750946</t>
   </si>
   <si>
     <t xml:space="preserve">3.95721864700317</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">3.94234228134155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9795343875885</t>
+    <t xml:space="preserve">3.97953391075134</t>
   </si>
   <si>
     <t xml:space="preserve">3.97209572792053</t>
@@ -2231,10 +2231,10 @@
     <t xml:space="preserve">4.098548412323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16549348831177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18780899047852</t>
+    <t xml:space="preserve">4.16549396514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18780851364136</t>
   </si>
   <si>
     <t xml:space="preserve">4.18037033081055</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">4.17293214797974</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11342477798462</t>
+    <t xml:space="preserve">4.11342525482178</t>
   </si>
   <si>
     <t xml:space="preserve">4.14317846298218</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">4.23243856430054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23987722396851</t>
+    <t xml:space="preserve">4.23987770080566</t>
   </si>
   <si>
     <t xml:space="preserve">4.26963090896606</t>
@@ -2273,13 +2273,13 @@
     <t xml:space="preserve">4.29194593429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26219272613525</t>
+    <t xml:space="preserve">4.2621922492981</t>
   </si>
   <si>
     <t xml:space="preserve">4.27706909179688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29938459396362</t>
+    <t xml:space="preserve">4.29938411712646</t>
   </si>
   <si>
     <t xml:space="preserve">4.28450775146484</t>
@@ -2294,16 +2294,16 @@
     <t xml:space="preserve">4.46302890777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47046709060669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45559024810791</t>
+    <t xml:space="preserve">4.47046661376953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45558977127075</t>
   </si>
   <si>
     <t xml:space="preserve">4.6638650894165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74568748474121</t>
+    <t xml:space="preserve">4.74568796157837</t>
   </si>
   <si>
     <t xml:space="preserve">4.79031753540039</t>
@@ -2330,7 +2330,7 @@
     <t xml:space="preserve">4.72337198257446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68618059158325</t>
+    <t xml:space="preserve">4.68618011474609</t>
   </si>
   <si>
     <t xml:space="preserve">4.08367109298706</t>
@@ -2345,25 +2345,25 @@
     <t xml:space="preserve">3.92746543884277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48116254806519</t>
+    <t xml:space="preserve">3.48116230964661</t>
   </si>
   <si>
     <t xml:space="preserve">3.38446378707886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37702512741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7187283039093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76335859298706</t>
+    <t xml:space="preserve">3.37702488899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71872854232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76335883140564</t>
   </si>
   <si>
     <t xml:space="preserve">2.54020714759827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57367992401123</t>
+    <t xml:space="preserve">2.57367968559265</t>
   </si>
   <si>
     <t xml:space="preserve">2.70385146141052</t>
@@ -2387,22 +2387,22 @@
     <t xml:space="preserve">2.83402323722839</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82658457756042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68525552749634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78939270973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80426955223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75220108032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7001326084137</t>
+    <t xml:space="preserve">2.826584815979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68525576591492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78939294815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80426979064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75220131874084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70013236999512</t>
   </si>
   <si>
     <t xml:space="preserve">2.7150092124939</t>
@@ -2411,25 +2411,25 @@
     <t xml:space="preserve">2.76707768440247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73732423782349</t>
+    <t xml:space="preserve">2.73732447624207</t>
   </si>
   <si>
     <t xml:space="preserve">2.69641304016113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60343360900879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66294050216675</t>
+    <t xml:space="preserve">2.60343337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66294026374817</t>
   </si>
   <si>
     <t xml:space="preserve">2.69269394874573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62946772575378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62574863433838</t>
+    <t xml:space="preserve">2.62946796417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6257483959198</t>
   </si>
   <si>
     <t xml:space="preserve">2.64062547683716</t>
@@ -2438,10 +2438,10 @@
     <t xml:space="preserve">2.65550208091736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.614590883255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60715246200562</t>
+    <t xml:space="preserve">2.61459112167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60715270042419</t>
   </si>
   <si>
     <t xml:space="preserve">2.63318705558777</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">2.59227561950684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55508375167847</t>
+    <t xml:space="preserve">2.55508399009705</t>
   </si>
   <si>
     <t xml:space="preserve">2.45466589927673</t>
@@ -2471,13 +2471,13 @@
     <t xml:space="preserve">2.33937096595764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23523354530334</t>
+    <t xml:space="preserve">2.23523330688477</t>
   </si>
   <si>
     <t xml:space="preserve">2.25754880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44722747802734</t>
+    <t xml:space="preserve">2.44722723960876</t>
   </si>
   <si>
     <t xml:space="preserve">2.3840012550354</t>
@@ -2498,10 +2498,10 @@
     <t xml:space="preserve">2.6108717918396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61831021308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77823543548584</t>
+    <t xml:space="preserve">2.61830997467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77823519706726</t>
   </si>
   <si>
     <t xml:space="preserve">2.91584539413452</t>
@@ -2522,7 +2522,7 @@
     <t xml:space="preserve">2.52904963493347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51045346260071</t>
+    <t xml:space="preserve">2.51045370101929</t>
   </si>
   <si>
     <t xml:space="preserve">2.58483743667603</t>
@@ -8853,7 +8853,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G144" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8879,7 +8879,7 @@
         <v>7.24187612533569</v>
       </c>
       <c r="G145" t="s">
-        <v>63</v>
+        <v>130</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -8931,7 +8931,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="s">
-        <v>14</v>
+        <v>132</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8957,7 +8957,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G148" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8983,7 +8983,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G149" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -9009,7 +9009,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -9061,7 +9061,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G152" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -9087,7 +9087,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G153" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -9113,7 +9113,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9139,7 +9139,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G155" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9165,7 +9165,7 @@
         <v>7.05130100250244</v>
       </c>
       <c r="G156" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -9191,7 +9191,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G157" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -9217,7 +9217,7 @@
         <v>7.13032007217407</v>
       </c>
       <c r="G158" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9243,7 +9243,7 @@
         <v>7.04200410842896</v>
       </c>
       <c r="G159" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9269,7 +9269,7 @@
         <v>7.0048189163208</v>
       </c>
       <c r="G160" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9295,7 +9295,7 @@
         <v>6.93509578704834</v>
       </c>
       <c r="G161" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9321,7 +9321,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G162" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9347,7 +9347,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G163" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9373,7 +9373,7 @@
         <v>6.78170585632324</v>
       </c>
       <c r="G164" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9399,7 +9399,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G165" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9425,7 +9425,7 @@
         <v>6.88396596908569</v>
       </c>
       <c r="G166" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9451,7 +9451,7 @@
         <v>6.87002086639404</v>
       </c>
       <c r="G167" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9477,7 +9477,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9503,7 +9503,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9529,7 +9529,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G170" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9555,7 +9555,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G171" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9581,7 +9581,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G172" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9607,7 +9607,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9633,7 +9633,7 @@
         <v>6.79565000534058</v>
       </c>
       <c r="G174" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9659,7 +9659,7 @@
         <v>6.69803810119629</v>
       </c>
       <c r="G175" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9711,7 +9711,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9737,7 +9737,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G178" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9763,7 +9763,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G179" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9789,7 +9789,7 @@
         <v>6.242516040802</v>
       </c>
       <c r="G180" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9841,7 +9841,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G182" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9867,7 +9867,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9893,7 +9893,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9919,7 +9919,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9945,7 +9945,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G186" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9971,7 +9971,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G187" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9997,7 +9997,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10023,7 +10023,7 @@
         <v>6.13095903396606</v>
       </c>
       <c r="G189" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -10075,7 +10075,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -10127,7 +10127,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G193" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10153,7 +10153,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G194" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10179,7 +10179,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G195" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10205,7 +10205,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10231,7 +10231,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G197" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10257,7 +10257,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G198" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10283,7 +10283,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10309,7 +10309,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10335,7 +10335,7 @@
         <v>5.99616193771362</v>
       </c>
       <c r="G201" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10361,7 +10361,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G202" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10387,7 +10387,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G203" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10413,7 +10413,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G204" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10439,7 +10439,7 @@
         <v>6.20532989501953</v>
       </c>
       <c r="G205" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10465,7 +10465,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10491,7 +10491,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10517,7 +10517,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G208" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10543,7 +10543,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10595,7 +10595,7 @@
         <v>6.65155601501465</v>
       </c>
       <c r="G211" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10621,7 +10621,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G212" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10647,7 +10647,7 @@
         <v>6.52140712738037</v>
       </c>
       <c r="G213" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10699,7 +10699,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10725,7 +10725,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G216" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10751,7 +10751,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10777,7 +10777,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G218" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10803,7 +10803,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10829,7 +10829,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G220" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10855,7 +10855,7 @@
         <v>6.34477615356445</v>
       </c>
       <c r="G221" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10881,7 +10881,7 @@
         <v>6.29364585876465</v>
       </c>
       <c r="G222" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10907,7 +10907,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G223" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10933,7 +10933,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10959,7 +10959,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10985,7 +10985,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11011,7 +11011,7 @@
         <v>6.07053279876709</v>
       </c>
       <c r="G227" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11037,7 +11037,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G228" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -11063,7 +11063,7 @@
         <v>5.74516010284424</v>
       </c>
       <c r="G229" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -11089,7 +11089,7 @@
         <v>5.88460493087769</v>
       </c>
       <c r="G230" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11115,7 +11115,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11141,7 +11141,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11167,7 +11167,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11193,7 +11193,7 @@
         <v>5.81023406982422</v>
       </c>
       <c r="G234" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11219,7 +11219,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11245,7 +11245,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11271,7 +11271,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11297,7 +11297,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11323,7 +11323,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11349,7 +11349,7 @@
         <v>6.14490413665771</v>
       </c>
       <c r="G240" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11375,7 +11375,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11401,7 +11401,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11427,7 +11427,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G243" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11453,7 +11453,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G244" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11505,7 +11505,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G246" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11583,7 +11583,7 @@
         <v>6.57718515396118</v>
       </c>
       <c r="G249" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11609,7 +11609,7 @@
         <v>6.53070402145386</v>
       </c>
       <c r="G250" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11635,7 +11635,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G251" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11661,7 +11661,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11687,7 +11687,7 @@
         <v>6.67479705810547</v>
       </c>
       <c r="G253" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11713,7 +11713,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G254" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11739,7 +11739,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11765,7 +11765,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11791,7 +11791,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G257" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11817,7 +11817,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G258" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11895,7 +11895,7 @@
         <v>7.05594921112061</v>
       </c>
       <c r="G261" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11947,7 +11947,7 @@
         <v>6.91650295257568</v>
       </c>
       <c r="G263" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11973,7 +11973,7 @@
         <v>7.00946712493896</v>
       </c>
       <c r="G264" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11999,7 +11999,7 @@
         <v>7.02341079711914</v>
       </c>
       <c r="G265" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12051,7 +12051,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G267" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12077,7 +12077,7 @@
         <v>6.94903993606567</v>
       </c>
       <c r="G268" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -12155,7 +12155,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G271" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12207,7 +12207,7 @@
         <v>6.82818794250488</v>
       </c>
       <c r="G273" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12233,7 +12233,7 @@
         <v>6.80494689941406</v>
       </c>
       <c r="G274" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12259,7 +12259,7 @@
         <v>6.75381708145142</v>
       </c>
       <c r="G275" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12311,7 +12311,7 @@
         <v>6.61901903152466</v>
       </c>
       <c r="G277" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12337,7 +12337,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12363,7 +12363,7 @@
         <v>6.47027683258057</v>
       </c>
       <c r="G279" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12389,7 +12389,7 @@
         <v>6.62831592559814</v>
       </c>
       <c r="G280" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12415,7 +12415,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G281" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12441,7 +12441,7 @@
         <v>6.57253694534302</v>
       </c>
       <c r="G282" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12519,7 +12519,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12597,7 +12597,7 @@
         <v>6.81424283981323</v>
       </c>
       <c r="G288" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12623,7 +12623,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G289" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12649,7 +12649,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G290" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12675,7 +12675,7 @@
         <v>6.95833683013916</v>
       </c>
       <c r="G291" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12701,7 +12701,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G292" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12727,7 +12727,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G293" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12753,7 +12753,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G294" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12779,7 +12779,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G295" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12805,7 +12805,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G296" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12857,7 +12857,7 @@
         <v>6.70268678665161</v>
       </c>
       <c r="G298" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12883,7 +12883,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G299" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12909,7 +12909,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G300" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -12935,7 +12935,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G301" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -12987,7 +12987,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G303" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13013,7 +13013,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G304" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -13039,7 +13039,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G305" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -13065,7 +13065,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G306" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -13091,7 +13091,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13143,7 +13143,7 @@
         <v>7.06989288330078</v>
       </c>
       <c r="G309" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13169,7 +13169,7 @@
         <v>7.17680215835571</v>
       </c>
       <c r="G310" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13195,7 +13195,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -13221,7 +13221,7 @@
         <v>7.41850709915161</v>
       </c>
       <c r="G312" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13247,7 +13247,7 @@
         <v>7.46963787078857</v>
       </c>
       <c r="G313" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13299,7 +13299,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G315" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13351,7 +13351,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G317" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13377,7 +13377,7 @@
         <v>7.60443496704102</v>
       </c>
       <c r="G318" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13403,7 +13403,7 @@
         <v>7.75782489776611</v>
       </c>
       <c r="G319" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13429,7 +13429,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G320" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13481,7 +13481,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G322" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13507,7 +13507,7 @@
         <v>7.59978723526001</v>
       </c>
       <c r="G323" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13533,7 +13533,7 @@
         <v>7.59513902664185</v>
       </c>
       <c r="G324" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13637,7 +13637,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G328" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13663,7 +13663,7 @@
         <v>7.46498918533325</v>
       </c>
       <c r="G329" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13715,7 +13715,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G331" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13741,7 +13741,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G332" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13767,7 +13767,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G333" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13793,7 +13793,7 @@
         <v>7.311598777771</v>
       </c>
       <c r="G334" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13819,7 +13819,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G335" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13845,7 +13845,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G336" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13871,7 +13871,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G337" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13897,7 +13897,7 @@
         <v>7.53471183776855</v>
       </c>
       <c r="G338" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13923,7 +13923,7 @@
         <v>7.66486120223999</v>
       </c>
       <c r="G339" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13949,7 +13949,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G340" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13975,7 +13975,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G341" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14001,7 +14001,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G342" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -14027,7 +14027,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G343" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -14053,7 +14053,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G344" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -14079,7 +14079,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G345" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -14105,7 +14105,7 @@
         <v>7.95769691467285</v>
       </c>
       <c r="G346" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -14131,7 +14131,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G347" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -14157,7 +14157,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G348" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14183,7 +14183,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G349" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14209,7 +14209,7 @@
         <v>8.16686630249023</v>
       </c>
       <c r="G350" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14235,7 +14235,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G351" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14261,7 +14261,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G352" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14287,7 +14287,7 @@
         <v>7.8554368019104</v>
       </c>
       <c r="G353" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14313,7 +14313,7 @@
         <v>7.79965877532959</v>
       </c>
       <c r="G354" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14339,7 +14339,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G355" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14365,7 +14365,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G356" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14391,7 +14391,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G357" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14417,7 +14417,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G358" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14443,7 +14443,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G359" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14469,7 +14469,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G360" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14495,7 +14495,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G361" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14521,7 +14521,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G362" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14547,7 +14547,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G363" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14573,7 +14573,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G364" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14599,7 +14599,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G365" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14625,7 +14625,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G366" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14651,7 +14651,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G367" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14677,7 +14677,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G368" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14703,7 +14703,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G369" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14729,7 +14729,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G370" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14755,7 +14755,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G371" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14781,7 +14781,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G372" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14807,7 +14807,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G373" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14833,7 +14833,7 @@
         <v>7.59048986434937</v>
       </c>
       <c r="G374" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14859,7 +14859,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G375" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14885,7 +14885,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G376" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14911,7 +14911,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G377" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14937,7 +14937,7 @@
         <v>7.4278039932251</v>
       </c>
       <c r="G378" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14963,7 +14963,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G379" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -14989,7 +14989,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G380" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -15015,7 +15015,7 @@
         <v>7.39991521835327</v>
       </c>
       <c r="G381" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -15041,7 +15041,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G382" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -15067,7 +15067,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G383" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -15093,7 +15093,7 @@
         <v>7.16750478744507</v>
       </c>
       <c r="G384" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -15119,7 +15119,7 @@
         <v>7.21863508224487</v>
       </c>
       <c r="G385" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -15145,7 +15145,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G386" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15171,7 +15171,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G387" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15197,7 +15197,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G388" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15223,7 +15223,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G389" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15249,7 +15249,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G390" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15275,7 +15275,7 @@
         <v>7.59048986434937</v>
       </c>
       <c r="G391" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15301,7 +15301,7 @@
         <v>7.55330514907837</v>
       </c>
       <c r="G392" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15327,7 +15327,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G393" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15353,7 +15353,7 @@
         <v>7.72064018249512</v>
       </c>
       <c r="G394" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15379,7 +15379,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G395" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15405,7 +15405,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G396" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15431,7 +15431,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G397" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15457,7 +15457,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G398" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15483,7 +15483,7 @@
         <v>7.72993612289429</v>
       </c>
       <c r="G399" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15509,7 +15509,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G400" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15535,7 +15535,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G401" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15561,7 +15561,7 @@
         <v>7.74388122558594</v>
       </c>
       <c r="G402" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15587,7 +15587,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G403" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15613,7 +15613,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G404" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15639,7 +15639,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G405" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15665,7 +15665,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G406" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15691,7 +15691,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G407" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15717,7 +15717,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G408" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15743,7 +15743,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G409" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15769,7 +15769,7 @@
         <v>7.82289981842041</v>
       </c>
       <c r="G410" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15795,7 +15795,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G411" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15821,7 +15821,7 @@
         <v>7.89262294769287</v>
       </c>
       <c r="G412" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15847,7 +15847,7 @@
         <v>7.81360292434692</v>
       </c>
       <c r="G413" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15873,7 +15873,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G414" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15899,7 +15899,7 @@
         <v>7.79501104354858</v>
       </c>
       <c r="G415" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15925,7 +15925,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G416" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15951,7 +15951,7 @@
         <v>8.01347637176514</v>
       </c>
       <c r="G417" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -15977,7 +15977,7 @@
         <v>7.99023485183716</v>
       </c>
       <c r="G418" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -16003,7 +16003,7 @@
         <v>7.93445587158203</v>
       </c>
       <c r="G419" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -16029,7 +16029,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G420" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -16055,7 +16055,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G421" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -16081,7 +16081,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G422" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -16107,7 +16107,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G423" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -16133,7 +16133,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G424" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -16159,7 +16159,7 @@
         <v>7.86008501052856</v>
       </c>
       <c r="G425" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -16185,7 +16185,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G426" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16211,7 +16211,7 @@
         <v>7.78106594085693</v>
       </c>
       <c r="G427" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16237,7 +16237,7 @@
         <v>7.89727115631104</v>
       </c>
       <c r="G428" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16263,7 +16263,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G429" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16289,7 +16289,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G430" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16315,7 +16315,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G431" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16341,7 +16341,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G432" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16367,7 +16367,7 @@
         <v>7.84149312973022</v>
       </c>
       <c r="G433" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16393,7 +16393,7 @@
         <v>7.92051219940186</v>
       </c>
       <c r="G434" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16419,7 +16419,7 @@
         <v>8.03206825256348</v>
       </c>
       <c r="G435" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16445,7 +16445,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G436" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16471,7 +16471,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G437" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16497,7 +16497,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G438" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16523,7 +16523,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G439" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16549,7 +16549,7 @@
         <v>8.19010734558105</v>
       </c>
       <c r="G440" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16575,7 +16575,7 @@
         <v>8.12503242492676</v>
       </c>
       <c r="G441" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16601,7 +16601,7 @@
         <v>8.08784675598145</v>
       </c>
       <c r="G442" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16627,7 +16627,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G443" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16653,7 +16653,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G444" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16679,7 +16679,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G445" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16705,7 +16705,7 @@
         <v>8.14362525939941</v>
       </c>
       <c r="G446" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16731,7 +16731,7 @@
         <v>8.12038421630859</v>
       </c>
       <c r="G447" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16757,7 +16757,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G448" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16783,7 +16783,7 @@
         <v>8.20869922637939</v>
       </c>
       <c r="G449" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16809,7 +16809,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G450" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16835,7 +16835,7 @@
         <v>8.22729206085205</v>
       </c>
       <c r="G451" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16861,7 +16861,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G452" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16887,7 +16887,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G453" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16913,7 +16913,7 @@
         <v>8.07390213012695</v>
       </c>
       <c r="G454" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16939,7 +16939,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G455" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16965,7 +16965,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G456" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -16991,7 +16991,7 @@
         <v>8.36673831939697</v>
       </c>
       <c r="G457" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -17017,7 +17017,7 @@
         <v>8.50618267059326</v>
       </c>
       <c r="G458" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -17043,7 +17043,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G459" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -17069,7 +17069,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G460" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -17095,7 +17095,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -17121,7 +17121,7 @@
         <v>8.5526647567749</v>
       </c>
       <c r="G462" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -17147,7 +17147,7 @@
         <v>8.54801654815674</v>
       </c>
       <c r="G463" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -17173,7 +17173,7 @@
         <v>8.69211101531982</v>
       </c>
       <c r="G464" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -17199,7 +17199,7 @@
         <v>8.74788856506348</v>
       </c>
       <c r="G465" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -17225,7 +17225,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G466" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17251,7 +17251,7 @@
         <v>8.60379505157471</v>
       </c>
       <c r="G467" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17277,7 +17277,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G468" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17303,7 +17303,7 @@
         <v>8.98959541320801</v>
       </c>
       <c r="G469" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17329,7 +17329,7 @@
         <v>9.22665309906006</v>
       </c>
       <c r="G470" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17355,7 +17355,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G471" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17381,7 +17381,7 @@
         <v>9.696120262146</v>
       </c>
       <c r="G472" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17407,7 +17407,7 @@
         <v>9.67752742767334</v>
       </c>
       <c r="G473" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17433,7 +17433,7 @@
         <v>9.55667400360107</v>
       </c>
       <c r="G474" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17459,7 +17459,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G475" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17485,7 +17485,7 @@
         <v>9.62174892425537</v>
       </c>
       <c r="G476" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17511,7 +17511,7 @@
         <v>9.43582057952881</v>
       </c>
       <c r="G477" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17537,7 +17537,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G478" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17563,7 +17563,7 @@
         <v>9.34285736083984</v>
       </c>
       <c r="G479" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17589,7 +17589,7 @@
         <v>9.2080602645874</v>
       </c>
       <c r="G480" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17615,7 +17615,7 @@
         <v>9.38933944702148</v>
       </c>
       <c r="G481" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17641,7 +17641,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G482" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17667,7 +17667,7 @@
         <v>9.91923332214355</v>
       </c>
       <c r="G483" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17693,7 +17693,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G484" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17719,7 +17719,7 @@
         <v>9.65893363952637</v>
       </c>
       <c r="G485" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17745,7 +17745,7 @@
         <v>10.0029001235962</v>
       </c>
       <c r="G486" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17771,7 +17771,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G487" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17797,7 +17797,7 @@
         <v>9.90063953399658</v>
       </c>
       <c r="G488" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17823,7 +17823,7 @@
         <v>10.0586776733398</v>
       </c>
       <c r="G489" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17849,7 +17849,7 @@
         <v>10.1144561767578</v>
       </c>
       <c r="G490" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17875,7 +17875,7 @@
         <v>10.0307893753052</v>
       </c>
       <c r="G491" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17901,7 +17901,7 @@
         <v>10.0121955871582</v>
       </c>
       <c r="G492" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17927,7 +17927,7 @@
         <v>9.76119422912598</v>
       </c>
       <c r="G493" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17953,7 +17953,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G494" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -17979,7 +17979,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G495" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -18005,7 +18005,7 @@
         <v>9.93782520294189</v>
       </c>
       <c r="G496" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -18031,7 +18031,7 @@
         <v>10.0772714614868</v>
       </c>
       <c r="G497" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -18057,7 +18057,7 @@
         <v>10.318977355957</v>
       </c>
       <c r="G498" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -18083,7 +18083,7 @@
         <v>10.3003835678101</v>
       </c>
       <c r="G499" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -18109,7 +18109,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G500" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -18135,7 +18135,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G501" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -18161,7 +18161,7 @@
         <v>10.411940574646</v>
       </c>
       <c r="G502" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18187,7 +18187,7 @@
         <v>10.1330490112305</v>
       </c>
       <c r="G503" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18213,7 +18213,7 @@
         <v>9.49159908294678</v>
       </c>
       <c r="G504" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18239,7 +18239,7 @@
         <v>9.11044788360596</v>
       </c>
       <c r="G505" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18265,7 +18265,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G506" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18291,7 +18291,7 @@
         <v>9.08255863189697</v>
       </c>
       <c r="G507" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18317,7 +18317,7 @@
         <v>8.88268661499023</v>
       </c>
       <c r="G508" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18343,7 +18343,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G509" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18369,7 +18369,7 @@
         <v>9.09650325775146</v>
       </c>
       <c r="G510" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18395,7 +18395,7 @@
         <v>8.96170616149902</v>
       </c>
       <c r="G511" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18421,7 +18421,7 @@
         <v>8.95240879058838</v>
       </c>
       <c r="G512" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18447,7 +18447,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G513" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18473,7 +18473,7 @@
         <v>9.1569299697876</v>
       </c>
       <c r="G514" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18499,7 +18499,7 @@
         <v>9.16622638702393</v>
       </c>
       <c r="G515" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18525,7 +18525,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G516" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18551,7 +18551,7 @@
         <v>9.31496810913086</v>
       </c>
       <c r="G517" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18577,7 +18577,7 @@
         <v>9.26848602294922</v>
       </c>
       <c r="G518" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18603,7 +18603,7 @@
         <v>9.00818824768066</v>
       </c>
       <c r="G519" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18629,7 +18629,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G520" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18655,7 +18655,7 @@
         <v>9.06396579742432</v>
       </c>
       <c r="G521" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18681,7 +18681,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G522" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18707,7 +18707,7 @@
         <v>8.8873348236084</v>
       </c>
       <c r="G523" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18733,7 +18733,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G524" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18759,7 +18759,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G525" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18785,7 +18785,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G526" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18811,7 +18811,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G527" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18837,7 +18837,7 @@
         <v>8.90592765808105</v>
       </c>
       <c r="G528" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18863,7 +18863,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18889,7 +18889,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G530" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18915,7 +18915,7 @@
         <v>8.85014915466309</v>
       </c>
       <c r="G531" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18941,7 +18941,7 @@
         <v>8.60844421386719</v>
       </c>
       <c r="G532" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18967,7 +18967,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G533" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -18993,7 +18993,7 @@
         <v>8.53407287597656</v>
       </c>
       <c r="G534" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -19019,7 +19019,7 @@
         <v>8.34814453125</v>
       </c>
       <c r="G535" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -19045,7 +19045,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G536" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -19071,7 +19071,7 @@
         <v>8.05995655059814</v>
       </c>
       <c r="G537" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -19097,7 +19097,7 @@
         <v>8.30166339874268</v>
       </c>
       <c r="G538" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -19123,7 +19123,7 @@
         <v>7.87403011322021</v>
       </c>
       <c r="G539" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -19149,7 +19149,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G540" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -19175,7 +19175,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G541" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19201,7 +19201,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G542" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19227,7 +19227,7 @@
         <v>7.68810176849365</v>
       </c>
       <c r="G543" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19253,7 +19253,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G544" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19279,7 +19279,7 @@
         <v>7.8182520866394</v>
       </c>
       <c r="G545" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19305,7 +19305,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G546" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19331,7 +19331,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G547" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19357,7 +19357,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G548" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19383,7 +19383,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G549" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19409,7 +19409,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G550" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19435,7 +19435,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G551" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19461,7 +19461,7 @@
         <v>7.49566698074341</v>
       </c>
       <c r="G552" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19487,7 +19487,7 @@
         <v>7.36086988449097</v>
       </c>
       <c r="G553" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19513,7 +19513,7 @@
         <v>7.17308282852173</v>
       </c>
       <c r="G554" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19539,7 +19539,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G555" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19565,7 +19565,7 @@
         <v>6.98622608184814</v>
       </c>
       <c r="G556" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19591,7 +19591,7 @@
         <v>7.08383798599243</v>
       </c>
       <c r="G557" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19617,7 +19617,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G558" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19643,7 +19643,7 @@
         <v>7.298583984375</v>
       </c>
       <c r="G559" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19669,7 +19669,7 @@
         <v>7.12102317810059</v>
       </c>
       <c r="G560" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19695,7 +19695,7 @@
         <v>7.03177785873413</v>
       </c>
       <c r="G561" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19721,7 +19721,7 @@
         <v>7.05501890182495</v>
       </c>
       <c r="G562" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19747,7 +19747,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G563" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19773,7 +19773,7 @@
         <v>6.82911682128906</v>
       </c>
       <c r="G564" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19799,7 +19799,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G565" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19825,7 +19825,7 @@
         <v>7.01225614547729</v>
       </c>
       <c r="G566" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19851,7 +19851,7 @@
         <v>6.98064804077148</v>
       </c>
       <c r="G567" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19877,7 +19877,7 @@
         <v>6.94439220428467</v>
       </c>
       <c r="G568" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19903,7 +19903,7 @@
         <v>6.71291303634644</v>
       </c>
       <c r="G569" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19929,7 +19929,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G570" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19955,7 +19955,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G571" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -19981,7 +19981,7 @@
         <v>7.27699995040894</v>
       </c>
       <c r="G572" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -20007,7 +20007,7 @@
         <v>7.97800016403198</v>
       </c>
       <c r="G573" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -20033,7 +20033,7 @@
         <v>7.58799982070923</v>
       </c>
       <c r="G574" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -20059,7 +20059,7 @@
         <v>7.75</v>
       </c>
       <c r="G575" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -20085,7 +20085,7 @@
         <v>8.04199981689453</v>
       </c>
       <c r="G576" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -20111,7 +20111,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G577" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -20137,7 +20137,7 @@
         <v>8.25899982452393</v>
       </c>
       <c r="G578" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -20163,7 +20163,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G579" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -20189,7 +20189,7 @@
         <v>7.83699989318848</v>
       </c>
       <c r="G580" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20215,7 +20215,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G581" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20241,7 +20241,7 @@
         <v>7.89900016784668</v>
       </c>
       <c r="G582" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20267,7 +20267,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G583" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20293,7 +20293,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G584" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20319,7 +20319,7 @@
         <v>7.86700010299683</v>
       </c>
       <c r="G585" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20345,7 +20345,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G586" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20371,7 +20371,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G587" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20397,7 +20397,7 @@
         <v>7.85799980163574</v>
       </c>
       <c r="G588" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20423,7 +20423,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G589" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20449,7 +20449,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G590" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20475,7 +20475,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G591" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20501,7 +20501,7 @@
         <v>7.71600008010864</v>
       </c>
       <c r="G592" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20527,7 +20527,7 @@
         <v>7.70100021362305</v>
       </c>
       <c r="G593" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20553,7 +20553,7 @@
         <v>7.76300001144409</v>
       </c>
       <c r="G594" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20579,7 +20579,7 @@
         <v>7.85699987411499</v>
       </c>
       <c r="G595" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20605,7 +20605,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G596" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20631,7 +20631,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20657,7 +20657,7 @@
         <v>8</v>
       </c>
       <c r="G598" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20683,7 +20683,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G599" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20709,7 +20709,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G600" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20735,7 +20735,7 @@
         <v>7.92600011825562</v>
       </c>
       <c r="G601" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20761,7 +20761,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G602" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20787,7 +20787,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G603" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20813,7 +20813,7 @@
         <v>8</v>
       </c>
       <c r="G604" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20839,7 +20839,7 @@
         <v>7.78399991989136</v>
       </c>
       <c r="G605" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20865,7 +20865,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G606" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20891,7 +20891,7 @@
         <v>7.44899988174438</v>
       </c>
       <c r="G607" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20917,7 +20917,7 @@
         <v>7.55900001525879</v>
       </c>
       <c r="G608" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -20943,7 +20943,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G609" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -20969,7 +20969,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G610" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -20995,7 +20995,7 @@
         <v>7.37099981307983</v>
       </c>
       <c r="G611" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -21021,7 +21021,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G612" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -21047,7 +21047,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G613" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -21073,7 +21073,7 @@
         <v>6.7649998664856</v>
       </c>
       <c r="G614" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -21099,7 +21099,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G615" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -21125,7 +21125,7 @@
         <v>7.27400016784668</v>
       </c>
       <c r="G616" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -21151,7 +21151,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G617" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -21177,7 +21177,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G618" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -21203,7 +21203,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G619" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21229,7 +21229,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G620" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21255,7 +21255,7 @@
         <v>7.32299995422363</v>
       </c>
       <c r="G621" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21281,7 +21281,7 @@
         <v>7.1710000038147</v>
       </c>
       <c r="G622" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21307,7 +21307,7 @@
         <v>7.08900022506714</v>
       </c>
       <c r="G623" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21333,7 +21333,7 @@
         <v>7.25899982452393</v>
       </c>
       <c r="G624" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21359,7 +21359,7 @@
         <v>7.11100006103516</v>
       </c>
       <c r="G625" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21385,7 +21385,7 @@
         <v>7.24900007247925</v>
       </c>
       <c r="G626" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21411,7 +21411,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G627" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21437,7 +21437,7 @@
         <v>6.97200012207031</v>
       </c>
       <c r="G628" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21463,7 +21463,7 @@
         <v>6.97399997711182</v>
       </c>
       <c r="G629" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21489,7 +21489,7 @@
         <v>6.92399978637695</v>
       </c>
       <c r="G630" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21515,7 +21515,7 @@
         <v>6.90299987792969</v>
       </c>
       <c r="G631" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21541,7 +21541,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G632" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21567,7 +21567,7 @@
         <v>6.96700000762939</v>
       </c>
       <c r="G633" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21593,7 +21593,7 @@
         <v>7</v>
       </c>
       <c r="G634" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21619,7 +21619,7 @@
         <v>6.875</v>
       </c>
       <c r="G635" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21645,7 +21645,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G636" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21671,7 +21671,7 @@
         <v>6.88199996948242</v>
       </c>
       <c r="G637" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21697,7 +21697,7 @@
         <v>7.04699993133545</v>
       </c>
       <c r="G638" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21723,7 +21723,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G639" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21749,7 +21749,7 @@
         <v>7</v>
       </c>
       <c r="G640" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21775,7 +21775,7 @@
         <v>6.93699979782104</v>
       </c>
       <c r="G641" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21801,7 +21801,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G642" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21827,7 +21827,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G643" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21853,7 +21853,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G644" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21879,7 +21879,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G645" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21905,7 +21905,7 @@
         <v>7.05399990081787</v>
       </c>
       <c r="G646" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21931,7 +21931,7 @@
         <v>7.06899976730347</v>
       </c>
       <c r="G647" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -21957,7 +21957,7 @@
         <v>7.12599992752075</v>
       </c>
       <c r="G648" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -21983,7 +21983,7 @@
         <v>7.17700004577637</v>
       </c>
       <c r="G649" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -22009,7 +22009,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G650" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -22035,7 +22035,7 @@
         <v>7.35099983215332</v>
       </c>
       <c r="G651" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22061,7 +22061,7 @@
         <v>7.21600008010864</v>
       </c>
       <c r="G652" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -22087,7 +22087,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G653" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -22113,7 +22113,7 @@
         <v>7.26100015640259</v>
       </c>
       <c r="G654" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22139,7 +22139,7 @@
         <v>7.06599998474121</v>
       </c>
       <c r="G655" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22165,7 +22165,7 @@
         <v>7.25</v>
       </c>
       <c r="G656" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22191,7 +22191,7 @@
         <v>7.05700016021729</v>
       </c>
       <c r="G657" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22217,7 +22217,7 @@
         <v>7.13100004196167</v>
       </c>
       <c r="G658" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22243,7 +22243,7 @@
         <v>7.23099994659424</v>
       </c>
       <c r="G659" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22269,7 +22269,7 @@
         <v>7.18300008773804</v>
       </c>
       <c r="G660" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22295,7 +22295,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G661" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22321,7 +22321,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G662" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22347,7 +22347,7 @@
         <v>6.93100023269653</v>
       </c>
       <c r="G663" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22373,7 +22373,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G664" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22399,7 +22399,7 @@
         <v>6.9210000038147</v>
       </c>
       <c r="G665" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22425,7 +22425,7 @@
         <v>6.90899991989136</v>
       </c>
       <c r="G666" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22451,7 +22451,7 @@
         <v>6.79300022125244</v>
       </c>
       <c r="G667" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22477,7 +22477,7 @@
         <v>6.66300010681152</v>
       </c>
       <c r="G668" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22503,7 +22503,7 @@
         <v>6.60699987411499</v>
       </c>
       <c r="G669" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22529,7 +22529,7 @@
         <v>6.49100017547607</v>
       </c>
       <c r="G670" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22555,7 +22555,7 @@
         <v>6.51900005340576</v>
       </c>
       <c r="G671" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22581,7 +22581,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22607,7 +22607,7 @@
         <v>6.69899988174438</v>
       </c>
       <c r="G673" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22633,7 +22633,7 @@
         <v>6.68699979782104</v>
       </c>
       <c r="G674" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22659,7 +22659,7 @@
         <v>6.58799982070923</v>
       </c>
       <c r="G675" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22685,7 +22685,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G676" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22711,7 +22711,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G677" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22737,7 +22737,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G678" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22763,7 +22763,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G679" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22789,7 +22789,7 @@
         <v>6.62099981307983</v>
       </c>
       <c r="G680" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22815,7 +22815,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G681" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22841,7 +22841,7 @@
         <v>6.56799983978271</v>
       </c>
       <c r="G682" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22867,7 +22867,7 @@
         <v>6.5310001373291</v>
       </c>
       <c r="G683" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22893,7 +22893,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G684" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22919,7 +22919,7 @@
         <v>6.57200002670288</v>
       </c>
       <c r="G685" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -22945,7 +22945,7 @@
         <v>6.58900022506714</v>
       </c>
       <c r="G686" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -22971,7 +22971,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G687" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -22997,7 +22997,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G688" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -23023,7 +23023,7 @@
         <v>6.58099985122681</v>
       </c>
       <c r="G689" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23049,7 +23049,7 @@
         <v>6.52299976348877</v>
       </c>
       <c r="G690" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -23075,7 +23075,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G691" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -23101,7 +23101,7 @@
         <v>6.95800018310547</v>
       </c>
       <c r="G692" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -23127,7 +23127,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G693" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -23153,7 +23153,7 @@
         <v>6.76900005340576</v>
       </c>
       <c r="G694" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -23179,7 +23179,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G695" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23205,7 +23205,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G696" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23231,7 +23231,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G697" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23257,7 +23257,7 @@
         <v>6.85099983215332</v>
       </c>
       <c r="G698" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23283,7 +23283,7 @@
         <v>6.75799989700317</v>
       </c>
       <c r="G699" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23309,7 +23309,7 @@
         <v>6.73899984359741</v>
       </c>
       <c r="G700" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23335,7 +23335,7 @@
         <v>6.61800003051758</v>
       </c>
       <c r="G701" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23361,7 +23361,7 @@
         <v>6.55700016021729</v>
       </c>
       <c r="G702" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23387,7 +23387,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G703" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23413,7 +23413,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G704" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23439,7 +23439,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G705" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23465,7 +23465,7 @@
         <v>6.30100011825562</v>
       </c>
       <c r="G706" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23491,7 +23491,7 @@
         <v>6.14099979400635</v>
       </c>
       <c r="G707" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23517,7 +23517,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G708" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23543,7 +23543,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G709" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23569,7 +23569,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G710" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23595,7 +23595,7 @@
         <v>5.95300006866455</v>
       </c>
       <c r="G711" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23621,7 +23621,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G712" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23647,7 +23647,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G713" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23673,7 +23673,7 @@
         <v>5.95900011062622</v>
       </c>
       <c r="G714" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23699,7 +23699,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G715" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23725,7 +23725,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G716" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23751,7 +23751,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G717" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23777,7 +23777,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G718" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23803,7 +23803,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G719" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23829,7 +23829,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G720" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23855,7 +23855,7 @@
         <v>6.00899982452393</v>
       </c>
       <c r="G721" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23881,7 +23881,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G722" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23907,7 +23907,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G723" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23933,7 +23933,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G724" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -23959,7 +23959,7 @@
         <v>6.25</v>
       </c>
       <c r="G725" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -23985,7 +23985,7 @@
         <v>6.23899984359741</v>
       </c>
       <c r="G726" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -24011,7 +24011,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G727" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -24037,7 +24037,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G728" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -24063,7 +24063,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G729" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -24089,7 +24089,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G730" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -24115,7 +24115,7 @@
         <v>6.2189998626709</v>
       </c>
       <c r="G731" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -24141,7 +24141,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G732" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -24167,7 +24167,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G733" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24193,7 +24193,7 @@
         <v>6.00299978256226</v>
       </c>
       <c r="G734" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24219,7 +24219,7 @@
         <v>6.03900003433228</v>
       </c>
       <c r="G735" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24245,7 +24245,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G736" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24271,7 +24271,7 @@
         <v>5.95100021362305</v>
       </c>
       <c r="G737" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24297,7 +24297,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G738" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24323,7 +24323,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G739" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24349,7 +24349,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G740" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24375,7 +24375,7 @@
         <v>6.02899980545044</v>
       </c>
       <c r="G741" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24401,7 +24401,7 @@
         <v>6.14300012588501</v>
       </c>
       <c r="G742" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24427,7 +24427,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G743" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24453,7 +24453,7 @@
         <v>6.10699987411499</v>
       </c>
       <c r="G744" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24479,7 +24479,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G745" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24505,7 +24505,7 @@
         <v>5.98299980163574</v>
       </c>
       <c r="G746" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24531,7 +24531,7 @@
         <v>5.88199996948242</v>
       </c>
       <c r="G747" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24557,7 +24557,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G748" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24583,7 +24583,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G749" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24609,7 +24609,7 @@
         <v>5.80700016021729</v>
       </c>
       <c r="G750" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24635,7 +24635,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G751" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24661,7 +24661,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G752" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24687,7 +24687,7 @@
         <v>5.65299987792969</v>
       </c>
       <c r="G753" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24713,7 +24713,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G754" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24739,7 +24739,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G755" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24765,7 +24765,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G756" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24791,7 +24791,7 @@
         <v>5.5</v>
       </c>
       <c r="G757" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24817,7 +24817,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G758" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24843,7 +24843,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G759" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24869,7 +24869,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G760" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24895,7 +24895,7 @@
         <v>5.4229998588562</v>
       </c>
       <c r="G761" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24921,7 +24921,7 @@
         <v>5.30700016021729</v>
       </c>
       <c r="G762" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -24947,7 +24947,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G763" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -24973,7 +24973,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G764" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -24999,7 +24999,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G765" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -25025,7 +25025,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G766" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -25051,7 +25051,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G767" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -25077,7 +25077,7 @@
         <v>5.90899991989136</v>
       </c>
       <c r="G768" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25103,7 +25103,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G769" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -25129,7 +25129,7 @@
         <v>5.91599988937378</v>
       </c>
       <c r="G770" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25155,7 +25155,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G771" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -25181,7 +25181,7 @@
         <v>5.81099987030029</v>
       </c>
       <c r="G772" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -25207,7 +25207,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G773" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25233,7 +25233,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G774" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25259,7 +25259,7 @@
         <v>5.84899997711182</v>
       </c>
       <c r="G775" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25285,7 +25285,7 @@
         <v>5.90199995040894</v>
       </c>
       <c r="G776" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25311,7 +25311,7 @@
         <v>5.83699989318848</v>
       </c>
       <c r="G777" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25337,7 +25337,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G778" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25363,7 +25363,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G779" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25389,7 +25389,7 @@
         <v>5.98899984359741</v>
       </c>
       <c r="G780" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25415,7 +25415,7 @@
         <v>6.14900016784668</v>
       </c>
       <c r="G781" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25441,7 +25441,7 @@
         <v>6.2810001373291</v>
       </c>
       <c r="G782" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25467,7 +25467,7 @@
         <v>6.23799991607666</v>
       </c>
       <c r="G783" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25493,7 +25493,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G784" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25519,7 +25519,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G785" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25545,7 +25545,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G786" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25571,7 +25571,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G787" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25597,7 +25597,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25623,7 +25623,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G789" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25649,7 +25649,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G790" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25675,7 +25675,7 @@
         <v>5.89599990844727</v>
       </c>
       <c r="G791" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25701,7 +25701,7 @@
         <v>6</v>
       </c>
       <c r="G792" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25727,7 +25727,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G793" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25753,7 +25753,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G794" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -25779,7 +25779,7 @@
         <v>6.06699991226196</v>
       </c>
       <c r="G795" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25805,7 +25805,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G796" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25831,7 +25831,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G797" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25857,7 +25857,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G798" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25883,7 +25883,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G799" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25909,7 +25909,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G800" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25935,7 +25935,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G801" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25961,7 +25961,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G802" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -25987,7 +25987,7 @@
         <v>6.31899976730347</v>
       </c>
       <c r="G803" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -26013,7 +26013,7 @@
         <v>6.18699979782104</v>
       </c>
       <c r="G804" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26039,7 +26039,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G805" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26065,7 +26065,7 @@
         <v>6.30800008773804</v>
       </c>
       <c r="G806" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26091,7 +26091,7 @@
         <v>6.36199998855591</v>
       </c>
       <c r="G807" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26117,7 +26117,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G808" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26143,7 +26143,7 @@
         <v>6.65299987792969</v>
       </c>
       <c r="G809" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26169,7 +26169,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G810" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26195,7 +26195,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G811" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26221,7 +26221,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26247,7 +26247,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G813" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26273,7 +26273,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G814" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26299,7 +26299,7 @@
         <v>6.65799999237061</v>
       </c>
       <c r="G815" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26325,7 +26325,7 @@
         <v>6.7039999961853</v>
       </c>
       <c r="G816" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26351,7 +26351,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G817" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26377,7 +26377,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G818" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26403,7 +26403,7 @@
         <v>6.64799976348877</v>
       </c>
       <c r="G819" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26429,7 +26429,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G820" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26455,7 +26455,7 @@
         <v>6.55600023269653</v>
       </c>
       <c r="G821" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26481,7 +26481,7 @@
         <v>6.48299980163574</v>
       </c>
       <c r="G822" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26507,7 +26507,7 @@
         <v>6.42799997329712</v>
       </c>
       <c r="G823" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26533,7 +26533,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G824" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26559,7 +26559,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G825" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26585,7 +26585,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G826" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26611,7 +26611,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G827" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26637,7 +26637,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G828" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26663,7 +26663,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G829" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26689,7 +26689,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G830" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26715,7 +26715,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G831" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26741,7 +26741,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G832" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26767,7 +26767,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G833" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26793,7 +26793,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G834" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26819,7 +26819,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G835" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26845,7 +26845,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G836" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26871,7 +26871,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G837" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26897,7 +26897,7 @@
         <v>6.75</v>
       </c>
       <c r="G838" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26923,7 +26923,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26949,7 +26949,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26975,7 +26975,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G841" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -27001,7 +27001,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G842" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -27027,7 +27027,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G843" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27053,7 +27053,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G844" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27079,7 +27079,7 @@
         <v>6.75</v>
       </c>
       <c r="G845" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27105,7 +27105,7 @@
         <v>6.75</v>
       </c>
       <c r="G846" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -27131,7 +27131,7 @@
         <v>6.75</v>
       </c>
       <c r="G847" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27157,7 +27157,7 @@
         <v>6.75</v>
       </c>
       <c r="G848" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -27183,7 +27183,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G849" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -27209,7 +27209,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G850" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27235,7 +27235,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G851" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27261,7 +27261,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G852" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27287,7 +27287,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G853" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27313,7 +27313,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G854" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27339,7 +27339,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27365,7 +27365,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G856" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27755,7 +27755,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G871" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28327,7 +28327,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G893" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -30953,7 +30953,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G994" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31239,7 +31239,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1005" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -31343,7 +31343,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1009" t="s">
-        <v>684</v>
+        <v>667</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -31499,7 +31499,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1015" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -31863,7 +31863,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1029" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -31915,7 +31915,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1031" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32123,7 +32123,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1039" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -70897,7 +70897,7 @@
     </row>
     <row r="2531">
       <c r="A2531" s="1" t="n">
-        <v>46002.6910416667</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2531" t="n">
         <v>244060</v>
@@ -70918,6 +70918,32 @@
         <v>1559</v>
       </c>
       <c r="H2531" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2532">
+      <c r="A2532" s="1" t="n">
+        <v>46003.6910069444</v>
+      </c>
+      <c r="B2532" t="n">
+        <v>138198</v>
+      </c>
+      <c r="C2532" t="n">
+        <v>3.40499997138977</v>
+      </c>
+      <c r="D2532" t="n">
+        <v>3.35500001907349</v>
+      </c>
+      <c r="E2532" t="n">
+        <v>3.36500000953674</v>
+      </c>
+      <c r="F2532" t="n">
+        <v>3.36500000953674</v>
+      </c>
+      <c r="G2532" t="s">
+        <v>1561</v>
+      </c>
+      <c r="H2532" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -38,667 +38,667 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72976922988892</t>
+    <t xml:space="preserve">4.72976970672607</t>
   </si>
   <si>
     <t xml:space="preserve">IGD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81178760528564</t>
+    <t xml:space="preserve">4.81178855895996</t>
   </si>
   <si>
     <t xml:space="preserve">4.76804494857788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76531076431274</t>
+    <t xml:space="preserve">4.7653112411499</t>
   </si>
   <si>
     <t xml:space="preserve">4.64775037765503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53839111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56573057174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67235612869263</t>
+    <t xml:space="preserve">4.53839159011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56573152542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67235565185547</t>
   </si>
   <si>
     <t xml:space="preserve">4.55206108093262</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33334302902222</t>
+    <t xml:space="preserve">4.33334350585938</t>
   </si>
   <si>
     <t xml:space="preserve">4.16383743286133</t>
   </si>
   <si>
+    <t xml:space="preserve">4.04627752304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60884213447571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88223838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95605564117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03807497024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97519397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785380363464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.813889503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96425819396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07088232040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92051386833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69632840156555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78654932975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45573902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49948263168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69086050987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56783199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63891530036926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755875587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93691778182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87130260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05994701385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00800180435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95332145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98612976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99159741401672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03260707855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05447864532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24038887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21031475067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37435340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33607769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34701251983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33881187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42903232574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52745580673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51105165481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46183967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5711989402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67508983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60947418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54932737350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48371171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34974765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42083072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42356538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2649941444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22398471832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22671937942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33060884475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40169286727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30600452423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36615133285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26772785186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32514238357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29233503341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27046251296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29506778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39895820617676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30873775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38802242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42629909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34428024291992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39075708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3032693862915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49522399902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57292604446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65062808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69091844558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67940664291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69379663467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66213989257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61609411239624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57580327987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63623857498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63048315048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63336086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63911628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56429243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35133028030396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066560745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08368873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95130658149719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97145175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16139125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20168161392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.247727394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27650547027588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03476524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84482598304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633683204651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470378875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01749801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784887313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83619260787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96281886100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05778884887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0923228263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25636053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40313196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33406400680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51824712753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41752147674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45493316650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4837121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45781230926514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53839206695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52975749969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48946762084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51536846160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25923919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38874292373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46644496917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3829870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36572027206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41464328765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35996389389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33694076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29377269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3139181137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19016981124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19880342483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22182655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26211643218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25348281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23046064376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14412355422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19592618942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16714668273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15563535690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11534547805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20743703842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14700174331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1786584854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07505559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9426736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79878115653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77575731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83907055854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74697875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74985671043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85921597480774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82468104362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79590201377869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87936067581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81029152870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76424622535706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72971177101135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71244430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72395539283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84194827079773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735331535339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06354427337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10958957672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11822319030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08656692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03764295578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00310945510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97433042526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91389465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93979549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92540645599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92828416824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89662790298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84770441055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273489952087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75849056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55703997612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64337563514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66927647590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65776491165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58006191253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59732985496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60308599472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63186478614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62610840797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6606433391571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61459732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80453634262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95994067192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07217741012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04339933395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12685680389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13261222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12110137939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36859750747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28226184844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33981895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34845161437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33118486404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30240631103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27075004577637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22758197784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2131929397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18153667449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09807825088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00598621368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10383415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0290093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06929922103882</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.04627704620361</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60884189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88223814964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95605540275574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0380744934082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97519326210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785380363464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81388926506042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96425771713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07088232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92051339149475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69632887840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78654932975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45573902130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49948215484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69086050987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56783199310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63891553878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497233390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755899429321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9369170665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87130260467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05994653701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00800132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95332193374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98612952232361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9915976524353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03260660171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05447816848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24038887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21031427383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37435293197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33607816696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3470139503479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33881235122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42903280258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52745628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51105213165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46184015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57119989395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67509031295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60947465896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54932689666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48371171951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34974765777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42083072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42356491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26499462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25405883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22398519515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22671842575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23765468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33060932159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40169334411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31967306137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30600452423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36615085601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26772832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32514190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29233407974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27046251296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29506778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39895868301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30873775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38802337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42629861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34427976608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39075660705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3032693862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49522399902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57292604446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65062808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67940664291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69379663467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66213941574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61609411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57580423355103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63623857498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63048315048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63336133956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63911581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56429290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35133075714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066560745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08368873596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95130753517151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97145223617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1613917350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20168161392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.247727394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27650594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03476572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755851745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84482645988464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633683204651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15851306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01749849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784839630127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83619260787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96281814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05778837203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0923228263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25636100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40313196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33406352996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5182466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41752099990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45493364334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48371124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45781087875366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53839159011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52975797653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48946809768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51536846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25923871994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38874244689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46644449234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38298654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36571931838989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41464281082153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35996341705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33694076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29377269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31391763687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19017028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19880390167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22182607650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26211595535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25348234176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23046064376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14412355422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19592618942261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16714715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15563583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11534452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20743656158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14700222015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1786584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07505559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94267416000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79878067970276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77575731277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83906984329224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74697923660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74985647201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85921621322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82468128204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79590225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87936091423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81029176712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76424598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72971177101135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71244406700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72395539283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84194779396057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735355377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06354379653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10958957672119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11822319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08656644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03764295578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00310897827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97432994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91389513015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93979597091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92540669441223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92828440666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89662790298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84770393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273489952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75849056243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55704021453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64337515830994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66927623748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65776467323303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58006238937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59732985496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60308599472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63186502456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62610864639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66064310073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61459755897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80453658103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95994067192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07217693328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04339933395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12685680389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13261222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12110137939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36859798431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28226137161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33981895446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34845161437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33118534088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30240678787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27074956893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2275824546814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21319341659546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18153619766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09807825088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00598621368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10383462905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02900981903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06929969787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21894836425781</t>
+    <t xml:space="preserve">4.21894884109497</t>
   </si>
   <si>
     <t xml:space="preserve">4.30816221237183</t>
@@ -713,7 +713,7 @@
     <t xml:space="preserve">4.51249074935913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37723112106323</t>
+    <t xml:space="preserve">4.37723064422607</t>
   </si>
   <si>
     <t xml:space="preserve">4.44342184066772</t>
@@ -722,16 +722,16 @@
     <t xml:space="preserve">4.59307098388672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62472772598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5700478553772</t>
+    <t xml:space="preserve">4.62472724914551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57004833221436</t>
   </si>
   <si>
     <t xml:space="preserve">4.71969699859619</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70818567276001</t>
+    <t xml:space="preserve">4.70818519592285</t>
   </si>
   <si>
     <t xml:space="preserve">4.80315494537354</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">4.70530796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7024302482605</t>
+    <t xml:space="preserve">4.70242977142334</t>
   </si>
   <si>
     <t xml:space="preserve">4.64487266540527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62184906005859</t>
+    <t xml:space="preserve">4.62184953689575</t>
   </si>
   <si>
     <t xml:space="preserve">4.54702472686768</t>
@@ -764,43 +764,43 @@
     <t xml:space="preserve">4.6045823097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71394062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66501665115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74559783935547</t>
+    <t xml:space="preserve">4.71394109725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66501760482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74559736251831</t>
   </si>
   <si>
     <t xml:space="preserve">4.76574325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74847602844238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78301048278809</t>
+    <t xml:space="preserve">4.74847555160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78301000595093</t>
   </si>
   <si>
     <t xml:space="preserve">4.77149868011475</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8233003616333</t>
+    <t xml:space="preserve">4.82329988479614</t>
   </si>
   <si>
     <t xml:space="preserve">4.92690277099609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94992637634277</t>
+    <t xml:space="preserve">4.94992685317993</t>
   </si>
   <si>
     <t xml:space="preserve">4.98446035385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02475070953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05640697479248</t>
+    <t xml:space="preserve">5.02475118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05640745162964</t>
   </si>
   <si>
     <t xml:space="preserve">4.89236879348755</t>
@@ -815,10 +815,10 @@
     <t xml:space="preserve">4.87592363357544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91160106658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93538570404053</t>
+    <t xml:space="preserve">4.91160202026367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93538618087769</t>
   </si>
   <si>
     <t xml:space="preserve">4.89970874786377</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">5.01268720626831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96809053421021</t>
+    <t xml:space="preserve">4.96809101104736</t>
   </si>
   <si>
     <t xml:space="preserve">4.97106409072876</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">4.89376258850098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94727849960327</t>
+    <t xml:space="preserve">4.94727897644043</t>
   </si>
   <si>
     <t xml:space="preserve">4.94133281707764</t>
@@ -848,22 +848,22 @@
     <t xml:space="preserve">4.92944002151489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88781595230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85511159896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79862260818481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77186489105225</t>
+    <t xml:space="preserve">4.88781642913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85511112213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79862308502197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77186441421509</t>
   </si>
   <si>
     <t xml:space="preserve">4.75105285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78673028945923</t>
+    <t xml:space="preserve">4.78673076629639</t>
   </si>
   <si>
     <t xml:space="preserve">4.73321390151978</t>
@@ -875,49 +875,49 @@
     <t xml:space="preserve">4.53401470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58455801010132</t>
+    <t xml:space="preserve">4.584557056427</t>
   </si>
   <si>
     <t xml:space="preserve">4.61726188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70348310470581</t>
+    <t xml:space="preserve">4.70348262786865</t>
   </si>
   <si>
     <t xml:space="preserve">4.72132158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63807439804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72726821899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81646108627319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83132696151733</t>
+    <t xml:space="preserve">4.63807392120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72726726531982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81646156311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83132743835449</t>
   </si>
   <si>
     <t xml:space="preserve">4.93835973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94430541992188</t>
+    <t xml:space="preserve">4.94430589675903</t>
   </si>
   <si>
     <t xml:space="preserve">4.98295640945435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95322513580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90565538406372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84619235992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89078950881958</t>
+    <t xml:space="preserve">4.95322561264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90565490722656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84619283676147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89078903198242</t>
   </si>
   <si>
     <t xml:space="preserve">5.00376796722412</t>
@@ -926,28 +926,28 @@
     <t xml:space="preserve">5.05431127548218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04836511611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99782180786133</t>
+    <t xml:space="preserve">5.04836559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99782133102417</t>
   </si>
   <si>
     <t xml:space="preserve">4.9859299659729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15837049484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12566709518433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11080074310303</t>
+    <t xml:space="preserve">5.15837144851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12566661834717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11080026626587</t>
   </si>
   <si>
     <t xml:space="preserve">5.07512283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0810694694519</t>
+    <t xml:space="preserve">5.08106899261475</t>
   </si>
   <si>
     <t xml:space="preserve">5.09593486785889</t>
@@ -962,25 +962,25 @@
     <t xml:space="preserve">5.02755308151245</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97700977325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05133867263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99484825134277</t>
+    <t xml:space="preserve">4.97701025009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05133819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99484872817993</t>
   </si>
   <si>
     <t xml:space="preserve">5.01566076278687</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06620454788208</t>
+    <t xml:space="preserve">5.06620407104492</t>
   </si>
   <si>
     <t xml:space="preserve">5.13755893707275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2326979637146</t>
+    <t xml:space="preserve">5.23269891738892</t>
   </si>
   <si>
     <t xml:space="preserve">5.2445912361145</t>
@@ -989,13 +989,13 @@
     <t xml:space="preserve">5.23864555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19702196121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17323637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18512868881226</t>
+    <t xml:space="preserve">5.197021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17323684692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1851282119751</t>
   </si>
   <si>
     <t xml:space="preserve">5.20891427993774</t>
@@ -1007,7 +1007,7 @@
     <t xml:space="preserve">5.2475643157959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25053691864014</t>
+    <t xml:space="preserve">5.25053739547729</t>
   </si>
   <si>
     <t xml:space="preserve">5.26242971420288</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">5.14945125579834</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16431665420532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21486043930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35162448883057</t>
+    <t xml:space="preserve">5.16431713104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21485948562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35162353515625</t>
   </si>
   <si>
     <t xml:space="preserve">5.44081687927246</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">5.47054862976074</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46757555007935</t>
+    <t xml:space="preserve">5.46757507324219</t>
   </si>
   <si>
     <t xml:space="preserve">5.55974245071411</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">5.59541988372803</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58947372436523</t>
+    <t xml:space="preserve">5.58947420120239</t>
   </si>
   <si>
     <t xml:space="preserve">5.50325298309326</t>
@@ -1055,31 +1055,31 @@
     <t xml:space="preserve">5.57758140563965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75002241134644</t>
+    <t xml:space="preserve">5.75002288818359</t>
   </si>
   <si>
     <t xml:space="preserve">5.90165233612061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91651821136475</t>
+    <t xml:space="preserve">5.91651773452759</t>
   </si>
   <si>
     <t xml:space="preserve">6.20193815231323</t>
   </si>
   <si>
-    <t xml:space="preserve">6.19004583358765</t>
+    <t xml:space="preserve">6.19004535675049</t>
   </si>
   <si>
     <t xml:space="preserve">6.11274385452271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12463617324829</t>
+    <t xml:space="preserve">6.12463569641113</t>
   </si>
   <si>
     <t xml:space="preserve">6.15436744689941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03544187545776</t>
+    <t xml:space="preserve">6.03544235229492</t>
   </si>
   <si>
     <t xml:space="preserve">5.97597980499268</t>
@@ -1088,22 +1088,22 @@
     <t xml:space="preserve">5.88975954055786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0057110786438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29113149642944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3446478843689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17815256118774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39816427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38627147674561</t>
+    <t xml:space="preserve">6.00571155548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29113101959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34464740753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17815208435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39816379547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38627052307129</t>
   </si>
   <si>
     <t xml:space="preserve">6.33275461196899</t>
@@ -1115,16 +1115,16 @@
     <t xml:space="preserve">6.46951818466187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41600227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40411043167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24356079101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35653924942017</t>
+    <t xml:space="preserve">6.41600275039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40410947799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24356126785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35653972625732</t>
   </si>
   <si>
     <t xml:space="preserve">6.44573402404785</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">6.60033655166626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58844327926636</t>
+    <t xml:space="preserve">6.58844375610352</t>
   </si>
   <si>
     <t xml:space="preserve">6.71926069259644</t>
@@ -1142,13 +1142,13 @@
     <t xml:space="preserve">6.65979862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48141145706177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07111930847168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82732343673706</t>
+    <t xml:space="preserve">6.48141098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07111978530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82732391357422</t>
   </si>
   <si>
     <t xml:space="preserve">5.76786088943481</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">5.80948448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.681640625</t>
+    <t xml:space="preserve">5.68164014816284</t>
   </si>
   <si>
     <t xml:space="preserve">5.73812913894653</t>
@@ -1166,55 +1166,55 @@
     <t xml:space="preserve">5.81840419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73218393325806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.72623634338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85705518722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86300086975098</t>
+    <t xml:space="preserve">5.73218441009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.72623682022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.8570556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86300134658813</t>
   </si>
   <si>
     <t xml:space="preserve">5.95814085006714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92841005325317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76191473007202</t>
+    <t xml:space="preserve">5.92840957641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76191520690918</t>
   </si>
   <si>
     <t xml:space="preserve">5.70839834213257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79759168624878</t>
+    <t xml:space="preserve">5.7975926399231</t>
   </si>
   <si>
     <t xml:space="preserve">5.75596857070923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68461322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69650650024414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66082811355591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50622653961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45865678787231</t>
+    <t xml:space="preserve">5.6846137046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69650602340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66082859039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50622701644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45865631103516</t>
   </si>
   <si>
     <t xml:space="preserve">5.33973121643066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15539741516113</t>
+    <t xml:space="preserve">5.15539646148682</t>
   </si>
   <si>
     <t xml:space="preserve">5.30999994277954</t>
@@ -1226,43 +1226,43 @@
     <t xml:space="preserve">4.91754722595215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00079584121704</t>
+    <t xml:space="preserve">5.00079536437988</t>
   </si>
   <si>
     <t xml:space="preserve">4.86997699737549</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85213851928711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14350509643555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75699901580811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79446029663086</t>
+    <t xml:space="preserve">4.85213899612427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14350557327271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75699853897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7944598197937</t>
   </si>
   <si>
     <t xml:space="preserve">4.70823955535889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58812522888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47752571105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46860551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53104162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66483211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66840028762817</t>
+    <t xml:space="preserve">4.58812475204468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47752618789673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46860599517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53104114532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66483163833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66839933395386</t>
   </si>
   <si>
     <t xml:space="preserve">4.55482625961304</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">4.51260757446289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41211605072021</t>
+    <t xml:space="preserve">4.41211557388306</t>
   </si>
   <si>
     <t xml:space="preserve">4.36811399459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29913806915283</t>
+    <t xml:space="preserve">4.29913759231567</t>
   </si>
   <si>
     <t xml:space="preserve">4.48525619506836</t>
@@ -1292,19 +1292,19 @@
     <t xml:space="preserve">4.4418478012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29378700256348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19210577011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57335996627808</t>
+    <t xml:space="preserve">4.29378652572632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19210529327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57336091995239</t>
   </si>
   <si>
     <t xml:space="preserve">4.65459394454956</t>
   </si>
   <si>
-    <t xml:space="preserve">5.10297584533691</t>
+    <t xml:space="preserve">5.10297536849976</t>
   </si>
   <si>
     <t xml:space="preserve">4.85351896286011</t>
@@ -1313,7 +1313,7 @@
     <t xml:space="preserve">4.95713901519775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14391136169434</t>
+    <t xml:space="preserve">5.14391183853149</t>
   </si>
   <si>
     <t xml:space="preserve">5.34731388092041</t>
@@ -1325,10 +1325,10 @@
     <t xml:space="preserve">5.17781209945679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01278686523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96993160247803</t>
+    <t xml:space="preserve">5.01278734207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96993112564087</t>
   </si>
   <si>
     <t xml:space="preserve">5.05244445800781</t>
@@ -1349,31 +1349,31 @@
     <t xml:space="preserve">5.02621936798096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01470565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08506488800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93539142608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92579793930054</t>
+    <t xml:space="preserve">5.01470613479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0850658416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93539190292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92579746246338</t>
   </si>
   <si>
     <t xml:space="preserve">4.9654541015625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02557992935181</t>
+    <t xml:space="preserve">5.02557945251465</t>
   </si>
   <si>
     <t xml:space="preserve">5.04029130935669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02110242843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11704683303833</t>
+    <t xml:space="preserve">5.02110195159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11704778671265</t>
   </si>
   <si>
     <t xml:space="preserve">5.0594801902771</t>
@@ -1382,22 +1382,22 @@
     <t xml:space="preserve">5.06971406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24497318267822</t>
+    <t xml:space="preserve">5.24497270584106</t>
   </si>
   <si>
     <t xml:space="preserve">5.14135265350342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97888708114624</t>
+    <t xml:space="preserve">4.97888660430908</t>
   </si>
   <si>
     <t xml:space="preserve">4.76461029052734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83496952056885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78124046325684</t>
+    <t xml:space="preserve">4.83497047424316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78124094009399</t>
   </si>
   <si>
     <t xml:space="preserve">4.73326873779297</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">4.66290903091431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5509729385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32710266113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57400035858154</t>
+    <t xml:space="preserve">4.55097341537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32710313796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57399988174438</t>
   </si>
   <si>
     <t xml:space="preserve">4.65267515182495</t>
@@ -1424,7 +1424,7 @@
     <t xml:space="preserve">4.63092708587646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72943019866943</t>
+    <t xml:space="preserve">4.72943067550659</t>
   </si>
   <si>
     <t xml:space="preserve">4.81961822509766</t>
@@ -1436,10 +1436,10 @@
     <t xml:space="preserve">4.68401670455933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58679294586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8741979598999</t>
+    <t xml:space="preserve">4.58679246902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87419843673706</t>
   </si>
   <si>
     <t xml:space="preserve">4.99108505249023</t>
@@ -1454,22 +1454,22 @@
     <t xml:space="preserve">5.03165197372437</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79375267028809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79512739181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7607479095459</t>
+    <t xml:space="preserve">4.79375219345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79512691497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76074838638306</t>
   </si>
   <si>
     <t xml:space="preserve">4.74630975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86113405227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79031372070312</t>
+    <t xml:space="preserve">4.86113452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79031419754028</t>
   </si>
   <si>
     <t xml:space="preserve">4.81300401687622</t>
@@ -1478,79 +1478,79 @@
     <t xml:space="preserve">4.72705793380737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77174997329712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73187065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84532022476196</t>
+    <t xml:space="preserve">4.77174949645996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73187112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8453197479248</t>
   </si>
   <si>
     <t xml:space="preserve">4.78687620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76968717575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91613960266113</t>
+    <t xml:space="preserve">4.76968669891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91614007949829</t>
   </si>
   <si>
     <t xml:space="preserve">4.97802114486694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96770811080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8267560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85013294219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86044645309448</t>
+    <t xml:space="preserve">4.96770763397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82675552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85013246536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86044692993164</t>
   </si>
   <si>
     <t xml:space="preserve">4.89963817596436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93470478057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99177312850952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05434131622314</t>
+    <t xml:space="preserve">4.93470430374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99177265167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05434226989746</t>
   </si>
   <si>
     <t xml:space="preserve">4.96151971817017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97939682006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99246025085449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85838460922241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98489713668823</t>
+    <t xml:space="preserve">4.9793963432312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99245977401733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8583836555481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98489761352539</t>
   </si>
   <si>
     <t xml:space="preserve">4.85219573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90307664871216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97183322906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93882942199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91682720184326</t>
+    <t xml:space="preserve">4.903076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9718337059021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93882989883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91682767868042</t>
   </si>
   <si>
     <t xml:space="preserve">4.83363151550293</t>
@@ -1565,7 +1565,7 @@
     <t xml:space="preserve">4.75043487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67067670822144</t>
+    <t xml:space="preserve">4.67067718505859</t>
   </si>
   <si>
     <t xml:space="preserve">4.58129262924194</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">4.5427885055542</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46303033828735</t>
+    <t xml:space="preserve">4.4630298614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.48228216171265</t>
@@ -1583,16 +1583,16 @@
     <t xml:space="preserve">4.51941061019897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60604524612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59779453277588</t>
+    <t xml:space="preserve">4.60604476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59779405593872</t>
   </si>
   <si>
     <t xml:space="preserve">4.52972412109375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53797483444214</t>
+    <t xml:space="preserve">4.5379753112793</t>
   </si>
   <si>
     <t xml:space="preserve">4.5792293548584</t>
@@ -1604,25 +1604,25 @@
     <t xml:space="preserve">4.57235383987427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55241394042969</t>
+    <t xml:space="preserve">4.55241441726685</t>
   </si>
   <si>
     <t xml:space="preserve">4.50634717941284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51597309112549</t>
+    <t xml:space="preserve">4.51597261428833</t>
   </si>
   <si>
     <t xml:space="preserve">4.49053287506104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52078580856323</t>
+    <t xml:space="preserve">4.52078676223755</t>
   </si>
   <si>
     <t xml:space="preserve">4.518723487854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53041172027588</t>
+    <t xml:space="preserve">4.53041219711304</t>
   </si>
   <si>
     <t xml:space="preserve">4.51047229766846</t>
@@ -1640,16 +1640,16 @@
     <t xml:space="preserve">4.78412628173828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66517639160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65417432785034</t>
+    <t xml:space="preserve">4.6651759147644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65417528152466</t>
   </si>
   <si>
     <t xml:space="preserve">4.70299291610718</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7304949760437</t>
+    <t xml:space="preserve">4.73049545288086</t>
   </si>
   <si>
     <t xml:space="preserve">4.71055555343628</t>
@@ -1658,13 +1658,13 @@
     <t xml:space="preserve">4.64661169052124</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63354778289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55035161972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50840950012207</t>
+    <t xml:space="preserve">4.63354730606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5503511428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50840902328491</t>
   </si>
   <si>
     <t xml:space="preserve">4.41558742523193</t>
@@ -1673,16 +1673,16 @@
     <t xml:space="preserve">4.42727661132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40046119689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33239078521729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2223801612854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20450258255005</t>
+    <t xml:space="preserve">4.40046072006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3323917388916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22237968444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20450305938721</t>
   </si>
   <si>
     <t xml:space="preserve">4.16256093978882</t>
@@ -1691,28 +1691,28 @@
     <t xml:space="preserve">4.06630086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09311628341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98791790008545</t>
+    <t xml:space="preserve">4.09311676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98791766166687</t>
   </si>
   <si>
     <t xml:space="preserve">4.05942487716675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09724187850952</t>
+    <t xml:space="preserve">4.09724140167236</t>
   </si>
   <si>
     <t xml:space="preserve">4.0497989654541</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0532374382019</t>
+    <t xml:space="preserve">4.05323696136475</t>
   </si>
   <si>
     <t xml:space="preserve">4.10480451583862</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09105396270752</t>
+    <t xml:space="preserve">4.09105348587036</t>
   </si>
   <si>
     <t xml:space="preserve">4.088303565979</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">4.13161993026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21962976455688</t>
+    <t xml:space="preserve">4.21962928771973</t>
   </si>
   <si>
     <t xml:space="preserve">4.28563594818115</t>
@@ -1730,7 +1730,7 @@
     <t xml:space="preserve">4.29732465744019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28976154327393</t>
+    <t xml:space="preserve">4.28976106643677</t>
   </si>
   <si>
     <t xml:space="preserve">4.22100496292114</t>
@@ -1739,13 +1739,13 @@
     <t xml:space="preserve">4.15293502807617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36608266830444</t>
+    <t xml:space="preserve">4.36608219146729</t>
   </si>
   <si>
     <t xml:space="preserve">4.27601051330566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22513008117676</t>
+    <t xml:space="preserve">4.2251296043396</t>
   </si>
   <si>
     <t xml:space="preserve">4.1948766708374</t>
@@ -1757,16 +1757,16 @@
     <t xml:space="preserve">4.15224742889404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13505792617798</t>
+    <t xml:space="preserve">4.13505840301514</t>
   </si>
   <si>
     <t xml:space="preserve">4.09174060821533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03260946273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03467226028442</t>
+    <t xml:space="preserve">4.0326099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03467273712158</t>
   </si>
   <si>
     <t xml:space="preserve">4.054612159729</t>
@@ -1778,7 +1778,7 @@
     <t xml:space="preserve">4.2237548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23544311523438</t>
+    <t xml:space="preserve">4.23544359207153</t>
   </si>
   <si>
     <t xml:space="preserve">4.19900226593018</t>
@@ -1790,76 +1790,76 @@
     <t xml:space="preserve">4.1137433052063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04429864883423</t>
+    <t xml:space="preserve">4.04429817199707</t>
   </si>
   <si>
     <t xml:space="preserve">4.02917289733887</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99273061752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99891877174377</t>
+    <t xml:space="preserve">3.99273085594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99891901016235</t>
   </si>
   <si>
     <t xml:space="preserve">3.96316480636597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88684439659119</t>
+    <t xml:space="preserve">3.88684487342834</t>
   </si>
   <si>
     <t xml:space="preserve">3.98241662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90540933609009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87378072738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78164625167847</t>
+    <t xml:space="preserve">3.90540862083435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87378096580505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78164601325989</t>
   </si>
   <si>
     <t xml:space="preserve">3.71013855934143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69501209259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73351573944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72870326042175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64894437789917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70051240921021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83115124702454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990830421448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9934184551239</t>
+    <t xml:space="preserve">3.69501233100891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7335159778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72870278358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64894509315491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70051288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83115172386169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990854263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99341797828674</t>
   </si>
   <si>
     <t xml:space="preserve">3.97829174995422</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06286239624023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.048424243927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06767559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04292345046997</t>
+    <t xml:space="preserve">4.06286287307739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04842376708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06767606735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04292392730713</t>
   </si>
   <si>
     <t xml:space="preserve">3.99548053741455</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">3.95491409301758</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04086112976074</t>
+    <t xml:space="preserve">4.04086065292358</t>
   </si>
   <si>
     <t xml:space="preserve">4.02160882949829</t>
@@ -1880,43 +1880,43 @@
     <t xml:space="preserve">4.01335763931274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97004127502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07180166244507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11786890029907</t>
+    <t xml:space="preserve">3.97004103660583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07180118560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11786842346191</t>
   </si>
   <si>
     <t xml:space="preserve">4.22788000106812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31864023208618</t>
+    <t xml:space="preserve">4.31863975524902</t>
   </si>
   <si>
     <t xml:space="preserve">4.2890739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29044914245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25057029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24919557571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26982259750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26294612884521</t>
+    <t xml:space="preserve">4.29044961929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25056982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24919509887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2698221206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26294660568237</t>
   </si>
   <si>
     <t xml:space="preserve">4.24231958389282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13643264770508</t>
+    <t xml:space="preserve">4.13643312454224</t>
   </si>
   <si>
     <t xml:space="preserve">4.05392456054688</t>
@@ -1928,10 +1928,10 @@
     <t xml:space="preserve">4.0896782875061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13230800628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17149925231934</t>
+    <t xml:space="preserve">4.13230752944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17149972915649</t>
   </si>
   <si>
     <t xml:space="preserve">4.23819398880005</t>
@@ -1943,7 +1943,7 @@
     <t xml:space="preserve">4.2189416885376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21481657028198</t>
+    <t xml:space="preserve">4.21481609344482</t>
   </si>
   <si>
     <t xml:space="preserve">4.16324853897095</t>
@@ -1958,7 +1958,7 @@
     <t xml:space="preserve">4.25400829315186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33720397949219</t>
+    <t xml:space="preserve">4.33720445632935</t>
   </si>
   <si>
     <t xml:space="preserve">4.37433338165283</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">4.57441663742065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47609376907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44171476364136</t>
+    <t xml:space="preserve">4.47609329223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44171571731567</t>
   </si>
   <si>
     <t xml:space="preserve">4.44859075546265</t>
@@ -1988,7 +1988,7 @@
     <t xml:space="preserve">4.60948276519775</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66173791885376</t>
+    <t xml:space="preserve">4.66173839569092</t>
   </si>
   <si>
     <t xml:space="preserve">4.60673236846924</t>
@@ -1997,10 +1997,10 @@
     <t xml:space="preserve">4.57097864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57166624069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50772190093994</t>
+    <t xml:space="preserve">4.5716667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5077223777771</t>
   </si>
   <si>
     <t xml:space="preserve">4.45752906799316</t>
@@ -2012,7 +2012,7 @@
     <t xml:space="preserve">4.46234226226807</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42796421051025</t>
+    <t xml:space="preserve">4.4279637336731</t>
   </si>
   <si>
     <t xml:space="preserve">4.54485082626343</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">4.55860233306885</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58610582351685</t>
+    <t xml:space="preserve">4.58610534667969</t>
   </si>
   <si>
     <t xml:space="preserve">4.45546674728394</t>
@@ -2033,16 +2033,16 @@
     <t xml:space="preserve">4.48296928405762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53109979629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56547784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59985637664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64111089706421</t>
+    <t xml:space="preserve">4.53109931945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56547832489014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59985685348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64111137390137</t>
   </si>
   <si>
     <t xml:space="preserve">4.61360836029053</t>
@@ -2051,16 +2051,16 @@
     <t xml:space="preserve">4.62048387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62735939025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7167444229126</t>
+    <t xml:space="preserve">4.62735986709595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71674394607544</t>
   </si>
   <si>
     <t xml:space="preserve">4.65486288070679</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4967212677002</t>
+    <t xml:space="preserve">4.49672079086304</t>
   </si>
   <si>
     <t xml:space="preserve">4.5522894859314</t>
@@ -2072,19 +2072,19 @@
     <t xml:space="preserve">4.60435819625854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62667274475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69361877441406</t>
+    <t xml:space="preserve">4.62667322158813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6936182975769</t>
   </si>
   <si>
     <t xml:space="preserve">4.73824834823608</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71593379974365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63411140441895</t>
+    <t xml:space="preserve">4.71593427658081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6341118812561</t>
   </si>
   <si>
     <t xml:space="preserve">4.65642690658569</t>
@@ -2102,7 +2102,7 @@
     <t xml:space="preserve">4.56716585159302</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55972719192505</t>
+    <t xml:space="preserve">4.55972766876221</t>
   </si>
   <si>
     <t xml:space="preserve">4.64898777008057</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">4.64155006408691</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5820426940918</t>
+    <t xml:space="preserve">4.58204221725464</t>
   </si>
   <si>
     <t xml:space="preserve">4.52997446060181</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">4.4481520652771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38120651245117</t>
+    <t xml:space="preserve">4.38120603561401</t>
   </si>
   <si>
     <t xml:space="preserve">4.42583703994751</t>
@@ -2135,13 +2135,13 @@
     <t xml:space="preserve">4.35889196395874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32913827896118</t>
+    <t xml:space="preserve">4.32913780212402</t>
   </si>
   <si>
     <t xml:space="preserve">4.32169961929321</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31426095962524</t>
+    <t xml:space="preserve">4.3142614364624</t>
   </si>
   <si>
     <t xml:space="preserve">4.33657646179199</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">4.49278211593628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48534393310547</t>
+    <t xml:space="preserve">4.48534440994263</t>
   </si>
   <si>
     <t xml:space="preserve">4.43327569961548</t>
@@ -2165,7 +2165,7 @@
     <t xml:space="preserve">4.40352153778076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38864469528198</t>
+    <t xml:space="preserve">4.38864517211914</t>
   </si>
   <si>
     <t xml:space="preserve">4.39608335494995</t>
@@ -2180,16 +2180,16 @@
     <t xml:space="preserve">4.20268583297729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19524669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10598611831665</t>
+    <t xml:space="preserve">4.19524717330933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10598659515381</t>
   </si>
   <si>
     <t xml:space="preserve">4.13573980331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01672601699829</t>
+    <t xml:space="preserve">4.01672554016113</t>
   </si>
   <si>
     <t xml:space="preserve">4.0241641998291</t>
@@ -2204,22 +2204,22 @@
     <t xml:space="preserve">3.95721864700317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89771151542664</t>
+    <t xml:space="preserve">3.89771199226379</t>
   </si>
   <si>
     <t xml:space="preserve">3.98697257041931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92002701759338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94234228134155</t>
+    <t xml:space="preserve">3.92002725601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94234204292297</t>
   </si>
   <si>
     <t xml:space="preserve">3.97953391075134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97209572792053</t>
+    <t xml:space="preserve">3.97209548950195</t>
   </si>
   <si>
     <t xml:space="preserve">4.04647922515869</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">4.06879425048828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.098548412323</t>
+    <t xml:space="preserve">4.09854793548584</t>
   </si>
   <si>
     <t xml:space="preserve">4.16549396514893</t>
@@ -2240,7 +2240,7 @@
     <t xml:space="preserve">4.18037033081055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17293214797974</t>
+    <t xml:space="preserve">4.17293167114258</t>
   </si>
   <si>
     <t xml:space="preserve">4.11342525482178</t>
@@ -2255,13 +2255,13 @@
     <t xml:space="preserve">4.15805530548096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03904056549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23243856430054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23987770080566</t>
+    <t xml:space="preserve">4.03904104232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2324390411377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23987722396851</t>
   </si>
   <si>
     <t xml:space="preserve">4.26963090896606</t>
@@ -2285,7 +2285,7 @@
     <t xml:space="preserve">4.28450775146484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41096019744873</t>
+    <t xml:space="preserve">4.41095972061157</t>
   </si>
   <si>
     <t xml:space="preserve">4.44071340560913</t>
@@ -2294,16 +2294,16 @@
     <t xml:space="preserve">4.46302890777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47046661376953</t>
+    <t xml:space="preserve">4.47046709060669</t>
   </si>
   <si>
     <t xml:space="preserve">4.45558977127075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6638650894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74568796157837</t>
+    <t xml:space="preserve">4.66386461257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74568748474121</t>
   </si>
   <si>
     <t xml:space="preserve">4.79031753540039</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">4.68618011474609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08367109298706</t>
+    <t xml:space="preserve">4.0836706161499</t>
   </si>
   <si>
     <t xml:space="preserve">4.06135606765747</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">3.96465730667114</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92746543884277</t>
+    <t xml:space="preserve">3.92746496200562</t>
   </si>
   <si>
     <t xml:space="preserve">3.48116230964661</t>
@@ -2351,31 +2351,31 @@
     <t xml:space="preserve">3.38446378707886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37702488899231</t>
+    <t xml:space="preserve">3.37702512741089</t>
   </si>
   <si>
     <t xml:space="preserve">2.71872854232788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76335883140564</t>
+    <t xml:space="preserve">2.76335859298706</t>
   </si>
   <si>
     <t xml:space="preserve">2.54020714759827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57367968559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70385146141052</t>
+    <t xml:space="preserve">2.57367992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7038516998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.64806365966797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77451610565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70757102966309</t>
+    <t xml:space="preserve">2.77451634407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70757079124451</t>
   </si>
   <si>
     <t xml:space="preserve">2.88609194755554</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">2.826584815979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68525576591492</t>
+    <t xml:space="preserve">2.68525552749634</t>
   </si>
   <si>
     <t xml:space="preserve">2.78939294815063</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">2.80426979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75220131874084</t>
+    <t xml:space="preserve">2.75220108032227</t>
   </si>
   <si>
     <t xml:space="preserve">2.70013236999512</t>
@@ -2414,19 +2414,19 @@
     <t xml:space="preserve">2.73732447624207</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69641304016113</t>
+    <t xml:space="preserve">2.69641327857971</t>
   </si>
   <si>
     <t xml:space="preserve">2.60343337059021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66294026374817</t>
+    <t xml:space="preserve">2.66294050216675</t>
   </si>
   <si>
     <t xml:space="preserve">2.69269394874573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62946796417236</t>
+    <t xml:space="preserve">2.62946772575378</t>
   </si>
   <si>
     <t xml:space="preserve">2.6257483959198</t>
@@ -2435,16 +2435,16 @@
     <t xml:space="preserve">2.64062547683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65550208091736</t>
+    <t xml:space="preserve">2.65550231933594</t>
   </si>
   <si>
     <t xml:space="preserve">2.61459112167358</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60715270042419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63318705558777</t>
+    <t xml:space="preserve">2.60715246200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63318681716919</t>
   </si>
   <si>
     <t xml:space="preserve">2.59227561950684</t>
@@ -2456,7 +2456,7 @@
     <t xml:space="preserve">2.45466589927673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42491245269775</t>
+    <t xml:space="preserve">2.42491221427917</t>
   </si>
   <si>
     <t xml:space="preserve">2.3951587677002</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">2.33937096595764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23523330688477</t>
+    <t xml:space="preserve">2.23523354530334</t>
   </si>
   <si>
     <t xml:space="preserve">2.25754880905151</t>
@@ -2498,16 +2498,16 @@
     <t xml:space="preserve">2.6108717918396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61830997467041</t>
+    <t xml:space="preserve">2.61831021308899</t>
   </si>
   <si>
     <t xml:space="preserve">2.77823519706726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91584539413452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54392671585083</t>
+    <t xml:space="preserve">2.9158456325531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54392647743225</t>
   </si>
   <si>
     <t xml:space="preserve">2.54764556884766</t>
@@ -2522,16 +2522,16 @@
     <t xml:space="preserve">2.52904963493347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51045370101929</t>
+    <t xml:space="preserve">2.51045346260071</t>
   </si>
   <si>
     <t xml:space="preserve">2.58483743667603</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58111834526062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59971404075623</t>
+    <t xml:space="preserve">2.58111810684204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5997142791748</t>
   </si>
   <si>
     <t xml:space="preserve">2.63690614700317</t>
@@ -8359,7 +8359,7 @@
         <v>6.18208885192871</v>
       </c>
       <c r="G125" t="s">
-        <v>113</v>
+        <v>39</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -8385,7 +8385,7 @@
         <v>6.20997905731201</v>
       </c>
       <c r="G126" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8411,7 +8411,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G127" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8437,7 +8437,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G128" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8463,7 +8463,7 @@
         <v>6.71663093566895</v>
       </c>
       <c r="G129" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8489,7 +8489,7 @@
         <v>6.48887014389038</v>
       </c>
       <c r="G130" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -8515,7 +8515,7 @@
         <v>6.24716377258301</v>
       </c>
       <c r="G131" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="H131" t="s">
         <v>9</v>
@@ -8541,7 +8541,7 @@
         <v>6.19603395462036</v>
       </c>
       <c r="G132" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -8567,7 +8567,7 @@
         <v>6.40055418014526</v>
       </c>
       <c r="G133" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8593,7 +8593,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G134" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8619,7 +8619,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G135" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -8671,7 +8671,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G137" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -8697,7 +8697,7 @@
         <v>7.11172723770142</v>
       </c>
       <c r="G138" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8723,7 +8723,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G139" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8749,7 +8749,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G140" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8775,7 +8775,7 @@
         <v>7.13496780395508</v>
       </c>
       <c r="G141" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8801,7 +8801,7 @@
         <v>7.19539403915405</v>
       </c>
       <c r="G142" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8879,7 +8879,7 @@
         <v>7.24187612533569</v>
       </c>
       <c r="G145" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -8905,7 +8905,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G146" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8931,7 +8931,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8957,7 +8957,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G148" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8983,7 +8983,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G149" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -9009,7 +9009,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -9061,7 +9061,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G152" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -9087,7 +9087,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G153" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -9113,7 +9113,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9139,7 +9139,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G155" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9165,7 +9165,7 @@
         <v>7.05130100250244</v>
       </c>
       <c r="G156" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -9217,7 +9217,7 @@
         <v>7.13032007217407</v>
       </c>
       <c r="G158" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9243,7 +9243,7 @@
         <v>7.04200410842896</v>
       </c>
       <c r="G159" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9269,7 +9269,7 @@
         <v>7.0048189163208</v>
       </c>
       <c r="G160" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9295,7 +9295,7 @@
         <v>6.93509578704834</v>
       </c>
       <c r="G161" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9321,7 +9321,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G162" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9347,7 +9347,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G163" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9373,7 +9373,7 @@
         <v>6.78170585632324</v>
       </c>
       <c r="G164" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9399,7 +9399,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G165" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9425,7 +9425,7 @@
         <v>6.88396596908569</v>
       </c>
       <c r="G166" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9451,7 +9451,7 @@
         <v>6.87002086639404</v>
       </c>
       <c r="G167" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9477,7 +9477,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9503,7 +9503,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9529,7 +9529,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G170" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9555,7 +9555,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G171" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9581,7 +9581,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G172" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9607,7 +9607,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9633,7 +9633,7 @@
         <v>6.79565000534058</v>
       </c>
       <c r="G174" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9659,7 +9659,7 @@
         <v>6.69803810119629</v>
       </c>
       <c r="G175" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9711,7 +9711,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9737,7 +9737,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G178" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9763,7 +9763,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G179" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9789,7 +9789,7 @@
         <v>6.242516040802</v>
       </c>
       <c r="G180" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9815,7 +9815,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G181" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -9841,7 +9841,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G182" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9867,7 +9867,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9893,7 +9893,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9919,7 +9919,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9945,7 +9945,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G186" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9971,7 +9971,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G187" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9997,7 +9997,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10023,7 +10023,7 @@
         <v>6.13095903396606</v>
       </c>
       <c r="G189" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -10049,7 +10049,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G190" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -10075,7 +10075,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -10101,7 +10101,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G192" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -10127,7 +10127,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G193" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10153,7 +10153,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G194" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10179,7 +10179,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G195" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10205,7 +10205,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10231,7 +10231,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G197" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10257,7 +10257,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G198" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10283,7 +10283,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10309,7 +10309,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10335,7 +10335,7 @@
         <v>5.99616193771362</v>
       </c>
       <c r="G201" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10361,7 +10361,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G202" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10387,7 +10387,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G203" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10413,7 +10413,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G204" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10439,7 +10439,7 @@
         <v>6.20532989501953</v>
       </c>
       <c r="G205" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10465,7 +10465,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10491,7 +10491,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10517,7 +10517,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G208" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10543,7 +10543,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10569,7 +10569,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G210" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -10595,7 +10595,7 @@
         <v>6.65155601501465</v>
       </c>
       <c r="G211" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10621,7 +10621,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G212" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10647,7 +10647,7 @@
         <v>6.52140712738037</v>
       </c>
       <c r="G213" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10699,7 +10699,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10725,7 +10725,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G216" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10751,7 +10751,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10777,7 +10777,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G218" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10803,7 +10803,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10829,7 +10829,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G220" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10855,7 +10855,7 @@
         <v>6.34477615356445</v>
       </c>
       <c r="G221" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10881,7 +10881,7 @@
         <v>6.29364585876465</v>
       </c>
       <c r="G222" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10907,7 +10907,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G223" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10933,7 +10933,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10959,7 +10959,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10985,7 +10985,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11011,7 +11011,7 @@
         <v>6.07053279876709</v>
       </c>
       <c r="G227" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11037,7 +11037,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G228" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -11063,7 +11063,7 @@
         <v>5.74516010284424</v>
       </c>
       <c r="G229" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -11089,7 +11089,7 @@
         <v>5.88460493087769</v>
       </c>
       <c r="G230" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11115,7 +11115,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11141,7 +11141,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11167,7 +11167,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11193,7 +11193,7 @@
         <v>5.81023406982422</v>
       </c>
       <c r="G234" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11219,7 +11219,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11245,7 +11245,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11271,7 +11271,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11297,7 +11297,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11323,7 +11323,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11349,7 +11349,7 @@
         <v>6.14490413665771</v>
       </c>
       <c r="G240" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11375,7 +11375,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11401,7 +11401,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11427,7 +11427,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G243" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11453,7 +11453,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G244" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11505,7 +11505,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G246" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11583,7 +11583,7 @@
         <v>6.57718515396118</v>
       </c>
       <c r="G249" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11609,7 +11609,7 @@
         <v>6.53070402145386</v>
       </c>
       <c r="G250" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11635,7 +11635,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G251" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11661,7 +11661,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11687,7 +11687,7 @@
         <v>6.67479705810547</v>
       </c>
       <c r="G253" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11713,7 +11713,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G254" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11739,7 +11739,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11765,7 +11765,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11791,7 +11791,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G257" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11817,7 +11817,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G258" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11843,7 +11843,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G259" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11895,7 +11895,7 @@
         <v>7.05594921112061</v>
       </c>
       <c r="G261" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11921,7 +11921,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G262" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -11947,7 +11947,7 @@
         <v>6.91650295257568</v>
       </c>
       <c r="G263" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11973,7 +11973,7 @@
         <v>7.00946712493896</v>
       </c>
       <c r="G264" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11999,7 +11999,7 @@
         <v>7.02341079711914</v>
       </c>
       <c r="G265" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12051,7 +12051,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G267" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12077,7 +12077,7 @@
         <v>6.94903993606567</v>
       </c>
       <c r="G268" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -12155,7 +12155,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G271" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H271" t="s">
         <v>9</v>
@@ -12181,7 +12181,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G272" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12207,7 +12207,7 @@
         <v>6.82818794250488</v>
       </c>
       <c r="G273" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H273" t="s">
         <v>9</v>
@@ -12233,7 +12233,7 @@
         <v>6.80494689941406</v>
       </c>
       <c r="G274" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H274" t="s">
         <v>9</v>
@@ -12259,7 +12259,7 @@
         <v>6.75381708145142</v>
       </c>
       <c r="G275" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H275" t="s">
         <v>9</v>
@@ -12285,7 +12285,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G276" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12311,7 +12311,7 @@
         <v>6.61901903152466</v>
       </c>
       <c r="G277" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H277" t="s">
         <v>9</v>
@@ -12337,7 +12337,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12363,7 +12363,7 @@
         <v>6.47027683258057</v>
       </c>
       <c r="G279" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H279" t="s">
         <v>9</v>
@@ -12389,7 +12389,7 @@
         <v>6.62831592559814</v>
       </c>
       <c r="G280" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H280" t="s">
         <v>9</v>
@@ -12415,7 +12415,7 @@
         <v>6.50746297836304</v>
       </c>
       <c r="G281" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H281" t="s">
         <v>9</v>
@@ -12441,7 +12441,7 @@
         <v>6.57253694534302</v>
       </c>
       <c r="G282" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H282" t="s">
         <v>9</v>
@@ -12467,7 +12467,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G283" t="s">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12493,7 +12493,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G284" t="s">
-        <v>20</v>
+        <v>227</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12519,7 +12519,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12545,7 +12545,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G286" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12623,7 +12623,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G289" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12649,7 +12649,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G290" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12701,7 +12701,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G292" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12727,7 +12727,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G293" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12753,7 +12753,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G294" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12779,7 +12779,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G295" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H295" t="s">
         <v>9</v>
@@ -12805,7 +12805,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G296" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H296" t="s">
         <v>9</v>
@@ -12831,7 +12831,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G297" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12883,7 +12883,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G299" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12935,7 +12935,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G301" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13039,7 +13039,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G305" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -13065,7 +13065,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G306" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -13091,7 +13091,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13117,7 +13117,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G308" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13195,7 +13195,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -70923,7 +70923,7 @@
     </row>
     <row r="2532">
       <c r="A2532" s="1" t="n">
-        <v>46003.6910069444</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2532" t="n">
         <v>138198</v>
@@ -70944,6 +70944,32 @@
         <v>1561</v>
       </c>
       <c r="H2532" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2533">
+      <c r="A2533" s="1" t="n">
+        <v>46006.6910648148</v>
+      </c>
+      <c r="B2533" t="n">
+        <v>191758</v>
+      </c>
+      <c r="C2533" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="D2533" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="E2533" t="n">
+        <v>3.36500000953674</v>
+      </c>
+      <c r="F2533" t="n">
+        <v>3.33999991416931</v>
+      </c>
+      <c r="G2533" t="s">
+        <v>1556</v>
+      </c>
+      <c r="H2533" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1589" uniqueCount="1589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1590" uniqueCount="1590">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">IGD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81178855895996</t>
+    <t xml:space="preserve">4.8117880821228</t>
   </si>
   <si>
     <t xml:space="preserve">4.76804494857788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7653112411499</t>
+    <t xml:space="preserve">4.76531076431274</t>
   </si>
   <si>
     <t xml:space="preserve">4.64775037765503</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">4.53839159011841</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56573152542114</t>
+    <t xml:space="preserve">4.56573104858398</t>
   </si>
   <si>
     <t xml:space="preserve">4.67235565185547</t>
@@ -74,91 +74,91 @@
     <t xml:space="preserve">4.16383743286133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04627752304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60884213447571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88223838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95605564117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03807497024536</t>
+    <t xml:space="preserve">4.04627656936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60884118080139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88223814964294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95605492591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0380744934082</t>
   </si>
   <si>
     <t xml:space="preserve">3.97519397735596</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94785380363464</t>
+    <t xml:space="preserve">3.94785356521606</t>
   </si>
   <si>
     <t xml:space="preserve">3.813889503479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96425819396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07088232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92051386833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69632840156555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78654932975769</t>
+    <t xml:space="preserve">3.96425795555115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07088279724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92051410675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69632887840271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78654956817627</t>
   </si>
   <si>
     <t xml:space="preserve">3.45573902130127</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49948263168335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69086050987244</t>
+    <t xml:space="preserve">3.49948215484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69086074829102</t>
   </si>
   <si>
     <t xml:space="preserve">3.56783199310303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63891530036926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755875587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93691778182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87130260467529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05994701385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00800180435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95332145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98612976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99159741401672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03260707855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05447864532471</t>
+    <t xml:space="preserve">3.63891506195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497281074524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755899429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93691730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87130236625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05994653701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00800085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95332169532776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98612999916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9915976524353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0326075553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05447816848755</t>
   </si>
   <si>
     <t xml:space="preserve">4.24038887023926</t>
@@ -179,22 +179,22 @@
     <t xml:space="preserve">4.33881187438965</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42903232574463</t>
+    <t xml:space="preserve">4.42903280258179</t>
   </si>
   <si>
     <t xml:space="preserve">4.52745580673218</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51105165481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46183967590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5711989402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67508983612061</t>
+    <t xml:space="preserve">4.51105260848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46184015274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57119941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67509031295776</t>
   </si>
   <si>
     <t xml:space="preserve">4.60947418212891</t>
@@ -209,28 +209,28 @@
     <t xml:space="preserve">4.34974765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42083072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42356538772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2649941444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25405883789062</t>
+    <t xml:space="preserve">4.42083024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42356443405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26499509811401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405788421631</t>
   </si>
   <si>
     <t xml:space="preserve">4.22398471832275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22671937942505</t>
+    <t xml:space="preserve">4.22671890258789</t>
   </si>
   <si>
     <t xml:space="preserve">4.23765468597412</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33060884475708</t>
+    <t xml:space="preserve">4.33060932159424</t>
   </si>
   <si>
     <t xml:space="preserve">4.40169286727905</t>
@@ -239,19 +239,19 @@
     <t xml:space="preserve">4.31967353820801</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30600452423096</t>
+    <t xml:space="preserve">4.3060040473938</t>
   </si>
   <si>
     <t xml:space="preserve">4.36615133285522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26772785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32514238357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29233503341675</t>
+    <t xml:space="preserve">4.26772832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32514142990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29233407974243</t>
   </si>
   <si>
     <t xml:space="preserve">4.27046251296997</t>
@@ -260,31 +260,31 @@
     <t xml:space="preserve">4.29506778717041</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39895820617676</t>
+    <t xml:space="preserve">4.39895868301392</t>
   </si>
   <si>
     <t xml:space="preserve">4.30873775482178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38802242279053</t>
+    <t xml:space="preserve">4.38802289962769</t>
   </si>
   <si>
     <t xml:space="preserve">4.42629909515381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34428024291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39075708389282</t>
+    <t xml:space="preserve">4.34427928924561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39075660705566</t>
   </si>
   <si>
     <t xml:space="preserve">4.3032693862915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49522399902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57292604446411</t>
+    <t xml:space="preserve">4.49522352218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57292509078979</t>
   </si>
   <si>
     <t xml:space="preserve">4.65062808990479</t>
@@ -296,34 +296,34 @@
     <t xml:space="preserve">4.67940664291382</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69379663467407</t>
+    <t xml:space="preserve">4.69379615783691</t>
   </si>
   <si>
     <t xml:space="preserve">4.66213989257812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61609411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57580327987671</t>
+    <t xml:space="preserve">4.61609315872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57580280303955</t>
   </si>
   <si>
     <t xml:space="preserve">4.63623857498169</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63048315048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63336086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63911628723145</t>
+    <t xml:space="preserve">4.63048267364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63336133956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6391167640686</t>
   </si>
   <si>
     <t xml:space="preserve">4.56429243087769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35133028030396</t>
+    <t xml:space="preserve">4.35133075714111</t>
   </si>
   <si>
     <t xml:space="preserve">4.06066560745239</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">4.08368873596191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95130658149719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97145175933838</t>
+    <t xml:space="preserve">3.95130681991577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97145247459412</t>
   </si>
   <si>
     <t xml:space="preserve">4.16139125823975</t>
@@ -347,25 +347,25 @@
     <t xml:space="preserve">4.247727394104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27650547027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03476524353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84482598304749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633683204651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15851306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01749801635742</t>
+    <t xml:space="preserve">4.27650594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03476572036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84482622146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633730888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470426559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15851354598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01749849319458</t>
   </si>
   <si>
     <t xml:space="preserve">3.86784887313843</t>
@@ -377,34 +377,31 @@
     <t xml:space="preserve">3.96281886100769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05778884887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0923228263855</t>
+    <t xml:space="preserve">4.05778932571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09232234954834</t>
   </si>
   <si>
     <t xml:space="preserve">4.25636053085327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40313196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33406400680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51824712753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41752147674561</t>
+    <t xml:space="preserve">4.40313243865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33406352996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5182466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41752052307129</t>
   </si>
   <si>
     <t xml:space="preserve">4.45493316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4837121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45781230926514</t>
+    <t xml:space="preserve">4.45781135559082</t>
   </si>
   <si>
     <t xml:space="preserve">4.53839206695557</t>
@@ -413,22 +410,22 @@
     <t xml:space="preserve">4.52975749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48946762084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51536846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25923919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38874292373657</t>
+    <t xml:space="preserve">4.48946809768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51536798477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25923871994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38874244689941</t>
   </si>
   <si>
     <t xml:space="preserve">4.46644496917725</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3829870223999</t>
+    <t xml:space="preserve">4.38298654556274</t>
   </si>
   <si>
     <t xml:space="preserve">4.36572027206421</t>
@@ -443,13 +440,13 @@
     <t xml:space="preserve">4.33694076538086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29377269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3139181137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19016981124878</t>
+    <t xml:space="preserve">4.29377365112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31391763687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19016933441162</t>
   </si>
   <si>
     <t xml:space="preserve">4.19880342483521</t>
@@ -458,13 +455,13 @@
     <t xml:space="preserve">4.22182655334473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26211643218994</t>
+    <t xml:space="preserve">4.2621169090271</t>
   </si>
   <si>
     <t xml:space="preserve">4.25348281860352</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23046064376831</t>
+    <t xml:space="preserve">4.23046016693115</t>
   </si>
   <si>
     <t xml:space="preserve">4.14412355422974</t>
@@ -473,13 +470,13 @@
     <t xml:space="preserve">4.19592618942261</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16714668273926</t>
+    <t xml:space="preserve">4.16714715957642</t>
   </si>
   <si>
     <t xml:space="preserve">4.15563535690308</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11534547805786</t>
+    <t xml:space="preserve">4.1153450012207</t>
   </si>
   <si>
     <t xml:space="preserve">4.20743703842163</t>
@@ -488,40 +485,40 @@
     <t xml:space="preserve">4.14700174331665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1786584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07505559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9426736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79878115653992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77575731277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83907055854797</t>
+    <t xml:space="preserve">4.17865800857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07505512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94267416000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497139930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7987802028656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77575755119324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83907032012939</t>
   </si>
   <si>
     <t xml:space="preserve">3.74697875976562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74985671043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85921597480774</t>
+    <t xml:space="preserve">3.74985647201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85921621322632</t>
   </si>
   <si>
     <t xml:space="preserve">3.82468104362488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79590201377869</t>
+    <t xml:space="preserve">3.79590225219727</t>
   </si>
   <si>
     <t xml:space="preserve">3.87936067581177</t>
@@ -530,25 +527,25 @@
     <t xml:space="preserve">3.81029152870178</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78439116477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76424622535706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72971177101135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71244430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72395539283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84194827079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735331535339</t>
+    <t xml:space="preserve">3.78439164161682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76424646377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72971153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7124445438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72395610809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84194779396057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735283851624</t>
   </si>
   <si>
     <t xml:space="preserve">4.06354427337646</t>
@@ -557,88 +554,88 @@
     <t xml:space="preserve">4.10958957672119</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11822319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08656692504883</t>
+    <t xml:space="preserve">4.11822271347046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08656644821167</t>
   </si>
   <si>
     <t xml:space="preserve">4.03764295578003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00310945510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97433042526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91389465332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93979549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92540645599365</t>
+    <t xml:space="preserve">4.00310897827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97432994842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91389489173889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93979573249817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92540597915649</t>
   </si>
   <si>
     <t xml:space="preserve">3.92828416824341</t>
   </si>
   <si>
-    <t xml:space="preserve">3.89662790298462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84770441055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273489952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75849056243896</t>
+    <t xml:space="preserve">3.89662766456604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84770369529724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273442268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75849032402039</t>
   </si>
   <si>
     <t xml:space="preserve">3.55703997612</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64337563514709</t>
+    <t xml:space="preserve">3.64337515830994</t>
   </si>
   <si>
     <t xml:space="preserve">3.66927647590637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65776491165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58006191253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59732985496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60308599472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63186478614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62610840797424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6606433391571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61459732055664</t>
+    <t xml:space="preserve">3.65776467323303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5800621509552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59732937812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60308575630188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63186407089233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62610864639282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66064310073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61459755897522</t>
   </si>
   <si>
     <t xml:space="preserve">3.80453634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95994067192078</t>
+    <t xml:space="preserve">3.9599404335022</t>
   </si>
   <si>
     <t xml:space="preserve">4.07217741012573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04339933395386</t>
+    <t xml:space="preserve">4.0433988571167</t>
   </si>
   <si>
     <t xml:space="preserve">4.12685680389404</t>
@@ -647,27 +644,30 @@
     <t xml:space="preserve">4.13261222839355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12110137939453</t>
+    <t xml:space="preserve">4.12110185623169</t>
   </si>
   <si>
     <t xml:space="preserve">4.36859750747681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28226184844971</t>
+    <t xml:space="preserve">4.28226137161255</t>
   </si>
   <si>
     <t xml:space="preserve">4.33981895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34845161437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33118486404419</t>
+    <t xml:space="preserve">4.34845209121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33118534088135</t>
   </si>
   <si>
     <t xml:space="preserve">4.30240631103516</t>
   </si>
   <si>
+    <t xml:space="preserve">4.26499462127686</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.27075004577637</t>
   </si>
   <si>
@@ -683,10 +683,10 @@
     <t xml:space="preserve">4.09807825088501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00598621368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10383415222168</t>
+    <t xml:space="preserve">4.00598669052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10383462905884</t>
   </si>
   <si>
     <t xml:space="preserve">4.0290093421936</t>
@@ -698,10 +698,10 @@
     <t xml:space="preserve">4.04627704620361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21894884109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30816221237183</t>
+    <t xml:space="preserve">4.21894788742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30816268920898</t>
   </si>
   <si>
     <t xml:space="preserve">4.14988040924072</t>
@@ -713,49 +713,49 @@
     <t xml:space="preserve">4.51249074935913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37723064422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44342184066772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59307098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62472724914551</t>
+    <t xml:space="preserve">4.37723016738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44342231750488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59307050704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62472772598267</t>
   </si>
   <si>
     <t xml:space="preserve">4.57004833221436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71969699859619</t>
+    <t xml:space="preserve">4.71969652175903</t>
   </si>
   <si>
     <t xml:space="preserve">4.70818519592285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80315494537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73120832443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70530796051025</t>
+    <t xml:space="preserve">4.80315446853638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73120784759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70530843734741</t>
   </si>
   <si>
     <t xml:space="preserve">4.70242977142334</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64487266540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62184953689575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54702472686768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52687978744507</t>
+    <t xml:space="preserve">4.64487218856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62184906005859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54702520370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52687931060791</t>
   </si>
   <si>
     <t xml:space="preserve">4.46068906784058</t>
@@ -767,40 +767,40 @@
     <t xml:space="preserve">4.71394109725952</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66501760482788</t>
+    <t xml:space="preserve">4.66501712799072</t>
   </si>
   <si>
     <t xml:space="preserve">4.74559736251831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76574325561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74847555160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78301000595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77149868011475</t>
+    <t xml:space="preserve">4.76574277877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74847602844238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78301048278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77149820327759</t>
   </si>
   <si>
     <t xml:space="preserve">4.82329988479614</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92690277099609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94992685317993</t>
+    <t xml:space="preserve">4.92690372467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94992637634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.98446035385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02475118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05640745162964</t>
+    <t xml:space="preserve">5.02475070953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0564079284668</t>
   </si>
   <si>
     <t xml:space="preserve">4.89236879348755</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">4.86359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82905578613281</t>
+    <t xml:space="preserve">4.82905626296997</t>
   </si>
   <si>
     <t xml:space="preserve">4.87592363357544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91160202026367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93538618087769</t>
+    <t xml:space="preserve">4.91160154342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93538570404053</t>
   </si>
   <si>
     <t xml:space="preserve">4.89970874786377</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">4.96809101104736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97106409072876</t>
+    <t xml:space="preserve">4.9710636138916</t>
   </si>
   <si>
     <t xml:space="preserve">4.89376258850098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94727897644043</t>
+    <t xml:space="preserve">4.94727849960327</t>
   </si>
   <si>
     <t xml:space="preserve">4.94133281707764</t>
@@ -848,49 +848,49 @@
     <t xml:space="preserve">4.92944002151489</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88781642913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85511112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79862308502197</t>
+    <t xml:space="preserve">4.88781595230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85511159896851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79862213134766</t>
   </si>
   <si>
     <t xml:space="preserve">4.77186441421509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75105285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78673076629639</t>
+    <t xml:space="preserve">4.75105237960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78673028945923</t>
   </si>
   <si>
     <t xml:space="preserve">4.73321390151978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66185903549194</t>
+    <t xml:space="preserve">4.66185855865479</t>
   </si>
   <si>
     <t xml:space="preserve">4.53401470184326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.584557056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61726188659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70348262786865</t>
+    <t xml:space="preserve">4.58455753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61726140975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70348310470581</t>
   </si>
   <si>
     <t xml:space="preserve">4.72132158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63807392120361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72726726531982</t>
+    <t xml:space="preserve">4.63807439804077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72726678848267</t>
   </si>
   <si>
     <t xml:space="preserve">4.81646156311035</t>
@@ -905,49 +905,49 @@
     <t xml:space="preserve">4.94430589675903</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98295640945435</t>
+    <t xml:space="preserve">4.9829568862915</t>
   </si>
   <si>
     <t xml:space="preserve">4.95322561264038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90565490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84619283676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89078903198242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00376796722412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05431127548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04836559295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99782133102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9859299659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15837144851685</t>
+    <t xml:space="preserve">4.90565538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84619235992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89078950881958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00376844406128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05431079864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0483660697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99782085418701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98592948913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15837097167969</t>
   </si>
   <si>
     <t xml:space="preserve">5.12566661834717</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11080026626587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.07512283325195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08106899261475</t>
+    <t xml:space="preserve">5.11080074310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.07512331008911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0810694694519</t>
   </si>
   <si>
     <t xml:space="preserve">5.09593486785889</t>
@@ -956,49 +956,49 @@
     <t xml:space="preserve">5.11377382278442</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03944540023804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02755308151245</t>
+    <t xml:space="preserve">5.0394458770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02755260467529</t>
   </si>
   <si>
     <t xml:space="preserve">4.97701025009155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05133819580078</t>
+    <t xml:space="preserve">5.05133771896362</t>
   </si>
   <si>
     <t xml:space="preserve">4.99484872817993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01566076278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06620407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13755893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23269891738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2445912361145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23864555358887</t>
+    <t xml:space="preserve">5.01566123962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06620454788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1375584602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2326979637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24459075927734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23864603042603</t>
   </si>
   <si>
     <t xml:space="preserve">5.197021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17323684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1851282119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20891427993774</t>
+    <t xml:space="preserve">5.17323637008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18512868881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20891380310059</t>
   </si>
   <si>
     <t xml:space="preserve">5.1940484046936</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">5.25053739547729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26242971420288</t>
+    <t xml:space="preserve">5.26243019104004</t>
   </si>
   <si>
     <t xml:space="preserve">5.14945125579834</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">5.44081687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64893627166748</t>
+    <t xml:space="preserve">5.64893674850464</t>
   </si>
   <si>
     <t xml:space="preserve">5.67866706848145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47054862976074</t>
+    <t xml:space="preserve">5.47054815292358</t>
   </si>
   <si>
     <t xml:space="preserve">5.46757507324219</t>
@@ -1043,52 +1043,52 @@
     <t xml:space="preserve">5.55974245071411</t>
   </si>
   <si>
-    <t xml:space="preserve">5.59541988372803</t>
+    <t xml:space="preserve">5.59541940689087</t>
   </si>
   <si>
     <t xml:space="preserve">5.58947420120239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50325298309326</t>
+    <t xml:space="preserve">5.5032525062561</t>
   </si>
   <si>
     <t xml:space="preserve">5.57758140563965</t>
   </si>
   <si>
-    <t xml:space="preserve">5.75002288818359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90165233612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91651773452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20193815231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19004535675049</t>
+    <t xml:space="preserve">5.75002241134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90165185928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91651821136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20193767547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19004583358765</t>
   </si>
   <si>
     <t xml:space="preserve">6.11274385452271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12463569641113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15436744689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03544235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97597980499268</t>
+    <t xml:space="preserve">6.12463617324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15436792373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03544187545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97598028182983</t>
   </si>
   <si>
     <t xml:space="preserve">5.88975954055786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.00571155548096</t>
+    <t xml:space="preserve">6.0057110786438</t>
   </si>
   <si>
     <t xml:space="preserve">6.29113101959229</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">6.39816379547119</t>
   </si>
   <si>
-    <t xml:space="preserve">6.38627052307129</t>
+    <t xml:space="preserve">6.38627147674561</t>
   </si>
   <si>
     <t xml:space="preserve">6.33275461196899</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">6.43384075164795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46951818466187</t>
+    <t xml:space="preserve">6.46951913833618</t>
   </si>
   <si>
     <t xml:space="preserve">6.41600275039673</t>
@@ -1121,25 +1121,25 @@
     <t xml:space="preserve">6.40410947799683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.24356126785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35653972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44573402404785</t>
+    <t xml:space="preserve">6.24356079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35654020309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44573354721069</t>
   </si>
   <si>
     <t xml:space="preserve">6.60033655166626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58844375610352</t>
+    <t xml:space="preserve">6.58844423294067</t>
   </si>
   <si>
     <t xml:space="preserve">6.71926069259644</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65979862213135</t>
+    <t xml:space="preserve">6.65979814529419</t>
   </si>
   <si>
     <t xml:space="preserve">6.48141098022461</t>
@@ -1157,22 +1157,22 @@
     <t xml:space="preserve">5.80948448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68164014816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73812913894653</t>
+    <t xml:space="preserve">5.68164110183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73812961578369</t>
   </si>
   <si>
     <t xml:space="preserve">5.81840419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73218441009521</t>
+    <t xml:space="preserve">5.73218393325806</t>
   </si>
   <si>
     <t xml:space="preserve">5.72623682022095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8570556640625</t>
+    <t xml:space="preserve">5.85705471038818</t>
   </si>
   <si>
     <t xml:space="preserve">5.86300134658813</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">5.95814085006714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92840957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76191520690918</t>
+    <t xml:space="preserve">5.92841005325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76191473007202</t>
   </si>
   <si>
     <t xml:space="preserve">5.70839834213257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7975926399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75596857070923</t>
+    <t xml:space="preserve">5.79759216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75596904754639</t>
   </si>
   <si>
     <t xml:space="preserve">5.6846137046814</t>
@@ -1208,13 +1208,13 @@
     <t xml:space="preserve">5.50622701644897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45865631103516</t>
+    <t xml:space="preserve">5.45865678787231</t>
   </si>
   <si>
     <t xml:space="preserve">5.33973121643066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15539646148682</t>
+    <t xml:space="preserve">5.15539693832397</t>
   </si>
   <si>
     <t xml:space="preserve">5.30999994277954</t>
@@ -1226,76 +1226,76 @@
     <t xml:space="preserve">4.91754722595215</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00079536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86997699737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85213899612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14350557327271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75699853897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7944598197937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70823955535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58812475204468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47752618789673</t>
+    <t xml:space="preserve">5.00079584121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86997747421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85213851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14350509643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75699901580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79446029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70824003219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58812522888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47752571105957</t>
   </si>
   <si>
     <t xml:space="preserve">4.46860599517822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53104114532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66483163833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66839933395386</t>
+    <t xml:space="preserve">4.53104162216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66483211517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6683988571167</t>
   </si>
   <si>
     <t xml:space="preserve">4.55482625961304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49774217605591</t>
+    <t xml:space="preserve">4.49774265289307</t>
   </si>
   <si>
     <t xml:space="preserve">4.51260757446289</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41211557388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36811399459839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29913759231567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48525619506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46503782272339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4418478012085</t>
+    <t xml:space="preserve">4.41211652755737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36811351776123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29913711547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48525524139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46503829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44184732437134</t>
   </si>
   <si>
     <t xml:space="preserve">4.29378652572632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19210529327393</t>
+    <t xml:space="preserve">4.19210577011108</t>
   </si>
   <si>
     <t xml:space="preserve">4.57336091995239</t>
@@ -1307,13 +1307,13 @@
     <t xml:space="preserve">5.10297536849976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85351896286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95713901519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14391183853149</t>
+    <t xml:space="preserve">4.85351848602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95713949203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14391088485718</t>
   </si>
   <si>
     <t xml:space="preserve">5.34731388092041</t>
@@ -1325,10 +1325,10 @@
     <t xml:space="preserve">5.17781209945679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01278734207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96993112564087</t>
+    <t xml:space="preserve">5.01278686523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96993160247803</t>
   </si>
   <si>
     <t xml:space="preserve">5.05244445800781</t>
@@ -1337,13 +1337,13 @@
     <t xml:space="preserve">4.9891209602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94498586654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03197574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0159854888916</t>
+    <t xml:space="preserve">4.94498634338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03197622299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01598501205444</t>
   </si>
   <si>
     <t xml:space="preserve">5.02621936798096</t>
@@ -1352,16 +1352,16 @@
     <t xml:space="preserve">5.01470613479614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0850658416748</t>
+    <t xml:space="preserve">5.08506536483765</t>
   </si>
   <si>
     <t xml:space="preserve">4.93539190292358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92579746246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9654541015625</t>
+    <t xml:space="preserve">4.92579698562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96545457839966</t>
   </si>
   <si>
     <t xml:space="preserve">5.02557945251465</t>
@@ -1370,10 +1370,10 @@
     <t xml:space="preserve">5.04029130935669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02110195159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11704778671265</t>
+    <t xml:space="preserve">5.02110242843628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11704730987549</t>
   </si>
   <si>
     <t xml:space="preserve">5.0594801902771</t>
@@ -1388,16 +1388,16 @@
     <t xml:space="preserve">5.14135265350342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97888660430908</t>
+    <t xml:space="preserve">4.97888708114624</t>
   </si>
   <si>
     <t xml:space="preserve">4.76461029052734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83497047424316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78124094009399</t>
+    <t xml:space="preserve">4.83496999740601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78124046325684</t>
   </si>
   <si>
     <t xml:space="preserve">4.73326873779297</t>
@@ -1409,13 +1409,13 @@
     <t xml:space="preserve">4.66290903091431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55097341537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32710313796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57399988174438</t>
+    <t xml:space="preserve">4.55097389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32710266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57400035858154</t>
   </si>
   <si>
     <t xml:space="preserve">4.65267515182495</t>
@@ -1436,7 +1436,7 @@
     <t xml:space="preserve">4.68401670455933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58679246902466</t>
+    <t xml:space="preserve">4.58679342269897</t>
   </si>
   <si>
     <t xml:space="preserve">4.87419843673706</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">4.86113452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79031419754028</t>
+    <t xml:space="preserve">4.79031467437744</t>
   </si>
   <si>
     <t xml:space="preserve">4.81300401687622</t>
@@ -1478,19 +1478,19 @@
     <t xml:space="preserve">4.72705793380737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77174949645996</t>
+    <t xml:space="preserve">4.77174997329712</t>
   </si>
   <si>
     <t xml:space="preserve">4.73187112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8453197479248</t>
+    <t xml:space="preserve">4.84532022476196</t>
   </si>
   <si>
     <t xml:space="preserve">4.78687620162964</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76968669891357</t>
+    <t xml:space="preserve">4.76968717575073</t>
   </si>
   <si>
     <t xml:space="preserve">4.91614007949829</t>
@@ -1517,19 +1517,19 @@
     <t xml:space="preserve">4.93470430374146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99177265167236</t>
+    <t xml:space="preserve">4.99177312850952</t>
   </si>
   <si>
     <t xml:space="preserve">5.05434226989746</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96151971817017</t>
+    <t xml:space="preserve">4.96152019500732</t>
   </si>
   <si>
     <t xml:space="preserve">4.9793963432312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99245977401733</t>
+    <t xml:space="preserve">4.99246025085449</t>
   </si>
   <si>
     <t xml:space="preserve">4.8583836555481</t>
@@ -1538,16 +1538,16 @@
     <t xml:space="preserve">4.98489761352539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85219573974609</t>
+    <t xml:space="preserve">4.85219621658325</t>
   </si>
   <si>
     <t xml:space="preserve">4.903076171875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9718337059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93882989883423</t>
+    <t xml:space="preserve">4.97183322906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93883037567139</t>
   </si>
   <si>
     <t xml:space="preserve">4.91682767868042</t>
@@ -1559,19 +1559,19 @@
     <t xml:space="preserve">4.76556205749512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75868606567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75043487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67067718505859</t>
+    <t xml:space="preserve">4.75868654251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75043535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67067670822144</t>
   </si>
   <si>
     <t xml:space="preserve">4.58129262924194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5427885055542</t>
+    <t xml:space="preserve">4.54278802871704</t>
   </si>
   <si>
     <t xml:space="preserve">4.4630298614502</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">4.48228216171265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51941061019897</t>
+    <t xml:space="preserve">4.51941108703613</t>
   </si>
   <si>
     <t xml:space="preserve">4.60604476928711</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">4.52972412109375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5379753112793</t>
+    <t xml:space="preserve">4.53797578811646</t>
   </si>
   <si>
     <t xml:space="preserve">4.5792293548584</t>
@@ -1610,19 +1610,19 @@
     <t xml:space="preserve">4.50634717941284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51597261428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49053287506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52078676223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.518723487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53041219711304</t>
+    <t xml:space="preserve">4.51597309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49053239822388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52078628540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51872301101685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5304126739502</t>
   </si>
   <si>
     <t xml:space="preserve">4.51047229766846</t>
@@ -1634,10 +1634,10 @@
     <t xml:space="preserve">4.485032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47746849060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78412628173828</t>
+    <t xml:space="preserve">4.47746896743774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78412580490112</t>
   </si>
   <si>
     <t xml:space="preserve">4.6651759147644</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">4.65417528152466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70299291610718</t>
+    <t xml:space="preserve">4.70299243927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.73049545288086</t>
@@ -1655,28 +1655,28 @@
     <t xml:space="preserve">4.71055555343628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64661169052124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63354730606079</t>
+    <t xml:space="preserve">4.64661121368408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63354778289795</t>
   </si>
   <si>
     <t xml:space="preserve">4.5503511428833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50840902328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41558742523193</t>
+    <t xml:space="preserve">4.50840950012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41558790206909</t>
   </si>
   <si>
     <t xml:space="preserve">4.42727661132812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40046072006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3323917388916</t>
+    <t xml:space="preserve">4.40046119689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33239126205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.22237968444824</t>
@@ -1700,7 +1700,7 @@
     <t xml:space="preserve">4.05942487716675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09724140167236</t>
+    <t xml:space="preserve">4.09724187850952</t>
   </si>
   <si>
     <t xml:space="preserve">4.0497989654541</t>
@@ -1709,31 +1709,31 @@
     <t xml:space="preserve">4.05323696136475</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10480451583862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09105348587036</t>
+    <t xml:space="preserve">4.10480499267578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0910530090332</t>
   </si>
   <si>
     <t xml:space="preserve">4.088303565979</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13161993026733</t>
+    <t xml:space="preserve">4.13162040710449</t>
   </si>
   <si>
     <t xml:space="preserve">4.21962928771973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28563594818115</t>
+    <t xml:space="preserve">4.28563642501831</t>
   </si>
   <si>
     <t xml:space="preserve">4.29732465744019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28976106643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22100496292114</t>
+    <t xml:space="preserve">4.28976154327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22100448608398</t>
   </si>
   <si>
     <t xml:space="preserve">4.15293502807617</t>
@@ -1748,25 +1748,25 @@
     <t xml:space="preserve">4.2251296043396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1948766708374</t>
+    <t xml:space="preserve">4.19487714767456</t>
   </si>
   <si>
     <t xml:space="preserve">4.12749481201172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15224742889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13505840301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09174060821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0326099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03467273712158</t>
+    <t xml:space="preserve">4.1522479057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13505792617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09174156188965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03260946273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03467226028442</t>
   </si>
   <si>
     <t xml:space="preserve">4.054612159729</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">4.14537143707275</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2237548828125</t>
+    <t xml:space="preserve">4.22375535964966</t>
   </si>
   <si>
     <t xml:space="preserve">4.23544359207153</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">4.04429817199707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02917289733887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99273085594177</t>
+    <t xml:space="preserve">4.02917242050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99273037910461</t>
   </si>
   <si>
     <t xml:space="preserve">3.99891901016235</t>
@@ -1808,10 +1808,10 @@
     <t xml:space="preserve">3.88684487342834</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98241662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90540862083435</t>
+    <t xml:space="preserve">3.982417345047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90540909767151</t>
   </si>
   <si>
     <t xml:space="preserve">3.87378096580505</t>
@@ -1823,22 +1823,22 @@
     <t xml:space="preserve">3.71013855934143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69501233100891</t>
+    <t xml:space="preserve">3.69501209259033</t>
   </si>
   <si>
     <t xml:space="preserve">3.7335159778595</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72870278358459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64894509315491</t>
+    <t xml:space="preserve">3.72870326042175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64894461631775</t>
   </si>
   <si>
     <t xml:space="preserve">3.70051288604736</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83115172386169</t>
+    <t xml:space="preserve">3.83115124702454</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990854263306</t>
@@ -1847,7 +1847,7 @@
     <t xml:space="preserve">3.99341797828674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97829174995422</t>
+    <t xml:space="preserve">3.97829127311707</t>
   </si>
   <si>
     <t xml:space="preserve">4.06286287307739</t>
@@ -1871,7 +1871,7 @@
     <t xml:space="preserve">4.04086065292358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02160882949829</t>
+    <t xml:space="preserve">4.02160835266113</t>
   </si>
   <si>
     <t xml:space="preserve">4.05804967880249</t>
@@ -1892,13 +1892,13 @@
     <t xml:space="preserve">4.22788000106812</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31863975524902</t>
+    <t xml:space="preserve">4.31864023208618</t>
   </si>
   <si>
     <t xml:space="preserve">4.2890739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29044961929321</t>
+    <t xml:space="preserve">4.2904486656189</t>
   </si>
   <si>
     <t xml:space="preserve">4.25056982040405</t>
@@ -1907,19 +1907,19 @@
     <t xml:space="preserve">4.24919509887695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2698221206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26294660568237</t>
+    <t xml:space="preserve">4.26982164382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26294708251953</t>
   </si>
   <si>
     <t xml:space="preserve">4.24231958389282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13643312454224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05392456054688</t>
+    <t xml:space="preserve">4.13643264770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05392503738403</t>
   </si>
   <si>
     <t xml:space="preserve">4.12543249130249</t>
@@ -1928,13 +1928,13 @@
     <t xml:space="preserve">4.0896782875061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13230752944946</t>
+    <t xml:space="preserve">4.13230800628662</t>
   </si>
   <si>
     <t xml:space="preserve">4.17149972915649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23819398880005</t>
+    <t xml:space="preserve">4.23819351196289</t>
   </si>
   <si>
     <t xml:space="preserve">4.22169208526611</t>
@@ -1943,13 +1943,13 @@
     <t xml:space="preserve">4.2189416885376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21481609344482</t>
+    <t xml:space="preserve">4.21481657028198</t>
   </si>
   <si>
     <t xml:space="preserve">4.16324853897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28494882583618</t>
+    <t xml:space="preserve">4.28494834899902</t>
   </si>
   <si>
     <t xml:space="preserve">4.34476757049561</t>
@@ -1964,13 +1964,13 @@
     <t xml:space="preserve">4.37433338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50359678268433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57441663742065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47609329223633</t>
+    <t xml:space="preserve">4.50359630584717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5744161605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47609376907349</t>
   </si>
   <si>
     <t xml:space="preserve">4.44171571731567</t>
@@ -1982,10 +1982,10 @@
     <t xml:space="preserve">4.55653953552246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57785415649414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60948276519775</t>
+    <t xml:space="preserve">4.5778546333313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60948324203491</t>
   </si>
   <si>
     <t xml:space="preserve">4.66173839569092</t>
@@ -1994,13 +1994,13 @@
     <t xml:space="preserve">4.60673236846924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57097864151001</t>
+    <t xml:space="preserve">4.57097911834717</t>
   </si>
   <si>
     <t xml:space="preserve">4.5716667175293</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5077223777771</t>
+    <t xml:space="preserve">4.50772285461426</t>
   </si>
   <si>
     <t xml:space="preserve">4.45752906799316</t>
@@ -2021,7 +2021,7 @@
     <t xml:space="preserve">4.52422380447388</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55860233306885</t>
+    <t xml:space="preserve">4.55860280990601</t>
   </si>
   <si>
     <t xml:space="preserve">4.58610534667969</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">4.48296928405762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53109931945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56547832489014</t>
+    <t xml:space="preserve">4.53109979629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56547784805298</t>
   </si>
   <si>
     <t xml:space="preserve">4.59985685348511</t>
@@ -2054,7 +2054,7 @@
     <t xml:space="preserve">4.62735986709595</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71674394607544</t>
+    <t xml:space="preserve">4.7167444229126</t>
   </si>
   <si>
     <t xml:space="preserve">4.65486288070679</t>
@@ -2063,10 +2063,10 @@
     <t xml:space="preserve">4.49672079086304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5522894859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6117959022522</t>
+    <t xml:space="preserve">4.55228900909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61179637908936</t>
   </si>
   <si>
     <t xml:space="preserve">4.60435819625854</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">4.65642690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58948183059692</t>
+    <t xml:space="preserve">4.58948135375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.51509761810303</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">4.55972766876221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64898777008057</t>
+    <t xml:space="preserve">4.64898824691772</t>
   </si>
   <si>
     <t xml:space="preserve">4.64155006408691</t>
@@ -2135,19 +2135,19 @@
     <t xml:space="preserve">4.35889196395874</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32913780212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32169961929321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3142614364624</t>
+    <t xml:space="preserve">4.32913827896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32170009613037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31426095962524</t>
   </si>
   <si>
     <t xml:space="preserve">4.33657646179199</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59691953659058</t>
+    <t xml:space="preserve">4.59691905975342</t>
   </si>
   <si>
     <t xml:space="preserve">4.50765895843506</t>
@@ -2156,13 +2156,13 @@
     <t xml:space="preserve">4.49278211593628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48534440994263</t>
+    <t xml:space="preserve">4.48534393310547</t>
   </si>
   <si>
     <t xml:space="preserve">4.43327569961548</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40352153778076</t>
+    <t xml:space="preserve">4.40352201461792</t>
   </si>
   <si>
     <t xml:space="preserve">4.38864517211914</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">4.24731588363647</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20268583297729</t>
+    <t xml:space="preserve">4.20268535614014</t>
   </si>
   <si>
     <t xml:space="preserve">4.19524717330933</t>
@@ -2207,10 +2207,10 @@
     <t xml:space="preserve">3.89771199226379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98697257041931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92002725601196</t>
+    <t xml:space="preserve">3.98697209358215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9200267791748</t>
   </si>
   <si>
     <t xml:space="preserve">3.94234204292297</t>
@@ -2222,7 +2222,7 @@
     <t xml:space="preserve">3.97209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04647922515869</t>
+    <t xml:space="preserve">4.04647970199585</t>
   </si>
   <si>
     <t xml:space="preserve">4.06879425048828</t>
@@ -2231,10 +2231,10 @@
     <t xml:space="preserve">4.09854793548584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16549396514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18780851364136</t>
+    <t xml:space="preserve">4.16549348831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18780899047852</t>
   </si>
   <si>
     <t xml:space="preserve">4.18037033081055</t>
@@ -2246,7 +2246,7 @@
     <t xml:space="preserve">4.11342525482178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14317846298218</t>
+    <t xml:space="preserve">4.14317798614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.1283016204834</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">4.15805530548096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03904104232788</t>
+    <t xml:space="preserve">4.03904151916504</t>
   </si>
   <si>
     <t xml:space="preserve">4.2324390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23987722396851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26963090896606</t>
+    <t xml:space="preserve">4.23987674713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26963043212891</t>
   </si>
   <si>
     <t xml:space="preserve">4.30682277679443</t>
@@ -2294,7 +2294,7 @@
     <t xml:space="preserve">4.46302890777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47046709060669</t>
+    <t xml:space="preserve">4.47046756744385</t>
   </si>
   <si>
     <t xml:space="preserve">4.45558977127075</t>
@@ -2324,16 +2324,16 @@
     <t xml:space="preserve">4.67130374908447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70849514007568</t>
+    <t xml:space="preserve">4.70849561691284</t>
   </si>
   <si>
     <t xml:space="preserve">4.72337198257446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68618011474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0836706161499</t>
+    <t xml:space="preserve">4.68618059158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08367109298706</t>
   </si>
   <si>
     <t xml:space="preserve">4.06135606765747</t>
@@ -2345,16 +2345,16 @@
     <t xml:space="preserve">3.92746496200562</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48116230964661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38446378707886</t>
+    <t xml:space="preserve">3.48116254806519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38446354866028</t>
   </si>
   <si>
     <t xml:space="preserve">3.37702512741089</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71872854232788</t>
+    <t xml:space="preserve">2.7187283039093</t>
   </si>
   <si>
     <t xml:space="preserve">2.76335859298706</t>
@@ -2366,7 +2366,7 @@
     <t xml:space="preserve">2.57367992401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7038516998291</t>
+    <t xml:space="preserve">2.70385146141052</t>
   </si>
   <si>
     <t xml:space="preserve">2.64806365966797</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">2.826584815979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68525552749634</t>
+    <t xml:space="preserve">2.68525528907776</t>
   </si>
   <si>
     <t xml:space="preserve">2.78939294815063</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">2.80426979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75220108032227</t>
+    <t xml:space="preserve">2.75220084190369</t>
   </si>
   <si>
     <t xml:space="preserve">2.70013236999512</t>
@@ -2408,16 +2408,16 @@
     <t xml:space="preserve">2.7150092124939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76707768440247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73732447624207</t>
+    <t xml:space="preserve">2.76707792282104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73732423782349</t>
   </si>
   <si>
     <t xml:space="preserve">2.69641327857971</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60343337059021</t>
+    <t xml:space="preserve">2.60343360900879</t>
   </si>
   <si>
     <t xml:space="preserve">2.66294050216675</t>
@@ -2429,7 +2429,7 @@
     <t xml:space="preserve">2.62946772575378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6257483959198</t>
+    <t xml:space="preserve">2.62574863433838</t>
   </si>
   <si>
     <t xml:space="preserve">2.64062547683716</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">2.3951587677002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40259718894958</t>
+    <t xml:space="preserve">2.40259695053101</t>
   </si>
   <si>
     <t xml:space="preserve">2.46954250335693</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">2.33937096595764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23523354530334</t>
+    <t xml:space="preserve">2.23523378372192</t>
   </si>
   <si>
     <t xml:space="preserve">2.25754880905151</t>
@@ -2480,16 +2480,16 @@
     <t xml:space="preserve">2.44722723960876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3840012550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41747403144836</t>
+    <t xml:space="preserve">2.38400101661682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41747379302979</t>
   </si>
   <si>
     <t xml:space="preserve">2.41375470161438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43978905677795</t>
+    <t xml:space="preserve">2.43978881835938</t>
   </si>
   <si>
     <t xml:space="preserve">2.51417303085327</t>
@@ -2498,16 +2498,16 @@
     <t xml:space="preserve">2.6108717918396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61831021308899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77823519706726</t>
+    <t xml:space="preserve">2.61831045150757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77823543548584</t>
   </si>
   <si>
     <t xml:space="preserve">2.9158456325531</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54392647743225</t>
+    <t xml:space="preserve">2.54392623901367</t>
   </si>
   <si>
     <t xml:space="preserve">2.54764556884766</t>
@@ -2534,7 +2534,7 @@
     <t xml:space="preserve">2.5997142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63690614700317</t>
+    <t xml:space="preserve">2.63690638542175</t>
   </si>
   <si>
     <t xml:space="preserve">2.68530678749084</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">2.66147232055664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62969350814819</t>
+    <t xml:space="preserve">2.62969374656677</t>
   </si>
   <si>
     <t xml:space="preserve">2.5740807056427</t>
@@ -2552,10 +2552,10 @@
     <t xml:space="preserve">2.51846814155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46285486221313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45491027832031</t>
+    <t xml:space="preserve">2.46285510063171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45491003990173</t>
   </si>
   <si>
     <t xml:space="preserve">2.42710399627686</t>
@@ -2606,10 +2606,10 @@
     <t xml:space="preserve">2.48668932914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51449537277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48271656036377</t>
+    <t xml:space="preserve">2.5144956111908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48271679878235</t>
   </si>
   <si>
     <t xml:space="preserve">2.43902087211609</t>
@@ -2627,10 +2627,10 @@
     <t xml:space="preserve">2.38340830802917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39532542228699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33176732063293</t>
+    <t xml:space="preserve">2.39532518386841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33176755905151</t>
   </si>
   <si>
     <t xml:space="preserve">2.37149095535278</t>
@@ -2645,22 +2645,22 @@
     <t xml:space="preserve">2.44696545600891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50257849693298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56613612174988</t>
+    <t xml:space="preserve">2.50257873535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5661358833313</t>
   </si>
   <si>
     <t xml:space="preserve">2.52244019508362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30396127700806</t>
+    <t xml:space="preserve">2.30396103858948</t>
   </si>
   <si>
     <t xml:space="preserve">2.28409934043884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30793356895447</t>
+    <t xml:space="preserve">2.30793380737305</t>
   </si>
   <si>
     <t xml:space="preserve">2.28807187080383</t>
@@ -2684,7 +2684,7 @@
     <t xml:space="preserve">1.96631169319153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97822880744934</t>
+    <t xml:space="preserve">1.97822856903076</t>
   </si>
   <si>
     <t xml:space="preserve">1.98220098018646</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">2.08548212051392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09342694282532</t>
+    <t xml:space="preserve">2.09342670440674</t>
   </si>
   <si>
     <t xml:space="preserve">2.0815098285675</t>
@@ -2726,7 +2726,7 @@
     <t xml:space="preserve">2.81242156028748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77269816398621</t>
+    <t xml:space="preserve">2.77269792556763</t>
   </si>
   <si>
     <t xml:space="preserve">2.74091935157776</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">2.86406207084656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84817290306091</t>
+    <t xml:space="preserve">2.84817266464233</t>
   </si>
   <si>
     <t xml:space="preserve">2.85611748695374</t>
@@ -2753,13 +2753,13 @@
     <t xml:space="preserve">2.78461503982544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87200665473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85214495658875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93556427955627</t>
+    <t xml:space="preserve">2.87200689315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85214519500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93556451797485</t>
   </si>
   <si>
     <t xml:space="preserve">2.96337080001831</t>
@@ -2777,13 +2777,13 @@
     <t xml:space="preserve">2.91173028945923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78064274787903</t>
+    <t xml:space="preserve">2.78064298629761</t>
   </si>
   <si>
     <t xml:space="preserve">2.83228325843811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94748139381409</t>
+    <t xml:space="preserve">2.94748163223267</t>
   </si>
   <si>
     <t xml:space="preserve">2.97926020622253</t>
@@ -2798,16 +2798,16 @@
     <t xml:space="preserve">2.8283109664917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90378570556641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93953680992126</t>
+    <t xml:space="preserve">2.90378546714783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93953657150269</t>
   </si>
   <si>
     <t xml:space="preserve">2.9435088634491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95542597770691</t>
+    <t xml:space="preserve">2.95542621612549</t>
   </si>
   <si>
     <t xml:space="preserve">2.97528767585754</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">2.99912190437317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96734285354614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88789629936218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80447673797607</t>
+    <t xml:space="preserve">2.96734309196472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8878960609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80447697639465</t>
   </si>
   <si>
     <t xml:space="preserve">2.82433867454529</t>
@@ -2840,13 +2840,13 @@
     <t xml:space="preserve">2.90775775909424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92364740371704</t>
+    <t xml:space="preserve">2.92364716529846</t>
   </si>
   <si>
     <t xml:space="preserve">2.98323249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02295589447021</t>
+    <t xml:space="preserve">3.02295613288879</t>
   </si>
   <si>
     <t xml:space="preserve">3.04679012298584</t>
@@ -2858,22 +2858,22 @@
     <t xml:space="preserve">3.17787742614746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05473494529724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11829209327698</t>
+    <t xml:space="preserve">3.05473470687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11829233169556</t>
   </si>
   <si>
     <t xml:space="preserve">3.04281759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10637521743774</t>
+    <t xml:space="preserve">3.10637545585632</t>
   </si>
   <si>
     <t xml:space="preserve">3.02692818641663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06665182113647</t>
+    <t xml:space="preserve">3.0666515827179</t>
   </si>
   <si>
     <t xml:space="preserve">3.07062411308289</t>
@@ -2909,22 +2909,22 @@
     <t xml:space="preserve">2.72502994537354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75283646583557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81639385223389</t>
+    <t xml:space="preserve">2.75283622741699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81639409065247</t>
   </si>
   <si>
     <t xml:space="preserve">2.99514961242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15404343605042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0745964050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13815402984619</t>
+    <t xml:space="preserve">3.15404367446899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07459616661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13815426826477</t>
   </si>
   <si>
     <t xml:space="preserve">3.0825412273407</t>
@@ -2945,7 +2945,7 @@
     <t xml:space="preserve">3.25335192680359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26924109458923</t>
+    <t xml:space="preserve">3.26924133300781</t>
   </si>
   <si>
     <t xml:space="preserve">3.30102038383484</t>
@@ -2954,7 +2954,7 @@
     <t xml:space="preserve">3.3288266658783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39635682106018</t>
+    <t xml:space="preserve">3.3963565826416</t>
   </si>
   <si>
     <t xml:space="preserve">3.2732138633728</t>
@@ -2963,25 +2963,25 @@
     <t xml:space="preserve">3.29307556152344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23746275901794</t>
+    <t xml:space="preserve">3.23746252059937</t>
   </si>
   <si>
     <t xml:space="preserve">3.23349046707153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20965600013733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25732421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2056839466095</t>
+    <t xml:space="preserve">3.20965623855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25732445716858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20568370819092</t>
   </si>
   <si>
     <t xml:space="preserve">3.2136287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22554564476013</t>
+    <t xml:space="preserve">3.22554540634155</t>
   </si>
   <si>
     <t xml:space="preserve">3.19773936271667</t>
@@ -2990,7 +2990,7 @@
     <t xml:space="preserve">3.20171165466309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26526927947998</t>
+    <t xml:space="preserve">3.2652690410614</t>
   </si>
   <si>
     <t xml:space="preserve">3.31690979003906</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">3.34471607208252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41224598884583</t>
+    <t xml:space="preserve">3.41224575042725</t>
   </si>
   <si>
     <t xml:space="preserve">3.40827345848083</t>
@@ -3011,25 +3011,25 @@
     <t xml:space="preserve">3.55922269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67044830322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69031047821045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69428253173828</t>
+    <t xml:space="preserve">3.67044854164124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69031023979187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69428277015686</t>
   </si>
   <si>
     <t xml:space="preserve">3.66647601127625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63866972923279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5194993019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45594167709351</t>
+    <t xml:space="preserve">3.63866949081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51949906349182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45594191551208</t>
   </si>
   <si>
     <t xml:space="preserve">3.52347159385681</t>
@@ -3044,13 +3044,13 @@
     <t xml:space="preserve">3.45196914672852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44005227088928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34074378013611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24540758132935</t>
+    <t xml:space="preserve">3.44005250930786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34074354171753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24540734291077</t>
   </si>
   <si>
     <t xml:space="preserve">3.26129674911499</t>
@@ -3059,13 +3059,13 @@
     <t xml:space="preserve">3.33677101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32485413551331</t>
+    <t xml:space="preserve">3.32485437393188</t>
   </si>
   <si>
     <t xml:space="preserve">3.22157311439514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30499243736267</t>
+    <t xml:space="preserve">3.30499267578125</t>
   </si>
   <si>
     <t xml:space="preserve">3.2811586856842</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">3.08651351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18979454040527</t>
+    <t xml:space="preserve">3.18979430198669</t>
   </si>
   <si>
     <t xml:space="preserve">3.24937987327576</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">3.19376683235168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27718591690063</t>
+    <t xml:space="preserve">3.27718615531921</t>
   </si>
   <si>
     <t xml:space="preserve">3.36457800865173</t>
@@ -3095,19 +3095,19 @@
     <t xml:space="preserve">3.37252235412598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24143505096436</t>
+    <t xml:space="preserve">3.24143481254578</t>
   </si>
   <si>
     <t xml:space="preserve">3.15007090568542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1262366771698</t>
+    <t xml:space="preserve">3.12623691558838</t>
   </si>
   <si>
     <t xml:space="preserve">3.09445810317993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0904860496521</t>
+    <t xml:space="preserve">3.09048581123352</t>
   </si>
   <si>
     <t xml:space="preserve">3.16993284225464</t>
@@ -3146,16 +3146,16 @@
     <t xml:space="preserve">3.18184995651245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17390489578247</t>
+    <t xml:space="preserve">3.17390513420105</t>
   </si>
   <si>
     <t xml:space="preserve">3.22951817512512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03884553909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00309419631958</t>
+    <t xml:space="preserve">3.03884530067444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00309443473816</t>
   </si>
   <si>
     <t xml:space="preserve">3.01103901863098</t>
@@ -3173,7 +3173,7 @@
     <t xml:space="preserve">2.92761969566345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79653215408325</t>
+    <t xml:space="preserve">2.79653239250183</t>
   </si>
   <si>
     <t xml:space="preserve">2.87995147705078</t>
@@ -3191,13 +3191,13 @@
     <t xml:space="preserve">3.28513097763062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36060523986816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37649488449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36855006217957</t>
+    <t xml:space="preserve">3.36060547828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37649464607239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36854982376099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53141665458679</t>
@@ -3212,10 +3212,10 @@
     <t xml:space="preserve">3.34868860244751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35663318634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32088208198547</t>
+    <t xml:space="preserve">3.35663294792175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32088184356689</t>
   </si>
   <si>
     <t xml:space="preserve">3.40032911300659</t>
@@ -3233,28 +3233,28 @@
     <t xml:space="preserve">3.48772025108337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47183132171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54333353042603</t>
+    <t xml:space="preserve">3.47183108329773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54333329200745</t>
   </si>
   <si>
     <t xml:space="preserve">3.54730606079102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55127763748169</t>
+    <t xml:space="preserve">3.55127787590027</t>
   </si>
   <si>
     <t xml:space="preserve">3.63072514533997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5910017490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67442107200623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61086320877075</t>
+    <t xml:space="preserve">3.59100151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67442083358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61086344718933</t>
   </si>
   <si>
     <t xml:space="preserve">3.62278032302856</t>
@@ -3263,7 +3263,7 @@
     <t xml:space="preserve">3.67839336395264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6505868434906</t>
+    <t xml:space="preserve">3.65058660507202</t>
   </si>
   <si>
     <t xml:space="preserve">3.61880779266357</t>
@@ -3272,7 +3272,7 @@
     <t xml:space="preserve">3.6346971988678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58702898025513</t>
+    <t xml:space="preserve">3.58702921867371</t>
   </si>
   <si>
     <t xml:space="preserve">3.53936100006104</t>
@@ -4779,6 +4779,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.42499995231628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34500002861023</t>
   </si>
 </sst>
 </file>
@@ -8879,7 +8882,7 @@
         <v>7.24187612533569</v>
       </c>
       <c r="G145" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -8905,7 +8908,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G146" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8931,7 +8934,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8957,7 +8960,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G148" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -8983,7 +8986,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G149" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -9009,7 +9012,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -9061,7 +9064,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G152" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -9087,7 +9090,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G153" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -9113,7 +9116,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9139,7 +9142,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G155" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9165,7 +9168,7 @@
         <v>7.05130100250244</v>
       </c>
       <c r="G156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -9217,7 +9220,7 @@
         <v>7.13032007217407</v>
       </c>
       <c r="G158" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9243,7 +9246,7 @@
         <v>7.04200410842896</v>
       </c>
       <c r="G159" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9269,7 +9272,7 @@
         <v>7.0048189163208</v>
       </c>
       <c r="G160" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9295,7 +9298,7 @@
         <v>6.93509578704834</v>
       </c>
       <c r="G161" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9321,7 +9324,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G162" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9347,7 +9350,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G163" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9373,7 +9376,7 @@
         <v>6.78170585632324</v>
       </c>
       <c r="G164" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9399,7 +9402,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G165" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9425,7 +9428,7 @@
         <v>6.88396596908569</v>
       </c>
       <c r="G166" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9451,7 +9454,7 @@
         <v>6.87002086639404</v>
       </c>
       <c r="G167" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9477,7 +9480,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9503,7 +9506,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9529,7 +9532,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G170" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9555,7 +9558,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G171" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9581,7 +9584,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G172" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9607,7 +9610,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9633,7 +9636,7 @@
         <v>6.79565000534058</v>
       </c>
       <c r="G174" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9659,7 +9662,7 @@
         <v>6.69803810119629</v>
       </c>
       <c r="G175" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9711,7 +9714,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9737,7 +9740,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G178" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9763,7 +9766,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G179" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9789,7 +9792,7 @@
         <v>6.242516040802</v>
       </c>
       <c r="G180" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9841,7 +9844,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G182" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9867,7 +9870,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9893,7 +9896,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9919,7 +9922,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9945,7 +9948,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G186" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9971,7 +9974,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G187" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -9997,7 +10000,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10023,7 +10026,7 @@
         <v>6.13095903396606</v>
       </c>
       <c r="G189" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -10075,7 +10078,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -10127,7 +10130,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G193" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10153,7 +10156,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G194" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10179,7 +10182,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G195" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10205,7 +10208,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10231,7 +10234,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G197" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10257,7 +10260,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G198" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10283,7 +10286,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10309,7 +10312,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10335,7 +10338,7 @@
         <v>5.99616193771362</v>
       </c>
       <c r="G201" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10361,7 +10364,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G202" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10387,7 +10390,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G203" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10413,7 +10416,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G204" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10439,7 +10442,7 @@
         <v>6.20532989501953</v>
       </c>
       <c r="G205" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10465,7 +10468,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10491,7 +10494,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10517,7 +10520,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G208" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10543,7 +10546,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10595,7 +10598,7 @@
         <v>6.65155601501465</v>
       </c>
       <c r="G211" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10621,7 +10624,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G212" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10647,7 +10650,7 @@
         <v>6.52140712738037</v>
       </c>
       <c r="G213" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10699,7 +10702,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10725,7 +10728,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G216" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10751,7 +10754,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10777,7 +10780,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G218" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10803,7 +10806,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10829,7 +10832,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G220" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10855,7 +10858,7 @@
         <v>6.34477615356445</v>
       </c>
       <c r="G221" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10881,7 +10884,7 @@
         <v>6.29364585876465</v>
       </c>
       <c r="G222" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10907,7 +10910,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G223" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10933,7 +10936,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10959,7 +10962,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -10985,7 +10988,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11011,7 +11014,7 @@
         <v>6.07053279876709</v>
       </c>
       <c r="G227" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11037,7 +11040,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G228" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -11063,7 +11066,7 @@
         <v>5.74516010284424</v>
       </c>
       <c r="G229" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -11089,7 +11092,7 @@
         <v>5.88460493087769</v>
       </c>
       <c r="G230" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11115,7 +11118,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11141,7 +11144,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11167,7 +11170,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11193,7 +11196,7 @@
         <v>5.81023406982422</v>
       </c>
       <c r="G234" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11219,7 +11222,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11245,7 +11248,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11271,7 +11274,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11297,7 +11300,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11323,7 +11326,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11349,7 +11352,7 @@
         <v>6.14490413665771</v>
       </c>
       <c r="G240" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11375,7 +11378,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11401,7 +11404,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11427,7 +11430,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G243" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11453,7 +11456,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G244" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11505,7 +11508,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G246" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11583,7 +11586,7 @@
         <v>6.57718515396118</v>
       </c>
       <c r="G249" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11609,7 +11612,7 @@
         <v>6.53070402145386</v>
       </c>
       <c r="G250" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11635,7 +11638,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G251" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11661,7 +11664,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11687,7 +11690,7 @@
         <v>6.67479705810547</v>
       </c>
       <c r="G253" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11713,7 +11716,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G254" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11739,7 +11742,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11765,7 +11768,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11791,7 +11794,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G257" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11817,7 +11820,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G258" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11895,7 +11898,7 @@
         <v>7.05594921112061</v>
       </c>
       <c r="G261" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11947,7 +11950,7 @@
         <v>6.91650295257568</v>
       </c>
       <c r="G263" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11973,7 +11976,7 @@
         <v>7.00946712493896</v>
       </c>
       <c r="G264" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -11999,7 +12002,7 @@
         <v>7.02341079711914</v>
       </c>
       <c r="G265" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12051,7 +12054,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G267" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12077,7 +12080,7 @@
         <v>6.94903993606567</v>
       </c>
       <c r="G268" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -12103,7 +12106,7 @@
         <v>6.88861417770386</v>
       </c>
       <c r="G269" t="s">
-        <v>67</v>
+        <v>217</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -12337,7 +12340,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12519,7 +12522,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12623,7 +12626,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G289" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12649,7 +12652,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G290" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12701,7 +12704,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G292" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12727,7 +12730,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G293" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12753,7 +12756,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G294" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12883,7 +12886,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G299" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12935,7 +12938,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G301" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13039,7 +13042,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G305" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -13065,7 +13068,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G306" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -13091,7 +13094,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13117,7 +13120,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G308" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13195,7 +13198,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -70949,7 +70952,7 @@
     </row>
     <row r="2533">
       <c r="A2533" s="1" t="n">
-        <v>46006.6910648148</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2533" t="n">
         <v>191758</v>
@@ -70970,6 +70973,32 @@
         <v>1556</v>
       </c>
       <c r="H2533" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2534">
+      <c r="A2534" s="1" t="n">
+        <v>46007.6911689815</v>
+      </c>
+      <c r="B2534" t="n">
+        <v>129868</v>
+      </c>
+      <c r="C2534" t="n">
+        <v>3.34999990463257</v>
+      </c>
+      <c r="D2534" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="E2534" t="n">
+        <v>3.3050000667572</v>
+      </c>
+      <c r="F2534" t="n">
+        <v>3.34500002861023</v>
+      </c>
+      <c r="G2534" t="s">
+        <v>1589</v>
+      </c>
+      <c r="H2534" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72977018356323</t>
+    <t xml:space="preserve">4.72976922988892</t>
   </si>
   <si>
     <t xml:space="preserve">IGD.MI</t>
@@ -50,367 +50,367 @@
     <t xml:space="preserve">4.76804494857788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76531076431274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64774990081787</t>
+    <t xml:space="preserve">4.7653112411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64775037765503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53839159011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56573104858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67235565185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55206155776978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33334350585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16383743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04627752304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60884189605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88223791122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95605516433716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03807497024536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97519397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785332679749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.813889503479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96425771713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07088232040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92051386833191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69632816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78654932975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45573902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49948215484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69086098670959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56783199310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63891506195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755970954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93691778182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87130260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05994653701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00800132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95332098007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98612928390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99159741401672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03260707855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05447816848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24038887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21031475067139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37435293197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33607769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34701299667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33881187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42903232574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52745532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51105165481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46184015274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5711989402771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67508983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60947465896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54932737350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4837121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34974718093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42083072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42356538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2649941444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22398471832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22671890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3306097984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40169286727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30600452423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36615133285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26772832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32514190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29233503341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27046251296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29506826400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39895868301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30873823165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38802289962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42629909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34427976608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39075708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30326986312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49522352218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57292604446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65062808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69091892242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67940664291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69379663467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66213989257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61609363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57580327987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63623809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63048315048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63336086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63911581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56429243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35133075714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08368873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95130705833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97145223617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1613917350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20168113708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24772691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27650594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03476476669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755875587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8448269367218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633778572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470378875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784887313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83619260787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96281838417053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05778884887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09232234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25636053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40313243865967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33406352996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51824712753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41752099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45493268966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45781135559082</t>
   </si>
   <si>
     <t xml:space="preserve">4.53839206695557</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56573057174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67235565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55206108093262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33334350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16383790969849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04627704620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60884165763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88223838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95605564117432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03807497024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9751935005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785380363464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81388974189758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96425771713257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07088232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92051434516907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69632887840271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78654932975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45573925971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49948239326477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69086050987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56783127784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63891553878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497257232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755970954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93691778182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87130212783813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05994653701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00800085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95332145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98612976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99159741401672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03260707855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05447864532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24038887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21031427383423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37435293197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33607769012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34701299667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33881187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42903232574463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52745628356934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51105165481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46184015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57119941711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67508983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60947465896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54932737350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48371171951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34974765777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42083072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42356491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2649941444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25405883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22398471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22671842575073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23765468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3306097984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40169286727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31967353820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30600452423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36615133285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26772832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32514190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29233407974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27046203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29506778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39895868301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30873775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38802289962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42629861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34427976608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39075708389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30326986312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49522352218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57292604446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65062808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091892242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67940664291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69379568099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66213941574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61609411239624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57580327987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63623857498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63048315048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63336086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63911628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56429290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35133028030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08368873596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95130705833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97145223617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1613917350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20168113708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24772691726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27650594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03476524353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755875587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84482645988464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633778572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470331192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15851306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01749801635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784887313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83619260787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96281886100769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05778932571411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0923228263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25636053085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40313196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33406352996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51824617385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41752147674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45493316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37435340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45781135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52975797653198</t>
+    <t xml:space="preserve">4.52975749969482</t>
   </si>
   <si>
     <t xml:space="preserve">4.48946762084961</t>
@@ -419,58 +419,58 @@
     <t xml:space="preserve">4.51536846160889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25923871994019</t>
+    <t xml:space="preserve">4.25923919677734</t>
   </si>
   <si>
     <t xml:space="preserve">4.38874292373657</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46644496917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3829870223999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36571979522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41464376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35996389389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33694076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29377269744873</t>
+    <t xml:space="preserve">4.46644449234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38298654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36572027206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41464328765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35996437072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33694124221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29377222061157</t>
   </si>
   <si>
     <t xml:space="preserve">4.3139181137085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19016981124878</t>
+    <t xml:space="preserve">4.19017028808594</t>
   </si>
   <si>
     <t xml:space="preserve">4.19880390167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22182655334473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2621169090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25348281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23045969009399</t>
+    <t xml:space="preserve">4.22182703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26211643218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25348234176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23046064376831</t>
   </si>
   <si>
     <t xml:space="preserve">4.14412403106689</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19592571258545</t>
+    <t xml:space="preserve">4.19592666625977</t>
   </si>
   <si>
     <t xml:space="preserve">4.16714715957642</t>
@@ -485,10 +485,10 @@
     <t xml:space="preserve">4.20743703842163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14700222015381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1786584854126</t>
+    <t xml:space="preserve">4.14700174331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17865896224976</t>
   </si>
   <si>
     <t xml:space="preserve">4.07505559921265</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">3.77575731277466</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83907079696655</t>
+    <t xml:space="preserve">3.83907055854797</t>
   </si>
   <si>
     <t xml:space="preserve">3.74697828292847</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74985671043396</t>
+    <t xml:space="preserve">3.7498562335968</t>
   </si>
   <si>
     <t xml:space="preserve">3.85921597480774</t>
@@ -527,52 +527,52 @@
     <t xml:space="preserve">3.87936067581177</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81029152870178</t>
+    <t xml:space="preserve">3.81029200553894</t>
   </si>
   <si>
     <t xml:space="preserve">3.78439116477966</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76424622535706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72971153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71244478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7239556312561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84194779396057</t>
+    <t xml:space="preserve">3.7642457485199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72971105575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71244430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72395634651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84194827079773</t>
   </si>
   <si>
     <t xml:space="preserve">3.99735331535339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06354379653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10958957672119</t>
+    <t xml:space="preserve">4.06354427337646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10959005355835</t>
   </si>
   <si>
     <t xml:space="preserve">4.11822271347046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08656740188599</t>
+    <t xml:space="preserve">4.08656644821167</t>
   </si>
   <si>
     <t xml:space="preserve">4.03764295578003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00310897827148</t>
+    <t xml:space="preserve">4.00310945510864</t>
   </si>
   <si>
     <t xml:space="preserve">3.97432994842529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91389465332031</t>
+    <t xml:space="preserve">3.91389513015747</t>
   </si>
   <si>
     <t xml:space="preserve">3.93979597091675</t>
@@ -581,19 +581,19 @@
     <t xml:space="preserve">3.92540645599365</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92828464508057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89662742614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84770393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273489952087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75848960876465</t>
+    <t xml:space="preserve">3.92828416824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89662837982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84770441055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273442268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75849008560181</t>
   </si>
   <si>
     <t xml:space="preserve">3.55703997612</t>
@@ -602,34 +602,34 @@
     <t xml:space="preserve">3.64337539672852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66927576065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65776515007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58006238937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59732985496521</t>
+    <t xml:space="preserve">3.66927647590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65776491165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58006167411804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59732961654663</t>
   </si>
   <si>
     <t xml:space="preserve">3.60308575630188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63186430931091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62610793113708</t>
+    <t xml:space="preserve">3.63186454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6261088848114</t>
   </si>
   <si>
     <t xml:space="preserve">3.66064310073853</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61459708213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80453681945801</t>
+    <t xml:space="preserve">3.61459732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80453634262085</t>
   </si>
   <si>
     <t xml:space="preserve">3.95994067192078</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">4.07217741012573</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0433988571167</t>
+    <t xml:space="preserve">4.04339933395386</t>
   </si>
   <si>
     <t xml:space="preserve">4.12685680389404</t>
@@ -647,19 +647,19 @@
     <t xml:space="preserve">4.13261222839355</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12110185623169</t>
+    <t xml:space="preserve">4.12110090255737</t>
   </si>
   <si>
     <t xml:space="preserve">4.36859750747681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28226137161255</t>
+    <t xml:space="preserve">4.28226184844971</t>
   </si>
   <si>
     <t xml:space="preserve">4.33981895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34845209121704</t>
+    <t xml:space="preserve">4.3484525680542</t>
   </si>
   <si>
     <t xml:space="preserve">4.33118534088135</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">4.30240631103516</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27075052261353</t>
+    <t xml:space="preserve">4.27075004577637</t>
   </si>
   <si>
     <t xml:space="preserve">4.22758197784424</t>
@@ -677,31 +677,31 @@
     <t xml:space="preserve">4.2131929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18153715133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09807777404785</t>
+    <t xml:space="preserve">4.18153667449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09807825088501</t>
   </si>
   <si>
     <t xml:space="preserve">4.00598621368408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10383462905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02900981903076</t>
+    <t xml:space="preserve">4.10383415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02901029586792</t>
   </si>
   <si>
     <t xml:space="preserve">4.06929969787598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21894788742065</t>
+    <t xml:space="preserve">4.21894836425781</t>
   </si>
   <si>
     <t xml:space="preserve">4.30816221237183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14988040924072</t>
+    <t xml:space="preserve">4.14987993240356</t>
   </si>
   <si>
     <t xml:space="preserve">4.47220039367676</t>
@@ -710,25 +710,25 @@
     <t xml:space="preserve">4.51249074935913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37723064422607</t>
+    <t xml:space="preserve">4.37723112106323</t>
   </si>
   <si>
     <t xml:space="preserve">4.44342184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59307098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62472724914551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5700478553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71969747543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70818567276001</t>
+    <t xml:space="preserve">4.5930700302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62472772598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57004833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71969699859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70818519592285</t>
   </si>
   <si>
     <t xml:space="preserve">4.80315446853638</t>
@@ -746,19 +746,19 @@
     <t xml:space="preserve">4.64487266540527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62184953689575</t>
+    <t xml:space="preserve">4.62184906005859</t>
   </si>
   <si>
     <t xml:space="preserve">4.54702472686768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52687978744507</t>
+    <t xml:space="preserve">4.52688026428223</t>
   </si>
   <si>
     <t xml:space="preserve">4.46068859100342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60458183288574</t>
+    <t xml:space="preserve">4.6045823097229</t>
   </si>
   <si>
     <t xml:space="preserve">4.71394109725952</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">4.66501712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74559688568115</t>
+    <t xml:space="preserve">4.74559736251831</t>
   </si>
   <si>
     <t xml:space="preserve">4.76574325561523</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">4.78301000595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77149820327759</t>
+    <t xml:space="preserve">4.77149868011475</t>
   </si>
   <si>
     <t xml:space="preserve">4.82329988479614</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">4.98446035385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02475070953369</t>
+    <t xml:space="preserve">5.02475118637085</t>
   </si>
   <si>
     <t xml:space="preserve">5.05640745162964</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">4.89236831665039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86358976364136</t>
+    <t xml:space="preserve">4.86359024047852</t>
   </si>
   <si>
     <t xml:space="preserve">4.82905578613281</t>
@@ -815,43 +815,43 @@
     <t xml:space="preserve">4.91160154342651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93538570404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89970874786377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9205207824707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01268720626831</t>
+    <t xml:space="preserve">4.93538665771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89970827102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92052030563354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01268672943115</t>
   </si>
   <si>
     <t xml:space="preserve">4.96809101104736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97106409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89376211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94727897644043</t>
+    <t xml:space="preserve">4.9710636138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89376306533813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94727849960327</t>
   </si>
   <si>
     <t xml:space="preserve">4.94133281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92943954467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88781595230103</t>
+    <t xml:space="preserve">4.92944002151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88781642913818</t>
   </si>
   <si>
     <t xml:space="preserve">4.85511112213135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79862213134766</t>
+    <t xml:space="preserve">4.79862260818481</t>
   </si>
   <si>
     <t xml:space="preserve">4.77186441421509</t>
@@ -863,25 +863,25 @@
     <t xml:space="preserve">4.78673028945923</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73321390151978</t>
+    <t xml:space="preserve">4.73321437835693</t>
   </si>
   <si>
     <t xml:space="preserve">4.66185855865479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53401470184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.584557056427</t>
+    <t xml:space="preserve">4.5340142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58455753326416</t>
   </si>
   <si>
     <t xml:space="preserve">4.61726188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70348310470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72132110595703</t>
+    <t xml:space="preserve">4.70348262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72132158279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.63807439804077</t>
@@ -893,10 +893,10 @@
     <t xml:space="preserve">4.81646156311035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83132743835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93835973739624</t>
+    <t xml:space="preserve">4.83132696151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9383602142334</t>
   </si>
   <si>
     <t xml:space="preserve">4.94430589675903</t>
@@ -908,7 +908,7 @@
     <t xml:space="preserve">4.95322561264038</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90565538406372</t>
+    <t xml:space="preserve">4.90565490722656</t>
   </si>
   <si>
     <t xml:space="preserve">4.84619283676147</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.00376796722412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05431175231934</t>
+    <t xml:space="preserve">5.05431079864502</t>
   </si>
   <si>
     <t xml:space="preserve">5.04836559295654</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">4.99782180786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9859299659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15837097167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12566661834717</t>
+    <t xml:space="preserve">4.98592948913574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15837144851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12566709518433</t>
   </si>
   <si>
     <t xml:space="preserve">5.11080074310303</t>
@@ -956,10 +956,10 @@
     <t xml:space="preserve">5.03944540023804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02755308151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97701072692871</t>
+    <t xml:space="preserve">5.02755355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97701025009155</t>
   </si>
   <si>
     <t xml:space="preserve">5.05133867263794</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">4.99484872817993</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01566123962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06620359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13755893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23269844055176</t>
+    <t xml:space="preserve">5.01566076278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06620407104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.13755941390991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23269891738892</t>
   </si>
   <si>
     <t xml:space="preserve">5.2445912361145</t>
@@ -986,19 +986,19 @@
     <t xml:space="preserve">5.23864555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19702100753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17323637008667</t>
+    <t xml:space="preserve">5.197021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17323684692383</t>
   </si>
   <si>
     <t xml:space="preserve">5.1851282119751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20891380310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19404888153076</t>
+    <t xml:space="preserve">5.20891427993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1940484046936</t>
   </si>
   <si>
     <t xml:space="preserve">5.2475643157959</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">5.21485948562622</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35162401199341</t>
+    <t xml:space="preserve">5.35162353515625</t>
   </si>
   <si>
     <t xml:space="preserve">5.44081687927246</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">5.6786675453186</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47054862976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46757555007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55974245071411</t>
+    <t xml:space="preserve">5.47054767608643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46757507324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55974292755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.59541940689087</t>
@@ -1049,16 +1049,16 @@
     <t xml:space="preserve">5.50325298309326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57758092880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75002241134644</t>
+    <t xml:space="preserve">5.57758140563965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75002336502075</t>
   </si>
   <si>
     <t xml:space="preserve">5.90165233612061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91651773452759</t>
+    <t xml:space="preserve">5.91651821136475</t>
   </si>
   <si>
     <t xml:space="preserve">6.20193815231323</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">6.19004487991333</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11274337768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12463665008545</t>
+    <t xml:space="preserve">6.11274433135986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12463569641113</t>
   </si>
   <si>
     <t xml:space="preserve">6.15436744689941</t>
@@ -1082,25 +1082,25 @@
     <t xml:space="preserve">5.97597980499268</t>
   </si>
   <si>
-    <t xml:space="preserve">5.8897590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00571155548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.29113101959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3446478843689</t>
+    <t xml:space="preserve">5.88975954055786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00571203231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.29113054275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.34464740753174</t>
   </si>
   <si>
     <t xml:space="preserve">6.17815256118774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39816331863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38627099990845</t>
+    <t xml:space="preserve">6.39816427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38627147674561</t>
   </si>
   <si>
     <t xml:space="preserve">6.33275461196899</t>
@@ -1109,37 +1109,37 @@
     <t xml:space="preserve">6.43384027481079</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46951818466187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41600179672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40410947799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24356174468994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35653972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44573402404785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60033559799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58844423294067</t>
+    <t xml:space="preserve">6.46951913833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41600275039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40410852432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24356031417847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35654020309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44573450088501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60033655166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58844327926636</t>
   </si>
   <si>
     <t xml:space="preserve">6.71926116943359</t>
   </si>
   <si>
-    <t xml:space="preserve">6.65979909896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48141050338745</t>
+    <t xml:space="preserve">6.65979814529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48141098022461</t>
   </si>
   <si>
     <t xml:space="preserve">6.07111978530884</t>
@@ -1148,22 +1148,22 @@
     <t xml:space="preserve">5.82732391357422</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76786041259766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.80948495864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73813009262085</t>
+    <t xml:space="preserve">5.76786088943481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.80948448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68163967132568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73812961578369</t>
   </si>
   <si>
     <t xml:space="preserve">5.81840419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73218393325806</t>
+    <t xml:space="preserve">5.7321834564209</t>
   </si>
   <si>
     <t xml:space="preserve">5.72623682022095</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">5.85705471038818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86300182342529</t>
+    <t xml:space="preserve">5.86300134658813</t>
   </si>
   <si>
     <t xml:space="preserve">5.95814085006714</t>
@@ -1181,31 +1181,31 @@
     <t xml:space="preserve">5.92840957641602</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76191473007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79759216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75596904754639</t>
+    <t xml:space="preserve">5.76191568374634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70839738845825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79759168624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75596857070923</t>
   </si>
   <si>
     <t xml:space="preserve">5.68461418151855</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69650602340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66082906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50622653961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.45865678787231</t>
+    <t xml:space="preserve">5.69650650024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66082859039307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50622701644897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.45865631103516</t>
   </si>
   <si>
     <t xml:space="preserve">5.33973121643066</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">5.15539693832397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30999994277954</t>
+    <t xml:space="preserve">5.3100004196167</t>
   </si>
   <si>
     <t xml:space="preserve">5.03647232055664</t>
@@ -1226,22 +1226,22 @@
     <t xml:space="preserve">5.00079488754272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86997699737549</t>
+    <t xml:space="preserve">4.86997747421265</t>
   </si>
   <si>
     <t xml:space="preserve">4.85213899612427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14350461959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75699853897095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79445934295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70823955535889</t>
+    <t xml:space="preserve">5.14350509643555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75699901580811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79446029663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70823907852173</t>
   </si>
   <si>
     <t xml:space="preserve">4.58812522888184</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">4.66483163833618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66839933395386</t>
+    <t xml:space="preserve">4.66839981079102</t>
   </si>
   <si>
     <t xml:space="preserve">4.55482625961304</t>
@@ -1268,10 +1268,10 @@
     <t xml:space="preserve">4.49774217605591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51260757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41211605072021</t>
+    <t xml:space="preserve">4.51260805130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41211652755737</t>
   </si>
   <si>
     <t xml:space="preserve">4.36811399459839</t>
@@ -1280,16 +1280,16 @@
     <t xml:space="preserve">4.29913806915283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4852557182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46503829956055</t>
+    <t xml:space="preserve">4.48525524139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46503782272339</t>
   </si>
   <si>
     <t xml:space="preserve">4.44184732437134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29378652572632</t>
+    <t xml:space="preserve">4.29378604888916</t>
   </si>
   <si>
     <t xml:space="preserve">4.19210577011108</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">5.34731388092041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28271055221558</t>
+    <t xml:space="preserve">5.28271102905273</t>
   </si>
   <si>
     <t xml:space="preserve">5.17781209945679</t>
@@ -1334,7 +1334,7 @@
     <t xml:space="preserve">4.9891209602356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94498586654663</t>
+    <t xml:space="preserve">4.94498634338379</t>
   </si>
   <si>
     <t xml:space="preserve">5.03197574615479</t>
@@ -1346,10 +1346,10 @@
     <t xml:space="preserve">5.02621936798096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0147066116333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08506536483765</t>
+    <t xml:space="preserve">5.01470613479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08506488800049</t>
   </si>
   <si>
     <t xml:space="preserve">4.93539190292358</t>
@@ -1361,7 +1361,7 @@
     <t xml:space="preserve">4.96545457839966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02557992935181</t>
+    <t xml:space="preserve">5.02557945251465</t>
   </si>
   <si>
     <t xml:space="preserve">5.04029130935669</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">5.05947971343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06971454620361</t>
+    <t xml:space="preserve">5.06971406936646</t>
   </si>
   <si>
     <t xml:space="preserve">5.24497270584106</t>
@@ -1397,25 +1397,25 @@
     <t xml:space="preserve">4.78124046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73326873779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71471929550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66290903091431</t>
+    <t xml:space="preserve">4.73326826095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71471881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66290950775146</t>
   </si>
   <si>
     <t xml:space="preserve">4.55097341537476</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32710266113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5740008354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65267515182495</t>
+    <t xml:space="preserve">4.32710313796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57399988174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65267467498779</t>
   </si>
   <si>
     <t xml:space="preserve">4.63092708587646</t>
@@ -1424,19 +1424,19 @@
     <t xml:space="preserve">4.72943067550659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81961822509766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79403352737427</t>
+    <t xml:space="preserve">4.81961870193481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79403305053711</t>
   </si>
   <si>
     <t xml:space="preserve">4.68401670455933</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58679294586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87419843673706</t>
+    <t xml:space="preserve">4.58679246902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87419891357422</t>
   </si>
   <si>
     <t xml:space="preserve">4.99108505249023</t>
@@ -1454,7 +1454,7 @@
     <t xml:space="preserve">4.79375171661377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79512739181519</t>
+    <t xml:space="preserve">4.79512786865234</t>
   </si>
   <si>
     <t xml:space="preserve">4.76074886322021</t>
@@ -1487,7 +1487,7 @@
     <t xml:space="preserve">4.7868766784668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76968717575073</t>
+    <t xml:space="preserve">4.76968669891357</t>
   </si>
   <si>
     <t xml:space="preserve">4.91614007949829</t>
@@ -1508,13 +1508,13 @@
     <t xml:space="preserve">4.86044692993164</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89963817596436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93470430374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99177312850952</t>
+    <t xml:space="preserve">4.8996376991272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93470478057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99177265167236</t>
   </si>
   <si>
     <t xml:space="preserve">5.0543417930603</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">4.97939682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99246025085449</t>
+    <t xml:space="preserve">4.99246072769165</t>
   </si>
   <si>
     <t xml:space="preserve">4.8583836555481</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">4.98489761352539</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85219669342041</t>
+    <t xml:space="preserve">4.85219621658325</t>
   </si>
   <si>
     <t xml:space="preserve">4.903076171875</t>
@@ -1550,19 +1550,19 @@
     <t xml:space="preserve">4.91682720184326</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83363151550293</t>
+    <t xml:space="preserve">4.83363199234009</t>
   </si>
   <si>
     <t xml:space="preserve">4.76556158065796</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75868654251099</t>
+    <t xml:space="preserve">4.75868606567383</t>
   </si>
   <si>
     <t xml:space="preserve">4.75043487548828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67067670822144</t>
+    <t xml:space="preserve">4.67067623138428</t>
   </si>
   <si>
     <t xml:space="preserve">4.58129215240479</t>
@@ -1589,7 +1589,7 @@
     <t xml:space="preserve">4.52972459793091</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5379753112793</t>
+    <t xml:space="preserve">4.53797483444214</t>
   </si>
   <si>
     <t xml:space="preserve">4.57922983169556</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">4.52078580856323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51872301101685</t>
+    <t xml:space="preserve">4.518723487854</t>
   </si>
   <si>
     <t xml:space="preserve">4.53041219711304</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">4.485032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4774694442749</t>
+    <t xml:space="preserve">4.47746896743774</t>
   </si>
   <si>
     <t xml:space="preserve">4.78412580490112</t>
@@ -1643,10 +1643,10 @@
     <t xml:space="preserve">4.65417528152466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70299243927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73049592971802</t>
+    <t xml:space="preserve">4.70299291610718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73049545288086</t>
   </si>
   <si>
     <t xml:space="preserve">4.71055555343628</t>
@@ -1670,10 +1670,10 @@
     <t xml:space="preserve">4.42727613449097</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40046072006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3323917388916</t>
+    <t xml:space="preserve">4.40046119689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33239126205444</t>
   </si>
   <si>
     <t xml:space="preserve">4.2223801612854</t>
@@ -1682,7 +1682,7 @@
     <t xml:space="preserve">4.20450305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16256093978882</t>
+    <t xml:space="preserve">4.16256141662598</t>
   </si>
   <si>
     <t xml:space="preserve">4.0663013458252</t>
@@ -1700,13 +1700,13 @@
     <t xml:space="preserve">4.09724187850952</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04979944229126</t>
+    <t xml:space="preserve">4.0497989654541</t>
   </si>
   <si>
     <t xml:space="preserve">4.05323696136475</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10480451583862</t>
+    <t xml:space="preserve">4.10480499267578</t>
   </si>
   <si>
     <t xml:space="preserve">4.09105348587036</t>
@@ -1721,7 +1721,7 @@
     <t xml:space="preserve">4.21962928771973</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28563594818115</t>
+    <t xml:space="preserve">4.28563642501831</t>
   </si>
   <si>
     <t xml:space="preserve">4.29732513427734</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">4.22100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15293502807617</t>
+    <t xml:space="preserve">4.15293550491333</t>
   </si>
   <si>
     <t xml:space="preserve">4.36608171463013</t>
@@ -1745,7 +1745,7 @@
     <t xml:space="preserve">4.22513008117676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19487714767456</t>
+    <t xml:space="preserve">4.1948766708374</t>
   </si>
   <si>
     <t xml:space="preserve">4.12749433517456</t>
@@ -1754,7 +1754,7 @@
     <t xml:space="preserve">4.15224742889404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13505887985229</t>
+    <t xml:space="preserve">4.13505840301514</t>
   </si>
   <si>
     <t xml:space="preserve">4.09174108505249</t>
@@ -1763,7 +1763,7 @@
     <t xml:space="preserve">4.03260946273804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03467226028442</t>
+    <t xml:space="preserve">4.03467273712158</t>
   </si>
   <si>
     <t xml:space="preserve">4.05461168289185</t>
@@ -1781,7 +1781,7 @@
     <t xml:space="preserve">4.19900226593018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1886887550354</t>
+    <t xml:space="preserve">4.18868923187256</t>
   </si>
   <si>
     <t xml:space="preserve">4.1137433052063</t>
@@ -1793,10 +1793,10 @@
     <t xml:space="preserve">4.02917242050171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99273037910461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99891901016235</t>
+    <t xml:space="preserve">3.99273085594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9989185333252</t>
   </si>
   <si>
     <t xml:space="preserve">3.96316480636597</t>
@@ -1805,25 +1805,25 @@
     <t xml:space="preserve">3.88684439659119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.982417345047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90540957450867</t>
+    <t xml:space="preserve">3.98241710662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90540909767151</t>
   </si>
   <si>
     <t xml:space="preserve">3.8737804889679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78164649009705</t>
+    <t xml:space="preserve">3.78164601325989</t>
   </si>
   <si>
     <t xml:space="preserve">3.71013832092285</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69501209259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73351573944092</t>
+    <t xml:space="preserve">3.69501233100891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7335159778595</t>
   </si>
   <si>
     <t xml:space="preserve">3.72870326042175</t>
@@ -1832,31 +1832,31 @@
     <t xml:space="preserve">3.64894485473633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70051264762878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83115172386169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990854263306</t>
+    <t xml:space="preserve">3.70051288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83115124702454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8999080657959</t>
   </si>
   <si>
     <t xml:space="preserve">3.9934184551239</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97829127311707</t>
+    <t xml:space="preserve">3.97829174995422</t>
   </si>
   <si>
     <t xml:space="preserve">4.06286287307739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.048424243927</t>
+    <t xml:space="preserve">4.04842376708984</t>
   </si>
   <si>
     <t xml:space="preserve">4.06767606735229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04292392730713</t>
+    <t xml:space="preserve">4.04292345046997</t>
   </si>
   <si>
     <t xml:space="preserve">3.99548101425171</t>
@@ -1883,10 +1883,10 @@
     <t xml:space="preserve">4.07180118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11786794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22788000106812</t>
+    <t xml:space="preserve">4.11786842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22788047790527</t>
   </si>
   <si>
     <t xml:space="preserve">4.31864023208618</t>
@@ -1901,7 +1901,7 @@
     <t xml:space="preserve">4.25057029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24919462203979</t>
+    <t xml:space="preserve">4.24919509887695</t>
   </si>
   <si>
     <t xml:space="preserve">4.2698221206665</t>
@@ -1940,10 +1940,10 @@
     <t xml:space="preserve">4.2189416885376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21481609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16324853897095</t>
+    <t xml:space="preserve">4.21481657028198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16324806213379</t>
   </si>
   <si>
     <t xml:space="preserve">4.28494882583618</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">4.37433338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50359678268433</t>
+    <t xml:space="preserve">4.50359630584717</t>
   </si>
   <si>
     <t xml:space="preserve">4.57441663742065</t>
@@ -1982,7 +1982,7 @@
     <t xml:space="preserve">4.5778546333313</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6094822883606</t>
+    <t xml:space="preserve">4.60948276519775</t>
   </si>
   <si>
     <t xml:space="preserve">4.66173839569092</t>
@@ -1991,7 +1991,7 @@
     <t xml:space="preserve">4.6067328453064</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57097911834717</t>
+    <t xml:space="preserve">4.57097864151001</t>
   </si>
   <si>
     <t xml:space="preserve">4.5716667175293</t>
@@ -2012,13 +2012,13 @@
     <t xml:space="preserve">4.42796421051025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54485130310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52422332763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55860233306885</t>
+    <t xml:space="preserve">4.54485082626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52422380447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55860280990601</t>
   </si>
   <si>
     <t xml:space="preserve">4.58610534667969</t>
@@ -2045,7 +2045,7 @@
     <t xml:space="preserve">4.61360836029053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62048435211182</t>
+    <t xml:space="preserve">4.62048387527466</t>
   </si>
   <si>
     <t xml:space="preserve">4.62735986709595</t>
@@ -2072,7 +2072,7 @@
     <t xml:space="preserve">4.62667322158813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6936182975769</t>
+    <t xml:space="preserve">4.69361877441406</t>
   </si>
   <si>
     <t xml:space="preserve">4.73824834823608</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">4.58948135375977</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51509761810303</t>
+    <t xml:space="preserve">4.51509809494019</t>
   </si>
   <si>
     <t xml:space="preserve">4.57460403442383</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">4.64898824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64154958724976</t>
+    <t xml:space="preserve">4.64155006408691</t>
   </si>
   <si>
     <t xml:space="preserve">4.58204221725464</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52997398376465</t>
+    <t xml:space="preserve">4.52997446060181</t>
   </si>
   <si>
     <t xml:space="preserve">4.44815158843994</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">4.42583703994751</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37376832962036</t>
+    <t xml:space="preserve">4.3737678527832</t>
   </si>
   <si>
     <t xml:space="preserve">4.41839838027954</t>
@@ -2135,7 +2135,7 @@
     <t xml:space="preserve">4.32913780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32169961929321</t>
+    <t xml:space="preserve">4.32169914245605</t>
   </si>
   <si>
     <t xml:space="preserve">4.3142614364624</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">4.49278211593628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48534440994263</t>
+    <t xml:space="preserve">4.48534393310547</t>
   </si>
   <si>
     <t xml:space="preserve">4.43327522277832</t>
@@ -2162,31 +2162,31 @@
     <t xml:space="preserve">4.40352201461792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38864517211914</t>
+    <t xml:space="preserve">4.3886456489563</t>
   </si>
   <si>
     <t xml:space="preserve">4.39608335494995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35145282745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24731588363647</t>
+    <t xml:space="preserve">4.35145330429077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24731540679932</t>
   </si>
   <si>
     <t xml:space="preserve">4.20268535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19524717330933</t>
+    <t xml:space="preserve">4.19524669647217</t>
   </si>
   <si>
     <t xml:space="preserve">4.10598659515381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13574028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01672601699829</t>
+    <t xml:space="preserve">4.13573980331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01672554016113</t>
   </si>
   <si>
     <t xml:space="preserve">4.0241641998291</t>
@@ -2216,19 +2216,19 @@
     <t xml:space="preserve">3.97953391075134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97209596633911</t>
+    <t xml:space="preserve">3.97209548950195</t>
   </si>
   <si>
     <t xml:space="preserve">4.04647922515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06879472732544</t>
+    <t xml:space="preserve">4.06879425048828</t>
   </si>
   <si>
     <t xml:space="preserve">4.098548412323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16549301147461</t>
+    <t xml:space="preserve">4.16549348831177</t>
   </si>
   <si>
     <t xml:space="preserve">4.18780899047852</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">4.14317798614502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1283016204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15805530548096</t>
+    <t xml:space="preserve">4.12830209732056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1580548286438</t>
   </si>
   <si>
     <t xml:space="preserve">4.03904104232788</t>
@@ -2267,16 +2267,16 @@
     <t xml:space="preserve">4.30682277679443</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2919454574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2621922492981</t>
+    <t xml:space="preserve">4.29194593429565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26219272613525</t>
   </si>
   <si>
     <t xml:space="preserve">4.27706956863403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29938411712646</t>
+    <t xml:space="preserve">4.29938459396362</t>
   </si>
   <si>
     <t xml:space="preserve">4.28450727462769</t>
@@ -2291,13 +2291,13 @@
     <t xml:space="preserve">4.46302843093872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47046709060669</t>
+    <t xml:space="preserve">4.47046756744385</t>
   </si>
   <si>
     <t xml:space="preserve">4.45558977127075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6638650894165</t>
+    <t xml:space="preserve">4.66386461257935</t>
   </si>
   <si>
     <t xml:space="preserve">4.74568700790405</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">4.61923456192017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75312519073486</t>
+    <t xml:space="preserve">4.75312566757202</t>
   </si>
   <si>
     <t xml:space="preserve">4.67130374908447</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">4.70849561691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72337198257446</t>
+    <t xml:space="preserve">4.7233715057373</t>
   </si>
   <si>
     <t xml:space="preserve">4.68618059158325</t>
@@ -2333,7 +2333,7 @@
     <t xml:space="preserve">4.08367109298706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06135559082031</t>
+    <t xml:space="preserve">4.06135606765747</t>
   </si>
   <si>
     <t xml:space="preserve">3.96465730667114</t>
@@ -2342,7 +2342,7 @@
     <t xml:space="preserve">3.92746543884277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48116230964661</t>
+    <t xml:space="preserve">3.48116254806519</t>
   </si>
   <si>
     <t xml:space="preserve">3.38446378707886</t>
@@ -2357,13 +2357,13 @@
     <t xml:space="preserve">2.76335859298706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54020714759827</t>
+    <t xml:space="preserve">2.54020738601685</t>
   </si>
   <si>
     <t xml:space="preserve">2.57367992401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70385146141052</t>
+    <t xml:space="preserve">2.7038516998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.64806365966797</t>
@@ -2393,7 +2393,7 @@
     <t xml:space="preserve">2.78939294815063</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80426955223083</t>
+    <t xml:space="preserve">2.80426979064941</t>
   </si>
   <si>
     <t xml:space="preserve">2.75220084190369</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">2.69269394874573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62946772575378</t>
+    <t xml:space="preserve">2.62946796417236</t>
   </si>
   <si>
     <t xml:space="preserve">2.62574863433838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64062523841858</t>
+    <t xml:space="preserve">2.64062547683716</t>
   </si>
   <si>
     <t xml:space="preserve">2.65550208091736</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">2.45466589927673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42491245269775</t>
+    <t xml:space="preserve">2.42491221427917</t>
   </si>
   <si>
     <t xml:space="preserve">2.39515900611877</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">2.33937096595764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23523354530334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25754880905151</t>
+    <t xml:space="preserve">2.23523378372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25754904747009</t>
   </si>
   <si>
     <t xml:space="preserve">2.44722723960876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3840012550354</t>
+    <t xml:space="preserve">2.38400101661682</t>
   </si>
   <si>
     <t xml:space="preserve">2.41747403144836</t>
@@ -2486,13 +2486,13 @@
     <t xml:space="preserve">2.41375494003296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43978881835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51417303085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61087155342102</t>
+    <t xml:space="preserve">2.43978905677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51417279243469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6108717918396</t>
   </si>
   <si>
     <t xml:space="preserve">2.61831021308899</t>
@@ -2513,28 +2513,28 @@
     <t xml:space="preserve">2.56624174118042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49929594993591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52904939651489</t>
+    <t xml:space="preserve">2.49929618835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52904963493347</t>
   </si>
   <si>
     <t xml:space="preserve">2.51045346260071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58483719825745</t>
+    <t xml:space="preserve">2.58483743667603</t>
   </si>
   <si>
     <t xml:space="preserve">2.58111810684204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5997142791748</t>
+    <t xml:space="preserve">2.59971404075623</t>
   </si>
   <si>
     <t xml:space="preserve">2.63690638542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68530654907227</t>
+    <t xml:space="preserve">2.68530631065369</t>
   </si>
   <si>
     <t xml:space="preserve">2.66147232055664</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">2.62969350814819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5740807056427</t>
+    <t xml:space="preserve">2.57408094406128</t>
   </si>
   <si>
     <t xml:space="preserve">2.51846790313721</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">2.45491027832031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42710423469543</t>
+    <t xml:space="preserve">2.42710399627686</t>
   </si>
   <si>
     <t xml:space="preserve">2.51052331924438</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">2.47079968452454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49066162109375</t>
+    <t xml:space="preserve">2.49066138267517</t>
   </si>
   <si>
     <t xml:space="preserve">2.53435730934143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59791469573975</t>
+    <t xml:space="preserve">2.59791493415833</t>
   </si>
   <si>
     <t xml:space="preserve">2.55024671554565</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">2.49463391304016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47874426841736</t>
+    <t xml:space="preserve">2.47874450683594</t>
   </si>
   <si>
     <t xml:space="preserve">2.4588828086853</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">2.39929747581482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41121459007263</t>
+    <t xml:space="preserve">2.41121482849121</t>
   </si>
   <si>
     <t xml:space="preserve">2.40724205970764</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">2.4429931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42313170433044</t>
+    <t xml:space="preserve">2.42313146591187</t>
   </si>
   <si>
     <t xml:space="preserve">2.48668932914734</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">2.3834080696106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39532542228699</t>
+    <t xml:space="preserve">2.39532518386841</t>
   </si>
   <si>
     <t xml:space="preserve">2.33176755905151</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">2.37149095535278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3357400894165</t>
+    <t xml:space="preserve">2.33573985099792</t>
   </si>
   <si>
     <t xml:space="preserve">2.35560154914856</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">2.56613612174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52244019508362</t>
+    <t xml:space="preserve">2.52243995666504</t>
   </si>
   <si>
     <t xml:space="preserve">2.30396127700806</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">2.28409957885742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30793356895447</t>
+    <t xml:space="preserve">2.30793333053589</t>
   </si>
   <si>
     <t xml:space="preserve">2.28807163238525</t>
@@ -2669,22 +2669,22 @@
     <t xml:space="preserve">2.18479084968567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1450674533844</t>
+    <t xml:space="preserve">2.14506721496582</t>
   </si>
   <si>
     <t xml:space="preserve">2.11328864097595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.05767560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96631169319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97822868824005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98220098018646</t>
+    <t xml:space="preserve">2.0576753616333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96631157398224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97822856903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98220086097717</t>
   </si>
   <si>
     <t xml:space="preserve">2.08548212051392</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">2.2602653503418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5899703502655</t>
+    <t xml:space="preserve">2.58997011184692</t>
   </si>
   <si>
     <t xml:space="preserve">2.72900223731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71311283111572</t>
+    <t xml:space="preserve">2.7131130695343</t>
   </si>
   <si>
     <t xml:space="preserve">2.88392400741577</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">2.81242156028748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77269816398621</t>
+    <t xml:space="preserve">2.77269792556763</t>
   </si>
   <si>
     <t xml:space="preserve">2.74091958999634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70119571685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8203661441803</t>
+    <t xml:space="preserve">2.70119595527649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82036638259888</t>
   </si>
   <si>
     <t xml:space="preserve">2.84420013427734</t>
@@ -2744,13 +2744,13 @@
     <t xml:space="preserve">2.84817266464233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85611724853516</t>
+    <t xml:space="preserve">2.85611748695374</t>
   </si>
   <si>
     <t xml:space="preserve">2.78461527824402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87200689315796</t>
+    <t xml:space="preserve">2.87200665473938</t>
   </si>
   <si>
     <t xml:space="preserve">2.85214495658875</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">2.96337080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87597894668579</t>
+    <t xml:space="preserve">2.87597918510437</t>
   </si>
   <si>
     <t xml:space="preserve">2.9514536857605</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">2.93159198760986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86008977890015</t>
+    <t xml:space="preserve">2.86008954048157</t>
   </si>
   <si>
     <t xml:space="preserve">2.8283109664917</t>
@@ -2807,10 +2807,10 @@
     <t xml:space="preserve">2.95542621612549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97528767585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9593985080719</t>
+    <t xml:space="preserve">2.97528791427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95939826965332</t>
   </si>
   <si>
     <t xml:space="preserve">2.99912190437317</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">2.96734309196472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8878960609436</t>
+    <t xml:space="preserve">2.88789629936218</t>
   </si>
   <si>
     <t xml:space="preserve">2.80447697639465</t>
@@ -2828,13 +2828,13 @@
     <t xml:space="preserve">2.82433867454529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80844926834106</t>
+    <t xml:space="preserve">2.80844950675964</t>
   </si>
   <si>
     <t xml:space="preserve">2.89186859130859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90775775909424</t>
+    <t xml:space="preserve">2.90775799751282</t>
   </si>
   <si>
     <t xml:space="preserve">2.92364740371704</t>
@@ -2849,19 +2849,19 @@
     <t xml:space="preserve">3.04679012298584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30896496772766</t>
+    <t xml:space="preserve">3.30896472930908</t>
   </si>
   <si>
     <t xml:space="preserve">3.17787766456604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05473494529724</t>
+    <t xml:space="preserve">3.05473470687866</t>
   </si>
   <si>
     <t xml:space="preserve">3.11829233169556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04281759262085</t>
+    <t xml:space="preserve">3.04281783103943</t>
   </si>
   <si>
     <t xml:space="preserve">3.10637521743774</t>
@@ -2873,13 +2873,13 @@
     <t xml:space="preserve">3.0666515827179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07062387466431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76078081130981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78858733177185</t>
+    <t xml:space="preserve">3.07062411308289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76078104972839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78858757019043</t>
   </si>
   <si>
     <t xml:space="preserve">2.84022808074951</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">2.74886417388916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69325113296509</t>
+    <t xml:space="preserve">2.69325137138367</t>
   </si>
   <si>
     <t xml:space="preserve">2.7568085193634</t>
@@ -2912,16 +2912,16 @@
     <t xml:space="preserve">2.81639409065247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99514937400818</t>
+    <t xml:space="preserve">2.99514961242676</t>
   </si>
   <si>
     <t xml:space="preserve">3.15404343605042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0745964050293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13815402984619</t>
+    <t xml:space="preserve">3.07459616661072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13815426826477</t>
   </si>
   <si>
     <t xml:space="preserve">3.0825412273407</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">3.2732138633728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29307532310486</t>
+    <t xml:space="preserve">3.29307556152344</t>
   </si>
   <si>
     <t xml:space="preserve">3.23746252059937</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">3.23349046707153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20965647697449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25732421875</t>
+    <t xml:space="preserve">3.20965623855591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25732445716858</t>
   </si>
   <si>
     <t xml:space="preserve">3.2056839466095</t>
@@ -2978,13 +2978,13 @@
     <t xml:space="preserve">3.2136287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22554540634155</t>
+    <t xml:space="preserve">3.22554564476013</t>
   </si>
   <si>
     <t xml:space="preserve">3.19773936271667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20171165466309</t>
+    <t xml:space="preserve">3.20171189308167</t>
   </si>
   <si>
     <t xml:space="preserve">3.26526927947998</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">3.35266041755676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34471583366394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41224575042725</t>
+    <t xml:space="preserve">3.34471607208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41224598884583</t>
   </si>
   <si>
     <t xml:space="preserve">3.40827345848083</t>
@@ -3014,34 +3014,34 @@
     <t xml:space="preserve">3.69031047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69428253173828</t>
+    <t xml:space="preserve">3.69428277015686</t>
   </si>
   <si>
     <t xml:space="preserve">3.66647601127625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63866996765137</t>
+    <t xml:space="preserve">3.63866972923279</t>
   </si>
   <si>
     <t xml:space="preserve">3.51949906349182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45594191551208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52347183227539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49169301986694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.404301404953</t>
+    <t xml:space="preserve">3.45594167709351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52347159385681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49169278144836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40430116653442</t>
   </si>
   <si>
     <t xml:space="preserve">3.45196914672852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44005227088928</t>
+    <t xml:space="preserve">3.44005250930786</t>
   </si>
   <si>
     <t xml:space="preserve">3.34074378013611</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">3.33677101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32485413551331</t>
+    <t xml:space="preserve">3.32485437393188</t>
   </si>
   <si>
     <t xml:space="preserve">3.22157311439514</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">3.2811586856842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06267929077148</t>
+    <t xml:space="preserve">3.06267952919006</t>
   </si>
   <si>
     <t xml:space="preserve">3.08651351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18979430198669</t>
+    <t xml:space="preserve">3.18979454040527</t>
   </si>
   <si>
     <t xml:space="preserve">3.24937987327576</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">3.37252259254456</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24143505096436</t>
+    <t xml:space="preserve">3.24143481254578</t>
   </si>
   <si>
     <t xml:space="preserve">3.15007090568542</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">3.16198801994324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07856893539429</t>
+    <t xml:space="preserve">3.07856869697571</t>
   </si>
   <si>
     <t xml:space="preserve">2.97131562232971</t>
@@ -3137,19 +3137,19 @@
     <t xml:space="preserve">3.11432003974915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1421263217926</t>
+    <t xml:space="preserve">3.14212608337402</t>
   </si>
   <si>
     <t xml:space="preserve">3.18184995651245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17390513420105</t>
+    <t xml:space="preserve">3.17390489578247</t>
   </si>
   <si>
     <t xml:space="preserve">3.22951793670654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03884530067444</t>
+    <t xml:space="preserve">3.03884553909302</t>
   </si>
   <si>
     <t xml:space="preserve">3.00309419631958</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">3.05076241493225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15801548957825</t>
+    <t xml:space="preserve">3.15801572799683</t>
   </si>
   <si>
     <t xml:space="preserve">3.21760106086731</t>
@@ -3176,10 +3176,10 @@
     <t xml:space="preserve">2.87995147705078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98720479011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03487300872803</t>
+    <t xml:space="preserve">2.98720455169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03487277030945</t>
   </si>
   <si>
     <t xml:space="preserve">2.91570258140564</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">3.28513121604919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36060547828674</t>
+    <t xml:space="preserve">3.36060523986816</t>
   </si>
   <si>
     <t xml:space="preserve">3.37649464607239</t>
@@ -3200,10 +3200,10 @@
     <t xml:space="preserve">3.53141665458679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57908463478088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42416310310364</t>
+    <t xml:space="preserve">3.5790843963623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42416286468506</t>
   </si>
   <si>
     <t xml:space="preserve">3.34868860244751</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">3.35663294792175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32088184356689</t>
+    <t xml:space="preserve">3.32088208198547</t>
   </si>
   <si>
     <t xml:space="preserve">3.40032911300659</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">3.54333329200745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54730582237244</t>
+    <t xml:space="preserve">3.54730606079102</t>
   </si>
   <si>
     <t xml:space="preserve">3.55127787590027</t>
@@ -3245,31 +3245,31 @@
     <t xml:space="preserve">3.63072538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5910017490387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67442083358765</t>
+    <t xml:space="preserve">3.59100151062012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67442107200623</t>
   </si>
   <si>
     <t xml:space="preserve">3.61086320877075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62278032302856</t>
+    <t xml:space="preserve">3.62278056144714</t>
   </si>
   <si>
     <t xml:space="preserve">3.67839336395264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6505868434906</t>
+    <t xml:space="preserve">3.65058660507202</t>
   </si>
   <si>
     <t xml:space="preserve">3.61880779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63469696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58702874183655</t>
+    <t xml:space="preserve">3.6346971988678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58702898025513</t>
   </si>
   <si>
     <t xml:space="preserve">3.53936100006104</t>
@@ -8871,7 +8871,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G144" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8923,7 +8923,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G146" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8949,7 +8949,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="s">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -9209,7 +9209,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G157" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -13135,7 +13135,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G308" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -71487,13 +71487,13 @@
     </row>
     <row r="2553">
       <c r="A2553" s="1" t="n">
-        <v>46041.6911458333</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B2553" t="n">
         <v>112825</v>
       </c>
       <c r="C2553" t="n">
-        <v>3.51999998092651</v>
+        <v>3.52500009536743</v>
       </c>
       <c r="D2553" t="n">
         <v>3.44000005722046</v>
@@ -71508,6 +71508,32 @@
         <v>1565</v>
       </c>
       <c r="H2553" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2554">
+      <c r="A2554" s="1" t="n">
+        <v>46042.6910763889</v>
+      </c>
+      <c r="B2554" t="n">
+        <v>156457</v>
+      </c>
+      <c r="C2554" t="n">
+        <v>3.50999999046326</v>
+      </c>
+      <c r="D2554" t="n">
+        <v>3.45499992370605</v>
+      </c>
+      <c r="E2554" t="n">
+        <v>3.50999999046326</v>
+      </c>
+      <c r="F2554" t="n">
+        <v>3.49000000953674</v>
+      </c>
+      <c r="G2554" t="s">
+        <v>1575</v>
+      </c>
+      <c r="H2554" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">IGD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81178855895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76804494857788</t>
+    <t xml:space="preserve">4.81178760528564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76804447174072</t>
   </si>
   <si>
     <t xml:space="preserve">4.7653112411499</t>
@@ -65,40 +65,40 @@
     <t xml:space="preserve">4.67235565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55206155776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33334350585938</t>
+    <t xml:space="preserve">4.55206060409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33334302902222</t>
   </si>
   <si>
     <t xml:space="preserve">4.16383743286133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04627752304077</t>
+    <t xml:space="preserve">4.04627704620361</t>
   </si>
   <si>
     <t xml:space="preserve">3.60884189605713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88223791122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95605516433716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03807497024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97519397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785332679749</t>
+    <t xml:space="preserve">3.88223838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9560546875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0380744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97519302368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785380363464</t>
   </si>
   <si>
     <t xml:space="preserve">3.813889503479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96425771713257</t>
+    <t xml:space="preserve">3.96425700187683</t>
   </si>
   <si>
     <t xml:space="preserve">4.07088232040405</t>
@@ -107,58 +107,58 @@
     <t xml:space="preserve">3.92051386833191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69632816314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78654932975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45573902130127</t>
+    <t xml:space="preserve">3.69632863998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78654956817627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45573878288269</t>
   </si>
   <si>
     <t xml:space="preserve">3.49948215484619</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69086098670959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56783199310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63891506195068</t>
+    <t xml:space="preserve">3.69086050987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56783223152161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6389148235321</t>
   </si>
   <si>
     <t xml:space="preserve">3.88497257232666</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82755970954895</t>
+    <t xml:space="preserve">3.82755923271179</t>
   </si>
   <si>
     <t xml:space="preserve">3.93691778182983</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87130260467529</t>
+    <t xml:space="preserve">3.87130284309387</t>
   </si>
   <si>
     <t xml:space="preserve">4.05994653701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00800132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95332098007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98612928390503</t>
+    <t xml:space="preserve">4.00800085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95332145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98612952232361</t>
   </si>
   <si>
     <t xml:space="preserve">3.99159741401672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03260707855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05447816848755</t>
+    <t xml:space="preserve">4.0326075553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05447864532471</t>
   </si>
   <si>
     <t xml:space="preserve">4.24038887023926</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">4.21031475067139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37435293197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33607769012451</t>
+    <t xml:space="preserve">4.37435340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33607816696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.34701299667358</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">4.42903232574463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52745532989502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51105165481567</t>
+    <t xml:space="preserve">4.52745580673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51105213165283</t>
   </si>
   <si>
     <t xml:space="preserve">4.46184015274048</t>
@@ -197,490 +197,490 @@
     <t xml:space="preserve">4.67508983612061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60947465896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54932737350464</t>
+    <t xml:space="preserve">4.60947418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54932689666748</t>
   </si>
   <si>
     <t xml:space="preserve">4.4837121963501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34974718093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42083072662354</t>
+    <t xml:space="preserve">4.34974765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42083024978638</t>
   </si>
   <si>
     <t xml:space="preserve">4.42356538772583</t>
   </si>
   <si>
+    <t xml:space="preserve">4.26499462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405836105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2239842414856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22671842575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3306097984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40169286727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3060040473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36615133285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26772832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32514238357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29233455657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27046203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29506778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39895868301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30873823165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38802337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42629909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34427976608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39075708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30326986312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49522352218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57292604446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65062808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69091844558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67940664291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69379615783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66213989257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61609363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57580327987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63623857498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63048267364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63336086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63911581039429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.564293384552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3513298034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08368873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95130753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97145223617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16139125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20168113708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24772691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27650594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03476524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755875587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84482622146606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633778572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470378875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15851354598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01749801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784911155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83619236946106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96281862258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05778884887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09232330322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25636005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40313196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33406400680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51824712753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41752099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45493268966675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45781183242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52975797653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48946809768677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51536846160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25923919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38874292373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46644496917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3829870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36572027206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41464328765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35996341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33694171905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29377317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31391763687134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19017028808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19880390167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22182655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2621169090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25348281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23046064376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14412403106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19592618942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16714715957642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15563535690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11534452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20743656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14700222015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17865800857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07505512237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94267344474792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497092247009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79878044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77575731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83907032012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74697852134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74985671043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85921597480774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82468104362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79590201377869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87936067581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81029176712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76424646377563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72971200942993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71244406700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72395658493042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84194779396057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735307693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06354379653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10958957672119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1182222366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08656644821167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03764295578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00310897827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97432994842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91389489173889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93979620933533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92540645599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92828416824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89662790298462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84770441055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273442268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75849056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55703997612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64337515830994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66927599906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65776443481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58006238937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59732937812805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60308599472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63186478614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6261088848114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6606433391571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61459732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80453634262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95994091033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07217693328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04339933395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12685680389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13261222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12110137939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36859798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28226137161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33981895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34845161437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33118486404419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30240631103516</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.2649941444397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25405883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22398471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22671890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23765468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3306097984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40169286727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31967353820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30600452423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36615133285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26772832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32514190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29233503341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27046251296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29506826400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39895868301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30873823165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38802289962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42629909515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34427976608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39075708389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30326986312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49522352218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57292604446411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65062808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091892242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67940664291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69379663467407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66213989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61609363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57580327987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63623809814453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63048315048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63336086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63911581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56429243087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35133075714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08368873596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95130705833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97145223617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1613917350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20168113708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24772691726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27650594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03476476669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755875587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8448269367218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633778572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15851306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01749849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784887313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83619260787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96281838417053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05778884887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09232234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25636053085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40313243865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33406352996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51824712753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41752099990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45493268966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45781135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53839206695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52975749969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48946762084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51536846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25923919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38874292373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46644449234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38298654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36572027206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41464328765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35996437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33694124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29377222061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3139181137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19017028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19880390167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22182703018188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26211643218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25348234176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23046064376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14412403106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19592666625977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16714715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15563583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11534547805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20743703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14700174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17865896224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07505559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94267320632935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79878067970276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77575731277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83907055854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74697828292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7498562335968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85921597480774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82468104362488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79590201377869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87936067581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81029200553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439116477966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7642457485199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72971105575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71244430541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72395634651184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84194827079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735331535339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06354427337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10959005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11822271347046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08656644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03764295578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00310945510864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97432994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91389513015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93979597091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92540645599365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92828416824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89662837982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84770441055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273442268372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75849008560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55703997612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64337539672852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66927647590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65776491165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58006167411804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59732961654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60308575630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63186454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6261088848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66064310073853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61459732055664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80453634262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95994067192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07217741012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04339933395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12685680389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13261222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12110090255737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36859750747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28226184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33981895446777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3484525680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33118534088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30240631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27075004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22758197784424</t>
+    <t xml:space="preserve">4.27074956893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2275824546814</t>
   </si>
   <si>
     <t xml:space="preserve">4.2131929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18153667449951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09807825088501</t>
+    <t xml:space="preserve">4.18153715133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09807872772217</t>
   </si>
   <si>
     <t xml:space="preserve">4.00598621368408</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">4.10383415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02901029586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06929969787598</t>
+    <t xml:space="preserve">4.0290093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06929922103882</t>
   </si>
   <si>
     <t xml:space="preserve">4.21894836425781</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">4.14987993240356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47220039367676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51249074935913</t>
+    <t xml:space="preserve">4.47220087051392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51249027252197</t>
   </si>
   <si>
     <t xml:space="preserve">4.37723112106323</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">4.44342184066772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5930700302124</t>
+    <t xml:space="preserve">4.59307050704956</t>
   </si>
   <si>
     <t xml:space="preserve">4.62472772598267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57004833221436</t>
+    <t xml:space="preserve">4.5700478553772</t>
   </si>
   <si>
     <t xml:space="preserve">4.71969699859619</t>
@@ -734,28 +734,28 @@
     <t xml:space="preserve">4.80315446853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73120832443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70530843734741</t>
+    <t xml:space="preserve">4.73120784759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70530796051025</t>
   </si>
   <si>
     <t xml:space="preserve">4.7024302482605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64487266540527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62184906005859</t>
+    <t xml:space="preserve">4.64487218856812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62185001373291</t>
   </si>
   <si>
     <t xml:space="preserve">4.54702472686768</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52688026428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46068859100342</t>
+    <t xml:space="preserve">4.52687978744507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46068954467773</t>
   </si>
   <si>
     <t xml:space="preserve">4.6045823097229</t>
@@ -764,25 +764,25 @@
     <t xml:space="preserve">4.71394109725952</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66501712799072</t>
+    <t xml:space="preserve">4.66501760482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.74559736251831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76574325561523</t>
+    <t xml:space="preserve">4.76574277877808</t>
   </si>
   <si>
     <t xml:space="preserve">4.74847555160522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78301000595093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77149868011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82329988479614</t>
+    <t xml:space="preserve">4.78301048278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77149820327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8233003616333</t>
   </si>
   <si>
     <t xml:space="preserve">4.92690277099609</t>
@@ -791,16 +791,16 @@
     <t xml:space="preserve">4.94992637634277</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98446035385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02475118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05640745162964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89236831665039</t>
+    <t xml:space="preserve">4.98446083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02475070953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05640697479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89236879348755</t>
   </si>
   <si>
     <t xml:space="preserve">4.86359024047852</t>
@@ -809,31 +809,31 @@
     <t xml:space="preserve">4.82905578613281</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87592363357544</t>
+    <t xml:space="preserve">4.8759241104126</t>
   </si>
   <si>
     <t xml:space="preserve">4.91160154342651</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93538665771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89970827102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92052030563354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01268672943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96809101104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9710636138916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89376306533813</t>
+    <t xml:space="preserve">4.93538570404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89970874786377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9205207824707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01268720626831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96809148788452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97106409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89376258850098</t>
   </si>
   <si>
     <t xml:space="preserve">4.94727849960327</t>
@@ -842,61 +842,61 @@
     <t xml:space="preserve">4.94133281707764</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92944002151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88781642913818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85511112213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79862260818481</t>
+    <t xml:space="preserve">4.92943954467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88781595230103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85511207580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79862213134766</t>
   </si>
   <si>
     <t xml:space="preserve">4.77186441421509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75105285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78673028945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73321437835693</t>
+    <t xml:space="preserve">4.75105237960815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78672981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73321390151978</t>
   </si>
   <si>
     <t xml:space="preserve">4.66185855865479</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5340142250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58455753326416</t>
+    <t xml:space="preserve">4.53401470184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.584557056427</t>
   </si>
   <si>
     <t xml:space="preserve">4.61726188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70348262786865</t>
+    <t xml:space="preserve">4.70348310470581</t>
   </si>
   <si>
     <t xml:space="preserve">4.72132158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63807439804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72726726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81646156311035</t>
+    <t xml:space="preserve">4.63807392120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72726678848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81646203994751</t>
   </si>
   <si>
     <t xml:space="preserve">4.83132696151733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9383602142334</t>
+    <t xml:space="preserve">4.93835973739624</t>
   </si>
   <si>
     <t xml:space="preserve">4.94430589675903</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">4.9829568862915</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95322561264038</t>
+    <t xml:space="preserve">4.95322513580322</t>
   </si>
   <si>
     <t xml:space="preserve">4.90565490722656</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">5.00376796722412</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05431079864502</t>
+    <t xml:space="preserve">5.05431127548218</t>
   </si>
   <si>
     <t xml:space="preserve">5.04836559295654</t>
@@ -929,16 +929,16 @@
     <t xml:space="preserve">4.99782180786133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98592948913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15837144851685</t>
+    <t xml:space="preserve">4.98592901229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15837049484253</t>
   </si>
   <si>
     <t xml:space="preserve">5.12566709518433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11080074310303</t>
+    <t xml:space="preserve">5.11080121994019</t>
   </si>
   <si>
     <t xml:space="preserve">5.07512283325195</t>
@@ -956,43 +956,43 @@
     <t xml:space="preserve">5.03944540023804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02755355834961</t>
+    <t xml:space="preserve">5.02755308151245</t>
   </si>
   <si>
     <t xml:space="preserve">4.97701025009155</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05133867263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99484872817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01566076278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06620407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13755941390991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23269891738892</t>
+    <t xml:space="preserve">5.05133819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99484825134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01566123962402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06620454788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1375584602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2326979637146</t>
   </si>
   <si>
     <t xml:space="preserve">5.2445912361145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23864555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.197021484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17323684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1851282119751</t>
+    <t xml:space="preserve">5.23864507675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19702196121216</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17323589324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18512868881226</t>
   </si>
   <si>
     <t xml:space="preserve">5.20891427993774</t>
@@ -1001,13 +1001,13 @@
     <t xml:space="preserve">5.1940484046936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2475643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25053739547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26242971420288</t>
+    <t xml:space="preserve">5.24756383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25053787231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26243019104004</t>
   </si>
   <si>
     <t xml:space="preserve">5.14945125579834</t>
@@ -1016,10 +1016,10 @@
     <t xml:space="preserve">5.16431713104248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21485948562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35162353515625</t>
+    <t xml:space="preserve">5.21485996246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35162448883057</t>
   </si>
   <si>
     <t xml:space="preserve">5.44081687927246</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">5.64893627166748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6786675453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47054767608643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46757507324219</t>
+    <t xml:space="preserve">5.67866706848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47054815292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46757555007935</t>
   </si>
   <si>
     <t xml:space="preserve">5.55974292755127</t>
@@ -1046,46 +1046,46 @@
     <t xml:space="preserve">5.58947420120239</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50325298309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57758140563965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75002336502075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.90165233612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91651821136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20193815231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19004487991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11274433135986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12463569641113</t>
+    <t xml:space="preserve">5.50325345993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57758092880249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75002241134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.90165185928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91651773452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20193719863892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19004535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11274385452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12463665008545</t>
   </si>
   <si>
     <t xml:space="preserve">6.15436744689941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03544235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97597980499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.88975954055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00571203231812</t>
+    <t xml:space="preserve">6.03544187545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97598028182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88976001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.0057110786438</t>
   </si>
   <si>
     <t xml:space="preserve">6.29113054275513</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">6.17815256118774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39816427230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38627147674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33275461196899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43384027481079</t>
+    <t xml:space="preserve">6.39816379547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38627099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33275508880615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43384075164795</t>
   </si>
   <si>
     <t xml:space="preserve">6.46951913833618</t>
@@ -1115,22 +1115,22 @@
     <t xml:space="preserve">6.41600275039673</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40410852432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24356031417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35654020309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44573450088501</t>
+    <t xml:space="preserve">6.40410900115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24356126785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35653924942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44573354721069</t>
   </si>
   <si>
     <t xml:space="preserve">6.60033655166626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58844327926636</t>
+    <t xml:space="preserve">6.58844375610352</t>
   </si>
   <si>
     <t xml:space="preserve">6.71926116943359</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">6.48141098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07111978530884</t>
+    <t xml:space="preserve">6.07111930847168</t>
   </si>
   <si>
     <t xml:space="preserve">5.82732391357422</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">5.80948448181152</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68163967132568</t>
+    <t xml:space="preserve">5.68164110183716</t>
   </si>
   <si>
     <t xml:space="preserve">5.73812961578369</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">5.81840419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7321834564209</t>
+    <t xml:space="preserve">5.73218393325806</t>
   </si>
   <si>
     <t xml:space="preserve">5.72623682022095</t>
@@ -1178,37 +1178,37 @@
     <t xml:space="preserve">5.95814085006714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92840957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76191568374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70839738845825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79759168624878</t>
+    <t xml:space="preserve">5.92841005325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76191520690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70839834213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.7975926399231</t>
   </si>
   <si>
     <t xml:space="preserve">5.75596857070923</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68461418151855</t>
+    <t xml:space="preserve">5.6846137046814</t>
   </si>
   <si>
     <t xml:space="preserve">5.69650650024414</t>
   </si>
   <si>
-    <t xml:space="preserve">5.66082859039307</t>
+    <t xml:space="preserve">5.66082811355591</t>
   </si>
   <si>
     <t xml:space="preserve">5.50622701644897</t>
   </si>
   <si>
-    <t xml:space="preserve">5.45865631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.33973121643066</t>
+    <t xml:space="preserve">5.458655834198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.33973073959351</t>
   </si>
   <si>
     <t xml:space="preserve">5.15539693832397</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">5.03647232055664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91754722595215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00079488754272</t>
+    <t xml:space="preserve">4.91754770278931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00079584121704</t>
   </si>
   <si>
     <t xml:space="preserve">4.86997747421265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85213899612427</t>
+    <t xml:space="preserve">4.85213851928711</t>
   </si>
   <si>
     <t xml:space="preserve">5.14350509643555</t>
@@ -1238,37 +1238,37 @@
     <t xml:space="preserve">4.75699901580811</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79446029663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70823907852173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58812522888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47752523422241</t>
+    <t xml:space="preserve">4.7944598197937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70824003219604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58812570571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47752618789673</t>
   </si>
   <si>
     <t xml:space="preserve">4.46860599517822</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53104162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66483163833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66839981079102</t>
+    <t xml:space="preserve">4.53104209899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66483211517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66839933395386</t>
   </si>
   <si>
     <t xml:space="preserve">4.55482625961304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49774217605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51260805130005</t>
+    <t xml:space="preserve">4.49774265289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51260852813721</t>
   </si>
   <si>
     <t xml:space="preserve">4.41211652755737</t>
@@ -1277,7 +1277,7 @@
     <t xml:space="preserve">4.36811399459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29913806915283</t>
+    <t xml:space="preserve">4.29913759231567</t>
   </si>
   <si>
     <t xml:space="preserve">4.48525524139404</t>
@@ -1289,7 +1289,7 @@
     <t xml:space="preserve">4.44184732437134</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29378604888916</t>
+    <t xml:space="preserve">4.29378700256348</t>
   </si>
   <si>
     <t xml:space="preserve">4.19210577011108</t>
@@ -1298,25 +1298,25 @@
     <t xml:space="preserve">4.57336091995239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6545934677124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1029748916626</t>
+    <t xml:space="preserve">4.65459442138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.10297536849976</t>
   </si>
   <si>
     <t xml:space="preserve">4.85351943969727</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95713901519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14391183853149</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34731388092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28271102905273</t>
+    <t xml:space="preserve">4.95713949203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14391136169434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34731435775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28271150588989</t>
   </si>
   <si>
     <t xml:space="preserve">5.17781209945679</t>
@@ -1328,7 +1328,7 @@
     <t xml:space="preserve">4.96993160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05244445800781</t>
+    <t xml:space="preserve">5.05244398117065</t>
   </si>
   <si>
     <t xml:space="preserve">4.9891209602356</t>
@@ -1349,16 +1349,16 @@
     <t xml:space="preserve">5.01470613479614</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08506488800049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93539190292358</t>
+    <t xml:space="preserve">5.08506536483765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93539142608643</t>
   </si>
   <si>
     <t xml:space="preserve">4.92579746246338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96545457839966</t>
+    <t xml:space="preserve">4.9654541015625</t>
   </si>
   <si>
     <t xml:space="preserve">5.02557945251465</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">5.04029130935669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02110242843628</t>
+    <t xml:space="preserve">5.02110195159912</t>
   </si>
   <si>
     <t xml:space="preserve">5.11704730987549</t>
@@ -1379,16 +1379,16 @@
     <t xml:space="preserve">5.06971406936646</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24497270584106</t>
+    <t xml:space="preserve">5.24497318267822</t>
   </si>
   <si>
     <t xml:space="preserve">5.14135265350342</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97888708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76461029052734</t>
+    <t xml:space="preserve">4.97888660430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7646107673645</t>
   </si>
   <si>
     <t xml:space="preserve">4.83496999740601</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">4.71471881866455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66290950775146</t>
+    <t xml:space="preserve">4.66290903091431</t>
   </si>
   <si>
     <t xml:space="preserve">4.55097341537476</t>
@@ -1412,22 +1412,22 @@
     <t xml:space="preserve">4.32710313796997</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57399988174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65267467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63092708587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72943067550659</t>
+    <t xml:space="preserve">4.57400035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65267515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63092756271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72943115234375</t>
   </si>
   <si>
     <t xml:space="preserve">4.81961870193481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79403305053711</t>
+    <t xml:space="preserve">4.79403352737427</t>
   </si>
   <si>
     <t xml:space="preserve">4.68401670455933</t>
@@ -1436,34 +1436,34 @@
     <t xml:space="preserve">4.58679246902466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.87419891357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99108505249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88932466506958</t>
+    <t xml:space="preserve">4.8741979598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99108457565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88932418823242</t>
   </si>
   <si>
     <t xml:space="preserve">4.9842095375061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03165197372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79375171661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79512786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76074886322021</t>
+    <t xml:space="preserve">5.03165245056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79375219345093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79512691497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76074838638306</t>
   </si>
   <si>
     <t xml:space="preserve">4.74630975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86113452911377</t>
+    <t xml:space="preserve">4.86113405227661</t>
   </si>
   <si>
     <t xml:space="preserve">4.79031419754028</t>
@@ -1472,22 +1472,22 @@
     <t xml:space="preserve">4.81300401687622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72705793380737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77174949645996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73187065124512</t>
+    <t xml:space="preserve">4.72705745697021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77174997329712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73187112808228</t>
   </si>
   <si>
     <t xml:space="preserve">4.84532022476196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7868766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76968669891357</t>
+    <t xml:space="preserve">4.78687620162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76968717575073</t>
   </si>
   <si>
     <t xml:space="preserve">4.91614007949829</t>
@@ -1505,34 +1505,34 @@
     <t xml:space="preserve">4.85013294219971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86044692993164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8996376991272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93470478057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99177265167236</t>
+    <t xml:space="preserve">4.86044645309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89963817596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93470430374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99177312850952</t>
   </si>
   <si>
     <t xml:space="preserve">5.0543417930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96152019500732</t>
+    <t xml:space="preserve">4.96151971817017</t>
   </si>
   <si>
     <t xml:space="preserve">4.97939682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99246072769165</t>
+    <t xml:space="preserve">4.99246025085449</t>
   </si>
   <si>
     <t xml:space="preserve">4.8583836555481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98489761352539</t>
+    <t xml:space="preserve">4.98489713668823</t>
   </si>
   <si>
     <t xml:space="preserve">4.85219621658325</t>
@@ -1544,13 +1544,13 @@
     <t xml:space="preserve">4.97183322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93882989883423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91682720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83363199234009</t>
+    <t xml:space="preserve">4.93883037567139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91682767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83363151550293</t>
   </si>
   <si>
     <t xml:space="preserve">4.76556158065796</t>
@@ -1559,13 +1559,13 @@
     <t xml:space="preserve">4.75868606567383</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75043487548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67067623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58129215240479</t>
+    <t xml:space="preserve">4.75043535232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67067718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58129262924194</t>
   </si>
   <si>
     <t xml:space="preserve">4.5427885055542</t>
@@ -1574,7 +1574,7 @@
     <t xml:space="preserve">4.4630298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48228168487549</t>
+    <t xml:space="preserve">4.48228216171265</t>
   </si>
   <si>
     <t xml:space="preserve">4.51941108703613</t>
@@ -1586,10 +1586,10 @@
     <t xml:space="preserve">4.59779357910156</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52972459793091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53797483444214</t>
+    <t xml:space="preserve">4.52972412109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53797578811646</t>
   </si>
   <si>
     <t xml:space="preserve">4.57922983169556</t>
@@ -1598,25 +1598,25 @@
     <t xml:space="preserve">4.55172634124756</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57235383987427</t>
+    <t xml:space="preserve">4.57235431671143</t>
   </si>
   <si>
     <t xml:space="preserve">4.55241394042969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50634670257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51597261428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49053287506104</t>
+    <t xml:space="preserve">4.50634717941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51597309112549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49053239822388</t>
   </si>
   <si>
     <t xml:space="preserve">4.52078580856323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.518723487854</t>
+    <t xml:space="preserve">4.51872301101685</t>
   </si>
   <si>
     <t xml:space="preserve">4.53041219711304</t>
@@ -1634,22 +1634,22 @@
     <t xml:space="preserve">4.47746896743774</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78412580490112</t>
+    <t xml:space="preserve">4.78412628173828</t>
   </si>
   <si>
     <t xml:space="preserve">4.6651759147644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65417528152466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70299291610718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73049545288086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71055555343628</t>
+    <t xml:space="preserve">4.6541748046875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70299243927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73049592971802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71055603027344</t>
   </si>
   <si>
     <t xml:space="preserve">4.64661169052124</t>
@@ -1661,7 +1661,7 @@
     <t xml:space="preserve">4.55035161972046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50840950012207</t>
+    <t xml:space="preserve">4.50840997695923</t>
   </si>
   <si>
     <t xml:space="preserve">4.41558742523193</t>
@@ -1670,25 +1670,25 @@
     <t xml:space="preserve">4.42727613449097</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40046119689941</t>
+    <t xml:space="preserve">4.40046072006226</t>
   </si>
   <si>
     <t xml:space="preserve">4.33239126205444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2223801612854</t>
+    <t xml:space="preserve">4.22237968444824</t>
   </si>
   <si>
     <t xml:space="preserve">4.20450305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16256141662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0663013458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09311628341675</t>
+    <t xml:space="preserve">4.16256093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06630086898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09311580657959</t>
   </si>
   <si>
     <t xml:space="preserve">3.98791766166687</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">4.05942487716675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09724187850952</t>
+    <t xml:space="preserve">4.09724235534668</t>
   </si>
   <si>
     <t xml:space="preserve">4.0497989654541</t>
@@ -1712,16 +1712,16 @@
     <t xml:space="preserve">4.09105348587036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08830308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13161993026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21962928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28563642501831</t>
+    <t xml:space="preserve">4.088303565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13162040710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21962976455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28563594818115</t>
   </si>
   <si>
     <t xml:space="preserve">4.29732513427734</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">4.22100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15293550491333</t>
+    <t xml:space="preserve">4.15293502807617</t>
   </si>
   <si>
     <t xml:space="preserve">4.36608171463013</t>
@@ -1751,7 +1751,7 @@
     <t xml:space="preserve">4.12749433517456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15224742889404</t>
+    <t xml:space="preserve">4.15224695205688</t>
   </si>
   <si>
     <t xml:space="preserve">4.13505840301514</t>
@@ -1760,16 +1760,16 @@
     <t xml:space="preserve">4.09174108505249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03260946273804</t>
+    <t xml:space="preserve">4.0326099395752</t>
   </si>
   <si>
     <t xml:space="preserve">4.03467273712158</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05461168289185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14537143707275</t>
+    <t xml:space="preserve">4.054612159729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14537191390991</t>
   </si>
   <si>
     <t xml:space="preserve">4.2237548828125</t>
@@ -1781,22 +1781,22 @@
     <t xml:space="preserve">4.19900226593018</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18868923187256</t>
+    <t xml:space="preserve">4.18868827819824</t>
   </si>
   <si>
     <t xml:space="preserve">4.1137433052063</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04429817199707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02917242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99273085594177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9989185333252</t>
+    <t xml:space="preserve">4.04429864883423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02917194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99273061752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99891901016235</t>
   </si>
   <si>
     <t xml:space="preserve">3.96316480636597</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">3.88684439659119</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98241710662842</t>
+    <t xml:space="preserve">3.982417345047</t>
   </si>
   <si>
     <t xml:space="preserve">3.90540909767151</t>
@@ -1814,64 +1814,64 @@
     <t xml:space="preserve">3.8737804889679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78164601325989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71013832092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69501233100891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7335159778595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72870326042175</t>
+    <t xml:space="preserve">3.78164649009705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71013855934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69501209259033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73351573944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72870302200317</t>
   </si>
   <si>
     <t xml:space="preserve">3.64894485473633</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70051288604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83115124702454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8999080657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9934184551239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97829174995422</t>
+    <t xml:space="preserve">3.70051264762878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83115100860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990878105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99341821670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97829127311707</t>
   </si>
   <si>
     <t xml:space="preserve">4.06286287307739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04842376708984</t>
+    <t xml:space="preserve">4.048424243927</t>
   </si>
   <si>
     <t xml:space="preserve">4.06767606735229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04292345046997</t>
+    <t xml:space="preserve">4.04292392730713</t>
   </si>
   <si>
     <t xml:space="preserve">3.99548101425171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95491433143616</t>
+    <t xml:space="preserve">3.954913854599</t>
   </si>
   <si>
     <t xml:space="preserve">4.04086065292358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02160882949829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05804967880249</t>
+    <t xml:space="preserve">4.02160835266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05805015563965</t>
   </si>
   <si>
     <t xml:space="preserve">4.01335763931274</t>
@@ -1886,40 +1886,40 @@
     <t xml:space="preserve">4.11786842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22788047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31864023208618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2890739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29044914245605</t>
+    <t xml:space="preserve">4.22788000106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31863975524902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28907346725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2904486656189</t>
   </si>
   <si>
     <t xml:space="preserve">4.25057029724121</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24919509887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2698221206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26294612884521</t>
+    <t xml:space="preserve">4.24919462203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26982259750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26294660568237</t>
   </si>
   <si>
     <t xml:space="preserve">4.24231958389282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13643312454224</t>
+    <t xml:space="preserve">4.13643264770508</t>
   </si>
   <si>
     <t xml:space="preserve">4.05392456054688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12543201446533</t>
+    <t xml:space="preserve">4.12543249130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.0896782875061</t>
@@ -1934,22 +1934,22 @@
     <t xml:space="preserve">4.23819398880005</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22169256210327</t>
+    <t xml:space="preserve">4.22169208526611</t>
   </si>
   <si>
     <t xml:space="preserve">4.2189416885376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21481657028198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16324806213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28494882583618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34476757049561</t>
+    <t xml:space="preserve">4.21481609344482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16324853897095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28494834899902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34476709365845</t>
   </si>
   <si>
     <t xml:space="preserve">4.25400829315186</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">4.37433338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50359630584717</t>
+    <t xml:space="preserve">4.50359725952148</t>
   </si>
   <si>
     <t xml:space="preserve">4.57441663742065</t>
@@ -1973,22 +1973,22 @@
     <t xml:space="preserve">4.44171524047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44859027862549</t>
+    <t xml:space="preserve">4.44859075546265</t>
   </si>
   <si>
     <t xml:space="preserve">4.55653953552246</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5778546333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60948276519775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66173839569092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6067328453064</t>
+    <t xml:space="preserve">4.57785511016846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60948324203491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66173791885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60673236846924</t>
   </si>
   <si>
     <t xml:space="preserve">4.57097864151001</t>
@@ -2006,31 +2006,31 @@
     <t xml:space="preserve">4.41971302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46234226226807</t>
+    <t xml:space="preserve">4.46234273910522</t>
   </si>
   <si>
     <t xml:space="preserve">4.42796421051025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54485082626343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52422380447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55860280990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58610534667969</t>
+    <t xml:space="preserve">4.54485130310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52422332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55860233306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58610486984253</t>
   </si>
   <si>
     <t xml:space="preserve">4.45546674728394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48296976089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53109931945801</t>
+    <t xml:space="preserve">4.48296928405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53109979629517</t>
   </si>
   <si>
     <t xml:space="preserve">4.56547784805298</t>
@@ -2048,16 +2048,16 @@
     <t xml:space="preserve">4.62048387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62735986709595</t>
+    <t xml:space="preserve">4.62735939025879</t>
   </si>
   <si>
     <t xml:space="preserve">4.71674394607544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65486240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49672079086304</t>
+    <t xml:space="preserve">4.65486288070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4967212677002</t>
   </si>
   <si>
     <t xml:space="preserve">4.5522894859314</t>
@@ -2072,25 +2072,25 @@
     <t xml:space="preserve">4.62667322158813</t>
   </si>
   <si>
-    <t xml:space="preserve">4.69361877441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73824834823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71593379974365</t>
+    <t xml:space="preserve">4.6936182975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73824882507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71593332290649</t>
   </si>
   <si>
     <t xml:space="preserve">4.63411140441895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65642690658569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58948135375977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51509809494019</t>
+    <t xml:space="preserve">4.65642642974854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58948087692261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51509761810303</t>
   </si>
   <si>
     <t xml:space="preserve">4.57460403442383</t>
@@ -2105,13 +2105,13 @@
     <t xml:space="preserve">4.64898824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64155006408691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58204221725464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52997446060181</t>
+    <t xml:space="preserve">4.64154958724976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5820426940918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52997398376465</t>
   </si>
   <si>
     <t xml:space="preserve">4.44815158843994</t>
@@ -2120,25 +2120,25 @@
     <t xml:space="preserve">4.38120651245117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42583703994751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3737678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41839838027954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35889148712158</t>
+    <t xml:space="preserve">4.42583656311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37376832962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4183988571167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35889196395874</t>
   </si>
   <si>
     <t xml:space="preserve">4.32913780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32169914245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3142614364624</t>
+    <t xml:space="preserve">4.32169961929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31426095962524</t>
   </si>
   <si>
     <t xml:space="preserve">4.33657598495483</t>
@@ -2153,7 +2153,7 @@
     <t xml:space="preserve">4.49278211593628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48534393310547</t>
+    <t xml:space="preserve">4.48534440994263</t>
   </si>
   <si>
     <t xml:space="preserve">4.43327522277832</t>
@@ -2162,16 +2162,16 @@
     <t xml:space="preserve">4.40352201461792</t>
   </si>
   <si>
-    <t xml:space="preserve">4.3886456489563</t>
+    <t xml:space="preserve">4.38864469528198</t>
   </si>
   <si>
     <t xml:space="preserve">4.39608335494995</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35145330429077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24731540679932</t>
+    <t xml:space="preserve">4.35145282745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24731588363647</t>
   </si>
   <si>
     <t xml:space="preserve">4.20268535614014</t>
@@ -2183,10 +2183,10 @@
     <t xml:space="preserve">4.10598659515381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13573980331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01672554016113</t>
+    <t xml:space="preserve">4.13574028015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01672601699829</t>
   </si>
   <si>
     <t xml:space="preserve">4.0241641998291</t>
@@ -2198,25 +2198,25 @@
     <t xml:space="preserve">3.9051501750946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95721912384033</t>
+    <t xml:space="preserve">3.95721888542175</t>
   </si>
   <si>
     <t xml:space="preserve">3.89771151542664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98697257041931</t>
+    <t xml:space="preserve">3.98697280883789</t>
   </si>
   <si>
     <t xml:space="preserve">3.9200267791748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94234204292297</t>
+    <t xml:space="preserve">3.94234228134155</t>
   </si>
   <si>
     <t xml:space="preserve">3.97953391075134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97209548950195</t>
+    <t xml:space="preserve">3.97209572792053</t>
   </si>
   <si>
     <t xml:space="preserve">4.04647922515869</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">4.16549348831177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18780899047852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18036985397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17293167114258</t>
+    <t xml:space="preserve">4.18780851364136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18037033081055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17293214797974</t>
   </si>
   <si>
     <t xml:space="preserve">4.11342525482178</t>
@@ -2249,7 +2249,7 @@
     <t xml:space="preserve">4.12830209732056</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1580548286438</t>
+    <t xml:space="preserve">4.15805530548096</t>
   </si>
   <si>
     <t xml:space="preserve">4.03904104232788</t>
@@ -2261,28 +2261,28 @@
     <t xml:space="preserve">4.23987722396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26963090896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30682277679443</t>
+    <t xml:space="preserve">4.26963043212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30682229995728</t>
   </si>
   <si>
     <t xml:space="preserve">4.29194593429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26219272613525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27706956863403</t>
+    <t xml:space="preserve">4.2621922492981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27706909179688</t>
   </si>
   <si>
     <t xml:space="preserve">4.29938459396362</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28450727462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41095972061157</t>
+    <t xml:space="preserve">4.28450775146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41096019744873</t>
   </si>
   <si>
     <t xml:space="preserve">4.44071340560913</t>
@@ -2291,22 +2291,22 @@
     <t xml:space="preserve">4.46302843093872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47046756744385</t>
+    <t xml:space="preserve">4.47046709060669</t>
   </si>
   <si>
     <t xml:space="preserve">4.45558977127075</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66386461257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74568700790405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79031801223755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70105695724487</t>
+    <t xml:space="preserve">4.6638650894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74568748474121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79031753540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70105743408203</t>
   </si>
   <si>
     <t xml:space="preserve">4.67874193191528</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">4.61923456192017</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75312566757202</t>
+    <t xml:space="preserve">4.75312519073486</t>
   </si>
   <si>
     <t xml:space="preserve">4.67130374908447</t>
@@ -2324,25 +2324,25 @@
     <t xml:space="preserve">4.70849561691284</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7233715057373</t>
+    <t xml:space="preserve">4.72337198257446</t>
   </si>
   <si>
     <t xml:space="preserve">4.68618059158325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08367109298706</t>
+    <t xml:space="preserve">4.0836706161499</t>
   </si>
   <si>
     <t xml:space="preserve">4.06135606765747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96465730667114</t>
+    <t xml:space="preserve">3.96465706825256</t>
   </si>
   <si>
     <t xml:space="preserve">3.92746543884277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48116254806519</t>
+    <t xml:space="preserve">3.48116230964661</t>
   </si>
   <si>
     <t xml:space="preserve">3.38446378707886</t>
@@ -2354,22 +2354,22 @@
     <t xml:space="preserve">2.71872854232788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76335859298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54020738601685</t>
+    <t xml:space="preserve">2.76335835456848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54020714759827</t>
   </si>
   <si>
     <t xml:space="preserve">2.57367992401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7038516998291</t>
+    <t xml:space="preserve">2.70385146141052</t>
   </si>
   <si>
     <t xml:space="preserve">2.64806365966797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77451634407043</t>
+    <t xml:space="preserve">2.77451610565186</t>
   </si>
   <si>
     <t xml:space="preserve">2.70757079124451</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">2.80798888206482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83402323722839</t>
+    <t xml:space="preserve">2.83402299880981</t>
   </si>
   <si>
     <t xml:space="preserve">2.826584815979</t>
@@ -2390,13 +2390,13 @@
     <t xml:space="preserve">2.68525552749634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78939294815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80426979064941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75220084190369</t>
+    <t xml:space="preserve">2.78939318656921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80426955223083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75220108032227</t>
   </si>
   <si>
     <t xml:space="preserve">2.7001326084137</t>
@@ -2408,7 +2408,7 @@
     <t xml:space="preserve">2.76707792282104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73732447624207</t>
+    <t xml:space="preserve">2.73732423782349</t>
   </si>
   <si>
     <t xml:space="preserve">2.69641327857971</t>
@@ -2423,19 +2423,19 @@
     <t xml:space="preserve">2.69269394874573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62946796417236</t>
+    <t xml:space="preserve">2.62946772575378</t>
   </si>
   <si>
     <t xml:space="preserve">2.62574863433838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64062547683716</t>
+    <t xml:space="preserve">2.64062523841858</t>
   </si>
   <si>
     <t xml:space="preserve">2.65550208091736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61459112167358</t>
+    <t xml:space="preserve">2.614590883255</t>
   </si>
   <si>
     <t xml:space="preserve">2.60715270042419</t>
@@ -2450,28 +2450,28 @@
     <t xml:space="preserve">2.55508399009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45466589927673</t>
+    <t xml:space="preserve">2.45466566085815</t>
   </si>
   <si>
     <t xml:space="preserve">2.42491221427917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39515900611877</t>
+    <t xml:space="preserve">2.3951587677002</t>
   </si>
   <si>
     <t xml:space="preserve">2.40259718894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46954226493835</t>
+    <t xml:space="preserve">2.46954250335693</t>
   </si>
   <si>
     <t xml:space="preserve">2.33937096595764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23523378372192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25754904747009</t>
+    <t xml:space="preserve">2.23523354530334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25754880905151</t>
   </si>
   <si>
     <t xml:space="preserve">2.44722723960876</t>
@@ -2480,19 +2480,19 @@
     <t xml:space="preserve">2.38400101661682</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41747403144836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41375494003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43978905677795</t>
+    <t xml:space="preserve">2.41747379302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41375470161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43978881835938</t>
   </si>
   <si>
     <t xml:space="preserve">2.51417279243469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6108717918396</t>
+    <t xml:space="preserve">2.61087155342102</t>
   </si>
   <si>
     <t xml:space="preserve">2.61831021308899</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">2.77823543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9158456325531</t>
+    <t xml:space="preserve">2.91584539413452</t>
   </si>
   <si>
     <t xml:space="preserve">2.54392647743225</t>
@@ -2513,7 +2513,7 @@
     <t xml:space="preserve">2.56624174118042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49929618835449</t>
+    <t xml:space="preserve">2.49929594993591</t>
   </si>
   <si>
     <t xml:space="preserve">2.52904963493347</t>
@@ -2528,13 +2528,13 @@
     <t xml:space="preserve">2.58111810684204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59971404075623</t>
+    <t xml:space="preserve">2.5997142791748</t>
   </si>
   <si>
     <t xml:space="preserve">2.63690638542175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68530631065369</t>
+    <t xml:space="preserve">2.68530654907227</t>
   </si>
   <si>
     <t xml:space="preserve">2.66147232055664</t>
@@ -2543,7 +2543,7 @@
     <t xml:space="preserve">2.62969350814819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57408094406128</t>
+    <t xml:space="preserve">2.5740807056427</t>
   </si>
   <si>
     <t xml:space="preserve">2.51846790313721</t>
@@ -2555,7 +2555,7 @@
     <t xml:space="preserve">2.45491027832031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42710399627686</t>
+    <t xml:space="preserve">2.42710423469543</t>
   </si>
   <si>
     <t xml:space="preserve">2.51052331924438</t>
@@ -2564,13 +2564,13 @@
     <t xml:space="preserve">2.47079968452454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49066138267517</t>
+    <t xml:space="preserve">2.49066162109375</t>
   </si>
   <si>
     <t xml:space="preserve">2.53435730934143</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59791493415833</t>
+    <t xml:space="preserve">2.59791469573975</t>
   </si>
   <si>
     <t xml:space="preserve">2.55024671554565</t>
@@ -2579,7 +2579,7 @@
     <t xml:space="preserve">2.49463391304016</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47874450683594</t>
+    <t xml:space="preserve">2.47874426841736</t>
   </si>
   <si>
     <t xml:space="preserve">2.4588828086853</t>
@@ -2588,7 +2588,7 @@
     <t xml:space="preserve">2.39929747581482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41121482849121</t>
+    <t xml:space="preserve">2.41121459007263</t>
   </si>
   <si>
     <t xml:space="preserve">2.40724205970764</t>
@@ -2597,7 +2597,7 @@
     <t xml:space="preserve">2.4429931640625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42313146591187</t>
+    <t xml:space="preserve">2.42313170433044</t>
   </si>
   <si>
     <t xml:space="preserve">2.48668932914734</t>
@@ -2624,7 +2624,7 @@
     <t xml:space="preserve">2.3834080696106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39532518386841</t>
+    <t xml:space="preserve">2.39532542228699</t>
   </si>
   <si>
     <t xml:space="preserve">2.33176755905151</t>
@@ -2633,7 +2633,7 @@
     <t xml:space="preserve">2.37149095535278</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33573985099792</t>
+    <t xml:space="preserve">2.3357400894165</t>
   </si>
   <si>
     <t xml:space="preserve">2.35560154914856</t>
@@ -2648,7 +2648,7 @@
     <t xml:space="preserve">2.56613612174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52243995666504</t>
+    <t xml:space="preserve">2.52244019508362</t>
   </si>
   <si>
     <t xml:space="preserve">2.30396127700806</t>
@@ -2657,7 +2657,7 @@
     <t xml:space="preserve">2.28409957885742</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30793333053589</t>
+    <t xml:space="preserve">2.30793356895447</t>
   </si>
   <si>
     <t xml:space="preserve">2.28807163238525</t>
@@ -2669,22 +2669,22 @@
     <t xml:space="preserve">2.18479084968567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14506721496582</t>
+    <t xml:space="preserve">2.1450674533844</t>
   </si>
   <si>
     <t xml:space="preserve">2.11328864097595</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0576753616333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96631157398224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97822856903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98220086097717</t>
+    <t xml:space="preserve">2.05767560005188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96631169319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97822868824005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98220098018646</t>
   </si>
   <si>
     <t xml:space="preserve">2.08548212051392</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">2.2602653503418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58997011184692</t>
+    <t xml:space="preserve">2.5899703502655</t>
   </si>
   <si>
     <t xml:space="preserve">2.72900223731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7131130695343</t>
+    <t xml:space="preserve">2.71311283111572</t>
   </si>
   <si>
     <t xml:space="preserve">2.88392400741577</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">2.81242156028748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77269792556763</t>
+    <t xml:space="preserve">2.77269816398621</t>
   </si>
   <si>
     <t xml:space="preserve">2.74091958999634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70119595527649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82036638259888</t>
+    <t xml:space="preserve">2.70119571685791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8203661441803</t>
   </si>
   <si>
     <t xml:space="preserve">2.84420013427734</t>
@@ -2744,13 +2744,13 @@
     <t xml:space="preserve">2.84817266464233</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85611748695374</t>
+    <t xml:space="preserve">2.85611724853516</t>
   </si>
   <si>
     <t xml:space="preserve">2.78461527824402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87200665473938</t>
+    <t xml:space="preserve">2.87200689315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.85214495658875</t>
@@ -2762,7 +2762,7 @@
     <t xml:space="preserve">2.96337080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87597918510437</t>
+    <t xml:space="preserve">2.87597894668579</t>
   </si>
   <si>
     <t xml:space="preserve">2.9514536857605</t>
@@ -2789,7 +2789,7 @@
     <t xml:space="preserve">2.93159198760986</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86008954048157</t>
+    <t xml:space="preserve">2.86008977890015</t>
   </si>
   <si>
     <t xml:space="preserve">2.8283109664917</t>
@@ -2807,10 +2807,10 @@
     <t xml:space="preserve">2.95542621612549</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97528791427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95939826965332</t>
+    <t xml:space="preserve">2.97528767585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9593985080719</t>
   </si>
   <si>
     <t xml:space="preserve">2.99912190437317</t>
@@ -2819,7 +2819,7 @@
     <t xml:space="preserve">2.96734309196472</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88789629936218</t>
+    <t xml:space="preserve">2.8878960609436</t>
   </si>
   <si>
     <t xml:space="preserve">2.80447697639465</t>
@@ -2828,13 +2828,13 @@
     <t xml:space="preserve">2.82433867454529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80844950675964</t>
+    <t xml:space="preserve">2.80844926834106</t>
   </si>
   <si>
     <t xml:space="preserve">2.89186859130859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90775799751282</t>
+    <t xml:space="preserve">2.90775775909424</t>
   </si>
   <si>
     <t xml:space="preserve">2.92364740371704</t>
@@ -2849,19 +2849,19 @@
     <t xml:space="preserve">3.04679012298584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30896472930908</t>
+    <t xml:space="preserve">3.30896496772766</t>
   </si>
   <si>
     <t xml:space="preserve">3.17787766456604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05473470687866</t>
+    <t xml:space="preserve">3.05473494529724</t>
   </si>
   <si>
     <t xml:space="preserve">3.11829233169556</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04281783103943</t>
+    <t xml:space="preserve">3.04281759262085</t>
   </si>
   <si>
     <t xml:space="preserve">3.10637521743774</t>
@@ -2873,13 +2873,13 @@
     <t xml:space="preserve">3.0666515827179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07062411308289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76078104972839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78858757019043</t>
+    <t xml:space="preserve">3.07062387466431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76078081130981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78858733177185</t>
   </si>
   <si>
     <t xml:space="preserve">2.84022808074951</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">2.74886417388916</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69325137138367</t>
+    <t xml:space="preserve">2.69325113296509</t>
   </si>
   <si>
     <t xml:space="preserve">2.7568085193634</t>
@@ -2912,16 +2912,16 @@
     <t xml:space="preserve">2.81639409065247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99514961242676</t>
+    <t xml:space="preserve">2.99514937400818</t>
   </si>
   <si>
     <t xml:space="preserve">3.15404343605042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07459616661072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13815426826477</t>
+    <t xml:space="preserve">3.0745964050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13815402984619</t>
   </si>
   <si>
     <t xml:space="preserve">3.0825412273407</t>
@@ -2957,7 +2957,7 @@
     <t xml:space="preserve">3.2732138633728</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29307556152344</t>
+    <t xml:space="preserve">3.29307532310486</t>
   </si>
   <si>
     <t xml:space="preserve">3.23746252059937</t>
@@ -2966,10 +2966,10 @@
     <t xml:space="preserve">3.23349046707153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20965623855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25732445716858</t>
+    <t xml:space="preserve">3.20965647697449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25732421875</t>
   </si>
   <si>
     <t xml:space="preserve">3.2056839466095</t>
@@ -2978,13 +2978,13 @@
     <t xml:space="preserve">3.2136287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22554564476013</t>
+    <t xml:space="preserve">3.22554540634155</t>
   </si>
   <si>
     <t xml:space="preserve">3.19773936271667</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20171189308167</t>
+    <t xml:space="preserve">3.20171165466309</t>
   </si>
   <si>
     <t xml:space="preserve">3.26526927947998</t>
@@ -2996,10 +2996,10 @@
     <t xml:space="preserve">3.35266041755676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34471607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41224598884583</t>
+    <t xml:space="preserve">3.34471583366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41224575042725</t>
   </si>
   <si>
     <t xml:space="preserve">3.40827345848083</t>
@@ -3014,34 +3014,34 @@
     <t xml:space="preserve">3.69031047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69428277015686</t>
+    <t xml:space="preserve">3.69428253173828</t>
   </si>
   <si>
     <t xml:space="preserve">3.66647601127625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63866972923279</t>
+    <t xml:space="preserve">3.63866996765137</t>
   </si>
   <si>
     <t xml:space="preserve">3.51949906349182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45594167709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52347159385681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49169278144836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40430116653442</t>
+    <t xml:space="preserve">3.45594191551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52347183227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49169301986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.404301404953</t>
   </si>
   <si>
     <t xml:space="preserve">3.45196914672852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44005250930786</t>
+    <t xml:space="preserve">3.44005227088928</t>
   </si>
   <si>
     <t xml:space="preserve">3.34074378013611</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">3.33677101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32485437393188</t>
+    <t xml:space="preserve">3.32485413551331</t>
   </si>
   <si>
     <t xml:space="preserve">3.22157311439514</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">3.2811586856842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06267952919006</t>
+    <t xml:space="preserve">3.06267929077148</t>
   </si>
   <si>
     <t xml:space="preserve">3.08651351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18979454040527</t>
+    <t xml:space="preserve">3.18979430198669</t>
   </si>
   <si>
     <t xml:space="preserve">3.24937987327576</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">3.37252259254456</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24143481254578</t>
+    <t xml:space="preserve">3.24143505096436</t>
   </si>
   <si>
     <t xml:space="preserve">3.15007090568542</t>
@@ -3113,7 +3113,7 @@
     <t xml:space="preserve">3.16198801994324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07856869697571</t>
+    <t xml:space="preserve">3.07856893539429</t>
   </si>
   <si>
     <t xml:space="preserve">2.97131562232971</t>
@@ -3137,19 +3137,19 @@
     <t xml:space="preserve">3.11432003974915</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14212608337402</t>
+    <t xml:space="preserve">3.1421263217926</t>
   </si>
   <si>
     <t xml:space="preserve">3.18184995651245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17390489578247</t>
+    <t xml:space="preserve">3.17390513420105</t>
   </si>
   <si>
     <t xml:space="preserve">3.22951793670654</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03884553909302</t>
+    <t xml:space="preserve">3.03884530067444</t>
   </si>
   <si>
     <t xml:space="preserve">3.00309419631958</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">3.05076241493225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15801572799683</t>
+    <t xml:space="preserve">3.15801548957825</t>
   </si>
   <si>
     <t xml:space="preserve">3.21760106086731</t>
@@ -3176,10 +3176,10 @@
     <t xml:space="preserve">2.87995147705078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98720455169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03487277030945</t>
+    <t xml:space="preserve">2.98720479011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03487300872803</t>
   </si>
   <si>
     <t xml:space="preserve">2.91570258140564</t>
@@ -3188,7 +3188,7 @@
     <t xml:space="preserve">3.28513121604919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36060523986816</t>
+    <t xml:space="preserve">3.36060547828674</t>
   </si>
   <si>
     <t xml:space="preserve">3.37649464607239</t>
@@ -3200,10 +3200,10 @@
     <t xml:space="preserve">3.53141665458679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5790843963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42416286468506</t>
+    <t xml:space="preserve">3.57908463478088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42416310310364</t>
   </si>
   <si>
     <t xml:space="preserve">3.34868860244751</t>
@@ -3212,7 +3212,7 @@
     <t xml:space="preserve">3.35663294792175</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32088208198547</t>
+    <t xml:space="preserve">3.32088184356689</t>
   </si>
   <si>
     <t xml:space="preserve">3.40032911300659</t>
@@ -3236,7 +3236,7 @@
     <t xml:space="preserve">3.54333329200745</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54730606079102</t>
+    <t xml:space="preserve">3.54730582237244</t>
   </si>
   <si>
     <t xml:space="preserve">3.55127787590027</t>
@@ -3245,31 +3245,31 @@
     <t xml:space="preserve">3.63072538375854</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59100151062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67442107200623</t>
+    <t xml:space="preserve">3.5910017490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67442083358765</t>
   </si>
   <si>
     <t xml:space="preserve">3.61086320877075</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62278056144714</t>
+    <t xml:space="preserve">3.62278032302856</t>
   </si>
   <si>
     <t xml:space="preserve">3.67839336395264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65058660507202</t>
+    <t xml:space="preserve">3.6505868434906</t>
   </si>
   <si>
     <t xml:space="preserve">3.61880779266357</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6346971988678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58702898025513</t>
+    <t xml:space="preserve">3.63469696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58702874183655</t>
   </si>
   <si>
     <t xml:space="preserve">3.53936100006104</t>
@@ -8949,7 +8949,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="s">
-        <v>131</v>
+        <v>14</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8975,7 +8975,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G148" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -9001,7 +9001,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G149" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -9027,7 +9027,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -9079,7 +9079,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G152" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -9105,7 +9105,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G153" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -9131,7 +9131,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9157,7 +9157,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G155" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9183,7 +9183,7 @@
         <v>7.05130100250244</v>
       </c>
       <c r="G156" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -9235,7 +9235,7 @@
         <v>7.13032007217407</v>
       </c>
       <c r="G158" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9261,7 +9261,7 @@
         <v>7.04200410842896</v>
       </c>
       <c r="G159" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9287,7 +9287,7 @@
         <v>7.0048189163208</v>
       </c>
       <c r="G160" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9313,7 +9313,7 @@
         <v>6.93509578704834</v>
       </c>
       <c r="G161" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9339,7 +9339,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G162" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9365,7 +9365,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G163" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9391,7 +9391,7 @@
         <v>6.78170585632324</v>
       </c>
       <c r="G164" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9417,7 +9417,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G165" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9443,7 +9443,7 @@
         <v>6.88396596908569</v>
       </c>
       <c r="G166" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9469,7 +9469,7 @@
         <v>6.87002086639404</v>
       </c>
       <c r="G167" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9495,7 +9495,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9521,7 +9521,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9547,7 +9547,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G170" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9573,7 +9573,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G171" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9599,7 +9599,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G172" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9625,7 +9625,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9651,7 +9651,7 @@
         <v>6.79565000534058</v>
       </c>
       <c r="G174" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9677,7 +9677,7 @@
         <v>6.69803810119629</v>
       </c>
       <c r="G175" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9729,7 +9729,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9755,7 +9755,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G178" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9781,7 +9781,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G179" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9807,7 +9807,7 @@
         <v>6.242516040802</v>
       </c>
       <c r="G180" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9859,7 +9859,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G182" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9885,7 +9885,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9911,7 +9911,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9937,7 +9937,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9963,7 +9963,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G186" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9989,7 +9989,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G187" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -10015,7 +10015,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10041,7 +10041,7 @@
         <v>6.13095903396606</v>
       </c>
       <c r="G189" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -10093,7 +10093,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -10145,7 +10145,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G193" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10171,7 +10171,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G194" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10197,7 +10197,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G195" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10223,7 +10223,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10249,7 +10249,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G197" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10275,7 +10275,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G198" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10301,7 +10301,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10327,7 +10327,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10353,7 +10353,7 @@
         <v>5.99616193771362</v>
       </c>
       <c r="G201" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10379,7 +10379,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G202" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10405,7 +10405,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G203" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10431,7 +10431,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G204" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10457,7 +10457,7 @@
         <v>6.20532989501953</v>
       </c>
       <c r="G205" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10483,7 +10483,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10509,7 +10509,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10535,7 +10535,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G208" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10561,7 +10561,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10613,7 +10613,7 @@
         <v>6.65155601501465</v>
       </c>
       <c r="G211" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10639,7 +10639,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G212" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10665,7 +10665,7 @@
         <v>6.52140712738037</v>
       </c>
       <c r="G213" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10717,7 +10717,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10743,7 +10743,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G216" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10769,7 +10769,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10795,7 +10795,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G218" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10821,7 +10821,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10847,7 +10847,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G220" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10873,7 +10873,7 @@
         <v>6.34477615356445</v>
       </c>
       <c r="G221" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10899,7 +10899,7 @@
         <v>6.29364585876465</v>
       </c>
       <c r="G222" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10925,7 +10925,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G223" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10951,7 +10951,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10977,7 +10977,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11003,7 +11003,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11029,7 +11029,7 @@
         <v>6.07053279876709</v>
       </c>
       <c r="G227" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11055,7 +11055,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G228" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -11081,7 +11081,7 @@
         <v>5.74516010284424</v>
       </c>
       <c r="G229" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -11107,7 +11107,7 @@
         <v>5.88460493087769</v>
       </c>
       <c r="G230" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11133,7 +11133,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11159,7 +11159,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11185,7 +11185,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11211,7 +11211,7 @@
         <v>5.81023406982422</v>
       </c>
       <c r="G234" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11237,7 +11237,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11263,7 +11263,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11289,7 +11289,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11315,7 +11315,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11341,7 +11341,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11367,7 +11367,7 @@
         <v>6.14490413665771</v>
       </c>
       <c r="G240" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11393,7 +11393,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11419,7 +11419,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11445,7 +11445,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G243" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11471,7 +11471,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G244" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11523,7 +11523,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G246" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11601,7 +11601,7 @@
         <v>6.57718515396118</v>
       </c>
       <c r="G249" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11627,7 +11627,7 @@
         <v>6.53070402145386</v>
       </c>
       <c r="G250" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11653,7 +11653,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G251" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11679,7 +11679,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11705,7 +11705,7 @@
         <v>6.67479705810547</v>
       </c>
       <c r="G253" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11731,7 +11731,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G254" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11757,7 +11757,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11783,7 +11783,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11809,7 +11809,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G257" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11835,7 +11835,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G258" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11913,7 +11913,7 @@
         <v>7.05594921112061</v>
       </c>
       <c r="G261" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11965,7 +11965,7 @@
         <v>6.91650295257568</v>
       </c>
       <c r="G263" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11991,7 +11991,7 @@
         <v>7.00946712493896</v>
       </c>
       <c r="G264" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12017,7 +12017,7 @@
         <v>7.02341079711914</v>
       </c>
       <c r="G265" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12069,7 +12069,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G267" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12095,7 +12095,7 @@
         <v>6.94903993606567</v>
       </c>
       <c r="G268" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -12121,7 +12121,7 @@
         <v>6.88861417770386</v>
       </c>
       <c r="G269" t="s">
-        <v>67</v>
+        <v>217</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -12355,7 +12355,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12537,7 +12537,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12641,7 +12641,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G289" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12667,7 +12667,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G290" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12719,7 +12719,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G292" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12745,7 +12745,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G293" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12771,7 +12771,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G294" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12901,7 +12901,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G299" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12953,7 +12953,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G301" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13057,7 +13057,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G305" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -13083,7 +13083,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G306" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -13109,7 +13109,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13213,7 +13213,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -71513,7 +71513,7 @@
     </row>
     <row r="2554">
       <c r="A2554" s="1" t="n">
-        <v>46042.6910763889</v>
+        <v>46042.3333333333</v>
       </c>
       <c r="B2554" t="n">
         <v>156457</v>
@@ -71534,6 +71534,32 @@
         <v>1575</v>
       </c>
       <c r="H2554" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2555">
+      <c r="A2555" s="1" t="n">
+        <v>46043.6911458333</v>
+      </c>
+      <c r="B2555" t="n">
+        <v>217231</v>
+      </c>
+      <c r="C2555" t="n">
+        <v>3.52999997138977</v>
+      </c>
+      <c r="D2555" t="n">
+        <v>3.47499990463257</v>
+      </c>
+      <c r="E2555" t="n">
+        <v>3.51500010490417</v>
+      </c>
+      <c r="F2555" t="n">
+        <v>3.50999999046326</v>
+      </c>
+      <c r="G2555" t="s">
+        <v>1577</v>
+      </c>
+      <c r="H2555" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72976970672607</t>
+    <t xml:space="preserve">4.72976922988892</t>
   </si>
   <si>
     <t xml:space="preserve">IGD.MI</t>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">4.81178855895996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76804447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76531076431274</t>
+    <t xml:space="preserve">4.76804494857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7653112411499</t>
   </si>
   <si>
     <t xml:space="preserve">4.64775037765503</t>
@@ -62,82 +62,82 @@
     <t xml:space="preserve">4.56573104858398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67235565185547</t>
+    <t xml:space="preserve">4.67235612869263</t>
   </si>
   <si>
     <t xml:space="preserve">4.55206108093262</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33334302902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16383695602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04627656936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60884165763855</t>
+    <t xml:space="preserve">4.33334350585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16383743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04627752304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60884189605713</t>
   </si>
   <si>
     <t xml:space="preserve">3.88223838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95605492591858</t>
+    <t xml:space="preserve">3.9560546875</t>
   </si>
   <si>
     <t xml:space="preserve">4.03807497024536</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97519326210022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785356521606</t>
+    <t xml:space="preserve">3.97519302368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9478542804718</t>
   </si>
   <si>
     <t xml:space="preserve">3.813889503479</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96425747871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07088279724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92051386833191</t>
+    <t xml:space="preserve">3.96425771713257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07088232040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92051434516907</t>
   </si>
   <si>
     <t xml:space="preserve">3.69632887840271</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78654932975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45573878288269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49948215484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69086003303528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56783199310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63891506195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497304916382</t>
+    <t xml:space="preserve">3.78654980659485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45573902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49948239326477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69086050987244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56783246994019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63891577720642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497257232666</t>
   </si>
   <si>
     <t xml:space="preserve">3.82755923271179</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93691778182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87130308151245</t>
+    <t xml:space="preserve">3.93691730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87130212783813</t>
   </si>
   <si>
     <t xml:space="preserve">4.05994701385498</t>
@@ -146,19 +146,19 @@
     <t xml:space="preserve">4.00800132751465</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95332169532776</t>
+    <t xml:space="preserve">3.95332193374634</t>
   </si>
   <si>
     <t xml:space="preserve">3.98612976074219</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99159717559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0326075553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05447816848755</t>
+    <t xml:space="preserve">3.99159741401672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03260660171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05447864532471</t>
   </si>
   <si>
     <t xml:space="preserve">4.2403883934021</t>
@@ -167,37 +167,37 @@
     <t xml:space="preserve">4.21031475067139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37435340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33607769012451</t>
+    <t xml:space="preserve">4.37435293197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33607721328735</t>
   </si>
   <si>
     <t xml:space="preserve">4.34701299667358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33881139755249</t>
+    <t xml:space="preserve">4.33881187438965</t>
   </si>
   <si>
     <t xml:space="preserve">4.42903232574463</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52745628356934</t>
+    <t xml:space="preserve">4.52745580673218</t>
   </si>
   <si>
     <t xml:space="preserve">4.51105213165283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46184015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5711989402771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67508983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60947513580322</t>
+    <t xml:space="preserve">4.46183967590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57119989395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67509031295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60947418212891</t>
   </si>
   <si>
     <t xml:space="preserve">4.54932689666748</t>
@@ -209,472 +209,472 @@
     <t xml:space="preserve">4.34974765777588</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42083120346069</t>
+    <t xml:space="preserve">4.42083024978638</t>
   </si>
   <si>
     <t xml:space="preserve">4.42356538772583</t>
   </si>
   <si>
+    <t xml:space="preserve">4.26499462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22398471832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22671890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33060884475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40169239044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31967401504517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30600452423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36615133285522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26772832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32514190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29233503341675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27046203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29506826400757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39895868301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30873775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38802242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42629909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34427976608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39075708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30326986312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49522399902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57292556762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65062808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69091892242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67940664291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69379663467407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66214036941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61609363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57580327987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63623857498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63048362731934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63336133956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63911628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56429195404053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35133075714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066560745239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08368873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95130705833435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97145175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16139125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20168161392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.247727394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27650594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03476524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755875587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84482645988464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633730888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470378875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01749801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784887313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83619260787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96281886100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05778932571411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0923228263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25636053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40313196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33406400680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51824712753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41752147674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45493364334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45781183242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53839206695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52975845336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48946762084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51536846160889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25923919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38874244689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4664454460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3829870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36571979522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41464328765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35996341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33694076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29377269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3139181137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19016981124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19880390167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22182655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2621169090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25348281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23046064376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14412355422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19592571258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16714668273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15563535690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11534547805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20743703842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14700174331665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17865800857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07505559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9426736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79878067970276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77575778961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83907055854797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74697828292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7498562335968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85921597480774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82468104362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79590201377869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87936115264893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81029152870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76424622535706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72971129417419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71244430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72395539283752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84194827079773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735331535339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06354379653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10959005355835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11822366714478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08656740188599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03764343261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00310897827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97432994842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91389465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93979549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92540597915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92828369140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89662742614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84770441055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273442268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75849056243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55704021453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64337563514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66927695274353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65776515007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58006191253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59732985496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60308599472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63186430931091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62610840797424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6606433391571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61459732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80453634262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95994019508362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07217693328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04339933395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12685680389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13261222839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12110137939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36859750747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28226137161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33981895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34845209121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33118534088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30240678787231</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.2649941444397</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25405883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22398471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22671890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23765468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33060932159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40169286727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31967401504517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3060040473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36615180969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26772928237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32514190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29233407974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27046203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29506778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39895868301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30873823165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38802242279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42629909515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34427976608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39075708389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30326986312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49522304534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57292652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65062808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091844558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67940664291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69379615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66213989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61609363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57580375671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63623857498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63048315048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63336086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63911628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56429195404053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35133028030396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08368921279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95130729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9714527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16139125823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20168161392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.247727394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27650594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03476572036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755875587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84482645988464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633754730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15851306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01749801635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784887313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83619260787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96281838417053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05778837203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0923228263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25636053085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40313243865967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33406352996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51824712753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41752099990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45493364334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37435388565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45781135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53839206695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52975749969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48946857452393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51536846160889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25923871994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38874340057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46644449234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38298654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36571884155273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41464328765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35996389389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33694076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29377222061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31391763687134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19017028808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19880342483521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22182607650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2621169090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25348281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23046016693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14412403106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19592523574829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16714668273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15563583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11534547805786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20743703842163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14700174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1786584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07505512237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94267392158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497187614441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79878044128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77575755119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83907079696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7469789981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74985694885254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85921621322632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82468152046204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79590249061584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87936091423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81029152870178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76424598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72971177101135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7124445438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72395586967468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84194779396057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735283851624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06354427337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10958909988403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11822319030762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08656692504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03764295578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00310897827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97433042526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91389489173889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93979549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92540621757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92828440666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89662766456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84770393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273466110229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75849032402039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55703997612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64337515830994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66927599906921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65776491165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58006262779236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59733033180237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60308575630188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63186454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6261088848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66064381599426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61459708213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80453634262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95994067192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07217741012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04339933395386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12685680389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13261270523071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12110137939453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36859750747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28226184844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33981943130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34845209121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33118486404419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30240631103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27075004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2275824546814</t>
+    <t xml:space="preserve">4.27074956893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22758197784424</t>
   </si>
   <si>
     <t xml:space="preserve">4.2131929397583</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">4.18153619766235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09807825088501</t>
+    <t xml:space="preserve">4.09807872772217</t>
   </si>
   <si>
     <t xml:space="preserve">4.00598669052124</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">4.10383415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02900981903076</t>
+    <t xml:space="preserve">4.0290093421936</t>
   </si>
   <si>
     <t xml:space="preserve">4.06929969787598</t>
@@ -701,46 +701,46 @@
     <t xml:space="preserve">4.21894836425781</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30816173553467</t>
+    <t xml:space="preserve">4.30816268920898</t>
   </si>
   <si>
     <t xml:space="preserve">4.14987993240356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47220039367676</t>
+    <t xml:space="preserve">4.47220087051392</t>
   </si>
   <si>
     <t xml:space="preserve">4.51249074935913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37723112106323</t>
+    <t xml:space="preserve">4.37723064422607</t>
   </si>
   <si>
     <t xml:space="preserve">4.44342231750488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59307146072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62472772598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5700478553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71969652175903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70818567276001</t>
+    <t xml:space="preserve">4.5930700302124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62472677230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57004833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71969699859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70818519592285</t>
   </si>
   <si>
     <t xml:space="preserve">4.80315446853638</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73120832443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7053074836731</t>
+    <t xml:space="preserve">4.73120784759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70530843734741</t>
   </si>
   <si>
     <t xml:space="preserve">4.70242977142334</t>
@@ -752,34 +752,34 @@
     <t xml:space="preserve">4.62184953689575</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54702520370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52687978744507</t>
+    <t xml:space="preserve">4.54702472686768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52688074111938</t>
   </si>
   <si>
     <t xml:space="preserve">4.46068906784058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6045823097229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71394109725952</t>
+    <t xml:space="preserve">4.60458183288574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71394062042236</t>
   </si>
   <si>
     <t xml:space="preserve">4.66501760482788</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74559783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76574277877808</t>
+    <t xml:space="preserve">4.74559736251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76574325561523</t>
   </si>
   <si>
     <t xml:space="preserve">4.74847555160522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78300952911377</t>
+    <t xml:space="preserve">4.78301000595093</t>
   </si>
   <si>
     <t xml:space="preserve">4.77149820327759</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">4.92690324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94992589950562</t>
+    <t xml:space="preserve">4.94992637634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.98446035385132</t>
@@ -800,7 +800,7 @@
     <t xml:space="preserve">5.02475070953369</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05640745162964</t>
+    <t xml:space="preserve">5.05640697479248</t>
   </si>
   <si>
     <t xml:space="preserve">4.89236879348755</t>
@@ -809,40 +809,40 @@
     <t xml:space="preserve">4.86359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82905626296997</t>
+    <t xml:space="preserve">4.82905530929565</t>
   </si>
   <si>
     <t xml:space="preserve">4.87592363357544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91160106658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93538618087769</t>
+    <t xml:space="preserve">4.91160154342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93538570404053</t>
   </si>
   <si>
     <t xml:space="preserve">4.89970874786377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92052125930786</t>
+    <t xml:space="preserve">4.9205207824707</t>
   </si>
   <si>
     <t xml:space="preserve">5.01268720626831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96809053421021</t>
+    <t xml:space="preserve">4.96809101104736</t>
   </si>
   <si>
     <t xml:space="preserve">4.9710636138916</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89376211166382</t>
+    <t xml:space="preserve">4.89376258850098</t>
   </si>
   <si>
     <t xml:space="preserve">4.94727849960327</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94133234024048</t>
+    <t xml:space="preserve">4.94133281707764</t>
   </si>
   <si>
     <t xml:space="preserve">4.92944002151489</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">4.88781642913818</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85511207580566</t>
+    <t xml:space="preserve">4.85511159896851</t>
   </si>
   <si>
     <t xml:space="preserve">4.79862260818481</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">4.77186441421509</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75105237960815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78672981262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73321437835693</t>
+    <t xml:space="preserve">4.75105285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78673076629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73321390151978</t>
   </si>
   <si>
     <t xml:space="preserve">4.66185903549194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53401517868042</t>
+    <t xml:space="preserve">4.53401470184326</t>
   </si>
   <si>
     <t xml:space="preserve">4.58455753326416</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">4.61726188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70348310470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72132110595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63807439804077</t>
+    <t xml:space="preserve">4.70348262786865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72132158279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63807392120361</t>
   </si>
   <si>
     <t xml:space="preserve">4.72726726531982</t>
@@ -896,22 +896,22 @@
     <t xml:space="preserve">4.81646156311035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83132696151733</t>
+    <t xml:space="preserve">4.83132743835449</t>
   </si>
   <si>
     <t xml:space="preserve">4.93835973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94430589675903</t>
+    <t xml:space="preserve">4.94430541992188</t>
   </si>
   <si>
     <t xml:space="preserve">4.98295640945435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95322513580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.90565538406372</t>
+    <t xml:space="preserve">4.95322561264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.90565490722656</t>
   </si>
   <si>
     <t xml:space="preserve">4.84619283676147</t>
@@ -926,19 +926,19 @@
     <t xml:space="preserve">5.05431127548218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04836511611938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99782180786133</t>
+    <t xml:space="preserve">5.04836559295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99782133102417</t>
   </si>
   <si>
     <t xml:space="preserve">4.98592948913574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15837049484253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.12566709518433</t>
+    <t xml:space="preserve">5.15837097167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.12566661834717</t>
   </si>
   <si>
     <t xml:space="preserve">5.11080074310303</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">5.07512283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08106994628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09593534469604</t>
+    <t xml:space="preserve">5.08106899261475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09593486785889</t>
   </si>
   <si>
     <t xml:space="preserve">5.11377382278442</t>
@@ -959,28 +959,28 @@
     <t xml:space="preserve">5.03944540023804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02755308151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97700977325439</t>
+    <t xml:space="preserve">5.02755355834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97701025009155</t>
   </si>
   <si>
     <t xml:space="preserve">5.05133867263794</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99484920501709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01566123962402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06620359420776</t>
+    <t xml:space="preserve">4.99484825134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01566076278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.06620454788208</t>
   </si>
   <si>
     <t xml:space="preserve">5.13755893707275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23269844055176</t>
+    <t xml:space="preserve">5.23269891738892</t>
   </si>
   <si>
     <t xml:space="preserve">5.2445912361145</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">5.23864555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19702196121216</t>
+    <t xml:space="preserve">5.197021484375</t>
   </si>
   <si>
     <t xml:space="preserve">5.17323637008667</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">5.1851282119751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20891380310059</t>
+    <t xml:space="preserve">5.20891427993774</t>
   </si>
   <si>
     <t xml:space="preserve">5.1940484046936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24756383895874</t>
+    <t xml:space="preserve">5.24756479263306</t>
   </si>
   <si>
     <t xml:space="preserve">5.25053739547729</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">5.16431713104248</t>
   </si>
   <si>
-    <t xml:space="preserve">5.21485948562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35162401199341</t>
+    <t xml:space="preserve">5.21485996246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35162353515625</t>
   </si>
   <si>
     <t xml:space="preserve">5.44081687927246</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">5.67866706848145</t>
   </si>
   <si>
-    <t xml:space="preserve">5.47054815292358</t>
+    <t xml:space="preserve">5.47054862976074</t>
   </si>
   <si>
     <t xml:space="preserve">5.46757507324219</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">5.58947372436523</t>
   </si>
   <si>
-    <t xml:space="preserve">5.5032525062561</t>
+    <t xml:space="preserve">5.50325298309326</t>
   </si>
   <si>
     <t xml:space="preserve">5.57758140563965</t>
@@ -1064,19 +1064,19 @@
     <t xml:space="preserve">5.91651821136475</t>
   </si>
   <si>
-    <t xml:space="preserve">6.20193767547607</t>
+    <t xml:space="preserve">6.20193815231323</t>
   </si>
   <si>
     <t xml:space="preserve">6.19004535675049</t>
   </si>
   <si>
-    <t xml:space="preserve">6.11274337768555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.12463617324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15436840057373</t>
+    <t xml:space="preserve">6.11274385452271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.12463569641113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15436792373657</t>
   </si>
   <si>
     <t xml:space="preserve">6.03544235229492</t>
@@ -1091,58 +1091,58 @@
     <t xml:space="preserve">6.00571155548096</t>
   </si>
   <si>
-    <t xml:space="preserve">6.29113054275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.34464740753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17815208435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39816331863403</t>
+    <t xml:space="preserve">6.29113101959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.3446478843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17815256118774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39816379547119</t>
   </si>
   <si>
     <t xml:space="preserve">6.38627099990845</t>
   </si>
   <si>
-    <t xml:space="preserve">6.33275508880615</t>
+    <t xml:space="preserve">6.33275461196899</t>
   </si>
   <si>
     <t xml:space="preserve">6.43384075164795</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46951866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41600275039673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40410900115967</t>
+    <t xml:space="preserve">6.46951818466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41600227355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40410947799683</t>
   </si>
   <si>
     <t xml:space="preserve">6.24356126785278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35653924942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44573497772217</t>
+    <t xml:space="preserve">6.35653972625732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44573402404785</t>
   </si>
   <si>
     <t xml:space="preserve">6.60033655166626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.58844327926636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71926069259644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65979909896851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48141145706177</t>
+    <t xml:space="preserve">6.58844375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71926116943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65979862213135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48141098022461</t>
   </si>
   <si>
     <t xml:space="preserve">6.07111978530884</t>
@@ -1154,43 +1154,43 @@
     <t xml:space="preserve">5.76786088943481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80948495864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68164014816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73812961578369</t>
+    <t xml:space="preserve">5.80948448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.681640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73812913894653</t>
   </si>
   <si>
     <t xml:space="preserve">5.81840419769287</t>
   </si>
   <si>
-    <t xml:space="preserve">5.7321834564209</t>
+    <t xml:space="preserve">5.73218488693237</t>
   </si>
   <si>
     <t xml:space="preserve">5.72623682022095</t>
   </si>
   <si>
-    <t xml:space="preserve">5.85705518722534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86300182342529</t>
+    <t xml:space="preserve">5.8570556640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86300134658813</t>
   </si>
   <si>
     <t xml:space="preserve">5.95814085006714</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92840957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76191520690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7975926399231</t>
+    <t xml:space="preserve">5.92841005325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76191473007202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70839834213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79759216308594</t>
   </si>
   <si>
     <t xml:space="preserve">5.75596857070923</t>
@@ -1199,13 +1199,13 @@
     <t xml:space="preserve">5.6846137046814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6965069770813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.66082906723022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.50622653961182</t>
+    <t xml:space="preserve">5.69650650024414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.66082811355591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50622701644897</t>
   </si>
   <si>
     <t xml:space="preserve">5.45865631103516</t>
@@ -1214,10 +1214,10 @@
     <t xml:space="preserve">5.33973121643066</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15539741516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.3100004196167</t>
+    <t xml:space="preserve">5.15539646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.30999994277954</t>
   </si>
   <si>
     <t xml:space="preserve">5.03647232055664</t>
@@ -1229,25 +1229,25 @@
     <t xml:space="preserve">5.00079536437988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86997747421265</t>
+    <t xml:space="preserve">4.86997699737549</t>
   </si>
   <si>
     <t xml:space="preserve">4.85213899612427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14350461959839</t>
+    <t xml:space="preserve">5.14350509643555</t>
   </si>
   <si>
     <t xml:space="preserve">4.75699853897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79445934295654</t>
+    <t xml:space="preserve">4.7944598197937</t>
   </si>
   <si>
     <t xml:space="preserve">4.70823955535889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58812522888184</t>
+    <t xml:space="preserve">4.58812475204468</t>
   </si>
   <si>
     <t xml:space="preserve">4.47752571105957</t>
@@ -1256,13 +1256,13 @@
     <t xml:space="preserve">4.46860551834106</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53104162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66483211517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66839981079102</t>
+    <t xml:space="preserve">4.53104114532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66483163833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66839933395386</t>
   </si>
   <si>
     <t xml:space="preserve">4.55482625961304</t>
@@ -1271,19 +1271,19 @@
     <t xml:space="preserve">4.49774217605591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51260805130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41211652755737</t>
+    <t xml:space="preserve">4.51260757446289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41211605072021</t>
   </si>
   <si>
     <t xml:space="preserve">4.36811399459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29913806915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48525524139404</t>
+    <t xml:space="preserve">4.29913759231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48525619506836</t>
   </si>
   <si>
     <t xml:space="preserve">4.46503782272339</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">4.57336091995239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6545934677124</t>
+    <t xml:space="preserve">4.65459394454956</t>
   </si>
   <si>
     <t xml:space="preserve">5.10297536849976</t>
@@ -1313,22 +1313,22 @@
     <t xml:space="preserve">4.95713901519775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14391136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34731340408325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28271102905273</t>
+    <t xml:space="preserve">5.14391183853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34731388092041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28271150588989</t>
   </si>
   <si>
     <t xml:space="preserve">5.17781209945679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01278686523438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96993207931519</t>
+    <t xml:space="preserve">5.01278734207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96993160247803</t>
   </si>
   <si>
     <t xml:space="preserve">5.05244445800781</t>
@@ -1340,7 +1340,7 @@
     <t xml:space="preserve">4.94498634338379</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03197622299194</t>
+    <t xml:space="preserve">5.03197526931763</t>
   </si>
   <si>
     <t xml:space="preserve">5.0159854888916</t>
@@ -1349,40 +1349,40 @@
     <t xml:space="preserve">5.02621936798096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01470565795898</t>
+    <t xml:space="preserve">5.0147066116333</t>
   </si>
   <si>
     <t xml:space="preserve">5.08506536483765</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93539190292358</t>
+    <t xml:space="preserve">4.93539142608643</t>
   </si>
   <si>
     <t xml:space="preserve">4.92579746246338</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96545457839966</t>
+    <t xml:space="preserve">4.9654541015625</t>
   </si>
   <si>
     <t xml:space="preserve">5.02557945251465</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04029178619385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02110195159912</t>
+    <t xml:space="preserve">5.04029083251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02110242843628</t>
   </si>
   <si>
     <t xml:space="preserve">5.11704730987549</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05947971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.06971454620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24497318267822</t>
+    <t xml:space="preserve">5.0594801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0697135925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24497270584106</t>
   </si>
   <si>
     <t xml:space="preserve">5.14135265350342</t>
@@ -1400,10 +1400,10 @@
     <t xml:space="preserve">4.78124094009399</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73326826095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71471881866455</t>
+    <t xml:space="preserve">4.73326873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71471929550171</t>
   </si>
   <si>
     <t xml:space="preserve">4.66290903091431</t>
@@ -1412,19 +1412,19 @@
     <t xml:space="preserve">4.55097341537476</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32710313796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57400035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65267467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63092756271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72943067550659</t>
+    <t xml:space="preserve">4.32710266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57399988174438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65267562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63092708587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72943019866943</t>
   </si>
   <si>
     <t xml:space="preserve">4.81961822509766</t>
@@ -1433,13 +1433,13 @@
     <t xml:space="preserve">4.79403305053711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68401718139648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58679294586182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8741979598999</t>
+    <t xml:space="preserve">4.68401670455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58679246902466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87419843673706</t>
   </si>
   <si>
     <t xml:space="preserve">4.99108505249023</t>
@@ -1448,7 +1448,7 @@
     <t xml:space="preserve">4.88932466506958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9842095375061</t>
+    <t xml:space="preserve">4.98421001434326</t>
   </si>
   <si>
     <t xml:space="preserve">5.03165197372437</t>
@@ -1457,37 +1457,37 @@
     <t xml:space="preserve">4.79375219345093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79512739181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76074886322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74630928039551</t>
+    <t xml:space="preserve">4.79512691497803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76074838638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74630975723267</t>
   </si>
   <si>
     <t xml:space="preserve">4.86113452911377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79031467437744</t>
+    <t xml:space="preserve">4.79031419754028</t>
   </si>
   <si>
     <t xml:space="preserve">4.81300401687622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72705745697021</t>
+    <t xml:space="preserve">4.72705793380737</t>
   </si>
   <si>
     <t xml:space="preserve">4.77174949645996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73187065124512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84532022476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7868766784668</t>
+    <t xml:space="preserve">4.73187112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8453197479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78687620162964</t>
   </si>
   <si>
     <t xml:space="preserve">4.76968669891357</t>
@@ -1502,22 +1502,22 @@
     <t xml:space="preserve">4.96770763397217</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8267560005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85013294219971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86044645309448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89963865280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9347038269043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99177312850952</t>
+    <t xml:space="preserve">4.82675552368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85013246536255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86044692993164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89963817596436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93470430374146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99177265167236</t>
   </si>
   <si>
     <t xml:space="preserve">5.05434226989746</t>
@@ -1529,22 +1529,22 @@
     <t xml:space="preserve">4.9793963432312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99246072769165</t>
+    <t xml:space="preserve">4.99245977401733</t>
   </si>
   <si>
     <t xml:space="preserve">4.8583836555481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98489713668823</t>
+    <t xml:space="preserve">4.98489761352539</t>
   </si>
   <si>
     <t xml:space="preserve">4.85219573974609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90307569503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97183275222778</t>
+    <t xml:space="preserve">4.903076171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9718337059021</t>
   </si>
   <si>
     <t xml:space="preserve">4.93882989883423</t>
@@ -1553,13 +1553,13 @@
     <t xml:space="preserve">4.91682767868042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83363199234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76556158065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75868558883667</t>
+    <t xml:space="preserve">4.83363151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76556205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75868606567383</t>
   </si>
   <si>
     <t xml:space="preserve">4.75043487548828</t>
@@ -1568,7 +1568,7 @@
     <t xml:space="preserve">4.67067718505859</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5812931060791</t>
+    <t xml:space="preserve">4.58129262924194</t>
   </si>
   <si>
     <t xml:space="preserve">4.5427885055542</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">4.51941061019897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60604429244995</t>
+    <t xml:space="preserve">4.60604476928711</t>
   </si>
   <si>
     <t xml:space="preserve">4.59779405593872</t>
@@ -1595,28 +1595,28 @@
     <t xml:space="preserve">4.5379753112793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57922983169556</t>
+    <t xml:space="preserve">4.5792293548584</t>
   </si>
   <si>
     <t xml:space="preserve">4.55172681808472</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57235431671143</t>
+    <t xml:space="preserve">4.57235383987427</t>
   </si>
   <si>
     <t xml:space="preserve">4.55241441726685</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50634670257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51597309112549</t>
+    <t xml:space="preserve">4.50634717941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51597261428833</t>
   </si>
   <si>
     <t xml:space="preserve">4.49053287506104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52078628540039</t>
+    <t xml:space="preserve">4.52078676223755</t>
   </si>
   <si>
     <t xml:space="preserve">4.518723487854</t>
@@ -1634,16 +1634,16 @@
     <t xml:space="preserve">4.485032081604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47746896743774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78412580490112</t>
+    <t xml:space="preserve">4.47746849060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78412628173828</t>
   </si>
   <si>
     <t xml:space="preserve">4.6651759147644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6541748046875</t>
+    <t xml:space="preserve">4.65417528152466</t>
   </si>
   <si>
     <t xml:space="preserve">4.70299291610718</t>
@@ -1655,22 +1655,22 @@
     <t xml:space="preserve">4.71055555343628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64661121368408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63354825973511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55035161972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50840997695923</t>
+    <t xml:space="preserve">4.64661169052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63354730606079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5503511428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50840902328491</t>
   </si>
   <si>
     <t xml:space="preserve">4.41558742523193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42727613449097</t>
+    <t xml:space="preserve">4.42727661132812</t>
   </si>
   <si>
     <t xml:space="preserve">4.40046072006226</t>
@@ -1682,25 +1682,25 @@
     <t xml:space="preserve">4.22237968444824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20450258255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16256046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0663013458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09311628341675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98791742324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05942535400391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09724187850952</t>
+    <t xml:space="preserve">4.20450305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16256093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06630086898804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09311676025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98791766166687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05942487716675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09724140167236</t>
   </si>
   <si>
     <t xml:space="preserve">4.0497989654541</t>
@@ -1715,22 +1715,22 @@
     <t xml:space="preserve">4.09105348587036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08830308914185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13162040710449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21962976455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28563642501831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29732513427734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28976154327393</t>
+    <t xml:space="preserve">4.088303565979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13161993026733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21962928771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28563594818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29732465744019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28976106643677</t>
   </si>
   <si>
     <t xml:space="preserve">4.22100496292114</t>
@@ -1739,19 +1739,19 @@
     <t xml:space="preserve">4.15293502807617</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36608266830444</t>
+    <t xml:space="preserve">4.36608219146729</t>
   </si>
   <si>
     <t xml:space="preserve">4.27601051330566</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22513008117676</t>
+    <t xml:space="preserve">4.2251296043396</t>
   </si>
   <si>
     <t xml:space="preserve">4.1948766708374</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12749433517456</t>
+    <t xml:space="preserve">4.12749481201172</t>
   </si>
   <si>
     <t xml:space="preserve">4.15224742889404</t>
@@ -1760,25 +1760,25 @@
     <t xml:space="preserve">4.13505840301514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09174108505249</t>
+    <t xml:space="preserve">4.09174060821533</t>
   </si>
   <si>
     <t xml:space="preserve">4.0326099395752</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03467226028442</t>
+    <t xml:space="preserve">4.03467273712158</t>
   </si>
   <si>
     <t xml:space="preserve">4.054612159729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14537191390991</t>
+    <t xml:space="preserve">4.14537143707275</t>
   </si>
   <si>
     <t xml:space="preserve">4.2237548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23544311523438</t>
+    <t xml:space="preserve">4.23544359207153</t>
   </si>
   <si>
     <t xml:space="preserve">4.19900226593018</t>
@@ -1793,61 +1793,61 @@
     <t xml:space="preserve">4.04429817199707</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02917242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99273109436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99891877174377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96316528320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88684463500977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.982417345047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90540885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87378072738647</t>
+    <t xml:space="preserve">4.02917289733887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99273085594177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99891901016235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96316480636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88684487342834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98241662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90540862083435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87378096580505</t>
   </si>
   <si>
     <t xml:space="preserve">3.78164601325989</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71013832092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69501256942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73351573944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72870254516602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64894461631775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70051264762878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83115100860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89990878105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99341821670532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97829151153564</t>
+    <t xml:space="preserve">3.71013855934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69501233100891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7335159778595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72870278358459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64894509315491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70051288604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83115172386169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89990854263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99341797828674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97829174995422</t>
   </si>
   <si>
     <t xml:space="preserve">4.06286287307739</t>
@@ -1856,19 +1856,19 @@
     <t xml:space="preserve">4.04842376708984</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06767654418945</t>
+    <t xml:space="preserve">4.06767606735229</t>
   </si>
   <si>
     <t xml:space="preserve">4.04292392730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99548077583313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95491433143616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04086112976074</t>
+    <t xml:space="preserve">3.99548053741455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95491409301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04086065292358</t>
   </si>
   <si>
     <t xml:space="preserve">4.02160882949829</t>
@@ -1877,7 +1877,7 @@
     <t xml:space="preserve">4.05804967880249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0133581161499</t>
+    <t xml:space="preserve">4.01335763931274</t>
   </si>
   <si>
     <t xml:space="preserve">3.97004103660583</t>
@@ -1886,34 +1886,34 @@
     <t xml:space="preserve">4.07180118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11786890029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22788047790527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31864023208618</t>
+    <t xml:space="preserve">4.11786842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22788000106812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31863975524902</t>
   </si>
   <si>
     <t xml:space="preserve">4.2890739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29044914245605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25057029724121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24919462203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26982259750366</t>
+    <t xml:space="preserve">4.29044961929321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25056982040405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24919509887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2698221206665</t>
   </si>
   <si>
     <t xml:space="preserve">4.26294660568237</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24231910705566</t>
+    <t xml:space="preserve">4.24231958389282</t>
   </si>
   <si>
     <t xml:space="preserve">4.13643312454224</t>
@@ -1922,16 +1922,16 @@
     <t xml:space="preserve">4.05392456054688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12543201446533</t>
+    <t xml:space="preserve">4.12543249130249</t>
   </si>
   <si>
     <t xml:space="preserve">4.0896782875061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13230800628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17149877548218</t>
+    <t xml:space="preserve">4.13230752944946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17149972915649</t>
   </si>
   <si>
     <t xml:space="preserve">4.23819398880005</t>
@@ -1940,7 +1940,7 @@
     <t xml:space="preserve">4.22169208526611</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21894216537476</t>
+    <t xml:space="preserve">4.2189416885376</t>
   </si>
   <si>
     <t xml:space="preserve">4.21481609344482</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">4.33720445632935</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37433385848999</t>
+    <t xml:space="preserve">4.37433338165283</t>
   </si>
   <si>
     <t xml:space="preserve">4.50359678268433</t>
@@ -1970,10 +1970,10 @@
     <t xml:space="preserve">4.57441663742065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47609376907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44171524047852</t>
+    <t xml:space="preserve">4.47609329223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44171571731567</t>
   </si>
   <si>
     <t xml:space="preserve">4.44859075546265</t>
@@ -1985,31 +1985,31 @@
     <t xml:space="preserve">4.57785415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6094822883606</t>
+    <t xml:space="preserve">4.60948276519775</t>
   </si>
   <si>
     <t xml:space="preserve">4.66173839569092</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6067328453064</t>
+    <t xml:space="preserve">4.60673236846924</t>
   </si>
   <si>
     <t xml:space="preserve">4.57097864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57166624069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50772190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45752954483032</t>
+    <t xml:space="preserve">4.5716667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5077223777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45752906799316</t>
   </si>
   <si>
     <t xml:space="preserve">4.41971302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46234178543091</t>
+    <t xml:space="preserve">4.46234226226807</t>
   </si>
   <si>
     <t xml:space="preserve">4.4279637336731</t>
@@ -2018,7 +2018,7 @@
     <t xml:space="preserve">4.54485082626343</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52422428131104</t>
+    <t xml:space="preserve">4.52422380447388</t>
   </si>
   <si>
     <t xml:space="preserve">4.55860233306885</t>
@@ -2030,10 +2030,10 @@
     <t xml:space="preserve">4.45546674728394</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48296976089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53109979629517</t>
+    <t xml:space="preserve">4.48296928405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53109931945801</t>
   </si>
   <si>
     <t xml:space="preserve">4.56547832489014</t>
@@ -2042,7 +2042,7 @@
     <t xml:space="preserve">4.59985685348511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64111089706421</t>
+    <t xml:space="preserve">4.64111137390137</t>
   </si>
   <si>
     <t xml:space="preserve">4.61360836029053</t>
@@ -2051,13 +2051,13 @@
     <t xml:space="preserve">4.62048387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62735939025879</t>
+    <t xml:space="preserve">4.62735986709595</t>
   </si>
   <si>
     <t xml:space="preserve">4.71674394607544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65486240386963</t>
+    <t xml:space="preserve">4.65486288070679</t>
   </si>
   <si>
     <t xml:space="preserve">4.49672079086304</t>
@@ -2066,7 +2066,7 @@
     <t xml:space="preserve">4.5522894859314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61179637908936</t>
+    <t xml:space="preserve">4.6117959022522</t>
   </si>
   <si>
     <t xml:space="preserve">4.60435819625854</t>
@@ -2078,10 +2078,10 @@
     <t xml:space="preserve">4.6936182975769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73824882507324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71593379974365</t>
+    <t xml:space="preserve">4.73824834823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71593427658081</t>
   </si>
   <si>
     <t xml:space="preserve">4.6341118812561</t>
@@ -2090,7 +2090,7 @@
     <t xml:space="preserve">4.65642690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58948135375977</t>
+    <t xml:space="preserve">4.58948183059692</t>
   </si>
   <si>
     <t xml:space="preserve">4.51509761810303</t>
@@ -2105,49 +2105,49 @@
     <t xml:space="preserve">4.55972766876221</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64898824691772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64154958724976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52997398376465</t>
+    <t xml:space="preserve">4.64898777008057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64155006408691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58204221725464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52997446060181</t>
   </si>
   <si>
     <t xml:space="preserve">4.4481520652771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38120651245117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42583656311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37376880645752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4183988571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35889148712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32913827896118</t>
+    <t xml:space="preserve">4.38120603561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42583703994751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37376832962036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41839838027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35889196395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32913780212402</t>
   </si>
   <si>
     <t xml:space="preserve">4.32169961929321</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31426095962524</t>
+    <t xml:space="preserve">4.3142614364624</t>
   </si>
   <si>
     <t xml:space="preserve">4.33657646179199</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59691905975342</t>
+    <t xml:space="preserve">4.59691953659058</t>
   </si>
   <si>
     <t xml:space="preserve">4.50765895843506</t>
@@ -2156,31 +2156,31 @@
     <t xml:space="preserve">4.49278211593628</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48534393310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.43327522277832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40352201461792</t>
+    <t xml:space="preserve">4.48534440994263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.43327569961548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40352153778076</t>
   </si>
   <si>
     <t xml:space="preserve">4.38864517211914</t>
   </si>
   <si>
-    <t xml:space="preserve">4.39608287811279</t>
+    <t xml:space="preserve">4.39608335494995</t>
   </si>
   <si>
     <t xml:space="preserve">4.35145282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24731540679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20268535614014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19524669647217</t>
+    <t xml:space="preserve">4.24731588363647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20268583297729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19524717330933</t>
   </si>
   <si>
     <t xml:space="preserve">4.10598659515381</t>
@@ -2192,49 +2192,49 @@
     <t xml:space="preserve">4.01672554016113</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02416372299194</t>
+    <t xml:space="preserve">4.0241641998291</t>
   </si>
   <si>
     <t xml:space="preserve">3.93490362167358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90514993667603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95721888542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89771175384521</t>
+    <t xml:space="preserve">3.9051501750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95721864700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89771199226379</t>
   </si>
   <si>
     <t xml:space="preserve">3.98697257041931</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92002654075623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94234228134155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97953367233276</t>
+    <t xml:space="preserve">3.92002725601196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94234204292297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97953391075134</t>
   </si>
   <si>
     <t xml:space="preserve">3.97209548950195</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04647970199585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06879472732544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.098548412323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16549301147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18780899047852</t>
+    <t xml:space="preserve">4.04647922515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06879425048828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09854793548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16549396514893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18780851364136</t>
   </si>
   <si>
     <t xml:space="preserve">4.18037033081055</t>
@@ -2246,10 +2246,10 @@
     <t xml:space="preserve">4.11342525482178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14317893981934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12830209732056</t>
+    <t xml:space="preserve">4.14317846298218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1283016204834</t>
   </si>
   <si>
     <t xml:space="preserve">4.15805530548096</t>
@@ -2261,13 +2261,13 @@
     <t xml:space="preserve">4.2324390411377</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23987674713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26963043212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30682229995728</t>
+    <t xml:space="preserve">4.23987722396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26963090896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30682277679443</t>
   </si>
   <si>
     <t xml:space="preserve">4.29194593429565</t>
@@ -2282,10 +2282,10 @@
     <t xml:space="preserve">4.29938411712646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28450727462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41096019744873</t>
+    <t xml:space="preserve">4.28450775146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41095972061157</t>
   </si>
   <si>
     <t xml:space="preserve">4.44071340560913</t>
@@ -2297,10 +2297,10 @@
     <t xml:space="preserve">4.47046709060669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45559024810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66386556625366</t>
+    <t xml:space="preserve">4.45558977127075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66386461257935</t>
   </si>
   <si>
     <t xml:space="preserve">4.74568748474121</t>
@@ -2309,7 +2309,7 @@
     <t xml:space="preserve">4.79031753540039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70105743408203</t>
+    <t xml:space="preserve">4.70105695724487</t>
   </si>
   <si>
     <t xml:space="preserve">4.67874193191528</t>
@@ -2324,7 +2324,7 @@
     <t xml:space="preserve">4.67130374908447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70849561691284</t>
+    <t xml:space="preserve">4.70849514007568</t>
   </si>
   <si>
     <t xml:space="preserve">4.72337198257446</t>
@@ -2333,55 +2333,55 @@
     <t xml:space="preserve">4.68618011474609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08367156982422</t>
+    <t xml:space="preserve">4.0836706161499</t>
   </si>
   <si>
     <t xml:space="preserve">4.06135606765747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96465682983398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92746543884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48116254806519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3844633102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37702488899231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7187283039093</t>
+    <t xml:space="preserve">3.96465730667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92746496200562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48116230964661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38446378707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37702512741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71872854232788</t>
   </si>
   <si>
     <t xml:space="preserve">2.76335859298706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54020738601685</t>
+    <t xml:space="preserve">2.54020714759827</t>
   </si>
   <si>
     <t xml:space="preserve">2.57367992401123</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70385146141052</t>
+    <t xml:space="preserve">2.7038516998291</t>
   </si>
   <si>
     <t xml:space="preserve">2.64806365966797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77451610565186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70757102966309</t>
+    <t xml:space="preserve">2.77451634407043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70757079124451</t>
   </si>
   <si>
     <t xml:space="preserve">2.88609194755554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8079891204834</t>
+    <t xml:space="preserve">2.80798888206482</t>
   </si>
   <si>
     <t xml:space="preserve">2.83402323722839</t>
@@ -2390,7 +2390,7 @@
     <t xml:space="preserve">2.826584815979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68525576591492</t>
+    <t xml:space="preserve">2.68525552749634</t>
   </si>
   <si>
     <t xml:space="preserve">2.78939294815063</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">2.80426979064941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75220084190369</t>
+    <t xml:space="preserve">2.75220108032227</t>
   </si>
   <si>
     <t xml:space="preserve">2.70013236999512</t>
@@ -2408,13 +2408,13 @@
     <t xml:space="preserve">2.7150092124939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76707792282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73732423782349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69641304016113</t>
+    <t xml:space="preserve">2.76707768440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73732447624207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69641327857971</t>
   </si>
   <si>
     <t xml:space="preserve">2.60343337059021</t>
@@ -2426,19 +2426,19 @@
     <t xml:space="preserve">2.69269394874573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62946796417236</t>
+    <t xml:space="preserve">2.62946772575378</t>
   </si>
   <si>
     <t xml:space="preserve">2.6257483959198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64062523841858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65550184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61459136009216</t>
+    <t xml:space="preserve">2.64062547683716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65550231933594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61459112167358</t>
   </si>
   <si>
     <t xml:space="preserve">2.60715246200562</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">2.63318681716919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59227585792542</t>
+    <t xml:space="preserve">2.59227561950684</t>
   </si>
   <si>
     <t xml:space="preserve">2.55508399009705</t>
@@ -2456,16 +2456,16 @@
     <t xml:space="preserve">2.45466589927673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42491245269775</t>
+    <t xml:space="preserve">2.42491221427917</t>
   </si>
   <si>
     <t xml:space="preserve">2.3951587677002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40259695053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46954274177551</t>
+    <t xml:space="preserve">2.40259718894958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46954250335693</t>
   </si>
   <si>
     <t xml:space="preserve">2.33937096595764</t>
@@ -2477,34 +2477,34 @@
     <t xml:space="preserve">2.25754880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44722747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38400101661682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41747379302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4137544631958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43978881835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51417279243469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61087203025818</t>
+    <t xml:space="preserve">2.44722723960876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3840012550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41747403144836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41375470161438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43978905677795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51417303085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6108717918396</t>
   </si>
   <si>
     <t xml:space="preserve">2.61831021308899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77823543548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91584539413452</t>
+    <t xml:space="preserve">2.77823519706726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9158456325531</t>
   </si>
   <si>
     <t xml:space="preserve">2.54392647743225</t>
@@ -2525,7 +2525,7 @@
     <t xml:space="preserve">2.51045346260071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58483719825745</t>
+    <t xml:space="preserve">2.58483743667603</t>
   </si>
   <si>
     <t xml:space="preserve">2.58111810684204</t>
@@ -2534,31 +2534,31 @@
     <t xml:space="preserve">2.5997142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63690638542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68530654907227</t>
+    <t xml:space="preserve">2.63690614700317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68530678749084</t>
   </si>
   <si>
     <t xml:space="preserve">2.66147232055664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62969374656677</t>
+    <t xml:space="preserve">2.62969350814819</t>
   </si>
   <si>
     <t xml:space="preserve">2.5740807056427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51846790313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46285510063171</t>
+    <t xml:space="preserve">2.51846814155579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46285486221313</t>
   </si>
   <si>
     <t xml:space="preserve">2.45491027832031</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42710375785828</t>
+    <t xml:space="preserve">2.42710399627686</t>
   </si>
   <si>
     <t xml:space="preserve">2.51052331924438</t>
@@ -2567,13 +2567,13 @@
     <t xml:space="preserve">2.47079968452454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49066162109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53435730934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59791493415833</t>
+    <t xml:space="preserve">2.49066138267517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53435754776001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59791469573975</t>
   </si>
   <si>
     <t xml:space="preserve">2.55024671554565</t>
@@ -2606,16 +2606,16 @@
     <t xml:space="preserve">2.48668932914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5144956111908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48271703720093</t>
+    <t xml:space="preserve">2.51449537277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48271656036377</t>
   </si>
   <si>
     <t xml:space="preserve">2.43902087211609</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57010817527771</t>
+    <t xml:space="preserve">2.57010841369629</t>
   </si>
   <si>
     <t xml:space="preserve">2.49860620498657</t>
@@ -2624,13 +2624,13 @@
     <t xml:space="preserve">2.391352891922</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3834080696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39532518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33176755905151</t>
+    <t xml:space="preserve">2.38340830802917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39532542228699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33176732063293</t>
   </si>
   <si>
     <t xml:space="preserve">2.37149095535278</t>
@@ -2645,16 +2645,16 @@
     <t xml:space="preserve">2.44696545600891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50257873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5661358833313</t>
+    <t xml:space="preserve">2.50257849693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56613612174988</t>
   </si>
   <si>
     <t xml:space="preserve">2.52244019508362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30396103858948</t>
+    <t xml:space="preserve">2.30396127700806</t>
   </si>
   <si>
     <t xml:space="preserve">2.28409934043884</t>
@@ -2663,7 +2663,7 @@
     <t xml:space="preserve">2.30793356895447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28807163238525</t>
+    <t xml:space="preserve">2.28807187080383</t>
   </si>
   <si>
     <t xml:space="preserve">2.25232076644897</t>
@@ -2675,28 +2675,28 @@
     <t xml:space="preserve">2.14506721496582</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11328864097595</t>
+    <t xml:space="preserve">2.11328840255737</t>
   </si>
   <si>
     <t xml:space="preserve">2.05767560005188</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96631157398224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97822856903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98220109939575</t>
+    <t xml:space="preserve">1.96631169319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97822880744934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98220098018646</t>
   </si>
   <si>
     <t xml:space="preserve">2.08548212051392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09342670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08150959014893</t>
+    <t xml:space="preserve">2.09342694282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0815098285675</t>
   </si>
   <si>
     <t xml:space="preserve">2.15301203727722</t>
@@ -2714,19 +2714,19 @@
     <t xml:space="preserve">2.72900223731995</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7131130695343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88392400741577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83625555038452</t>
+    <t xml:space="preserve">2.71311283111572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88392376899719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8362557888031</t>
   </si>
   <si>
     <t xml:space="preserve">2.81242156028748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77269792556763</t>
+    <t xml:space="preserve">2.77269816398621</t>
   </si>
   <si>
     <t xml:space="preserve">2.74091935157776</t>
@@ -2735,28 +2735,28 @@
     <t xml:space="preserve">2.70119595527649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8203661441803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84420013427734</t>
+    <t xml:space="preserve">2.82036638259888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84420037269592</t>
   </si>
   <si>
     <t xml:space="preserve">2.86406207084656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84817266464233</t>
+    <t xml:space="preserve">2.84817290306091</t>
   </si>
   <si>
     <t xml:space="preserve">2.85611748695374</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78461527824402</t>
+    <t xml:space="preserve">2.78461503982544</t>
   </si>
   <si>
     <t xml:space="preserve">2.87200665473938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85214519500732</t>
+    <t xml:space="preserve">2.85214495658875</t>
   </si>
   <si>
     <t xml:space="preserve">2.93556427955627</t>
@@ -2765,7 +2765,7 @@
     <t xml:space="preserve">2.96337080001831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87597918510437</t>
+    <t xml:space="preserve">2.87597894668579</t>
   </si>
   <si>
     <t xml:space="preserve">2.9514536857605</t>
@@ -2774,16 +2774,16 @@
     <t xml:space="preserve">2.91967487335205</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91173005104065</t>
+    <t xml:space="preserve">2.91173028945923</t>
   </si>
   <si>
     <t xml:space="preserve">2.78064274787903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83228349685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94748163223267</t>
+    <t xml:space="preserve">2.83228325843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94748139381409</t>
   </si>
   <si>
     <t xml:space="preserve">2.97926020622253</t>
@@ -2798,16 +2798,16 @@
     <t xml:space="preserve">2.8283109664917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90378546714783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93953657150269</t>
+    <t xml:space="preserve">2.90378570556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93953680992126</t>
   </si>
   <si>
     <t xml:space="preserve">2.9435088634491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95542621612549</t>
+    <t xml:space="preserve">2.95542597770691</t>
   </si>
   <si>
     <t xml:space="preserve">2.97528767585754</t>
@@ -2816,28 +2816,28 @@
     <t xml:space="preserve">2.95939826965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99912214279175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96734309196472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8878960609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80447697639465</t>
+    <t xml:space="preserve">2.99912190437317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96734285354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88789629936218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80447673797607</t>
   </si>
   <si>
     <t xml:space="preserve">2.82433867454529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80844950675964</t>
+    <t xml:space="preserve">2.80844926834106</t>
   </si>
   <si>
     <t xml:space="preserve">2.89186859130859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90775799751282</t>
+    <t xml:space="preserve">2.90775775909424</t>
   </si>
   <si>
     <t xml:space="preserve">2.92364740371704</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">2.98323249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02295613288879</t>
+    <t xml:space="preserve">3.02295589447021</t>
   </si>
   <si>
     <t xml:space="preserve">3.04679012298584</t>
@@ -2855,13 +2855,13 @@
     <t xml:space="preserve">3.30896496772766</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17787766456604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05473470687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11829233169556</t>
+    <t xml:space="preserve">3.17787742614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05473494529724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11829209327698</t>
   </si>
   <si>
     <t xml:space="preserve">3.04281759262085</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">3.02692818641663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0666515827179</t>
+    <t xml:space="preserve">3.06665182113647</t>
   </si>
   <si>
     <t xml:space="preserve">3.07062411308289</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">2.84022808074951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79256010055542</t>
+    <t xml:space="preserve">2.79255986213684</t>
   </si>
   <si>
     <t xml:space="preserve">2.80050468444824</t>
@@ -2909,10 +2909,10 @@
     <t xml:space="preserve">2.72502994537354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75283622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81639409065247</t>
+    <t xml:space="preserve">2.75283646583557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81639385223389</t>
   </si>
   <si>
     <t xml:space="preserve">2.99514961242676</t>
@@ -2921,40 +2921,40 @@
     <t xml:space="preserve">3.15404343605042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07459616661072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13815426826477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.08254098892212</t>
+    <t xml:space="preserve">3.0745964050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13815402984619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0825412273407</t>
   </si>
   <si>
     <t xml:space="preserve">3.14609885215759</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09843039512634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18582248687744</t>
+    <t xml:space="preserve">3.09843063354492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18582224845886</t>
   </si>
   <si>
     <t xml:space="preserve">3.13020944595337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25335216522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26924133300781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30102062225342</t>
+    <t xml:space="preserve">3.25335192680359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26924109458923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30102038383484</t>
   </si>
   <si>
     <t xml:space="preserve">3.3288266658783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3963565826416</t>
+    <t xml:space="preserve">3.39635682106018</t>
   </si>
   <si>
     <t xml:space="preserve">3.2732138633728</t>
@@ -2963,34 +2963,34 @@
     <t xml:space="preserve">3.29307556152344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23746228218079</t>
+    <t xml:space="preserve">3.23746275901794</t>
   </si>
   <si>
     <t xml:space="preserve">3.23349046707153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20965623855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25732445716858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20568370819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.21362853050232</t>
+    <t xml:space="preserve">3.20965600013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2056839466095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2136287689209</t>
   </si>
   <si>
     <t xml:space="preserve">3.22554564476013</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1977391242981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20171189308167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2652690410614</t>
+    <t xml:space="preserve">3.19773936271667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20171165466309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26526927947998</t>
   </si>
   <si>
     <t xml:space="preserve">3.31690979003906</t>
@@ -3011,22 +3011,22 @@
     <t xml:space="preserve">3.55922269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67044878005981</t>
+    <t xml:space="preserve">3.67044830322266</t>
   </si>
   <si>
     <t xml:space="preserve">3.69031047821045</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69428277015686</t>
+    <t xml:space="preserve">3.69428253173828</t>
   </si>
   <si>
     <t xml:space="preserve">3.66647601127625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63866925239563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51949906349182</t>
+    <t xml:space="preserve">3.63866972923279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5194993019104</t>
   </si>
   <si>
     <t xml:space="preserve">3.45594167709351</t>
@@ -3038,28 +3038,28 @@
     <t xml:space="preserve">3.49169278144836</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40430092811584</t>
+    <t xml:space="preserve">3.40430116653442</t>
   </si>
   <si>
     <t xml:space="preserve">3.45196914672852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44005250930786</t>
+    <t xml:space="preserve">3.44005227088928</t>
   </si>
   <si>
     <t xml:space="preserve">3.34074378013611</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24540734291077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26129698753357</t>
+    <t xml:space="preserve">3.24540758132935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26129674911499</t>
   </si>
   <si>
     <t xml:space="preserve">3.33677101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32485437393188</t>
+    <t xml:space="preserve">3.32485413551331</t>
   </si>
   <si>
     <t xml:space="preserve">3.22157311439514</t>
@@ -3077,7 +3077,7 @@
     <t xml:space="preserve">3.08651351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18979430198669</t>
+    <t xml:space="preserve">3.18979454040527</t>
   </si>
   <si>
     <t xml:space="preserve">3.24937987327576</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">3.19376683235168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27718639373779</t>
+    <t xml:space="preserve">3.27718591690063</t>
   </si>
   <si>
     <t xml:space="preserve">3.36457800865173</t>
@@ -3095,19 +3095,19 @@
     <t xml:space="preserve">3.37252235412598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24143481254578</t>
+    <t xml:space="preserve">3.24143505096436</t>
   </si>
   <si>
     <t xml:space="preserve">3.15007090568542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12623691558838</t>
+    <t xml:space="preserve">3.1262366771698</t>
   </si>
   <si>
     <t xml:space="preserve">3.09445810317993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09048581123352</t>
+    <t xml:space="preserve">3.0904860496521</t>
   </si>
   <si>
     <t xml:space="preserve">3.16993284225464</t>
@@ -3116,7 +3116,7 @@
     <t xml:space="preserve">3.16198825836182</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07856869697571</t>
+    <t xml:space="preserve">3.07856893539429</t>
   </si>
   <si>
     <t xml:space="preserve">2.97131562232971</t>
@@ -3125,13 +3125,13 @@
     <t xml:space="preserve">2.99117732048035</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89584064483643</t>
+    <t xml:space="preserve">2.895840883255</t>
   </si>
   <si>
     <t xml:space="preserve">3.0189836025238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31293725967407</t>
+    <t xml:space="preserve">3.31293749809265</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596031188965</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">3.17390489578247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22951793670654</t>
+    <t xml:space="preserve">3.22951817512512</t>
   </si>
   <si>
     <t xml:space="preserve">3.03884553909302</t>
@@ -3158,7 +3158,7 @@
     <t xml:space="preserve">3.00309419631958</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0110387802124</t>
+    <t xml:space="preserve">3.01103901863098</t>
   </si>
   <si>
     <t xml:space="preserve">3.05076217651367</t>
@@ -3170,7 +3170,7 @@
     <t xml:space="preserve">3.21760106086731</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92761945724487</t>
+    <t xml:space="preserve">2.92761969566345</t>
   </si>
   <si>
     <t xml:space="preserve">2.79653215408325</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">2.87995147705078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98720479011536</t>
+    <t xml:space="preserve">2.98720502853394</t>
   </si>
   <si>
     <t xml:space="preserve">3.03487277030945</t>
@@ -3188,22 +3188,22 @@
     <t xml:space="preserve">2.91570258140564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28513121604919</t>
+    <t xml:space="preserve">3.28513097763062</t>
   </si>
   <si>
     <t xml:space="preserve">3.36060523986816</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37649464607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36854982376099</t>
+    <t xml:space="preserve">3.37649488449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36855006217957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53141665458679</t>
   </si>
   <si>
-    <t xml:space="preserve">3.57908487319946</t>
+    <t xml:space="preserve">3.57908463478088</t>
   </si>
   <si>
     <t xml:space="preserve">3.42416310310364</t>
@@ -3212,67 +3212,67 @@
     <t xml:space="preserve">3.34868860244751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35663294792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32088184356689</t>
+    <t xml:space="preserve">3.35663318634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32088208198547</t>
   </si>
   <si>
     <t xml:space="preserve">3.40032911300659</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39238429069519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38443946838379</t>
+    <t xml:space="preserve">3.39238405227661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38443970680237</t>
   </si>
   <si>
     <t xml:space="preserve">3.46388673782349</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48772048950195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.47183108329773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54333329200745</t>
+    <t xml:space="preserve">3.48772025108337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.47183132171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54333353042603</t>
   </si>
   <si>
     <t xml:space="preserve">3.54730606079102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55127787590027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63072490692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59100127220154</t>
+    <t xml:space="preserve">3.55127763748169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63072514533997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5910017490387</t>
   </si>
   <si>
     <t xml:space="preserve">3.67442107200623</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61086344718933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62278008460999</t>
+    <t xml:space="preserve">3.61086320877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62278032302856</t>
   </si>
   <si>
     <t xml:space="preserve">3.67839336395264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65058660507202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61880803108215</t>
+    <t xml:space="preserve">3.6505868434906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61880779266357</t>
   </si>
   <si>
     <t xml:space="preserve">3.6346971988678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58702921867371</t>
+    <t xml:space="preserve">3.58702898025513</t>
   </si>
   <si>
     <t xml:space="preserve">3.53936100006104</t>
@@ -8871,7 +8871,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G144" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="H144" t="s">
         <v>9</v>
@@ -8923,7 +8923,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G146" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H146" t="s">
         <v>9</v>
@@ -8949,7 +8949,7 @@
         <v>7.33019208908081</v>
       </c>
       <c r="G147" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="H147" t="s">
         <v>9</v>
@@ -8975,7 +8975,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G148" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H148" t="s">
         <v>9</v>
@@ -9001,7 +9001,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G149" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H149" t="s">
         <v>9</v>
@@ -9027,7 +9027,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G150" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H150" t="s">
         <v>9</v>
@@ -9079,7 +9079,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G152" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H152" t="s">
         <v>9</v>
@@ -9105,7 +9105,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G153" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="H153" t="s">
         <v>9</v>
@@ -9131,7 +9131,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G154" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H154" t="s">
         <v>9</v>
@@ -9157,7 +9157,7 @@
         <v>7.07918977737427</v>
       </c>
       <c r="G155" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="H155" t="s">
         <v>9</v>
@@ -9183,7 +9183,7 @@
         <v>7.05130100250244</v>
       </c>
       <c r="G156" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="H156" t="s">
         <v>9</v>
@@ -9209,7 +9209,7 @@
         <v>7.06524515151978</v>
       </c>
       <c r="G157" t="s">
-        <v>130</v>
+        <v>51</v>
       </c>
       <c r="H157" t="s">
         <v>9</v>
@@ -9235,7 +9235,7 @@
         <v>7.13032007217407</v>
       </c>
       <c r="G158" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H158" t="s">
         <v>9</v>
@@ -9261,7 +9261,7 @@
         <v>7.04200410842896</v>
       </c>
       <c r="G159" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="H159" t="s">
         <v>9</v>
@@ -9287,7 +9287,7 @@
         <v>7.0048189163208</v>
       </c>
       <c r="G160" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="H160" t="s">
         <v>9</v>
@@ -9313,7 +9313,7 @@
         <v>6.93509578704834</v>
       </c>
       <c r="G161" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="H161" t="s">
         <v>9</v>
@@ -9339,7 +9339,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G162" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H162" t="s">
         <v>9</v>
@@ -9365,7 +9365,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G163" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H163" t="s">
         <v>9</v>
@@ -9391,7 +9391,7 @@
         <v>6.78170585632324</v>
       </c>
       <c r="G164" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="H164" t="s">
         <v>9</v>
@@ -9417,7 +9417,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G165" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H165" t="s">
         <v>9</v>
@@ -9443,7 +9443,7 @@
         <v>6.88396596908569</v>
       </c>
       <c r="G166" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="H166" t="s">
         <v>9</v>
@@ -9469,7 +9469,7 @@
         <v>6.87002086639404</v>
       </c>
       <c r="G167" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="H167" t="s">
         <v>9</v>
@@ -9495,7 +9495,7 @@
         <v>6.83283615112305</v>
       </c>
       <c r="G168" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="H168" t="s">
         <v>9</v>
@@ -9521,7 +9521,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G169" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H169" t="s">
         <v>9</v>
@@ -9547,7 +9547,7 @@
         <v>6.77705812454224</v>
       </c>
       <c r="G170" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="H170" t="s">
         <v>9</v>
@@ -9573,7 +9573,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G171" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H171" t="s">
         <v>9</v>
@@ -9599,7 +9599,7 @@
         <v>6.71198320388794</v>
       </c>
       <c r="G172" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H172" t="s">
         <v>9</v>
@@ -9625,7 +9625,7 @@
         <v>6.64690780639648</v>
       </c>
       <c r="G173" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="H173" t="s">
         <v>9</v>
@@ -9651,7 +9651,7 @@
         <v>6.79565000534058</v>
       </c>
       <c r="G174" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="H174" t="s">
         <v>9</v>
@@ -9677,7 +9677,7 @@
         <v>6.69803810119629</v>
       </c>
       <c r="G175" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="H175" t="s">
         <v>9</v>
@@ -9729,7 +9729,7 @@
         <v>6.74916791915894</v>
       </c>
       <c r="G177" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="H177" t="s">
         <v>9</v>
@@ -9755,7 +9755,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G178" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H178" t="s">
         <v>9</v>
@@ -9781,7 +9781,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G179" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H179" t="s">
         <v>9</v>
@@ -9807,7 +9807,7 @@
         <v>6.242516040802</v>
       </c>
       <c r="G180" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="H180" t="s">
         <v>9</v>
@@ -9859,7 +9859,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G182" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H182" t="s">
         <v>9</v>
@@ -9885,7 +9885,7 @@
         <v>6.09842205047607</v>
       </c>
       <c r="G183" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="H183" t="s">
         <v>9</v>
@@ -9911,7 +9911,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G184" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H184" t="s">
         <v>9</v>
@@ -9937,7 +9937,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G185" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H185" t="s">
         <v>9</v>
@@ -9963,7 +9963,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G186" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H186" t="s">
         <v>9</v>
@@ -9989,7 +9989,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G187" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H187" t="s">
         <v>9</v>
@@ -10015,7 +10015,7 @@
         <v>6.17744112014771</v>
       </c>
       <c r="G188" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H188" t="s">
         <v>9</v>
@@ -10041,7 +10041,7 @@
         <v>6.13095903396606</v>
       </c>
       <c r="G189" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H189" t="s">
         <v>9</v>
@@ -10093,7 +10093,7 @@
         <v>6.26575708389282</v>
       </c>
       <c r="G191" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="H191" t="s">
         <v>9</v>
@@ -10145,7 +10145,7 @@
         <v>6.23322010040283</v>
       </c>
       <c r="G193" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H193" t="s">
         <v>9</v>
@@ -10171,7 +10171,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G194" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H194" t="s">
         <v>9</v>
@@ -10197,7 +10197,7 @@
         <v>6.0565881729126</v>
       </c>
       <c r="G195" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="H195" t="s">
         <v>9</v>
@@ -10223,7 +10223,7 @@
         <v>6.11236715316772</v>
       </c>
       <c r="G196" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H196" t="s">
         <v>9</v>
@@ -10249,7 +10249,7 @@
         <v>6.13560819625854</v>
       </c>
       <c r="G197" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H197" t="s">
         <v>9</v>
@@ -10275,7 +10275,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G198" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H198" t="s">
         <v>9</v>
@@ -10301,7 +10301,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G199" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H199" t="s">
         <v>9</v>
@@ -10327,7 +10327,7 @@
         <v>6.02405118942261</v>
       </c>
       <c r="G200" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="H200" t="s">
         <v>9</v>
@@ -10353,7 +10353,7 @@
         <v>5.99616193771362</v>
       </c>
       <c r="G201" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H201" t="s">
         <v>9</v>
@@ -10379,7 +10379,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G202" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H202" t="s">
         <v>9</v>
@@ -10405,7 +10405,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G203" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H203" t="s">
         <v>9</v>
@@ -10431,7 +10431,7 @@
         <v>6.07982921600342</v>
       </c>
       <c r="G204" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="H204" t="s">
         <v>9</v>
@@ -10457,7 +10457,7 @@
         <v>6.20532989501953</v>
       </c>
       <c r="G205" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H205" t="s">
         <v>9</v>
@@ -10483,7 +10483,7 @@
         <v>6.45633316040039</v>
       </c>
       <c r="G206" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H206" t="s">
         <v>9</v>
@@ -10509,7 +10509,7 @@
         <v>6.56324100494385</v>
       </c>
       <c r="G207" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H207" t="s">
         <v>9</v>
@@ -10535,7 +10535,7 @@
         <v>6.5818338394165</v>
       </c>
       <c r="G208" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="H208" t="s">
         <v>9</v>
@@ -10561,7 +10561,7 @@
         <v>6.63761186599731</v>
       </c>
       <c r="G209" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H209" t="s">
         <v>9</v>
@@ -10613,7 +10613,7 @@
         <v>6.65155601501465</v>
       </c>
       <c r="G211" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="H211" t="s">
         <v>9</v>
@@ -10639,7 +10639,7 @@
         <v>6.600426197052</v>
       </c>
       <c r="G212" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="H212" t="s">
         <v>9</v>
@@ -10665,7 +10665,7 @@
         <v>6.52140712738037</v>
       </c>
       <c r="G213" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="H213" t="s">
         <v>9</v>
@@ -10717,7 +10717,7 @@
         <v>6.46562910079956</v>
       </c>
       <c r="G215" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="H215" t="s">
         <v>9</v>
@@ -10743,7 +10743,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G216" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H216" t="s">
         <v>9</v>
@@ -10769,7 +10769,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G217" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H217" t="s">
         <v>9</v>
@@ -10795,7 +10795,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G218" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H218" t="s">
         <v>9</v>
@@ -10821,7 +10821,7 @@
         <v>6.36336898803711</v>
       </c>
       <c r="G219" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="H219" t="s">
         <v>9</v>
@@ -10847,7 +10847,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G220" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H220" t="s">
         <v>9</v>
@@ -10873,7 +10873,7 @@
         <v>6.34477615356445</v>
       </c>
       <c r="G221" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="H221" t="s">
         <v>9</v>
@@ -10899,7 +10899,7 @@
         <v>6.29364585876465</v>
       </c>
       <c r="G222" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="H222" t="s">
         <v>9</v>
@@ -10925,7 +10925,7 @@
         <v>6.15420007705688</v>
       </c>
       <c r="G223" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="H223" t="s">
         <v>9</v>
@@ -10951,7 +10951,7 @@
         <v>6.21462678909302</v>
       </c>
       <c r="G224" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="H224" t="s">
         <v>9</v>
@@ -10977,7 +10977,7 @@
         <v>6.05193996429443</v>
       </c>
       <c r="G225" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H225" t="s">
         <v>9</v>
@@ -11003,7 +11003,7 @@
         <v>6.06123685836792</v>
       </c>
       <c r="G226" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="H226" t="s">
         <v>9</v>
@@ -11029,7 +11029,7 @@
         <v>6.07053279876709</v>
       </c>
       <c r="G227" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="H227" t="s">
         <v>9</v>
@@ -11055,7 +11055,7 @@
         <v>6.01475477218628</v>
       </c>
       <c r="G228" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="H228" t="s">
         <v>9</v>
@@ -11081,7 +11081,7 @@
         <v>5.74516010284424</v>
       </c>
       <c r="G229" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="H229" t="s">
         <v>9</v>
@@ -11107,7 +11107,7 @@
         <v>5.88460493087769</v>
       </c>
       <c r="G230" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="H230" t="s">
         <v>9</v>
@@ -11133,7 +11133,7 @@
         <v>5.92643880844116</v>
       </c>
       <c r="G231" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H231" t="s">
         <v>9</v>
@@ -11159,7 +11159,7 @@
         <v>5.90784597396851</v>
       </c>
       <c r="G232" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="H232" t="s">
         <v>9</v>
@@ -11185,7 +11185,7 @@
         <v>5.78234481811523</v>
       </c>
       <c r="G233" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="H233" t="s">
         <v>9</v>
@@ -11211,7 +11211,7 @@
         <v>5.81023406982422</v>
       </c>
       <c r="G234" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="H234" t="s">
         <v>9</v>
@@ -11237,7 +11237,7 @@
         <v>5.81953096389771</v>
       </c>
       <c r="G235" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="H235" t="s">
         <v>9</v>
@@ -11263,7 +11263,7 @@
         <v>5.86601305007935</v>
       </c>
       <c r="G236" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H236" t="s">
         <v>9</v>
@@ -11289,7 +11289,7 @@
         <v>5.85671615600586</v>
       </c>
       <c r="G237" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H237" t="s">
         <v>9</v>
@@ -11315,7 +11315,7 @@
         <v>5.91249513626099</v>
       </c>
       <c r="G238" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H238" t="s">
         <v>9</v>
@@ -11341,7 +11341,7 @@
         <v>5.83812379837036</v>
       </c>
       <c r="G239" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H239" t="s">
         <v>9</v>
@@ -11367,7 +11367,7 @@
         <v>6.14490413665771</v>
       </c>
       <c r="G240" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H240" t="s">
         <v>9</v>
@@ -11393,7 +11393,7 @@
         <v>6.20068216323853</v>
       </c>
       <c r="G241" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="H241" t="s">
         <v>9</v>
@@ -11419,7 +11419,7 @@
         <v>6.3959059715271</v>
       </c>
       <c r="G242" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H242" t="s">
         <v>9</v>
@@ -11445,7 +11445,7 @@
         <v>6.34012794494629</v>
       </c>
       <c r="G243" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="H243" t="s">
         <v>9</v>
@@ -11471,7 +11471,7 @@
         <v>6.36801719665527</v>
       </c>
       <c r="G244" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H244" t="s">
         <v>9</v>
@@ -11523,7 +11523,7 @@
         <v>6.32153511047363</v>
       </c>
       <c r="G246" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="H246" t="s">
         <v>9</v>
@@ -11601,7 +11601,7 @@
         <v>6.57718515396118</v>
       </c>
       <c r="G249" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H249" t="s">
         <v>9</v>
@@ -11627,7 +11627,7 @@
         <v>6.53070402145386</v>
       </c>
       <c r="G250" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H250" t="s">
         <v>9</v>
@@ -11653,7 +11653,7 @@
         <v>6.6655011177063</v>
       </c>
       <c r="G251" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H251" t="s">
         <v>9</v>
@@ -11679,7 +11679,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G252" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H252" t="s">
         <v>9</v>
@@ -11705,7 +11705,7 @@
         <v>6.67479705810547</v>
       </c>
       <c r="G253" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H253" t="s">
         <v>9</v>
@@ -11731,7 +11731,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G254" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H254" t="s">
         <v>9</v>
@@ -11757,7 +11757,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G255" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H255" t="s">
         <v>9</v>
@@ -11783,7 +11783,7 @@
         <v>6.69338989257812</v>
       </c>
       <c r="G256" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="H256" t="s">
         <v>9</v>
@@ -11809,7 +11809,7 @@
         <v>6.7305760383606</v>
       </c>
       <c r="G257" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="H257" t="s">
         <v>9</v>
@@ -11835,7 +11835,7 @@
         <v>6.76776123046875</v>
       </c>
       <c r="G258" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="H258" t="s">
         <v>9</v>
@@ -11913,7 +11913,7 @@
         <v>7.05594921112061</v>
       </c>
       <c r="G261" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H261" t="s">
         <v>9</v>
@@ -11965,7 +11965,7 @@
         <v>6.91650295257568</v>
       </c>
       <c r="G263" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H263" t="s">
         <v>9</v>
@@ -11991,7 +11991,7 @@
         <v>7.00946712493896</v>
       </c>
       <c r="G264" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H264" t="s">
         <v>9</v>
@@ -12017,7 +12017,7 @@
         <v>7.02341079711914</v>
       </c>
       <c r="G265" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H265" t="s">
         <v>9</v>
@@ -12069,7 +12069,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G267" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H267" t="s">
         <v>9</v>
@@ -12095,7 +12095,7 @@
         <v>6.94903993606567</v>
       </c>
       <c r="G268" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H268" t="s">
         <v>9</v>
@@ -12121,7 +12121,7 @@
         <v>6.88861417770386</v>
       </c>
       <c r="G269" t="s">
-        <v>67</v>
+        <v>218</v>
       </c>
       <c r="H269" t="s">
         <v>9</v>
@@ -12355,7 +12355,7 @@
         <v>6.41914701461792</v>
       </c>
       <c r="G278" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="H278" t="s">
         <v>9</v>
@@ -12537,7 +12537,7 @@
         <v>6.65620517730713</v>
       </c>
       <c r="G285" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H285" t="s">
         <v>9</v>
@@ -12641,7 +12641,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G289" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H289" t="s">
         <v>9</v>
@@ -12667,7 +12667,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G290" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H290" t="s">
         <v>9</v>
@@ -12719,7 +12719,7 @@
         <v>6.99552202224731</v>
       </c>
       <c r="G292" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H292" t="s">
         <v>9</v>
@@ -12745,7 +12745,7 @@
         <v>6.96763277053833</v>
       </c>
       <c r="G293" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="H293" t="s">
         <v>9</v>
@@ -12771,7 +12771,7 @@
         <v>6.8188910484314</v>
       </c>
       <c r="G294" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="H294" t="s">
         <v>9</v>
@@ -12901,7 +12901,7 @@
         <v>6.87931823730469</v>
       </c>
       <c r="G299" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H299" t="s">
         <v>9</v>
@@ -12953,7 +12953,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G301" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H301" t="s">
         <v>9</v>
@@ -13057,7 +13057,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G305" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="H305" t="s">
         <v>9</v>
@@ -13083,7 +13083,7 @@
         <v>7.31624698638916</v>
       </c>
       <c r="G306" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="H306" t="s">
         <v>9</v>
@@ -13109,7 +13109,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G307" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="H307" t="s">
         <v>9</v>
@@ -13135,7 +13135,7 @@
         <v>7.20004320144653</v>
       </c>
       <c r="G308" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H308" t="s">
         <v>9</v>
@@ -13213,7 +13213,7 @@
         <v>7.21398687362671</v>
       </c>
       <c r="G311" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="H311" t="s">
         <v>9</v>
@@ -71617,7 +71617,7 @@
     </row>
     <row r="2558">
       <c r="A2558" s="1" t="n">
-        <v>46048.6911342593</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B2558" t="n">
         <v>95268</v>
@@ -71638,6 +71638,32 @@
         <v>1573</v>
       </c>
       <c r="H2558" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2559">
+      <c r="A2559" s="1" t="n">
+        <v>46049.6911574074</v>
+      </c>
+      <c r="B2559" t="n">
+        <v>57346</v>
+      </c>
+      <c r="C2559" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="D2559" t="n">
+        <v>3.48499989509583</v>
+      </c>
+      <c r="E2559" t="n">
+        <v>3.49499988555908</v>
+      </c>
+      <c r="F2559" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G2559" t="s">
+        <v>1563</v>
+      </c>
+      <c r="H2559" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1597" uniqueCount="1597">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="1598">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">IGD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81178855895996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76804494857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7653112411499</t>
+    <t xml:space="preserve">4.8117880821228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76804399490356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76531171798706</t>
   </si>
   <si>
     <t xml:space="preserve">4.64775037765503</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">4.67235612869263</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55206155776978</t>
+    <t xml:space="preserve">4.55206060409546</t>
   </si>
   <si>
     <t xml:space="preserve">4.33334302902222</t>
@@ -74,55 +74,55 @@
     <t xml:space="preserve">4.16383743286133</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04627752304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60884165763855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8822386264801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9560558795929</t>
+    <t xml:space="preserve">4.04627704620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60884189605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88223838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95605564117432</t>
   </si>
   <si>
     <t xml:space="preserve">4.0380744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97519373893738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785380363464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81388926506042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96425724029541</t>
+    <t xml:space="preserve">3.97519397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785356521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81388902664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96425747871399</t>
   </si>
   <si>
     <t xml:space="preserve">4.07088232040405</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92051386833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69632816314697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78654909133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45573902130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49948287010193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69086003303528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56783223152161</t>
+    <t xml:space="preserve">3.92051362991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69632840156555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78654980659485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45573925971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49948215484619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69086074829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56783199310303</t>
   </si>
   <si>
     <t xml:space="preserve">3.63891506195068</t>
@@ -131,295 +131,295 @@
     <t xml:space="preserve">3.88497233390808</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82755947113037</t>
+    <t xml:space="preserve">3.82755923271179</t>
   </si>
   <si>
     <t xml:space="preserve">3.93691754341125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87130260467529</t>
+    <t xml:space="preserve">3.87130236625671</t>
   </si>
   <si>
     <t xml:space="preserve">4.05994653701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00800132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95332145690918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98612952232361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99159717559814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03260707855225</t>
+    <t xml:space="preserve">4.00800180435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9533212184906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98612928390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99159741401672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0326075553894</t>
   </si>
   <si>
     <t xml:space="preserve">4.05447816848755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24038887023926</t>
+    <t xml:space="preserve">4.24038934707642</t>
   </si>
   <si>
     <t xml:space="preserve">4.21031475067139</t>
   </si>
   <si>
+    <t xml:space="preserve">4.37435340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33607769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34701299667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33881139755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42903280258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52745580673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51105117797852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46184062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57119989395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67509031295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60947418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54932689666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4837121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34974813461304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42083024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42356491088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26499462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22398519515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22671890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3306097984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40169286727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3060040473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36615180969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26772880554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32514190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29233407974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27046203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29506731033325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39895915985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30873775482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38802289962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42629861831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34427976608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39075708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30326986312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49522399902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57292652130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65062808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69091844558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67940616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69379568099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66213941574097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61609363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57580327987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63623905181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63048315048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63336086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6391167640686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56429290771484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35133075714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08368921279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95130753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97145175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16139125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20168161392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24772691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27650594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03476524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755875587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84482645988464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633730888367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470378875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15851354598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784911155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83619260787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96281838417053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05778884887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0923228263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25636005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40313196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33406352996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51824712753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41752147674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45493364334106</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.37435293197632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33607816696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34701299667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33881139755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42903280258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52745580673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51105165481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46184015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57119989395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67508983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60947418212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54932689666748</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.48371171951294</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34974765777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42083072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42356538772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2649941444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25405883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22398471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22671890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23765468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3306097984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40169334411621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31967353820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30600452423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36615133285522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26772832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32514190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29233407974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27046298980713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29506826400757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39895915985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30873870849609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38802289962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42629909515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34428024291992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39075708389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3032693862915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49522352218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57292652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65062761306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67940711975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69379615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66213941574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61609363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57580327987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63623905181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63048315048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63336086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63911581039429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56429243087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35133075714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08368873596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95130753517151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97145223617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16139078140259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20168161392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.247727394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2765064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03476476669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755851745605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8448269367218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633730888367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15851306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01749849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784887313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83619260787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96281862258911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05778789520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0923228263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25636100769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40313196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3340630531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51824712753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41752099990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45493316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37435340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48371124267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45781135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53839159011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52975749969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48946809768677</t>
+    <t xml:space="preserve">4.45781183242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53839206695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52975845336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48946762084961</t>
   </si>
   <si>
     <t xml:space="preserve">4.51536798477173</t>
@@ -428,7 +428,7 @@
     <t xml:space="preserve">4.25923919677734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38874244689941</t>
+    <t xml:space="preserve">4.38874292373657</t>
   </si>
   <si>
     <t xml:space="preserve">4.46644449234009</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">4.38298654556274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36571931838989</t>
+    <t xml:space="preserve">4.36571979522705</t>
   </si>
   <si>
     <t xml:space="preserve">4.41464376449585</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">4.35996341705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33694076538086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29377269744873</t>
+    <t xml:space="preserve">4.33694124221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29377317428589</t>
   </si>
   <si>
     <t xml:space="preserve">4.31391763687134</t>
@@ -461,103 +461,103 @@
     <t xml:space="preserve">4.19880342483521</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22182607650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26211643218994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25348281860352</t>
+    <t xml:space="preserve">4.22182655334473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2621169090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25348329544067</t>
   </si>
   <si>
     <t xml:space="preserve">4.23046016693115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14412355422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19592618942261</t>
+    <t xml:space="preserve">4.14412403106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19592571258545</t>
   </si>
   <si>
     <t xml:space="preserve">4.16714715957642</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15563583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1153450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20743703842163</t>
+    <t xml:space="preserve">4.15563535690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11534452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20743608474731</t>
   </si>
   <si>
     <t xml:space="preserve">4.14700174331665</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1786584854126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0750560760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9426736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79878067970276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77575731277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83907079696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74697923660278</t>
+    <t xml:space="preserve">4.17865800857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07505559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94267344474792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497163772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79878091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77575707435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83907032012939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74697875976562</t>
   </si>
   <si>
     <t xml:space="preserve">3.74985599517822</t>
   </si>
   <si>
-    <t xml:space="preserve">3.85921573638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8246808052063</t>
+    <t xml:space="preserve">3.85921597480774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82468128204346</t>
   </si>
   <si>
     <t xml:space="preserve">3.79590225219727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87936043739319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81029176712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7843918800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76424598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72971177101135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71244406700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72395634651184</t>
+    <t xml:space="preserve">3.87936067581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8102912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439140319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76424622535706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72971129417419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7124445438385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72395539283752</t>
   </si>
   <si>
     <t xml:space="preserve">3.84194827079773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99735355377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06354379653931</t>
+    <t xml:space="preserve">3.99735307693481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06354331970215</t>
   </si>
   <si>
     <t xml:space="preserve">4.10959005355835</t>
@@ -569,46 +569,46 @@
     <t xml:space="preserve">4.08656644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03764343261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00310897827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97432994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91389513015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93979597091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92540621757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92828440666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89662742614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84770441055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273513793945</t>
+    <t xml:space="preserve">4.03764295578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00310850143433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97432971000671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91389489173889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93979620933533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92540669441223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92828392982483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8966269493103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84770393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273489952087</t>
   </si>
   <si>
     <t xml:space="preserve">3.75849008560181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55703997612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64337515830994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66927695274353</t>
+    <t xml:space="preserve">3.55704021453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64337539672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66927623748779</t>
   </si>
   <si>
     <t xml:space="preserve">3.65776467323303</t>
@@ -623,28 +623,28 @@
     <t xml:space="preserve">3.6030855178833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63186430931091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62610816955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66064357757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61459732055664</t>
+    <t xml:space="preserve">3.63186478614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6261088848114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66064262390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61459684371948</t>
   </si>
   <si>
     <t xml:space="preserve">3.80453610420227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95994067192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07217741012573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04339933395386</t>
+    <t xml:space="preserve">3.9599404335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07217693328857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0433988571167</t>
   </si>
   <si>
     <t xml:space="preserve">4.12685680389404</t>
@@ -653,31 +653,31 @@
     <t xml:space="preserve">4.13261270523071</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12110185623169</t>
+    <t xml:space="preserve">4.12110137939453</t>
   </si>
   <si>
     <t xml:space="preserve">4.36859750747681</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28226137161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33981943130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3484525680542</t>
+    <t xml:space="preserve">4.28226089477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33981895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34845161437988</t>
   </si>
   <si>
     <t xml:space="preserve">4.33118534088135</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30240678787231</t>
+    <t xml:space="preserve">4.30240631103516</t>
   </si>
   <si>
     <t xml:space="preserve">4.27075004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2275824546814</t>
+    <t xml:space="preserve">4.22758293151855</t>
   </si>
   <si>
     <t xml:space="preserve">4.2131929397583</t>
@@ -686,28 +686,31 @@
     <t xml:space="preserve">4.18153619766235</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09807777404785</t>
+    <t xml:space="preserve">4.09807825088501</t>
   </si>
   <si>
     <t xml:space="preserve">4.00598621368408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10383462905884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02901029586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06929969787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21894836425781</t>
+    <t xml:space="preserve">4.10383415222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0290093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06929922103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04627656936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21894884109497</t>
   </si>
   <si>
     <t xml:space="preserve">4.30816221237183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14988040924072</t>
+    <t xml:space="preserve">4.14987993240356</t>
   </si>
   <si>
     <t xml:space="preserve">4.47220087051392</t>
@@ -722,19 +725,19 @@
     <t xml:space="preserve">4.44342231750488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59307050704956</t>
+    <t xml:space="preserve">4.59307098388672</t>
   </si>
   <si>
     <t xml:space="preserve">4.62472772598267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57004833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71969747543335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70818567276001</t>
+    <t xml:space="preserve">4.57004880905151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71969652175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70818519592285</t>
   </si>
   <si>
     <t xml:space="preserve">4.80315494537354</t>
@@ -746,13 +749,13 @@
     <t xml:space="preserve">4.70530796051025</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7024302482605</t>
+    <t xml:space="preserve">4.70242977142334</t>
   </si>
   <si>
     <t xml:space="preserve">4.64487266540527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62184953689575</t>
+    <t xml:space="preserve">4.62185001373291</t>
   </si>
   <si>
     <t xml:space="preserve">4.54702520370483</t>
@@ -761,7 +764,7 @@
     <t xml:space="preserve">4.52687978744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46068906784058</t>
+    <t xml:space="preserve">4.46068954467773</t>
   </si>
   <si>
     <t xml:space="preserve">4.60458278656006</t>
@@ -770,61 +773,61 @@
     <t xml:space="preserve">4.71394062042236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66501712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74559783935547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76574277877808</t>
+    <t xml:space="preserve">4.66501760482788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74559736251831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76574325561523</t>
   </si>
   <si>
     <t xml:space="preserve">4.74847555160522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78301048278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77149868011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82329988479614</t>
+    <t xml:space="preserve">4.78301000595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77149820327759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8233003616333</t>
   </si>
   <si>
     <t xml:space="preserve">4.92690324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94992637634277</t>
+    <t xml:space="preserve">4.94992589950562</t>
   </si>
   <si>
     <t xml:space="preserve">4.98446035385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02475118637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05640745162964</t>
+    <t xml:space="preserve">5.02475070953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0564079284668</t>
   </si>
   <si>
     <t xml:space="preserve">4.89236879348755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86358976364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82905626296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8759241104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91160106658936</t>
+    <t xml:space="preserve">4.86359024047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82905530929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87592363357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9116005897522</t>
   </si>
   <si>
     <t xml:space="preserve">4.93538570404053</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89970874786377</t>
+    <t xml:space="preserve">4.89970827102661</t>
   </si>
   <si>
     <t xml:space="preserve">4.9205207824707</t>
@@ -833,40 +836,40 @@
     <t xml:space="preserve">5.01268720626831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96809101104736</t>
+    <t xml:space="preserve">4.96809053421021</t>
   </si>
   <si>
     <t xml:space="preserve">4.97106409072876</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89376211166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94727849960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94133234024048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92943954467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88781595230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85511112213135</t>
+    <t xml:space="preserve">4.89376258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94727802276611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94133281707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92944002151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88781642913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85511159896851</t>
   </si>
   <si>
     <t xml:space="preserve">4.79862260818481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77186489105225</t>
+    <t xml:space="preserve">4.77186441421509</t>
   </si>
   <si>
     <t xml:space="preserve">4.75105285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78673028945923</t>
+    <t xml:space="preserve">4.78672981262207</t>
   </si>
   <si>
     <t xml:space="preserve">4.73321437835693</t>
@@ -887,13 +890,13 @@
     <t xml:space="preserve">4.70348310470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72132158279419</t>
+    <t xml:space="preserve">4.72132205963135</t>
   </si>
   <si>
     <t xml:space="preserve">4.63807392120361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72726678848267</t>
+    <t xml:space="preserve">4.72726726531982</t>
   </si>
   <si>
     <t xml:space="preserve">4.81646108627319</t>
@@ -908,7 +911,7 @@
     <t xml:space="preserve">4.94430541992188</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98295640945435</t>
+    <t xml:space="preserve">4.9829568862915</t>
   </si>
   <si>
     <t xml:space="preserve">4.95322513580322</t>
@@ -923,16 +926,16 @@
     <t xml:space="preserve">4.89078903198242</t>
   </si>
   <si>
-    <t xml:space="preserve">5.00376844406128</t>
+    <t xml:space="preserve">5.00376796722412</t>
   </si>
   <si>
     <t xml:space="preserve">5.05431127548218</t>
   </si>
   <si>
-    <t xml:space="preserve">5.04836463928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99782133102417</t>
+    <t xml:space="preserve">5.04836511611938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99782180786133</t>
   </si>
   <si>
     <t xml:space="preserve">4.98592948913574</t>
@@ -947,34 +950,34 @@
     <t xml:space="preserve">5.11080074310303</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07512283325195</t>
+    <t xml:space="preserve">5.07512235641479</t>
   </si>
   <si>
     <t xml:space="preserve">5.0810694694519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.09593486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.11377429962158</t>
+    <t xml:space="preserve">5.09593534469604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.11377382278442</t>
   </si>
   <si>
     <t xml:space="preserve">5.03944540023804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02755355834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97700977325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05133867263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99484872817993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01566076278687</t>
+    <t xml:space="preserve">5.02755308151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97701025009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05133819580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99484825134277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01566123962402</t>
   </si>
   <si>
     <t xml:space="preserve">5.06620407104492</t>
@@ -986,40 +989,40 @@
     <t xml:space="preserve">5.23269844055176</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24459171295166</t>
+    <t xml:space="preserve">5.2445912361145</t>
   </si>
   <si>
     <t xml:space="preserve">5.23864555358887</t>
   </si>
   <si>
-    <t xml:space="preserve">5.19702100753784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17323637008667</t>
+    <t xml:space="preserve">5.197021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17323684692383</t>
   </si>
   <si>
     <t xml:space="preserve">5.1851282119751</t>
   </si>
   <si>
-    <t xml:space="preserve">5.20891427993774</t>
+    <t xml:space="preserve">5.20891380310059</t>
   </si>
   <si>
     <t xml:space="preserve">5.1940484046936</t>
   </si>
   <si>
-    <t xml:space="preserve">5.24756383895874</t>
+    <t xml:space="preserve">5.2475643157959</t>
   </si>
   <si>
     <t xml:space="preserve">5.25053739547729</t>
   </si>
   <si>
-    <t xml:space="preserve">5.26243019104004</t>
+    <t xml:space="preserve">5.26242971420288</t>
   </si>
   <si>
     <t xml:space="preserve">5.14945125579834</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16431713104248</t>
+    <t xml:space="preserve">5.16431760787964</t>
   </si>
   <si>
     <t xml:space="preserve">5.21485948562622</t>
@@ -1031,10 +1034,10 @@
     <t xml:space="preserve">5.44081687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64893674850464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67866706848145</t>
+    <t xml:space="preserve">5.64893627166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6786675453186</t>
   </si>
   <si>
     <t xml:space="preserve">5.47054862976074</t>
@@ -1049,19 +1052,19 @@
     <t xml:space="preserve">5.59541940689087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58947372436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.5032525062561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.57758188247681</t>
+    <t xml:space="preserve">5.58947420120239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.50325298309326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.57758140563965</t>
   </si>
   <si>
     <t xml:space="preserve">5.75002241134644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90165138244629</t>
+    <t xml:space="preserve">5.90165233612061</t>
   </si>
   <si>
     <t xml:space="preserve">5.91651725769043</t>
@@ -1070,16 +1073,16 @@
     <t xml:space="preserve">6.20193815231323</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1900463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.11274337768555</t>
+    <t xml:space="preserve">6.19004535675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.11274385452271</t>
   </si>
   <si>
     <t xml:space="preserve">6.12463617324829</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15436792373657</t>
+    <t xml:space="preserve">6.15436744689941</t>
   </si>
   <si>
     <t xml:space="preserve">6.03544235229492</t>
@@ -1088,10 +1091,10 @@
     <t xml:space="preserve">5.97598028182983</t>
   </si>
   <si>
-    <t xml:space="preserve">5.88975954055786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.0057110786438</t>
+    <t xml:space="preserve">5.8897590637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00571060180664</t>
   </si>
   <si>
     <t xml:space="preserve">6.29113054275513</t>
@@ -1100,13 +1103,13 @@
     <t xml:space="preserve">6.34464836120605</t>
   </si>
   <si>
-    <t xml:space="preserve">6.17815160751343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39816379547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38627099990845</t>
+    <t xml:space="preserve">6.17815256118774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39816331863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38627195358276</t>
   </si>
   <si>
     <t xml:space="preserve">6.33275508880615</t>
@@ -1121,22 +1124,22 @@
     <t xml:space="preserve">6.41600227355957</t>
   </si>
   <si>
-    <t xml:space="preserve">6.40410900115967</t>
+    <t xml:space="preserve">6.40410947799683</t>
   </si>
   <si>
     <t xml:space="preserve">6.24356126785278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35653972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44573497772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6003360748291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58844327926636</t>
+    <t xml:space="preserve">6.35653924942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44573402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60033655166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5884428024292</t>
   </si>
   <si>
     <t xml:space="preserve">6.71926021575928</t>
@@ -1148,7 +1151,7 @@
     <t xml:space="preserve">6.48141098022461</t>
   </si>
   <si>
-    <t xml:space="preserve">6.07111978530884</t>
+    <t xml:space="preserve">6.071120262146</t>
   </si>
   <si>
     <t xml:space="preserve">5.82732391357422</t>
@@ -1166,64 +1169,64 @@
     <t xml:space="preserve">5.73812913894653</t>
   </si>
   <si>
-    <t xml:space="preserve">5.81840467453003</t>
+    <t xml:space="preserve">5.81840419769287</t>
   </si>
   <si>
     <t xml:space="preserve">5.73218393325806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72623634338379</t>
+    <t xml:space="preserve">5.72623682022095</t>
   </si>
   <si>
     <t xml:space="preserve">5.85705471038818</t>
   </si>
   <si>
-    <t xml:space="preserve">5.86300086975098</t>
+    <t xml:space="preserve">5.86300134658813</t>
   </si>
   <si>
     <t xml:space="preserve">5.9581413269043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92841005325317</t>
+    <t xml:space="preserve">5.92840909957886</t>
   </si>
   <si>
     <t xml:space="preserve">5.76191473007202</t>
   </si>
   <si>
-    <t xml:space="preserve">5.70839834213257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79759216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75596857070923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6846137046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69650602340698</t>
+    <t xml:space="preserve">5.70839786529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79759168624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75596809387207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68461322784424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69650650024414</t>
   </si>
   <si>
     <t xml:space="preserve">5.66082859039307</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50622653961182</t>
+    <t xml:space="preserve">5.50622701644897</t>
   </si>
   <si>
     <t xml:space="preserve">5.45865678787231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33973073959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15539741516113</t>
+    <t xml:space="preserve">5.33973121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15539693832397</t>
   </si>
   <si>
     <t xml:space="preserve">5.30999994277954</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0364727973938</t>
+    <t xml:space="preserve">5.03647232055664</t>
   </si>
   <si>
     <t xml:space="preserve">4.91754674911499</t>
@@ -1238,13 +1241,13 @@
     <t xml:space="preserve">4.85213899612427</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14350509643555</t>
+    <t xml:space="preserve">5.14350461959839</t>
   </si>
   <si>
     <t xml:space="preserve">4.75699949264526</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7944598197937</t>
+    <t xml:space="preserve">4.79446029663086</t>
   </si>
   <si>
     <t xml:space="preserve">4.70824003219604</t>
@@ -1256,7 +1259,7 @@
     <t xml:space="preserve">4.47752571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46860647201538</t>
+    <t xml:space="preserve">4.46860599517822</t>
   </si>
   <si>
     <t xml:space="preserve">4.53104162216187</t>
@@ -1280,7 +1283,7 @@
     <t xml:space="preserve">4.41211652755737</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36811351776123</t>
+    <t xml:space="preserve">4.36811399459839</t>
   </si>
   <si>
     <t xml:space="preserve">4.29913759231567</t>
@@ -1289,16 +1292,16 @@
     <t xml:space="preserve">4.4852557182312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46503782272339</t>
+    <t xml:space="preserve">4.46503829956055</t>
   </si>
   <si>
     <t xml:space="preserve">4.4418478012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29378652572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19210529327393</t>
+    <t xml:space="preserve">4.29378604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19210577011108</t>
   </si>
   <si>
     <t xml:space="preserve">4.57336091995239</t>
@@ -1316,7 +1319,7 @@
     <t xml:space="preserve">4.95713901519775</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14391183853149</t>
+    <t xml:space="preserve">5.14391136169434</t>
   </si>
   <si>
     <t xml:space="preserve">5.34731435775757</t>
@@ -1325,16 +1328,16 @@
     <t xml:space="preserve">5.28271102905273</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17781162261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.01278686523438</t>
+    <t xml:space="preserve">5.17781209945679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01278734207153</t>
   </si>
   <si>
     <t xml:space="preserve">4.96993160247803</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05244445800781</t>
+    <t xml:space="preserve">5.05244398117065</t>
   </si>
   <si>
     <t xml:space="preserve">4.98912048339844</t>
@@ -1346,31 +1349,31 @@
     <t xml:space="preserve">5.03197622299194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0159854888916</t>
+    <t xml:space="preserve">5.01598501205444</t>
   </si>
   <si>
     <t xml:space="preserve">5.02621936798096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01470613479614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08506536483765</t>
+    <t xml:space="preserve">5.01470565795898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08506488800049</t>
   </si>
   <si>
     <t xml:space="preserve">4.93539190292358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.92579793930054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9654541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02557992935181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.04029130935669</t>
+    <t xml:space="preserve">4.92579746246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96545457839966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02557945251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.04029083251953</t>
   </si>
   <si>
     <t xml:space="preserve">5.02110242843628</t>
@@ -1391,7 +1394,7 @@
     <t xml:space="preserve">5.14135313034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97888708114624</t>
+    <t xml:space="preserve">4.97888660430908</t>
   </si>
   <si>
     <t xml:space="preserve">4.76461029052734</t>
@@ -1403,13 +1406,13 @@
     <t xml:space="preserve">4.78124046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73326826095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71471834182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66290950775146</t>
+    <t xml:space="preserve">4.73326873779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71471881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66290903091431</t>
   </si>
   <si>
     <t xml:space="preserve">4.55097341537476</t>
@@ -1421,34 +1424,34 @@
     <t xml:space="preserve">4.57399988174438</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65267515182495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63092708587646</t>
+    <t xml:space="preserve">4.65267562866211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63092756271362</t>
   </si>
   <si>
     <t xml:space="preserve">4.72943067550659</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81961870193481</t>
+    <t xml:space="preserve">4.81961822509766</t>
   </si>
   <si>
     <t xml:space="preserve">4.79403305053711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68401670455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58679246902466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87419843673706</t>
+    <t xml:space="preserve">4.68401622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58679294586182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8741979598999</t>
   </si>
   <si>
     <t xml:space="preserve">4.99108505249023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88932514190674</t>
+    <t xml:space="preserve">4.88932466506958</t>
   </si>
   <si>
     <t xml:space="preserve">4.98421001434326</t>
@@ -1460,7 +1463,7 @@
     <t xml:space="preserve">4.79375267028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79512739181519</t>
+    <t xml:space="preserve">4.79512691497803</t>
   </si>
   <si>
     <t xml:space="preserve">4.76074838638306</t>
@@ -1469,10 +1472,10 @@
     <t xml:space="preserve">4.74630975723267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86113405227661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79031372070312</t>
+    <t xml:space="preserve">4.86113452911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79031419754028</t>
   </si>
   <si>
     <t xml:space="preserve">4.81300401687622</t>
@@ -1484,13 +1487,13 @@
     <t xml:space="preserve">4.77174997329712</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73187112808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84532022476196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78687620162964</t>
+    <t xml:space="preserve">4.73187065124512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84532070159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7868766784668</t>
   </si>
   <si>
     <t xml:space="preserve">4.76968669891357</t>
@@ -1502,7 +1505,7 @@
     <t xml:space="preserve">4.97802114486694</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96770763397217</t>
+    <t xml:space="preserve">4.96770811080933</t>
   </si>
   <si>
     <t xml:space="preserve">4.82675552368164</t>
@@ -1511,7 +1514,7 @@
     <t xml:space="preserve">4.85013294219971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86044692993164</t>
+    <t xml:space="preserve">4.86044645309448</t>
   </si>
   <si>
     <t xml:space="preserve">4.89963817596436</t>
@@ -1523,7 +1526,7 @@
     <t xml:space="preserve">4.99177312850952</t>
   </si>
   <si>
-    <t xml:space="preserve">5.0543417930603</t>
+    <t xml:space="preserve">5.05434226989746</t>
   </si>
   <si>
     <t xml:space="preserve">4.96151971817017</t>
@@ -1532,7 +1535,7 @@
     <t xml:space="preserve">4.97939682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99246072769165</t>
+    <t xml:space="preserve">4.99246025085449</t>
   </si>
   <si>
     <t xml:space="preserve">4.85838413238525</t>
@@ -1553,7 +1556,7 @@
     <t xml:space="preserve">4.93882989883423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91682720184326</t>
+    <t xml:space="preserve">4.91682767868042</t>
   </si>
   <si>
     <t xml:space="preserve">4.83363151550293</t>
@@ -1562,10 +1565,10 @@
     <t xml:space="preserve">4.76556205749512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75868606567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75043535232544</t>
+    <t xml:space="preserve">4.75868654251099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75043487548828</t>
   </si>
   <si>
     <t xml:space="preserve">4.67067718505859</t>
@@ -1574,7 +1577,7 @@
     <t xml:space="preserve">4.58129262924194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54278802871704</t>
+    <t xml:space="preserve">4.5427885055542</t>
   </si>
   <si>
     <t xml:space="preserve">4.4630298614502</t>
@@ -1583,10 +1586,10 @@
     <t xml:space="preserve">4.48228216171265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51941108703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60604524612427</t>
+    <t xml:space="preserve">4.51941061019897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60604476928711</t>
   </si>
   <si>
     <t xml:space="preserve">4.59779405593872</t>
@@ -1595,7 +1598,7 @@
     <t xml:space="preserve">4.52972412109375</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53797483444214</t>
+    <t xml:space="preserve">4.5379753112793</t>
   </si>
   <si>
     <t xml:space="preserve">4.5792293548584</t>
@@ -1616,13 +1619,13 @@
     <t xml:space="preserve">4.51597261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49053287506104</t>
+    <t xml:space="preserve">4.49053335189819</t>
   </si>
   <si>
     <t xml:space="preserve">4.52078533172607</t>
   </si>
   <si>
-    <t xml:space="preserve">4.518723487854</t>
+    <t xml:space="preserve">4.51872396469116</t>
   </si>
   <si>
     <t xml:space="preserve">4.53041219711304</t>
@@ -1631,10 +1634,10 @@
     <t xml:space="preserve">4.51047229766846</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52491140365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48503160476685</t>
+    <t xml:space="preserve">4.52491188049316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.485032081604</t>
   </si>
   <si>
     <t xml:space="preserve">4.47746896743774</t>
@@ -1643,7 +1646,7 @@
     <t xml:space="preserve">4.78412628173828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66517639160156</t>
+    <t xml:space="preserve">4.6651759147644</t>
   </si>
   <si>
     <t xml:space="preserve">4.6541748046875</t>
@@ -1664,16 +1667,16 @@
     <t xml:space="preserve">4.63354825973511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5503511428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50840950012207</t>
+    <t xml:space="preserve">4.55035161972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50840902328491</t>
   </si>
   <si>
     <t xml:space="preserve">4.41558742523193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42727613449097</t>
+    <t xml:space="preserve">4.42727661132812</t>
   </si>
   <si>
     <t xml:space="preserve">4.40046072006226</t>
@@ -1682,13 +1685,13 @@
     <t xml:space="preserve">4.33239126205444</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22237968444824</t>
+    <t xml:space="preserve">4.2223801612854</t>
   </si>
   <si>
     <t xml:space="preserve">4.20450305938721</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16256141662598</t>
+    <t xml:space="preserve">4.16256093978882</t>
   </si>
   <si>
     <t xml:space="preserve">4.06630086898804</t>
@@ -1697,7 +1700,7 @@
     <t xml:space="preserve">4.09311676025391</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98791790008545</t>
+    <t xml:space="preserve">3.98791742324829</t>
   </si>
   <si>
     <t xml:space="preserve">4.05942487716675</t>
@@ -1706,7 +1709,7 @@
     <t xml:space="preserve">4.09724140167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0497989654541</t>
+    <t xml:space="preserve">4.04979944229126</t>
   </si>
   <si>
     <t xml:space="preserve">4.05323696136475</t>
@@ -1739,13 +1742,13 @@
     <t xml:space="preserve">4.22100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15293455123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36608266830444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27601051330566</t>
+    <t xml:space="preserve">4.15293502807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36608219146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27601003646851</t>
   </si>
   <si>
     <t xml:space="preserve">4.22513008117676</t>
@@ -1754,22 +1757,22 @@
     <t xml:space="preserve">4.19487714767456</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12749481201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15224742889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13505840301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09174156188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0326099395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03467226028442</t>
+    <t xml:space="preserve">4.12749528884888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1522479057312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13505792617798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09174108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03260946273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03467273712158</t>
   </si>
   <si>
     <t xml:space="preserve">4.054612159729</t>
@@ -1784,28 +1787,28 @@
     <t xml:space="preserve">4.23544359207153</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19900226593018</t>
+    <t xml:space="preserve">4.19900178909302</t>
   </si>
   <si>
     <t xml:space="preserve">4.1886887550354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11374378204346</t>
+    <t xml:space="preserve">4.1137433052063</t>
   </si>
   <si>
     <t xml:space="preserve">4.04429864883423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02917194366455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99273061752319</t>
+    <t xml:space="preserve">4.02917242050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99273109436035</t>
   </si>
   <si>
     <t xml:space="preserve">3.99891877174377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96316480636597</t>
+    <t xml:space="preserve">3.96316528320312</t>
   </si>
   <si>
     <t xml:space="preserve">3.88684439659119</t>
@@ -1814,7 +1817,7 @@
     <t xml:space="preserve">3.98241710662842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90540933609009</t>
+    <t xml:space="preserve">3.90540885925293</t>
   </si>
   <si>
     <t xml:space="preserve">3.87378072738647</t>
@@ -1829,7 +1832,7 @@
     <t xml:space="preserve">3.69501256942749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73351573944092</t>
+    <t xml:space="preserve">3.73351621627808</t>
   </si>
   <si>
     <t xml:space="preserve">3.72870302200317</t>
@@ -1838,22 +1841,22 @@
     <t xml:space="preserve">3.64894461631775</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70051264762878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83115148544312</t>
+    <t xml:space="preserve">3.70051240921021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83115172386169</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990830421448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.9934184551239</t>
+    <t xml:space="preserve">3.99341797828674</t>
   </si>
   <si>
     <t xml:space="preserve">3.97829174995422</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06286334991455</t>
+    <t xml:space="preserve">4.06286287307739</t>
   </si>
   <si>
     <t xml:space="preserve">4.048424243927</t>
@@ -1898,10 +1901,10 @@
     <t xml:space="preserve">4.31864023208618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28907442092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2904486656189</t>
+    <t xml:space="preserve">4.2890739440918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29044914245605</t>
   </si>
   <si>
     <t xml:space="preserve">4.25057029724121</t>
@@ -1925,13 +1928,13 @@
     <t xml:space="preserve">4.05392503738403</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12543249130249</t>
+    <t xml:space="preserve">4.12543201446533</t>
   </si>
   <si>
     <t xml:space="preserve">4.0896782875061</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13230800628662</t>
+    <t xml:space="preserve">4.13230752944946</t>
   </si>
   <si>
     <t xml:space="preserve">4.17149925231934</t>
@@ -1946,7 +1949,7 @@
     <t xml:space="preserve">4.2189416885376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21481704711914</t>
+    <t xml:space="preserve">4.21481657028198</t>
   </si>
   <si>
     <t xml:space="preserve">4.16324853897095</t>
@@ -1955,7 +1958,7 @@
     <t xml:space="preserve">4.28494834899902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34476709365845</t>
+    <t xml:space="preserve">4.34476757049561</t>
   </si>
   <si>
     <t xml:space="preserve">4.25400829315186</t>
@@ -1973,16 +1976,16 @@
     <t xml:space="preserve">4.57441663742065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47609424591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44171476364136</t>
+    <t xml:space="preserve">4.47609376907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44171524047852</t>
   </si>
   <si>
     <t xml:space="preserve">4.44859075546265</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55653953552246</t>
+    <t xml:space="preserve">4.55654001235962</t>
   </si>
   <si>
     <t xml:space="preserve">4.57785415649414</t>
@@ -1997,13 +2000,13 @@
     <t xml:space="preserve">4.60673236846924</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57097911834717</t>
+    <t xml:space="preserve">4.57097864151001</t>
   </si>
   <si>
     <t xml:space="preserve">4.57166624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5077223777771</t>
+    <t xml:space="preserve">4.50772190093994</t>
   </si>
   <si>
     <t xml:space="preserve">4.45752906799316</t>
@@ -2012,13 +2015,13 @@
     <t xml:space="preserve">4.41971302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46234273910522</t>
+    <t xml:space="preserve">4.46234226226807</t>
   </si>
   <si>
     <t xml:space="preserve">4.4279637336731</t>
   </si>
   <si>
-    <t xml:space="preserve">4.54485130310059</t>
+    <t xml:space="preserve">4.54485082626343</t>
   </si>
   <si>
     <t xml:space="preserve">4.52422380447388</t>
@@ -2027,13 +2030,13 @@
     <t xml:space="preserve">4.55860280990601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58610534667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45546674728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48296976089478</t>
+    <t xml:space="preserve">4.58610582351685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45546627044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48296928405762</t>
   </si>
   <si>
     <t xml:space="preserve">4.53109979629517</t>
@@ -2045,16 +2048,16 @@
     <t xml:space="preserve">4.59985685348511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64111089706421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61360836029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62048387527466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62735939025879</t>
+    <t xml:space="preserve">4.64111137390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61360883712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62048435211182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62735986709595</t>
   </si>
   <si>
     <t xml:space="preserve">4.7167444229126</t>
@@ -2069,10 +2072,7 @@
     <t xml:space="preserve">4.55228900909424</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6117959022522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54485082626343</t>
+    <t xml:space="preserve">4.61179637908936</t>
   </si>
   <si>
     <t xml:space="preserve">4.60435819625854</t>
@@ -2096,7 +2096,7 @@
     <t xml:space="preserve">4.65642690658569</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58948183059692</t>
+    <t xml:space="preserve">4.58948135375977</t>
   </si>
   <si>
     <t xml:space="preserve">4.51509761810303</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">4.56716537475586</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55972766876221</t>
+    <t xml:space="preserve">4.55972719192505</t>
   </si>
   <si>
     <t xml:space="preserve">4.64898824691772</t>
@@ -2120,13 +2120,13 @@
     <t xml:space="preserve">4.5820426940918</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52997446060181</t>
+    <t xml:space="preserve">4.52997398376465</t>
   </si>
   <si>
     <t xml:space="preserve">4.4481520652771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38120603561401</t>
+    <t xml:space="preserve">4.38120651245117</t>
   </si>
   <si>
     <t xml:space="preserve">4.42583703994751</t>
@@ -2153,10 +2153,10 @@
     <t xml:space="preserve">4.33657646179199</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59691953659058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50765895843506</t>
+    <t xml:space="preserve">4.59691905975342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50765943527222</t>
   </si>
   <si>
     <t xml:space="preserve">4.49278211593628</t>
@@ -2165,10 +2165,10 @@
     <t xml:space="preserve">4.48534393310547</t>
   </si>
   <si>
-    <t xml:space="preserve">4.43327569961548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40352201461792</t>
+    <t xml:space="preserve">4.43327522277832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40352153778076</t>
   </si>
   <si>
     <t xml:space="preserve">4.38864517211914</t>
@@ -2177,7 +2177,7 @@
     <t xml:space="preserve">4.39608287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35145282745361</t>
+    <t xml:space="preserve">4.35145330429077</t>
   </si>
   <si>
     <t xml:space="preserve">4.24731588363647</t>
@@ -2195,13 +2195,13 @@
     <t xml:space="preserve">4.13573980331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01672601699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0241641998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93490409851074</t>
+    <t xml:space="preserve">4.01672554016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02416467666626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93490362167358</t>
   </si>
   <si>
     <t xml:space="preserve">3.9051501750946</t>
@@ -2213,16 +2213,16 @@
     <t xml:space="preserve">3.89771151542664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98697257041931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92002701759338</t>
+    <t xml:space="preserve">3.98697209358215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92002654075623</t>
   </si>
   <si>
     <t xml:space="preserve">3.94234228134155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97953391075134</t>
+    <t xml:space="preserve">3.97953343391418</t>
   </si>
   <si>
     <t xml:space="preserve">3.97209572792053</t>
@@ -2234,16 +2234,16 @@
     <t xml:space="preserve">4.06879425048828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09854793548584</t>
+    <t xml:space="preserve">4.098548412323</t>
   </si>
   <si>
     <t xml:space="preserve">4.16549348831177</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18780851364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18037033081055</t>
+    <t xml:space="preserve">4.18780899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18036985397339</t>
   </si>
   <si>
     <t xml:space="preserve">4.17293214797974</t>
@@ -2255,25 +2255,25 @@
     <t xml:space="preserve">4.14317798614502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12830114364624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15805530548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03904056549072</t>
+    <t xml:space="preserve">4.1283016204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15805578231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03904104232788</t>
   </si>
   <si>
     <t xml:space="preserve">4.23243856430054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23987770080566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26963090896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30682277679443</t>
+    <t xml:space="preserve">4.23987722396851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26963043212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30682229995728</t>
   </si>
   <si>
     <t xml:space="preserve">4.29194593429565</t>
@@ -2285,19 +2285,19 @@
     <t xml:space="preserve">4.27706909179688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29938459396362</t>
+    <t xml:space="preserve">4.29938411712646</t>
   </si>
   <si>
     <t xml:space="preserve">4.28450775146484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41095972061157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44071340560913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46302890777588</t>
+    <t xml:space="preserve">4.41096019744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44071388244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46302843093872</t>
   </si>
   <si>
     <t xml:space="preserve">4.47046709060669</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">4.79031753540039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70105695724487</t>
+    <t xml:space="preserve">4.70105743408203</t>
   </si>
   <si>
     <t xml:space="preserve">4.67874193191528</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">4.75312566757202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67130374908447</t>
+    <t xml:space="preserve">4.67130422592163</t>
   </si>
   <si>
     <t xml:space="preserve">4.70849514007568</t>
@@ -2342,10 +2342,10 @@
     <t xml:space="preserve">4.08367109298706</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06135559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96465730667114</t>
+    <t xml:space="preserve">4.06135606765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96465706825256</t>
   </si>
   <si>
     <t xml:space="preserve">3.92746543884277</t>
@@ -2357,10 +2357,10 @@
     <t xml:space="preserve">3.38446354866028</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37702512741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71872854232788</t>
+    <t xml:space="preserve">3.37702488899231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7187283039093</t>
   </si>
   <si>
     <t xml:space="preserve">2.76335859298706</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">2.54020714759827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57367992401123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70385146141052</t>
+    <t xml:space="preserve">2.57367968559265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70385122299194</t>
   </si>
   <si>
     <t xml:space="preserve">2.64806365966797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77451610565186</t>
+    <t xml:space="preserve">2.77451634407043</t>
   </si>
   <si>
     <t xml:space="preserve">2.70757102966309</t>
@@ -2390,25 +2390,25 @@
     <t xml:space="preserve">2.8079891204834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83402323722839</t>
+    <t xml:space="preserve">2.83402347564697</t>
   </si>
   <si>
     <t xml:space="preserve">2.826584815979</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68525576591492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78939270973206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80426955223083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75220131874084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7001326084137</t>
+    <t xml:space="preserve">2.68525552749634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78939294815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80426979064941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75220108032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70013236999512</t>
   </si>
   <si>
     <t xml:space="preserve">2.7150092124939</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">2.76707792282104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73732399940491</t>
+    <t xml:space="preserve">2.73732423782349</t>
   </si>
   <si>
     <t xml:space="preserve">2.69641304016113</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">2.69269394874573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62946772575378</t>
+    <t xml:space="preserve">2.62946796417236</t>
   </si>
   <si>
     <t xml:space="preserve">2.62574887275696</t>
@@ -2441,13 +2441,13 @@
     <t xml:space="preserve">2.64062547683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65550208091736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.614590883255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60715270042419</t>
+    <t xml:space="preserve">2.65550184249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61459112167358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60715246200562</t>
   </si>
   <si>
     <t xml:space="preserve">2.63318705558777</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">2.51417303085327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6108717918396</t>
+    <t xml:space="preserve">2.61087203025818</t>
   </si>
   <si>
     <t xml:space="preserve">2.61831021308899</t>
@@ -2510,7 +2510,7 @@
     <t xml:space="preserve">2.77823519706726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91584539413452</t>
+    <t xml:space="preserve">2.9158456325531</t>
   </si>
   <si>
     <t xml:space="preserve">2.54392671585083</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">2.58111834526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59971404075623</t>
+    <t xml:space="preserve">2.5997142791748</t>
   </si>
   <si>
     <t xml:space="preserve">2.63690614700317</t>
@@ -4803,6 +4803,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.44000005722046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60999989509583</t>
   </si>
 </sst>
 </file>
@@ -12491,7 +12494,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G283" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12517,7 +12520,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G284" t="s">
-        <v>20</v>
+        <v>229</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12621,7 +12624,7 @@
         <v>6.81424283981323</v>
       </c>
       <c r="G288" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12699,7 +12702,7 @@
         <v>6.95833683013916</v>
       </c>
       <c r="G291" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12881,7 +12884,7 @@
         <v>6.70268678665161</v>
       </c>
       <c r="G298" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12933,7 +12936,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G300" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -13011,7 +13014,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G303" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13037,7 +13040,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G304" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -13167,7 +13170,7 @@
         <v>7.06989288330078</v>
       </c>
       <c r="G309" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13193,7 +13196,7 @@
         <v>7.17680215835571</v>
       </c>
       <c r="G310" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13245,7 +13248,7 @@
         <v>7.41850709915161</v>
       </c>
       <c r="G312" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13271,7 +13274,7 @@
         <v>7.46963787078857</v>
       </c>
       <c r="G313" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13323,7 +13326,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G315" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13375,7 +13378,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G317" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13401,7 +13404,7 @@
         <v>7.60443496704102</v>
       </c>
       <c r="G318" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13427,7 +13430,7 @@
         <v>7.75782489776611</v>
       </c>
       <c r="G319" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13453,7 +13456,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G320" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13505,7 +13508,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G322" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13531,7 +13534,7 @@
         <v>7.59978723526001</v>
       </c>
       <c r="G323" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13557,7 +13560,7 @@
         <v>7.59513902664185</v>
       </c>
       <c r="G324" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13661,7 +13664,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G328" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13687,7 +13690,7 @@
         <v>7.46498918533325</v>
       </c>
       <c r="G329" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13739,7 +13742,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G331" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13765,7 +13768,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G332" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13791,7 +13794,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G333" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13817,7 +13820,7 @@
         <v>7.311598777771</v>
       </c>
       <c r="G334" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13843,7 +13846,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G335" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13869,7 +13872,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G336" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13895,7 +13898,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G337" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13921,7 +13924,7 @@
         <v>7.53471183776855</v>
       </c>
       <c r="G338" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13947,7 +13950,7 @@
         <v>7.66486120223999</v>
       </c>
       <c r="G339" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -13973,7 +13976,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G340" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -13999,7 +14002,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G341" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14025,7 +14028,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G342" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -14051,7 +14054,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G343" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -14077,7 +14080,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G344" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -14103,7 +14106,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G345" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -14129,7 +14132,7 @@
         <v>7.95769691467285</v>
       </c>
       <c r="G346" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -14155,7 +14158,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G347" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -14181,7 +14184,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G348" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14207,7 +14210,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G349" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14233,7 +14236,7 @@
         <v>8.16686630249023</v>
       </c>
       <c r="G350" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14259,7 +14262,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G351" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14285,7 +14288,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G352" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14311,7 +14314,7 @@
         <v>7.8554368019104</v>
       </c>
       <c r="G353" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14337,7 +14340,7 @@
         <v>7.79965877532959</v>
       </c>
       <c r="G354" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14363,7 +14366,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G355" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14389,7 +14392,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G356" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14415,7 +14418,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G357" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14441,7 +14444,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G358" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14467,7 +14470,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G359" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14493,7 +14496,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G360" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14519,7 +14522,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G361" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14545,7 +14548,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G362" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14571,7 +14574,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G363" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14597,7 +14600,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G364" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14623,7 +14626,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G365" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14649,7 +14652,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G366" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14675,7 +14678,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G367" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14701,7 +14704,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G368" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14727,7 +14730,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G369" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14753,7 +14756,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G370" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14779,7 +14782,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G371" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14805,7 +14808,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G372" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14831,7 +14834,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G373" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14857,7 +14860,7 @@
         <v>7.59048986434937</v>
       </c>
       <c r="G374" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14883,7 +14886,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G375" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14909,7 +14912,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G376" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14935,7 +14938,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G377" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -14961,7 +14964,7 @@
         <v>7.4278039932251</v>
       </c>
       <c r="G378" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -14987,7 +14990,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G379" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -15013,7 +15016,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G380" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -15039,7 +15042,7 @@
         <v>7.39991521835327</v>
       </c>
       <c r="G381" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -15065,7 +15068,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G382" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -15091,7 +15094,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G383" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -15117,7 +15120,7 @@
         <v>7.16750478744507</v>
       </c>
       <c r="G384" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -15143,7 +15146,7 @@
         <v>7.21863508224487</v>
       </c>
       <c r="G385" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -15169,7 +15172,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G386" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15195,7 +15198,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G387" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15221,7 +15224,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G388" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15247,7 +15250,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G389" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15273,7 +15276,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G390" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15299,7 +15302,7 @@
         <v>7.59048986434937</v>
       </c>
       <c r="G391" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15325,7 +15328,7 @@
         <v>7.55330514907837</v>
       </c>
       <c r="G392" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15351,7 +15354,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G393" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15377,7 +15380,7 @@
         <v>7.72064018249512</v>
       </c>
       <c r="G394" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15403,7 +15406,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G395" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15429,7 +15432,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G396" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15455,7 +15458,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G397" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15481,7 +15484,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G398" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15507,7 +15510,7 @@
         <v>7.72993612289429</v>
       </c>
       <c r="G399" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15533,7 +15536,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G400" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15559,7 +15562,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G401" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15585,7 +15588,7 @@
         <v>7.74388122558594</v>
       </c>
       <c r="G402" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15611,7 +15614,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G403" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15637,7 +15640,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G404" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15663,7 +15666,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G405" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15689,7 +15692,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G406" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15715,7 +15718,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G407" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15741,7 +15744,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G408" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15767,7 +15770,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G409" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15793,7 +15796,7 @@
         <v>7.82289981842041</v>
       </c>
       <c r="G410" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15819,7 +15822,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G411" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15845,7 +15848,7 @@
         <v>7.89262294769287</v>
       </c>
       <c r="G412" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15871,7 +15874,7 @@
         <v>7.81360292434692</v>
       </c>
       <c r="G413" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15897,7 +15900,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G414" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15923,7 +15926,7 @@
         <v>7.79501104354858</v>
       </c>
       <c r="G415" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15949,7 +15952,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G416" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -15975,7 +15978,7 @@
         <v>8.01347637176514</v>
       </c>
       <c r="G417" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -16001,7 +16004,7 @@
         <v>7.99023485183716</v>
       </c>
       <c r="G418" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -16027,7 +16030,7 @@
         <v>7.93445587158203</v>
       </c>
       <c r="G419" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -16053,7 +16056,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G420" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -16079,7 +16082,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G421" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -16105,7 +16108,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G422" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -16131,7 +16134,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G423" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -16157,7 +16160,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G424" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -16183,7 +16186,7 @@
         <v>7.86008501052856</v>
       </c>
       <c r="G425" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -16209,7 +16212,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G426" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16235,7 +16238,7 @@
         <v>7.78106594085693</v>
       </c>
       <c r="G427" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16261,7 +16264,7 @@
         <v>7.89727115631104</v>
       </c>
       <c r="G428" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16287,7 +16290,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G429" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16313,7 +16316,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G430" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16339,7 +16342,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G431" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16365,7 +16368,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G432" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16391,7 +16394,7 @@
         <v>7.84149312973022</v>
       </c>
       <c r="G433" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16417,7 +16420,7 @@
         <v>7.92051219940186</v>
       </c>
       <c r="G434" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16443,7 +16446,7 @@
         <v>8.03206825256348</v>
       </c>
       <c r="G435" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16469,7 +16472,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G436" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16495,7 +16498,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G437" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16521,7 +16524,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G438" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16547,7 +16550,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G439" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16573,7 +16576,7 @@
         <v>8.19010734558105</v>
       </c>
       <c r="G440" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16599,7 +16602,7 @@
         <v>8.12503242492676</v>
       </c>
       <c r="G441" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16625,7 +16628,7 @@
         <v>8.08784675598145</v>
       </c>
       <c r="G442" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16651,7 +16654,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G443" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16677,7 +16680,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G444" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16703,7 +16706,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G445" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16729,7 +16732,7 @@
         <v>8.14362525939941</v>
       </c>
       <c r="G446" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16755,7 +16758,7 @@
         <v>8.12038421630859</v>
       </c>
       <c r="G447" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16781,7 +16784,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G448" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16807,7 +16810,7 @@
         <v>8.20869922637939</v>
       </c>
       <c r="G449" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16833,7 +16836,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G450" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16859,7 +16862,7 @@
         <v>8.22729206085205</v>
       </c>
       <c r="G451" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16885,7 +16888,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G452" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16911,7 +16914,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G453" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16937,7 +16940,7 @@
         <v>8.07390213012695</v>
       </c>
       <c r="G454" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -16963,7 +16966,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G455" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -16989,7 +16992,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G456" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -17015,7 +17018,7 @@
         <v>8.36673831939697</v>
       </c>
       <c r="G457" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -17041,7 +17044,7 @@
         <v>8.50618267059326</v>
       </c>
       <c r="G458" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -17067,7 +17070,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G459" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -17093,7 +17096,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G460" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -17119,7 +17122,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -17145,7 +17148,7 @@
         <v>8.5526647567749</v>
       </c>
       <c r="G462" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -17171,7 +17174,7 @@
         <v>8.54801654815674</v>
       </c>
       <c r="G463" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -17197,7 +17200,7 @@
         <v>8.69211101531982</v>
       </c>
       <c r="G464" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -17223,7 +17226,7 @@
         <v>8.74788856506348</v>
       </c>
       <c r="G465" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -17249,7 +17252,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G466" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17275,7 +17278,7 @@
         <v>8.60379505157471</v>
       </c>
       <c r="G467" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17301,7 +17304,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G468" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17327,7 +17330,7 @@
         <v>8.98959541320801</v>
       </c>
       <c r="G469" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17353,7 +17356,7 @@
         <v>9.22665309906006</v>
       </c>
       <c r="G470" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17379,7 +17382,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G471" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17405,7 +17408,7 @@
         <v>9.696120262146</v>
       </c>
       <c r="G472" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17431,7 +17434,7 @@
         <v>9.67752742767334</v>
       </c>
       <c r="G473" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17457,7 +17460,7 @@
         <v>9.55667400360107</v>
       </c>
       <c r="G474" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17483,7 +17486,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G475" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17509,7 +17512,7 @@
         <v>9.62174892425537</v>
       </c>
       <c r="G476" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17535,7 +17538,7 @@
         <v>9.43582057952881</v>
       </c>
       <c r="G477" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17561,7 +17564,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G478" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17587,7 +17590,7 @@
         <v>9.34285736083984</v>
       </c>
       <c r="G479" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17613,7 +17616,7 @@
         <v>9.2080602645874</v>
       </c>
       <c r="G480" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17639,7 +17642,7 @@
         <v>9.38933944702148</v>
       </c>
       <c r="G481" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17665,7 +17668,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G482" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17691,7 +17694,7 @@
         <v>9.91923332214355</v>
       </c>
       <c r="G483" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17717,7 +17720,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G484" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17743,7 +17746,7 @@
         <v>9.65893363952637</v>
       </c>
       <c r="G485" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17769,7 +17772,7 @@
         <v>10.0029001235962</v>
       </c>
       <c r="G486" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17795,7 +17798,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G487" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17821,7 +17824,7 @@
         <v>9.90063953399658</v>
       </c>
       <c r="G488" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17847,7 +17850,7 @@
         <v>10.0586776733398</v>
       </c>
       <c r="G489" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17873,7 +17876,7 @@
         <v>10.1144561767578</v>
       </c>
       <c r="G490" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17899,7 +17902,7 @@
         <v>10.0307893753052</v>
       </c>
       <c r="G491" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17925,7 +17928,7 @@
         <v>10.0121955871582</v>
       </c>
       <c r="G492" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17951,7 +17954,7 @@
         <v>9.76119422912598</v>
       </c>
       <c r="G493" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -17977,7 +17980,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G494" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -18003,7 +18006,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G495" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -18029,7 +18032,7 @@
         <v>9.93782520294189</v>
       </c>
       <c r="G496" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -18055,7 +18058,7 @@
         <v>10.0772714614868</v>
       </c>
       <c r="G497" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -18081,7 +18084,7 @@
         <v>10.318977355957</v>
       </c>
       <c r="G498" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -18107,7 +18110,7 @@
         <v>10.3003835678101</v>
       </c>
       <c r="G499" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -18133,7 +18136,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G500" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -18159,7 +18162,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G501" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -18185,7 +18188,7 @@
         <v>10.411940574646</v>
       </c>
       <c r="G502" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18211,7 +18214,7 @@
         <v>10.1330490112305</v>
       </c>
       <c r="G503" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18237,7 +18240,7 @@
         <v>9.49159908294678</v>
       </c>
       <c r="G504" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18263,7 +18266,7 @@
         <v>9.11044788360596</v>
       </c>
       <c r="G505" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18289,7 +18292,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G506" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18315,7 +18318,7 @@
         <v>9.08255863189697</v>
       </c>
       <c r="G507" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18341,7 +18344,7 @@
         <v>8.88268661499023</v>
       </c>
       <c r="G508" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18367,7 +18370,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G509" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18393,7 +18396,7 @@
         <v>9.09650325775146</v>
       </c>
       <c r="G510" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18419,7 +18422,7 @@
         <v>8.96170616149902</v>
       </c>
       <c r="G511" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18445,7 +18448,7 @@
         <v>8.95240879058838</v>
       </c>
       <c r="G512" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18471,7 +18474,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G513" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18497,7 +18500,7 @@
         <v>9.1569299697876</v>
       </c>
       <c r="G514" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18523,7 +18526,7 @@
         <v>9.16622638702393</v>
       </c>
       <c r="G515" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18549,7 +18552,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G516" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18575,7 +18578,7 @@
         <v>9.31496810913086</v>
       </c>
       <c r="G517" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18601,7 +18604,7 @@
         <v>9.26848602294922</v>
       </c>
       <c r="G518" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18627,7 +18630,7 @@
         <v>9.00818824768066</v>
       </c>
       <c r="G519" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18653,7 +18656,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G520" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18679,7 +18682,7 @@
         <v>9.06396579742432</v>
       </c>
       <c r="G521" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18705,7 +18708,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G522" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18731,7 +18734,7 @@
         <v>8.8873348236084</v>
       </c>
       <c r="G523" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18757,7 +18760,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G524" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18783,7 +18786,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G525" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18809,7 +18812,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G526" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18835,7 +18838,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G527" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18861,7 +18864,7 @@
         <v>8.90592765808105</v>
       </c>
       <c r="G528" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18887,7 +18890,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18913,7 +18916,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G530" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18939,7 +18942,7 @@
         <v>8.85014915466309</v>
       </c>
       <c r="G531" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -18965,7 +18968,7 @@
         <v>8.60844421386719</v>
       </c>
       <c r="G532" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -18991,7 +18994,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G533" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -19017,7 +19020,7 @@
         <v>8.53407287597656</v>
       </c>
       <c r="G534" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -19043,7 +19046,7 @@
         <v>8.34814453125</v>
       </c>
       <c r="G535" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -19069,7 +19072,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G536" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -19095,7 +19098,7 @@
         <v>8.05995655059814</v>
       </c>
       <c r="G537" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -19121,7 +19124,7 @@
         <v>8.30166339874268</v>
       </c>
       <c r="G538" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -19147,7 +19150,7 @@
         <v>7.87403011322021</v>
       </c>
       <c r="G539" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -19173,7 +19176,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G540" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -19199,7 +19202,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G541" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19225,7 +19228,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G542" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19251,7 +19254,7 @@
         <v>7.68810176849365</v>
       </c>
       <c r="G543" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19277,7 +19280,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G544" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19303,7 +19306,7 @@
         <v>7.8182520866394</v>
       </c>
       <c r="G545" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19329,7 +19332,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G546" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19355,7 +19358,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G547" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19381,7 +19384,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G548" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19407,7 +19410,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G549" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19433,7 +19436,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G550" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19459,7 +19462,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G551" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19485,7 +19488,7 @@
         <v>7.49566698074341</v>
       </c>
       <c r="G552" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19511,7 +19514,7 @@
         <v>7.36086988449097</v>
       </c>
       <c r="G553" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19537,7 +19540,7 @@
         <v>7.17308282852173</v>
       </c>
       <c r="G554" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19563,7 +19566,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G555" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19589,7 +19592,7 @@
         <v>6.98622608184814</v>
       </c>
       <c r="G556" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19615,7 +19618,7 @@
         <v>7.08383798599243</v>
       </c>
       <c r="G557" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19641,7 +19644,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G558" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19667,7 +19670,7 @@
         <v>7.298583984375</v>
       </c>
       <c r="G559" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19693,7 +19696,7 @@
         <v>7.12102317810059</v>
       </c>
       <c r="G560" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19719,7 +19722,7 @@
         <v>7.03177785873413</v>
       </c>
       <c r="G561" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19745,7 +19748,7 @@
         <v>7.05501890182495</v>
       </c>
       <c r="G562" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19771,7 +19774,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G563" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19797,7 +19800,7 @@
         <v>6.82911682128906</v>
       </c>
       <c r="G564" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19823,7 +19826,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G565" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19849,7 +19852,7 @@
         <v>7.01225614547729</v>
       </c>
       <c r="G566" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19875,7 +19878,7 @@
         <v>6.98064804077148</v>
       </c>
       <c r="G567" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19901,7 +19904,7 @@
         <v>6.94439220428467</v>
       </c>
       <c r="G568" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19927,7 +19930,7 @@
         <v>6.71291303634644</v>
       </c>
       <c r="G569" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19953,7 +19956,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G570" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -19979,7 +19982,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G571" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -20005,7 +20008,7 @@
         <v>7.27699995040894</v>
       </c>
       <c r="G572" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -20031,7 +20034,7 @@
         <v>7.97800016403198</v>
       </c>
       <c r="G573" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -20057,7 +20060,7 @@
         <v>7.58799982070923</v>
       </c>
       <c r="G574" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -20083,7 +20086,7 @@
         <v>7.75</v>
       </c>
       <c r="G575" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -20109,7 +20112,7 @@
         <v>8.04199981689453</v>
       </c>
       <c r="G576" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -20135,7 +20138,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G577" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -20161,7 +20164,7 @@
         <v>8.25899982452393</v>
       </c>
       <c r="G578" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -20187,7 +20190,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G579" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -20213,7 +20216,7 @@
         <v>7.83699989318848</v>
       </c>
       <c r="G580" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20239,7 +20242,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G581" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20265,7 +20268,7 @@
         <v>7.89900016784668</v>
       </c>
       <c r="G582" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20291,7 +20294,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G583" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20317,7 +20320,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G584" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20343,7 +20346,7 @@
         <v>7.86700010299683</v>
       </c>
       <c r="G585" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20369,7 +20372,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G586" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20395,7 +20398,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G587" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20421,7 +20424,7 @@
         <v>7.85799980163574</v>
       </c>
       <c r="G588" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20447,7 +20450,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G589" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20473,7 +20476,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G590" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20499,7 +20502,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G591" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20525,7 +20528,7 @@
         <v>7.71600008010864</v>
       </c>
       <c r="G592" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20551,7 +20554,7 @@
         <v>7.70100021362305</v>
       </c>
       <c r="G593" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20577,7 +20580,7 @@
         <v>7.76300001144409</v>
       </c>
       <c r="G594" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20603,7 +20606,7 @@
         <v>7.85699987411499</v>
       </c>
       <c r="G595" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20629,7 +20632,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G596" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20655,7 +20658,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20681,7 +20684,7 @@
         <v>8</v>
       </c>
       <c r="G598" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20707,7 +20710,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G599" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20733,7 +20736,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G600" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20759,7 +20762,7 @@
         <v>7.92600011825562</v>
       </c>
       <c r="G601" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20785,7 +20788,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G602" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20811,7 +20814,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G603" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20837,7 +20840,7 @@
         <v>8</v>
       </c>
       <c r="G604" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20863,7 +20866,7 @@
         <v>7.78399991989136</v>
       </c>
       <c r="G605" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20889,7 +20892,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G606" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20915,7 +20918,7 @@
         <v>7.44899988174438</v>
       </c>
       <c r="G607" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20941,7 +20944,7 @@
         <v>7.55900001525879</v>
       </c>
       <c r="G608" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -20967,7 +20970,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G609" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -20993,7 +20996,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G610" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -21019,7 +21022,7 @@
         <v>7.37099981307983</v>
       </c>
       <c r="G611" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -21045,7 +21048,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G612" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -21071,7 +21074,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G613" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -21097,7 +21100,7 @@
         <v>6.7649998664856</v>
       </c>
       <c r="G614" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -21123,7 +21126,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G615" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -21149,7 +21152,7 @@
         <v>7.27400016784668</v>
       </c>
       <c r="G616" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -21175,7 +21178,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G617" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -21201,7 +21204,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G618" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -21227,7 +21230,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G619" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21253,7 +21256,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G620" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21279,7 +21282,7 @@
         <v>7.32299995422363</v>
       </c>
       <c r="G621" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21305,7 +21308,7 @@
         <v>7.1710000038147</v>
       </c>
       <c r="G622" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21331,7 +21334,7 @@
         <v>7.08900022506714</v>
       </c>
       <c r="G623" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21357,7 +21360,7 @@
         <v>7.25899982452393</v>
       </c>
       <c r="G624" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21383,7 +21386,7 @@
         <v>7.11100006103516</v>
       </c>
       <c r="G625" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21409,7 +21412,7 @@
         <v>7.24900007247925</v>
       </c>
       <c r="G626" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21435,7 +21438,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G627" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21461,7 +21464,7 @@
         <v>6.97200012207031</v>
       </c>
       <c r="G628" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21487,7 +21490,7 @@
         <v>6.97399997711182</v>
       </c>
       <c r="G629" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21513,7 +21516,7 @@
         <v>6.92399978637695</v>
       </c>
       <c r="G630" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21539,7 +21542,7 @@
         <v>6.90299987792969</v>
       </c>
       <c r="G631" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21565,7 +21568,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G632" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21591,7 +21594,7 @@
         <v>6.96700000762939</v>
       </c>
       <c r="G633" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21617,7 +21620,7 @@
         <v>7</v>
       </c>
       <c r="G634" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21643,7 +21646,7 @@
         <v>6.875</v>
       </c>
       <c r="G635" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21669,7 +21672,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G636" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21695,7 +21698,7 @@
         <v>6.88199996948242</v>
       </c>
       <c r="G637" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21721,7 +21724,7 @@
         <v>7.04699993133545</v>
       </c>
       <c r="G638" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21747,7 +21750,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G639" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21773,7 +21776,7 @@
         <v>7</v>
       </c>
       <c r="G640" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21799,7 +21802,7 @@
         <v>6.93699979782104</v>
       </c>
       <c r="G641" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21825,7 +21828,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G642" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21851,7 +21854,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G643" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21877,7 +21880,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G644" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21903,7 +21906,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G645" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21929,7 +21932,7 @@
         <v>7.05399990081787</v>
       </c>
       <c r="G646" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21955,7 +21958,7 @@
         <v>7.06899976730347</v>
       </c>
       <c r="G647" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -21981,7 +21984,7 @@
         <v>7.12599992752075</v>
       </c>
       <c r="G648" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -22007,7 +22010,7 @@
         <v>7.17700004577637</v>
       </c>
       <c r="G649" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -22033,7 +22036,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G650" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -22059,7 +22062,7 @@
         <v>7.35099983215332</v>
       </c>
       <c r="G651" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22085,7 +22088,7 @@
         <v>7.21600008010864</v>
       </c>
       <c r="G652" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -22111,7 +22114,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G653" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -22137,7 +22140,7 @@
         <v>7.26100015640259</v>
       </c>
       <c r="G654" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22163,7 +22166,7 @@
         <v>7.06599998474121</v>
       </c>
       <c r="G655" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22189,7 +22192,7 @@
         <v>7.25</v>
       </c>
       <c r="G656" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22215,7 +22218,7 @@
         <v>7.05700016021729</v>
       </c>
       <c r="G657" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22241,7 +22244,7 @@
         <v>7.13100004196167</v>
       </c>
       <c r="G658" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22267,7 +22270,7 @@
         <v>7.23099994659424</v>
       </c>
       <c r="G659" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22293,7 +22296,7 @@
         <v>7.18300008773804</v>
       </c>
       <c r="G660" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22319,7 +22322,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G661" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22345,7 +22348,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G662" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22371,7 +22374,7 @@
         <v>6.93100023269653</v>
       </c>
       <c r="G663" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22397,7 +22400,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G664" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22423,7 +22426,7 @@
         <v>6.9210000038147</v>
       </c>
       <c r="G665" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22449,7 +22452,7 @@
         <v>6.90899991989136</v>
       </c>
       <c r="G666" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22475,7 +22478,7 @@
         <v>6.79300022125244</v>
       </c>
       <c r="G667" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22501,7 +22504,7 @@
         <v>6.66300010681152</v>
       </c>
       <c r="G668" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22527,7 +22530,7 @@
         <v>6.60699987411499</v>
       </c>
       <c r="G669" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22553,7 +22556,7 @@
         <v>6.49100017547607</v>
       </c>
       <c r="G670" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22579,7 +22582,7 @@
         <v>6.51900005340576</v>
       </c>
       <c r="G671" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22605,7 +22608,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22631,7 +22634,7 @@
         <v>6.69899988174438</v>
       </c>
       <c r="G673" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22657,7 +22660,7 @@
         <v>6.68699979782104</v>
       </c>
       <c r="G674" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22683,7 +22686,7 @@
         <v>6.58799982070923</v>
       </c>
       <c r="G675" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22709,7 +22712,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G676" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22735,7 +22738,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G677" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22761,7 +22764,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G678" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22787,7 +22790,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G679" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22813,7 +22816,7 @@
         <v>6.62099981307983</v>
       </c>
       <c r="G680" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22839,7 +22842,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G681" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22865,7 +22868,7 @@
         <v>6.56799983978271</v>
       </c>
       <c r="G682" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22891,7 +22894,7 @@
         <v>6.5310001373291</v>
       </c>
       <c r="G683" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22917,7 +22920,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G684" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22943,7 +22946,7 @@
         <v>6.57200002670288</v>
       </c>
       <c r="G685" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -22969,7 +22972,7 @@
         <v>6.58900022506714</v>
       </c>
       <c r="G686" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -22995,7 +22998,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G687" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -23021,7 +23024,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G688" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -23047,7 +23050,7 @@
         <v>6.58099985122681</v>
       </c>
       <c r="G689" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23073,7 +23076,7 @@
         <v>6.52299976348877</v>
       </c>
       <c r="G690" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -23099,7 +23102,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G691" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -23125,7 +23128,7 @@
         <v>6.95800018310547</v>
       </c>
       <c r="G692" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -23151,7 +23154,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G693" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -23177,7 +23180,7 @@
         <v>6.76900005340576</v>
       </c>
       <c r="G694" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -23203,7 +23206,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G695" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23229,7 +23232,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G696" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23255,7 +23258,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G697" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23281,7 +23284,7 @@
         <v>6.85099983215332</v>
       </c>
       <c r="G698" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23307,7 +23310,7 @@
         <v>6.75799989700317</v>
       </c>
       <c r="G699" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23333,7 +23336,7 @@
         <v>6.73899984359741</v>
       </c>
       <c r="G700" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23359,7 +23362,7 @@
         <v>6.61800003051758</v>
       </c>
       <c r="G701" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23385,7 +23388,7 @@
         <v>6.55700016021729</v>
       </c>
       <c r="G702" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23411,7 +23414,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G703" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23437,7 +23440,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G704" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23463,7 +23466,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G705" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23489,7 +23492,7 @@
         <v>6.30100011825562</v>
       </c>
       <c r="G706" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23515,7 +23518,7 @@
         <v>6.14099979400635</v>
       </c>
       <c r="G707" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23541,7 +23544,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G708" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23567,7 +23570,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G709" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23593,7 +23596,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G710" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23619,7 +23622,7 @@
         <v>5.95300006866455</v>
       </c>
       <c r="G711" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23645,7 +23648,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G712" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23671,7 +23674,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G713" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23697,7 +23700,7 @@
         <v>5.95900011062622</v>
       </c>
       <c r="G714" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23723,7 +23726,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G715" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23749,7 +23752,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G716" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23775,7 +23778,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G717" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23801,7 +23804,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G718" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23827,7 +23830,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G719" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23853,7 +23856,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G720" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23879,7 +23882,7 @@
         <v>6.00899982452393</v>
       </c>
       <c r="G721" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23905,7 +23908,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G722" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23931,7 +23934,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G723" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23957,7 +23960,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G724" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -23983,7 +23986,7 @@
         <v>6.25</v>
       </c>
       <c r="G725" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -24009,7 +24012,7 @@
         <v>6.23899984359741</v>
       </c>
       <c r="G726" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -24035,7 +24038,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G727" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -24061,7 +24064,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G728" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -24087,7 +24090,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G729" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -24113,7 +24116,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G730" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -24139,7 +24142,7 @@
         <v>6.2189998626709</v>
       </c>
       <c r="G731" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -24165,7 +24168,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G732" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -24191,7 +24194,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G733" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24217,7 +24220,7 @@
         <v>6.00299978256226</v>
       </c>
       <c r="G734" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24243,7 +24246,7 @@
         <v>6.03900003433228</v>
       </c>
       <c r="G735" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24269,7 +24272,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G736" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24295,7 +24298,7 @@
         <v>5.95100021362305</v>
       </c>
       <c r="G737" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24321,7 +24324,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G738" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24347,7 +24350,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G739" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24373,7 +24376,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G740" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24399,7 +24402,7 @@
         <v>6.02899980545044</v>
       </c>
       <c r="G741" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24425,7 +24428,7 @@
         <v>6.14300012588501</v>
       </c>
       <c r="G742" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24451,7 +24454,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G743" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24477,7 +24480,7 @@
         <v>6.10699987411499</v>
       </c>
       <c r="G744" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24503,7 +24506,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G745" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24529,7 +24532,7 @@
         <v>5.98299980163574</v>
       </c>
       <c r="G746" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24555,7 +24558,7 @@
         <v>5.88199996948242</v>
       </c>
       <c r="G747" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24581,7 +24584,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G748" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24607,7 +24610,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G749" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24633,7 +24636,7 @@
         <v>5.80700016021729</v>
       </c>
       <c r="G750" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24659,7 +24662,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G751" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24685,7 +24688,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G752" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24711,7 +24714,7 @@
         <v>5.65299987792969</v>
       </c>
       <c r="G753" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24737,7 +24740,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G754" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24763,7 +24766,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G755" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24789,7 +24792,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G756" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24815,7 +24818,7 @@
         <v>5.5</v>
       </c>
       <c r="G757" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24841,7 +24844,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G758" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24867,7 +24870,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G759" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24893,7 +24896,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G760" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24919,7 +24922,7 @@
         <v>5.4229998588562</v>
       </c>
       <c r="G761" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24945,7 +24948,7 @@
         <v>5.30700016021729</v>
       </c>
       <c r="G762" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -24971,7 +24974,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G763" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -24997,7 +25000,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G764" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -25023,7 +25026,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G765" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -25049,7 +25052,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G766" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -25075,7 +25078,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G767" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -25101,7 +25104,7 @@
         <v>5.90899991989136</v>
       </c>
       <c r="G768" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25127,7 +25130,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G769" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -25153,7 +25156,7 @@
         <v>5.91599988937378</v>
       </c>
       <c r="G770" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25179,7 +25182,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G771" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -25205,7 +25208,7 @@
         <v>5.81099987030029</v>
       </c>
       <c r="G772" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -25231,7 +25234,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G773" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25257,7 +25260,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G774" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25283,7 +25286,7 @@
         <v>5.84899997711182</v>
       </c>
       <c r="G775" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25309,7 +25312,7 @@
         <v>5.90199995040894</v>
       </c>
       <c r="G776" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25335,7 +25338,7 @@
         <v>5.83699989318848</v>
       </c>
       <c r="G777" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25361,7 +25364,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G778" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25387,7 +25390,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G779" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25413,7 +25416,7 @@
         <v>5.98899984359741</v>
       </c>
       <c r="G780" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25439,7 +25442,7 @@
         <v>6.14900016784668</v>
       </c>
       <c r="G781" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25465,7 +25468,7 @@
         <v>6.2810001373291</v>
       </c>
       <c r="G782" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25491,7 +25494,7 @@
         <v>6.23799991607666</v>
       </c>
       <c r="G783" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25517,7 +25520,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G784" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25543,7 +25546,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G785" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25569,7 +25572,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G786" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25595,7 +25598,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G787" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25621,7 +25624,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25647,7 +25650,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G789" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25673,7 +25676,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G790" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25699,7 +25702,7 @@
         <v>5.89599990844727</v>
       </c>
       <c r="G791" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25725,7 +25728,7 @@
         <v>6</v>
       </c>
       <c r="G792" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25751,7 +25754,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G793" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25777,7 +25780,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G794" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -25803,7 +25806,7 @@
         <v>6.06699991226196</v>
       </c>
       <c r="G795" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25829,7 +25832,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G796" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25855,7 +25858,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G797" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25881,7 +25884,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G798" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25907,7 +25910,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G799" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25933,7 +25936,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G800" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25959,7 +25962,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G801" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -25985,7 +25988,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G802" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26011,7 +26014,7 @@
         <v>6.31899976730347</v>
       </c>
       <c r="G803" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -26037,7 +26040,7 @@
         <v>6.18699979782104</v>
       </c>
       <c r="G804" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26063,7 +26066,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G805" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26089,7 +26092,7 @@
         <v>6.30800008773804</v>
       </c>
       <c r="G806" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26115,7 +26118,7 @@
         <v>6.36199998855591</v>
       </c>
       <c r="G807" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26141,7 +26144,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G808" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26167,7 +26170,7 @@
         <v>6.65299987792969</v>
       </c>
       <c r="G809" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26193,7 +26196,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G810" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26219,7 +26222,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G811" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26245,7 +26248,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26271,7 +26274,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G813" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26297,7 +26300,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G814" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26323,7 +26326,7 @@
         <v>6.65799999237061</v>
       </c>
       <c r="G815" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26349,7 +26352,7 @@
         <v>6.7039999961853</v>
       </c>
       <c r="G816" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26375,7 +26378,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G817" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26401,7 +26404,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G818" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26427,7 +26430,7 @@
         <v>6.64799976348877</v>
       </c>
       <c r="G819" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26453,7 +26456,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G820" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26479,7 +26482,7 @@
         <v>6.55600023269653</v>
       </c>
       <c r="G821" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26505,7 +26508,7 @@
         <v>6.48299980163574</v>
       </c>
       <c r="G822" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26531,7 +26534,7 @@
         <v>6.42799997329712</v>
       </c>
       <c r="G823" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26557,7 +26560,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G824" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26583,7 +26586,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G825" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26609,7 +26612,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G826" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26635,7 +26638,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G827" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26661,7 +26664,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G828" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26687,7 +26690,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G829" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26713,7 +26716,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G830" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26739,7 +26742,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G831" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26765,7 +26768,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G832" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26791,7 +26794,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G833" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26817,7 +26820,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G834" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26843,7 +26846,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G835" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26869,7 +26872,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G836" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26895,7 +26898,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G837" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26921,7 +26924,7 @@
         <v>6.75</v>
       </c>
       <c r="G838" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26947,7 +26950,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -26973,7 +26976,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -26999,7 +27002,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G841" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -27025,7 +27028,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G842" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -27051,7 +27054,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G843" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27077,7 +27080,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G844" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27103,7 +27106,7 @@
         <v>6.75</v>
       </c>
       <c r="G845" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27129,7 +27132,7 @@
         <v>6.75</v>
       </c>
       <c r="G846" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -27155,7 +27158,7 @@
         <v>6.75</v>
       </c>
       <c r="G847" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27181,7 +27184,7 @@
         <v>6.75</v>
       </c>
       <c r="G848" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -27207,7 +27210,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G849" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -27233,7 +27236,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G850" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27259,7 +27262,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G851" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27285,7 +27288,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G852" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27311,7 +27314,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G853" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27337,7 +27340,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G854" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27363,7 +27366,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27389,7 +27392,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G856" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27779,7 +27782,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G871" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28351,7 +28354,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G893" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -30977,7 +30980,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G994" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31263,7 +31266,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1005" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -31367,7 +31370,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1009" t="s">
-        <v>686</v>
+        <v>669</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -31523,7 +31526,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1015" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -31887,7 +31890,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1029" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -31939,7 +31942,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1031" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32147,7 +32150,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1039" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -71727,10 +71730,10 @@
     </row>
     <row r="2562">
       <c r="A2562" s="1" t="n">
-        <v>46052.6381481482</v>
+        <v>46052.3333333333</v>
       </c>
       <c r="B2562" t="n">
-        <v>35817</v>
+        <v>75483</v>
       </c>
       <c r="C2562" t="n">
         <v>3.58500003814697</v>
@@ -71742,12 +71745,38 @@
         <v>3.58500003814697</v>
       </c>
       <c r="F2562" t="n">
-        <v>3.54500007629395</v>
+        <v>3.5699999332428</v>
       </c>
       <c r="G2562" t="s">
-        <v>1578</v>
+        <v>1574</v>
       </c>
       <c r="H2562" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2563">
+      <c r="A2563" s="1" t="n">
+        <v>46055.6913078704</v>
+      </c>
+      <c r="B2563" t="n">
+        <v>302623</v>
+      </c>
+      <c r="C2563" t="n">
+        <v>3.61500000953674</v>
+      </c>
+      <c r="D2563" t="n">
+        <v>3.52500009536743</v>
+      </c>
+      <c r="E2563" t="n">
+        <v>3.52500009536743</v>
+      </c>
+      <c r="F2563" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="G2563" t="s">
+        <v>1597</v>
+      </c>
+      <c r="H2563" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="1598">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="1599">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,391 +38,391 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72976922988892</t>
+    <t xml:space="preserve">4.72976970672607</t>
   </si>
   <si>
     <t xml:space="preserve">IGD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8117880821228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76804399490356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76531171798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64775037765503</t>
+    <t xml:space="preserve">4.81178855895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76804447174072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76531076431274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64774990081787</t>
   </si>
   <si>
     <t xml:space="preserve">4.53839111328125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56573104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67235612869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55206060409546</t>
+    <t xml:space="preserve">4.56573057174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67235660552979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55206108093262</t>
   </si>
   <si>
     <t xml:space="preserve">4.33334302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16383743286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04627704620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60884189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88223838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95605564117432</t>
+    <t xml:space="preserve">4.16383695602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04627752304077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60884165763855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8822386264801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9560558795929</t>
   </si>
   <si>
     <t xml:space="preserve">4.0380744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97519397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785356521606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81388902664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96425747871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07088232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92051362991333</t>
+    <t xml:space="preserve">3.97519326210022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785380363464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81388926506042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96425724029541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07088184356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92051434516907</t>
   </si>
   <si>
     <t xml:space="preserve">3.69632840156555</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78654980659485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45573925971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49948215484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69086074829102</t>
+    <t xml:space="preserve">3.78654909133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45573878288269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49948263168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69086027145386</t>
   </si>
   <si>
     <t xml:space="preserve">3.56783199310303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63891506195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497233390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755923271179</t>
+    <t xml:space="preserve">3.63891530036926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497185707092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755899429321</t>
   </si>
   <si>
     <t xml:space="preserve">3.93691754341125</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87130236625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05994653701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00800180435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9533212184906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98612928390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99159741401672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0326075553894</t>
+    <t xml:space="preserve">3.87130308151245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05994606018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00800085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95332145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98612999916077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99159717559814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03260707855225</t>
   </si>
   <si>
     <t xml:space="preserve">4.05447816848755</t>
   </si>
   <si>
-    <t xml:space="preserve">4.24038934707642</t>
+    <t xml:space="preserve">4.24038887023926</t>
   </si>
   <si>
     <t xml:space="preserve">4.21031475067139</t>
   </si>
   <si>
+    <t xml:space="preserve">4.37435293197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33607816696167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34701299667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33881187438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42903327941895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52745628356934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51105165481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46184015274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57119989395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67509031295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60947418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54932689666748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48371171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34974765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42083072662354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42356443405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2649941444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22398471832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22671842575073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33060932159424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40169334411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30600452423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36615085601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26772832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32514238357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29233407974243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27046251296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29506778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39895868301392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30873823165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38802289962769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42629814147949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34427976608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39075708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30326986312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49522352218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57292604446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65062808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69091796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67940711975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69379568099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66213989257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61609315872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57580327987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63623857498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63048315048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63336086273193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63911628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56429243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35133075714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08368873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95130753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9714527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16139078140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20168161392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.247727394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2765064239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03476524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755851745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84482645988464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633778572083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470426559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01749801635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784887313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8361930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96281862258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05778837203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0923228263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25636053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40313196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3340630531311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5182466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41752099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45493316650391</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.37435340881348</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33607769012451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34701299667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33881139755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42903280258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52745580673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51105117797852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46184062957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57119989395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67509031295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60947418212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54932689666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4837121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34974813461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42083024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42356491088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26499462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25405883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22398519515991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22671890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23765468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3306097984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40169286727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31967353820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3060040473938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36615180969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26772880554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32514190673828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29233407974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27046203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29506731033325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39895915985107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30873775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38802289962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42629861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34427976608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39075708389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30326986312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49522399902344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57292652130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65062808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091844558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67940616607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69379568099976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66213941574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61609363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57580327987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63623905181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63048315048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63336086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6391167640686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56429290771484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35133075714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08368921279907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95130753517151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97145175933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16139125823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20168161392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24772691726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27650594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03476524353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755875587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84482645988464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633730888367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15851354598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01749849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784911155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83619260787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96281838417053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05778884887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0923228263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25636005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40313196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33406352996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51824712753296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41752147674561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45493364334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37435293197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48371171951294</t>
+    <t xml:space="preserve">4.48371124267578</t>
   </si>
   <si>
     <t xml:space="preserve">4.45781183242798</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53839206695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52975845336914</t>
+    <t xml:space="preserve">4.53839159011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52975797653198</t>
   </si>
   <si>
     <t xml:space="preserve">4.48946762084961</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51536798477173</t>
+    <t xml:space="preserve">4.51536846160889</t>
   </si>
   <si>
     <t xml:space="preserve">4.25923919677734</t>
@@ -437,184 +437,184 @@
     <t xml:space="preserve">4.38298654556274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36571979522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41464376449585</t>
+    <t xml:space="preserve">4.36571931838989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41464328765869</t>
   </si>
   <si>
     <t xml:space="preserve">4.35996341705322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33694124221802</t>
+    <t xml:space="preserve">4.33694076538086</t>
   </si>
   <si>
     <t xml:space="preserve">4.29377317428589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31391763687134</t>
+    <t xml:space="preserve">4.3139181137085</t>
   </si>
   <si>
     <t xml:space="preserve">4.19016981124878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19880342483521</t>
+    <t xml:space="preserve">4.19880390167236</t>
   </si>
   <si>
     <t xml:space="preserve">4.22182655334473</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2621169090271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25348329544067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23046016693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14412403106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19592571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16714715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15563535690308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11534452438354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20743608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14700174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17865800857544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07505559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94267344474792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79878091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77575707435608</t>
+    <t xml:space="preserve">4.26211643218994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25348234176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23046064376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14412355422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19592618942261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16714763641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15563583374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1153450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20743656158447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14700222015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1786584854126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0750560760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9426736831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497139930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79878044128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77575755119324</t>
   </si>
   <si>
     <t xml:space="preserve">3.83907032012939</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74697875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74985599517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85921597480774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82468128204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79590225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87936067581177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8102912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439140319824</t>
+    <t xml:space="preserve">3.74697852134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74985647201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85921573638916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82468104362488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79590249061584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87936043739319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81029152870178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439164161682</t>
   </si>
   <si>
     <t xml:space="preserve">3.76424622535706</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72971129417419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7124445438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72395539283752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84194827079773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735307693481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06354331970215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10959005355835</t>
+    <t xml:space="preserve">3.72971153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71244406700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72395586967468</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84194803237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735355377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06354379653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10958909988403</t>
   </si>
   <si>
     <t xml:space="preserve">4.11822319030762</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08656644821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03764295578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00310850143433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97432971000671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.91389489173889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93979620933533</t>
+    <t xml:space="preserve">4.08656692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03764343261719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00310945510864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97432994842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91389465332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93979597091675</t>
   </si>
   <si>
     <t xml:space="preserve">3.92540669441223</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92828392982483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8966269493103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84770393371582</t>
+    <t xml:space="preserve">3.92828488349915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89662742614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84770464897156</t>
   </si>
   <si>
     <t xml:space="preserve">3.75273489952087</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75849008560181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55704021453857</t>
+    <t xml:space="preserve">3.75848984718323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55703997612</t>
   </si>
   <si>
     <t xml:space="preserve">3.64337539672852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66927623748779</t>
+    <t xml:space="preserve">3.66927599906921</t>
   </si>
   <si>
     <t xml:space="preserve">3.65776467323303</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58006238937378</t>
+    <t xml:space="preserve">3.58006310462952</t>
   </si>
   <si>
     <t xml:space="preserve">3.59732985496521</t>
@@ -623,49 +623,49 @@
     <t xml:space="preserve">3.6030855178833</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63186478614807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6261088848114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66064262390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61459684371948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80453610420227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9599404335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07217693328857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0433988571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12685680389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13261270523071</t>
+    <t xml:space="preserve">3.63186454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62610793113708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66064310073853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61459708213806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80453658103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95994067192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07217741012573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04339933395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1268572807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13261222839355</t>
   </si>
   <si>
     <t xml:space="preserve">4.12110137939453</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36859750747681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28226089477539</t>
+    <t xml:space="preserve">4.36859798431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28226137161255</t>
   </si>
   <si>
     <t xml:space="preserve">4.33981895446777</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34845161437988</t>
+    <t xml:space="preserve">4.34845209121704</t>
   </si>
   <si>
     <t xml:space="preserve">4.33118534088135</t>
@@ -677,70 +677,70 @@
     <t xml:space="preserve">4.27075004577637</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22758293151855</t>
+    <t xml:space="preserve">4.2275824546814</t>
   </si>
   <si>
     <t xml:space="preserve">4.2131929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18153619766235</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09807825088501</t>
+    <t xml:space="preserve">4.18153667449951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09807777404785</t>
   </si>
   <si>
     <t xml:space="preserve">4.00598621368408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10383415222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0290093421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06929922103882</t>
+    <t xml:space="preserve">4.10383462905884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.02900981903076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06929969787598</t>
   </si>
   <si>
     <t xml:space="preserve">4.04627656936646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21894884109497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30816221237183</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14987993240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47220087051392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51249074935913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37723112106323</t>
+    <t xml:space="preserve">4.21894836425781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30816173553467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14988040924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47220039367676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51249027252197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37723064422607</t>
   </si>
   <si>
     <t xml:space="preserve">4.44342231750488</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59307098388672</t>
+    <t xml:space="preserve">4.59307050704956</t>
   </si>
   <si>
     <t xml:space="preserve">4.62472772598267</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57004880905151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71969652175903</t>
+    <t xml:space="preserve">4.57004833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71969699859619</t>
   </si>
   <si>
     <t xml:space="preserve">4.70818519592285</t>
   </si>
   <si>
-    <t xml:space="preserve">4.80315494537354</t>
+    <t xml:space="preserve">4.80315446853638</t>
   </si>
   <si>
     <t xml:space="preserve">4.73120832443237</t>
@@ -755,22 +755,22 @@
     <t xml:space="preserve">4.64487266540527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62185001373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54702520370483</t>
+    <t xml:space="preserve">4.62184953689575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54702472686768</t>
   </si>
   <si>
     <t xml:space="preserve">4.52687978744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46068954467773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60458278656006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71394062042236</t>
+    <t xml:space="preserve">4.46068906784058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6045823097229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71394109725952</t>
   </si>
   <si>
     <t xml:space="preserve">4.66501760482788</t>
@@ -791,13 +791,13 @@
     <t xml:space="preserve">4.77149820327759</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8233003616333</t>
+    <t xml:space="preserve">4.82329988479614</t>
   </si>
   <si>
     <t xml:space="preserve">4.92690324783325</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94992589950562</t>
+    <t xml:space="preserve">4.94992637634277</t>
   </si>
   <si>
     <t xml:space="preserve">4.98446035385132</t>
@@ -809,52 +809,52 @@
     <t xml:space="preserve">5.0564079284668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89236879348755</t>
+    <t xml:space="preserve">4.89236831665039</t>
   </si>
   <si>
     <t xml:space="preserve">4.86359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82905530929565</t>
+    <t xml:space="preserve">4.82905673980713</t>
   </si>
   <si>
     <t xml:space="preserve">4.87592363357544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9116005897522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93538570404053</t>
+    <t xml:space="preserve">4.91160154342651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93538618087769</t>
   </si>
   <si>
     <t xml:space="preserve">4.89970827102661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9205207824707</t>
+    <t xml:space="preserve">4.92052030563354</t>
   </si>
   <si>
     <t xml:space="preserve">5.01268720626831</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96809053421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97106409072876</t>
+    <t xml:space="preserve">4.96809101104736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9710636138916</t>
   </si>
   <si>
     <t xml:space="preserve">4.89376258850098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94727802276611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94133281707764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92944002151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88781642913818</t>
+    <t xml:space="preserve">4.94727849960327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94133234024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92943954467773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88781595230103</t>
   </si>
   <si>
     <t xml:space="preserve">4.85511159896851</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">4.75105285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78672981262207</t>
+    <t xml:space="preserve">4.78673028945923</t>
   </si>
   <si>
     <t xml:space="preserve">4.73321437835693</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66185903549194</t>
+    <t xml:space="preserve">4.6618595123291</t>
   </si>
   <si>
     <t xml:space="preserve">4.53401470184326</t>
@@ -884,22 +884,22 @@
     <t xml:space="preserve">4.58455753326416</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61726188659668</t>
+    <t xml:space="preserve">4.61726140975952</t>
   </si>
   <si>
     <t xml:space="preserve">4.70348310470581</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72132205963135</t>
+    <t xml:space="preserve">4.72132158279419</t>
   </si>
   <si>
     <t xml:space="preserve">4.63807392120361</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72726726531982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81646108627319</t>
+    <t xml:space="preserve">4.72726774215698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81646156311035</t>
   </si>
   <si>
     <t xml:space="preserve">4.83132696151733</t>
@@ -908,22 +908,22 @@
     <t xml:space="preserve">4.93835973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94430541992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9829568862915</t>
+    <t xml:space="preserve">4.94430589675903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98295640945435</t>
   </si>
   <si>
     <t xml:space="preserve">4.95322513580322</t>
   </si>
   <si>
-    <t xml:space="preserve">4.90565490722656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.84619283676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89078903198242</t>
+    <t xml:space="preserve">4.90565538406372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.84619235992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89078950881958</t>
   </si>
   <si>
     <t xml:space="preserve">5.00376796722412</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">4.98592948913574</t>
   </si>
   <si>
-    <t xml:space="preserve">5.15837049484253</t>
+    <t xml:space="preserve">5.15837001800537</t>
   </si>
   <si>
     <t xml:space="preserve">5.12566661834717</t>
@@ -950,46 +950,46 @@
     <t xml:space="preserve">5.11080074310303</t>
   </si>
   <si>
-    <t xml:space="preserve">5.07512235641479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0810694694519</t>
+    <t xml:space="preserve">5.07512283325195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08106994628906</t>
   </si>
   <si>
     <t xml:space="preserve">5.09593534469604</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11377382278442</t>
+    <t xml:space="preserve">5.11377429962158</t>
   </si>
   <si>
     <t xml:space="preserve">5.03944540023804</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02755308151245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97701025009155</t>
+    <t xml:space="preserve">5.02755260467529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97700977325439</t>
   </si>
   <si>
     <t xml:space="preserve">5.05133819580078</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99484825134277</t>
+    <t xml:space="preserve">4.99484872817993</t>
   </si>
   <si>
     <t xml:space="preserve">5.01566123962402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06620407104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.13755893707275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23269844055176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2445912361145</t>
+    <t xml:space="preserve">5.06620454788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1375584602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.2326979637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24459075927734</t>
   </si>
   <si>
     <t xml:space="preserve">5.23864555358887</t>
@@ -998,13 +998,13 @@
     <t xml:space="preserve">5.197021484375</t>
   </si>
   <si>
-    <t xml:space="preserve">5.17323684692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1851282119751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20891380310059</t>
+    <t xml:space="preserve">5.17323637008667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18512773513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20891427993774</t>
   </si>
   <si>
     <t xml:space="preserve">5.1940484046936</t>
@@ -1013,22 +1013,22 @@
     <t xml:space="preserve">5.2475643157959</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25053739547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26242971420288</t>
+    <t xml:space="preserve">5.25053787231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26243019104004</t>
   </si>
   <si>
     <t xml:space="preserve">5.14945125579834</t>
   </si>
   <si>
-    <t xml:space="preserve">5.16431760787964</t>
+    <t xml:space="preserve">5.16431713104248</t>
   </si>
   <si>
     <t xml:space="preserve">5.21485948562622</t>
   </si>
   <si>
-    <t xml:space="preserve">5.35162401199341</t>
+    <t xml:space="preserve">5.35162448883057</t>
   </si>
   <si>
     <t xml:space="preserve">5.44081687927246</t>
@@ -1037,124 +1037,124 @@
     <t xml:space="preserve">5.64893627166748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6786675453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47054862976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46757555007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55974245071411</t>
+    <t xml:space="preserve">5.67866706848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47054815292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46757507324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55974292755127</t>
   </si>
   <si>
     <t xml:space="preserve">5.59541940689087</t>
   </si>
   <si>
-    <t xml:space="preserve">5.58947420120239</t>
+    <t xml:space="preserve">5.58947372436523</t>
   </si>
   <si>
     <t xml:space="preserve">5.50325298309326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57758140563965</t>
+    <t xml:space="preserve">5.57758092880249</t>
   </si>
   <si>
     <t xml:space="preserve">5.75002241134644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90165233612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91651725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20193815231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19004535675049</t>
+    <t xml:space="preserve">5.90165185928345</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91651821136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20193767547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19004487991333</t>
   </si>
   <si>
     <t xml:space="preserve">6.11274385452271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12463617324829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15436744689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03544235229492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97598028182983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8897590637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.00571060180664</t>
+    <t xml:space="preserve">6.12463665008545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15436792373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03544187545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97597980499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.88976001739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.00571155548096</t>
   </si>
   <si>
     <t xml:space="preserve">6.29113054275513</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34464836120605</t>
+    <t xml:space="preserve">6.34464740753174</t>
   </si>
   <si>
     <t xml:space="preserve">6.17815256118774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39816331863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38627195358276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33275508880615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43384075164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46951866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41600227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40410947799683</t>
+    <t xml:space="preserve">6.39816427230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38627099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33275413513184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43384027481079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46951818466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41600275039673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40410995483398</t>
   </si>
   <si>
     <t xml:space="preserve">6.24356126785278</t>
   </si>
   <si>
-    <t xml:space="preserve">6.35653924942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44573402404785</t>
+    <t xml:space="preserve">6.35654020309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44573354721069</t>
   </si>
   <si>
     <t xml:space="preserve">6.60033655166626</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5884428024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71926021575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.65979862213135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.48141098022461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.071120262146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.82732391357422</t>
+    <t xml:space="preserve">6.58844375610352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71926069259644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.65979814529419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.48141050338745</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07111930847168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.82732343673706</t>
   </si>
   <si>
     <t xml:space="preserve">5.76786088943481</t>
@@ -1163,10 +1163,10 @@
     <t xml:space="preserve">5.80948495864868</t>
   </si>
   <si>
-    <t xml:space="preserve">5.68164014816284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73812913894653</t>
+    <t xml:space="preserve">5.68164110183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73812961578369</t>
   </si>
   <si>
     <t xml:space="preserve">5.81840419769287</t>
@@ -1175,10 +1175,10 @@
     <t xml:space="preserve">5.73218393325806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72623682022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.85705471038818</t>
+    <t xml:space="preserve">5.72623634338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85705518722534</t>
   </si>
   <si>
     <t xml:space="preserve">5.86300134658813</t>
@@ -1187,25 +1187,25 @@
     <t xml:space="preserve">5.9581413269043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92840909957886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76191473007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.79759168624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75596809387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.68461322784424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69650650024414</t>
+    <t xml:space="preserve">5.92840957641602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76191520690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70839834213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79759216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75596857070923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6846137046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69650554656982</t>
   </si>
   <si>
     <t xml:space="preserve">5.66082859039307</t>
@@ -1217,31 +1217,31 @@
     <t xml:space="preserve">5.45865678787231</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33973121643066</t>
+    <t xml:space="preserve">5.33973073959351</t>
   </si>
   <si>
     <t xml:space="preserve">5.15539693832397</t>
   </si>
   <si>
-    <t xml:space="preserve">5.30999994277954</t>
+    <t xml:space="preserve">5.3100004196167</t>
   </si>
   <si>
     <t xml:space="preserve">5.03647232055664</t>
   </si>
   <si>
-    <t xml:space="preserve">4.91754674911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00079536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.86997699737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85213899612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14350461959839</t>
+    <t xml:space="preserve">4.91754722595215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00079488754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.86997747421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85213851928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14350509643555</t>
   </si>
   <si>
     <t xml:space="preserve">4.75699949264526</t>
@@ -1253,10 +1253,10 @@
     <t xml:space="preserve">4.70824003219604</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58812570571899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47752571105957</t>
+    <t xml:space="preserve">4.58812522888184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47752618789673</t>
   </si>
   <si>
     <t xml:space="preserve">4.46860599517822</t>
@@ -1265,22 +1265,22 @@
     <t xml:space="preserve">4.53104162216187</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66483163833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66839981079102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55482625961304</t>
+    <t xml:space="preserve">4.66483211517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66840028762817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5548267364502</t>
   </si>
   <si>
     <t xml:space="preserve">4.49774217605591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51260805130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41211652755737</t>
+    <t xml:space="preserve">4.51260852813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41211605072021</t>
   </si>
   <si>
     <t xml:space="preserve">4.36811399459839</t>
@@ -1289,13 +1289,13 @@
     <t xml:space="preserve">4.29913759231567</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4852557182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46503829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4418478012085</t>
+    <t xml:space="preserve">4.48525524139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46503877639771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44184732437134</t>
   </si>
   <si>
     <t xml:space="preserve">4.29378604888916</t>
@@ -1307,7 +1307,7 @@
     <t xml:space="preserve">4.57336091995239</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6545934677124</t>
+    <t xml:space="preserve">4.65459394454956</t>
   </si>
   <si>
     <t xml:space="preserve">5.10297536849976</t>
@@ -1325,13 +1325,13 @@
     <t xml:space="preserve">5.34731435775757</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28271102905273</t>
+    <t xml:space="preserve">5.28271150588989</t>
   </si>
   <si>
     <t xml:space="preserve">5.17781209945679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01278734207153</t>
+    <t xml:space="preserve">5.01278686523438</t>
   </si>
   <si>
     <t xml:space="preserve">4.96993160247803</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">5.05244398117065</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98912048339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.94498634338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03197622299194</t>
+    <t xml:space="preserve">4.9891209602356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.94498586654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.03197574615479</t>
   </si>
   <si>
     <t xml:space="preserve">5.01598501205444</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">5.02621936798096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01470565795898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.08506488800049</t>
+    <t xml:space="preserve">5.01470613479614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.08506536483765</t>
   </si>
   <si>
     <t xml:space="preserve">4.93539190292358</t>
@@ -1370,13 +1370,13 @@
     <t xml:space="preserve">4.96545457839966</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02557945251465</t>
+    <t xml:space="preserve">5.02557992935181</t>
   </si>
   <si>
     <t xml:space="preserve">5.04029083251953</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02110242843628</t>
+    <t xml:space="preserve">5.02110195159912</t>
   </si>
   <si>
     <t xml:space="preserve">5.11704683303833</t>
@@ -1385,16 +1385,16 @@
     <t xml:space="preserve">5.05947971343994</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06971406936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24497318267822</t>
+    <t xml:space="preserve">5.06971454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24497270584106</t>
   </si>
   <si>
     <t xml:space="preserve">5.14135313034058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97888660430908</t>
+    <t xml:space="preserve">4.97888708114624</t>
   </si>
   <si>
     <t xml:space="preserve">4.76461029052734</t>
@@ -1406,28 +1406,28 @@
     <t xml:space="preserve">4.78124046325684</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73326873779297</t>
+    <t xml:space="preserve">4.73326826095581</t>
   </si>
   <si>
     <t xml:space="preserve">4.71471881866455</t>
   </si>
   <si>
-    <t xml:space="preserve">4.66290903091431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55097341537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32710313796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57399988174438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65267562866211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63092756271362</t>
+    <t xml:space="preserve">4.66290950775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55097389221191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32710266113281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57400035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65267515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63092708587646</t>
   </si>
   <si>
     <t xml:space="preserve">4.72943067550659</t>
@@ -1439,7 +1439,7 @@
     <t xml:space="preserve">4.79403305053711</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68401622772217</t>
+    <t xml:space="preserve">4.68401670455933</t>
   </si>
   <si>
     <t xml:space="preserve">4.58679294586182</t>
@@ -1448,13 +1448,13 @@
     <t xml:space="preserve">4.8741979598999</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99108505249023</t>
+    <t xml:space="preserve">4.99108457565308</t>
   </si>
   <si>
     <t xml:space="preserve">4.88932466506958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.98421001434326</t>
+    <t xml:space="preserve">4.9842095375061</t>
   </si>
   <si>
     <t xml:space="preserve">5.03165197372437</t>
@@ -1463,13 +1463,13 @@
     <t xml:space="preserve">4.79375267028809</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79512691497803</t>
+    <t xml:space="preserve">4.79512739181519</t>
   </si>
   <si>
     <t xml:space="preserve">4.76074838638306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74630975723267</t>
+    <t xml:space="preserve">4.74630928039551</t>
   </si>
   <si>
     <t xml:space="preserve">4.86113452911377</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">4.81300401687622</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72705745697021</t>
+    <t xml:space="preserve">4.72705793380737</t>
   </si>
   <si>
     <t xml:space="preserve">4.77174997329712</t>
@@ -1490,10 +1490,10 @@
     <t xml:space="preserve">4.73187065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84532070159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7868766784668</t>
+    <t xml:space="preserve">4.84532022476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.78687620162964</t>
   </si>
   <si>
     <t xml:space="preserve">4.76968669891357</t>
@@ -1502,10 +1502,10 @@
     <t xml:space="preserve">4.91614007949829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97802114486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96770811080933</t>
+    <t xml:space="preserve">4.97802066802979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96770763397217</t>
   </si>
   <si>
     <t xml:space="preserve">4.82675552368164</t>
@@ -1514,19 +1514,19 @@
     <t xml:space="preserve">4.85013294219971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86044645309448</t>
+    <t xml:space="preserve">4.86044692993164</t>
   </si>
   <si>
     <t xml:space="preserve">4.89963817596436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93470478057861</t>
+    <t xml:space="preserve">4.93470430374146</t>
   </si>
   <si>
     <t xml:space="preserve">4.99177312850952</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05434226989746</t>
+    <t xml:space="preserve">5.0543417930603</t>
   </si>
   <si>
     <t xml:space="preserve">4.96151971817017</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">4.97939682006836</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99246025085449</t>
+    <t xml:space="preserve">4.99246072769165</t>
   </si>
   <si>
     <t xml:space="preserve">4.85838413238525</t>
@@ -1544,7 +1544,7 @@
     <t xml:space="preserve">4.98489713668823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85219621658325</t>
+    <t xml:space="preserve">4.85219573974609</t>
   </si>
   <si>
     <t xml:space="preserve">4.903076171875</t>
@@ -1559,10 +1559,10 @@
     <t xml:space="preserve">4.91682767868042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83363151550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76556205749512</t>
+    <t xml:space="preserve">4.83363199234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76556158065796</t>
   </si>
   <si>
     <t xml:space="preserve">4.75868654251099</t>
@@ -1583,28 +1583,28 @@
     <t xml:space="preserve">4.4630298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48228216171265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51941061019897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60604476928711</t>
+    <t xml:space="preserve">4.48228168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51941108703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60604524612427</t>
   </si>
   <si>
     <t xml:space="preserve">4.59779405593872</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52972412109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5379753112793</t>
+    <t xml:space="preserve">4.52972459793091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53797483444214</t>
   </si>
   <si>
     <t xml:space="preserve">4.5792293548584</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55172634124756</t>
+    <t xml:space="preserve">4.55172729492188</t>
   </si>
   <si>
     <t xml:space="preserve">4.57235383987427</t>
@@ -1619,22 +1619,22 @@
     <t xml:space="preserve">4.51597261428833</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49053335189819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52078533172607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51872396469116</t>
+    <t xml:space="preserve">4.49053287506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52078580856323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51872301101685</t>
   </si>
   <si>
     <t xml:space="preserve">4.53041219711304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51047229766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52491188049316</t>
+    <t xml:space="preserve">4.5104718208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52491140365601</t>
   </si>
   <si>
     <t xml:space="preserve">4.485032081604</t>
@@ -1652,28 +1652,28 @@
     <t xml:space="preserve">4.6541748046875</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70299291610718</t>
+    <t xml:space="preserve">4.70299243927002</t>
   </si>
   <si>
     <t xml:space="preserve">4.73049545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71055555343628</t>
+    <t xml:space="preserve">4.71055603027344</t>
   </si>
   <si>
     <t xml:space="preserve">4.64661121368408</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63354825973511</t>
+    <t xml:space="preserve">4.63354730606079</t>
   </si>
   <si>
     <t xml:space="preserve">4.55035161972046</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50840902328491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41558742523193</t>
+    <t xml:space="preserve">4.50840997695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41558790206909</t>
   </si>
   <si>
     <t xml:space="preserve">4.42727661132812</t>
@@ -1682,10 +1682,10 @@
     <t xml:space="preserve">4.40046072006226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33239126205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2223801612854</t>
+    <t xml:space="preserve">4.33239078521729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22237968444824</t>
   </si>
   <si>
     <t xml:space="preserve">4.20450305938721</t>
@@ -1697,7 +1697,7 @@
     <t xml:space="preserve">4.06630086898804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09311676025391</t>
+    <t xml:space="preserve">4.09311628341675</t>
   </si>
   <si>
     <t xml:space="preserve">3.98791742324829</t>
@@ -1706,13 +1706,13 @@
     <t xml:space="preserve">4.05942487716675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09724140167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04979944229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05323696136475</t>
+    <t xml:space="preserve">4.09724187850952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04979848861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0532374382019</t>
   </si>
   <si>
     <t xml:space="preserve">4.10480499267578</t>
@@ -1727,16 +1727,16 @@
     <t xml:space="preserve">4.13161993026733</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21962928771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28563642501831</t>
+    <t xml:space="preserve">4.21962976455688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28563594818115</t>
   </si>
   <si>
     <t xml:space="preserve">4.29732513427734</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28976154327393</t>
+    <t xml:space="preserve">4.28976202011108</t>
   </si>
   <si>
     <t xml:space="preserve">4.22100448608398</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">4.36608219146729</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27601003646851</t>
+    <t xml:space="preserve">4.27601051330566</t>
   </si>
   <si>
     <t xml:space="preserve">4.22513008117676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19487714767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12749528884888</t>
+    <t xml:space="preserve">4.1948766708374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12749481201172</t>
   </si>
   <si>
     <t xml:space="preserve">4.1522479057312</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13505792617798</t>
+    <t xml:space="preserve">4.13505840301514</t>
   </si>
   <si>
     <t xml:space="preserve">4.09174108505249</t>
@@ -1772,7 +1772,7 @@
     <t xml:space="preserve">4.03260946273804</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03467273712158</t>
+    <t xml:space="preserve">4.03467226028442</t>
   </si>
   <si>
     <t xml:space="preserve">4.054612159729</t>
@@ -1781,43 +1781,43 @@
     <t xml:space="preserve">4.14537191390991</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2237548828125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23544359207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19900178909302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1886887550354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1137433052063</t>
+    <t xml:space="preserve">4.22375535964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23544311523438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19900226593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18868827819824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11374282836914</t>
   </si>
   <si>
     <t xml:space="preserve">4.04429864883423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02917242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99273109436035</t>
+    <t xml:space="preserve">4.02917194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99273061752319</t>
   </si>
   <si>
     <t xml:space="preserve">3.99891877174377</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96316528320312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88684439659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98241710662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90540885925293</t>
+    <t xml:space="preserve">3.96316480636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88684487342834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98241662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90540933609009</t>
   </si>
   <si>
     <t xml:space="preserve">3.87378072738647</t>
@@ -1829,13 +1829,13 @@
     <t xml:space="preserve">3.71013879776001</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69501256942749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73351621627808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72870302200317</t>
+    <t xml:space="preserve">3.69501233100891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73351573944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72870278358459</t>
   </si>
   <si>
     <t xml:space="preserve">3.64894461631775</t>
@@ -1844,55 +1844,55 @@
     <t xml:space="preserve">3.70051240921021</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83115172386169</t>
+    <t xml:space="preserve">3.83115100860596</t>
   </si>
   <si>
     <t xml:space="preserve">3.89990830421448</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99341797828674</t>
+    <t xml:space="preserve">3.9934184551239</t>
   </si>
   <si>
     <t xml:space="preserve">3.97829174995422</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06286287307739</t>
+    <t xml:space="preserve">4.06286239624023</t>
   </si>
   <si>
     <t xml:space="preserve">4.048424243927</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06767559051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04292345046997</t>
+    <t xml:space="preserve">4.06767606735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04292392730713</t>
   </si>
   <si>
     <t xml:space="preserve">3.99548053741455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95491409301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04086112976074</t>
+    <t xml:space="preserve">3.95491456985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04086065292358</t>
   </si>
   <si>
     <t xml:space="preserve">4.02160882949829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05804967880249</t>
+    <t xml:space="preserve">4.05805015563965</t>
   </si>
   <si>
     <t xml:space="preserve">4.01335763931274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97004127502441</t>
+    <t xml:space="preserve">3.97004079818726</t>
   </si>
   <si>
     <t xml:space="preserve">4.07180118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11786890029907</t>
+    <t xml:space="preserve">4.11786937713623</t>
   </si>
   <si>
     <t xml:space="preserve">4.22788047790527</t>
@@ -1901,22 +1901,22 @@
     <t xml:space="preserve">4.31864023208618</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2890739440918</t>
+    <t xml:space="preserve">4.28907442092896</t>
   </si>
   <si>
     <t xml:space="preserve">4.29044914245605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25057029724121</t>
+    <t xml:space="preserve">4.25056982040405</t>
   </si>
   <si>
     <t xml:space="preserve">4.24919509887695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2698221206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26294612884521</t>
+    <t xml:space="preserve">4.26982164382935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26294660568237</t>
   </si>
   <si>
     <t xml:space="preserve">4.24231958389282</t>
@@ -1925,13 +1925,13 @@
     <t xml:space="preserve">4.13643312454224</t>
   </si>
   <si>
-    <t xml:space="preserve">4.05392503738403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12543201446533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0896782875061</t>
+    <t xml:space="preserve">4.05392456054688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12543249130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08967876434326</t>
   </si>
   <si>
     <t xml:space="preserve">4.13230752944946</t>
@@ -1940,16 +1940,16 @@
     <t xml:space="preserve">4.17149925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23819398880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22169208526611</t>
+    <t xml:space="preserve">4.23819351196289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22169256210327</t>
   </si>
   <si>
     <t xml:space="preserve">4.2189416885376</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21481657028198</t>
+    <t xml:space="preserve">4.21481704711914</t>
   </si>
   <si>
     <t xml:space="preserve">4.16324853897095</t>
@@ -1958,19 +1958,19 @@
     <t xml:space="preserve">4.28494834899902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34476757049561</t>
+    <t xml:space="preserve">4.34476709365845</t>
   </si>
   <si>
     <t xml:space="preserve">4.25400829315186</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33720445632935</t>
+    <t xml:space="preserve">4.33720397949219</t>
   </si>
   <si>
     <t xml:space="preserve">4.37433338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50359678268433</t>
+    <t xml:space="preserve">4.50359630584717</t>
   </si>
   <si>
     <t xml:space="preserve">4.57441663742065</t>
@@ -1991,31 +1991,31 @@
     <t xml:space="preserve">4.57785415649414</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6094822883606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66173791885376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60673236846924</t>
+    <t xml:space="preserve">4.60948276519775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66173839569092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60673189163208</t>
   </si>
   <si>
     <t xml:space="preserve">4.57097864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57166624069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50772190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45752906799316</t>
+    <t xml:space="preserve">4.5716667175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5077223777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45752954483032</t>
   </si>
   <si>
     <t xml:space="preserve">4.41971302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46234226226807</t>
+    <t xml:space="preserve">4.46234273910522</t>
   </si>
   <si>
     <t xml:space="preserve">4.4279637336731</t>
@@ -2030,13 +2030,13 @@
     <t xml:space="preserve">4.55860280990601</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58610582351685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45546627044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48296928405762</t>
+    <t xml:space="preserve">4.58610534667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45546674728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48296976089478</t>
   </si>
   <si>
     <t xml:space="preserve">4.53109979629517</t>
@@ -2048,16 +2048,16 @@
     <t xml:space="preserve">4.59985685348511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64111137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61360883712769</t>
+    <t xml:space="preserve">4.64111089706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61360836029053</t>
   </si>
   <si>
     <t xml:space="preserve">4.62048435211182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62735986709595</t>
+    <t xml:space="preserve">4.62735939025879</t>
   </si>
   <si>
     <t xml:space="preserve">4.7167444229126</t>
@@ -2081,7 +2081,7 @@
     <t xml:space="preserve">4.62667274475098</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6936182975769</t>
+    <t xml:space="preserve">4.69361877441406</t>
   </si>
   <si>
     <t xml:space="preserve">4.73824882507324</t>
@@ -2093,7 +2093,7 @@
     <t xml:space="preserve">4.63411140441895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65642690658569</t>
+    <t xml:space="preserve">4.65642642974854</t>
   </si>
   <si>
     <t xml:space="preserve">4.58948135375977</t>
@@ -2105,10 +2105,10 @@
     <t xml:space="preserve">4.57460451126099</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56716537475586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55972719192505</t>
+    <t xml:space="preserve">4.56716585159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55972766876221</t>
   </si>
   <si>
     <t xml:space="preserve">4.64898824691772</t>
@@ -2117,10 +2117,10 @@
     <t xml:space="preserve">4.64154958724976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5820426940918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52997398376465</t>
+    <t xml:space="preserve">4.58204317092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52997446060181</t>
   </si>
   <si>
     <t xml:space="preserve">4.4481520652771</t>
@@ -2153,10 +2153,10 @@
     <t xml:space="preserve">4.33657646179199</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59691905975342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50765943527222</t>
+    <t xml:space="preserve">4.59691953659058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50765895843506</t>
   </si>
   <si>
     <t xml:space="preserve">4.49278211593628</t>
@@ -2171,13 +2171,13 @@
     <t xml:space="preserve">4.40352153778076</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38864517211914</t>
+    <t xml:space="preserve">4.38864469528198</t>
   </si>
   <si>
     <t xml:space="preserve">4.39608287811279</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35145330429077</t>
+    <t xml:space="preserve">4.35145282745361</t>
   </si>
   <si>
     <t xml:space="preserve">4.24731588363647</t>
@@ -2195,34 +2195,34 @@
     <t xml:space="preserve">4.13573980331421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.01672554016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.02416467666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93490362167358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9051501750946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95721912384033</t>
+    <t xml:space="preserve">4.01672601699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0241641998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93490409851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90515065193176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95721864700317</t>
   </si>
   <si>
     <t xml:space="preserve">3.89771151542664</t>
   </si>
   <si>
-    <t xml:space="preserve">3.98697209358215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92002654075623</t>
+    <t xml:space="preserve">3.98697257041931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92002701759338</t>
   </si>
   <si>
     <t xml:space="preserve">3.94234228134155</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97953343391418</t>
+    <t xml:space="preserve">3.9795343875885</t>
   </si>
   <si>
     <t xml:space="preserve">3.97209572792053</t>
@@ -2243,7 +2243,7 @@
     <t xml:space="preserve">4.18780899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18036985397339</t>
+    <t xml:space="preserve">4.18037033081055</t>
   </si>
   <si>
     <t xml:space="preserve">4.17293214797974</t>
@@ -2252,16 +2252,16 @@
     <t xml:space="preserve">4.11342477798462</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14317798614502</t>
+    <t xml:space="preserve">4.14317846298218</t>
   </si>
   <si>
     <t xml:space="preserve">4.1283016204834</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15805578231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03904104232788</t>
+    <t xml:space="preserve">4.15805530548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03904056549072</t>
   </si>
   <si>
     <t xml:space="preserve">4.23243856430054</t>
@@ -2270,22 +2270,22 @@
     <t xml:space="preserve">4.23987722396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26963043212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30682229995728</t>
+    <t xml:space="preserve">4.26963090896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30682277679443</t>
   </si>
   <si>
     <t xml:space="preserve">4.29194593429565</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2621922492981</t>
+    <t xml:space="preserve">4.26219272613525</t>
   </si>
   <si>
     <t xml:space="preserve">4.27706909179688</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29938411712646</t>
+    <t xml:space="preserve">4.29938459396362</t>
   </si>
   <si>
     <t xml:space="preserve">4.28450775146484</t>
@@ -2294,10 +2294,10 @@
     <t xml:space="preserve">4.41096019744873</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44071388244629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46302843093872</t>
+    <t xml:space="preserve">4.44071340560913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46302890777588</t>
   </si>
   <si>
     <t xml:space="preserve">4.47046709060669</t>
@@ -2315,7 +2315,7 @@
     <t xml:space="preserve">4.79031753540039</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70105743408203</t>
+    <t xml:space="preserve">4.70105695724487</t>
   </si>
   <si>
     <t xml:space="preserve">4.67874193191528</t>
@@ -2327,7 +2327,7 @@
     <t xml:space="preserve">4.75312566757202</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67130422592163</t>
+    <t xml:space="preserve">4.67130374908447</t>
   </si>
   <si>
     <t xml:space="preserve">4.70849514007568</t>
@@ -2345,7 +2345,7 @@
     <t xml:space="preserve">4.06135606765747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96465706825256</t>
+    <t xml:space="preserve">3.96465730667114</t>
   </si>
   <si>
     <t xml:space="preserve">3.92746543884277</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">3.48116254806519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38446354866028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37702488899231</t>
+    <t xml:space="preserve">3.38446378707886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37702512741089</t>
   </si>
   <si>
     <t xml:space="preserve">2.7187283039093</t>
@@ -2369,16 +2369,16 @@
     <t xml:space="preserve">2.54020714759827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57367968559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70385122299194</t>
+    <t xml:space="preserve">2.57367992401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70385146141052</t>
   </si>
   <si>
     <t xml:space="preserve">2.64806365966797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77451634407043</t>
+    <t xml:space="preserve">2.77451610565186</t>
   </si>
   <si>
     <t xml:space="preserve">2.70757102966309</t>
@@ -2387,34 +2387,34 @@
     <t xml:space="preserve">2.88609194755554</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8079891204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83402347564697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.826584815979</t>
+    <t xml:space="preserve">2.80798888206482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83402323722839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82658457756042</t>
   </si>
   <si>
     <t xml:space="preserve">2.68525552749634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78939294815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80426979064941</t>
+    <t xml:space="preserve">2.78939270973206</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80426955223083</t>
   </si>
   <si>
     <t xml:space="preserve">2.75220108032227</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70013236999512</t>
+    <t xml:space="preserve">2.7001326084137</t>
   </si>
   <si>
     <t xml:space="preserve">2.7150092124939</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76707792282104</t>
+    <t xml:space="preserve">2.76707768440247</t>
   </si>
   <si>
     <t xml:space="preserve">2.73732423782349</t>
@@ -2423,28 +2423,28 @@
     <t xml:space="preserve">2.69641304016113</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60343337059021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66294026374817</t>
+    <t xml:space="preserve">2.60343360900879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66294050216675</t>
   </si>
   <si>
     <t xml:space="preserve">2.69269394874573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62946796417236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62574887275696</t>
+    <t xml:space="preserve">2.62946772575378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62574863433838</t>
   </si>
   <si>
     <t xml:space="preserve">2.64062547683716</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65550184249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61459112167358</t>
+    <t xml:space="preserve">2.65550208091736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.614590883255</t>
   </si>
   <si>
     <t xml:space="preserve">2.60715246200562</t>
@@ -2453,7 +2453,7 @@
     <t xml:space="preserve">2.63318705558777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59227585792542</t>
+    <t xml:space="preserve">2.59227561950684</t>
   </si>
   <si>
     <t xml:space="preserve">2.55508375167847</t>
@@ -2462,7 +2462,7 @@
     <t xml:space="preserve">2.45466589927673</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42491221427917</t>
+    <t xml:space="preserve">2.42491245269775</t>
   </si>
   <si>
     <t xml:space="preserve">2.3951587677002</t>
@@ -2471,7 +2471,7 @@
     <t xml:space="preserve">2.40259718894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46954274177551</t>
+    <t xml:space="preserve">2.46954250335693</t>
   </si>
   <si>
     <t xml:space="preserve">2.33937096595764</t>
@@ -2483,7 +2483,7 @@
     <t xml:space="preserve">2.25754880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44722723960876</t>
+    <t xml:space="preserve">2.44722747802734</t>
   </si>
   <si>
     <t xml:space="preserve">2.3840012550354</t>
@@ -2495,22 +2495,22 @@
     <t xml:space="preserve">2.41375470161438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43978881835938</t>
+    <t xml:space="preserve">2.43978905677795</t>
   </si>
   <si>
     <t xml:space="preserve">2.51417303085327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61087203025818</t>
+    <t xml:space="preserve">2.6108717918396</t>
   </si>
   <si>
     <t xml:space="preserve">2.61831021308899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77823519706726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9158456325531</t>
+    <t xml:space="preserve">2.77823543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91584539413452</t>
   </si>
   <si>
     <t xml:space="preserve">2.54392671585083</t>
@@ -2528,7 +2528,7 @@
     <t xml:space="preserve">2.52904963493347</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51045370101929</t>
+    <t xml:space="preserve">2.51045346260071</t>
   </si>
   <si>
     <t xml:space="preserve">2.58483743667603</t>
@@ -2537,7 +2537,7 @@
     <t xml:space="preserve">2.58111834526062</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5997142791748</t>
+    <t xml:space="preserve">2.59971404075623</t>
   </si>
   <si>
     <t xml:space="preserve">2.63690614700317</t>
@@ -2549,7 +2549,7 @@
     <t xml:space="preserve">2.66147232055664</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62969374656677</t>
+    <t xml:space="preserve">2.62969350814819</t>
   </si>
   <si>
     <t xml:space="preserve">2.5740807056427</t>
@@ -2558,10 +2558,10 @@
     <t xml:space="preserve">2.51846814155579</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46285510063171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45491003990173</t>
+    <t xml:space="preserve">2.46285486221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45491027832031</t>
   </si>
   <si>
     <t xml:space="preserve">2.42710399627686</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">2.48668932914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5144956111908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48271679878235</t>
+    <t xml:space="preserve">2.51449537277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48271656036377</t>
   </si>
   <si>
     <t xml:space="preserve">2.43902087211609</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">2.38340830802917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.39532518386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33176755905151</t>
+    <t xml:space="preserve">2.39532542228699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33176732063293</t>
   </si>
   <si>
     <t xml:space="preserve">2.37149095535278</t>
@@ -2651,22 +2651,22 @@
     <t xml:space="preserve">2.44696545600891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50257873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5661358833313</t>
+    <t xml:space="preserve">2.50257849693298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56613612174988</t>
   </si>
   <si>
     <t xml:space="preserve">2.52244019508362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30396103858948</t>
+    <t xml:space="preserve">2.30396127700806</t>
   </si>
   <si>
     <t xml:space="preserve">2.28409934043884</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30793380737305</t>
+    <t xml:space="preserve">2.30793356895447</t>
   </si>
   <si>
     <t xml:space="preserve">2.28807187080383</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">1.96631169319153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97822856903076</t>
+    <t xml:space="preserve">1.97822880744934</t>
   </si>
   <si>
     <t xml:space="preserve">1.98220098018646</t>
@@ -2699,7 +2699,7 @@
     <t xml:space="preserve">2.08548212051392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09342670440674</t>
+    <t xml:space="preserve">2.09342694282532</t>
   </si>
   <si>
     <t xml:space="preserve">2.0815098285675</t>
@@ -2732,7 +2732,7 @@
     <t xml:space="preserve">2.81242156028748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77269792556763</t>
+    <t xml:space="preserve">2.77269816398621</t>
   </si>
   <si>
     <t xml:space="preserve">2.74091935157776</t>
@@ -2750,7 +2750,7 @@
     <t xml:space="preserve">2.86406207084656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84817266464233</t>
+    <t xml:space="preserve">2.84817290306091</t>
   </si>
   <si>
     <t xml:space="preserve">2.85611748695374</t>
@@ -2759,13 +2759,13 @@
     <t xml:space="preserve">2.78461503982544</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87200689315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85214519500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93556451797485</t>
+    <t xml:space="preserve">2.87200665473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85214495658875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93556427955627</t>
   </si>
   <si>
     <t xml:space="preserve">2.96337080001831</t>
@@ -2783,13 +2783,13 @@
     <t xml:space="preserve">2.91173028945923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78064298629761</t>
+    <t xml:space="preserve">2.78064274787903</t>
   </si>
   <si>
     <t xml:space="preserve">2.83228325843811</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94748163223267</t>
+    <t xml:space="preserve">2.94748139381409</t>
   </si>
   <si>
     <t xml:space="preserve">2.97926020622253</t>
@@ -2804,16 +2804,16 @@
     <t xml:space="preserve">2.8283109664917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90378546714783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93953657150269</t>
+    <t xml:space="preserve">2.90378570556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93953680992126</t>
   </si>
   <si>
     <t xml:space="preserve">2.9435088634491</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95542621612549</t>
+    <t xml:space="preserve">2.95542597770691</t>
   </si>
   <si>
     <t xml:space="preserve">2.97528767585754</t>
@@ -2825,13 +2825,13 @@
     <t xml:space="preserve">2.99912190437317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96734309196472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8878960609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80447697639465</t>
+    <t xml:space="preserve">2.96734285354614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88789629936218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80447673797607</t>
   </si>
   <si>
     <t xml:space="preserve">2.82433867454529</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">2.90775775909424</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92364716529846</t>
+    <t xml:space="preserve">2.92364740371704</t>
   </si>
   <si>
     <t xml:space="preserve">2.98323249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02295613288879</t>
+    <t xml:space="preserve">3.02295589447021</t>
   </si>
   <si>
     <t xml:space="preserve">3.04679012298584</t>
@@ -2864,22 +2864,22 @@
     <t xml:space="preserve">3.17787742614746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05473470687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11829233169556</t>
+    <t xml:space="preserve">3.05473494529724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11829209327698</t>
   </si>
   <si>
     <t xml:space="preserve">3.04281759262085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10637545585632</t>
+    <t xml:space="preserve">3.10637521743774</t>
   </si>
   <si>
     <t xml:space="preserve">3.02692818641663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0666515827179</t>
+    <t xml:space="preserve">3.06665182113647</t>
   </si>
   <si>
     <t xml:space="preserve">3.07062411308289</t>
@@ -2915,22 +2915,22 @@
     <t xml:space="preserve">2.72502994537354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75283622741699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81639409065247</t>
+    <t xml:space="preserve">2.75283646583557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81639385223389</t>
   </si>
   <si>
     <t xml:space="preserve">2.99514961242676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15404367446899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07459616661072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13815426826477</t>
+    <t xml:space="preserve">3.15404343605042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0745964050293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13815402984619</t>
   </si>
   <si>
     <t xml:space="preserve">3.0825412273407</t>
@@ -2951,7 +2951,7 @@
     <t xml:space="preserve">3.25335192680359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26924133300781</t>
+    <t xml:space="preserve">3.26924109458923</t>
   </si>
   <si>
     <t xml:space="preserve">3.30102038383484</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">3.3288266658783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3963565826416</t>
+    <t xml:space="preserve">3.39635682106018</t>
   </si>
   <si>
     <t xml:space="preserve">3.2732138633728</t>
@@ -2969,25 +2969,25 @@
     <t xml:space="preserve">3.29307556152344</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23746252059937</t>
+    <t xml:space="preserve">3.23746275901794</t>
   </si>
   <si>
     <t xml:space="preserve">3.23349046707153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20965623855591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25732445716858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20568370819092</t>
+    <t xml:space="preserve">3.20965600013733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25732421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2056839466095</t>
   </si>
   <si>
     <t xml:space="preserve">3.2136287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22554540634155</t>
+    <t xml:space="preserve">3.22554564476013</t>
   </si>
   <si>
     <t xml:space="preserve">3.19773936271667</t>
@@ -2996,7 +2996,7 @@
     <t xml:space="preserve">3.20171165466309</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2652690410614</t>
+    <t xml:space="preserve">3.26526927947998</t>
   </si>
   <si>
     <t xml:space="preserve">3.31690979003906</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">3.34471607208252</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41224575042725</t>
+    <t xml:space="preserve">3.41224598884583</t>
   </si>
   <si>
     <t xml:space="preserve">3.40827345848083</t>
@@ -3017,25 +3017,25 @@
     <t xml:space="preserve">3.55922269821167</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67044854164124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69031023979187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69428277015686</t>
+    <t xml:space="preserve">3.67044830322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69031047821045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69428253173828</t>
   </si>
   <si>
     <t xml:space="preserve">3.66647601127625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63866949081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51949906349182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45594191551208</t>
+    <t xml:space="preserve">3.63866972923279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5194993019104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45594167709351</t>
   </si>
   <si>
     <t xml:space="preserve">3.52347159385681</t>
@@ -3050,13 +3050,13 @@
     <t xml:space="preserve">3.45196914672852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.44005250930786</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34074354171753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24540734291077</t>
+    <t xml:space="preserve">3.44005227088928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34074378013611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24540758132935</t>
   </si>
   <si>
     <t xml:space="preserve">3.26129674911499</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">3.33677101135254</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32485437393188</t>
+    <t xml:space="preserve">3.32485413551331</t>
   </si>
   <si>
     <t xml:space="preserve">3.22157311439514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30499267578125</t>
+    <t xml:space="preserve">3.30499243736267</t>
   </si>
   <si>
     <t xml:space="preserve">3.2811586856842</t>
@@ -3083,7 +3083,7 @@
     <t xml:space="preserve">3.08651351928711</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18979430198669</t>
+    <t xml:space="preserve">3.18979454040527</t>
   </si>
   <si>
     <t xml:space="preserve">3.24937987327576</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">3.19376683235168</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27718615531921</t>
+    <t xml:space="preserve">3.27718591690063</t>
   </si>
   <si>
     <t xml:space="preserve">3.36457800865173</t>
@@ -3101,19 +3101,19 @@
     <t xml:space="preserve">3.37252235412598</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24143481254578</t>
+    <t xml:space="preserve">3.24143505096436</t>
   </si>
   <si>
     <t xml:space="preserve">3.15007090568542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12623691558838</t>
+    <t xml:space="preserve">3.1262366771698</t>
   </si>
   <si>
     <t xml:space="preserve">3.09445810317993</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09048581123352</t>
+    <t xml:space="preserve">3.0904860496521</t>
   </si>
   <si>
     <t xml:space="preserve">3.16993284225464</t>
@@ -3152,16 +3152,16 @@
     <t xml:space="preserve">3.18184995651245</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17390513420105</t>
+    <t xml:space="preserve">3.17390489578247</t>
   </si>
   <si>
     <t xml:space="preserve">3.22951817512512</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03884530067444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00309443473816</t>
+    <t xml:space="preserve">3.03884553909302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00309419631958</t>
   </si>
   <si>
     <t xml:space="preserve">3.01103901863098</t>
@@ -3179,7 +3179,7 @@
     <t xml:space="preserve">2.92761969566345</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79653239250183</t>
+    <t xml:space="preserve">2.79653215408325</t>
   </si>
   <si>
     <t xml:space="preserve">2.87995147705078</t>
@@ -3197,13 +3197,13 @@
     <t xml:space="preserve">3.28513097763062</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36060547828674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37649464607239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36854982376099</t>
+    <t xml:space="preserve">3.36060523986816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37649488449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36855006217957</t>
   </si>
   <si>
     <t xml:space="preserve">3.53141665458679</t>
@@ -3218,10 +3218,10 @@
     <t xml:space="preserve">3.34868860244751</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35663294792175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32088184356689</t>
+    <t xml:space="preserve">3.35663318634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32088208198547</t>
   </si>
   <si>
     <t xml:space="preserve">3.40032911300659</t>
@@ -3239,28 +3239,28 @@
     <t xml:space="preserve">3.48772025108337</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47183108329773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54333329200745</t>
+    <t xml:space="preserve">3.47183132171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54333353042603</t>
   </si>
   <si>
     <t xml:space="preserve">3.54730606079102</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55127787590027</t>
+    <t xml:space="preserve">3.55127763748169</t>
   </si>
   <si>
     <t xml:space="preserve">3.63072514533997</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59100151062012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67442083358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61086344718933</t>
+    <t xml:space="preserve">3.5910017490387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67442107200623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61086320877075</t>
   </si>
   <si>
     <t xml:space="preserve">3.62278032302856</t>
@@ -3269,7 +3269,7 @@
     <t xml:space="preserve">3.67839336395264</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65058660507202</t>
+    <t xml:space="preserve">3.6505868434906</t>
   </si>
   <si>
     <t xml:space="preserve">3.61880779266357</t>
@@ -3278,7 +3278,7 @@
     <t xml:space="preserve">3.6346971988678</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58702921867371</t>
+    <t xml:space="preserve">3.58702898025513</t>
   </si>
   <si>
     <t xml:space="preserve">3.53936100006104</t>
@@ -4806,6 +4806,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.60999989509583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61999988555908</t>
   </si>
 </sst>
 </file>
@@ -71756,7 +71759,7 @@
     </row>
     <row r="2563">
       <c r="A2563" s="1" t="n">
-        <v>46055.6913078704</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B2563" t="n">
         <v>302623</v>
@@ -71777,6 +71780,32 @@
         <v>1597</v>
       </c>
       <c r="H2563" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2564">
+      <c r="A2564" s="1" t="n">
+        <v>46056.6910532407</v>
+      </c>
+      <c r="B2564" t="n">
+        <v>122359</v>
+      </c>
+      <c r="C2564" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="D2564" t="n">
+        <v>3.56500005722046</v>
+      </c>
+      <c r="E2564" t="n">
+        <v>3.60999989509583</v>
+      </c>
+      <c r="F2564" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="G2564" t="s">
+        <v>1598</v>
+      </c>
+      <c r="H2564" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1610" uniqueCount="1610">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="1611">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,16 +38,16 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72976970672607</t>
+    <t xml:space="preserve">4.72976922988892</t>
   </si>
   <si>
     <t xml:space="preserve">IGD.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">4.81178760528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76804542541504</t>
+    <t xml:space="preserve">4.81178855895996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76804447174072</t>
   </si>
   <si>
     <t xml:space="preserve">4.7653112411499</t>
@@ -56,19 +56,19 @@
     <t xml:space="preserve">4.64775037765503</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53839111328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56573104858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67235565185547</t>
+    <t xml:space="preserve">4.53839159011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56573057174683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67235612869263</t>
   </si>
   <si>
     <t xml:space="preserve">4.55206155776978</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33334255218506</t>
+    <t xml:space="preserve">4.33334398269653</t>
   </si>
   <si>
     <t xml:space="preserve">4.16383695602417</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">3.88223814964294</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95605540275574</t>
+    <t xml:space="preserve">3.95605492591858</t>
   </si>
   <si>
     <t xml:space="preserve">4.03807497024536</t>
@@ -92,91 +92,91 @@
     <t xml:space="preserve">3.9751935005188</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94785404205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81388878822327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96425819396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07088232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92051386833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69632863998413</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78654956817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45573902130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49948215484619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69086050987244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56783199310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63891577720642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497233390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755875587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93691730499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87130284309387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05994653701782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00800085067749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95332217216492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98612928390503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99159693717957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03260660171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05447864532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2403883934021</t>
+    <t xml:space="preserve">3.94785451889038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81388926506042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96425747871399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07088184356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92051410675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69632840156555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78654980659485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45573925971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49948239326477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69086074829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56783223152161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63891506195068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497281074524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755970954895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93691754341125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87130236625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05994701385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00800180435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9533212184906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98612976074219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99159741401672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03260707855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05447816848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24038887023926</t>
   </si>
   <si>
     <t xml:space="preserve">4.21031475067139</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37435293197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33607769012451</t>
+    <t xml:space="preserve">4.37435340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33607816696167</t>
   </si>
   <si>
     <t xml:space="preserve">4.34701347351074</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33881139755249</t>
+    <t xml:space="preserve">4.33881187438965</t>
   </si>
   <si>
     <t xml:space="preserve">4.42903280258179</t>
@@ -188,52 +188,52 @@
     <t xml:space="preserve">4.51105213165283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46183967590332</t>
+    <t xml:space="preserve">4.46184015274048</t>
   </si>
   <si>
     <t xml:space="preserve">4.57119941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">4.67508983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60947465896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54932737350464</t>
+    <t xml:space="preserve">4.67509031295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60947418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54932689666748</t>
   </si>
   <si>
     <t xml:space="preserve">4.4837121963501</t>
   </si>
   <si>
-    <t xml:space="preserve">4.34974718093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42083024978638</t>
+    <t xml:space="preserve">4.34974765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42083072662354</t>
   </si>
   <si>
     <t xml:space="preserve">4.42356538772583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2649941444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25405883789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22398519515991</t>
+    <t xml:space="preserve">4.26499462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405836105347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22398471832275</t>
   </si>
   <si>
     <t xml:space="preserve">4.22671890258789</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23765516281128</t>
+    <t xml:space="preserve">4.2376537322998</t>
   </si>
   <si>
     <t xml:space="preserve">4.3306097984314</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40169334411621</t>
+    <t xml:space="preserve">4.40169239044189</t>
   </si>
   <si>
     <t xml:space="preserve">4.31967353820801</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">4.30600452423096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36615180969238</t>
+    <t xml:space="preserve">4.36615085601807</t>
   </si>
   <si>
     <t xml:space="preserve">4.26772832870483</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">4.27046251296997</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29506874084473</t>
+    <t xml:space="preserve">4.29506778717041</t>
   </si>
   <si>
     <t xml:space="preserve">4.39895868301392</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">4.38802337646484</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42629909515381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34427928924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39075756072998</t>
+    <t xml:space="preserve">4.42629861831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34427976608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39075708389282</t>
   </si>
   <si>
     <t xml:space="preserve">4.30326986312866</t>
@@ -287,13 +287,13 @@
     <t xml:space="preserve">4.57292556762695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65062808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091844558716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67940616607666</t>
+    <t xml:space="preserve">4.65062761306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69091892242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67940664291382</t>
   </si>
   <si>
     <t xml:space="preserve">4.69379615783691</t>
@@ -305,43 +305,43 @@
     <t xml:space="preserve">4.61609363555908</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57580375671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63623857498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63048267364502</t>
+    <t xml:space="preserve">4.57580327987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63623905181885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63048315048218</t>
   </si>
   <si>
     <t xml:space="preserve">4.63336133956909</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6391167640686</t>
+    <t xml:space="preserve">4.63911628723145</t>
   </si>
   <si>
     <t xml:space="preserve">4.56429243087769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35133123397827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066560745239</t>
+    <t xml:space="preserve">4.35133075714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066608428955</t>
   </si>
   <si>
     <t xml:space="preserve">4.08368873596191</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95130753517151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97145223617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1613917350769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20168113708496</t>
+    <t xml:space="preserve">3.95130729675293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97145175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16139125823975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20168161392212</t>
   </si>
   <si>
     <t xml:space="preserve">4.24772691726685</t>
@@ -353,28 +353,31 @@
     <t xml:space="preserve">4.03476524353027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84482622146606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633730888367</t>
+    <t xml:space="preserve">3.82755827903748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84482669830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633778572083</t>
   </si>
   <si>
     <t xml:space="preserve">4.22470378875732</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15851306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01749801635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784911155701</t>
+    <t xml:space="preserve">4.15851354598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784887313843</t>
   </si>
   <si>
     <t xml:space="preserve">3.83619260787964</t>
   </si>
   <si>
-    <t xml:space="preserve">3.96281838417053</t>
+    <t xml:space="preserve">3.96281814575195</t>
   </si>
   <si>
     <t xml:space="preserve">4.05778837203979</t>
@@ -389,31 +392,28 @@
     <t xml:space="preserve">4.40313196182251</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33406400680542</t>
+    <t xml:space="preserve">4.3340630531311</t>
   </si>
   <si>
     <t xml:space="preserve">4.5182466506958</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41752099990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45493364334106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48371171951294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45781183242798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53839159011841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52975797653198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48946762084961</t>
+    <t xml:space="preserve">4.41752052307129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45493316650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45781135559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53839206695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52975749969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48946809768677</t>
   </si>
   <si>
     <t xml:space="preserve">4.51536893844604</t>
@@ -422,70 +422,70 @@
     <t xml:space="preserve">4.25923871994019</t>
   </si>
   <si>
-    <t xml:space="preserve">4.38874292373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46644496917725</t>
+    <t xml:space="preserve">4.38874197006226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46644401550293</t>
   </si>
   <si>
     <t xml:space="preserve">4.38298654556274</t>
   </si>
   <si>
-    <t xml:space="preserve">4.36571979522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41464328765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35996341705322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33694124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29377269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3139181137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19017028808594</t>
+    <t xml:space="preserve">4.36572027206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41464376449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35996437072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33694076538086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29377317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31391716003418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19016981124878</t>
   </si>
   <si>
     <t xml:space="preserve">4.19880390167236</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22182607650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26211643218994</t>
+    <t xml:space="preserve">4.22182703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2621169090271</t>
   </si>
   <si>
     <t xml:space="preserve">4.25348234176636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23046016693115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14412355422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19592571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16714668273926</t>
+    <t xml:space="preserve">4.23046064376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14412403106689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19592666625977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16714715957642</t>
   </si>
   <si>
     <t xml:space="preserve">4.15563583374023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1153450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20743656158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14700269699097</t>
+    <t xml:space="preserve">4.11534547805786</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20743703842163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14700174331665</t>
   </si>
   <si>
     <t xml:space="preserve">4.17865800857544</t>
@@ -494,67 +494,67 @@
     <t xml:space="preserve">4.07505559921265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94267392158508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79878091812134</t>
+    <t xml:space="preserve">3.94267416000366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79878067970276</t>
   </si>
   <si>
     <t xml:space="preserve">3.77575755119324</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83907032012939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74697875976562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7498562335968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85921573638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82468128204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79590225219727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87936067581177</t>
+    <t xml:space="preserve">3.83907079696655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7469789981842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74985671043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8592164516449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82468056678772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79590272903442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87936091423035</t>
   </si>
   <si>
     <t xml:space="preserve">3.81029176712036</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78439140319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76424646377563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72971129417419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7124445438385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72395586967468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84194850921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735355377197</t>
+    <t xml:space="preserve">3.78439116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76424551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72971177101135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71244478225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72395634651184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84194803237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735307693481</t>
   </si>
   <si>
     <t xml:space="preserve">4.06354427337646</t>
   </si>
   <si>
-    <t xml:space="preserve">4.10959005355835</t>
+    <t xml:space="preserve">4.10958957672119</t>
   </si>
   <si>
     <t xml:space="preserve">4.11822319030762</t>
@@ -563,79 +563,79 @@
     <t xml:space="preserve">4.08656644821167</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03764343261719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00310897827148</t>
+    <t xml:space="preserve">4.03764295578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00310850143433</t>
   </si>
   <si>
     <t xml:space="preserve">3.97432994842529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91389489173889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93979620933533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92540621757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92828392982483</t>
+    <t xml:space="preserve">3.91389513015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93979597091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92540693283081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92828440666199</t>
   </si>
   <si>
     <t xml:space="preserve">3.89662742614746</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84770441055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75273466110229</t>
+    <t xml:space="preserve">3.84770393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273442268372</t>
   </si>
   <si>
     <t xml:space="preserve">3.75849008560181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55703949928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64337563514709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66927695274353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65776515007019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58006191253662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59733009338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60308575630188</t>
+    <t xml:space="preserve">3.55703997612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64337539672852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66927671432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65776491165161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58006238937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59732961654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60308599472046</t>
   </si>
   <si>
     <t xml:space="preserve">3.63186454772949</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62610864639282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66064357757568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6145977973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80453681945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95994091033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07217693328857</t>
+    <t xml:space="preserve">3.6261088848114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6606433391571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61459708213806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80453658103943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95994067192078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07217741012573</t>
   </si>
   <si>
     <t xml:space="preserve">4.04339933395386</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">4.12685680389404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13261270523071</t>
+    <t xml:space="preserve">4.13261222839355</t>
   </si>
   <si>
     <t xml:space="preserve">4.12110185623169</t>
@@ -656,16 +656,16 @@
     <t xml:space="preserve">4.28226137161255</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33981943130493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34845161437988</t>
+    <t xml:space="preserve">4.33981895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3484525680542</t>
   </si>
   <si>
     <t xml:space="preserve">4.33118486404419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.30240631103516</t>
+    <t xml:space="preserve">4.302405834198</t>
   </si>
   <si>
     <t xml:space="preserve">4.27075004577637</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">4.2131929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18153667449951</t>
+    <t xml:space="preserve">4.18153619766235</t>
   </si>
   <si>
     <t xml:space="preserve">4.09807825088501</t>
@@ -689,25 +689,22 @@
     <t xml:space="preserve">4.10383415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0290093421936</t>
+    <t xml:space="preserve">4.02900981903076</t>
   </si>
   <si>
     <t xml:space="preserve">4.06929969787598</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04627752304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21894836425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30816268920898</t>
+    <t xml:space="preserve">4.21894931793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30816221237183</t>
   </si>
   <si>
     <t xml:space="preserve">4.14987993240356</t>
   </si>
   <si>
-    <t xml:space="preserve">4.47220134735107</t>
+    <t xml:space="preserve">4.47220039367676</t>
   </si>
   <si>
     <t xml:space="preserve">4.51249074935913</t>
@@ -716,25 +713,25 @@
     <t xml:space="preserve">4.37723112106323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44342231750488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59307098388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62472772598267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5700478553772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71969699859619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70818519592285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.80315494537354</t>
+    <t xml:space="preserve">4.44342184066772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59307050704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62472820281982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57004833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71969652175903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70818567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.80315446853638</t>
   </si>
   <si>
     <t xml:space="preserve">4.73120832443237</t>
@@ -749,7 +746,7 @@
     <t xml:space="preserve">4.64487266540527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62185001373291</t>
+    <t xml:space="preserve">4.62184906005859</t>
   </si>
   <si>
     <t xml:space="preserve">4.54702472686768</t>
@@ -758,22 +755,22 @@
     <t xml:space="preserve">4.52687978744507</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46068954467773</t>
+    <t xml:space="preserve">4.46068906784058</t>
   </si>
   <si>
     <t xml:space="preserve">4.6045823097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71394062042236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66501760482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74559736251831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76574277877808</t>
+    <t xml:space="preserve">4.71394109725952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66501712799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74559783935547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76574325561523</t>
   </si>
   <si>
     <t xml:space="preserve">4.74847602844238</t>
@@ -782,10 +779,10 @@
     <t xml:space="preserve">4.78301000595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77149868011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82329988479614</t>
+    <t xml:space="preserve">4.7714991569519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8233003616333</t>
   </si>
   <si>
     <t xml:space="preserve">4.92690277099609</t>
@@ -797,7 +794,7 @@
     <t xml:space="preserve">4.98446035385132</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02475118637085</t>
+    <t xml:space="preserve">5.02475070953369</t>
   </si>
   <si>
     <t xml:space="preserve">5.05640745162964</t>
@@ -809,16 +806,16 @@
     <t xml:space="preserve">4.86359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82905578613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.8759241104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91160154342651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.93538570404053</t>
+    <t xml:space="preserve">4.82905530929565</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.87592363357544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91160106658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.93538618087769</t>
   </si>
   <si>
     <t xml:space="preserve">4.89970874786377</t>
@@ -833,22 +830,22 @@
     <t xml:space="preserve">4.96809101104736</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97106409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89376306533813</t>
+    <t xml:space="preserve">4.97106313705444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89376258850098</t>
   </si>
   <si>
     <t xml:space="preserve">4.94727897644043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94133281707764</t>
+    <t xml:space="preserve">4.94133329391479</t>
   </si>
   <si>
     <t xml:space="preserve">4.92944049835205</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88781642913818</t>
+    <t xml:space="preserve">4.88781595230103</t>
   </si>
   <si>
     <t xml:space="preserve">4.85511159896851</t>
@@ -857,7 +854,7 @@
     <t xml:space="preserve">4.79862260818481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77186441421509</t>
+    <t xml:space="preserve">4.77186393737793</t>
   </si>
   <si>
     <t xml:space="preserve">4.75105237960815</t>
@@ -872,22 +869,22 @@
     <t xml:space="preserve">4.66185903549194</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53401470184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58455753326416</t>
+    <t xml:space="preserve">4.53401374816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.584557056427</t>
   </si>
   <si>
     <t xml:space="preserve">4.61726188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70348262786865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72132110595703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63807392120361</t>
+    <t xml:space="preserve">4.70348310470581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72132158279419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63807439804077</t>
   </si>
   <si>
     <t xml:space="preserve">4.72726774215698</t>
@@ -896,13 +893,13 @@
     <t xml:space="preserve">4.81646156311035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83132791519165</t>
+    <t xml:space="preserve">4.83132696151733</t>
   </si>
   <si>
     <t xml:space="preserve">4.93835973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94430589675903</t>
+    <t xml:space="preserve">4.94430541992188</t>
   </si>
   <si>
     <t xml:space="preserve">4.98295640945435</t>
@@ -917,10 +914,10 @@
     <t xml:space="preserve">4.84619283676147</t>
   </si>
   <si>
-    <t xml:space="preserve">4.89078950881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.00376796722412</t>
+    <t xml:space="preserve">4.89078998565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.00376844406128</t>
   </si>
   <si>
     <t xml:space="preserve">5.05431127548218</t>
@@ -929,7 +926,7 @@
     <t xml:space="preserve">5.04836511611938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99782180786133</t>
+    <t xml:space="preserve">4.99782133102417</t>
   </si>
   <si>
     <t xml:space="preserve">4.9859299659729</t>
@@ -941,16 +938,16 @@
     <t xml:space="preserve">5.12566709518433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11080074310303</t>
+    <t xml:space="preserve">5.11080026626587</t>
   </si>
   <si>
     <t xml:space="preserve">5.07512283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08106899261475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.09593534469604</t>
+    <t xml:space="preserve">5.08106994628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.09593486785889</t>
   </si>
   <si>
     <t xml:space="preserve">5.11377429962158</t>
@@ -965,7 +962,7 @@
     <t xml:space="preserve">4.97700977325439</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05133867263794</t>
+    <t xml:space="preserve">5.05133819580078</t>
   </si>
   <si>
     <t xml:space="preserve">4.99484872817993</t>
@@ -974,55 +971,55 @@
     <t xml:space="preserve">5.01566123962402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06620407104492</t>
+    <t xml:space="preserve">5.06620454788208</t>
   </si>
   <si>
     <t xml:space="preserve">5.13755893707275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.2326979637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24459075927734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.23864555358887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19702196121216</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.17323637008667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.18512916564941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20891427993774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1940484046936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.2475643157959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.25053691864014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26242971420288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14945125579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16431713104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21485996246338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35162448883057</t>
+    <t xml:space="preserve">5.23269891738892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24459171295166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.23864603042603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.197021484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.17323589324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.18512773513794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20891380310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.19404888153076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24756383895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.25053739547729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26242923736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1494517326355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16431760787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21485948562622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35162401199341</t>
   </si>
   <si>
     <t xml:space="preserve">5.44081687927246</t>
@@ -1031,19 +1028,19 @@
     <t xml:space="preserve">5.64893627166748</t>
   </si>
   <si>
-    <t xml:space="preserve">5.6786675453186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.47054862976074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.46757555007935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55974245071411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59541940689087</t>
+    <t xml:space="preserve">5.67866706848145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.47054815292358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.46757507324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55974197387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59541988372803</t>
   </si>
   <si>
     <t xml:space="preserve">5.58947420120239</t>
@@ -1052,7 +1049,7 @@
     <t xml:space="preserve">5.50325298309326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57758140563965</t>
+    <t xml:space="preserve">5.57758188247681</t>
   </si>
   <si>
     <t xml:space="preserve">5.75002241134644</t>
@@ -1061,7 +1058,7 @@
     <t xml:space="preserve">5.90165185928345</t>
   </si>
   <si>
-    <t xml:space="preserve">5.91651773452759</t>
+    <t xml:space="preserve">5.91651725769043</t>
   </si>
   <si>
     <t xml:space="preserve">6.20193815231323</t>
@@ -1073,76 +1070,76 @@
     <t xml:space="preserve">6.11274385452271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.12463665008545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15436792373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.03544139862061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97597980499268</t>
+    <t xml:space="preserve">6.12463617324829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15436744689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.03544282913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97597932815552</t>
   </si>
   <si>
     <t xml:space="preserve">5.88975954055786</t>
   </si>
   <si>
-    <t xml:space="preserve">6.0057110786438</t>
+    <t xml:space="preserve">6.00571155548096</t>
   </si>
   <si>
     <t xml:space="preserve">6.29113101959229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3446478843689</t>
+    <t xml:space="preserve">6.34464740753174</t>
   </si>
   <si>
     <t xml:space="preserve">6.17815256118774</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39816331863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38627052307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.33275413513184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.43384122848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46951866149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41600322723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40411043167114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24356031417847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35653924942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44573450088501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60033702850342</t>
+    <t xml:space="preserve">6.39816379547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38627099990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.33275461196899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.43383979797363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46951818466187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41600227355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40410947799683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24356079101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35654020309448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44573402404785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60033559799194</t>
   </si>
   <si>
     <t xml:space="preserve">6.58844327926636</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71926021575928</t>
+    <t xml:space="preserve">6.71926116943359</t>
   </si>
   <si>
     <t xml:space="preserve">6.65979862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48141098022461</t>
+    <t xml:space="preserve">6.48141050338745</t>
   </si>
   <si>
     <t xml:space="preserve">6.07111978530884</t>
@@ -1154,16 +1151,16 @@
     <t xml:space="preserve">5.76786088943481</t>
   </si>
   <si>
-    <t xml:space="preserve">5.80948448181152</t>
+    <t xml:space="preserve">5.80948495864868</t>
   </si>
   <si>
     <t xml:space="preserve">5.681640625</t>
   </si>
   <si>
-    <t xml:space="preserve">5.73812913894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.81840467453003</t>
+    <t xml:space="preserve">5.73813009262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.81840419769287</t>
   </si>
   <si>
     <t xml:space="preserve">5.73218393325806</t>
@@ -1178,28 +1175,28 @@
     <t xml:space="preserve">5.86300134658813</t>
   </si>
   <si>
-    <t xml:space="preserve">5.95814085006714</t>
+    <t xml:space="preserve">5.9581413269043</t>
   </si>
   <si>
     <t xml:space="preserve">5.92840957641602</t>
   </si>
   <si>
-    <t xml:space="preserve">5.76191473007202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.70839786529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.7975926399231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75596857070923</t>
+    <t xml:space="preserve">5.76191520690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.70839834213257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.79759216308594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75596809387207</t>
   </si>
   <si>
     <t xml:space="preserve">5.6846137046814</t>
   </si>
   <si>
-    <t xml:space="preserve">5.69650602340698</t>
+    <t xml:space="preserve">5.69650650024414</t>
   </si>
   <si>
     <t xml:space="preserve">5.66082859039307</t>
@@ -1211,16 +1208,16 @@
     <t xml:space="preserve">5.45865631103516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33973121643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15539693832397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.30999994277954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.03647232055664</t>
+    <t xml:space="preserve">5.33973073959351</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15539741516113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.3100004196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0364727973938</t>
   </si>
   <si>
     <t xml:space="preserve">4.91754722595215</t>
@@ -1229,16 +1226,16 @@
     <t xml:space="preserve">5.00079536437988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86997699737549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85213804244995</t>
+    <t xml:space="preserve">4.86997747421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85213899612427</t>
   </si>
   <si>
     <t xml:space="preserve">5.14350509643555</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75699901580811</t>
+    <t xml:space="preserve">4.75699853897095</t>
   </si>
   <si>
     <t xml:space="preserve">4.7944598197937</t>
@@ -1247,31 +1244,31 @@
     <t xml:space="preserve">4.70823955535889</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58812522888184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47752618789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46860647201538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53104162216187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6648325920105</t>
+    <t xml:space="preserve">4.58812570571899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47752571105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46860599517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53104114532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66483211517334</t>
   </si>
   <si>
     <t xml:space="preserve">4.66839933395386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55482578277588</t>
+    <t xml:space="preserve">4.55482625961304</t>
   </si>
   <si>
     <t xml:space="preserve">4.49774217605591</t>
   </si>
   <si>
-    <t xml:space="preserve">4.51260805130005</t>
+    <t xml:space="preserve">4.51260757446289</t>
   </si>
   <si>
     <t xml:space="preserve">4.41211652755737</t>
@@ -1280,22 +1277,22 @@
     <t xml:space="preserve">4.36811399459839</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29913806915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4852557182312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46503734588623</t>
+    <t xml:space="preserve">4.29913759231567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48525524139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46503829956055</t>
   </si>
   <si>
     <t xml:space="preserve">4.4418478012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29378652572632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19210529327393</t>
+    <t xml:space="preserve">4.29378604888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19210577011108</t>
   </si>
   <si>
     <t xml:space="preserve">4.57336091995239</t>
@@ -1307,10 +1304,10 @@
     <t xml:space="preserve">5.10297536849976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85351896286011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.95713901519775</t>
+    <t xml:space="preserve">4.85351848602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.95713949203491</t>
   </si>
   <si>
     <t xml:space="preserve">5.14391136169434</t>
@@ -1319,13 +1316,13 @@
     <t xml:space="preserve">5.34731388092041</t>
   </si>
   <si>
-    <t xml:space="preserve">5.28271102905273</t>
+    <t xml:space="preserve">5.28271150588989</t>
   </si>
   <si>
     <t xml:space="preserve">5.17781209945679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01278686523438</t>
+    <t xml:space="preserve">5.01278734207153</t>
   </si>
   <si>
     <t xml:space="preserve">4.96993207931519</t>
@@ -1340,16 +1337,16 @@
     <t xml:space="preserve">4.94498586654663</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03197574615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0159854888916</t>
+    <t xml:space="preserve">5.03197622299194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01598501205444</t>
   </si>
   <si>
     <t xml:space="preserve">5.02621936798096</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01470613479614</t>
+    <t xml:space="preserve">5.0147066116333</t>
   </si>
   <si>
     <t xml:space="preserve">5.08506536483765</t>
@@ -1361,10 +1358,10 @@
     <t xml:space="preserve">4.92579793930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9654541015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02557945251465</t>
+    <t xml:space="preserve">4.96545505523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02557992935181</t>
   </si>
   <si>
     <t xml:space="preserve">5.04029130935669</t>
@@ -1379,16 +1376,16 @@
     <t xml:space="preserve">5.0594801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06971406936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24497318267822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14135217666626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97888660430908</t>
+    <t xml:space="preserve">5.06971454620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24497270584106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14135313034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97888708114624</t>
   </si>
   <si>
     <t xml:space="preserve">4.7646107673645</t>
@@ -1415,16 +1412,16 @@
     <t xml:space="preserve">4.32710313796997</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57399988174438</t>
+    <t xml:space="preserve">4.5740008354187</t>
   </si>
   <si>
     <t xml:space="preserve">4.65267467498779</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63092756271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72943067550659</t>
+    <t xml:space="preserve">4.63092708587646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72943115234375</t>
   </si>
   <si>
     <t xml:space="preserve">4.81961870193481</t>
@@ -1433,13 +1430,13 @@
     <t xml:space="preserve">4.79403352737427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68401718139648</t>
+    <t xml:space="preserve">4.68401670455933</t>
   </si>
   <si>
     <t xml:space="preserve">4.58679294586182</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8741979598999</t>
+    <t xml:space="preserve">4.87419843673706</t>
   </si>
   <si>
     <t xml:space="preserve">4.99108505249023</t>
@@ -1451,16 +1448,16 @@
     <t xml:space="preserve">4.9842095375061</t>
   </si>
   <si>
-    <t xml:space="preserve">5.03165197372437</t>
+    <t xml:space="preserve">5.03165149688721</t>
   </si>
   <si>
     <t xml:space="preserve">4.79375219345093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79512739181519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7607479095459</t>
+    <t xml:space="preserve">4.79512786865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76074886322021</t>
   </si>
   <si>
     <t xml:space="preserve">4.74630975723267</t>
@@ -1469,7 +1466,7 @@
     <t xml:space="preserve">4.86113405227661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79031372070312</t>
+    <t xml:space="preserve">4.79031467437744</t>
   </si>
   <si>
     <t xml:space="preserve">4.81300401687622</t>
@@ -1484,10 +1481,10 @@
     <t xml:space="preserve">4.73187065124512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.8453197479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.78687620162964</t>
+    <t xml:space="preserve">4.84532022476196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.7868766784668</t>
   </si>
   <si>
     <t xml:space="preserve">4.76968669891357</t>
@@ -1496,19 +1493,19 @@
     <t xml:space="preserve">4.91614007949829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.9780216217041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96770763397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.82675552368164</t>
+    <t xml:space="preserve">4.97802114486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96770715713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.82675504684448</t>
   </si>
   <si>
     <t xml:space="preserve">4.85013294219971</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86044597625732</t>
+    <t xml:space="preserve">4.86044645309448</t>
   </si>
   <si>
     <t xml:space="preserve">4.89963817596436</t>
@@ -1517,16 +1514,16 @@
     <t xml:space="preserve">4.93470430374146</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99177265167236</t>
+    <t xml:space="preserve">4.99177312850952</t>
   </si>
   <si>
     <t xml:space="preserve">5.0543417930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96151971817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97939682006836</t>
+    <t xml:space="preserve">4.96152019500732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.9793963432312</t>
   </si>
   <si>
     <t xml:space="preserve">4.99246025085449</t>
@@ -1538,7 +1535,7 @@
     <t xml:space="preserve">4.98489713668823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85219573974609</t>
+    <t xml:space="preserve">4.85219621658325</t>
   </si>
   <si>
     <t xml:space="preserve">4.903076171875</t>
@@ -1547,37 +1544,37 @@
     <t xml:space="preserve">4.97183322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93882989883423</t>
+    <t xml:space="preserve">4.93882942199707</t>
   </si>
   <si>
     <t xml:space="preserve">4.91682767868042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83363103866577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76556158065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75868558883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75043487548828</t>
+    <t xml:space="preserve">4.83363151550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76556205749512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75868606567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75043535232544</t>
   </si>
   <si>
     <t xml:space="preserve">4.67067670822144</t>
   </si>
   <si>
-    <t xml:space="preserve">4.58129262924194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5427885055542</t>
+    <t xml:space="preserve">4.58129215240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54278802871704</t>
   </si>
   <si>
     <t xml:space="preserve">4.4630298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48228216171265</t>
+    <t xml:space="preserve">4.48228168487549</t>
   </si>
   <si>
     <t xml:space="preserve">4.51941061019897</t>
@@ -1586,7 +1583,7 @@
     <t xml:space="preserve">4.60604524612427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.59779357910156</t>
+    <t xml:space="preserve">4.59779405593872</t>
   </si>
   <si>
     <t xml:space="preserve">4.52972412109375</t>
@@ -1595,22 +1592,22 @@
     <t xml:space="preserve">4.5379753112793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5792293548584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55172681808472</t>
+    <t xml:space="preserve">4.57922983169556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55172634124756</t>
   </si>
   <si>
     <t xml:space="preserve">4.57235383987427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55241441726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50634717941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51597309112549</t>
+    <t xml:space="preserve">4.55241394042969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50634670257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51597261428833</t>
   </si>
   <si>
     <t xml:space="preserve">4.49053287506104</t>
@@ -1622,13 +1619,13 @@
     <t xml:space="preserve">4.518723487854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.53041172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51047277450562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52491140365601</t>
+    <t xml:space="preserve">4.53041219711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5104718208313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52491092681885</t>
   </si>
   <si>
     <t xml:space="preserve">4.485032081604</t>
@@ -1643,7 +1640,7 @@
     <t xml:space="preserve">4.6651759147644</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6541748046875</t>
+    <t xml:space="preserve">4.65417528152466</t>
   </si>
   <si>
     <t xml:space="preserve">4.70299291610718</t>
@@ -1652,43 +1649,43 @@
     <t xml:space="preserve">4.73049545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7105565071106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6466121673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63354730606079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55035161972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50840997695923</t>
+    <t xml:space="preserve">4.71055555343628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64661169052124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63354778289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5503511428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.50840950012207</t>
   </si>
   <si>
     <t xml:space="preserve">4.41558742523193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42727613449097</t>
+    <t xml:space="preserve">4.42727661132812</t>
   </si>
   <si>
     <t xml:space="preserve">4.40046072006226</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33239126205444</t>
+    <t xml:space="preserve">4.3323917388916</t>
   </si>
   <si>
     <t xml:space="preserve">4.22237968444824</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20450258255005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16256046295166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06630086898804</t>
+    <t xml:space="preserve">4.20450305938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16256093978882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06630039215088</t>
   </si>
   <si>
     <t xml:space="preserve">4.09311628341675</t>
@@ -1700,7 +1697,7 @@
     <t xml:space="preserve">4.05942487716675</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09724187850952</t>
+    <t xml:space="preserve">4.09724140167236</t>
   </si>
   <si>
     <t xml:space="preserve">4.0497989654541</t>
@@ -1718,28 +1715,28 @@
     <t xml:space="preserve">4.08830308914185</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13161993026733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21962928771973</t>
+    <t xml:space="preserve">4.13162040710449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21962976455688</t>
   </si>
   <si>
     <t xml:space="preserve">4.28563594818115</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29732465744019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28976202011108</t>
+    <t xml:space="preserve">4.29732513427734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28976154327393</t>
   </si>
   <si>
     <t xml:space="preserve">4.22100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15293455123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36608266830444</t>
+    <t xml:space="preserve">4.15293502807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36608219146729</t>
   </si>
   <si>
     <t xml:space="preserve">4.27601051330566</t>
@@ -1748,7 +1745,7 @@
     <t xml:space="preserve">4.22513008117676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1948766708374</t>
+    <t xml:space="preserve">4.19487714767456</t>
   </si>
   <si>
     <t xml:space="preserve">4.12749481201172</t>
@@ -1760,10 +1757,10 @@
     <t xml:space="preserve">4.13505840301514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09174060821533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0326099395752</t>
+    <t xml:space="preserve">4.09174108505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03260946273804</t>
   </si>
   <si>
     <t xml:space="preserve">4.03467273712158</t>
@@ -1778,7 +1775,7 @@
     <t xml:space="preserve">4.2237548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23544359207153</t>
+    <t xml:space="preserve">4.23544311523438</t>
   </si>
   <si>
     <t xml:space="preserve">4.19900226593018</t>
@@ -1787,16 +1784,16 @@
     <t xml:space="preserve">4.1886887550354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1137433052063</t>
+    <t xml:space="preserve">4.11374378204346</t>
   </si>
   <si>
     <t xml:space="preserve">4.04429864883423</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02917242050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99273061752319</t>
+    <t xml:space="preserve">4.02917194366455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99273085594177</t>
   </si>
   <si>
     <t xml:space="preserve">3.99891901016235</t>
@@ -1805,37 +1802,37 @@
     <t xml:space="preserve">3.96316480636597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88684439659119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98241639137268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90540862083435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8737804889679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78164649009705</t>
+    <t xml:space="preserve">3.88684415817261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98241710662842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90540885925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87378120422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78164625167847</t>
   </si>
   <si>
     <t xml:space="preserve">3.71013855934143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69501209259033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73351573944092</t>
+    <t xml:space="preserve">3.69501185417175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7335159778595</t>
   </si>
   <si>
     <t xml:space="preserve">3.72870302200317</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64894485473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70051240921021</t>
+    <t xml:space="preserve">3.64894461631775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70051264762878</t>
   </si>
   <si>
     <t xml:space="preserve">3.83115148544312</t>
@@ -1844,25 +1841,25 @@
     <t xml:space="preserve">3.8999080657959</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99341869354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97829127311707</t>
+    <t xml:space="preserve">3.9934184551239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97829174995422</t>
   </si>
   <si>
     <t xml:space="preserve">4.06286287307739</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04842376708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06767606735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04292392730713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99548053741455</t>
+    <t xml:space="preserve">4.048424243927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06767559051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04292345046997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99548125267029</t>
   </si>
   <si>
     <t xml:space="preserve">3.95491409301758</t>
@@ -1880,16 +1877,16 @@
     <t xml:space="preserve">4.01335763931274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97004079818726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07180213928223</t>
+    <t xml:space="preserve">3.97004055976868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07180118560791</t>
   </si>
   <si>
     <t xml:space="preserve">4.11786842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">4.22788047790527</t>
+    <t xml:space="preserve">4.22788000106812</t>
   </si>
   <si>
     <t xml:space="preserve">4.31863975524902</t>
@@ -1901,22 +1898,22 @@
     <t xml:space="preserve">4.29044914245605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25057029724121</t>
+    <t xml:space="preserve">4.25057077407837</t>
   </si>
   <si>
     <t xml:space="preserve">4.24919509887695</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26982259750366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26294660568237</t>
+    <t xml:space="preserve">4.2698221206665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26294612884521</t>
   </si>
   <si>
     <t xml:space="preserve">4.24231958389282</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13643312454224</t>
+    <t xml:space="preserve">4.13643360137939</t>
   </si>
   <si>
     <t xml:space="preserve">4.05392408370972</t>
@@ -1925,7 +1922,7 @@
     <t xml:space="preserve">4.12543201446533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08967781066895</t>
+    <t xml:space="preserve">4.0896782875061</t>
   </si>
   <si>
     <t xml:space="preserve">4.13230800628662</t>
@@ -1934,19 +1931,19 @@
     <t xml:space="preserve">4.17149925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23819446563721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22169208526611</t>
+    <t xml:space="preserve">4.23819398880005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22169256210327</t>
   </si>
   <si>
     <t xml:space="preserve">4.21894216537476</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21481609344482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16324806213379</t>
+    <t xml:space="preserve">4.21481704711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16324853897095</t>
   </si>
   <si>
     <t xml:space="preserve">4.28494834899902</t>
@@ -1955,7 +1952,7 @@
     <t xml:space="preserve">4.34476757049561</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2540078163147</t>
+    <t xml:space="preserve">4.25400829315186</t>
   </si>
   <si>
     <t xml:space="preserve">4.33720445632935</t>
@@ -1967,16 +1964,16 @@
     <t xml:space="preserve">4.50359678268433</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57441711425781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.47609376907349</t>
+    <t xml:space="preserve">4.57441663742065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.47609424591064</t>
   </si>
   <si>
     <t xml:space="preserve">4.44171524047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4485912322998</t>
+    <t xml:space="preserve">4.44859027862549</t>
   </si>
   <si>
     <t xml:space="preserve">4.55653953552246</t>
@@ -1997,78 +1994,81 @@
     <t xml:space="preserve">4.57097864151001</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5716667175293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.50772190093994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45752859115601</t>
+    <t xml:space="preserve">4.57166624069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5077223777771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45752906799316</t>
   </si>
   <si>
     <t xml:space="preserve">4.41971302032471</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46234226226807</t>
+    <t xml:space="preserve">4.46234273910522</t>
   </si>
   <si>
     <t xml:space="preserve">4.42796421051025</t>
   </si>
   <si>
+    <t xml:space="preserve">4.54485082626343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52422332763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55860233306885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58610534667969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45546627044678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48296976089478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53109931945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56547784805298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59985685348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64111089706421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61360883712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62048387527466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.62736034393311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71674394607544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65486288070679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49672079086304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5522894859314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6117959022522</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.54485130310059</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52422380447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55860280990601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58610486984253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45546674728394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48296928405762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53109979629517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56547784805298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59985685348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64111137390137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61360836029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6204833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.62735986709595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71674394607544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65486240386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49672079086304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5522894859314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61179637908936</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.60435819625854</t>
   </si>
   <si>
@@ -2078,7 +2078,7 @@
     <t xml:space="preserve">4.6936182975769</t>
   </si>
   <si>
-    <t xml:space="preserve">4.73824882507324</t>
+    <t xml:space="preserve">4.73824834823608</t>
   </si>
   <si>
     <t xml:space="preserve">4.71593379974365</t>
@@ -2087,7 +2087,7 @@
     <t xml:space="preserve">4.63411140441895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65642642974854</t>
+    <t xml:space="preserve">4.65642690658569</t>
   </si>
   <si>
     <t xml:space="preserve">4.58948135375977</t>
@@ -2096,22 +2096,22 @@
     <t xml:space="preserve">4.51509761810303</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57460451126099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56716585159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55972766876221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64898777008057</t>
+    <t xml:space="preserve">4.57460403442383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56716632843018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55972814559937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64898824691772</t>
   </si>
   <si>
     <t xml:space="preserve">4.64154958724976</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5820426940918</t>
+    <t xml:space="preserve">4.58204221725464</t>
   </si>
   <si>
     <t xml:space="preserve">4.52997398376465</t>
@@ -2129,10 +2129,10 @@
     <t xml:space="preserve">4.37376832962036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.4183988571167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35889196395874</t>
+    <t xml:space="preserve">4.41839838027954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35889148712158</t>
   </si>
   <si>
     <t xml:space="preserve">4.32913780212402</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">4.59691953659058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50765943527222</t>
+    <t xml:space="preserve">4.50765895843506</t>
   </si>
   <si>
     <t xml:space="preserve">4.49278211593628</t>
@@ -2162,10 +2162,10 @@
     <t xml:space="preserve">4.43327522277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40352153778076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38864469528198</t>
+    <t xml:space="preserve">4.40352201461792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38864517211914</t>
   </si>
   <si>
     <t xml:space="preserve">4.39608335494995</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">4.20268535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19524669647217</t>
+    <t xml:space="preserve">4.19524717330933</t>
   </si>
   <si>
     <t xml:space="preserve">4.10598659515381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13573980331421</t>
+    <t xml:space="preserve">4.13574028015137</t>
   </si>
   <si>
     <t xml:space="preserve">4.01672601699829</t>
@@ -2198,55 +2198,55 @@
     <t xml:space="preserve">3.93490362167358</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90515065193176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95721888542175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89771199226379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98697280883789</t>
+    <t xml:space="preserve">3.9051501750946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95721912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89771151542664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98697257041931</t>
   </si>
   <si>
     <t xml:space="preserve">3.9200267791748</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94234228134155</t>
+    <t xml:space="preserve">3.94234204292297</t>
   </si>
   <si>
     <t xml:space="preserve">3.97953391075134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97209525108337</t>
+    <t xml:space="preserve">3.97209596633911</t>
   </si>
   <si>
     <t xml:space="preserve">4.04647922515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06879425048828</t>
+    <t xml:space="preserve">4.06879472732544</t>
   </si>
   <si>
     <t xml:space="preserve">4.098548412323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16549396514893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18780851364136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18037033081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17293214797974</t>
+    <t xml:space="preserve">4.16549301147461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18780899047852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18036985397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17293167114258</t>
   </si>
   <si>
     <t xml:space="preserve">4.11342525482178</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14317846298218</t>
+    <t xml:space="preserve">4.14317798614502</t>
   </si>
   <si>
     <t xml:space="preserve">4.1283016204834</t>
@@ -2255,37 +2255,37 @@
     <t xml:space="preserve">4.15805530548096</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03904056549072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23243856430054</t>
+    <t xml:space="preserve">4.03904104232788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2324390411377</t>
   </si>
   <si>
     <t xml:space="preserve">4.23987722396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26963043212891</t>
+    <t xml:space="preserve">4.26963090896606</t>
   </si>
   <si>
     <t xml:space="preserve">4.30682277679443</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29194641113281</t>
+    <t xml:space="preserve">4.2919454574585</t>
   </si>
   <si>
     <t xml:space="preserve">4.2621922492981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27706909179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29938459396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28450775146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41096019744873</t>
+    <t xml:space="preserve">4.27706956863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29938411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28450727462769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41095972061157</t>
   </si>
   <si>
     <t xml:space="preserve">4.44071340560913</t>
@@ -2303,19 +2303,19 @@
     <t xml:space="preserve">4.6638650894165</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74568748474121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.79031753540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70105743408203</t>
+    <t xml:space="preserve">4.74568700790405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.79031801223755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70105695724487</t>
   </si>
   <si>
     <t xml:space="preserve">4.67874193191528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61923503875732</t>
+    <t xml:space="preserve">4.61923456192017</t>
   </si>
   <si>
     <t xml:space="preserve">4.75312519073486</t>
@@ -2324,25 +2324,25 @@
     <t xml:space="preserve">4.67130374908447</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70849514007568</t>
+    <t xml:space="preserve">4.70849561691284</t>
   </si>
   <si>
     <t xml:space="preserve">4.72337198257446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68618011474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0836706161499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06135606765747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96465706825256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92746496200562</t>
+    <t xml:space="preserve">4.68618059158325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08367109298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06135559082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96465730667114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92746543884277</t>
   </si>
   <si>
     <t xml:space="preserve">3.48116230964661</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">2.54020714759827</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57367968559265</t>
+    <t xml:space="preserve">2.57367992401123</t>
   </si>
   <si>
     <t xml:space="preserve">2.70385146141052</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">2.64806365966797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77451610565186</t>
+    <t xml:space="preserve">2.77451634407043</t>
   </si>
   <si>
     <t xml:space="preserve">2.70757079124451</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">2.80798888206482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83402299880981</t>
+    <t xml:space="preserve">2.83402323722839</t>
   </si>
   <si>
     <t xml:space="preserve">2.826584815979</t>
@@ -2399,10 +2399,10 @@
     <t xml:space="preserve">2.80426955223083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75220131874084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70013236999512</t>
+    <t xml:space="preserve">2.75220084190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7001326084137</t>
   </si>
   <si>
     <t xml:space="preserve">2.71500945091248</t>
@@ -2411,7 +2411,7 @@
     <t xml:space="preserve">2.76707792282104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73732423782349</t>
+    <t xml:space="preserve">2.73732447624207</t>
   </si>
   <si>
     <t xml:space="preserve">2.69641327857971</t>
@@ -2420,7 +2420,7 @@
     <t xml:space="preserve">2.60343337059021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66294050216675</t>
+    <t xml:space="preserve">2.66294026374817</t>
   </si>
   <si>
     <t xml:space="preserve">2.69269394874573</t>
@@ -2429,16 +2429,16 @@
     <t xml:space="preserve">2.62946772575378</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6257483959198</t>
+    <t xml:space="preserve">2.62574863433838</t>
   </si>
   <si>
     <t xml:space="preserve">2.64062523841858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65550231933594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.614590883255</t>
+    <t xml:space="preserve">2.65550208091736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61459112167358</t>
   </si>
   <si>
     <t xml:space="preserve">2.60715270042419</t>
@@ -2453,19 +2453,19 @@
     <t xml:space="preserve">2.55508399009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45466566085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42491221427917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3951587677002</t>
+    <t xml:space="preserve">2.45466589927673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42491245269775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.39515900611877</t>
   </si>
   <si>
     <t xml:space="preserve">2.40259718894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46954250335693</t>
+    <t xml:space="preserve">2.46954226493835</t>
   </si>
   <si>
     <t xml:space="preserve">2.33937096595764</t>
@@ -2477,34 +2477,34 @@
     <t xml:space="preserve">2.25754880905151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44722747802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38400101661682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41747379302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41375470161438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43978905677795</t>
+    <t xml:space="preserve">2.44722723960876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3840012550354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41747403144836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41375494003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43978881835938</t>
   </si>
   <si>
     <t xml:space="preserve">2.51417303085327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6108717918396</t>
+    <t xml:space="preserve">2.61087155342102</t>
   </si>
   <si>
     <t xml:space="preserve">2.61831021308899</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77823519706726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91584539413452</t>
+    <t xml:space="preserve">2.77823543548584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9158456325531</t>
   </si>
   <si>
     <t xml:space="preserve">2.54392647743225</t>
@@ -2519,13 +2519,13 @@
     <t xml:space="preserve">2.49929594993591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52904963493347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51045370101929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58483743667603</t>
+    <t xml:space="preserve">2.52904939651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51045346260071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58483719825745</t>
   </si>
   <si>
     <t xml:space="preserve">2.58111810684204</t>
@@ -2534,10 +2534,10 @@
     <t xml:space="preserve">2.5997142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63690614700317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68530678749084</t>
+    <t xml:space="preserve">2.63690638542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68530654907227</t>
   </si>
   <si>
     <t xml:space="preserve">2.66147232055664</t>
@@ -2549,16 +2549,16 @@
     <t xml:space="preserve">2.5740807056427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51846814155579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46285510063171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45491051673889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42710399627686</t>
+    <t xml:space="preserve">2.51846790313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46285486221313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45491027832031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42710423469543</t>
   </si>
   <si>
     <t xml:space="preserve">2.51052331924438</t>
@@ -2567,7 +2567,7 @@
     <t xml:space="preserve">2.47079968452454</t>
   </si>
   <si>
-    <t xml:space="preserve">2.49066138267517</t>
+    <t xml:space="preserve">2.49066162109375</t>
   </si>
   <si>
     <t xml:space="preserve">2.53435730934143</t>
@@ -2594,13 +2594,13 @@
     <t xml:space="preserve">2.41121459007263</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40724229812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44299340248108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42313146591187</t>
+    <t xml:space="preserve">2.40724205970764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4429931640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42313170433044</t>
   </si>
   <si>
     <t xml:space="preserve">2.48668932914734</t>
@@ -2612,10 +2612,10 @@
     <t xml:space="preserve">2.48271679878235</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43902087211609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57010841369629</t>
+    <t xml:space="preserve">2.43902111053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57010817527771</t>
   </si>
   <si>
     <t xml:space="preserve">2.49860620498657</t>
@@ -2645,25 +2645,25 @@
     <t xml:space="preserve">2.44696545600891</t>
   </si>
   <si>
-    <t xml:space="preserve">2.50257849693298</t>
+    <t xml:space="preserve">2.50257873535156</t>
   </si>
   <si>
     <t xml:space="preserve">2.56613612174988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5224404335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30396151542664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28409934043884</t>
+    <t xml:space="preserve">2.52244019508362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30396127700806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28409957885742</t>
   </si>
   <si>
     <t xml:space="preserve">2.30793356895447</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28807187080383</t>
+    <t xml:space="preserve">2.28807163238525</t>
   </si>
   <si>
     <t xml:space="preserve">2.25232076644897</t>
@@ -2684,19 +2684,19 @@
     <t xml:space="preserve">1.96631169319153</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97822892665863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.98220121860504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0854823589325</t>
+    <t xml:space="preserve">1.97822868824005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.98220098018646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08548212051392</t>
   </si>
   <si>
     <t xml:space="preserve">2.09342670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0815098285675</t>
+    <t xml:space="preserve">2.08150959014893</t>
   </si>
   <si>
     <t xml:space="preserve">2.15301203727722</t>
@@ -2705,10 +2705,10 @@
     <t xml:space="preserve">2.05370330810547</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26026511192322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58997011184692</t>
+    <t xml:space="preserve">2.2602653503418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5899703502655</t>
   </si>
   <si>
     <t xml:space="preserve">2.72900223731995</t>
@@ -2717,10 +2717,10 @@
     <t xml:space="preserve">2.71311283111572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88392376899719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8362557888031</t>
+    <t xml:space="preserve">2.88392400741577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83625555038452</t>
   </si>
   <si>
     <t xml:space="preserve">2.81242156028748</t>
@@ -2738,13 +2738,13 @@
     <t xml:space="preserve">2.8203661441803</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84420037269592</t>
+    <t xml:space="preserve">2.84420013427734</t>
   </si>
   <si>
     <t xml:space="preserve">2.86406207084656</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84817290306091</t>
+    <t xml:space="preserve">2.84817266464233</t>
   </si>
   <si>
     <t xml:space="preserve">2.85611724853516</t>
@@ -2753,7 +2753,7 @@
     <t xml:space="preserve">2.78461527824402</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87200665473938</t>
+    <t xml:space="preserve">2.87200689315796</t>
   </si>
   <si>
     <t xml:space="preserve">2.85214495658875</t>
@@ -2780,13 +2780,13 @@
     <t xml:space="preserve">2.78064274787903</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83228349685669</t>
+    <t xml:space="preserve">2.83228325843811</t>
   </si>
   <si>
     <t xml:space="preserve">2.94748139381409</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97925996780396</t>
+    <t xml:space="preserve">2.97926020622253</t>
   </si>
   <si>
     <t xml:space="preserve">2.93159198760986</t>
@@ -2801,7 +2801,7 @@
     <t xml:space="preserve">2.90378570556641</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93953680992126</t>
+    <t xml:space="preserve">2.93953657150269</t>
   </si>
   <si>
     <t xml:space="preserve">2.9435088634491</t>
@@ -2819,13 +2819,13 @@
     <t xml:space="preserve">2.99912190437317</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96734285354614</t>
+    <t xml:space="preserve">2.96734309196472</t>
   </si>
   <si>
     <t xml:space="preserve">2.8878960609436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80447673797607</t>
+    <t xml:space="preserve">2.80447697639465</t>
   </si>
   <si>
     <t xml:space="preserve">2.82433867454529</t>
@@ -2837,7 +2837,7 @@
     <t xml:space="preserve">2.89186859130859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90775799751282</t>
+    <t xml:space="preserve">2.90775775909424</t>
   </si>
   <si>
     <t xml:space="preserve">2.92364740371704</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">2.98323249816895</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02295589447021</t>
+    <t xml:space="preserve">3.02295613288879</t>
   </si>
   <si>
     <t xml:space="preserve">3.04679012298584</t>
@@ -2873,16 +2873,16 @@
     <t xml:space="preserve">3.02692818641663</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06665182113647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07062411308289</t>
+    <t xml:space="preserve">3.0666515827179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07062387466431</t>
   </si>
   <si>
     <t xml:space="preserve">2.76078081130981</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78858757019043</t>
+    <t xml:space="preserve">2.78858733177185</t>
   </si>
   <si>
     <t xml:space="preserve">2.84022808074951</t>
@@ -2897,7 +2897,7 @@
     <t xml:space="preserve">2.76872563362122</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74886393547058</t>
+    <t xml:space="preserve">2.74886417388916</t>
   </si>
   <si>
     <t xml:space="preserve">2.69325113296509</t>
@@ -2912,10 +2912,10 @@
     <t xml:space="preserve">2.75283622741699</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81639385223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99514961242676</t>
+    <t xml:space="preserve">2.81639409065247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99514937400818</t>
   </si>
   <si>
     <t xml:space="preserve">3.15404343605042</t>
@@ -2930,16 +2930,16 @@
     <t xml:space="preserve">3.0825412273407</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14609885215759</t>
+    <t xml:space="preserve">3.14609861373901</t>
   </si>
   <si>
     <t xml:space="preserve">3.09843063354492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18582224845886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13020920753479</t>
+    <t xml:space="preserve">3.18582248687744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13020944595337</t>
   </si>
   <si>
     <t xml:space="preserve">3.25335192680359</t>
@@ -2969,7 +2969,7 @@
     <t xml:space="preserve">3.23349046707153</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20965623855591</t>
+    <t xml:space="preserve">3.20965647697449</t>
   </si>
   <si>
     <t xml:space="preserve">3.25732421875</t>
@@ -2981,10 +2981,10 @@
     <t xml:space="preserve">3.2136287689209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22554564476013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1977391242981</t>
+    <t xml:space="preserve">3.22554540634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19773936271667</t>
   </si>
   <si>
     <t xml:space="preserve">3.20171165466309</t>
@@ -2999,16 +2999,16 @@
     <t xml:space="preserve">3.35266041755676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34471607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41224598884583</t>
+    <t xml:space="preserve">3.34471583366394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41224575042725</t>
   </si>
   <si>
     <t xml:space="preserve">3.40827345848083</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55922293663025</t>
+    <t xml:space="preserve">3.55922269821167</t>
   </si>
   <si>
     <t xml:space="preserve">3.67044830322266</t>
@@ -3026,22 +3026,22 @@
     <t xml:space="preserve">3.63866996765137</t>
   </si>
   <si>
-    <t xml:space="preserve">3.5194993019104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45594167709351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52347159385681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49169278144836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40430092811584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45196938514709</t>
+    <t xml:space="preserve">3.51949906349182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45594191551208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52347183227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49169301986694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.404301404953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45196914672852</t>
   </si>
   <si>
     <t xml:space="preserve">3.44005227088928</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">3.26129674911499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33677124977112</t>
+    <t xml:space="preserve">3.33677101135254</t>
   </si>
   <si>
     <t xml:space="preserve">3.32485413551331</t>
@@ -3065,13 +3065,13 @@
     <t xml:space="preserve">3.22157311439514</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30499243736267</t>
+    <t xml:space="preserve">3.30499267578125</t>
   </si>
   <si>
     <t xml:space="preserve">3.2811586856842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06267952919006</t>
+    <t xml:space="preserve">3.06267929077148</t>
   </si>
   <si>
     <t xml:space="preserve">3.08651351928711</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">3.36457800865173</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37252235412598</t>
+    <t xml:space="preserve">3.37252259254456</t>
   </si>
   <si>
     <t xml:space="preserve">3.24143505096436</t>
@@ -3119,7 +3119,7 @@
     <t xml:space="preserve">3.07856893539429</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97131538391113</t>
+    <t xml:space="preserve">2.97131562232971</t>
   </si>
   <si>
     <t xml:space="preserve">2.99117732048035</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">3.0189836025238</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31293725967407</t>
+    <t xml:space="preserve">3.31293749809265</t>
   </si>
   <si>
     <t xml:space="preserve">3.16596031188965</t>
@@ -3149,7 +3149,7 @@
     <t xml:space="preserve">3.17390513420105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22951817512512</t>
+    <t xml:space="preserve">3.22951793670654</t>
   </si>
   <si>
     <t xml:space="preserve">3.03884530067444</t>
@@ -3164,7 +3164,7 @@
     <t xml:space="preserve">3.05076241493225</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15801572799683</t>
+    <t xml:space="preserve">3.15801548957825</t>
   </si>
   <si>
     <t xml:space="preserve">3.21760106086731</t>
@@ -3179,10 +3179,10 @@
     <t xml:space="preserve">2.87995147705078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98720502853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03487277030945</t>
+    <t xml:space="preserve">2.98720479011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03487300872803</t>
   </si>
   <si>
     <t xml:space="preserve">2.91570258140564</t>
@@ -3194,10 +3194,10 @@
     <t xml:space="preserve">3.36060547828674</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37649488449097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36855006217957</t>
+    <t xml:space="preserve">3.37649464607239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36854982376099</t>
   </si>
   <si>
     <t xml:space="preserve">3.53141665458679</t>
@@ -3209,7 +3209,7 @@
     <t xml:space="preserve">3.42416310310364</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34868836402893</t>
+    <t xml:space="preserve">3.34868860244751</t>
   </si>
   <si>
     <t xml:space="preserve">3.35663294792175</t>
@@ -3224,19 +3224,19 @@
     <t xml:space="preserve">3.39238429069519</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38443970680237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.46388649940491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.48772048950195</t>
+    <t xml:space="preserve">3.38443946838379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46388673782349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.48772072792053</t>
   </si>
   <si>
     <t xml:space="preserve">3.47183108329773</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54333353042603</t>
+    <t xml:space="preserve">3.54333329200745</t>
   </si>
   <si>
     <t xml:space="preserve">3.54730582237244</t>
@@ -3251,7 +3251,7 @@
     <t xml:space="preserve">3.5910017490387</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67442107200623</t>
+    <t xml:space="preserve">3.67442083358765</t>
   </si>
   <si>
     <t xml:space="preserve">3.61086320877075</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">3.63469696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58702921867371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53936076164246</t>
+    <t xml:space="preserve">3.58702874183655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53936100006104</t>
   </si>
   <si>
     <t xml:space="preserve">3.55525064468384</t>
@@ -4842,6 +4842,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.17999982833862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32000017166138</t>
   </si>
 </sst>
 </file>
@@ -8422,7 +8425,7 @@
         <v>6.18208885192871</v>
       </c>
       <c r="G125" t="s">
-        <v>39</v>
+        <v>113</v>
       </c>
       <c r="H125" t="s">
         <v>9</v>
@@ -8448,7 +8451,7 @@
         <v>6.20997905731201</v>
       </c>
       <c r="G126" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="H126" t="s">
         <v>9</v>
@@ -8474,7 +8477,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G127" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H127" t="s">
         <v>9</v>
@@ -8500,7 +8503,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G128" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H128" t="s">
         <v>9</v>
@@ -8526,7 +8529,7 @@
         <v>6.71663093566895</v>
       </c>
       <c r="G129" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="H129" t="s">
         <v>9</v>
@@ -8552,7 +8555,7 @@
         <v>6.48887014389038</v>
       </c>
       <c r="G130" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H130" t="s">
         <v>9</v>
@@ -8578,7 +8581,7 @@
         <v>6.24716377258301</v>
       </c>
       <c r="G131" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="H131" t="s">
         <v>9</v>
@@ -8604,7 +8607,7 @@
         <v>6.19603395462036</v>
       </c>
       <c r="G132" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="H132" t="s">
         <v>9</v>
@@ -8630,7 +8633,7 @@
         <v>6.40055418014526</v>
       </c>
       <c r="G133" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="H133" t="s">
         <v>9</v>
@@ -8656,7 +8659,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G134" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H134" t="s">
         <v>9</v>
@@ -8682,7 +8685,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G135" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H135" t="s">
         <v>9</v>
@@ -8734,7 +8737,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G137" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H137" t="s">
         <v>9</v>
@@ -8760,7 +8763,7 @@
         <v>7.11172723770142</v>
       </c>
       <c r="G138" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="H138" t="s">
         <v>9</v>
@@ -8786,7 +8789,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G139" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H139" t="s">
         <v>9</v>
@@ -8812,7 +8815,7 @@
         <v>7.29765510559082</v>
       </c>
       <c r="G140" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="H140" t="s">
         <v>9</v>
@@ -8838,7 +8841,7 @@
         <v>7.13496780395508</v>
       </c>
       <c r="G141" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H141" t="s">
         <v>9</v>
@@ -8864,7 +8867,7 @@
         <v>7.19539403915405</v>
       </c>
       <c r="G142" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H142" t="s">
         <v>9</v>
@@ -8942,7 +8945,7 @@
         <v>7.24187612533569</v>
       </c>
       <c r="G145" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="H145" t="s">
         <v>9</v>
@@ -9878,7 +9881,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G181" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H181" t="s">
         <v>9</v>
@@ -10112,7 +10115,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G190" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H190" t="s">
         <v>9</v>
@@ -10164,7 +10167,7 @@
         <v>6.22857093811035</v>
       </c>
       <c r="G192" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H192" t="s">
         <v>9</v>
@@ -10632,7 +10635,7 @@
         <v>6.60972309112549</v>
       </c>
       <c r="G210" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="H210" t="s">
         <v>9</v>
@@ -11906,7 +11909,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G259" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H259" t="s">
         <v>9</v>
@@ -11984,7 +11987,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G262" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="H262" t="s">
         <v>9</v>
@@ -12244,7 +12247,7 @@
         <v>6.87466907501221</v>
       </c>
       <c r="G272" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="H272" t="s">
         <v>9</v>
@@ -12348,7 +12351,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G276" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="H276" t="s">
         <v>9</v>
@@ -12530,7 +12533,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G283" t="s">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="H283" t="s">
         <v>9</v>
@@ -12556,7 +12559,7 @@
         <v>6.53535223007202</v>
       </c>
       <c r="G284" t="s">
-        <v>227</v>
+        <v>20</v>
       </c>
       <c r="H284" t="s">
         <v>9</v>
@@ -12608,7 +12611,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G286" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H286" t="s">
         <v>9</v>
@@ -12660,7 +12663,7 @@
         <v>6.81424283981323</v>
       </c>
       <c r="G288" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H288" t="s">
         <v>9</v>
@@ -12738,7 +12741,7 @@
         <v>6.95833683013916</v>
       </c>
       <c r="G291" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H291" t="s">
         <v>9</v>
@@ -12894,7 +12897,7 @@
         <v>6.8235387802124</v>
       </c>
       <c r="G297" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="H297" t="s">
         <v>9</v>
@@ -12920,7 +12923,7 @@
         <v>6.70268678665161</v>
       </c>
       <c r="G298" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H298" t="s">
         <v>9</v>
@@ -12972,7 +12975,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G300" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H300" t="s">
         <v>9</v>
@@ -13050,7 +13053,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G303" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H303" t="s">
         <v>9</v>
@@ -13076,7 +13079,7 @@
         <v>7.2232837677002</v>
       </c>
       <c r="G304" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H304" t="s">
         <v>9</v>
@@ -13206,7 +13209,7 @@
         <v>7.06989288330078</v>
       </c>
       <c r="G309" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H309" t="s">
         <v>9</v>
@@ -13232,7 +13235,7 @@
         <v>7.17680215835571</v>
       </c>
       <c r="G310" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H310" t="s">
         <v>9</v>
@@ -13284,7 +13287,7 @@
         <v>7.41850709915161</v>
       </c>
       <c r="G312" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H312" t="s">
         <v>9</v>
@@ -13310,7 +13313,7 @@
         <v>7.46963787078857</v>
       </c>
       <c r="G313" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H313" t="s">
         <v>9</v>
@@ -13362,7 +13365,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G315" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H315" t="s">
         <v>9</v>
@@ -13414,7 +13417,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G317" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H317" t="s">
         <v>9</v>
@@ -13440,7 +13443,7 @@
         <v>7.60443496704102</v>
       </c>
       <c r="G318" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H318" t="s">
         <v>9</v>
@@ -13466,7 +13469,7 @@
         <v>7.75782489776611</v>
       </c>
       <c r="G319" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H319" t="s">
         <v>9</v>
@@ -13492,7 +13495,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G320" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H320" t="s">
         <v>9</v>
@@ -13544,7 +13547,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G322" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H322" t="s">
         <v>9</v>
@@ -13570,7 +13573,7 @@
         <v>7.59978723526001</v>
       </c>
       <c r="G323" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H323" t="s">
         <v>9</v>
@@ -13596,7 +13599,7 @@
         <v>7.59513902664185</v>
       </c>
       <c r="G324" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H324" t="s">
         <v>9</v>
@@ -13700,7 +13703,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G328" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H328" t="s">
         <v>9</v>
@@ -13726,7 +13729,7 @@
         <v>7.46498918533325</v>
       </c>
       <c r="G329" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H329" t="s">
         <v>9</v>
@@ -13778,7 +13781,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G331" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H331" t="s">
         <v>9</v>
@@ -13804,7 +13807,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G332" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H332" t="s">
         <v>9</v>
@@ -13830,7 +13833,7 @@
         <v>7.34413623809814</v>
       </c>
       <c r="G333" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H333" t="s">
         <v>9</v>
@@ -13856,7 +13859,7 @@
         <v>7.311598777771</v>
       </c>
       <c r="G334" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H334" t="s">
         <v>9</v>
@@ -13882,7 +13885,7 @@
         <v>7.20469093322754</v>
       </c>
       <c r="G335" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H335" t="s">
         <v>9</v>
@@ -13908,7 +13911,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G336" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H336" t="s">
         <v>9</v>
@@ -13934,7 +13937,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G337" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H337" t="s">
         <v>9</v>
@@ -13960,7 +13963,7 @@
         <v>7.53471183776855</v>
       </c>
       <c r="G338" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H338" t="s">
         <v>9</v>
@@ -13986,7 +13989,7 @@
         <v>7.66486120223999</v>
       </c>
       <c r="G339" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H339" t="s">
         <v>9</v>
@@ -14012,7 +14015,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G340" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H340" t="s">
         <v>9</v>
@@ -14038,7 +14041,7 @@
         <v>7.6973991394043</v>
       </c>
       <c r="G341" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H341" t="s">
         <v>9</v>
@@ -14064,7 +14067,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G342" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H342" t="s">
         <v>9</v>
@@ -14090,7 +14093,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G343" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H343" t="s">
         <v>9</v>
@@ -14116,7 +14119,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G344" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H344" t="s">
         <v>9</v>
@@ -14142,7 +14145,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G345" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H345" t="s">
         <v>9</v>
@@ -14168,7 +14171,7 @@
         <v>7.95769691467285</v>
       </c>
       <c r="G346" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H346" t="s">
         <v>9</v>
@@ -14194,7 +14197,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G347" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H347" t="s">
         <v>9</v>
@@ -14220,7 +14223,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G348" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H348" t="s">
         <v>9</v>
@@ -14246,7 +14249,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G349" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H349" t="s">
         <v>9</v>
@@ -14272,7 +14275,7 @@
         <v>8.16686630249023</v>
       </c>
       <c r="G350" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H350" t="s">
         <v>9</v>
@@ -14298,7 +14301,7 @@
         <v>8.11573600769043</v>
       </c>
       <c r="G351" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H351" t="s">
         <v>9</v>
@@ -14324,7 +14327,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G352" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H352" t="s">
         <v>9</v>
@@ -14350,7 +14353,7 @@
         <v>7.8554368019104</v>
       </c>
       <c r="G353" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H353" t="s">
         <v>9</v>
@@ -14376,7 +14379,7 @@
         <v>7.79965877532959</v>
       </c>
       <c r="G354" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H354" t="s">
         <v>9</v>
@@ -14402,7 +14405,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G355" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H355" t="s">
         <v>9</v>
@@ -14428,7 +14431,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G356" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H356" t="s">
         <v>9</v>
@@ -14454,7 +14457,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G357" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H357" t="s">
         <v>9</v>
@@ -14480,7 +14483,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G358" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H358" t="s">
         <v>9</v>
@@ -14506,7 +14509,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G359" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H359" t="s">
         <v>9</v>
@@ -14532,7 +14535,7 @@
         <v>7.67880582809448</v>
       </c>
       <c r="G360" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H360" t="s">
         <v>9</v>
@@ -14558,7 +14561,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G361" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H361" t="s">
         <v>9</v>
@@ -14584,7 +14587,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G362" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H362" t="s">
         <v>9</v>
@@ -14610,7 +14613,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G363" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H363" t="s">
         <v>9</v>
@@ -14636,7 +14639,7 @@
         <v>7.83684396743774</v>
       </c>
       <c r="G364" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H364" t="s">
         <v>9</v>
@@ -14662,7 +14665,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G365" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H365" t="s">
         <v>9</v>
@@ -14688,7 +14691,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G366" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H366" t="s">
         <v>9</v>
@@ -14714,7 +14717,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G367" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H367" t="s">
         <v>9</v>
@@ -14740,7 +14743,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G368" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H368" t="s">
         <v>9</v>
@@ -14766,7 +14769,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G369" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H369" t="s">
         <v>9</v>
@@ -14792,7 +14795,7 @@
         <v>7.69275093078613</v>
       </c>
       <c r="G370" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H370" t="s">
         <v>9</v>
@@ -14818,7 +14821,7 @@
         <v>7.72528791427612</v>
       </c>
       <c r="G371" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H371" t="s">
         <v>9</v>
@@ -14844,7 +14847,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G372" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H372" t="s">
         <v>9</v>
@@ -14870,7 +14873,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G373" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H373" t="s">
         <v>9</v>
@@ -14896,7 +14899,7 @@
         <v>7.59048986434937</v>
       </c>
       <c r="G374" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H374" t="s">
         <v>9</v>
@@ -14922,7 +14925,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G375" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H375" t="s">
         <v>9</v>
@@ -14948,7 +14951,7 @@
         <v>7.50217485427856</v>
       </c>
       <c r="G376" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H376" t="s">
         <v>9</v>
@@ -14974,7 +14977,7 @@
         <v>7.46034097671509</v>
       </c>
       <c r="G377" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H377" t="s">
         <v>9</v>
@@ -15000,7 +15003,7 @@
         <v>7.4278039932251</v>
       </c>
       <c r="G378" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H378" t="s">
         <v>9</v>
@@ -15026,7 +15029,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G379" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H379" t="s">
         <v>9</v>
@@ -15052,7 +15055,7 @@
         <v>7.48358201980591</v>
       </c>
       <c r="G380" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H380" t="s">
         <v>9</v>
@@ -15078,7 +15081,7 @@
         <v>7.39991521835327</v>
       </c>
       <c r="G381" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H381" t="s">
         <v>9</v>
@@ -15104,7 +15107,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G382" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H382" t="s">
         <v>9</v>
@@ -15130,7 +15133,7 @@
         <v>7.0884861946106</v>
       </c>
       <c r="G383" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H383" t="s">
         <v>9</v>
@@ -15156,7 +15159,7 @@
         <v>7.16750478744507</v>
       </c>
       <c r="G384" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H384" t="s">
         <v>9</v>
@@ -15182,7 +15185,7 @@
         <v>7.21863508224487</v>
       </c>
       <c r="G385" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H385" t="s">
         <v>9</v>
@@ -15208,7 +15211,7 @@
         <v>7.35343313217163</v>
       </c>
       <c r="G386" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H386" t="s">
         <v>9</v>
@@ -15234,7 +15237,7 @@
         <v>7.38132190704346</v>
       </c>
       <c r="G387" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H387" t="s">
         <v>9</v>
@@ -15260,7 +15263,7 @@
         <v>7.25117301940918</v>
       </c>
       <c r="G388" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H388" t="s">
         <v>9</v>
@@ -15286,7 +15289,7 @@
         <v>7.39061784744263</v>
       </c>
       <c r="G389" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H389" t="s">
         <v>9</v>
@@ -15312,7 +15315,7 @@
         <v>7.53006410598755</v>
       </c>
       <c r="G390" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H390" t="s">
         <v>9</v>
@@ -15338,7 +15341,7 @@
         <v>7.59048986434937</v>
       </c>
       <c r="G391" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H391" t="s">
         <v>9</v>
@@ -15364,7 +15367,7 @@
         <v>7.55330514907837</v>
       </c>
       <c r="G392" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H392" t="s">
         <v>9</v>
@@ -15390,7 +15393,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G393" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H393" t="s">
         <v>9</v>
@@ -15416,7 +15419,7 @@
         <v>7.72064018249512</v>
       </c>
       <c r="G394" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H394" t="s">
         <v>9</v>
@@ -15442,7 +15445,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G395" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H395" t="s">
         <v>9</v>
@@ -15468,7 +15471,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G396" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H396" t="s">
         <v>9</v>
@@ -15494,7 +15497,7 @@
         <v>7.71599102020264</v>
       </c>
       <c r="G397" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H397" t="s">
         <v>9</v>
@@ -15520,7 +15523,7 @@
         <v>7.7671217918396</v>
       </c>
       <c r="G398" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H398" t="s">
         <v>9</v>
@@ -15546,7 +15549,7 @@
         <v>7.72993612289429</v>
       </c>
       <c r="G399" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H399" t="s">
         <v>9</v>
@@ -15572,7 +15575,7 @@
         <v>7.79036283493042</v>
       </c>
       <c r="G400" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H400" t="s">
         <v>9</v>
@@ -15598,7 +15601,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G401" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H401" t="s">
         <v>9</v>
@@ -15624,7 +15627,7 @@
         <v>7.74388122558594</v>
       </c>
       <c r="G402" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H402" t="s">
         <v>9</v>
@@ -15650,7 +15653,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G403" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H403" t="s">
         <v>9</v>
@@ -15676,7 +15679,7 @@
         <v>7.66021299362183</v>
       </c>
       <c r="G404" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H404" t="s">
         <v>9</v>
@@ -15702,7 +15705,7 @@
         <v>7.66950988769531</v>
       </c>
       <c r="G405" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H405" t="s">
         <v>9</v>
@@ -15728,7 +15731,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G406" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H406" t="s">
         <v>9</v>
@@ -15754,7 +15757,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G407" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H407" t="s">
         <v>9</v>
@@ -15780,7 +15783,7 @@
         <v>7.64626884460449</v>
       </c>
       <c r="G408" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H408" t="s">
         <v>9</v>
@@ -15806,7 +15809,7 @@
         <v>7.77177000045776</v>
       </c>
       <c r="G409" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H409" t="s">
         <v>9</v>
@@ -15832,7 +15835,7 @@
         <v>7.82289981842041</v>
       </c>
       <c r="G410" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H410" t="s">
         <v>9</v>
@@ -15858,7 +15861,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G411" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H411" t="s">
         <v>9</v>
@@ -15884,7 +15887,7 @@
         <v>7.89262294769287</v>
       </c>
       <c r="G412" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H412" t="s">
         <v>9</v>
@@ -15910,7 +15913,7 @@
         <v>7.81360292434692</v>
       </c>
       <c r="G413" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H413" t="s">
         <v>9</v>
@@ -15936,7 +15939,7 @@
         <v>7.70669507980347</v>
       </c>
       <c r="G414" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H414" t="s">
         <v>9</v>
@@ -15962,7 +15965,7 @@
         <v>7.79501104354858</v>
       </c>
       <c r="G415" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H415" t="s">
         <v>9</v>
@@ -15988,7 +15991,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G416" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H416" t="s">
         <v>9</v>
@@ -16014,7 +16017,7 @@
         <v>8.01347637176514</v>
       </c>
       <c r="G417" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H417" t="s">
         <v>9</v>
@@ -16040,7 +16043,7 @@
         <v>7.99023485183716</v>
       </c>
       <c r="G418" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H418" t="s">
         <v>9</v>
@@ -16066,7 +16069,7 @@
         <v>7.93445587158203</v>
       </c>
       <c r="G419" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H419" t="s">
         <v>9</v>
@@ -16092,7 +16095,7 @@
         <v>7.94375276565552</v>
       </c>
       <c r="G420" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H420" t="s">
         <v>9</v>
@@ -16118,7 +16121,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G421" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H421" t="s">
         <v>9</v>
@@ -16144,7 +16147,7 @@
         <v>7.99488306045532</v>
       </c>
       <c r="G422" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H422" t="s">
         <v>9</v>
@@ -16170,7 +16173,7 @@
         <v>7.96699380874634</v>
       </c>
       <c r="G423" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H423" t="s">
         <v>9</v>
@@ -16196,7 +16199,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G424" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H424" t="s">
         <v>9</v>
@@ -16222,7 +16225,7 @@
         <v>7.86008501052856</v>
       </c>
       <c r="G425" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H425" t="s">
         <v>9</v>
@@ -16248,7 +16251,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G426" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H426" t="s">
         <v>9</v>
@@ -16274,7 +16277,7 @@
         <v>7.78106594085693</v>
       </c>
       <c r="G427" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H427" t="s">
         <v>9</v>
@@ -16300,7 +16303,7 @@
         <v>7.89727115631104</v>
       </c>
       <c r="G428" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H428" t="s">
         <v>9</v>
@@ -16326,7 +16329,7 @@
         <v>7.87867784500122</v>
       </c>
       <c r="G429" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H429" t="s">
         <v>9</v>
@@ -16352,7 +16355,7 @@
         <v>7.90191888809204</v>
       </c>
       <c r="G430" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H430" t="s">
         <v>9</v>
@@ -16378,7 +16381,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G431" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H431" t="s">
         <v>9</v>
@@ -16404,7 +16407,7 @@
         <v>7.80895519256592</v>
       </c>
       <c r="G432" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H432" t="s">
         <v>9</v>
@@ -16430,7 +16433,7 @@
         <v>7.84149312973022</v>
       </c>
       <c r="G433" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H433" t="s">
         <v>9</v>
@@ -16456,7 +16459,7 @@
         <v>7.92051219940186</v>
       </c>
       <c r="G434" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H434" t="s">
         <v>9</v>
@@ -16482,7 +16485,7 @@
         <v>8.03206825256348</v>
       </c>
       <c r="G435" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H435" t="s">
         <v>9</v>
@@ -16508,7 +16511,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G436" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H436" t="s">
         <v>9</v>
@@ -16534,7 +16537,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G437" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H437" t="s">
         <v>9</v>
@@ -16560,7 +16563,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G438" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H438" t="s">
         <v>9</v>
@@ -16586,7 +16589,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G439" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H439" t="s">
         <v>9</v>
@@ -16612,7 +16615,7 @@
         <v>8.19010734558105</v>
       </c>
       <c r="G440" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H440" t="s">
         <v>9</v>
@@ -16638,7 +16641,7 @@
         <v>8.12503242492676</v>
       </c>
       <c r="G441" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H441" t="s">
         <v>9</v>
@@ -16664,7 +16667,7 @@
         <v>8.08784675598145</v>
       </c>
       <c r="G442" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H442" t="s">
         <v>9</v>
@@ -16690,7 +16693,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G443" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H443" t="s">
         <v>9</v>
@@ -16716,7 +16719,7 @@
         <v>8.10643863677979</v>
       </c>
       <c r="G444" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H444" t="s">
         <v>9</v>
@@ -16742,7 +16745,7 @@
         <v>8.06460571289062</v>
       </c>
       <c r="G445" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H445" t="s">
         <v>9</v>
@@ -16768,7 +16771,7 @@
         <v>8.14362525939941</v>
       </c>
       <c r="G446" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H446" t="s">
         <v>9</v>
@@ -16794,7 +16797,7 @@
         <v>8.12038421630859</v>
       </c>
       <c r="G447" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H447" t="s">
         <v>9</v>
@@ -16820,7 +16823,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G448" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H448" t="s">
         <v>9</v>
@@ -16846,7 +16849,7 @@
         <v>8.20869922637939</v>
       </c>
       <c r="G449" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H449" t="s">
         <v>9</v>
@@ -16872,7 +16875,7 @@
         <v>8.20405101776123</v>
       </c>
       <c r="G450" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H450" t="s">
         <v>9</v>
@@ -16898,7 +16901,7 @@
         <v>8.22729206085205</v>
       </c>
       <c r="G451" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H451" t="s">
         <v>9</v>
@@ -16924,7 +16927,7 @@
         <v>8.18080997467041</v>
       </c>
       <c r="G452" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H452" t="s">
         <v>9</v>
@@ -16950,7 +16953,7 @@
         <v>8.05066108703613</v>
       </c>
       <c r="G453" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H453" t="s">
         <v>9</v>
@@ -16976,7 +16979,7 @@
         <v>8.07390213012695</v>
       </c>
       <c r="G454" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H454" t="s">
         <v>9</v>
@@ -17002,7 +17005,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G455" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H455" t="s">
         <v>9</v>
@@ -17028,7 +17031,7 @@
         <v>8.19940280914307</v>
       </c>
       <c r="G456" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H456" t="s">
         <v>9</v>
@@ -17054,7 +17057,7 @@
         <v>8.36673831939697</v>
       </c>
       <c r="G457" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H457" t="s">
         <v>9</v>
@@ -17080,7 +17083,7 @@
         <v>8.50618267059326</v>
       </c>
       <c r="G458" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H458" t="s">
         <v>9</v>
@@ -17106,7 +17109,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G459" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H459" t="s">
         <v>9</v>
@@ -17132,7 +17135,7 @@
         <v>8.83155727386475</v>
       </c>
       <c r="G460" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H460" t="s">
         <v>9</v>
@@ -17158,7 +17161,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G461" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H461" t="s">
         <v>9</v>
@@ -17184,7 +17187,7 @@
         <v>8.5526647567749</v>
       </c>
       <c r="G462" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H462" t="s">
         <v>9</v>
@@ -17210,7 +17213,7 @@
         <v>8.54801654815674</v>
       </c>
       <c r="G463" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H463" t="s">
         <v>9</v>
@@ -17236,7 +17239,7 @@
         <v>8.69211101531982</v>
       </c>
       <c r="G464" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H464" t="s">
         <v>9</v>
@@ -17262,7 +17265,7 @@
         <v>8.74788856506348</v>
       </c>
       <c r="G465" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H465" t="s">
         <v>9</v>
@@ -17288,7 +17291,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G466" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H466" t="s">
         <v>9</v>
@@ -17314,7 +17317,7 @@
         <v>8.60379505157471</v>
       </c>
       <c r="G467" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H467" t="s">
         <v>9</v>
@@ -17340,7 +17343,7 @@
         <v>8.72000026702881</v>
       </c>
       <c r="G468" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H468" t="s">
         <v>9</v>
@@ -17366,7 +17369,7 @@
         <v>8.98959541320801</v>
       </c>
       <c r="G469" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H469" t="s">
         <v>9</v>
@@ -17392,7 +17395,7 @@
         <v>9.22665309906006</v>
       </c>
       <c r="G470" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H470" t="s">
         <v>9</v>
@@ -17418,7 +17421,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G471" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H471" t="s">
         <v>9</v>
@@ -17444,7 +17447,7 @@
         <v>9.696120262146</v>
       </c>
       <c r="G472" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H472" t="s">
         <v>9</v>
@@ -17470,7 +17473,7 @@
         <v>9.67752742767334</v>
       </c>
       <c r="G473" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H473" t="s">
         <v>9</v>
@@ -17496,7 +17499,7 @@
         <v>9.55667400360107</v>
       </c>
       <c r="G474" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H474" t="s">
         <v>9</v>
@@ -17522,7 +17525,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G475" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H475" t="s">
         <v>9</v>
@@ -17548,7 +17551,7 @@
         <v>9.62174892425537</v>
       </c>
       <c r="G476" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H476" t="s">
         <v>9</v>
@@ -17574,7 +17577,7 @@
         <v>9.43582057952881</v>
       </c>
       <c r="G477" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H477" t="s">
         <v>9</v>
@@ -17600,7 +17603,7 @@
         <v>9.57526683807373</v>
       </c>
       <c r="G478" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H478" t="s">
         <v>9</v>
@@ -17626,7 +17629,7 @@
         <v>9.34285736083984</v>
       </c>
       <c r="G479" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H479" t="s">
         <v>9</v>
@@ -17652,7 +17655,7 @@
         <v>9.2080602645874</v>
       </c>
       <c r="G480" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H480" t="s">
         <v>9</v>
@@ -17678,7 +17681,7 @@
         <v>9.38933944702148</v>
       </c>
       <c r="G481" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H481" t="s">
         <v>9</v>
@@ -17704,7 +17707,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G482" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H482" t="s">
         <v>9</v>
@@ -17730,7 +17733,7 @@
         <v>9.91923332214355</v>
       </c>
       <c r="G483" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H483" t="s">
         <v>9</v>
@@ -17756,7 +17759,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G484" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H484" t="s">
         <v>9</v>
@@ -17782,7 +17785,7 @@
         <v>9.65893363952637</v>
       </c>
       <c r="G485" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H485" t="s">
         <v>9</v>
@@ -17808,7 +17811,7 @@
         <v>10.0029001235962</v>
       </c>
       <c r="G486" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H486" t="s">
         <v>9</v>
@@ -17834,7 +17837,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G487" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H487" t="s">
         <v>9</v>
@@ -17860,7 +17863,7 @@
         <v>9.90063953399658</v>
       </c>
       <c r="G488" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H488" t="s">
         <v>9</v>
@@ -17886,7 +17889,7 @@
         <v>10.0586776733398</v>
       </c>
       <c r="G489" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H489" t="s">
         <v>9</v>
@@ -17912,7 +17915,7 @@
         <v>10.1144561767578</v>
       </c>
       <c r="G490" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H490" t="s">
         <v>9</v>
@@ -17938,7 +17941,7 @@
         <v>10.0307893753052</v>
       </c>
       <c r="G491" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H491" t="s">
         <v>9</v>
@@ -17964,7 +17967,7 @@
         <v>10.0121955871582</v>
       </c>
       <c r="G492" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H492" t="s">
         <v>9</v>
@@ -17990,7 +17993,7 @@
         <v>9.76119422912598</v>
       </c>
       <c r="G493" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H493" t="s">
         <v>9</v>
@@ -18016,7 +18019,7 @@
         <v>9.83556461334229</v>
       </c>
       <c r="G494" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H494" t="s">
         <v>9</v>
@@ -18042,7 +18045,7 @@
         <v>9.98430728912354</v>
       </c>
       <c r="G495" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H495" t="s">
         <v>9</v>
@@ -18068,7 +18071,7 @@
         <v>9.93782520294189</v>
       </c>
       <c r="G496" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H496" t="s">
         <v>9</v>
@@ -18094,7 +18097,7 @@
         <v>10.0772714614868</v>
       </c>
       <c r="G497" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H497" t="s">
         <v>9</v>
@@ -18120,7 +18123,7 @@
         <v>10.318977355957</v>
       </c>
       <c r="G498" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H498" t="s">
         <v>9</v>
@@ -18146,7 +18149,7 @@
         <v>10.3003835678101</v>
       </c>
       <c r="G499" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H499" t="s">
         <v>9</v>
@@ -18172,7 +18175,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G500" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H500" t="s">
         <v>9</v>
@@ -18198,7 +18201,7 @@
         <v>10.504903793335</v>
       </c>
       <c r="G501" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H501" t="s">
         <v>9</v>
@@ -18224,7 +18227,7 @@
         <v>10.411940574646</v>
       </c>
       <c r="G502" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H502" t="s">
         <v>9</v>
@@ -18250,7 +18253,7 @@
         <v>10.1330490112305</v>
       </c>
       <c r="G503" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H503" t="s">
         <v>9</v>
@@ -18276,7 +18279,7 @@
         <v>9.49159908294678</v>
       </c>
       <c r="G504" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H504" t="s">
         <v>9</v>
@@ -18302,7 +18305,7 @@
         <v>9.11044788360596</v>
       </c>
       <c r="G505" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H505" t="s">
         <v>9</v>
@@ -18328,7 +18331,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G506" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H506" t="s">
         <v>9</v>
@@ -18354,7 +18357,7 @@
         <v>9.08255863189697</v>
       </c>
       <c r="G507" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H507" t="s">
         <v>9</v>
@@ -18380,7 +18383,7 @@
         <v>8.88268661499023</v>
       </c>
       <c r="G508" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H508" t="s">
         <v>9</v>
@@ -18406,7 +18409,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G509" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H509" t="s">
         <v>9</v>
@@ -18432,7 +18435,7 @@
         <v>9.09650325775146</v>
       </c>
       <c r="G510" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H510" t="s">
         <v>9</v>
@@ -18458,7 +18461,7 @@
         <v>8.96170616149902</v>
       </c>
       <c r="G511" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H511" t="s">
         <v>9</v>
@@ -18484,7 +18487,7 @@
         <v>8.95240879058838</v>
       </c>
       <c r="G512" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H512" t="s">
         <v>9</v>
@@ -18510,7 +18513,7 @@
         <v>9.01748371124268</v>
       </c>
       <c r="G513" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H513" t="s">
         <v>9</v>
@@ -18536,7 +18539,7 @@
         <v>9.1569299697876</v>
       </c>
       <c r="G514" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H514" t="s">
         <v>9</v>
@@ -18562,7 +18565,7 @@
         <v>9.16622638702393</v>
       </c>
       <c r="G515" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H515" t="s">
         <v>9</v>
@@ -18588,7 +18591,7 @@
         <v>9.24989414215088</v>
       </c>
       <c r="G516" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H516" t="s">
         <v>9</v>
@@ -18614,7 +18617,7 @@
         <v>9.31496810913086</v>
       </c>
       <c r="G517" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H517" t="s">
         <v>9</v>
@@ -18640,7 +18643,7 @@
         <v>9.26848602294922</v>
       </c>
       <c r="G518" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H518" t="s">
         <v>9</v>
@@ -18666,7 +18669,7 @@
         <v>9.00818824768066</v>
       </c>
       <c r="G519" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H519" t="s">
         <v>9</v>
@@ -18692,7 +18695,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G520" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H520" t="s">
         <v>9</v>
@@ -18718,7 +18721,7 @@
         <v>9.06396579742432</v>
       </c>
       <c r="G521" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H521" t="s">
         <v>9</v>
@@ -18744,7 +18747,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G522" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H522" t="s">
         <v>9</v>
@@ -18770,7 +18773,7 @@
         <v>8.8873348236084</v>
       </c>
       <c r="G523" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H523" t="s">
         <v>9</v>
@@ -18796,7 +18799,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G524" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H524" t="s">
         <v>9</v>
@@ -18822,7 +18825,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G525" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H525" t="s">
         <v>9</v>
@@ -18848,7 +18851,7 @@
         <v>8.97100162506104</v>
       </c>
       <c r="G526" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H526" t="s">
         <v>9</v>
@@ -18874,7 +18877,7 @@
         <v>8.99889087677002</v>
       </c>
       <c r="G527" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H527" t="s">
         <v>9</v>
@@ -18900,7 +18903,7 @@
         <v>8.90592765808105</v>
       </c>
       <c r="G528" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H528" t="s">
         <v>9</v>
@@ -18926,7 +18929,7 @@
         <v>8.87803840637207</v>
       </c>
       <c r="G529" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H529" t="s">
         <v>9</v>
@@ -18952,7 +18955,7 @@
         <v>8.92451953887939</v>
       </c>
       <c r="G530" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H530" t="s">
         <v>9</v>
@@ -18978,7 +18981,7 @@
         <v>8.85014915466309</v>
       </c>
       <c r="G531" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H531" t="s">
         <v>9</v>
@@ -19004,7 +19007,7 @@
         <v>8.60844421386719</v>
       </c>
       <c r="G532" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H532" t="s">
         <v>9</v>
@@ -19030,7 +19033,7 @@
         <v>8.73859310150146</v>
       </c>
       <c r="G533" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H533" t="s">
         <v>9</v>
@@ -19056,7 +19059,7 @@
         <v>8.53407287597656</v>
       </c>
       <c r="G534" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H534" t="s">
         <v>9</v>
@@ -19082,7 +19085,7 @@
         <v>8.34814453125</v>
       </c>
       <c r="G535" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H535" t="s">
         <v>9</v>
@@ -19108,7 +19111,7 @@
         <v>8.15292072296143</v>
       </c>
       <c r="G536" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H536" t="s">
         <v>9</v>
@@ -19134,7 +19137,7 @@
         <v>8.05995655059814</v>
       </c>
       <c r="G537" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H537" t="s">
         <v>9</v>
@@ -19160,7 +19163,7 @@
         <v>8.30166339874268</v>
       </c>
       <c r="G538" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H538" t="s">
         <v>9</v>
@@ -19186,7 +19189,7 @@
         <v>7.87403011322021</v>
       </c>
       <c r="G539" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H539" t="s">
         <v>9</v>
@@ -19212,7 +19215,7 @@
         <v>7.65091705322266</v>
       </c>
       <c r="G540" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H540" t="s">
         <v>9</v>
@@ -19238,7 +19241,7 @@
         <v>7.62302780151367</v>
       </c>
       <c r="G541" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H541" t="s">
         <v>9</v>
@@ -19264,7 +19267,7 @@
         <v>7.28835821151733</v>
       </c>
       <c r="G542" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H542" t="s">
         <v>9</v>
@@ -19290,7 +19293,7 @@
         <v>7.68810176849365</v>
       </c>
       <c r="G543" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H543" t="s">
         <v>9</v>
@@ -19316,7 +19319,7 @@
         <v>7.57654619216919</v>
       </c>
       <c r="G544" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H544" t="s">
         <v>9</v>
@@ -19342,7 +19345,7 @@
         <v>7.8182520866394</v>
       </c>
       <c r="G545" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H545" t="s">
         <v>9</v>
@@ -19368,7 +19371,7 @@
         <v>7.61373090744019</v>
       </c>
       <c r="G546" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H546" t="s">
         <v>9</v>
@@ -19394,7 +19397,7 @@
         <v>7.73458385467529</v>
       </c>
       <c r="G547" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H547" t="s">
         <v>9</v>
@@ -19420,7 +19423,7 @@
         <v>7.58584213256836</v>
       </c>
       <c r="G548" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H548" t="s">
         <v>9</v>
@@ -19446,7 +19449,7 @@
         <v>8.0413646697998</v>
       </c>
       <c r="G549" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H549" t="s">
         <v>9</v>
@@ -19472,7 +19475,7 @@
         <v>7.64162015914917</v>
       </c>
       <c r="G550" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H550" t="s">
         <v>9</v>
@@ -19498,7 +19501,7 @@
         <v>7.43709993362427</v>
       </c>
       <c r="G551" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H551" t="s">
         <v>9</v>
@@ -19524,7 +19527,7 @@
         <v>7.49566698074341</v>
       </c>
       <c r="G552" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H552" t="s">
         <v>9</v>
@@ -19550,7 +19553,7 @@
         <v>7.36086988449097</v>
       </c>
       <c r="G553" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H553" t="s">
         <v>9</v>
@@ -19576,7 +19579,7 @@
         <v>7.17308282852173</v>
       </c>
       <c r="G554" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H554" t="s">
         <v>9</v>
@@ -19602,7 +19605,7 @@
         <v>7.00017118453979</v>
       </c>
       <c r="G555" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H555" t="s">
         <v>9</v>
@@ -19628,7 +19631,7 @@
         <v>6.98622608184814</v>
       </c>
       <c r="G556" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H556" t="s">
         <v>9</v>
@@ -19654,7 +19657,7 @@
         <v>7.08383798599243</v>
       </c>
       <c r="G557" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H557" t="s">
         <v>9</v>
@@ -19680,7 +19683,7 @@
         <v>7.29300594329834</v>
       </c>
       <c r="G558" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H558" t="s">
         <v>9</v>
@@ -19706,7 +19709,7 @@
         <v>7.298583984375</v>
       </c>
       <c r="G559" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H559" t="s">
         <v>9</v>
@@ -19732,7 +19735,7 @@
         <v>7.12102317810059</v>
       </c>
       <c r="G560" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H560" t="s">
         <v>9</v>
@@ -19758,7 +19761,7 @@
         <v>7.03177785873413</v>
       </c>
       <c r="G561" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H561" t="s">
         <v>9</v>
@@ -19784,7 +19787,7 @@
         <v>7.05501890182495</v>
       </c>
       <c r="G562" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H562" t="s">
         <v>9</v>
@@ -19810,7 +19813,7 @@
         <v>6.89791011810303</v>
       </c>
       <c r="G563" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H563" t="s">
         <v>9</v>
@@ -19836,7 +19839,7 @@
         <v>6.82911682128906</v>
       </c>
       <c r="G564" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H564" t="s">
         <v>9</v>
@@ -19862,7 +19865,7 @@
         <v>6.72127914428711</v>
       </c>
       <c r="G565" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H565" t="s">
         <v>9</v>
@@ -19888,7 +19891,7 @@
         <v>7.01225614547729</v>
       </c>
       <c r="G566" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H566" t="s">
         <v>9</v>
@@ -19914,7 +19917,7 @@
         <v>6.98064804077148</v>
       </c>
       <c r="G567" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H567" t="s">
         <v>9</v>
@@ -19940,7 +19943,7 @@
         <v>6.94439220428467</v>
       </c>
       <c r="G568" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H568" t="s">
         <v>9</v>
@@ -19966,7 +19969,7 @@
         <v>6.71291303634644</v>
       </c>
       <c r="G569" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H569" t="s">
         <v>9</v>
@@ -19992,7 +19995,7 @@
         <v>6.55394506454468</v>
       </c>
       <c r="G570" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H570" t="s">
         <v>9</v>
@@ -20018,7 +20021,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G571" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H571" t="s">
         <v>9</v>
@@ -20044,7 +20047,7 @@
         <v>7.27699995040894</v>
       </c>
       <c r="G572" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H572" t="s">
         <v>9</v>
@@ -20070,7 +20073,7 @@
         <v>7.97800016403198</v>
       </c>
       <c r="G573" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H573" t="s">
         <v>9</v>
@@ -20096,7 +20099,7 @@
         <v>7.58799982070923</v>
       </c>
       <c r="G574" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H574" t="s">
         <v>9</v>
@@ -20122,7 +20125,7 @@
         <v>7.75</v>
       </c>
       <c r="G575" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H575" t="s">
         <v>9</v>
@@ -20148,7 +20151,7 @@
         <v>8.04199981689453</v>
       </c>
       <c r="G576" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H576" t="s">
         <v>9</v>
@@ -20174,7 +20177,7 @@
         <v>8.35999965667725</v>
       </c>
       <c r="G577" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H577" t="s">
         <v>9</v>
@@ -20200,7 +20203,7 @@
         <v>8.25899982452393</v>
       </c>
       <c r="G578" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H578" t="s">
         <v>9</v>
@@ -20226,7 +20229,7 @@
         <v>8.09500026702881</v>
       </c>
       <c r="G579" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H579" t="s">
         <v>9</v>
@@ -20252,7 +20255,7 @@
         <v>7.83699989318848</v>
       </c>
       <c r="G580" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H580" t="s">
         <v>9</v>
@@ -20278,7 +20281,7 @@
         <v>7.76999998092651</v>
       </c>
       <c r="G581" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H581" t="s">
         <v>9</v>
@@ -20304,7 +20307,7 @@
         <v>7.89900016784668</v>
       </c>
       <c r="G582" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H582" t="s">
         <v>9</v>
@@ -20330,7 +20333,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G583" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H583" t="s">
         <v>9</v>
@@ -20356,7 +20359,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G584" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H584" t="s">
         <v>9</v>
@@ -20382,7 +20385,7 @@
         <v>7.86700010299683</v>
       </c>
       <c r="G585" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H585" t="s">
         <v>9</v>
@@ -20408,7 +20411,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G586" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H586" t="s">
         <v>9</v>
@@ -20434,7 +20437,7 @@
         <v>7.84200000762939</v>
       </c>
       <c r="G587" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H587" t="s">
         <v>9</v>
@@ -20460,7 +20463,7 @@
         <v>7.85799980163574</v>
       </c>
       <c r="G588" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H588" t="s">
         <v>9</v>
@@ -20486,7 +20489,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G589" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H589" t="s">
         <v>9</v>
@@ -20512,7 +20515,7 @@
         <v>7.94999980926514</v>
       </c>
       <c r="G590" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H590" t="s">
         <v>9</v>
@@ -20538,7 +20541,7 @@
         <v>7.80000019073486</v>
       </c>
       <c r="G591" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H591" t="s">
         <v>9</v>
@@ -20564,7 +20567,7 @@
         <v>7.71600008010864</v>
       </c>
       <c r="G592" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H592" t="s">
         <v>9</v>
@@ -20590,7 +20593,7 @@
         <v>7.70100021362305</v>
       </c>
       <c r="G593" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H593" t="s">
         <v>9</v>
@@ -20616,7 +20619,7 @@
         <v>7.76300001144409</v>
       </c>
       <c r="G594" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H594" t="s">
         <v>9</v>
@@ -20642,7 +20645,7 @@
         <v>7.85699987411499</v>
       </c>
       <c r="G595" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H595" t="s">
         <v>9</v>
@@ -20668,7 +20671,7 @@
         <v>7.88000011444092</v>
       </c>
       <c r="G596" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H596" t="s">
         <v>9</v>
@@ -20694,7 +20697,7 @@
         <v>7.84999990463257</v>
       </c>
       <c r="G597" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H597" t="s">
         <v>9</v>
@@ -20720,7 +20723,7 @@
         <v>8</v>
       </c>
       <c r="G598" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H598" t="s">
         <v>9</v>
@@ -20746,7 +20749,7 @@
         <v>7.90999984741211</v>
       </c>
       <c r="G599" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H599" t="s">
         <v>9</v>
@@ -20772,7 +20775,7 @@
         <v>7.84000015258789</v>
       </c>
       <c r="G600" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H600" t="s">
         <v>9</v>
@@ -20798,7 +20801,7 @@
         <v>7.92600011825562</v>
       </c>
       <c r="G601" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H601" t="s">
         <v>9</v>
@@ -20824,7 +20827,7 @@
         <v>8.19999980926514</v>
       </c>
       <c r="G602" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H602" t="s">
         <v>9</v>
@@ -20850,7 +20853,7 @@
         <v>8.03800010681152</v>
       </c>
       <c r="G603" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H603" t="s">
         <v>9</v>
@@ -20876,7 +20879,7 @@
         <v>8</v>
       </c>
       <c r="G604" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H604" t="s">
         <v>9</v>
@@ -20902,7 +20905,7 @@
         <v>7.78399991989136</v>
       </c>
       <c r="G605" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H605" t="s">
         <v>9</v>
@@ -20928,7 +20931,7 @@
         <v>7.73099994659424</v>
       </c>
       <c r="G606" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H606" t="s">
         <v>9</v>
@@ -20954,7 +20957,7 @@
         <v>7.44899988174438</v>
       </c>
       <c r="G607" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H607" t="s">
         <v>9</v>
@@ -20980,7 +20983,7 @@
         <v>7.55900001525879</v>
       </c>
       <c r="G608" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H608" t="s">
         <v>9</v>
@@ -21006,7 +21009,7 @@
         <v>7.47499990463257</v>
       </c>
       <c r="G609" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H609" t="s">
         <v>9</v>
@@ -21032,7 +21035,7 @@
         <v>7.40000009536743</v>
       </c>
       <c r="G610" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H610" t="s">
         <v>9</v>
@@ -21058,7 +21061,7 @@
         <v>7.37099981307983</v>
       </c>
       <c r="G611" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H611" t="s">
         <v>9</v>
@@ -21084,7 +21087,7 @@
         <v>7.28999996185303</v>
       </c>
       <c r="G612" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H612" t="s">
         <v>9</v>
@@ -21110,7 +21113,7 @@
         <v>7.11499977111816</v>
       </c>
       <c r="G613" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H613" t="s">
         <v>9</v>
@@ -21136,7 +21139,7 @@
         <v>6.7649998664856</v>
       </c>
       <c r="G614" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H614" t="s">
         <v>9</v>
@@ -21162,7 +21165,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G615" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H615" t="s">
         <v>9</v>
@@ -21188,7 +21191,7 @@
         <v>7.27400016784668</v>
       </c>
       <c r="G616" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H616" t="s">
         <v>9</v>
@@ -21214,7 +21217,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G617" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H617" t="s">
         <v>9</v>
@@ -21240,7 +21243,7 @@
         <v>7.39400005340576</v>
       </c>
       <c r="G618" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H618" t="s">
         <v>9</v>
@@ -21266,7 +21269,7 @@
         <v>7.53499984741211</v>
       </c>
       <c r="G619" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H619" t="s">
         <v>9</v>
@@ -21292,7 +21295,7 @@
         <v>7.49499988555908</v>
       </c>
       <c r="G620" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H620" t="s">
         <v>9</v>
@@ -21318,7 +21321,7 @@
         <v>7.32299995422363</v>
       </c>
       <c r="G621" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H621" t="s">
         <v>9</v>
@@ -21344,7 +21347,7 @@
         <v>7.1710000038147</v>
       </c>
       <c r="G622" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H622" t="s">
         <v>9</v>
@@ -21370,7 +21373,7 @@
         <v>7.08900022506714</v>
       </c>
       <c r="G623" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H623" t="s">
         <v>9</v>
@@ -21396,7 +21399,7 @@
         <v>7.25899982452393</v>
       </c>
       <c r="G624" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H624" t="s">
         <v>9</v>
@@ -21422,7 +21425,7 @@
         <v>7.11100006103516</v>
       </c>
       <c r="G625" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H625" t="s">
         <v>9</v>
@@ -21448,7 +21451,7 @@
         <v>7.24900007247925</v>
       </c>
       <c r="G626" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H626" t="s">
         <v>9</v>
@@ -21474,7 +21477,7 @@
         <v>7.31799983978271</v>
       </c>
       <c r="G627" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H627" t="s">
         <v>9</v>
@@ -21500,7 +21503,7 @@
         <v>6.97200012207031</v>
       </c>
       <c r="G628" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H628" t="s">
         <v>9</v>
@@ -21526,7 +21529,7 @@
         <v>6.97399997711182</v>
       </c>
       <c r="G629" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H629" t="s">
         <v>9</v>
@@ -21552,7 +21555,7 @@
         <v>6.92399978637695</v>
       </c>
       <c r="G630" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H630" t="s">
         <v>9</v>
@@ -21578,7 +21581,7 @@
         <v>6.90299987792969</v>
       </c>
       <c r="G631" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H631" t="s">
         <v>9</v>
@@ -21604,7 +21607,7 @@
         <v>7.07000017166138</v>
       </c>
       <c r="G632" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H632" t="s">
         <v>9</v>
@@ -21630,7 +21633,7 @@
         <v>6.96700000762939</v>
       </c>
       <c r="G633" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H633" t="s">
         <v>9</v>
@@ -21656,7 +21659,7 @@
         <v>7</v>
       </c>
       <c r="G634" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H634" t="s">
         <v>9</v>
@@ -21682,7 +21685,7 @@
         <v>6.875</v>
       </c>
       <c r="G635" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H635" t="s">
         <v>9</v>
@@ -21708,7 +21711,7 @@
         <v>6.94000005722046</v>
       </c>
       <c r="G636" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H636" t="s">
         <v>9</v>
@@ -21734,7 +21737,7 @@
         <v>6.88199996948242</v>
       </c>
       <c r="G637" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H637" t="s">
         <v>9</v>
@@ -21760,7 +21763,7 @@
         <v>7.04699993133545</v>
       </c>
       <c r="G638" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H638" t="s">
         <v>9</v>
@@ -21786,7 +21789,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G639" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H639" t="s">
         <v>9</v>
@@ -21812,7 +21815,7 @@
         <v>7</v>
       </c>
       <c r="G640" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H640" t="s">
         <v>9</v>
@@ -21838,7 +21841,7 @@
         <v>6.93699979782104</v>
       </c>
       <c r="G641" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H641" t="s">
         <v>9</v>
@@ -21864,7 +21867,7 @@
         <v>7.15000009536743</v>
       </c>
       <c r="G642" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H642" t="s">
         <v>9</v>
@@ -21890,7 +21893,7 @@
         <v>7.23999977111816</v>
       </c>
       <c r="G643" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H643" t="s">
         <v>9</v>
@@ -21916,7 +21919,7 @@
         <v>7.22499990463257</v>
       </c>
       <c r="G644" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H644" t="s">
         <v>9</v>
@@ -21942,7 +21945,7 @@
         <v>7.01999998092651</v>
       </c>
       <c r="G645" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H645" t="s">
         <v>9</v>
@@ -21968,7 +21971,7 @@
         <v>7.05399990081787</v>
       </c>
       <c r="G646" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H646" t="s">
         <v>9</v>
@@ -21994,7 +21997,7 @@
         <v>7.06899976730347</v>
       </c>
       <c r="G647" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H647" t="s">
         <v>9</v>
@@ -22020,7 +22023,7 @@
         <v>7.12599992752075</v>
       </c>
       <c r="G648" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H648" t="s">
         <v>9</v>
@@ -22046,7 +22049,7 @@
         <v>7.17700004577637</v>
       </c>
       <c r="G649" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H649" t="s">
         <v>9</v>
@@ -22072,7 +22075,7 @@
         <v>7.26000022888184</v>
       </c>
       <c r="G650" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H650" t="s">
         <v>9</v>
@@ -22098,7 +22101,7 @@
         <v>7.35099983215332</v>
       </c>
       <c r="G651" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H651" t="s">
         <v>9</v>
@@ -22124,7 +22127,7 @@
         <v>7.21600008010864</v>
       </c>
       <c r="G652" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H652" t="s">
         <v>9</v>
@@ -22150,7 +22153,7 @@
         <v>7.24200010299683</v>
       </c>
       <c r="G653" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H653" t="s">
         <v>9</v>
@@ -22176,7 +22179,7 @@
         <v>7.26100015640259</v>
       </c>
       <c r="G654" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H654" t="s">
         <v>9</v>
@@ -22202,7 +22205,7 @@
         <v>7.06599998474121</v>
       </c>
       <c r="G655" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H655" t="s">
         <v>9</v>
@@ -22228,7 +22231,7 @@
         <v>7.25</v>
       </c>
       <c r="G656" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H656" t="s">
         <v>9</v>
@@ -22254,7 +22257,7 @@
         <v>7.05700016021729</v>
       </c>
       <c r="G657" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H657" t="s">
         <v>9</v>
@@ -22280,7 +22283,7 @@
         <v>7.13100004196167</v>
       </c>
       <c r="G658" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H658" t="s">
         <v>9</v>
@@ -22306,7 +22309,7 @@
         <v>7.23099994659424</v>
       </c>
       <c r="G659" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H659" t="s">
         <v>9</v>
@@ -22332,7 +22335,7 @@
         <v>7.18300008773804</v>
       </c>
       <c r="G660" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H660" t="s">
         <v>9</v>
@@ -22358,7 +22361,7 @@
         <v>7.15100002288818</v>
       </c>
       <c r="G661" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H661" t="s">
         <v>9</v>
@@ -22384,7 +22387,7 @@
         <v>7.03000020980835</v>
       </c>
       <c r="G662" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H662" t="s">
         <v>9</v>
@@ -22410,7 +22413,7 @@
         <v>6.93100023269653</v>
       </c>
       <c r="G663" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H663" t="s">
         <v>9</v>
@@ -22436,7 +22439,7 @@
         <v>6.96199989318848</v>
       </c>
       <c r="G664" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H664" t="s">
         <v>9</v>
@@ -22462,7 +22465,7 @@
         <v>6.9210000038147</v>
       </c>
       <c r="G665" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="H665" t="s">
         <v>9</v>
@@ -22488,7 +22491,7 @@
         <v>6.90899991989136</v>
       </c>
       <c r="G666" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H666" t="s">
         <v>9</v>
@@ -22514,7 +22517,7 @@
         <v>6.79300022125244</v>
       </c>
       <c r="G667" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="H667" t="s">
         <v>9</v>
@@ -22540,7 +22543,7 @@
         <v>6.66300010681152</v>
       </c>
       <c r="G668" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="H668" t="s">
         <v>9</v>
@@ -22566,7 +22569,7 @@
         <v>6.60699987411499</v>
       </c>
       <c r="G669" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="H669" t="s">
         <v>9</v>
@@ -22592,7 +22595,7 @@
         <v>6.49100017547607</v>
       </c>
       <c r="G670" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="H670" t="s">
         <v>9</v>
@@ -22618,7 +22621,7 @@
         <v>6.51900005340576</v>
       </c>
       <c r="G671" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="H671" t="s">
         <v>9</v>
@@ -22644,7 +22647,7 @@
         <v>6.57299995422363</v>
       </c>
       <c r="G672" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
       <c r="H672" t="s">
         <v>9</v>
@@ -22670,7 +22673,7 @@
         <v>6.69899988174438</v>
       </c>
       <c r="G673" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="H673" t="s">
         <v>9</v>
@@ -22696,7 +22699,7 @@
         <v>6.68699979782104</v>
       </c>
       <c r="G674" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="H674" t="s">
         <v>9</v>
@@ -22722,7 +22725,7 @@
         <v>6.58799982070923</v>
       </c>
       <c r="G675" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="H675" t="s">
         <v>9</v>
@@ -22748,7 +22751,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G676" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H676" t="s">
         <v>9</v>
@@ -22774,7 +22777,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G677" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H677" t="s">
         <v>9</v>
@@ -22800,7 +22803,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G678" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H678" t="s">
         <v>9</v>
@@ -22826,7 +22829,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G679" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H679" t="s">
         <v>9</v>
@@ -22852,7 +22855,7 @@
         <v>6.62099981307983</v>
       </c>
       <c r="G680" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="H680" t="s">
         <v>9</v>
@@ -22878,7 +22881,7 @@
         <v>6.55399990081787</v>
       </c>
       <c r="G681" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="H681" t="s">
         <v>9</v>
@@ -22904,7 +22907,7 @@
         <v>6.56799983978271</v>
       </c>
       <c r="G682" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="H682" t="s">
         <v>9</v>
@@ -22930,7 +22933,7 @@
         <v>6.5310001373291</v>
       </c>
       <c r="G683" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="H683" t="s">
         <v>9</v>
@@ -22956,7 +22959,7 @@
         <v>6.57499980926514</v>
       </c>
       <c r="G684" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="H684" t="s">
         <v>9</v>
@@ -22982,7 +22985,7 @@
         <v>6.57200002670288</v>
       </c>
       <c r="G685" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="H685" t="s">
         <v>9</v>
@@ -23008,7 +23011,7 @@
         <v>6.58900022506714</v>
       </c>
       <c r="G686" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="H686" t="s">
         <v>9</v>
@@ -23034,7 +23037,7 @@
         <v>6.59999990463257</v>
       </c>
       <c r="G687" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="H687" t="s">
         <v>9</v>
@@ -23060,7 +23063,7 @@
         <v>6.55999994277954</v>
       </c>
       <c r="G688" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="H688" t="s">
         <v>9</v>
@@ -23086,7 +23089,7 @@
         <v>6.58099985122681</v>
       </c>
       <c r="G689" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="H689" t="s">
         <v>9</v>
@@ -23112,7 +23115,7 @@
         <v>6.52299976348877</v>
       </c>
       <c r="G690" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="H690" t="s">
         <v>9</v>
@@ -23138,7 +23141,7 @@
         <v>6.51200008392334</v>
       </c>
       <c r="G691" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="H691" t="s">
         <v>9</v>
@@ -23164,7 +23167,7 @@
         <v>6.95800018310547</v>
       </c>
       <c r="G692" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="H692" t="s">
         <v>9</v>
@@ -23190,7 +23193,7 @@
         <v>6.78499984741211</v>
       </c>
       <c r="G693" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="H693" t="s">
         <v>9</v>
@@ -23216,7 +23219,7 @@
         <v>6.76900005340576</v>
       </c>
       <c r="G694" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="H694" t="s">
         <v>9</v>
@@ -23242,7 +23245,7 @@
         <v>6.84000015258789</v>
       </c>
       <c r="G695" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="H695" t="s">
         <v>9</v>
@@ -23268,7 +23271,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G696" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H696" t="s">
         <v>9</v>
@@ -23294,7 +23297,7 @@
         <v>6.88000011444092</v>
       </c>
       <c r="G697" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="H697" t="s">
         <v>9</v>
@@ -23320,7 +23323,7 @@
         <v>6.85099983215332</v>
       </c>
       <c r="G698" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="H698" t="s">
         <v>9</v>
@@ -23346,7 +23349,7 @@
         <v>6.75799989700317</v>
       </c>
       <c r="G699" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="H699" t="s">
         <v>9</v>
@@ -23372,7 +23375,7 @@
         <v>6.73899984359741</v>
       </c>
       <c r="G700" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="H700" t="s">
         <v>9</v>
@@ -23398,7 +23401,7 @@
         <v>6.61800003051758</v>
       </c>
       <c r="G701" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="H701" t="s">
         <v>9</v>
@@ -23424,7 +23427,7 @@
         <v>6.55700016021729</v>
       </c>
       <c r="G702" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="H702" t="s">
         <v>9</v>
@@ -23450,7 +23453,7 @@
         <v>6.42199993133545</v>
       </c>
       <c r="G703" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="H703" t="s">
         <v>9</v>
@@ -23476,7 +23479,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G704" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H704" t="s">
         <v>9</v>
@@ -23502,7 +23505,7 @@
         <v>6.40000009536743</v>
       </c>
       <c r="G705" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="H705" t="s">
         <v>9</v>
@@ -23528,7 +23531,7 @@
         <v>6.30100011825562</v>
       </c>
       <c r="G706" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="H706" t="s">
         <v>9</v>
@@ -23554,7 +23557,7 @@
         <v>6.14099979400635</v>
       </c>
       <c r="G707" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="H707" t="s">
         <v>9</v>
@@ -23580,7 +23583,7 @@
         <v>6.11499977111816</v>
       </c>
       <c r="G708" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="H708" t="s">
         <v>9</v>
@@ -23606,7 +23609,7 @@
         <v>6.05399990081787</v>
       </c>
       <c r="G709" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="H709" t="s">
         <v>9</v>
@@ -23632,7 +23635,7 @@
         <v>5.91400003433228</v>
       </c>
       <c r="G710" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="H710" t="s">
         <v>9</v>
@@ -23658,7 +23661,7 @@
         <v>5.95300006866455</v>
       </c>
       <c r="G711" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="H711" t="s">
         <v>9</v>
@@ -23684,7 +23687,7 @@
         <v>5.80000019073486</v>
       </c>
       <c r="G712" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="H712" t="s">
         <v>9</v>
@@ -23710,7 +23713,7 @@
         <v>5.90399980545044</v>
       </c>
       <c r="G713" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="H713" t="s">
         <v>9</v>
@@ -23736,7 +23739,7 @@
         <v>5.95900011062622</v>
       </c>
       <c r="G714" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="H714" t="s">
         <v>9</v>
@@ -23762,7 +23765,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G715" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H715" t="s">
         <v>9</v>
@@ -23788,7 +23791,7 @@
         <v>5.89499998092651</v>
       </c>
       <c r="G716" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="H716" t="s">
         <v>9</v>
@@ -23814,7 +23817,7 @@
         <v>5.96999979019165</v>
       </c>
       <c r="G717" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="H717" t="s">
         <v>9</v>
@@ -23840,7 +23843,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G718" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H718" t="s">
         <v>9</v>
@@ -23866,7 +23869,7 @@
         <v>5.94600009918213</v>
       </c>
       <c r="G719" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="H719" t="s">
         <v>9</v>
@@ -23892,7 +23895,7 @@
         <v>5.94999980926514</v>
       </c>
       <c r="G720" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="H720" t="s">
         <v>9</v>
@@ -23918,7 +23921,7 @@
         <v>6.00899982452393</v>
       </c>
       <c r="G721" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="H721" t="s">
         <v>9</v>
@@ -23944,7 +23947,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G722" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H722" t="s">
         <v>9</v>
@@ -23970,7 +23973,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G723" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H723" t="s">
         <v>9</v>
@@ -23996,7 +23999,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G724" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H724" t="s">
         <v>9</v>
@@ -24022,7 +24025,7 @@
         <v>6.25</v>
       </c>
       <c r="G725" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="H725" t="s">
         <v>9</v>
@@ -24048,7 +24051,7 @@
         <v>6.23899984359741</v>
       </c>
       <c r="G726" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="H726" t="s">
         <v>9</v>
@@ -24074,7 +24077,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G727" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H727" t="s">
         <v>9</v>
@@ -24100,7 +24103,7 @@
         <v>6.03999996185303</v>
       </c>
       <c r="G728" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="H728" t="s">
         <v>9</v>
@@ -24126,7 +24129,7 @@
         <v>6.34999990463257</v>
       </c>
       <c r="G729" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="H729" t="s">
         <v>9</v>
@@ -24152,7 +24155,7 @@
         <v>6.13899993896484</v>
       </c>
       <c r="G730" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="H730" t="s">
         <v>9</v>
@@ -24178,7 +24181,7 @@
         <v>6.2189998626709</v>
       </c>
       <c r="G731" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="H731" t="s">
         <v>9</v>
@@ -24204,7 +24207,7 @@
         <v>6.14499998092651</v>
       </c>
       <c r="G732" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="H732" t="s">
         <v>9</v>
@@ -24230,7 +24233,7 @@
         <v>6.10099983215332</v>
       </c>
       <c r="G733" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="H733" t="s">
         <v>9</v>
@@ -24256,7 +24259,7 @@
         <v>6.00299978256226</v>
       </c>
       <c r="G734" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="H734" t="s">
         <v>9</v>
@@ -24282,7 +24285,7 @@
         <v>6.03900003433228</v>
       </c>
       <c r="G735" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="H735" t="s">
         <v>9</v>
@@ -24308,7 +24311,7 @@
         <v>6.01399993896484</v>
       </c>
       <c r="G736" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="H736" t="s">
         <v>9</v>
@@ -24334,7 +24337,7 @@
         <v>5.95100021362305</v>
       </c>
       <c r="G737" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="H737" t="s">
         <v>9</v>
@@ -24360,7 +24363,7 @@
         <v>5.86499977111816</v>
       </c>
       <c r="G738" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="H738" t="s">
         <v>9</v>
@@ -24386,7 +24389,7 @@
         <v>5.86800003051758</v>
       </c>
       <c r="G739" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="H739" t="s">
         <v>9</v>
@@ -24412,7 +24415,7 @@
         <v>5.89699983596802</v>
       </c>
       <c r="G740" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="H740" t="s">
         <v>9</v>
@@ -24438,7 +24441,7 @@
         <v>6.02899980545044</v>
       </c>
       <c r="G741" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="H741" t="s">
         <v>9</v>
@@ -24464,7 +24467,7 @@
         <v>6.14300012588501</v>
       </c>
       <c r="G742" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="H742" t="s">
         <v>9</v>
@@ -24490,7 +24493,7 @@
         <v>6.15999984741211</v>
       </c>
       <c r="G743" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="H743" t="s">
         <v>9</v>
@@ -24516,7 +24519,7 @@
         <v>6.10699987411499</v>
       </c>
       <c r="G744" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="H744" t="s">
         <v>9</v>
@@ -24542,7 +24545,7 @@
         <v>6.09200000762939</v>
       </c>
       <c r="G745" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="H745" t="s">
         <v>9</v>
@@ -24568,7 +24571,7 @@
         <v>5.98299980163574</v>
       </c>
       <c r="G746" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="H746" t="s">
         <v>9</v>
@@ -24594,7 +24597,7 @@
         <v>5.88199996948242</v>
       </c>
       <c r="G747" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="H747" t="s">
         <v>9</v>
@@ -24620,7 +24623,7 @@
         <v>5.8899998664856</v>
       </c>
       <c r="G748" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="H748" t="s">
         <v>9</v>
@@ -24646,7 +24649,7 @@
         <v>5.8600001335144</v>
       </c>
       <c r="G749" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="H749" t="s">
         <v>9</v>
@@ -24672,7 +24675,7 @@
         <v>5.80700016021729</v>
       </c>
       <c r="G750" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="H750" t="s">
         <v>9</v>
@@ -24698,7 +24701,7 @@
         <v>5.81599998474121</v>
       </c>
       <c r="G751" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="H751" t="s">
         <v>9</v>
@@ -24724,7 +24727,7 @@
         <v>5.76399993896484</v>
       </c>
       <c r="G752" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="H752" t="s">
         <v>9</v>
@@ -24750,7 +24753,7 @@
         <v>5.65299987792969</v>
       </c>
       <c r="G753" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="H753" t="s">
         <v>9</v>
@@ -24776,7 +24779,7 @@
         <v>5.79199981689453</v>
       </c>
       <c r="G754" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="H754" t="s">
         <v>9</v>
@@ -24802,7 +24805,7 @@
         <v>5.67999982833862</v>
       </c>
       <c r="G755" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="H755" t="s">
         <v>9</v>
@@ -24828,7 +24831,7 @@
         <v>5.63399982452393</v>
       </c>
       <c r="G756" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="H756" t="s">
         <v>9</v>
@@ -24854,7 +24857,7 @@
         <v>5.5</v>
       </c>
       <c r="G757" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="H757" t="s">
         <v>9</v>
@@ -24880,7 +24883,7 @@
         <v>5.39599990844727</v>
       </c>
       <c r="G758" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="H758" t="s">
         <v>9</v>
@@ -24906,7 +24909,7 @@
         <v>5.37400007247925</v>
       </c>
       <c r="G759" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="H759" t="s">
         <v>9</v>
@@ -24932,7 +24935,7 @@
         <v>5.42999982833862</v>
       </c>
       <c r="G760" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="H760" t="s">
         <v>9</v>
@@ -24958,7 +24961,7 @@
         <v>5.4229998588562</v>
       </c>
       <c r="G761" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="H761" t="s">
         <v>9</v>
@@ -24984,7 +24987,7 @@
         <v>5.30700016021729</v>
       </c>
       <c r="G762" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="H762" t="s">
         <v>9</v>
@@ -25010,7 +25013,7 @@
         <v>5.38199996948242</v>
       </c>
       <c r="G763" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="H763" t="s">
         <v>9</v>
@@ -25036,7 +25039,7 @@
         <v>5.57200002670288</v>
       </c>
       <c r="G764" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="H764" t="s">
         <v>9</v>
@@ -25062,7 +25065,7 @@
         <v>5.67199993133545</v>
       </c>
       <c r="G765" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="H765" t="s">
         <v>9</v>
@@ -25088,7 +25091,7 @@
         <v>5.80800008773804</v>
       </c>
       <c r="G766" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="H766" t="s">
         <v>9</v>
@@ -25114,7 +25117,7 @@
         <v>5.78599977493286</v>
       </c>
       <c r="G767" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="H767" t="s">
         <v>9</v>
@@ -25140,7 +25143,7 @@
         <v>5.90899991989136</v>
       </c>
       <c r="G768" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="H768" t="s">
         <v>9</v>
@@ -25166,7 +25169,7 @@
         <v>5.88800001144409</v>
       </c>
       <c r="G769" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="H769" t="s">
         <v>9</v>
@@ -25192,7 +25195,7 @@
         <v>5.91599988937378</v>
       </c>
       <c r="G770" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="H770" t="s">
         <v>9</v>
@@ -25218,7 +25221,7 @@
         <v>5.88000011444092</v>
       </c>
       <c r="G771" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="H771" t="s">
         <v>9</v>
@@ -25244,7 +25247,7 @@
         <v>5.81099987030029</v>
       </c>
       <c r="G772" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="H772" t="s">
         <v>9</v>
@@ -25270,7 +25273,7 @@
         <v>5.7519998550415</v>
       </c>
       <c r="G773" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="H773" t="s">
         <v>9</v>
@@ -25296,7 +25299,7 @@
         <v>5.8769998550415</v>
       </c>
       <c r="G774" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="H774" t="s">
         <v>9</v>
@@ -25322,7 +25325,7 @@
         <v>5.84899997711182</v>
       </c>
       <c r="G775" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="H775" t="s">
         <v>9</v>
@@ -25348,7 +25351,7 @@
         <v>5.90199995040894</v>
       </c>
       <c r="G776" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="H776" t="s">
         <v>9</v>
@@ -25374,7 +25377,7 @@
         <v>5.83699989318848</v>
       </c>
       <c r="G777" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="H777" t="s">
         <v>9</v>
@@ -25400,7 +25403,7 @@
         <v>5.77400016784668</v>
       </c>
       <c r="G778" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="H778" t="s">
         <v>9</v>
@@ -25426,7 +25429,7 @@
         <v>5.92199993133545</v>
       </c>
       <c r="G779" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="H779" t="s">
         <v>9</v>
@@ -25452,7 +25455,7 @@
         <v>5.98899984359741</v>
       </c>
       <c r="G780" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="H780" t="s">
         <v>9</v>
@@ -25478,7 +25481,7 @@
         <v>6.14900016784668</v>
       </c>
       <c r="G781" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="H781" t="s">
         <v>9</v>
@@ -25504,7 +25507,7 @@
         <v>6.2810001373291</v>
       </c>
       <c r="G782" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="H782" t="s">
         <v>9</v>
@@ -25530,7 +25533,7 @@
         <v>6.23799991607666</v>
       </c>
       <c r="G783" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="H783" t="s">
         <v>9</v>
@@ -25556,7 +25559,7 @@
         <v>6.23999977111816</v>
       </c>
       <c r="G784" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="H784" t="s">
         <v>9</v>
@@ -25582,7 +25585,7 @@
         <v>6.18200016021729</v>
       </c>
       <c r="G785" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="H785" t="s">
         <v>9</v>
@@ -25608,7 +25611,7 @@
         <v>6.17999982833862</v>
       </c>
       <c r="G786" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="H786" t="s">
         <v>9</v>
@@ -25634,7 +25637,7 @@
         <v>6.21000003814697</v>
       </c>
       <c r="G787" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="H787" t="s">
         <v>9</v>
@@ -25660,7 +25663,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G788" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="H788" t="s">
         <v>9</v>
@@ -25686,7 +25689,7 @@
         <v>6.17000007629395</v>
       </c>
       <c r="G789" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="H789" t="s">
         <v>9</v>
@@ -25712,7 +25715,7 @@
         <v>6.01599979400635</v>
       </c>
       <c r="G790" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="H790" t="s">
         <v>9</v>
@@ -25738,7 +25741,7 @@
         <v>5.89599990844727</v>
       </c>
       <c r="G791" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="H791" t="s">
         <v>9</v>
@@ -25764,7 +25767,7 @@
         <v>6</v>
       </c>
       <c r="G792" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="H792" t="s">
         <v>9</v>
@@ -25790,7 +25793,7 @@
         <v>5.94799995422363</v>
       </c>
       <c r="G793" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="H793" t="s">
         <v>9</v>
@@ -25816,7 +25819,7 @@
         <v>6.01000022888184</v>
       </c>
       <c r="G794" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="H794" t="s">
         <v>9</v>
@@ -25842,7 +25845,7 @@
         <v>6.06699991226196</v>
       </c>
       <c r="G795" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="H795" t="s">
         <v>9</v>
@@ -25868,7 +25871,7 @@
         <v>6.16400003433228</v>
       </c>
       <c r="G796" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="H796" t="s">
         <v>9</v>
@@ -25894,7 +25897,7 @@
         <v>6.1399998664856</v>
       </c>
       <c r="G797" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="H797" t="s">
         <v>9</v>
@@ -25920,7 +25923,7 @@
         <v>6.13600015640259</v>
       </c>
       <c r="G798" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="H798" t="s">
         <v>9</v>
@@ -25946,7 +25949,7 @@
         <v>6.13000011444092</v>
       </c>
       <c r="G799" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="H799" t="s">
         <v>9</v>
@@ -25972,7 +25975,7 @@
         <v>6.05499982833862</v>
       </c>
       <c r="G800" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="H800" t="s">
         <v>9</v>
@@ -25998,7 +26001,7 @@
         <v>6.13700008392334</v>
       </c>
       <c r="G801" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="H801" t="s">
         <v>9</v>
@@ -26024,7 +26027,7 @@
         <v>6.23199987411499</v>
       </c>
       <c r="G802" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="H802" t="s">
         <v>9</v>
@@ -26050,7 +26053,7 @@
         <v>6.31899976730347</v>
       </c>
       <c r="G803" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="H803" t="s">
         <v>9</v>
@@ -26076,7 +26079,7 @@
         <v>6.18699979782104</v>
       </c>
       <c r="G804" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="H804" t="s">
         <v>9</v>
@@ -26102,7 +26105,7 @@
         <v>6.23299980163574</v>
       </c>
       <c r="G805" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="H805" t="s">
         <v>9</v>
@@ -26128,7 +26131,7 @@
         <v>6.30800008773804</v>
       </c>
       <c r="G806" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="H806" t="s">
         <v>9</v>
@@ -26154,7 +26157,7 @@
         <v>6.36199998855591</v>
       </c>
       <c r="G807" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="H807" t="s">
         <v>9</v>
@@ -26180,7 +26183,7 @@
         <v>6.55000019073486</v>
       </c>
       <c r="G808" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="H808" t="s">
         <v>9</v>
@@ -26206,7 +26209,7 @@
         <v>6.65299987792969</v>
       </c>
       <c r="G809" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="H809" t="s">
         <v>9</v>
@@ -26232,7 +26235,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G810" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H810" t="s">
         <v>9</v>
@@ -26258,7 +26261,7 @@
         <v>6.43900012969971</v>
       </c>
       <c r="G811" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="H811" t="s">
         <v>9</v>
@@ -26284,7 +26287,7 @@
         <v>6.46000003814697</v>
       </c>
       <c r="G812" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="H812" t="s">
         <v>9</v>
@@ -26310,7 +26313,7 @@
         <v>6.46999979019165</v>
       </c>
       <c r="G813" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="H813" t="s">
         <v>9</v>
@@ -26336,7 +26339,7 @@
         <v>6.6269998550415</v>
       </c>
       <c r="G814" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="H814" t="s">
         <v>9</v>
@@ -26362,7 +26365,7 @@
         <v>6.65799999237061</v>
       </c>
       <c r="G815" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="H815" t="s">
         <v>9</v>
@@ -26388,7 +26391,7 @@
         <v>6.7039999961853</v>
       </c>
       <c r="G816" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="H816" t="s">
         <v>9</v>
@@ -26414,7 +26417,7 @@
         <v>6.78000020980835</v>
       </c>
       <c r="G817" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="H817" t="s">
         <v>9</v>
@@ -26440,7 +26443,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G818" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H818" t="s">
         <v>9</v>
@@ -26466,7 +26469,7 @@
         <v>6.64799976348877</v>
       </c>
       <c r="G819" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H819" t="s">
         <v>9</v>
@@ -26492,7 +26495,7 @@
         <v>6.64900016784668</v>
       </c>
       <c r="G820" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="H820" t="s">
         <v>9</v>
@@ -26518,7 +26521,7 @@
         <v>6.55600023269653</v>
       </c>
       <c r="G821" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H821" t="s">
         <v>9</v>
@@ -26544,7 +26547,7 @@
         <v>6.48299980163574</v>
       </c>
       <c r="G822" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="H822" t="s">
         <v>9</v>
@@ -26570,7 +26573,7 @@
         <v>6.42799997329712</v>
       </c>
       <c r="G823" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="H823" t="s">
         <v>9</v>
@@ -26596,7 +26599,7 @@
         <v>6.51000022888184</v>
       </c>
       <c r="G824" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="H824" t="s">
         <v>9</v>
@@ -26622,7 +26625,7 @@
         <v>6.48999977111816</v>
       </c>
       <c r="G825" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="H825" t="s">
         <v>9</v>
@@ -26648,7 +26651,7 @@
         <v>6.44000005722046</v>
       </c>
       <c r="G826" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="H826" t="s">
         <v>9</v>
@@ -26674,7 +26677,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G827" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H827" t="s">
         <v>9</v>
@@ -26700,7 +26703,7 @@
         <v>6.57999992370605</v>
       </c>
       <c r="G828" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="H828" t="s">
         <v>9</v>
@@ -26726,7 +26729,7 @@
         <v>6.61999988555908</v>
       </c>
       <c r="G829" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="H829" t="s">
         <v>9</v>
@@ -26752,7 +26755,7 @@
         <v>6.63000011444092</v>
       </c>
       <c r="G830" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="H830" t="s">
         <v>9</v>
@@ -26778,7 +26781,7 @@
         <v>6.65999984741211</v>
       </c>
       <c r="G831" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="H831" t="s">
         <v>9</v>
@@ -26804,7 +26807,7 @@
         <v>6.67000007629395</v>
       </c>
       <c r="G832" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="H832" t="s">
         <v>9</v>
@@ -26830,7 +26833,7 @@
         <v>6.48000001907349</v>
       </c>
       <c r="G833" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="H833" t="s">
         <v>9</v>
@@ -26856,7 +26859,7 @@
         <v>6.51999998092651</v>
       </c>
       <c r="G834" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="H834" t="s">
         <v>9</v>
@@ -26882,7 +26885,7 @@
         <v>6.59000015258789</v>
       </c>
       <c r="G835" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="H835" t="s">
         <v>9</v>
@@ -26908,7 +26911,7 @@
         <v>6.6399998664856</v>
       </c>
       <c r="G836" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="H836" t="s">
         <v>9</v>
@@ -26934,7 +26937,7 @@
         <v>6.69000005722046</v>
       </c>
       <c r="G837" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="H837" t="s">
         <v>9</v>
@@ -26960,7 +26963,7 @@
         <v>6.75</v>
       </c>
       <c r="G838" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H838" t="s">
         <v>9</v>
@@ -26986,7 +26989,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G839" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H839" t="s">
         <v>9</v>
@@ -27012,7 +27015,7 @@
         <v>6.71000003814697</v>
       </c>
       <c r="G840" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="H840" t="s">
         <v>9</v>
@@ -27038,7 +27041,7 @@
         <v>6.71999979019165</v>
       </c>
       <c r="G841" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="H841" t="s">
         <v>9</v>
@@ -27064,7 +27067,7 @@
         <v>6.73000001907349</v>
       </c>
       <c r="G842" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="H842" t="s">
         <v>9</v>
@@ -27090,7 +27093,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G843" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H843" t="s">
         <v>9</v>
@@ -27116,7 +27119,7 @@
         <v>6.65000009536743</v>
       </c>
       <c r="G844" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="H844" t="s">
         <v>9</v>
@@ -27142,7 +27145,7 @@
         <v>6.75</v>
       </c>
       <c r="G845" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H845" t="s">
         <v>9</v>
@@ -27168,7 +27171,7 @@
         <v>6.75</v>
       </c>
       <c r="G846" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H846" t="s">
         <v>9</v>
@@ -27194,7 +27197,7 @@
         <v>6.75</v>
       </c>
       <c r="G847" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H847" t="s">
         <v>9</v>
@@ -27220,7 +27223,7 @@
         <v>6.75</v>
       </c>
       <c r="G848" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="H848" t="s">
         <v>9</v>
@@ -27246,7 +27249,7 @@
         <v>6.69999980926514</v>
       </c>
       <c r="G849" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="H849" t="s">
         <v>9</v>
@@ -27272,7 +27275,7 @@
         <v>6.8600001335144</v>
       </c>
       <c r="G850" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="H850" t="s">
         <v>9</v>
@@ -27298,7 +27301,7 @@
         <v>6.76999998092651</v>
       </c>
       <c r="G851" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="H851" t="s">
         <v>9</v>
@@ -27324,7 +27327,7 @@
         <v>6.53999996185303</v>
       </c>
       <c r="G852" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="H852" t="s">
         <v>9</v>
@@ -27350,7 +27353,7 @@
         <v>6.6100001335144</v>
       </c>
       <c r="G853" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="H853" t="s">
         <v>9</v>
@@ -27376,7 +27379,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G854" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H854" t="s">
         <v>9</v>
@@ -27402,7 +27405,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G855" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H855" t="s">
         <v>9</v>
@@ -27428,7 +27431,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G856" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="H856" t="s">
         <v>9</v>
@@ -27818,7 +27821,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G871" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="H871" t="s">
         <v>9</v>
@@ -28390,7 +28393,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G893" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H893" t="s">
         <v>9</v>
@@ -31016,7 +31019,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G994" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H994" t="s">
         <v>9</v>
@@ -31302,7 +31305,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1005" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1005" t="s">
         <v>9</v>
@@ -31406,7 +31409,7 @@
         <v>6.1100001335144</v>
       </c>
       <c r="G1009" t="s">
-        <v>667</v>
+        <v>684</v>
       </c>
       <c r="H1009" t="s">
         <v>9</v>
@@ -31562,7 +31565,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1015" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1015" t="s">
         <v>9</v>
@@ -31926,7 +31929,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1029" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1029" t="s">
         <v>9</v>
@@ -31978,7 +31981,7 @@
         <v>6.19999980926514</v>
       </c>
       <c r="G1031" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="H1031" t="s">
         <v>9</v>
@@ -32186,7 +32189,7 @@
         <v>6.11999988555908</v>
       </c>
       <c r="G1039" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="H1039" t="s">
         <v>9</v>
@@ -72234,7 +72237,7 @@
     </row>
     <row r="2580">
       <c r="A2580" s="1" t="n">
-        <v>46078.6912268518</v>
+        <v>46078.3333333333</v>
       </c>
       <c r="B2580" t="n">
         <v>81828</v>
@@ -72255,6 +72258,32 @@
         <v>1609</v>
       </c>
       <c r="H2580" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2581">
+      <c r="A2581" s="1" t="n">
+        <v>46079.6909837963</v>
+      </c>
+      <c r="B2581" t="n">
+        <v>240678</v>
+      </c>
+      <c r="C2581" t="n">
+        <v>4.32499980926514</v>
+      </c>
+      <c r="D2581" t="n">
+        <v>4.14499998092651</v>
+      </c>
+      <c r="E2581" t="n">
+        <v>4.21999979019165</v>
+      </c>
+      <c r="F2581" t="n">
+        <v>4.32000017166138</v>
+      </c>
+      <c r="G2581" t="s">
+        <v>1610</v>
+      </c>
+      <c r="H2581" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1611" uniqueCount="1611">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="1612">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,415 +47,415 @@
     <t xml:space="preserve">4.81178855895996</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76804447174072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7653112411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64775037765503</t>
+    <t xml:space="preserve">4.76804494857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76531171798706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64774990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53839111328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56573152542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67235612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.55206060409546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33334302902222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16383743286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04627704620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60884189605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88223838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95605564117432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0380744934082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97519397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94785380363464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81388902664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96425747871399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07088184356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92051434516907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69632816314697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78654932975769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45573925971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49948263168335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69085955619812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56783175468445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63891530036926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.88497257232666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755923271179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93691778182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87130236625671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05994653701782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00800132751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95332145690918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98612952232361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99159741401672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03260707855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05447816848755</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24038887023926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21031522750854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.37435340881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33607769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34701251983643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33881139755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42903232574463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52745532989502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51105213165283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46184015274048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57119941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67508983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60947465896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54932737350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.4837121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34974765777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42083024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42356538772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26499462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22398471832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22671890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33061027526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40169286727905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3060040473938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36615180969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26772832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32514190673828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29233455657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27046203613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29506778717041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39895915985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30873823165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38802242279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42629909515381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34427976608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39075708389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30327033996582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49522399902344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57292604446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65062761306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69091844558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67940616607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69379615783691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66214036941528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61609363555908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57580327987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63623857498169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63048267364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63336038589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63911628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56429243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35133075714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08368873596191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95130753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9714527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16139078140259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20168161392212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24772691726685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27650594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03476476669312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755827903748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84482717514038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633754730225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470426559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01749897003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784911155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83619260787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96281909942627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05778837203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0923228263855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25636053085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40313196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33406400680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5182466506958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41752147674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45493364334106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45781183242798</t>
   </si>
   <si>
     <t xml:space="preserve">4.53839159011841</t>
   </si>
   <si>
-    <t xml:space="preserve">4.56573057174683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67235612869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55206155776978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33334398269653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16383695602417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04627656936646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60884189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88223814964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95605492591858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03807497024536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9751935005188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94785451889038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81388926506042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96425747871399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07088184356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92051410675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69632840156555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78654980659485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45573925971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49948239326477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69086074829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56783223152161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63891506195068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88497281074524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755970954895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93691754341125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87130236625671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05994701385498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00800180435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9533212184906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98612976074219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99159741401672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03260707855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05447816848755</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24038887023926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21031475067139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37435340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33607816696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34701347351074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33881187438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42903280258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52745580673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51105213165283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46184015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57119941711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67509031295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60947418212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54932689666748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4837121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34974765777588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42083072662354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42356538772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26499462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25405836105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22398471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22671890258789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2376537322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3306097984314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40169239044189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31967353820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30600452423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36615085601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26772832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32514142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29233407974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27046251296997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29506778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39895868301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30873775482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38802337646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42629861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34427976608276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39075708389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30326986312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49522352218628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57292556762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65062761306763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091892242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67940664291382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69379615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66213989257812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61609363555908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57580327987671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63623905181885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63048315048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63336133956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63911628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56429243087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35133075714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066608428955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08368873596191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95130729675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97145175933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16139125823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20168161392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24772691726685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2765064239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03476524353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755827903748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84482669830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633778572083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470378875732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15851354598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01749849319458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784887313843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83619260787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96281814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05778837203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0923228263855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25636005401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40313196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3340630531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5182466506958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41752052307129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45493316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45781135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53839206695557</t>
-  </si>
-  <si>
     <t xml:space="preserve">4.52975749969482</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48946809768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51536893844604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25923871994019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38874197006226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46644401550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38298654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36572027206421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41464376449585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35996437072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33694076538086</t>
+    <t xml:space="preserve">4.48946762084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51536798477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25923919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38874244689941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46644449234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3829870223999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36571979522705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41464328765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35996389389038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33694171905518</t>
   </si>
   <si>
     <t xml:space="preserve">4.29377317428589</t>
   </si>
   <si>
-    <t xml:space="preserve">4.31391716003418</t>
+    <t xml:space="preserve">4.31391763687134</t>
   </si>
   <si>
     <t xml:space="preserve">4.19016981124878</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19880390167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22182703018188</t>
+    <t xml:space="preserve">4.19880342483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22182607650757</t>
   </si>
   <si>
     <t xml:space="preserve">4.2621169090271</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">4.25348234176636</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23046064376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14412403106689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19592666625977</t>
+    <t xml:space="preserve">4.23045969009399</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14412355422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19592571258545</t>
   </si>
   <si>
     <t xml:space="preserve">4.16714715957642</t>
@@ -485,67 +485,67 @@
     <t xml:space="preserve">4.20743703842163</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14700174331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17865800857544</t>
+    <t xml:space="preserve">4.14700222015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1786584854126</t>
   </si>
   <si>
     <t xml:space="preserve">4.07505559921265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94267416000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497116088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79878067970276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77575755119324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83907079696655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7469789981842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74985671043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8592164516449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82468056678772</t>
+    <t xml:space="preserve">3.94267344474792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497139930725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79878091812134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77575731277466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83907008171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74697852134705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7498562335968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85921597480774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82468032836914</t>
   </si>
   <si>
     <t xml:space="preserve">3.79590272903442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87936091423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81029176712036</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78439116477966</t>
+    <t xml:space="preserve">3.87936067581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81029224395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439164161682</t>
   </si>
   <si>
     <t xml:space="preserve">3.76424551010132</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72971177101135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71244478225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72395634651184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84194803237915</t>
+    <t xml:space="preserve">3.72971153259277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71244406700134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72395610809326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84194779396057</t>
   </si>
   <si>
     <t xml:space="preserve">3.99735307693481</t>
@@ -566,94 +566,94 @@
     <t xml:space="preserve">4.03764295578003</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00310850143433</t>
+    <t xml:space="preserve">4.00310897827148</t>
   </si>
   <si>
     <t xml:space="preserve">3.97432994842529</t>
   </si>
   <si>
-    <t xml:space="preserve">3.91389513015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93979597091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92540693283081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92828440666199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89662742614746</t>
+    <t xml:space="preserve">3.91389536857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93979620933533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92540645599365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92828416824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89662790298462</t>
   </si>
   <si>
     <t xml:space="preserve">3.84770393371582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75273442268372</t>
+    <t xml:space="preserve">3.75273489952087</t>
   </si>
   <si>
     <t xml:space="preserve">3.75849008560181</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55703997612</t>
+    <t xml:space="preserve">3.55703973770142</t>
   </si>
   <si>
     <t xml:space="preserve">3.64337539672852</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66927671432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65776491165161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58006238937378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59732961654663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60308599472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63186454772949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.6261088848114</t>
+    <t xml:space="preserve">3.66927599906921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65776443481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58006191253662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59732985496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6030855178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63186478614807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62610840797424</t>
   </si>
   <si>
     <t xml:space="preserve">3.6606433391571</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61459708213806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80453658103943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95994067192078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07217741012573</t>
+    <t xml:space="preserve">3.61459732055664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80453681945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9599404335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07217693328857</t>
   </si>
   <si>
     <t xml:space="preserve">4.04339933395386</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12685680389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13261222839355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12110185623169</t>
+    <t xml:space="preserve">4.1268572807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13261270523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12110137939453</t>
   </si>
   <si>
     <t xml:space="preserve">4.36859798431396</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28226137161255</t>
+    <t xml:space="preserve">4.28226184844971</t>
   </si>
   <si>
     <t xml:space="preserve">4.33981895446777</t>
@@ -665,19 +665,19 @@
     <t xml:space="preserve">4.33118486404419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.302405834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27075004577637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2275824546814</t>
+    <t xml:space="preserve">4.30240631103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27074956893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22758197784424</t>
   </si>
   <si>
     <t xml:space="preserve">4.2131929397583</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18153619766235</t>
+    <t xml:space="preserve">4.18153715133667</t>
   </si>
   <si>
     <t xml:space="preserve">4.09807825088501</t>
@@ -689,19 +689,19 @@
     <t xml:space="preserve">4.10383415222168</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02900981903076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06929969787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21894931793213</t>
+    <t xml:space="preserve">4.0290093421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06929922103882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21894836425781</t>
   </si>
   <si>
     <t xml:space="preserve">4.30816221237183</t>
   </si>
   <si>
-    <t xml:space="preserve">4.14987993240356</t>
+    <t xml:space="preserve">4.14987945556641</t>
   </si>
   <si>
     <t xml:space="preserve">4.47220039367676</t>
@@ -710,22 +710,22 @@
     <t xml:space="preserve">4.51249074935913</t>
   </si>
   <si>
-    <t xml:space="preserve">4.37723112106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.44342184066772</t>
+    <t xml:space="preserve">4.37723159790039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.44342279434204</t>
   </si>
   <si>
     <t xml:space="preserve">4.59307050704956</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62472820281982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57004833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71969652175903</t>
+    <t xml:space="preserve">4.62472772598267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5700478553772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71969699859619</t>
   </si>
   <si>
     <t xml:space="preserve">4.70818567276001</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">4.64487266540527</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62184906005859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54702472686768</t>
+    <t xml:space="preserve">4.62185001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54702520370483</t>
   </si>
   <si>
     <t xml:space="preserve">4.52687978744507</t>
@@ -761,10 +761,10 @@
     <t xml:space="preserve">4.6045823097229</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71394109725952</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66501712799072</t>
+    <t xml:space="preserve">4.71394062042236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66501760482788</t>
   </si>
   <si>
     <t xml:space="preserve">4.74559783935547</t>
@@ -773,13 +773,13 @@
     <t xml:space="preserve">4.76574325561523</t>
   </si>
   <si>
-    <t xml:space="preserve">4.74847602844238</t>
+    <t xml:space="preserve">4.74847555160522</t>
   </si>
   <si>
     <t xml:space="preserve">4.78301000595093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7714991569519</t>
+    <t xml:space="preserve">4.77149868011475</t>
   </si>
   <si>
     <t xml:space="preserve">4.8233003616333</t>
@@ -788,16 +788,16 @@
     <t xml:space="preserve">4.92690277099609</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94992637634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.98446035385132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02475070953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.05640745162964</t>
+    <t xml:space="preserve">4.94992589950562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98446083068848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.02475118637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.05640697479248</t>
   </si>
   <si>
     <t xml:space="preserve">4.89236879348755</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">4.86359024047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.82905530929565</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.87592363357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.91160106658936</t>
+    <t xml:space="preserve">4.82905578613281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.8759241104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.91160154342651</t>
   </si>
   <si>
     <t xml:space="preserve">4.93538618087769</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">4.9205207824707</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01268720626831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96809101104736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97106313705444</t>
+    <t xml:space="preserve">5.01268768310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96809053421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97106456756592</t>
   </si>
   <si>
     <t xml:space="preserve">4.89376258850098</t>
@@ -839,112 +839,112 @@
     <t xml:space="preserve">4.94727897644043</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94133329391479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.92944049835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.88781595230103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85511159896851</t>
+    <t xml:space="preserve">4.94133234024048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.92944002151489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.88781642913818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85511112213135</t>
   </si>
   <si>
     <t xml:space="preserve">4.79862260818481</t>
   </si>
   <si>
-    <t xml:space="preserve">4.77186393737793</t>
+    <t xml:space="preserve">4.77186441421509</t>
   </si>
   <si>
     <t xml:space="preserve">4.75105237960815</t>
   </si>
   <si>
-    <t xml:space="preserve">4.78673028945923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73321390151978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66185903549194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53401374816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.584557056427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61726188659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70348310470581</t>
+    <t xml:space="preserve">4.78672981262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73321485519409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66185855865479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5340142250061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58455753326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61726140975952</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70348262786865</t>
   </si>
   <si>
     <t xml:space="preserve">4.72132158279419</t>
   </si>
   <si>
-    <t xml:space="preserve">4.63807439804077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72726774215698</t>
+    <t xml:space="preserve">4.63807392120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72726726531982</t>
   </si>
   <si>
     <t xml:space="preserve">4.81646156311035</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83132696151733</t>
+    <t xml:space="preserve">4.83132743835449</t>
   </si>
   <si>
     <t xml:space="preserve">4.93835973739624</t>
   </si>
   <si>
-    <t xml:space="preserve">4.94430541992188</t>
+    <t xml:space="preserve">4.94430589675903</t>
   </si>
   <si>
     <t xml:space="preserve">4.98295640945435</t>
   </si>
   <si>
-    <t xml:space="preserve">4.95322561264038</t>
+    <t xml:space="preserve">4.95322513580322</t>
   </si>
   <si>
     <t xml:space="preserve">4.90565538406372</t>
   </si>
   <si>
-    <t xml:space="preserve">4.84619283676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.89078998565674</t>
+    <t xml:space="preserve">4.84619331359863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.89078950881958</t>
   </si>
   <si>
     <t xml:space="preserve">5.00376844406128</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05431127548218</t>
+    <t xml:space="preserve">5.05431175231934</t>
   </si>
   <si>
     <t xml:space="preserve">5.04836511611938</t>
   </si>
   <si>
-    <t xml:space="preserve">4.99782133102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9859299659729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15837097167969</t>
+    <t xml:space="preserve">4.99782180786133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.98593044281006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15837049484253</t>
   </si>
   <si>
     <t xml:space="preserve">5.12566709518433</t>
   </si>
   <si>
-    <t xml:space="preserve">5.11080026626587</t>
+    <t xml:space="preserve">5.11080121994019</t>
   </si>
   <si>
     <t xml:space="preserve">5.07512283325195</t>
   </si>
   <si>
-    <t xml:space="preserve">5.08106994628906</t>
+    <t xml:space="preserve">5.08106899261475</t>
   </si>
   <si>
     <t xml:space="preserve">5.09593486785889</t>
@@ -971,76 +971,76 @@
     <t xml:space="preserve">5.01566123962402</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06620454788208</t>
+    <t xml:space="preserve">5.06620407104492</t>
   </si>
   <si>
     <t xml:space="preserve">5.13755893707275</t>
   </si>
   <si>
-    <t xml:space="preserve">5.23269891738892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24459171295166</t>
+    <t xml:space="preserve">5.23269844055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24459075927734</t>
   </si>
   <si>
     <t xml:space="preserve">5.23864603042603</t>
   </si>
   <si>
-    <t xml:space="preserve">5.197021484375</t>
+    <t xml:space="preserve">5.19702196121216</t>
   </si>
   <si>
     <t xml:space="preserve">5.17323589324951</t>
   </si>
   <si>
-    <t xml:space="preserve">5.18512773513794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.20891380310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.19404888153076</t>
+    <t xml:space="preserve">5.18512868881226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.20891427993774</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.1940484046936</t>
   </si>
   <si>
     <t xml:space="preserve">5.24756383895874</t>
   </si>
   <si>
-    <t xml:space="preserve">5.25053739547729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.26242923736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.1494517326355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.16431760787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.21485948562622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.35162401199341</t>
+    <t xml:space="preserve">5.25053787231445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.26242971420288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14945125579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.16431665420532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.21485996246338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.35162448883057</t>
   </si>
   <si>
     <t xml:space="preserve">5.44081687927246</t>
   </si>
   <si>
-    <t xml:space="preserve">5.64893627166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.67866706848145</t>
+    <t xml:space="preserve">5.64893674850464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.6786675453186</t>
   </si>
   <si>
     <t xml:space="preserve">5.47054815292358</t>
   </si>
   <si>
-    <t xml:space="preserve">5.46757507324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.55974197387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.59541988372803</t>
+    <t xml:space="preserve">5.46757555007935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.55974245071411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.59541940689087</t>
   </si>
   <si>
     <t xml:space="preserve">5.58947420120239</t>
@@ -1049,22 +1049,22 @@
     <t xml:space="preserve">5.50325298309326</t>
   </si>
   <si>
-    <t xml:space="preserve">5.57758188247681</t>
+    <t xml:space="preserve">5.57758140563965</t>
   </si>
   <si>
     <t xml:space="preserve">5.75002241134644</t>
   </si>
   <si>
-    <t xml:space="preserve">5.90165185928345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.91651725769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.20193815231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.19004535675049</t>
+    <t xml:space="preserve">5.90165138244629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.91651773452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.20193767547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.19004583358765</t>
   </si>
   <si>
     <t xml:space="preserve">6.11274385452271</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">6.15436744689941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.03544282913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.97597932815552</t>
+    <t xml:space="preserve">6.03544187545776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.97597980499268</t>
   </si>
   <si>
     <t xml:space="preserve">5.88975954055786</t>
@@ -1091,46 +1091,46 @@
     <t xml:space="preserve">6.29113101959229</t>
   </si>
   <si>
-    <t xml:space="preserve">6.34464740753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.17815256118774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39816379547119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.38627099990845</t>
+    <t xml:space="preserve">6.3446478843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.17815208435059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39816331863403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.38627147674561</t>
   </si>
   <si>
     <t xml:space="preserve">6.33275461196899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.43383979797363</t>
+    <t xml:space="preserve">6.43384075164795</t>
   </si>
   <si>
     <t xml:space="preserve">6.46951818466187</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41600227355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.40410947799683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.24356079101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.35654020309448</t>
+    <t xml:space="preserve">6.41600322723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.40410900115967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.24356174468994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.35653972625732</t>
   </si>
   <si>
     <t xml:space="preserve">6.44573402404785</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60033559799194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.58844327926636</t>
+    <t xml:space="preserve">6.6003360748291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.58844375610352</t>
   </si>
   <si>
     <t xml:space="preserve">6.71926116943359</t>
@@ -1139,10 +1139,10 @@
     <t xml:space="preserve">6.65979862213135</t>
   </si>
   <si>
-    <t xml:space="preserve">6.48141050338745</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.07111978530884</t>
+    <t xml:space="preserve">6.48141098022461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.07111930847168</t>
   </si>
   <si>
     <t xml:space="preserve">5.82732391357422</t>
@@ -1154,10 +1154,10 @@
     <t xml:space="preserve">5.80948495864868</t>
   </si>
   <si>
-    <t xml:space="preserve">5.681640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.73813009262085</t>
+    <t xml:space="preserve">5.68164014816284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.73812913894653</t>
   </si>
   <si>
     <t xml:space="preserve">5.81840419769287</t>
@@ -1166,52 +1166,52 @@
     <t xml:space="preserve">5.73218393325806</t>
   </si>
   <si>
-    <t xml:space="preserve">5.72623634338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.8570556640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.86300134658813</t>
+    <t xml:space="preserve">5.72623729705811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.85705518722534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.86300086975098</t>
   </si>
   <si>
     <t xml:space="preserve">5.9581413269043</t>
   </si>
   <si>
-    <t xml:space="preserve">5.92840957641602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.76191520690918</t>
+    <t xml:space="preserve">5.92841005325317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.76191473007202</t>
   </si>
   <si>
     <t xml:space="preserve">5.70839834213257</t>
   </si>
   <si>
-    <t xml:space="preserve">5.79759216308594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.75596809387207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.6846137046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.69650650024414</t>
+    <t xml:space="preserve">5.7975926399231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.75596904754639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.68461418151855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.69650602340698</t>
   </si>
   <si>
     <t xml:space="preserve">5.66082859039307</t>
   </si>
   <si>
-    <t xml:space="preserve">5.50622701644897</t>
+    <t xml:space="preserve">5.50622653961182</t>
   </si>
   <si>
     <t xml:space="preserve">5.45865631103516</t>
   </si>
   <si>
-    <t xml:space="preserve">5.33973073959351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.15539741516113</t>
+    <t xml:space="preserve">5.33973121643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.15539693832397</t>
   </si>
   <si>
     <t xml:space="preserve">5.3100004196167</t>
@@ -1226,10 +1226,10 @@
     <t xml:space="preserve">5.00079536437988</t>
   </si>
   <si>
-    <t xml:space="preserve">4.86997747421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.85213899612427</t>
+    <t xml:space="preserve">4.86997699737549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.85213851928711</t>
   </si>
   <si>
     <t xml:space="preserve">5.14350509643555</t>
@@ -1241,22 +1241,22 @@
     <t xml:space="preserve">4.7944598197937</t>
   </si>
   <si>
-    <t xml:space="preserve">4.70823955535889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58812570571899</t>
+    <t xml:space="preserve">4.70823907852173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58812522888184</t>
   </si>
   <si>
     <t xml:space="preserve">4.47752571105957</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46860599517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53104114532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66483211517334</t>
+    <t xml:space="preserve">4.46860647201538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53104162216187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66483163833618</t>
   </si>
   <si>
     <t xml:space="preserve">4.66839933395386</t>
@@ -1265,16 +1265,16 @@
     <t xml:space="preserve">4.55482625961304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.49774217605591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51260757446289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41211652755737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36811399459839</t>
+    <t xml:space="preserve">4.49774265289307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51260805130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41211605072021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36811351776123</t>
   </si>
   <si>
     <t xml:space="preserve">4.29913759231567</t>
@@ -1283,22 +1283,22 @@
     <t xml:space="preserve">4.48525524139404</t>
   </si>
   <si>
-    <t xml:space="preserve">4.46503829956055</t>
+    <t xml:space="preserve">4.46503782272339</t>
   </si>
   <si>
     <t xml:space="preserve">4.4418478012085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29378604888916</t>
+    <t xml:space="preserve">4.29378652572632</t>
   </si>
   <si>
     <t xml:space="preserve">4.19210577011108</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57336091995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65459394454956</t>
+    <t xml:space="preserve">4.57335996627808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65459442138672</t>
   </si>
   <si>
     <t xml:space="preserve">5.10297536849976</t>
@@ -1310,25 +1310,25 @@
     <t xml:space="preserve">4.95713949203491</t>
   </si>
   <si>
-    <t xml:space="preserve">5.14391136169434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.34731388092041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.28271150588989</t>
+    <t xml:space="preserve">5.14391183853149</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.34731435775757</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.28271102905273</t>
   </si>
   <si>
     <t xml:space="preserve">5.17781209945679</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01278734207153</t>
+    <t xml:space="preserve">5.01278686523438</t>
   </si>
   <si>
     <t xml:space="preserve">4.96993207931519</t>
   </si>
   <si>
-    <t xml:space="preserve">5.05244398117065</t>
+    <t xml:space="preserve">5.05244445800781</t>
   </si>
   <si>
     <t xml:space="preserve">4.9891209602356</t>
@@ -1340,13 +1340,13 @@
     <t xml:space="preserve">5.03197622299194</t>
   </si>
   <si>
-    <t xml:space="preserve">5.01598501205444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.02621936798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.0147066116333</t>
+    <t xml:space="preserve">5.0159854888916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.0262188911438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.01470613479614</t>
   </si>
   <si>
     <t xml:space="preserve">5.08506536483765</t>
@@ -1358,7 +1358,7 @@
     <t xml:space="preserve">4.92579793930054</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96545505523682</t>
+    <t xml:space="preserve">4.9654541015625</t>
   </si>
   <si>
     <t xml:space="preserve">5.02557992935181</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">5.04029130935669</t>
   </si>
   <si>
-    <t xml:space="preserve">5.02110242843628</t>
+    <t xml:space="preserve">5.02110290527344</t>
   </si>
   <si>
     <t xml:space="preserve">5.11704730987549</t>
@@ -1376,22 +1376,22 @@
     <t xml:space="preserve">5.0594801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">5.06971454620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.24497270584106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.14135313034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.97888708114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.7646107673645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.83496999740601</t>
+    <t xml:space="preserve">5.06971406936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.24497318267822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.14135265350342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97888660430908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76461029052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.83496952056885</t>
   </si>
   <si>
     <t xml:space="preserve">4.78124046325684</t>
@@ -1406,19 +1406,19 @@
     <t xml:space="preserve">4.66290903091431</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55097341537476</t>
+    <t xml:space="preserve">4.5509729385376</t>
   </si>
   <si>
     <t xml:space="preserve">4.32710313796997</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5740008354187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65267467498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63092708587646</t>
+    <t xml:space="preserve">4.57400035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65267515182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63092756271362</t>
   </si>
   <si>
     <t xml:space="preserve">4.72943115234375</t>
@@ -1430,7 +1430,7 @@
     <t xml:space="preserve">4.79403352737427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68401670455933</t>
+    <t xml:space="preserve">4.68401718139648</t>
   </si>
   <si>
     <t xml:space="preserve">4.58679294586182</t>
@@ -1442,7 +1442,7 @@
     <t xml:space="preserve">4.99108505249023</t>
   </si>
   <si>
-    <t xml:space="preserve">4.88932466506958</t>
+    <t xml:space="preserve">4.88932514190674</t>
   </si>
   <si>
     <t xml:space="preserve">4.9842095375061</t>
@@ -1454,28 +1454,28 @@
     <t xml:space="preserve">4.79375219345093</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79512786865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76074886322021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.74630975723267</t>
+    <t xml:space="preserve">4.79512739181519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76074838638306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.74631023406982</t>
   </si>
   <si>
     <t xml:space="preserve">4.86113405227661</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79031467437744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.81300401687622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.72705745697021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.77174949645996</t>
+    <t xml:space="preserve">4.79031419754028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.81300449371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.72705793380737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.77174997329712</t>
   </si>
   <si>
     <t xml:space="preserve">4.73187065124512</t>
@@ -1484,19 +1484,19 @@
     <t xml:space="preserve">4.84532022476196</t>
   </si>
   <si>
-    <t xml:space="preserve">4.7868766784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.76968669891357</t>
+    <t xml:space="preserve">4.78687620162964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.76968717575073</t>
   </si>
   <si>
     <t xml:space="preserve">4.91614007949829</t>
   </si>
   <si>
-    <t xml:space="preserve">4.97802114486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.96770715713501</t>
+    <t xml:space="preserve">4.9780216217041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.96770763397217</t>
   </si>
   <si>
     <t xml:space="preserve">4.82675504684448</t>
@@ -1511,22 +1511,22 @@
     <t xml:space="preserve">4.89963817596436</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93470430374146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99177312850952</t>
+    <t xml:space="preserve">4.93470478057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99177265167236</t>
   </si>
   <si>
     <t xml:space="preserve">5.0543417930603</t>
   </si>
   <si>
-    <t xml:space="preserve">4.96152019500732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.9793963432312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.99246025085449</t>
+    <t xml:space="preserve">4.96151971817017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.97939682006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.99246072769165</t>
   </si>
   <si>
     <t xml:space="preserve">4.8583836555481</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">4.98489713668823</t>
   </si>
   <si>
-    <t xml:space="preserve">4.85219621658325</t>
+    <t xml:space="preserve">4.85219573974609</t>
   </si>
   <si>
     <t xml:space="preserve">4.903076171875</t>
@@ -1544,46 +1544,46 @@
     <t xml:space="preserve">4.97183322906494</t>
   </si>
   <si>
-    <t xml:space="preserve">4.93882942199707</t>
+    <t xml:space="preserve">4.93883037567139</t>
   </si>
   <si>
     <t xml:space="preserve">4.91682767868042</t>
   </si>
   <si>
-    <t xml:space="preserve">4.83363151550293</t>
+    <t xml:space="preserve">4.83363103866577</t>
   </si>
   <si>
     <t xml:space="preserve">4.76556205749512</t>
   </si>
   <si>
-    <t xml:space="preserve">4.75868606567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75043535232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67067670822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58129215240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54278802871704</t>
+    <t xml:space="preserve">4.75868558883667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75043487548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67067718505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58129262924194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5427885055542</t>
   </si>
   <si>
     <t xml:space="preserve">4.4630298614502</t>
   </si>
   <si>
-    <t xml:space="preserve">4.48228168487549</t>
+    <t xml:space="preserve">4.48228216171265</t>
   </si>
   <si>
     <t xml:space="preserve">4.51941061019897</t>
   </si>
   <si>
-    <t xml:space="preserve">4.60604524612427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.59779405593872</t>
+    <t xml:space="preserve">4.60604476928711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.59779357910156</t>
   </si>
   <si>
     <t xml:space="preserve">4.52972412109375</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">4.5379753112793</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57922983169556</t>
+    <t xml:space="preserve">4.5792293548584</t>
   </si>
   <si>
     <t xml:space="preserve">4.55172634124756</t>
@@ -1604,25 +1604,25 @@
     <t xml:space="preserve">4.55241394042969</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50634670257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51597261428833</t>
+    <t xml:space="preserve">4.50634717941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51597309112549</t>
   </si>
   <si>
     <t xml:space="preserve">4.49053287506104</t>
   </si>
   <si>
-    <t xml:space="preserve">4.52078580856323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.518723487854</t>
+    <t xml:space="preserve">4.52078533172607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51872301101685</t>
   </si>
   <si>
     <t xml:space="preserve">4.53041219711304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5104718208313</t>
+    <t xml:space="preserve">4.51047277450562</t>
   </si>
   <si>
     <t xml:space="preserve">4.52491092681885</t>
@@ -1637,10 +1637,10 @@
     <t xml:space="preserve">4.78412628173828</t>
   </si>
   <si>
-    <t xml:space="preserve">4.6651759147644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65417528152466</t>
+    <t xml:space="preserve">4.66517639160156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.6541748046875</t>
   </si>
   <si>
     <t xml:space="preserve">4.70299291610718</t>
@@ -1649,7 +1649,7 @@
     <t xml:space="preserve">4.73049545288086</t>
   </si>
   <si>
-    <t xml:space="preserve">4.71055555343628</t>
+    <t xml:space="preserve">4.71055603027344</t>
   </si>
   <si>
     <t xml:space="preserve">4.64661169052124</t>
@@ -1658,7 +1658,7 @@
     <t xml:space="preserve">4.63354778289795</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5503511428833</t>
+    <t xml:space="preserve">4.55035161972046</t>
   </si>
   <si>
     <t xml:space="preserve">4.50840950012207</t>
@@ -1667,10 +1667,10 @@
     <t xml:space="preserve">4.41558742523193</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42727661132812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40046072006226</t>
+    <t xml:space="preserve">4.42727613449097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40046119689941</t>
   </si>
   <si>
     <t xml:space="preserve">4.3323917388916</t>
@@ -1709,7 +1709,7 @@
     <t xml:space="preserve">4.10480499267578</t>
   </si>
   <si>
-    <t xml:space="preserve">4.09105348587036</t>
+    <t xml:space="preserve">4.0910530090332</t>
   </si>
   <si>
     <t xml:space="preserve">4.08830308914185</t>
@@ -1718,13 +1718,13 @@
     <t xml:space="preserve">4.13162040710449</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21962976455688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28563594818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29732513427734</t>
+    <t xml:space="preserve">4.21962928771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28563642501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2973256111145</t>
   </si>
   <si>
     <t xml:space="preserve">4.28976154327393</t>
@@ -1733,7 +1733,7 @@
     <t xml:space="preserve">4.22100448608398</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15293502807617</t>
+    <t xml:space="preserve">4.15293455123901</t>
   </si>
   <si>
     <t xml:space="preserve">4.36608219146729</t>
@@ -1745,28 +1745,28 @@
     <t xml:space="preserve">4.22513008117676</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19487714767456</t>
+    <t xml:space="preserve">4.1948766708374</t>
   </si>
   <si>
     <t xml:space="preserve">4.12749481201172</t>
   </si>
   <si>
-    <t xml:space="preserve">4.15224742889404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13505840301514</t>
+    <t xml:space="preserve">4.15224695205688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13505792617798</t>
   </si>
   <si>
     <t xml:space="preserve">4.09174108505249</t>
   </si>
   <si>
-    <t xml:space="preserve">4.03260946273804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03467273712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05461168289185</t>
+    <t xml:space="preserve">4.0326099395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03467226028442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.054612159729</t>
   </si>
   <si>
     <t xml:space="preserve">4.14537191390991</t>
@@ -1775,7 +1775,7 @@
     <t xml:space="preserve">4.2237548828125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.23544311523438</t>
+    <t xml:space="preserve">4.23544359207153</t>
   </si>
   <si>
     <t xml:space="preserve">4.19900226593018</t>
@@ -1784,7 +1784,7 @@
     <t xml:space="preserve">4.1886887550354</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11374378204346</t>
+    <t xml:space="preserve">4.1137433052063</t>
   </si>
   <si>
     <t xml:space="preserve">4.04429864883423</t>
@@ -1793,7 +1793,7 @@
     <t xml:space="preserve">4.02917194366455</t>
   </si>
   <si>
-    <t xml:space="preserve">3.99273085594177</t>
+    <t xml:space="preserve">3.99273061752319</t>
   </si>
   <si>
     <t xml:space="preserve">3.99891901016235</t>
@@ -1802,28 +1802,28 @@
     <t xml:space="preserve">3.96316480636597</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88684415817261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98241710662842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.90540885925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87378120422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78164625167847</t>
+    <t xml:space="preserve">3.88684439659119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98241686820984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.90540909767151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8737804889679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78164601325989</t>
   </si>
   <si>
     <t xml:space="preserve">3.71013855934143</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69501185417175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7335159778595</t>
+    <t xml:space="preserve">3.69501256942749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73351573944092</t>
   </si>
   <si>
     <t xml:space="preserve">3.72870302200317</t>
@@ -1838,28 +1838,28 @@
     <t xml:space="preserve">3.83115148544312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8999080657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9934184551239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97829174995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06286287307739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.048424243927</t>
+    <t xml:space="preserve">3.89990854263306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99341821670532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97829127311707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06286334991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04842376708984</t>
   </si>
   <si>
     <t xml:space="preserve">4.06767559051514</t>
   </si>
   <si>
-    <t xml:space="preserve">4.04292345046997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99548125267029</t>
+    <t xml:space="preserve">4.04292392730713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99548101425171</t>
   </si>
   <si>
     <t xml:space="preserve">3.95491409301758</t>
@@ -1868,7 +1868,7 @@
     <t xml:space="preserve">4.04086065292358</t>
   </si>
   <si>
-    <t xml:space="preserve">4.02160835266113</t>
+    <t xml:space="preserve">4.02160882949829</t>
   </si>
   <si>
     <t xml:space="preserve">4.05804967880249</t>
@@ -1877,82 +1877,82 @@
     <t xml:space="preserve">4.01335763931274</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97004055976868</t>
+    <t xml:space="preserve">3.97004103660583</t>
   </si>
   <si>
     <t xml:space="preserve">4.07180118560791</t>
   </si>
   <si>
-    <t xml:space="preserve">4.11786842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22788000106812</t>
+    <t xml:space="preserve">4.11786890029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22788095474243</t>
   </si>
   <si>
     <t xml:space="preserve">4.31863975524902</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2890739440918</t>
+    <t xml:space="preserve">4.28907442092896</t>
   </si>
   <si>
     <t xml:space="preserve">4.29044914245605</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25057077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24919509887695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.2698221206665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26294612884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.24231958389282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.13643360137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05392408370972</t>
+    <t xml:space="preserve">4.25057029724121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24919462203979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26982259750366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26294660568237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.24232006072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13643312454224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05392456054688</t>
   </si>
   <si>
     <t xml:space="preserve">4.12543201446533</t>
   </si>
   <si>
-    <t xml:space="preserve">4.0896782875061</t>
+    <t xml:space="preserve">4.08967781066895</t>
   </si>
   <si>
     <t xml:space="preserve">4.13230800628662</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17149925231934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23819398880005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22169256210327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21894216537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21481704711914</t>
+    <t xml:space="preserve">4.17149972915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23819446563721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22169160842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2189416885376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21481657028198</t>
   </si>
   <si>
     <t xml:space="preserve">4.16324853897095</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28494834899902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34476757049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25400829315186</t>
+    <t xml:space="preserve">4.28494882583618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34476709365845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2540078163147</t>
   </si>
   <si>
     <t xml:space="preserve">4.33720445632935</t>
@@ -1961,7 +1961,7 @@
     <t xml:space="preserve">4.37433338165283</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50359678268433</t>
+    <t xml:space="preserve">4.50359725952148</t>
   </si>
   <si>
     <t xml:space="preserve">4.57441663742065</t>
@@ -1973,16 +1973,16 @@
     <t xml:space="preserve">4.44171524047852</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44859027862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.55653953552246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.5778546333313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60948324203491</t>
+    <t xml:space="preserve">4.44859075546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.5565390586853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57785415649414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60948276519775</t>
   </si>
   <si>
     <t xml:space="preserve">4.66173839569092</t>
@@ -1997,43 +1997,43 @@
     <t xml:space="preserve">4.57166624069214</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5077223777771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45752906799316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41971302032471</t>
+    <t xml:space="preserve">4.50772285461426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45752859115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41971254348755</t>
   </si>
   <si>
     <t xml:space="preserve">4.46234273910522</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42796421051025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54485082626343</t>
+    <t xml:space="preserve">4.4279637336731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54485177993774</t>
   </si>
   <si>
     <t xml:space="preserve">4.52422332763672</t>
   </si>
   <si>
-    <t xml:space="preserve">4.55860233306885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.58610534667969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45546627044678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48296976089478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53109931945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56547784805298</t>
+    <t xml:space="preserve">4.55860280990601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.58610486984253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45546674728394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48296928405762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53109979629517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56547832489014</t>
   </si>
   <si>
     <t xml:space="preserve">4.59985685348511</t>
@@ -2042,25 +2042,25 @@
     <t xml:space="preserve">4.64111089706421</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61360883712769</t>
+    <t xml:space="preserve">4.61360836029053</t>
   </si>
   <si>
     <t xml:space="preserve">4.62048387527466</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62736034393311</t>
+    <t xml:space="preserve">4.62735939025879</t>
   </si>
   <si>
     <t xml:space="preserve">4.71674394607544</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65486288070679</t>
+    <t xml:space="preserve">4.65486240386963</t>
   </si>
   <si>
     <t xml:space="preserve">4.49672079086304</t>
   </si>
   <si>
-    <t xml:space="preserve">4.5522894859314</t>
+    <t xml:space="preserve">4.55228900909424</t>
   </si>
   <si>
     <t xml:space="preserve">4.6117959022522</t>
@@ -2072,22 +2072,22 @@
     <t xml:space="preserve">4.60435819625854</t>
   </si>
   <si>
-    <t xml:space="preserve">4.62667322158813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.6936182975769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.73824834823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.71593379974365</t>
+    <t xml:space="preserve">4.62667274475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69361877441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.73824882507324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.71593332290649</t>
   </si>
   <si>
     <t xml:space="preserve">4.63411140441895</t>
   </si>
   <si>
-    <t xml:space="preserve">4.65642690658569</t>
+    <t xml:space="preserve">4.65642642974854</t>
   </si>
   <si>
     <t xml:space="preserve">4.58948135375977</t>
@@ -2096,10 +2096,10 @@
     <t xml:space="preserve">4.51509761810303</t>
   </si>
   <si>
-    <t xml:space="preserve">4.57460403442383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56716632843018</t>
+    <t xml:space="preserve">4.57460451126099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56716537475586</t>
   </si>
   <si>
     <t xml:space="preserve">4.55972814559937</t>
@@ -2108,7 +2108,7 @@
     <t xml:space="preserve">4.64898824691772</t>
   </si>
   <si>
-    <t xml:space="preserve">4.64154958724976</t>
+    <t xml:space="preserve">4.6415491104126</t>
   </si>
   <si>
     <t xml:space="preserve">4.58204221725464</t>
@@ -2117,19 +2117,19 @@
     <t xml:space="preserve">4.52997398376465</t>
   </si>
   <si>
-    <t xml:space="preserve">4.44815158843994</t>
+    <t xml:space="preserve">4.4481520652771</t>
   </si>
   <si>
     <t xml:space="preserve">4.38120651245117</t>
   </si>
   <si>
-    <t xml:space="preserve">4.42583703994751</t>
+    <t xml:space="preserve">4.42583656311035</t>
   </si>
   <si>
     <t xml:space="preserve">4.37376832962036</t>
   </si>
   <si>
-    <t xml:space="preserve">4.41839838027954</t>
+    <t xml:space="preserve">4.4183988571167</t>
   </si>
   <si>
     <t xml:space="preserve">4.35889148712158</t>
@@ -2138,7 +2138,7 @@
     <t xml:space="preserve">4.32913780212402</t>
   </si>
   <si>
-    <t xml:space="preserve">4.32169961929321</t>
+    <t xml:space="preserve">4.32169914245605</t>
   </si>
   <si>
     <t xml:space="preserve">4.3142614364624</t>
@@ -2150,7 +2150,7 @@
     <t xml:space="preserve">4.59691953659058</t>
   </si>
   <si>
-    <t xml:space="preserve">4.50765895843506</t>
+    <t xml:space="preserve">4.5076584815979</t>
   </si>
   <si>
     <t xml:space="preserve">4.49278211593628</t>
@@ -2162,16 +2162,16 @@
     <t xml:space="preserve">4.43327522277832</t>
   </si>
   <si>
-    <t xml:space="preserve">4.40352201461792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38864517211914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39608335494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35145282745361</t>
+    <t xml:space="preserve">4.40352153778076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38864469528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39608287811279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35145330429077</t>
   </si>
   <si>
     <t xml:space="preserve">4.24731588363647</t>
@@ -2180,16 +2180,16 @@
     <t xml:space="preserve">4.20268535614014</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19524717330933</t>
+    <t xml:space="preserve">4.19524669647217</t>
   </si>
   <si>
     <t xml:space="preserve">4.10598659515381</t>
   </si>
   <si>
-    <t xml:space="preserve">4.13574028015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01672601699829</t>
+    <t xml:space="preserve">4.13573980331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01672554016113</t>
   </si>
   <si>
     <t xml:space="preserve">4.0241641998291</t>
@@ -2201,49 +2201,49 @@
     <t xml:space="preserve">3.9051501750946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95721912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.89771151542664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98697257041931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9200267791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94234204292297</t>
+    <t xml:space="preserve">3.95721888542175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89771199226379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98697233200073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92002701759338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94234180450439</t>
   </si>
   <si>
     <t xml:space="preserve">3.97953391075134</t>
   </si>
   <si>
-    <t xml:space="preserve">3.97209596633911</t>
+    <t xml:space="preserve">3.97209525108337</t>
   </si>
   <si>
     <t xml:space="preserve">4.04647922515869</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06879472732544</t>
+    <t xml:space="preserve">4.06879425048828</t>
   </si>
   <si>
     <t xml:space="preserve">4.098548412323</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16549301147461</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18780899047852</t>
+    <t xml:space="preserve">4.16549348831177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18780851364136</t>
   </si>
   <si>
     <t xml:space="preserve">4.18036985397339</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17293167114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11342525482178</t>
+    <t xml:space="preserve">4.17293214797974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11342477798462</t>
   </si>
   <si>
     <t xml:space="preserve">4.14317798614502</t>
@@ -2264,28 +2264,28 @@
     <t xml:space="preserve">4.23987722396851</t>
   </si>
   <si>
-    <t xml:space="preserve">4.26963090896606</t>
+    <t xml:space="preserve">4.26963043212891</t>
   </si>
   <si>
     <t xml:space="preserve">4.30682277679443</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2919454574585</t>
+    <t xml:space="preserve">4.29194593429565</t>
   </si>
   <si>
     <t xml:space="preserve">4.2621922492981</t>
   </si>
   <si>
-    <t xml:space="preserve">4.27706956863403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29938411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28450727462769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41095972061157</t>
+    <t xml:space="preserve">4.27706909179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29938459396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28450775146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41096019744873</t>
   </si>
   <si>
     <t xml:space="preserve">4.44071340560913</t>
@@ -2297,7 +2297,7 @@
     <t xml:space="preserve">4.47046709060669</t>
   </si>
   <si>
-    <t xml:space="preserve">4.45558977127075</t>
+    <t xml:space="preserve">4.45559024810791</t>
   </si>
   <si>
     <t xml:space="preserve">4.6638650894165</t>
@@ -2306,7 +2306,7 @@
     <t xml:space="preserve">4.74568700790405</t>
   </si>
   <si>
-    <t xml:space="preserve">4.79031801223755</t>
+    <t xml:space="preserve">4.79031753540039</t>
   </si>
   <si>
     <t xml:space="preserve">4.70105695724487</t>
@@ -2315,46 +2315,46 @@
     <t xml:space="preserve">4.67874193191528</t>
   </si>
   <si>
-    <t xml:space="preserve">4.61923456192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.75312519073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67130374908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.70849561691284</t>
+    <t xml:space="preserve">4.61923503875732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.75312566757202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67130327224731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.70849514007568</t>
   </si>
   <si>
     <t xml:space="preserve">4.72337198257446</t>
   </si>
   <si>
-    <t xml:space="preserve">4.68618059158325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08367109298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06135559082031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96465730667114</t>
+    <t xml:space="preserve">4.68618011474609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.0836706161499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06135606765747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96465754508972</t>
   </si>
   <si>
     <t xml:space="preserve">3.92746543884277</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48116230964661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38446378707886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37702512741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71872854232788</t>
+    <t xml:space="preserve">3.48116278648376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38446354866028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37702536582947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7187283039093</t>
   </si>
   <si>
     <t xml:space="preserve">2.76335859298706</t>
@@ -2372,7 +2372,7 @@
     <t xml:space="preserve">2.64806365966797</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77451634407043</t>
+    <t xml:space="preserve">2.77451610565186</t>
   </si>
   <si>
     <t xml:space="preserve">2.70757079124451</t>
@@ -2384,34 +2384,34 @@
     <t xml:space="preserve">2.80798888206482</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83402323722839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.826584815979</t>
+    <t xml:space="preserve">2.83402299880981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82658457756042</t>
   </si>
   <si>
     <t xml:space="preserve">2.68525552749634</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78939294815063</t>
+    <t xml:space="preserve">2.78939270973206</t>
   </si>
   <si>
     <t xml:space="preserve">2.80426955223083</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75220084190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7001326084137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71500945091248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76707792282104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73732447624207</t>
+    <t xml:space="preserve">2.75220108032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70013236999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7150092124939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76707768440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73732399940491</t>
   </si>
   <si>
     <t xml:space="preserve">2.69641327857971</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">2.60343337059021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66294026374817</t>
+    <t xml:space="preserve">2.66294050216675</t>
   </si>
   <si>
     <t xml:space="preserve">2.69269394874573</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62946772575378</t>
+    <t xml:space="preserve">2.62946796417236</t>
   </si>
   <si>
     <t xml:space="preserve">2.62574863433838</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">2.65550208091736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61459112167358</t>
+    <t xml:space="preserve">2.614590883255</t>
   </si>
   <si>
     <t xml:space="preserve">2.60715270042419</t>
@@ -2447,25 +2447,25 @@
     <t xml:space="preserve">2.63318681716919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59227561950684</t>
+    <t xml:space="preserve">2.59227585792542</t>
   </si>
   <si>
     <t xml:space="preserve">2.55508399009705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45466589927673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42491245269775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.39515900611877</t>
+    <t xml:space="preserve">2.45466566085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42491221427917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3951587677002</t>
   </si>
   <si>
     <t xml:space="preserve">2.40259718894958</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46954226493835</t>
+    <t xml:space="preserve">2.46954250335693</t>
   </si>
   <si>
     <t xml:space="preserve">2.33937096595764</t>
@@ -2483,19 +2483,19 @@
     <t xml:space="preserve">2.3840012550354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41747403144836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41375494003296</t>
+    <t xml:space="preserve">2.41747379302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41375470161438</t>
   </si>
   <si>
     <t xml:space="preserve">2.43978881835938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51417303085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61087155342102</t>
+    <t xml:space="preserve">2.51417279243469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6108717918396</t>
   </si>
   <si>
     <t xml:space="preserve">2.61831021308899</t>
@@ -2504,37 +2504,37 @@
     <t xml:space="preserve">2.77823543548584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9158456325531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54392647743225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54764556884766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56624174118042</t>
+    <t xml:space="preserve">2.91584539413452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54392623901367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54764533042908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56624150276184</t>
   </si>
   <si>
     <t xml:space="preserve">2.49929594993591</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52904939651489</t>
+    <t xml:space="preserve">2.52904963493347</t>
   </si>
   <si>
     <t xml:space="preserve">2.51045346260071</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58483719825745</t>
+    <t xml:space="preserve">2.58483743667603</t>
   </si>
   <si>
     <t xml:space="preserve">2.58111810684204</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5997142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63690638542175</t>
+    <t xml:space="preserve">2.59971404075623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63690614700317</t>
   </si>
   <si>
     <t xml:space="preserve">2.68530654907227</t>
@@ -4845,6 +4845,9 @@
   </si>
   <si>
     <t xml:space="preserve">4.32000017166138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36499977111816</t>
   </si>
 </sst>
 </file>
@@ -72263,7 +72266,7 @@
     </row>
     <row r="2581">
       <c r="A2581" s="1" t="n">
-        <v>46079.6909837963</v>
+        <v>46079.3333333333</v>
       </c>
       <c r="B2581" t="n">
         <v>240678</v>
@@ -72284,6 +72287,32 @@
         <v>1610</v>
       </c>
       <c r="H2581" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2582">
+      <c r="A2582" s="1" t="n">
+        <v>46080.691099537</v>
+      </c>
+      <c r="B2582" t="n">
+        <v>627082</v>
+      </c>
+      <c r="C2582" t="n">
+        <v>4.52500009536743</v>
+      </c>
+      <c r="D2582" t="n">
+        <v>4.17000007629395</v>
+      </c>
+      <c r="E2582" t="n">
+        <v>4.34000015258789</v>
+      </c>
+      <c r="F2582" t="n">
+        <v>4.36499977111816</v>
+      </c>
+      <c r="G2582" t="s">
+        <v>1611</v>
+      </c>
+      <c r="H2582" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/IGD.MI.xlsx
+++ b/data/IGD.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1616" uniqueCount="1616">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1617" uniqueCount="1617">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">4.72976970672607</t>
+    <t xml:space="preserve">4.72976922988892</t>
   </si>
   <si>
     <t xml:space="preserve">IGD.MI</t>
@@ -50,13 +50,13 @@
     <t xml:space="preserve">4.76804447174072</t>
   </si>
   <si>
-    <t xml:space="preserve">4.76531171798706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.64775037765503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53839063644409</t>
+    <t xml:space="preserve">4.7653112411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.64774990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53839111328125</t>
   </si>
   <si>
     <t xml:space="preserve">4.56573104858398</t>
@@ -68,49 +68,49 @@
     <t xml:space="preserve">4.55206108093262</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33334302902222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16383743286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.04627752304077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60884189605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.88223814964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95605540275574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.0380744934082</t>
+    <t xml:space="preserve">4.33334350585938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16383695602417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04627704620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60884213447571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8822386264801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95605492591858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03807497024536</t>
   </si>
   <si>
     <t xml:space="preserve">3.97519326210022</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94785380363464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81388998031616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96425724029541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07088232040405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92051386833191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69632840156555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78654909133911</t>
+    <t xml:space="preserve">3.94785356521606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81388878822327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96425795555115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07088184356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92051339149475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69632863998413</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78654956817627</t>
   </si>
   <si>
     <t xml:space="preserve">3.45573902130127</t>
@@ -119,40 +119,40 @@
     <t xml:space="preserve">3.49948239326477</t>
   </si>
   <si>
-    <t xml:space="preserve">3.6908597946167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56783246994019</t>
+    <t xml:space="preserve">3.69086074829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56783175468445</t>
   </si>
   <si>
     <t xml:space="preserve">3.63891506195068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.88497233390808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755923271179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93691754341125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87130260467529</t>
+    <t xml:space="preserve">3.88497281074524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755875587463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93691730499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87130284309387</t>
   </si>
   <si>
     <t xml:space="preserve">4.05994653701782</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00800132751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95332193374634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98612952232361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9915976524353</t>
+    <t xml:space="preserve">4.00800085067749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95332217216492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98612928390503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99159789085388</t>
   </si>
   <si>
     <t xml:space="preserve">4.03260707855225</t>
@@ -167,517 +167,520 @@
     <t xml:space="preserve">4.21031427383423</t>
   </si>
   <si>
+    <t xml:space="preserve">4.37435245513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33607769012451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34701299667358</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33881139755249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42903280258179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52745580673218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51105165481567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46184062957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57119941711426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67508983612061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.60947418212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.54932737350464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48371171951294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34974718093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42083024978638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42356443405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2649941444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25405883789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22398519515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22671890258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23765468597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3306097984314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40169334411621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.31967353820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30600452423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36615180969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.26772832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.32514142990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29233455657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27046251296997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29506874084473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39895915985107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30873823165894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38802337646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.42629861831665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34427976608276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.39075756072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30326986312866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.49522352218628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57292604446411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.65062761306763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69091844558716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.67940664291382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.69379568099976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.66213989257812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.61609315872192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.57580327987671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63623809814453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63048315048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63336133956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.63911628723145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.56429243087769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35133075714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06066608428955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08368921279907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.95130753517151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97145175933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1613917350769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20168209075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.247727394104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.27650594711304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03476524353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82755899429321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84482598304749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85633707046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22470426559448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15851354598999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.01749849319458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86784887313843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83619260787964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.96281886100769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.05778884887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.09232234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25636005401611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.40313196182251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33406352996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51824712753296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41752147674561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.45493316650391</t>
+  </si>
+  <si>
     <t xml:space="preserve">4.37435293197632</t>
   </si>
   <si>
-    <t xml:space="preserve">4.33607816696167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34701299667358</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33881139755249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42903280258179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52745580673218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51105165481567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46184015274048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57119941711426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67508983612061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.60947465896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.54932737350464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.4837121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34974813461304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42083024978638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42356491088867</t>
+    <t xml:space="preserve">4.45781183242798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.53839159011841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.52975797653198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.48946762084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.51536798477173</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25923919677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38874292373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.46644401550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.38298654556274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36572027206421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.41464376449585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.35996341705322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33694124221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29377317428589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.3139181137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19016981124878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19880342483521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.22182703018188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.2621169090271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25348281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.23046016693115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14412355422974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19592571258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16714763641357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.15563535690308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11534452438354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20743608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14700222015381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17865800857544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07505559921265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94267392158508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.86497116088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79878115653992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77575707435608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83907008171082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74697875976562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74985671043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85921621322632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82468128204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79590225219727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87936067581177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81029176712036</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78439116477966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76424551010132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72971129417419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71244430541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7239556312561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84194803237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.99735355377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.06354331970215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.10959053039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.11822319030762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08656692504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.03764295578003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.00310897827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.97432994842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.91389536857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93979620933533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92540669441223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92828440666199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.89662742614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84770369529724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75273442268372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75849008560181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55703973770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64337563514709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66927671432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65776515007019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58006286621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59732961654663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6030855178833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63186454772949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6261088848114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66064262390137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61459684371948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80453586578369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.9599404335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07217645645142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.04339933395386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12685632705688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.13261270523071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12110137939453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.36859750747681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28226137161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33981895446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.34845161437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.33118534088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.30240678787231</t>
   </si>
   <si>
     <t xml:space="preserve">4.26499462127686</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25405836105347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22398471832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22671937942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23765468597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33060932159424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40169286727905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.31967353820801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30600452423096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36615180969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26772832870483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.32514142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29233407974243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27046203613281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29506778717041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39895868301392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30873823165894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38802289962769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.42629861831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.34427928924561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.39075756072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.30326986312866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.49522304534912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57292556762695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.65062856674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69091892242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.67940711975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.69379615783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.66213941574097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.61609315872192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.57580280303955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63623857498169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63048315048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63336086273193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.63911628723145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.56429243087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35133075714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06066560745239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08368825912476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.95130705833435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.97145223617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16139125823975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20168161392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.247727394104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.27650594711304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03476476669312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82755875587463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8448269367218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85633754730225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22470426559448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15851354598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.01749801635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86784934997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83619260787964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.96281814575195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.05778837203979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.09232234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25636053085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.40313196182251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3340630531311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51824617385864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41752099990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45493268966675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.37435340881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.45781135559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.53839206695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.52975845336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.48946809768677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.51536798477173</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25923919677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38874244689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.46644449234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.38298654556274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.36571979522705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.41464328765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.35996389389038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.33694124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29377269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.3139181137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19016981124878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19880390167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.22182607650757</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.26211595535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25348281860352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.23046064376831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14412355422974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19592571258545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16714715957642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.15563583374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1153450012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20743656158447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14700126647949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17865896224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07505559921265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.9426736831665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.86497163772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79878091812134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77575731277466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83907055854797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74697923660278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7498562335968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85921573638916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82468056678772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79590249061584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87936091423035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81029200553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7843918800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76424598693848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72971153259277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71244406700134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72395610809326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84194779396057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.99735355377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.06354427337646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.10959005355835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.11822366714478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08656597137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.03764295578003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.00310897827148</t>
-  </si>
-  <